--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>95375</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.25500011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.24499988555908</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.25</v>
+        <v>2.24499988555908</v>
       </c>
       <c r="E2719" t="n">
         <v>2.25500011444092</v>
@@ -62906,6 +62906,29 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>158402</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.27500009536743</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.20499992370605</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.27500009536743</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.23499989509583</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>181324</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.29500007629395</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.26500010490417</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>122799</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>106963</v>
+        <v>197304</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.29500007629395</v>
+        <v>2.28500008583069</v>
       </c>
       <c r="D2715" t="n">
         <v>2.25500011444092</v>
       </c>
       <c r="E2715" t="n">
+        <v>2.26500010490417</v>
+      </c>
+      <c r="F2715" t="n">
         <v>2.25999999046326</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>2.28500008583069</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>83538</v>
+        <v>106963</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.28999996185303</v>
+        <v>2.29500007629395</v>
       </c>
       <c r="D2716" t="n">
         <v>2.25500011444092</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.25500011444092</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.26500010490417</v>
+        <v>2.28500008583069</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,13 +62842,13 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>43019</v>
+        <v>83538</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.27999997138977</v>
+        <v>2.28999996185303</v>
       </c>
       <c r="D2717" t="n">
         <v>2.25500011444092</v>
@@ -62857,7 +62857,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.25999999046326</v>
+        <v>2.26500010490417</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>104628</v>
+        <v>43019</v>
       </c>
       <c r="C2718" t="n">
         <v>2.27999997138977</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.25</v>
+        <v>2.25500011444092</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.26999998092651</v>
+        <v>2.25500011444092</v>
       </c>
       <c r="F2718" t="n">
         <v>2.25999999046326</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>95375</v>
+        <v>104628</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.28999996185303</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.24499988555908</v>
+        <v>2.25</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.25500011444092</v>
+        <v>2.26999998092651</v>
       </c>
       <c r="F2719" t="n">
-        <v>2.24499988555908</v>
+        <v>2.25999999046326</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>158402</v>
+        <v>95375</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.27500009536743</v>
+        <v>2.28999996185303</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.20499992370605</v>
+        <v>2.24499988555908</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.27500009536743</v>
+        <v>2.25500011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.23499989509583</v>
+        <v>2.24499988555908</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>181324</v>
+        <v>158402</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.29500007629395</v>
+        <v>2.27500009536743</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.22000002861023</v>
+        <v>2.20499992370605</v>
       </c>
       <c r="E2721" t="n">
-        <v>2.26500010490417</v>
+        <v>2.27500009536743</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.27999997138977</v>
+        <v>2.23499989509583</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>122799</v>
+        <v>181324</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.29999995231628</v>
+        <v>2.29500007629395</v>
       </c>
       <c r="D2722" t="n">
         <v>2.22000002861023</v>
       </c>
       <c r="E2722" t="n">
-        <v>2.29999995231628</v>
+        <v>2.26500010490417</v>
       </c>
       <c r="F2722" t="n">
-        <v>2.23000001907349</v>
+        <v>2.27999997138977</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>145408</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.23499989509583</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8573009967804</v>
+        <v>2.85730147361755</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86872506141663</v>
+        <v>2.86872529983521</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525803565979</v>
+        <v>2.80525827407837</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G8" t="n">
-        <v>2.73290538787842</v>
+        <v>2.732905626297</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928339958191</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408214569092</v>
+        <v>2.56408190727234</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G13" t="n">
-        <v>2.546311378479</v>
+        <v>2.54631114006042</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915974617004</v>
+        <v>2.56915926933289</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138850212097</v>
+        <v>2.55138874053955</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662058830261</v>
+        <v>2.56662106513977</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696158409119</v>
+        <v>2.50696134567261</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107929229736</v>
+        <v>2.53107905387878</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349408149719</v>
+        <v>2.44349384307861</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482580184937</v>
+        <v>2.28482556343079</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.13885045051575</v>
+        <v>2.13885068893433</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36098623275757</v>
+        <v>2.36098670959473</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798361778259</v>
+        <v>2.32798337936401</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928339958191</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G42" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66055250167847</v>
+        <v>2.66055274009705</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>2.6338963508606</v>
+        <v>2.63389611244202</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G47" t="n">
-        <v>2.68086194992065</v>
+        <v>2.68086171150208</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G51" t="n">
-        <v>2.7392520904541</v>
+        <v>2.73925185203552</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84333872795105</v>
+        <v>2.84333848953247</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172863006592</v>
+        <v>2.90172839164734</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853998184204</v>
+        <v>2.93853974342346</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>2.94869446754456</v>
+        <v>2.94869422912598</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835394859314</v>
+        <v>3.00835371017456</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423600196838</v>
+        <v>2.98423624038696</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566006660461</v>
+        <v>2.99566030502319</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327658653259</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200724601746</v>
+        <v>3.00200700759888</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711544036865</v>
+        <v>2.92711520195007</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819874763489</v>
+        <v>2.99819850921631</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.04643392562866</v>
+        <v>3.04643416404724</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702246665955</v>
+        <v>3.16702151298523</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702246665955</v>
+        <v>3.16702151298523</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798188209534</v>
+        <v>3.1479823589325</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.098477602005</v>
+        <v>3.09847736358643</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244010925293</v>
+        <v>3.11244058609009</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086155891418</v>
+        <v>3.09086108207703</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959221839905</v>
+        <v>3.08959245681763</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374075889587</v>
+        <v>3.03374099731445</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327658653259</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04643392562866</v>
+        <v>3.04643416404724</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424492835999</v>
+        <v>2.87424468994141</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92722606658936</v>
+        <v>2.92722582817078</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.11266136169434</v>
+        <v>3.11266088485718</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941530227661</v>
+        <v>3.09941554069519</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577436447144</v>
+        <v>3.14577484130859</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140504837036</v>
+        <v>3.20140480995178</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>3.1921329498291</v>
+        <v>3.19213318824768</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584318161011</v>
+        <v>3.23584342002869</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.2318696975708</v>
+        <v>3.23186922073364</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802760124207</v>
+        <v>3.20802783966064</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829133033752</v>
+        <v>3.16829180717468</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.159019947052</v>
+        <v>3.15901947021484</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516821861267</v>
+        <v>2.73516798019409</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.86762142181396</v>
+        <v>2.86762189865112</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91133165359497</v>
+        <v>2.91133141517639</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060351371765</v>
+        <v>2.92060327529907</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841380119324</v>
+        <v>2.74841356277466</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907841682434</v>
+        <v>2.84907793998718</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047093391418</v>
+        <v>2.94047141075134</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708867073059</v>
+        <v>2.74708890914917</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152656555176</v>
+        <v>2.78152680397034</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>2.90073537826538</v>
+        <v>2.9007351398468</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709420204163</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802278518677</v>
+        <v>3.00802254676819</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.91530537605286</v>
+        <v>2.9153048992157</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397566795349</v>
+        <v>2.71397590637207</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364336013794</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="n">
-        <v>2.67291450500488</v>
+        <v>2.67291498184204</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60138988494873</v>
+        <v>2.60139012336731</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.5417857170105</v>
+        <v>2.54178547859192</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152222633362</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73384356498718</v>
+        <v>2.73384308815002</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364336013794</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="n">
-        <v>2.66496801376343</v>
+        <v>2.66496777534485</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702056884766</v>
+        <v>2.65702033042908</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.66231846809387</v>
+        <v>2.66231870651245</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="n">
-        <v>2.56562733650208</v>
+        <v>2.56562757492065</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907336235046</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801267623901</v>
+        <v>2.60801243782043</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754850387573</v>
+        <v>2.57754826545715</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>2.58284664154053</v>
+        <v>2.58284640312195</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>2.58284664154053</v>
+        <v>2.58284640312195</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.58284664154053</v>
+        <v>2.58284640312195</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675130844116</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979668617249</v>
+        <v>2.43979644775391</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.41198110580444</v>
+        <v>2.4119815826416</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="n">
-        <v>2.46893620491028</v>
+        <v>2.4689359664917</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761155128479</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="n">
-        <v>2.27290487289429</v>
+        <v>2.27290511131287</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="n">
-        <v>2.24641394615173</v>
+        <v>2.24641418457031</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.28615021705627</v>
+        <v>2.28615045547485</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="n">
-        <v>2.43449831008911</v>
+        <v>2.43449854850769</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36959624290466</v>
+        <v>2.36959600448608</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741110801697</v>
+        <v>2.39741086959839</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211320877075</v>
+        <v>2.39211297035217</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.50337433815002</v>
+        <v>2.50337409973145</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>2.44376993179321</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503106117249</v>
+        <v>2.55503082275391</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.58284664154053</v>
+        <v>2.58284640312195</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152222633362</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="n">
-        <v>2.48483061790466</v>
+        <v>2.48483085632324</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496248245239</v>
+        <v>2.46496272087097</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48085713386536</v>
+        <v>2.48085737228394</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026109695435</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416600227356</v>
+        <v>2.38416576385498</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098394393921</v>
+        <v>2.26098370552063</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495766639709</v>
+        <v>2.26495790481567</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>2.22522163391113</v>
+        <v>2.22522139549255</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="n">
-        <v>2.22389721870422</v>
+        <v>2.22389698028564</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548536300659</v>
+        <v>2.18548560142517</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237693786621</v>
+        <v>2.35237717628479</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="n">
-        <v>2.41198110580444</v>
+        <v>2.4119815826416</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="n">
-        <v>2.44906806945801</v>
+        <v>2.44906830787659</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46893620491028</v>
+        <v>2.4689359664917</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026109695435</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="n">
-        <v>2.49145317077637</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026109695435</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204968452454</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675130844116</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5325140953064</v>
+        <v>2.53251385688782</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="n">
-        <v>2.48483061790466</v>
+        <v>2.48483085632324</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675130844116</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204968452454</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.50337433815002</v>
+        <v>2.50337409973145</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960129737854</v>
+        <v>2.56960153579712</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059292793274</v>
+        <v>2.52059316635132</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072550773621</v>
+        <v>2.50072526931763</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363806724548</v>
+        <v>2.46363854408264</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.44376993179321</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138483047485</v>
+        <v>2.40138506889343</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356972694397</v>
+        <v>2.37356996536255</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019251823425</v>
+        <v>2.38019227981567</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.36562252044678</v>
+        <v>2.36562204360962</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985997200012</v>
+        <v>2.32985973358154</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476227760315</v>
+        <v>2.39476203918457</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006041526794</v>
+        <v>2.40006065368652</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886786460876</v>
+        <v>2.37886762619019</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35767507553101</v>
+        <v>2.35767531394958</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.36429786682129</v>
+        <v>2.36429762840271</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807620048523</v>
+        <v>2.49807596206665</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="n">
-        <v>2.50469899177551</v>
+        <v>2.50469875335693</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761155128479</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49145317077637</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>2.56297850608826</v>
+        <v>2.56297826766968</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622385025024</v>
+        <v>2.57622361183167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60006546974182</v>
+        <v>2.6000657081604</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211826324463</v>
+        <v>2.59211802482605</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.70073008537292</v>
+        <v>2.70073056221008</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.82126307487488</v>
+        <v>2.8212628364563</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642910957336</v>
+        <v>2.84642958641052</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252372741699</v>
+        <v>2.93252420425415</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.06497764587402</v>
+        <v>3.06497716903687</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709420204163</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907841682434</v>
+        <v>2.84907793998718</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="n">
-        <v>2.86099934577942</v>
+        <v>2.86099910736084</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444489479065</v>
+        <v>2.94444537162781</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.99477696418762</v>
+        <v>2.9947772026062</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="n">
-        <v>3.04510951042175</v>
+        <v>3.04510974884033</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848695755005</v>
+        <v>3.03848719596863</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504093170166</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093558311462</v>
+        <v>2.97093605995178</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>2.92722606658936</v>
+        <v>2.92722582817078</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G335" t="n">
-        <v>2.88219165802002</v>
+        <v>2.8821918964386</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97226023674011</v>
+        <v>2.97225999832153</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="n">
-        <v>3.09146881103516</v>
+        <v>3.09146809577942</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484578132629</v>
+        <v>3.08484601974487</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10471415519714</v>
+        <v>3.1047146320343</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637063980103</v>
+        <v>3.1563708782196</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>2.84775400161743</v>
+        <v>2.84775376319885</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887811660767</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772770881653</v>
+        <v>2.91772747039795</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093518257141</v>
+        <v>2.89093494415283</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644323348999</v>
+        <v>2.78644299507141</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="n">
-        <v>2.79448103904724</v>
+        <v>2.79448127746582</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.76768827438354</v>
+        <v>2.76768851280212</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="n">
-        <v>2.64846086502075</v>
+        <v>2.64846062660217</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="n">
-        <v>2.72080087661743</v>
+        <v>2.72080111503601</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.656498670578</v>
+        <v>2.65649890899658</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>2.64846086502075</v>
+        <v>2.64846062660217</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568712234497</v>
+        <v>2.62568688392639</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621524810791</v>
+        <v>2.59621500968933</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="n">
-        <v>2.53727126121521</v>
+        <v>2.53727102279663</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>2.56540298461914</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G399" t="n">
-        <v>2.60693192481995</v>
+        <v>2.60693216323853</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.6310453414917</v>
+        <v>2.63104557991028</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095118522644</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G409" t="n">
-        <v>2.67391443252563</v>
+        <v>2.67391395568848</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338535308838</v>
+        <v>2.70338582992554</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.56138443946838</v>
+        <v>2.5613842010498</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459191322327</v>
+        <v>2.53459167480469</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172377586365</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="n">
-        <v>2.59755492210388</v>
+        <v>2.5975546836853</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157370567322</v>
+        <v>2.60157346725464</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200719833374</v>
+        <v>2.55200695991516</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095118522644</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.71678256988525</v>
+        <v>2.7167820930481</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323599815369</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.8534255027771</v>
+        <v>2.85342502593994</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="n">
-        <v>2.90165209770203</v>
+        <v>2.90165185928345</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>2.91504859924316</v>
+        <v>2.91504883766174</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>2.88021802902222</v>
+        <v>2.88021779060364</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>2.86012363433838</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682152748108</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323599815369</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="n">
-        <v>2.8574435710907</v>
+        <v>2.85744404792786</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682152748108</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>2.79448103904724</v>
+        <v>2.79448127746582</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868932723999</v>
+        <v>2.83868885040283</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887811660767</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567064285278</v>
+        <v>2.90567111968994</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>2.86012363433838</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86012363433838</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710542678833</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916201591492</v>
+        <v>2.93916177749634</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710542678833</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>2.92576551437378</v>
+        <v>2.92576575279236</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88155746459961</v>
+        <v>2.88155722618103</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370844841003</v>
+        <v>2.91370892524719</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.93246364593506</v>
+        <v>2.93246340751648</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>2.90834999084473</v>
+        <v>2.90835022926331</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G474" t="n">
-        <v>2.89629340171814</v>
+        <v>2.89629316329956</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.88557696342468</v>
+        <v>2.8855767250061</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>2.88021802902222</v>
+        <v>2.88021779060364</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314136505127</v>
+        <v>2.79314160346985</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.5881769657135</v>
+        <v>2.58817744255066</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300729751587</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.66587615013123</v>
+        <v>2.66587591171265</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266867637634</v>
+        <v>2.69266891479492</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927265167236</v>
+        <v>2.67927241325378</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="n">
-        <v>2.64980030059814</v>
+        <v>2.64980053901672</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62970590591431</v>
+        <v>2.62970614433289</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300729751587</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.56138443946838</v>
+        <v>2.5613842010498</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51315760612488</v>
+        <v>2.51315784454346</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057312965393</v>
+        <v>2.53057289123535</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449704170227</v>
+        <v>2.51449728012085</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119541168213</v>
+        <v>2.52119517326355</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.50846910476685</v>
+        <v>2.50846862792969</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>2.54195976257324</v>
+        <v>2.54196000099182</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5386106967926</v>
+        <v>2.53861045837402</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59554529190063</v>
+        <v>2.59554505348206</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578127861023</v>
+        <v>2.64578175544739</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56540298461914</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172377586365</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.54865765571594</v>
+        <v>2.5486581325531</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148731231689</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827960014343</v>
+        <v>2.46827983856201</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.4046471118927</v>
+        <v>2.40464687347412</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G548" t="n">
-        <v>2.39125061035156</v>
+        <v>2.39125037193298</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>2.39794898033142</v>
+        <v>2.39794874191284</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G550" t="n">
-        <v>2.377854347229</v>
+        <v>2.37785410881042</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="n">
-        <v>2.38120365142822</v>
+        <v>2.38120341300964</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>2.26398515701294</v>
+        <v>2.26398539543152</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695592880249</v>
+        <v>2.18695616722107</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="n">
-        <v>2.34436321258545</v>
+        <v>2.34436368942261</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.25058913230896</v>
+        <v>2.2505886554718</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483590126038</v>
+        <v>2.44483613967896</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804313659668</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148731231689</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.42474150657654</v>
+        <v>2.42474126815796</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804313659668</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804313659668</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172377586365</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="n">
-        <v>2.50177073478699</v>
+        <v>2.50177049636841</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="n">
-        <v>2.48837399482727</v>
+        <v>2.48837423324585</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.31998920440674</v>
+        <v>2.31998944282532</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310486793518</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393630981445</v>
+        <v>2.23393654823303</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>2.26491522789001</v>
+        <v>2.26491546630859</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.22361016273499</v>
+        <v>2.22360992431641</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295763015747</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494570732117</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>2.22016763687134</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295763015747</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>2.22016763687134</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>2.35441112518311</v>
+        <v>2.35441088676453</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.34752631187439</v>
+        <v>2.34752655029297</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915823936462</v>
+        <v>2.39915800094604</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473679542542</v>
+        <v>2.36473703384399</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310486793518</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27524185180664</v>
+        <v>2.27524209022522</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30277895927429</v>
+        <v>2.30277872085571</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.30622053146362</v>
+        <v>2.3062207698822</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.31998920440674</v>
+        <v>2.31998944282532</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082088470459</v>
+        <v>2.24082064628601</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>2.19263100624084</v>
+        <v>2.19263076782227</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607305526733</v>
+        <v>2.19607329368591</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.1444411277771</v>
+        <v>2.14444160461426</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15821003913879</v>
+        <v>2.15820980072021</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.22361016273499</v>
+        <v>2.22360992431641</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23049426078796</v>
+        <v>2.23049402236938</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.22016763687134</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393630981445</v>
+        <v>2.23393654823303</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.30622053146362</v>
+        <v>2.3062207698822</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>2.24426293373108</v>
+        <v>2.2442626953125</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001968383789</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G693" t="n">
-        <v>2.1272304058075</v>
+        <v>2.12723064422607</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494570732117</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>2.08248329162598</v>
+        <v>2.0824830532074</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494570732117</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266160488129</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266160488129</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266160488129</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841871261597</v>
+        <v>1.84841859340668</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="n">
-        <v>1.81399750709534</v>
+        <v>1.81399774551392</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.88284015655518</v>
+        <v>1.8828399181366</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070364952087</v>
+        <v>1.92070317268372</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921943664551</v>
+        <v>1.97921919822693</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298799037933</v>
+        <v>1.99298787117004</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610353469849</v>
+        <v>1.98610401153564</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429341316223</v>
+        <v>2.03429317474365</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="n">
-        <v>2.05838799476624</v>
+        <v>2.05838823318481</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.07559895515442</v>
+        <v>2.075599193573</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.07559895515442</v>
+        <v>2.075599193573</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>2.04461979866028</v>
+        <v>2.04462003707886</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.0618302822113</v>
+        <v>2.06183052062988</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889293193817</v>
+        <v>1.96889317035675</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758750915527</v>
+        <v>1.92758798599243</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200883388519</v>
+        <v>1.96200859546661</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="n">
-        <v>2.23049426078796</v>
+        <v>2.23049402236938</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="n">
-        <v>2.17197847366333</v>
+        <v>2.17197823524475</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="n">
-        <v>2.33375787734985</v>
+        <v>2.33375811576843</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.49209547042847</v>
+        <v>2.49209523200989</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390559196472</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390559196472</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>2.50242161750793</v>
+        <v>2.50242185592651</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093764305115</v>
+        <v>2.56093811988831</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.64354848861694</v>
+        <v>2.64354872703552</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="n">
-        <v>2.67108559608459</v>
+        <v>2.67108607292175</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224342346191</v>
+        <v>2.60224318504333</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601161956787</v>
+        <v>2.61601185798645</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880113601685</v>
+        <v>2.59880137443542</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>2.56438016891479</v>
+        <v>2.56437993049622</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>2.65731692314148</v>
+        <v>2.65731716156006</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.69173860549927</v>
+        <v>2.69173884391785</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>2.70206499099731</v>
+        <v>2.70206475257874</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090740203857</v>
+        <v>2.77090716362</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.7123908996582</v>
+        <v>2.71239113807678</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>2.76058125495911</v>
+        <v>2.76058101654053</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>2.76746511459351</v>
+        <v>2.76746535301208</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304414749146</v>
+        <v>2.73304390907288</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>2.6642017364502</v>
+        <v>2.66420125961304</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322257995605</v>
+        <v>2.63322281837463</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="n">
-        <v>2.51619029045105</v>
+        <v>2.51619005203247</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390559196472</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.4266951084137</v>
+        <v>2.42669534683228</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423221588135</v>
+        <v>2.45423197746277</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390559196472</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357920646667</v>
+        <v>2.43357944488525</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="n">
-        <v>2.49553751945496</v>
+        <v>2.49553775787354</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>2.4989800453186</v>
+        <v>2.49897980690002</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.35441112518311</v>
+        <v>2.35441088676453</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031582832336</v>
+        <v>2.33031606674194</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295763015747</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001968383789</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>2.07904100418091</v>
+        <v>2.07904076576233</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.07559895515442</v>
+        <v>2.075599193573</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026301383972</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302963256836</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026301383972</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>1.94579637050629</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026301383972</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834658622742</v>
+        <v>1.97834610939026</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302963256836</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94579637050629</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601217746735</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792860507965</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069498538971</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601217746735</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8987785577774</v>
+        <v>1.89877879619598</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302963256836</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>2.07238149642944</v>
+        <v>2.07238125801086</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792860507965</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069498538971</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601217746735</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.86261165142059</v>
+        <v>1.86261141300201</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792860507965</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199125766754</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.62752461433411</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390756607056</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327353954315</v>
+        <v>1.57327365875244</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.5768905878067</v>
+        <v>1.57689046859741</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.59135723114014</v>
+        <v>1.59135746955872</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007518768311</v>
+        <v>1.66007494926453</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944092273712</v>
+        <v>1.60944104194641</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>1.61305785179138</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>1.70347571372986</v>
+        <v>1.70347547531128</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.7468763589859</v>
+        <v>1.74687647819519</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.62752461433411</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>1.61305785179138</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>1.61305785179138</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.6456081867218</v>
+        <v>1.64560806751251</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.6998587846756</v>
+        <v>1.69985890388489</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G954" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.62752461433411</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390756607056</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199125766754</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944092273712</v>
+        <v>1.60944104194641</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837468624115</v>
+        <v>1.63837480545044</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900883197784</v>
+        <v>1.68900871276855</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>1.70347571372986</v>
+        <v>1.70347547531128</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624209403992</v>
+        <v>1.69624221324921</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.77942681312561</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772655010223</v>
+        <v>1.75772643089294</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>1.70347571372986</v>
+        <v>1.70347547531128</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>1.72879278659821</v>
+        <v>1.7287929058075</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.77942681312561</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.9349457025528</v>
+        <v>1.93494594097137</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G999" t="n">
-        <v>1.9168621301651</v>
+        <v>1.91686236858368</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196339607239</v>
+        <v>1.98196315765381</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.03621435165405</v>
+        <v>2.03621411323547</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.00366353988647</v>
+        <v>2.0036633014679</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.01813054084778</v>
+        <v>2.0181303024292</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919653892517</v>
+        <v>1.98919677734375</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196339607239</v>
+        <v>1.98196315765381</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.94579637050629</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346172332764</v>
+        <v>1.87346148490906</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814476966858</v>
+        <v>1.84814465045929</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728011131287</v>
+        <v>2.00728034973145</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964297771454</v>
+        <v>1.73964273929596</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77581024169922</v>
+        <v>1.77581012248993</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.77942681312561</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77942681312561</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559383869171</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899448394775</v>
+        <v>1.85899460315704</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644426822662</v>
+        <v>1.82644438743591</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176134109497</v>
+        <v>1.85176122188568</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559383869171</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.77942681312561</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.60582423210144</v>
+        <v>1.60582411289215</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.51178932189941</v>
+        <v>1.51178956031799</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285567760468</v>
+        <v>1.48285579681396</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366837501526</v>
+        <v>1.43366825580597</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448083400726</v>
+        <v>1.38448095321655</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.35120713710785</v>
+        <v>1.35120701789856</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.2441520690918</v>
+        <v>1.24415218830109</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.07922959327698</v>
+        <v>1.07922971248627</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00400185585022</v>
+        <v>1.00400173664093</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.00834202766418</v>
+        <v>1.0083419084549</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.13854384422302</v>
+        <v>1.13854372501373</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.23547196388245</v>
+        <v>1.23547184467316</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.2441520690918</v>
+        <v>1.24415218830109</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.13854384422302</v>
+        <v>1.13854372501373</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968518733978</v>
+        <v>1.22968530654907</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.29478621482849</v>
+        <v>1.2947860956192</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.20653831958771</v>
+        <v>1.20653820037842</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100508213043</v>
+        <v>1.22100496292114</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.20075154304504</v>
+        <v>1.20075142383575</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.1240770816803</v>
+        <v>1.12407696247101</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318915843964</v>
+        <v>1.05318927764893</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.0430623292923</v>
+        <v>1.04306244850159</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.02859556674957</v>
+        <v>1.02859568595886</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.06910264492035</v>
+        <v>1.06910288333893</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.15735077857971</v>
+        <v>1.157350897789</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011751651764</v>
+        <v>1.15011739730835</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.13565051555634</v>
+        <v>1.13565063476562</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212304115295</v>
+        <v>1.08212292194366</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382354259491</v>
+        <v>1.10382330417633</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.12552356719971</v>
+        <v>1.125523686409</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237658023834</v>
+        <v>1.10237669944763</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.07633626461029</v>
+        <v>1.076336145401</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.10092985630035</v>
+        <v>1.10092997550964</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476271152496</v>
+        <v>1.06476283073425</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501636981964</v>
+        <v>1.08501648902893</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.07054948806763</v>
+        <v>1.07054936885834</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.08935630321503</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.08356976509094</v>
+        <v>1.08356964588165</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501636981964</v>
+        <v>1.08501648902893</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.08356976509094</v>
+        <v>1.08356964588165</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595589637756</v>
+        <v>1.04595577716827</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981698036194</v>
+        <v>0.990981578826904</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.00689518451691</v>
+        <v>1.0068953037262</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088309764862</v>
+        <v>0.988088190555573</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.975068151950836</v>
+        <v>0.975068032741547</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.00400185585022</v>
+        <v>1.00400173664093</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.00834202766418</v>
+        <v>1.0083419084549</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088309764862</v>
+        <v>0.988088190555573</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321691036224</v>
+        <v>0.995321810245514</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.01991546154022</v>
+        <v>1.01991534233093</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.01991546154022</v>
+        <v>1.01991534233093</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.00834202766418</v>
+        <v>1.0083419084549</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.97651469707489</v>
+        <v>0.97651481628418</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.966387808322906</v>
+        <v>0.966387987136841</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.966387808322906</v>
+        <v>0.966387987136841</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.966387808322906</v>
+        <v>0.966387987136841</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047874927521</v>
+        <v>0.962047755718231</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.963494658470154</v>
+        <v>0.963494539260864</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880670547485</v>
+        <v>0.925880610942841</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687724113464</v>
+        <v>0.944687485694885</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687724113464</v>
+        <v>0.944687485694885</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900828361511</v>
+        <v>0.938900947570801</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.898393452167511</v>
+        <v>0.898393630981445</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.907073676586151</v>
+        <v>0.907073616981506</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093834400177</v>
+        <v>0.920093894004822</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901286959648132</v>
+        <v>0.901286900043488</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840235710144</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.889713406562805</v>
+        <v>0.88971334695816</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093834400177</v>
+        <v>0.920093894004822</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413729190826</v>
+        <v>0.911413669586182</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413729190826</v>
+        <v>0.911413669586182</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.97651469707489</v>
+        <v>0.97651481628418</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.918647110462189</v>
+        <v>0.918647170066833</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753901004791</v>
+        <v>0.915753841400146</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013203144073</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.824612379074097</v>
+        <v>0.824612438678741</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.828952491283417</v>
+        <v>0.828952550888062</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871681213379</v>
+        <v>0.776871800422668</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024431228638</v>
+        <v>0.732024371623993</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.771085023880005</v>
+        <v>0.77108496427536</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211853027344</v>
+        <v>0.781211793422699</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191635608673</v>
+        <v>0.768191695213318</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079320430756</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901286959648132</v>
+        <v>0.901286900043488</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840235710144</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967064857483</v>
+        <v>0.909967184066772</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.894053399562836</v>
+        <v>0.89405345916748</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.879586637020111</v>
+        <v>0.879586577415466</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.889713406562805</v>
+        <v>0.88971334695816</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013203144073</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013203144073</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119636058807</v>
+        <v>0.865119755268097</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.885373294353485</v>
+        <v>0.88537335395813</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.86222630739212</v>
+        <v>0.862226366996765</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779702663422</v>
+        <v>0.860779643058777</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459688663483</v>
+        <v>0.869459807872772</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840235710144</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.907073676586151</v>
+        <v>0.907073616981506</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733564376831</v>
+        <v>0.902733623981476</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.881033301353455</v>
+        <v>0.881033360958099</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013203144073</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.854992985725403</v>
+        <v>0.854992866516113</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779702663422</v>
+        <v>0.860779643058777</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206149578094</v>
+        <v>0.84920608997345</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079320430756</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.852099478244781</v>
+        <v>0.852099537849426</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.836185932159424</v>
+        <v>0.836185991764069</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119636058807</v>
+        <v>0.865119755268097</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.975068151950836</v>
+        <v>0.975068032741547</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.01991546154022</v>
+        <v>1.01991534233093</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408204555511</v>
+        <v>0.979408085346222</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778310775757</v>
+        <v>1.07778298854828</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.02280867099762</v>
+        <v>1.0228089094162</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768355369568</v>
+        <v>0.996768474578857</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.04161584377289</v>
+        <v>1.0416157245636</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.07922959327698</v>
+        <v>1.07922971248627</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.08935630321503</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.10092985630035</v>
+        <v>1.10092997550964</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.17037117481232</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.17037117481232</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.15879738330841</v>
+        <v>1.1587975025177</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16603088378906</v>
+        <v>1.16603076457977</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.13999056816101</v>
+        <v>1.13999044895172</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049788475037</v>
+        <v>1.18049776554108</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.17037117481232</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.16892445087433</v>
+        <v>1.16892433166504</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.18339109420776</v>
+        <v>1.18339121341705</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.16603088378906</v>
+        <v>1.16603076457977</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.30201959609985</v>
+        <v>1.30201971530914</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491316318512</v>
+        <v>1.30491304397583</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057287216187</v>
+        <v>1.30057299137115</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.29189276695251</v>
+        <v>1.2918928861618</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635964870453</v>
+        <v>1.30635976791382</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030534267426</v>
+        <v>1.45030522346497</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>2.25</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>45618</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>2.21499991416931</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>2.21499991416931</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85730147361755</v>
+        <v>2.8573009967804</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6085090637207</v>
+        <v>2.60850954055786</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928339958191</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408190727234</v>
+        <v>2.56408214569092</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.50061464309692</v>
+        <v>2.5006148815155</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66436052322388</v>
+        <v>2.6643602848053</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915926933289</v>
+        <v>2.56915974617004</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5386950969696</v>
+        <v>2.53869485855103</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662106513977</v>
+        <v>2.56662130355835</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107905387878</v>
+        <v>2.53107881546021</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349384307861</v>
+        <v>2.44349431991577</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2860951423645</v>
+        <v>2.28609490394592</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482556343079</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36098670959473</v>
+        <v>2.36098623275757</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798337936401</v>
+        <v>2.32798361778259</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.486652135849</v>
+        <v>2.48665189743042</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6186637878418</v>
+        <v>2.61866402626038</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.55519652366638</v>
+        <v>2.55519676208496</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928339958191</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G41" t="n">
-        <v>2.6085090637207</v>
+        <v>2.60850954055786</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6085090637207</v>
+        <v>2.60850954055786</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63389611244202</v>
+        <v>2.6338963508606</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658975601196</v>
+        <v>2.64658951759338</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213129043579</v>
+        <v>2.68213105201721</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6935555934906</v>
+        <v>2.69355535507202</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G50" t="n">
-        <v>2.65039801597595</v>
+        <v>2.65039777755737</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G51" t="n">
-        <v>2.73925185203552</v>
+        <v>2.7392520904541</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172839164734</v>
+        <v>2.90172863006592</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504140853882</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>2.94869422912598</v>
+        <v>2.94869470596313</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104687690735</v>
+        <v>3.02104783058167</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423624038696</v>
+        <v>2.98423647880554</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200700759888</v>
+        <v>3.00200724601746</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>2.98931384086609</v>
+        <v>2.98931360244751</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182145118713</v>
+        <v>3.07182121276855</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643392562866</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702151298523</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702151298523</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.1479823589325</v>
+        <v>3.14798188209534</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.09847736358643</v>
+        <v>3.09847784042358</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244058609009</v>
+        <v>3.11244082450867</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086108207703</v>
+        <v>3.09086155891418</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959245681763</v>
+        <v>3.08959221839905</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547451019287</v>
+        <v>3.06547379493713</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374099731445</v>
+        <v>3.03374123573303</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G88" t="n">
-        <v>3.05912756919861</v>
+        <v>3.05912804603577</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643392562866</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>2.93384861946106</v>
+        <v>2.93384885787964</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974327087402</v>
+        <v>2.94974303245544</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.11266088485718</v>
+        <v>3.1126606464386</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577484130859</v>
+        <v>3.14577460289001</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140480995178</v>
+        <v>3.20140528678894</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>3.19213318824768</v>
+        <v>3.19213342666626</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584342002869</v>
+        <v>3.23584294319153</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.23186922073364</v>
+        <v>3.23186945915222</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610691070557</v>
+        <v>3.19610738754272</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802783966064</v>
+        <v>3.20802760124207</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829180717468</v>
+        <v>3.16829109191895</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.15901947021484</v>
+        <v>3.15901970863342</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133646965027</v>
+        <v>3.11133670806885</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.25</v>
       </c>
       <c r="G115" t="n">
-        <v>2.81464028358459</v>
+        <v>2.81464076042175</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516798019409</v>
+        <v>2.73516821861267</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69278287887573</v>
+        <v>2.69278311729431</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85040283203125</v>
+        <v>2.85040259361267</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.86762189865112</v>
+        <v>2.86762166023254</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91133141517639</v>
+        <v>2.91133165359497</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060327529907</v>
+        <v>2.92060279846191</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.8159646987915</v>
+        <v>2.81596493721008</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841356277466</v>
+        <v>2.74841332435608</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708890914917</v>
+        <v>2.74708843231201</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>2.9007351398468</v>
+        <v>2.90073537826538</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709420204163</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802254676819</v>
+        <v>3.00802230834961</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>2.95371651649475</v>
+        <v>2.95371675491333</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.9153048992157</v>
+        <v>2.91530513763428</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>2.74179100990295</v>
+        <v>2.74179077148438</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="n">
-        <v>2.63715243339539</v>
+        <v>2.63715267181396</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397590637207</v>
+        <v>2.71397566795349</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364336013794</v>
+        <v>2.66364312171936</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112591743469</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>2.6358277797699</v>
+        <v>2.63582801818848</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112591743469</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60139012336731</v>
+        <v>2.60138988494873</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.54178547859192</v>
+        <v>2.5417857170105</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152198791504</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159008979797</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>2.67556381225586</v>
+        <v>2.67556405067444</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7219226360321</v>
+        <v>2.72192287445068</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.71529984474182</v>
+        <v>2.71530032157898</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73384308815002</v>
+        <v>2.73384356498718</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364336013794</v>
+        <v>2.66364312171936</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702033042908</v>
+        <v>2.65702056884766</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159008979797</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.66231870651245</v>
+        <v>2.66231846809387</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6186089515686</v>
+        <v>2.61860871315002</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="n">
-        <v>2.56562757492065</v>
+        <v>2.56562733650208</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.6358277797699</v>
+        <v>2.63582801818848</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801243782043</v>
+        <v>2.60801267623901</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754826545715</v>
+        <v>2.57754850387573</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.4119815826416</v>
+        <v>2.41198134422302</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36827158927917</v>
+        <v>2.3682713508606</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761155128479</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992855072021</v>
+        <v>2.41992831230164</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078855514526</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="n">
-        <v>2.24641418457031</v>
+        <v>2.24641394615173</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.28615045547485</v>
+        <v>2.2861499786377</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655110359192</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36959600448608</v>
+        <v>2.36959624290466</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078855514526</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741086959839</v>
+        <v>2.39741110801697</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="n">
-        <v>2.34575438499451</v>
+        <v>2.34575462341309</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211297035217</v>
+        <v>2.39211344718933</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655110359192</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503082275391</v>
+        <v>2.55503153800964</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152198791504</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324247360229</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>2.51661944389343</v>
+        <v>2.51661968231201</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496272087097</v>
+        <v>2.46496248245239</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48085737228394</v>
+        <v>2.48085713386536</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47026109695435</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416576385498</v>
+        <v>2.38416600227356</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>2.3444299697876</v>
+        <v>2.34442973136902</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.33780717849731</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.33780717849731</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098370552063</v>
+        <v>2.26098394393921</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495790481567</v>
+        <v>2.26495742797852</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>2.22522139549255</v>
+        <v>2.22522163391113</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548560142517</v>
+        <v>2.18548536300659</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237717628479</v>
+        <v>2.35237693786621</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="n">
-        <v>2.40668296813965</v>
+        <v>2.40668320655823</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="n">
-        <v>2.4119815826416</v>
+        <v>2.41198134422302</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.47026109695435</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="n">
-        <v>2.49145340919495</v>
+        <v>2.49145364761353</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.47026109695435</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324247360229</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="n">
-        <v>2.54708385467529</v>
+        <v>2.54708409309387</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.53251385688782</v>
+        <v>2.53251433372498</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960153579712</v>
+        <v>2.56960105895996</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059316635132</v>
+        <v>2.52059292793274</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072526931763</v>
+        <v>2.50072503089905</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363854408264</v>
+        <v>2.4636378288269</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="n">
-        <v>2.34310507774353</v>
+        <v>2.34310531616211</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="n">
-        <v>2.42257785797119</v>
+        <v>2.42257738113403</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.36562204360962</v>
+        <v>2.3656222820282</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>2.32191300392151</v>
+        <v>2.32191276550293</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="n">
-        <v>2.35502600669861</v>
+        <v>2.35502648353577</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476203918457</v>
+        <v>2.39476227760315</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.41727948188782</v>
+        <v>2.41727924346924</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933203697205</v>
+        <v>2.40933227539062</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006065368652</v>
+        <v>2.40006041526794</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999183654785</v>
+        <v>2.30999207496643</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="n">
-        <v>2.34575438499451</v>
+        <v>2.34575462341309</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933203697205</v>
+        <v>2.40933227539062</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="n">
-        <v>2.50469875335693</v>
+        <v>2.50469899177551</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761155128479</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49145340919495</v>
+        <v>2.49145364761353</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>2.56297826766968</v>
+        <v>2.56297850608826</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.6000657081604</v>
+        <v>2.60006546974182</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211802482605</v>
+        <v>2.59211850166321</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.70073056221008</v>
+        <v>2.7007303237915</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.71529984474182</v>
+        <v>2.71530032157898</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.8212628364563</v>
+        <v>2.82126331329346</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642958641052</v>
+        <v>2.84642910957336</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252420425415</v>
+        <v>2.93252396583557</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.06497716903687</v>
+        <v>3.0649778842926</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709420204163</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="n">
-        <v>2.86099910736084</v>
+        <v>2.86099934577942</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444537162781</v>
+        <v>2.94444513320923</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="n">
-        <v>2.93914699554443</v>
+        <v>2.93914723396301</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848719596863</v>
+        <v>3.03848671913147</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.0040488243103</v>
+        <v>3.00404906272888</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504117012024</v>
+        <v>2.95504140853882</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90868258476257</v>
+        <v>2.90868234634399</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093605995178</v>
+        <v>2.97093558311462</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067185401917</v>
+        <v>3.01067161560059</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="n">
-        <v>3.09146809577942</v>
+        <v>3.09146857261658</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173230171204</v>
+        <v>3.05173206329346</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484601974487</v>
+        <v>3.08484578132629</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="n">
-        <v>3.1047146320343</v>
+        <v>3.10471391677856</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.00669836997986</v>
+        <v>3.00669813156128</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981137275696</v>
+        <v>3.03981161117554</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159538269043</v>
+        <v>2.87159490585327</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="n">
-        <v>2.95121884346008</v>
+        <v>2.95121836662292</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887835502625</v>
+        <v>2.87887811660767</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="n">
-        <v>2.89227437973022</v>
+        <v>2.89227485656738</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772747039795</v>
+        <v>2.91772723197937</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="n">
-        <v>2.92308616638184</v>
+        <v>2.92308592796326</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093494415283</v>
+        <v>2.89093470573425</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897298812866</v>
+        <v>2.89897274971008</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G362" t="n">
-        <v>2.85476493835449</v>
+        <v>2.85476469993591</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.82395315170288</v>
+        <v>2.8239529132843</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.83333086967468</v>
+        <v>2.8333306312561</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644299507141</v>
+        <v>2.78644323348999</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276378631592</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="n">
-        <v>2.66989493370056</v>
+        <v>2.66989517211914</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>2.69936728477478</v>
+        <v>2.6993670463562</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68730998039246</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="n">
-        <v>2.70204615592957</v>
+        <v>2.70204639434814</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G376" t="n">
-        <v>2.6672158241272</v>
+        <v>2.66721606254578</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649890899658</v>
+        <v>2.656498670578</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="n">
-        <v>2.66855549812317</v>
+        <v>2.66855525970459</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568688392639</v>
+        <v>2.62568712234497</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>2.56942224502563</v>
+        <v>2.56942248344421</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="n">
-        <v>2.60291337966919</v>
+        <v>2.60291314125061</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="n">
-        <v>2.59487557411194</v>
+        <v>2.59487533569336</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870532989502</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="n">
-        <v>2.72214102745056</v>
+        <v>2.72214078903198</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946120262146</v>
+        <v>2.71946144104004</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68730998039246</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="n">
-        <v>2.64310216903687</v>
+        <v>2.64310240745544</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.63104557991028</v>
+        <v>2.6310453414917</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>2.60961151123047</v>
+        <v>2.60961103439331</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095094680786</v>
+        <v>2.61095118522644</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.64042329788208</v>
+        <v>2.6404230594635</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381932258606</v>
+        <v>2.65381908416748</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G410" t="n">
-        <v>2.6672158241272</v>
+        <v>2.66721606254578</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338582992554</v>
+        <v>2.70338559150696</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="n">
-        <v>2.60291337966919</v>
+        <v>2.60291314125061</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.5613842010498</v>
+        <v>2.56138443946838</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344079017639</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459167480469</v>
+        <v>2.53459191322327</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="n">
-        <v>2.5225350856781</v>
+        <v>2.52253484725952</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172377586365</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G423" t="n">
-        <v>2.48636484146118</v>
+        <v>2.4863646030426</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502540588379</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47162890434265</v>
+        <v>2.47162866592407</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56004476547241</v>
+        <v>2.56004452705383</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="n">
-        <v>2.5975546836853</v>
+        <v>2.59755492210388</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157346725464</v>
+        <v>2.60157370567322</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095094680786</v>
+        <v>2.61095118522644</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7167820930481</v>
+        <v>2.71678233146667</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85342502593994</v>
+        <v>2.85342574119568</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="n">
-        <v>2.88691592216492</v>
+        <v>2.8869161605835</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>2.91504883766174</v>
+        <v>2.91504836082458</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>2.88021779060364</v>
+        <v>2.88021802902222</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136843681335</v>
+        <v>2.84136867523193</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="n">
-        <v>2.85744404792786</v>
+        <v>2.85744380950928</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663249969482</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663249969482</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868885040283</v>
+        <v>2.83868956565857</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887835502625</v>
+        <v>2.87887811660767</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567111968994</v>
+        <v>2.90567088127136</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.88691592216492</v>
+        <v>2.8869161605835</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.84002876281738</v>
+        <v>2.8400285243988</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="n">
-        <v>2.86280274391174</v>
+        <v>2.86280250549316</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710494995117</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710494995117</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>2.92576575279236</v>
+        <v>2.92576551437378</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88155722618103</v>
+        <v>2.88155746459961</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648266792297</v>
+        <v>2.93648242950439</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8855767250061</v>
+        <v>2.88557648658752</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>2.88021779060364</v>
+        <v>2.88021802902222</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270811080933</v>
+        <v>2.84270787239075</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314160346985</v>
+        <v>2.79314184188843</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76233005523682</v>
+        <v>2.7623302936554</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.64042329788208</v>
+        <v>2.6404230594635</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.58817744255066</v>
+        <v>2.58817720413208</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300729751587</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.66587591171265</v>
+        <v>2.66587615013123</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="n">
-        <v>2.59487557411194</v>
+        <v>2.59487533569336</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266891479492</v>
+        <v>2.69266867637634</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.624347448349</v>
+        <v>2.62434768676758</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276378631592</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300729751587</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344079017639</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.5613842010498</v>
+        <v>2.56138443946838</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344079017639</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057289123535</v>
+        <v>2.53057312965393</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449728012085</v>
+        <v>2.51449704170227</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502540588379</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502540588379</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884692192078</v>
+        <v>2.58884716033936</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526163101196</v>
+        <v>2.53526139259338</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>2.54196000099182</v>
+        <v>2.54195952415466</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.53861045837402</v>
+        <v>2.5386106967926</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870532989502</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59554505348206</v>
+        <v>2.59554481506348</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578175544739</v>
+        <v>2.64578151702881</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.57879948616028</v>
+        <v>2.57879972457886</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172377586365</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526163101196</v>
+        <v>2.53526139259338</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5486581325531</v>
+        <v>2.54865789413452</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818544387817</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488309860229</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827983856201</v>
+        <v>2.46827936172485</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G546" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818544387817</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.40464687347412</v>
+        <v>2.4046471118927</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G550" t="n">
-        <v>2.37785410881042</v>
+        <v>2.377854347229</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="n">
-        <v>2.38120341300964</v>
+        <v>2.38120317459106</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.38790154457092</v>
+        <v>2.3879017829895</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>2.20705080032349</v>
+        <v>2.20705103874207</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G557" t="n">
-        <v>2.20705080032349</v>
+        <v>2.20705103874207</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>2.2271454334259</v>
+        <v>2.22714519500732</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G559" t="n">
-        <v>2.24723958969116</v>
+        <v>2.24723982810974</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.24389052391052</v>
+        <v>2.24389028549194</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365429878235</v>
+        <v>2.19365453720093</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337063789368</v>
+        <v>2.13337087631226</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.25728702545166</v>
+        <v>2.25728678703308</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>2.27403235435486</v>
+        <v>2.27403283119202</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.2505886554718</v>
+        <v>2.25058889389038</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24389052391052</v>
+        <v>2.24389028549194</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.4113450050354</v>
+        <v>2.41134524345398</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.38455247879028</v>
+        <v>2.3845522403717</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483613967896</v>
+        <v>2.44483590126038</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.42474126815796</v>
+        <v>2.42474150657654</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818544387817</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502540588379</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172377586365</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="n">
-        <v>2.50177049636841</v>
+        <v>2.50177073478699</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488309860229</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.31998944282532</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>2.26491546630859</v>
+        <v>2.26491522789001</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556799888611</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>2.20295763015747</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.20984172821045</v>
+        <v>2.20984148979187</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>2.2201681137085</v>
+        <v>2.22016787528992</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.20295763015747</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>2.2201681137085</v>
+        <v>2.22016787528992</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>2.20984172821045</v>
+        <v>2.20984148979187</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770498275757</v>
+        <v>2.24770522117615</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589438438416</v>
+        <v>2.29589462280273</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408402442932</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915800094604</v>
+        <v>2.39915823936462</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473703384399</v>
+        <v>2.36473679542542</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27524209022522</v>
+        <v>2.27524185180664</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30277872085571</v>
+        <v>2.30277895927429</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556799888611</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.3062207698822</v>
+        <v>2.30622053146362</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.31998944282532</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589438438416</v>
+        <v>2.29589462280273</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>2.19263076782227</v>
+        <v>2.19263100624084</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607329368591</v>
+        <v>2.19607305526733</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.14444160461426</v>
+        <v>2.1444411277771</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23049402236938</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.2201681137085</v>
+        <v>2.22016787528992</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.3062207698822</v>
+        <v>2.30622053146362</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G669" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.20984172821045</v>
+        <v>2.20984148979187</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G677" t="n">
-        <v>2.13411498069763</v>
+        <v>2.13411450386047</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>2.1203465461731</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11001968383789</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G685" t="n">
-        <v>2.13411498069763</v>
+        <v>2.13411450386047</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>2.13067293167114</v>
+        <v>2.13067269325256</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>2.1203465461731</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>2.13067293167114</v>
+        <v>2.13067269325256</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>2.05150413513184</v>
+        <v>2.05150389671326</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>2.0824830532074</v>
+        <v>2.08248329162598</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>1.98266160488129</v>
+        <v>1.98266184329987</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512461662292</v>
+        <v>1.95512473583221</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168256759644</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>1.98266160488129</v>
+        <v>1.98266184329987</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>1.98266160488129</v>
+        <v>1.98266184329987</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841859340668</v>
+        <v>1.84841871261597</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="n">
-        <v>1.81399774551392</v>
+        <v>1.81399750709534</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070317268372</v>
+        <v>1.92070341110229</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414557933807</v>
+        <v>1.92414534091949</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921919822693</v>
+        <v>1.97921943664551</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298787117004</v>
+        <v>1.99298799037933</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610401153564</v>
+        <v>1.98610377311707</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429317474365</v>
+        <v>2.03429341316223</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>2.04462003707886</v>
+        <v>2.04461979866028</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.06183052062988</v>
+        <v>2.0618302822113</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889317035675</v>
+        <v>1.96889269351959</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168256759644</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758798599243</v>
+        <v>1.92758774757385</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200859546661</v>
+        <v>1.96200883388519</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="n">
-        <v>2.23049402236938</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.20984172821045</v>
+        <v>2.20984148979187</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G752" t="n">
-        <v>2.13411498069763</v>
+        <v>2.13411450386047</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.08936738967896</v>
+        <v>2.08936762809753</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G757" t="n">
-        <v>2.13411498069763</v>
+        <v>2.13411450386047</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="n">
-        <v>2.17197823524475</v>
+        <v>2.17197847366333</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408402442932</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.44390559196472</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.44390559196472</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144222259521</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144222259521</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144222259521</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>2.50242185592651</v>
+        <v>2.50242161750793</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307415008545</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307415008545</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093811988831</v>
+        <v>2.56093788146973</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="n">
-        <v>2.6056854724884</v>
+        <v>2.60568523406982</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.64354872703552</v>
+        <v>2.64354848861694</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67797017097473</v>
+        <v>2.67796993255615</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880137443542</v>
+        <v>2.59880113601685</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090716362</v>
+        <v>2.77090740203857</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>2.73992800712585</v>
+        <v>2.73992824554443</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681234359741</v>
+        <v>2.74681258201599</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.7055070400238</v>
+        <v>2.70550680160522</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>2.76746535301208</v>
+        <v>2.76746511459351</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.7055070400238</v>
+        <v>2.70550680160522</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>2.66420125961304</v>
+        <v>2.66420149803162</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912752151489</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912752151489</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912752151489</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322281837463</v>
+        <v>2.63322234153748</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="n">
-        <v>2.51619005203247</v>
+        <v>2.51619029045105</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>2.44390559196472</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423197746277</v>
+        <v>2.45423221588135</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>2.44390559196472</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>2.45079016685486</v>
+        <v>2.45078992843628</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734764099121</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357944488525</v>
+        <v>2.43357968330383</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734764099121</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144222259521</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.505863904953</v>
+        <v>2.50586414337158</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013739585876</v>
+        <v>2.43013715744019</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="n">
-        <v>2.38883185386658</v>
+        <v>2.388831615448</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>2.31654739379883</v>
+        <v>2.31654715538025</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>2.20295763015747</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G856" t="n">
-        <v>2.13411498069763</v>
+        <v>2.13411450386047</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11001968383789</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.95302963256836</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579637050629</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834610939026</v>
+        <v>1.97834634780884</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.95302963256836</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579637050629</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.880695104599</v>
+        <v>1.88069474697113</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.89877879619598</v>
+        <v>1.8987785577774</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.95302963256836</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>2.07238125801086</v>
+        <v>2.07238149642944</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.83006107807159</v>
+        <v>1.8300609588623</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.880695104599</v>
+        <v>1.88069474697113</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389381408691</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474364757538</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389381408691</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>1.7143257856369</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390756607056</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262528419495</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>1.61667442321777</v>
+        <v>1.61667430400848</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.62029111385345</v>
+        <v>1.62029099464417</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>1.61667442321777</v>
+        <v>1.61667430400848</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.57689046859741</v>
+        <v>1.5768905878067</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.59135746955872</v>
+        <v>1.59135723114014</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G930" t="n">
-        <v>1.58412384986877</v>
+        <v>1.58412396907806</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007494926453</v>
+        <v>1.66007518768311</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>1.59497404098511</v>
+        <v>1.59497392177582</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645837783813</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>1.70347547531128</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.67454195022583</v>
+        <v>1.67454206943512</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G939" t="n">
-        <v>1.72517609596252</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G941" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.74687647819519</v>
+        <v>1.7468763589859</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G950" t="n">
-        <v>1.61667442321777</v>
+        <v>1.61667430400848</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.62029111385345</v>
+        <v>1.62029099464417</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64560806751251</v>
+        <v>1.6456081867218</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.69985890388489</v>
+        <v>1.6998587846756</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G954" t="n">
-        <v>1.7143257856369</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390756607056</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837480545044</v>
+        <v>1.63837468624115</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262528419495</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262528419495</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900871276855</v>
+        <v>1.68900883197784</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>1.70347547531128</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624221324921</v>
+        <v>1.6962423324585</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262528419495</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G974" t="n">
-        <v>1.67454195022583</v>
+        <v>1.67454206943512</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772643089294</v>
+        <v>1.75772678852081</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>1.70347547531128</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G986" t="n">
-        <v>1.72517609596252</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>1.7287929058075</v>
+        <v>1.72879278659821</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>1.7143257856369</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>1.7143257856369</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.93494594097137</v>
+        <v>1.9349457025528</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G999" t="n">
-        <v>1.91686236858368</v>
+        <v>1.9168621301651</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196315765381</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.03621411323547</v>
+        <v>2.03621435165405</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.0036633014679</v>
+        <v>2.00366353988647</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.0181303024292</v>
+        <v>2.01813054084778</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196315765381</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281358718872</v>
+        <v>1.99281334877014</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387982368469</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387982368469</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856275081635</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579637050629</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856275081635</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814465045929</v>
+        <v>1.84814476966858</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856275081635</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728034973145</v>
+        <v>2.00728011131287</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387982368469</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474364757538</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.72517609596252</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964273929596</v>
+        <v>1.73964297771454</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77581012248993</v>
+        <v>1.77581024169922</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.81559383869171</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899460315704</v>
+        <v>1.85899472236633</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.81921076774597</v>
+        <v>1.81921064853668</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176122188568</v>
+        <v>1.85176134109497</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.81559383869171</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262528419495</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645837783813</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645837783813</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.60582411289215</v>
+        <v>1.60582423210144</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965708732605</v>
+        <v>1.56965696811676</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.51178956031799</v>
+        <v>1.5117894411087</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448095321655</v>
+        <v>1.38448083400726</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.35120701789856</v>
+        <v>1.35120713710785</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.07922971248627</v>
+        <v>1.07922947406769</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.13854372501373</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.2267918586731</v>
+        <v>1.22679197788239</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.23547184467316</v>
+        <v>1.23547196388245</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.2267918586731</v>
+        <v>1.22679197788239</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.17760443687439</v>
+        <v>1.1776043176651</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.13854372501373</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968530654907</v>
+        <v>1.22968518733978</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.19351804256439</v>
+        <v>1.1935179233551</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.2947860956192</v>
+        <v>1.29478621482849</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.20653820037842</v>
+        <v>1.20653831958771</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100496292114</v>
+        <v>1.22100508213043</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.12407696247101</v>
+        <v>1.1240770816803</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318927764893</v>
+        <v>1.05318915843964</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04306244850159</v>
+        <v>1.0430623292923</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.02859568595886</v>
+        <v>1.02859556674957</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.06910288333893</v>
+        <v>1.06910276412964</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.157350897789</v>
+        <v>1.15735077857971</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.13565063476562</v>
+        <v>1.13565051555634</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382330417633</v>
+        <v>1.10382342338562</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.125523686409</v>
+        <v>1.12552356719971</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237669944763</v>
+        <v>1.10237658023834</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.076336145401</v>
+        <v>1.07633626461029</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501648902893</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501648902893</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.0748895406723</v>
+        <v>1.07488942146301</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595577716827</v>
+        <v>1.04595589637756</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846861839294</v>
+        <v>1.01846873760223</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981578826904</v>
+        <v>0.990981698036194</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.0068953037262</v>
+        <v>1.00689518451691</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.975068032741547</v>
+        <v>0.975068151950836</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321810245514</v>
+        <v>0.995321691036224</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.97651481628418</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.966387987136841</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.966387987136841</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.966387987136841</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.967834651470184</v>
+        <v>0.967834532260895</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047755718231</v>
+        <v>0.962047874927521</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.963494539260864</v>
+        <v>0.963494658470154</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880610942841</v>
+        <v>0.925880670547485</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687485694885</v>
+        <v>0.944687724113464</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687485694885</v>
+        <v>0.944687724113464</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454104423523</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900947570801</v>
+        <v>0.938900828361511</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.92154061794281</v>
+        <v>0.921540558338165</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.898393630981445</v>
+        <v>0.898393571376801</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454104423523</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901286900043488</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.88971334695816</v>
+        <v>0.889713406562805</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.97651481628418</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748078346252</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951920986175537</v>
+        <v>0.951921105384827</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.918647170066833</v>
+        <v>0.918647110462189</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753841400146</v>
+        <v>0.915753901004791</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.826059103012085</v>
+        <v>0.82605904340744</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871800422668</v>
+        <v>0.776871740818024</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024371623993</v>
+        <v>0.732024431228638</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.77108496427536</v>
+        <v>0.771085023880005</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211793422699</v>
+        <v>0.781211853027344</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191695213318</v>
+        <v>0.768191635608673</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.833292484283447</v>
+        <v>0.833292543888092</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.850652873516083</v>
+        <v>0.850652813911438</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799800872803</v>
+        <v>0.873799741268158</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901286900043488</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967184066772</v>
+        <v>0.909967064857483</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.89405345916748</v>
+        <v>0.894053399562836</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.879586577415466</v>
+        <v>0.879586637020111</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.88971334695816</v>
+        <v>0.889713406562805</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693189144135</v>
+        <v>0.876693308353424</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.88537335395813</v>
+        <v>0.885373294353485</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.862226366996765</v>
+        <v>0.86222630739212</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779821872711</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459807872772</v>
+        <v>0.869459688663483</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733623981476</v>
+        <v>0.902733683586121</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.881033360958099</v>
+        <v>0.881033301353455</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.854992866516113</v>
+        <v>0.854992985725403</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779821872711</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.84920608997345</v>
+        <v>0.849206149578094</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.852099537849426</v>
+        <v>0.852099597454071</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.826059103012085</v>
+        <v>0.82605904340744</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312761306763</v>
+        <v>0.846312642097473</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799800872803</v>
+        <v>0.873799741268158</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.975068032741547</v>
+        <v>0.975068151950836</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408085346222</v>
+        <v>0.979408204555511</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748078346252</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778298854828</v>
+        <v>1.07778310775757</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.0228089094162</v>
+        <v>1.02280879020691</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768474578857</v>
+        <v>0.996768355369568</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748078346252</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.0416157245636</v>
+        <v>1.04161584377289</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.07922971248627</v>
+        <v>1.07922947406769</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458415985107</v>
+        <v>1.16458427906036</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.19351804256439</v>
+        <v>1.1935179233551</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.13999044895172</v>
+        <v>1.13999056816101</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049776554108</v>
+        <v>1.18049788475037</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.17905104160309</v>
+        <v>1.17905116081238</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.17905104160309</v>
+        <v>1.17905116081238</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.30201971530914</v>
+        <v>1.30201959609985</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491304397583</v>
+        <v>1.30491316318512</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057299137115</v>
+        <v>1.30057287216187</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.2918928861618</v>
+        <v>1.29189276695251</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635976791382</v>
+        <v>1.30635964870453</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030522346497</v>
+        <v>1.45030534267426</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.42932820320129</v>
+        <v>1.429328083992</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.35046672821045</v>
+        <v>1.35046684741974</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.36376452445984</v>
+        <v>1.36376440525055</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.45980441570282</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.34307909011841</v>
+        <v>1.34307897090912</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.25294935703278</v>
+        <v>1.25294947624207</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.23817408084869</v>
+        <v>1.2381739616394</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.19384813308716</v>
+        <v>1.19384801387787</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.18498277664185</v>
+        <v>1.18498289585114</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.1657749414444</v>
+        <v>1.16577482223511</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.27067995071411</v>
+        <v>1.27067983150482</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.27806746959686</v>
+        <v>1.27806758880615</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.26772475242615</v>
+        <v>1.26772463321686</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614066123962</v>
+        <v>1.30614078044891</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.3681972026825</v>
+        <v>1.36819708347321</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.32682621479034</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.35785436630249</v>
+        <v>1.35785448551178</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.28102254867554</v>
+        <v>1.28102266788483</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.27806746959686</v>
+        <v>1.27806758880615</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.37853991985321</v>
+        <v>1.3785400390625</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.45980441570282</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.35046672821045</v>
+        <v>1.35046684741974</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36376452445984</v>
+        <v>1.36376440525055</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.35046672821045</v>
+        <v>1.35046684741974</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.32682621479034</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.34307909011841</v>
+        <v>1.34307897090912</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.34898912906647</v>
+        <v>1.34898924827576</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.32682621479034</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.34307909011841</v>
+        <v>1.34307897090912</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.45980441570282</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.3681972026825</v>
+        <v>1.36819708347321</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.42286586761475</v>
+        <v>1.42286598682404</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.34898912906647</v>
+        <v>1.34898924827576</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.27658998966217</v>
+        <v>1.27659010887146</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862329006195</v>
+        <v>1.20862340927124</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.32682621479034</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.65853261947632</v>
+        <v>1.65853273868561</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.68438947200775</v>
+        <v>1.68438959121704</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.70655250549316</v>
+        <v>1.70655274391174</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.70655250549316</v>
+        <v>1.70655274391174</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.71024644374847</v>
+        <v>1.71024656295776</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.65114498138428</v>
+        <v>1.65114486217499</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64375734329224</v>
+        <v>1.64375746250153</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.64375734329224</v>
+        <v>1.64375746250153</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.60681879520416</v>
+        <v>1.60681891441345</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924847602844</v>
+        <v>1.52924835681915</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420679092407</v>
+        <v>1.61420667171478</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.63267588615417</v>
+        <v>1.63267600536346</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.677001953125</v>
+        <v>1.67700183391571</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.40981030464172</v>
+        <v>1.40981018543243</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.40981030464172</v>
+        <v>1.40981018543243</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609040737152</v>
+        <v>1.37609028816223</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.37769615650177</v>
+        <v>1.37769603729248</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.36645615100861</v>
+        <v>1.3664562702179</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.27653670310974</v>
+        <v>1.27653658390045</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688411712646</v>
+        <v>1.48688399791718</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082698345184</v>
+        <v>1.47082710266113</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820455551147</v>
+        <v>1.40820443630219</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.38893604278564</v>
+        <v>1.38893616199493</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.38893604278564</v>
+        <v>1.38893616199493</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.36645615100861</v>
+        <v>1.3664562702179</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558200836182</v>
+        <v>1.34558188915253</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.25726807117462</v>
+        <v>1.25726819038391</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.22836542129517</v>
+        <v>1.22836530208588</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.15129160881042</v>
+        <v>1.15129148960114</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.25726807117462</v>
+        <v>1.25726819038391</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267415046692</v>
+        <v>1.20267403125763</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.22836542129517</v>
+        <v>1.22836530208588</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741084575653</v>
+        <v>1.29741072654724</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.25726807117462</v>
+        <v>1.25726819038391</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.3327362537384</v>
+        <v>1.33273613452911</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383360385895</v>
+        <v>1.30383348464966</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.25726807117462</v>
+        <v>1.25726819038391</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.1866170167923</v>
+        <v>1.18661713600159</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.22836542129517</v>
+        <v>1.22836530208588</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.40981030464172</v>
+        <v>1.40981018543243</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828486919403</v>
+        <v>1.31828498840332</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206698894501</v>
+        <v>1.48206686973572</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.47885572910309</v>
+        <v>1.4788556098938</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.5029411315918</v>
+        <v>1.50294125080109</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.45958709716797</v>
+        <v>1.45958697795868</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>2.22000002861023</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>51094</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.09500002861023</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.08999991416931</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>265902</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.13499999046326</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.08999991416931</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.10500001907349</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.10500001907349</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.10500001907349</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>276522</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.13499999046326</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.13499999046326</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>2.13499999046326</v>
       </c>
       <c r="D2737" t="n">
-        <v>2.09500002861023</v>
+        <v>2.08500003814697</v>
       </c>
       <c r="E2737" t="n">
         <v>2.13499999046326</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.08500003814697</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>156103</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.11500000953674</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.0699999332428</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.07999992370605</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>179188</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.10500001907349</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>165019</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -447,7 +447,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86872553825378</v>
+        <v>2.86872577667236</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525827407837</v>
+        <v>2.80525803565979</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7709858417511</v>
+        <v>2.77098608016968</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G8" t="n">
-        <v>2.73290538787842</v>
+        <v>2.732905626297</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928292274475</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5006148815155</v>
+        <v>2.50061464309692</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66436052322388</v>
+        <v>2.66436076164246</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915926933289</v>
+        <v>2.56915903091431</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5628125667572</v>
+        <v>2.56281280517578</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965498924255</v>
+        <v>2.51965475082397</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.53869485855103</v>
+        <v>2.5386950969696</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662106513977</v>
+        <v>2.56662082672119</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696158409119</v>
+        <v>2.50696134567261</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107905387878</v>
+        <v>2.53107881546021</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349384307861</v>
+        <v>2.44349360466003</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2860951423645</v>
+        <v>2.28609538078308</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482580184937</v>
+        <v>2.28482556343079</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135806083679</v>
+        <v>2.22135829925537</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798361778259</v>
+        <v>2.32798337936401</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.48665189743042</v>
+        <v>2.486652135849</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.61866354942322</v>
+        <v>2.6186637878418</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928292274475</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58566069602966</v>
+        <v>2.58566093444824</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66055274009705</v>
+        <v>2.66055226325989</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>2.63389611244202</v>
+        <v>2.6338963508606</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658999443054</v>
+        <v>2.64658951759338</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213152885437</v>
+        <v>2.68213129043579</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.69355535507202</v>
+        <v>2.6935555934906</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G50" t="n">
-        <v>2.65039777755737</v>
+        <v>2.65039753913879</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.74179077148438</v>
+        <v>2.7417905330658</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.9017288684845</v>
+        <v>2.90172815322876</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169708251953</v>
+        <v>2.98169732093811</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504140853882</v>
+        <v>2.95504093170166</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835394859314</v>
+        <v>3.00835371017456</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104735374451</v>
+        <v>3.02104711532593</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327587127686</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200724601746</v>
+        <v>3.00200700759888</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.91949915885925</v>
+        <v>2.91949939727783</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711520195007</v>
+        <v>2.92711567878723</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819874763489</v>
+        <v>2.99819898605347</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G70" t="n">
-        <v>3.0603973865509</v>
+        <v>3.06039714813232</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>2.98931360244751</v>
+        <v>2.98931384086609</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G75" t="n">
-        <v>3.12894225120544</v>
+        <v>3.12894129753113</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702222824097</v>
+        <v>3.16702198982239</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702222824097</v>
+        <v>3.16702198982239</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244058609009</v>
+        <v>3.11244034767151</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086108207703</v>
+        <v>3.09086132049561</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959245681763</v>
+        <v>3.08959197998047</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327587127686</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03054022789001</v>
+        <v>3.03053951263428</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398096084595</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974303245544</v>
+        <v>2.94974327087402</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398096084595</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92722630500793</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G98" t="n">
-        <v>3.08881950378418</v>
+        <v>3.0888192653656</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.11266088485718</v>
+        <v>3.1126606464386</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941554069519</v>
+        <v>3.09941577911377</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G101" t="n">
-        <v>3.07822322845459</v>
+        <v>3.07822299003601</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140480995178</v>
+        <v>3.20140552520752</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.17888784408569</v>
+        <v>3.17888808250427</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>3.1921329498291</v>
+        <v>3.19213342666626</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584294319153</v>
+        <v>3.23584270477295</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.23186993598938</v>
+        <v>3.2318696975708</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610714912415</v>
+        <v>3.19610738754272</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802760124207</v>
+        <v>3.20802783966064</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829133033752</v>
+        <v>3.16829180717468</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.15901970863342</v>
+        <v>3.159019947052</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133646965027</v>
+        <v>3.11133670806885</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G113" t="n">
-        <v>3.08881950378418</v>
+        <v>3.0888192653656</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.25</v>
       </c>
       <c r="G115" t="n">
-        <v>2.81464028358459</v>
+        <v>2.81464052200317</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516821861267</v>
+        <v>2.73516798019409</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>2.69543194770813</v>
+        <v>2.69543242454529</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8676221370697</v>
+        <v>2.86762189865112</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398096084595</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596517562866</v>
+        <v>2.81596493721008</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841356277466</v>
+        <v>2.74841332435608</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047117233276</v>
+        <v>2.94047141075134</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152656555176</v>
+        <v>2.78152680397034</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802230834961</v>
+        <v>3.00802254676819</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>2.95371651649475</v>
+        <v>2.95371675491333</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.91530513763428</v>
+        <v>2.9153048992157</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397590637207</v>
+        <v>2.71397566795349</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="n">
-        <v>2.69940590858459</v>
+        <v>2.69940567016602</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112639427185</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112639427185</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60138988494873</v>
+        <v>2.60139012336731</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.5417857170105</v>
+        <v>2.54178547859192</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152151107788</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.6424503326416</v>
+        <v>2.64245080947876</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>2.67556428909302</v>
+        <v>2.67556381225586</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.72192311286926</v>
+        <v>2.7219226360321</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71530032157898</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="n">
-        <v>2.7338433265686</v>
+        <v>2.73384356498718</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G164" t="n">
-        <v>2.69543194770813</v>
+        <v>2.69543242454529</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="n">
-        <v>2.56562733650208</v>
+        <v>2.56562757492065</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907288551331</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754826545715</v>
+        <v>2.57754850387573</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>2.56430315971375</v>
+        <v>2.56430292129517</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979620933533</v>
+        <v>2.43979644775391</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.41198134422302</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36827158927917</v>
+        <v>2.3682713508606</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40270948410034</v>
+        <v>2.40270924568176</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761226654053</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992831230164</v>
+        <v>2.41992855072021</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="n">
-        <v>2.2782027721405</v>
+        <v>2.27820301055908</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="n">
-        <v>2.27290511131287</v>
+        <v>2.27290487289429</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.2861499786377</v>
+        <v>2.28615021705627</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="n">
-        <v>2.43449831008911</v>
+        <v>2.43449854850769</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.42655110359192</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741110801697</v>
+        <v>2.39741158485413</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211320877075</v>
+        <v>2.39211297035217</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.42655110359192</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.45833969116211</v>
+        <v>2.45833992958069</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337386131287</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.4543662071228</v>
+        <v>2.45436644554138</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="n">
-        <v>2.45304179191589</v>
+        <v>2.45304203033447</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="n">
-        <v>2.48350596427917</v>
+        <v>2.48350620269775</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503129959106</v>
+        <v>2.55503106117249</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152151107788</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>2.5444347858429</v>
+        <v>2.54443454742432</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264595985413</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>2.51661992073059</v>
+        <v>2.51661968231201</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496295928955</v>
+        <v>2.46496272087097</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416600227356</v>
+        <v>2.38416624069214</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495790481567</v>
+        <v>2.26495766639709</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="n">
-        <v>2.22389721870422</v>
+        <v>2.22389698028564</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548560142517</v>
+        <v>2.18548536300659</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>2.25171208381653</v>
+        <v>2.25171232223511</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608693122864</v>
+        <v>2.39608669281006</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="n">
-        <v>2.41198134422302</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="n">
-        <v>2.48350596427917</v>
+        <v>2.48350620269775</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="n">
-        <v>2.49145317077637</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="n">
-        <v>2.50204968452454</v>
+        <v>2.50204992294312</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.5325140953064</v>
+        <v>2.53251385688782</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264595985413</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="n">
-        <v>2.50204968452454</v>
+        <v>2.50204992294312</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337386131287</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.53648781776428</v>
+        <v>2.53648734092712</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960105895996</v>
+        <v>2.56960129737854</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="n">
-        <v>2.55768036842346</v>
+        <v>2.55768013000488</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="n">
-        <v>2.55768036842346</v>
+        <v>2.55768013000488</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.5205934047699</v>
+        <v>2.52059316635132</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072526931763</v>
+        <v>2.50072503089905</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363806724548</v>
+        <v>2.4636378288269</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="n">
-        <v>2.4239022731781</v>
+        <v>2.42390203475952</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138506889343</v>
+        <v>2.40138459205627</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356972694397</v>
+        <v>2.37356996536255</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019204139709</v>
+        <v>2.38019227981567</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.3656222820282</v>
+        <v>2.36562275886536</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>2.36164903640747</v>
+        <v>2.36164855957031</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="n">
-        <v>2.32853507995605</v>
+        <v>2.32853555679321</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>2.32191276550293</v>
+        <v>2.32191300392151</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985973358154</v>
+        <v>2.32985997200012</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="n">
-        <v>2.35502624511719</v>
+        <v>2.35502600669861</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.4172797203064</v>
+        <v>2.41727948188782</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886762619019</v>
+        <v>2.37886786460876</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.36429786682129</v>
+        <v>2.36429762840271</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807596206665</v>
+        <v>2.49807620048523</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761226654053</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49145317077637</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622408866882</v>
+        <v>2.57622361183167</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60006546974182</v>
+        <v>2.6000657081604</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211802482605</v>
+        <v>2.59211850166321</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71530032157898</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642887115479</v>
+        <v>2.84642934799194</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="n">
-        <v>2.86099886894226</v>
+        <v>2.86099934577942</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444489479065</v>
+        <v>2.94444513320923</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="n">
-        <v>2.93914723396301</v>
+        <v>2.93914699554443</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.9921281337738</v>
+        <v>2.99212861061096</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.9947772026062</v>
+        <v>2.99477744102478</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="n">
-        <v>3.04510951042175</v>
+        <v>3.04510998725891</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="n">
-        <v>3.05040764808655</v>
+        <v>3.05040788650513</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.00404858589172</v>
+        <v>3.00404906272888</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504140853882</v>
+        <v>2.95504093170166</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093605995178</v>
+        <v>2.9709358215332</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>2.92722630500793</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97225999832153</v>
+        <v>2.97225975990295</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067185401917</v>
+        <v>3.01067137718201</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="n">
-        <v>2.99875068664551</v>
+        <v>2.99875044822693</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.5</v>
       </c>
       <c r="G340" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967974662781</v>
+        <v>3.05967926979065</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.0517315864563</v>
+        <v>3.05173206329346</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484554290771</v>
+        <v>3.08484578132629</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10471415519714</v>
+        <v>3.10471391677856</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637016296387</v>
+        <v>3.15637040138245</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967974662781</v>
+        <v>3.05967926979065</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981161117554</v>
+        <v>3.03981137275696</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>4.5</v>
       </c>
       <c r="G351" t="n">
-        <v>2.98020792007446</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887787818909</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772747039795</v>
+        <v>2.91772723197937</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093494415283</v>
+        <v>2.89093470573425</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897298812866</v>
+        <v>2.89897274971008</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.82395315170288</v>
+        <v>2.82395339012146</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.8333306312561</v>
+        <v>2.83333086967468</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644347190857</v>
+        <v>2.78644323348999</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276330947876</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>2.69936728477478</v>
+        <v>2.6993670463562</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>2.67257404327393</v>
+        <v>2.67257452011108</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="n">
-        <v>2.72080087661743</v>
+        <v>2.72080111503601</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="n">
-        <v>2.70204615592957</v>
+        <v>2.70204639434814</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.656498670578</v>
+        <v>2.65649843215942</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>2.65247988700867</v>
+        <v>2.65247964859009</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="n">
-        <v>2.66855525970459</v>
+        <v>2.66855549812317</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621500968933</v>
+        <v>2.59621477127075</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="n">
-        <v>2.53727102279663</v>
+        <v>2.53727149963379</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>2.5654034614563</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625444412231</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G393" t="n">
-        <v>2.71544241905212</v>
+        <v>2.7154426574707</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="n">
-        <v>2.72214102745056</v>
+        <v>2.72214078903198</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946167945862</v>
+        <v>2.71946144104004</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63238525390625</v>
+        <v>2.63238549232483</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="n">
-        <v>2.64310240745544</v>
+        <v>2.64310216903687</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.63104557991028</v>
+        <v>2.63104581832886</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381932258606</v>
+        <v>2.65381908416748</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="n">
-        <v>2.6631965637207</v>
+        <v>2.66319704055786</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="n">
-        <v>2.67257404327393</v>
+        <v>2.67257452011108</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338582992554</v>
+        <v>2.70338559150696</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.56138443946838</v>
+        <v>2.5613842010498</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459167480469</v>
+        <v>2.53459143638611</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172306060791</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G426" t="n">
-        <v>2.48770451545715</v>
+        <v>2.48770475387573</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200719833374</v>
+        <v>2.55200695991516</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G431" t="n">
-        <v>2.58951687812805</v>
+        <v>2.58951663970947</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7167820930481</v>
+        <v>2.71678233146667</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189656257629</v>
+        <v>2.81189608573914</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323599815369</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>2.92040681838989</v>
+        <v>2.92040705680847</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>2.88021779060364</v>
+        <v>2.88021802902222</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682200431824</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323599815369</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682200431824</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663202285767</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625444412231</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625444412231</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663202285767</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868885040283</v>
+        <v>2.83868932723999</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887787818909</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="n">
-        <v>2.95523738861084</v>
+        <v>2.95523762702942</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567088127136</v>
+        <v>2.90567111968994</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.84002828598022</v>
+        <v>2.8400285243988</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="n">
-        <v>2.86280274391174</v>
+        <v>2.86280250549316</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710494995117</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92040681838989</v>
+        <v>2.92040705680847</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710494995117</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370892524719</v>
+        <v>2.91370868682861</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648290634155</v>
+        <v>2.93648242950439</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.9324631690979</v>
+        <v>2.93246364593506</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>2.90835022926331</v>
+        <v>2.90835046768188</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031266212463</v>
+        <v>2.90031242370605</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>2.88021779060364</v>
+        <v>2.88021802902222</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270787239075</v>
+        <v>2.84270763397217</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314160346985</v>
+        <v>2.79314136505127</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76233005523682</v>
+        <v>2.76232981681824</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.58817744255066</v>
+        <v>2.58817720413208</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300777435303</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G487" t="n">
-        <v>2.63238525390625</v>
+        <v>2.63238549232483</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.66587615013123</v>
+        <v>2.6658763885498</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>2.65247988700867</v>
+        <v>2.65247964859009</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266891479492</v>
+        <v>2.69266867637634</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927241325378</v>
+        <v>2.67927265167236</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.63238525390625</v>
+        <v>2.63238549232483</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.62434720993042</v>
+        <v>2.624347448349</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276330947876</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300777435303</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.56138443946838</v>
+        <v>2.5613842010498</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449704170227</v>
+        <v>2.51449728012085</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119493484497</v>
+        <v>2.52119541168213</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884716033936</v>
+        <v>2.58884692192078</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526186943054</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.52856349945068</v>
+        <v>2.52856373786926</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59554529190063</v>
+        <v>2.59554505348206</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578151702881</v>
+        <v>2.64578175544739</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>2.5654034614563</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172306060791</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526186943054</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818496704102</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148731231689</v>
+        <v>2.44148683547974</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827960014343</v>
+        <v>2.46827983856201</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G546" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818496704102</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>2.26398515701294</v>
+        <v>2.26398539543152</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700336456299</v>
+        <v>2.19700312614441</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365453720093</v>
+        <v>2.19365429878235</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337087631226</v>
+        <v>2.1333703994751</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.2773814201355</v>
+        <v>2.27738165855408</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695616722107</v>
+        <v>2.18695640563965</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.25728702545166</v>
+        <v>2.25728726387024</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.25058889389038</v>
+        <v>2.25058913230896</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.33096718788147</v>
+        <v>2.33096694946289</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41134524345398</v>
+        <v>2.41134548187256</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483637809753</v>
+        <v>2.44483590126038</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148731231689</v>
+        <v>2.44148683547974</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.42474126815796</v>
+        <v>2.42474174499512</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.45153450965881</v>
+        <v>2.45153427124023</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.44818520545959</v>
+        <v>2.44818496704102</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507236480713</v>
+        <v>2.49507260322571</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172306060791</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="n">
-        <v>2.45153450965881</v>
+        <v>2.45153427124023</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507236480713</v>
+        <v>2.49507260322571</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="n">
-        <v>2.54028534889221</v>
+        <v>2.54028511047363</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.43702173233032</v>
+        <v>2.43702149391174</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.31998944282532</v>
+        <v>2.3199896812439</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310534477234</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393607139587</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556847572327</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>2.20295715332031</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.20295715332031</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770498275757</v>
+        <v>2.24770522117615</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>2.32687401771545</v>
+        <v>2.32687377929688</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408450126648</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.34752655029297</v>
+        <v>2.34752631187439</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28212594985962</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915800094604</v>
+        <v>2.39915776252747</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473703384399</v>
+        <v>2.36473679542542</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310534477234</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.29933643341064</v>
+        <v>2.29933667182922</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27524209022522</v>
+        <v>2.27524185180664</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.33719992637634</v>
+        <v>2.33720016479492</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556847572327</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.31998944282532</v>
+        <v>2.3199896812439</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082064628601</v>
+        <v>2.24082088470459</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>2.19263076782227</v>
+        <v>2.19263052940369</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607329368591</v>
+        <v>2.19607305526733</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.14444160461426</v>
+        <v>2.1444411277771</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15820956230164</v>
+        <v>2.15820980072021</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23049449920654</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393607139587</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="n">
-        <v>2.29933643341064</v>
+        <v>2.29933667182922</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G669" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>2.15476775169373</v>
+        <v>2.15476751327515</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11002016067505</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690449714661</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>2.13067269325256</v>
+        <v>2.13067293167114</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690449714661</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G693" t="n">
-        <v>2.12723088264465</v>
+        <v>2.1272304058075</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378883361816</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>2.13067269325256</v>
+        <v>2.13067293167114</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672558784485</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672558784485</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>2.08248353004456</v>
+        <v>2.0824830532074</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512449741364</v>
+        <v>1.95512461662292</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.94135618209839</v>
+        <v>1.94135594367981</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841859340668</v>
+        <v>1.84841895103455</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="n">
-        <v>1.81399738788605</v>
+        <v>1.81399762630463</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.88284003734589</v>
+        <v>1.8828399181366</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070329189301</v>
+        <v>1.92070317268372</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414569854736</v>
+        <v>1.92414557933807</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921931743622</v>
+        <v>1.97921943664551</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298810958862</v>
+        <v>1.99298799037933</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610377311707</v>
+        <v>1.98610353469849</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429341316223</v>
+        <v>2.03429365158081</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="n">
-        <v>2.05838823318481</v>
+        <v>2.05838847160339</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>2.04806208610535</v>
+        <v>2.04806160926819</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>2.04461979866028</v>
+        <v>2.0446195602417</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889317035675</v>
+        <v>1.96889293193817</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758762836456</v>
+        <v>1.92758774757385</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200859546661</v>
+        <v>1.96200895309448</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="n">
-        <v>2.15476775169373</v>
+        <v>2.15476751327515</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672558784485</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="n">
-        <v>2.23049449920654</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15476775169373</v>
+        <v>2.15476751327515</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378883361816</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.28212594985962</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408450126648</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.49209523200989</v>
+        <v>2.49209570884705</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046378135681</v>
+        <v>2.44046354293823</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>2.53684282302856</v>
+        <v>2.53684306144714</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307486534119</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307486534119</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093788146973</v>
+        <v>2.56093764305115</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="n">
-        <v>2.6056854724884</v>
+        <v>2.60568571090698</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945366859436</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.64354848861694</v>
+        <v>2.64354872703552</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945366859436</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224342346191</v>
+        <v>2.60224318504333</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>2.59535884857178</v>
+        <v>2.59535908699036</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880113601685</v>
+        <v>2.59880137443542</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>2.56437969207764</v>
+        <v>2.56437993049622</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G801" t="n">
-        <v>2.69862294197083</v>
+        <v>2.69862270355225</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>2.70206475257874</v>
+        <v>2.70206451416016</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>2.68485450744629</v>
+        <v>2.68485403060913</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090716362</v>
+        <v>2.77090740203857</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.71239113807678</v>
+        <v>2.71239137649536</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="n">
-        <v>2.72960186004639</v>
+        <v>2.72960162162781</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681258201599</v>
+        <v>2.74681234359741</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.72960186004639</v>
+        <v>2.72960162162781</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>2.72615957260132</v>
+        <v>2.72615933418274</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>2.76746511459351</v>
+        <v>2.76746487617493</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G821" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>2.66420149803162</v>
+        <v>2.66420125961304</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>2.59535884857178</v>
+        <v>2.59535908699036</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="n">
-        <v>2.51619029045105</v>
+        <v>2.51619005203247</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.42669534683228</v>
+        <v>2.42669558525085</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50586414337158</v>
+        <v>2.505863904953</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>2.49897956848145</v>
+        <v>2.49897980690002</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013691902161</v>
+        <v>2.43013739585876</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>2.31654715538025</v>
+        <v>2.31654739379883</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031582832336</v>
+        <v>2.33031606674194</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>2.18230438232422</v>
+        <v>2.1823046207428</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>2.20295715332031</v>
+        <v>2.20295739173889</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11002016067505</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085136413574</v>
+        <v>2.03085112571716</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>2.13748216629028</v>
+        <v>2.1374819278717</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06153082847595</v>
+        <v>2.06153130531311</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.94217932224274</v>
+        <v>1.94217920303345</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579601287842</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026277542114</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579601287842</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>1.93132925033569</v>
+        <v>1.93132889270782</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.9023951292038</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G886" t="n">
-        <v>1.89154529571533</v>
+        <v>1.89154541492462</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.89154529571533</v>
+        <v>1.89154541492462</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069486618042</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.9023951292038</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93132925033569</v>
+        <v>1.93132889270782</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.83006119728088</v>
+        <v>1.83006083965302</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069486618042</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.9023951292038</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.86261141300201</v>
+        <v>1.86261165142059</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431179523468</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474364757538</v>
+        <v>1.80474400520325</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199149608612</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G918" t="n">
-        <v>1.6817752122879</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327365875244</v>
+        <v>1.57327377796173</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.66369163990021</v>
+        <v>1.6636917591095</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.59135746955872</v>
+        <v>1.59135735034943</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.59859073162079</v>
+        <v>1.59859085083008</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944092273712</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>1.59497404098511</v>
+        <v>1.59497392177582</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>1.61305773258209</v>
+        <v>1.6130576133728</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G939" t="n">
-        <v>1.72517573833466</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.74687659740448</v>
+        <v>1.7468763589859</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>1.61305773258209</v>
+        <v>1.6130576133728</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>1.61305773258209</v>
+        <v>1.6130576133728</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64560806751251</v>
+        <v>1.64560830593109</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.69985890388489</v>
+        <v>1.69985902309418</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.6275247335434</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G956" t="n">
-        <v>1.63114142417908</v>
+        <v>1.63114130496979</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199149608612</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G959" t="n">
-        <v>1.63475787639618</v>
+        <v>1.63475811481476</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944092273712</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837480545044</v>
+        <v>1.63837492465973</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G963" t="n">
-        <v>1.6817752122879</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624221324921</v>
+        <v>1.6962423324585</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G974" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730856895447</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G977" t="n">
-        <v>1.6817752122879</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.7794269323349</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134312152863</v>
+        <v>1.76134300231934</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G986" t="n">
-        <v>1.72517573833466</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>1.72879266738892</v>
+        <v>1.72879278659821</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.7794269323349</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666043281555</v>
+        <v>1.78666031360626</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666043281555</v>
+        <v>1.78666031360626</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984479427338</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G996" t="n">
-        <v>2.01451373100281</v>
+        <v>2.01451396942139</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.93494582176208</v>
+        <v>1.9349457025528</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.06153082847595</v>
+        <v>2.06153130531311</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.05429768562317</v>
+        <v>2.05429792404175</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.04344749450684</v>
+        <v>2.04344773292542</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281346797943</v>
+        <v>1.99281334877014</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99643003940582</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579601287842</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.93132925033569</v>
+        <v>1.93132889270782</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346172332764</v>
+        <v>1.87346148490906</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814476966858</v>
+        <v>1.84814465045929</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984479427338</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728058815002</v>
+        <v>2.00728034973145</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.98558008670807</v>
+        <v>1.98557996749878</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.98558008670807</v>
+        <v>1.98557996749878</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984479427338</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431179523468</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474364757538</v>
+        <v>1.80474400520325</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.72517573833466</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964297771454</v>
+        <v>1.73964273929596</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77581000328064</v>
+        <v>1.77581012248993</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.7794269323349</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.7794269323349</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899460315704</v>
+        <v>1.85899472236633</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.81921064853668</v>
+        <v>1.81921076774597</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644426822662</v>
+        <v>1.82644414901733</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176122188568</v>
+        <v>1.85176134109497</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.7794269323349</v>
+        <v>1.77942669391632</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965720653534</v>
+        <v>1.56965708732605</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.5117894411087</v>
+        <v>1.51178932189941</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285555839539</v>
+        <v>1.48285567760468</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448083400726</v>
+        <v>1.38448095321655</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412856578827</v>
+        <v>1.01412868499756</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.07922959327698</v>
+        <v>1.07922947406769</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.23547196388245</v>
+        <v>1.23547208309174</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.17760443687439</v>
+        <v>1.17760455608368</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968530654907</v>
+        <v>1.22968518733978</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.20219814777374</v>
+        <v>1.20219802856445</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.17181754112244</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.20509159564972</v>
+        <v>1.20509147644043</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.20219814777374</v>
+        <v>1.20219802856445</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.17181754112244</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.14288401603699</v>
+        <v>1.14288377761841</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156388282776</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.15590405464172</v>
+        <v>1.15590417385101</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.15590405464172</v>
+        <v>1.15590417385101</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318927764893</v>
+        <v>1.05318915843964</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.02714884281158</v>
+        <v>1.02714896202087</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978851318359</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428243160248</v>
+        <v>0.992428183555603</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.02859556674957</v>
+        <v>1.02859568595886</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011739730835</v>
+        <v>1.15011727809906</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.13565063476562</v>
+        <v>1.13565051555634</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.17181754112244</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.19641137123108</v>
+        <v>1.19641149044037</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.18917787075043</v>
+        <v>1.18917810916901</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.09658992290497</v>
+        <v>1.09658980369568</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212292194366</v>
+        <v>1.08212304115295</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.12263023853302</v>
+        <v>1.12263035774231</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382330417633</v>
+        <v>1.10382318496704</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237669944763</v>
+        <v>1.10237658023834</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.0560827255249</v>
+        <v>1.05608260631561</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.07633626461029</v>
+        <v>1.07633638381958</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.060422539711</v>
+        <v>1.06042265892029</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156388282776</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.08790981769562</v>
+        <v>1.08790969848633</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501648902893</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501648902893</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.0748895406723</v>
+        <v>1.07488965988159</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846861839294</v>
+        <v>1.01846873760223</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.0068953037262</v>
+        <v>1.00689518451691</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088369369507</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.01702213287354</v>
+        <v>1.01702201366425</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088369369507</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.01702213287354</v>
+        <v>1.01702201366425</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.972174763679504</v>
+        <v>0.97217470407486</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.96783459186554</v>
+        <v>0.967834711074829</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047934532166</v>
+        <v>0.962047755718231</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.963494539260864</v>
+        <v>0.963494658470154</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880610942841</v>
+        <v>0.925880670547485</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.930220723152161</v>
+        <v>0.930220663547516</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.930220723152161</v>
+        <v>0.930220663547516</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.921540677547455</v>
+        <v>0.921540498733521</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.898393571376801</v>
+        <v>0.898393511772156</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160011291504</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.886819958686829</v>
+        <v>0.886820018291473</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093774795532</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901286900043488</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.88971346616745</v>
+        <v>0.88971334695816</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093774795532</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928773999214172</v>
+        <v>0.928774058818817</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951920986175537</v>
+        <v>0.951921045780182</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753901004791</v>
+        <v>0.915753841400146</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.81737893819809</v>
+        <v>0.817379057407379</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871681213379</v>
+        <v>0.776871740818024</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024371623993</v>
+        <v>0.732024312019348</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191695213318</v>
+        <v>0.768191576004028</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079320430756</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.850652813911438</v>
+        <v>0.850652873516083</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.895500183105469</v>
+        <v>0.895500242710114</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901286900043488</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.863673031330109</v>
+        <v>0.863672971725464</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.886819958686829</v>
+        <v>0.886820018291473</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.895500183105469</v>
+        <v>0.895500242710114</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.894053339958191</v>
+        <v>0.89405345916748</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.886819958686829</v>
+        <v>0.886820018291473</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.88971346616745</v>
+        <v>0.88971334695816</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119695663452</v>
+        <v>0.865119814872742</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.862226247787476</v>
+        <v>0.862226366996765</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520400524139</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733623981476</v>
+        <v>0.902733564376831</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160011291504</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013203144073</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.84920608997345</v>
+        <v>0.849206149578094</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079320430756</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.843419373035431</v>
+        <v>0.843419313430786</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.836186051368713</v>
+        <v>0.836185932159424</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845819950104</v>
+        <v>0.831845879554749</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312761306763</v>
+        <v>0.846312701702118</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119695663452</v>
+        <v>0.865119814872742</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.878139913082123</v>
+        <v>0.878139853477478</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.946134090423584</v>
+        <v>0.946134209632874</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978851318359</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408025741577</v>
+        <v>0.979408085346222</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778286933899</v>
+        <v>1.07778298854828</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768414974213</v>
+        <v>0.996768534183502</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884922504425</v>
+        <v>1.04884910583496</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.07922959327698</v>
+        <v>1.07922947406769</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.21955835819244</v>
+        <v>1.21955847740173</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458415985107</v>
+        <v>1.16458427906036</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.14288401603699</v>
+        <v>1.14288377761841</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049788475037</v>
+        <v>1.18049776554108</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.18339121341705</v>
+        <v>1.18339109420776</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.17181754112244</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156388282776</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491304397583</v>
+        <v>1.30491292476654</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.27453255653381</v>
+        <v>1.27453243732452</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.29189276695251</v>
+        <v>1.2918928861618</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.33674013614655</v>
+        <v>1.33674025535583</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030534267426</v>
+        <v>1.45030522346497</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.429328083992</v>
+        <v>1.42932820320129</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.36376452445984</v>
+        <v>1.36376440525055</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.43911874294281</v>
+        <v>1.4391188621521</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537161827087</v>
+        <v>1.45537173748016</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.45684933662415</v>
+        <v>1.45684921741486</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.42877602577209</v>
+        <v>1.42877614498138</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.36671960353851</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.33273637294769</v>
+        <v>1.3327362537384</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.2618145942688</v>
+        <v>1.26181471347809</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.23817420005798</v>
+        <v>1.23817408084869</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.18646025657654</v>
+        <v>1.18646037578583</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.21010100841522</v>
+        <v>1.21010088920593</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.21896624565125</v>
+        <v>1.21896612644196</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.18498277664185</v>
+        <v>1.18498289585114</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.16134226322174</v>
+        <v>1.16134238243103</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.19237041473389</v>
+        <v>1.19237053394318</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.14065682888031</v>
+        <v>1.1406569480896</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.18350517749786</v>
+        <v>1.18350529670715</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.27067995071411</v>
+        <v>1.27067983150482</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.25738215446472</v>
+        <v>1.25738203525543</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.2618145942688</v>
+        <v>1.26181471347809</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614066123962</v>
+        <v>1.30614078044891</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.36671960353851</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.25738215446472</v>
+        <v>1.25738203525543</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.25885963439941</v>
+        <v>1.25885951519012</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479267597198</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.43911874294281</v>
+        <v>1.4391188621521</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.54771757125854</v>
+        <v>1.54771769046783</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.55879902839661</v>
+        <v>1.55879890918732</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.55879902839661</v>
+        <v>1.55879890918732</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.44798398017883</v>
+        <v>1.44798409938812</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.42877602577209</v>
+        <v>1.42877614498138</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36376452445984</v>
+        <v>1.36376440525055</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816713809967</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.50708556175232</v>
+        <v>1.50708544254303</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.50708556175232</v>
+        <v>1.50708544254303</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.47605729103088</v>
+        <v>1.47605717182159</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816713809967</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.54402375221252</v>
+        <v>1.54402363300323</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.43025350570679</v>
+        <v>1.43025362491608</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479267597198</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.4169557094574</v>
+        <v>1.41695582866669</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862340927124</v>
+        <v>1.20862329006195</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.26920247077942</v>
+        <v>1.26920235157013</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.54771757125854</v>
+        <v>1.54771769046783</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62528812885284</v>
+        <v>1.62528824806213</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.6548388004303</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.69916486740112</v>
+        <v>1.69916498661041</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.72132802009583</v>
+        <v>1.72132790088654</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.71024656295776</v>
+        <v>1.71024644374847</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.69547128677368</v>
+        <v>1.69547116756439</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.66592049598694</v>
+        <v>1.66592037677765</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.55879902839661</v>
+        <v>1.55879890918732</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420667171478</v>
+        <v>1.61420655250549</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.6548388004303</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.66592049598694</v>
+        <v>1.66592037677765</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.63782060146332</v>
+        <v>1.63782048225403</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.64986336231232</v>
+        <v>1.64986348152161</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.63782060146332</v>
+        <v>1.63782048225403</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.63782060146332</v>
+        <v>1.63782048225403</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.64986336231232</v>
+        <v>1.64986348152161</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.63782060146332</v>
+        <v>1.63782048225403</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.44834721088409</v>
+        <v>1.4483470916748</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="n">
-        <v>1.31186211109161</v>
+        <v>1.31186199188232</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688399791718</v>
+        <v>1.48688411712646</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.44834721088409</v>
+        <v>1.4483470916748</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.4178386926651</v>
+        <v>1.41783881187439</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.32470786571503</v>
+        <v>1.32470774650574</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.33434200286865</v>
+        <v>1.33434188365936</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558200836182</v>
+        <v>1.34558188915253</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="n">
-        <v>1.27011382579803</v>
+        <v>1.27011370658875</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.22675967216492</v>
+        <v>1.22675979137421</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.23639392852783</v>
+        <v>1.23639380931854</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.23639392852783</v>
+        <v>1.23639380931854</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.28295934200287</v>
+        <v>1.28295946121216</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.25566232204437</v>
+        <v>1.25566244125366</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.23960530757904</v>
+        <v>1.23960542678833</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.16895425319672</v>
+        <v>1.16895413398743</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.16895425319672</v>
+        <v>1.16895413398743</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.13844573497772</v>
+        <v>1.13844585418701</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.13362872600555</v>
+        <v>1.13362860679626</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.17216563224792</v>
+        <v>1.17216575145721</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267415046692</v>
+        <v>1.20267403125763</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.1593199968338</v>
+        <v>1.15932011604309</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.26208519935608</v>
+        <v>1.26208531856537</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.33273637294769</v>
+        <v>1.3327362537384</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.34718763828278</v>
+        <v>1.34718751907349</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383360385895</v>
+        <v>1.30383348464966</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.3054393529892</v>
+        <v>1.30543947219849</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.31346786022186</v>
+        <v>1.31346774101257</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.32470786571503</v>
+        <v>1.32470774650574</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.32470786571503</v>
+        <v>1.32470774650574</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.28938210010529</v>
+        <v>1.28938221931458</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.23799967765808</v>
+        <v>1.23799979686737</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.22675967216492</v>
+        <v>1.22675979137421</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.2074910402298</v>
+        <v>1.20749115943909</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.19464552402496</v>
+        <v>1.19464564323425</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.23639392852783</v>
+        <v>1.23639380931854</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.23639392852783</v>
+        <v>1.23639380931854</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.23639392852783</v>
+        <v>1.23639380931854</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.23960530757904</v>
+        <v>1.23960542678833</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.2412109375</v>
+        <v>1.24121105670929</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.25405669212341</v>
+        <v>1.2540568113327</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.27332508563995</v>
+        <v>1.27332520484924</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.33434200286865</v>
+        <v>1.33434188365936</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.31507360935211</v>
+        <v>1.31507349014282</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.32470786571503</v>
+        <v>1.32470774650574</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.44995284080505</v>
+        <v>1.44995296001434</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.41302168369293</v>
+        <v>1.41302156448364</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.41302168369293</v>
+        <v>1.41302156448364</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.37127315998077</v>
+        <v>1.37127327919006</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.37930190563202</v>
+        <v>1.37930178642273</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828498840332</v>
+        <v>1.31828486919403</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206698894501</v>
+        <v>1.48206686973572</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.5334495306015</v>
+        <v>1.53344964981079</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.44995284080505</v>
+        <v>1.44995296001434</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.51899814605713</v>
+        <v>1.51899826526642</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>2.0699999332428</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>174987</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>2.0550000667572</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -421,7 +421,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85730123519897</v>
+        <v>2.8573009967804</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86872577667236</v>
+        <v>2.86872529983521</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525803565979</v>
+        <v>2.80525827407837</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76717758178711</v>
+        <v>2.76717782020569</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.77098608016968</v>
+        <v>2.7709858417511</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928292274475</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G13" t="n">
-        <v>2.546311378479</v>
+        <v>2.54631114006042</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.50061464309692</v>
+        <v>2.50061440467834</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915903091431</v>
+        <v>2.56915926933289</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965475082397</v>
+        <v>2.51965498924255</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662082672119</v>
+        <v>2.56662058830261</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G23" t="n">
-        <v>2.53361797332764</v>
+        <v>2.53361773490906</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696134567261</v>
+        <v>2.50696182250977</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107881546021</v>
+        <v>2.53107905387878</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349360466003</v>
+        <v>2.44349384307861</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28609538078308</v>
+        <v>2.2860951423645</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482556343079</v>
+        <v>2.28482604026794</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.13885068893433</v>
+        <v>2.13885045051575</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135829925537</v>
+        <v>2.22135806083679</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.486652135849</v>
+        <v>2.48665189743042</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6186637878418</v>
+        <v>2.61866402626038</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.55519676208496</v>
+        <v>2.55519652366638</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928292274475</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49553751945496</v>
+        <v>2.49553728103638</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>2.6338963508606</v>
+        <v>2.63389611244202</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658951759338</v>
+        <v>2.64658999443054</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213129043579</v>
+        <v>2.68213105201721</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6935555934906</v>
+        <v>2.69355535507202</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G50" t="n">
-        <v>2.65039753913879</v>
+        <v>2.65039777755737</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G52" t="n">
-        <v>2.76717758178711</v>
+        <v>2.76717782020569</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.7417905330658</v>
+        <v>2.74179077148438</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84333848953247</v>
+        <v>2.84333825111389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172815322876</v>
+        <v>2.9017288684845</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853950500488</v>
+        <v>2.93853998184204</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95757985115051</v>
+        <v>2.95757961273193</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169732093811</v>
+        <v>2.98169755935669</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504093170166</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>2.94869422912598</v>
+        <v>2.94869375228882</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104711532593</v>
+        <v>3.02104759216309</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423647880554</v>
+        <v>2.98423624038696</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711567878723</v>
+        <v>2.92711544036865</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182121276855</v>
+        <v>3.07182168960571</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798212051392</v>
+        <v>3.14798188209534</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.09847712516785</v>
+        <v>3.09847784042358</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244034767151</v>
+        <v>3.11244010925293</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086132049561</v>
+        <v>3.09086155891418</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959197998047</v>
+        <v>3.08959221839905</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374099731445</v>
+        <v>3.03374075889587</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G88" t="n">
-        <v>3.05912780761719</v>
+        <v>3.05912756919861</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053951263428</v>
+        <v>3.03053998947144</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974327087402</v>
+        <v>2.94974303245544</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424445152283</v>
+        <v>2.87424421310425</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.1126606464386</v>
+        <v>3.11266112327576</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941577911377</v>
+        <v>3.09941554069519</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140552520752</v>
+        <v>3.20140528678894</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.17888808250427</v>
+        <v>3.17888784408569</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>3.19213342666626</v>
+        <v>3.19213318824768</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584270477295</v>
+        <v>3.23584318161011</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610738754272</v>
+        <v>3.19610691070557</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802783966064</v>
+        <v>3.20802736282349</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133670806885</v>
+        <v>3.11133646965027</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516798019409</v>
+        <v>2.73516821861267</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>2.69543242454529</v>
+        <v>2.69543218612671</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85040283203125</v>
+        <v>2.85040259361267</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.86762189865112</v>
+        <v>2.86762166023254</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596493721008</v>
+        <v>2.8159646987915</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841332435608</v>
+        <v>2.74841380119324</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047141075134</v>
+        <v>2.94047117233276</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708867073059</v>
+        <v>2.74708843231201</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802254676819</v>
+        <v>3.00802230834961</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.9153048992157</v>
+        <v>2.91530513763428</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364336013794</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112639427185</v>
+        <v>2.64112591743469</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112639427185</v>
+        <v>2.64112591743469</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60139012336731</v>
+        <v>2.60138988494873</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.54178547859192</v>
+        <v>2.54178595542908</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152174949646</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159056663513</v>
+        <v>2.67159008979797</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245080947876</v>
+        <v>2.6424503326416</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.71530032157898</v>
+        <v>2.7153000831604</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73384356498718</v>
+        <v>2.7338433265686</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364336013794</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="n">
-        <v>2.66496777534485</v>
+        <v>2.66496801376343</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702033042908</v>
+        <v>2.65702056884766</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G164" t="n">
-        <v>2.69543242454529</v>
+        <v>2.69543218612671</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159056663513</v>
+        <v>2.67159008979797</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801243782043</v>
+        <v>2.60801267623901</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754850387573</v>
+        <v>2.57754826545715</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979644775391</v>
+        <v>2.43979668617249</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="n">
-        <v>2.3682713508606</v>
+        <v>2.36827158927917</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40270924568176</v>
+        <v>2.40270948410034</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761226654053</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>2.45039248466492</v>
+        <v>2.45039296150208</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>2.27158045768738</v>
+        <v>2.2715802192688</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="n">
-        <v>2.24641370773315</v>
+        <v>2.24641394615173</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.28615021705627</v>
+        <v>2.2861499786377</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.45039248466492</v>
+        <v>2.45039296150208</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655086517334</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36959600448608</v>
+        <v>2.36959624290466</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741158485413</v>
+        <v>2.39741134643555</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211297035217</v>
+        <v>2.39211320877075</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655086517334</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.45833992958069</v>
+        <v>2.45833969116211</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.50337386131287</v>
+        <v>2.50337409973145</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="n">
-        <v>2.45304203033447</v>
+        <v>2.45304155349731</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>2.44377017021179</v>
+        <v>2.44376993179321</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.45039248466492</v>
+        <v>2.45039296150208</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152174949646</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>2.51661968231201</v>
+        <v>2.51661944389343</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026062011719</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>2.3444299697876</v>
+        <v>2.34442973136902</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.2450897693634</v>
+        <v>2.24508929252625</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.2450897693634</v>
+        <v>2.24508929252625</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098418235779</v>
+        <v>2.26098370552063</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495766639709</v>
+        <v>2.26495742797852</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>2.22522163391113</v>
+        <v>2.22522139549255</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482580184937</v>
+        <v>2.28482604026794</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237717628479</v>
+        <v>2.35237669944763</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608669281006</v>
+        <v>2.39608693122864</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="n">
-        <v>2.44906830787659</v>
+        <v>2.44906806945801</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.45039248466492</v>
+        <v>2.45039296150208</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026062011719</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G251" t="n">
-        <v>2.50602316856384</v>
+        <v>2.50602340698242</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.47026085853577</v>
+        <v>2.47026062011719</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204968452454</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="n">
-        <v>2.54708385467529</v>
+        <v>2.54708409309387</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.54973316192627</v>
+        <v>2.54973292350769</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.53251385688782</v>
+        <v>2.5325140953064</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204968452454</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.50337386131287</v>
+        <v>2.50337409973145</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.53648734092712</v>
+        <v>2.5364875793457</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="n">
-        <v>2.55768013000488</v>
+        <v>2.55768036842346</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165385246277</v>
+        <v>2.56165409088135</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="n">
-        <v>2.55768013000488</v>
+        <v>2.55768036842346</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059316635132</v>
+        <v>2.5205934047699</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072503089905</v>
+        <v>2.50072550773621</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.4636378288269</v>
+        <v>2.46363830566406</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.44377017021179</v>
+        <v>2.44376993179321</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="n">
-        <v>2.42390203475952</v>
+        <v>2.42390179634094</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138459205627</v>
+        <v>2.40138483047485</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356996536255</v>
+        <v>2.37356948852539</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019227981567</v>
+        <v>2.38019251823425</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.36562275886536</v>
+        <v>2.36562252044678</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>2.36164855957031</v>
+        <v>2.36164903640747</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="n">
-        <v>2.32853555679321</v>
+        <v>2.32853531837463</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="n">
-        <v>2.35502600669861</v>
+        <v>2.35502624511719</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476227760315</v>
+        <v>2.39476203918457</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933203697205</v>
+        <v>2.40933227539062</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006065368652</v>
+        <v>2.40006041526794</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.40403389930725</v>
+        <v>2.40403413772583</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999183654785</v>
+        <v>2.30999207496643</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.36429762840271</v>
+        <v>2.36429786682129</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933203697205</v>
+        <v>2.40933227539062</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761226654053</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.54973316192627</v>
+        <v>2.54973292350769</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622361183167</v>
+        <v>2.57622385025024</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.6000657081604</v>
+        <v>2.60006546974182</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.7007303237915</v>
+        <v>2.70073008537292</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.71530032157898</v>
+        <v>2.7153000831604</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.82126331329346</v>
+        <v>2.82126307487488</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642934799194</v>
+        <v>2.84642910957336</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252420425415</v>
+        <v>2.93252396583557</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.0649778842926</v>
+        <v>3.06497716903687</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02789092063904</v>
+        <v>3.02789068222046</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="n">
-        <v>2.86099934577942</v>
+        <v>2.860999584198</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444513320923</v>
+        <v>2.94444465637207</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.99212861061096</v>
+        <v>2.99212837219238</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.99477744102478</v>
+        <v>2.99477696418762</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="n">
-        <v>3.04510998725891</v>
+        <v>3.04510974884033</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="n">
-        <v>3.05040788650513</v>
+        <v>3.05040764808655</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848671913147</v>
+        <v>3.03848695755005</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.00404906272888</v>
+        <v>3.0040488243103</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504093170166</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.9709358215332</v>
+        <v>2.97093558311462</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97225975990295</v>
+        <v>2.97225999832153</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067137718201</v>
+        <v>3.01067185401917</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967926979065</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173206329346</v>
+        <v>3.05173277854919</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484578132629</v>
+        <v>3.08484554290771</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637040138245</v>
+        <v>3.15637063980103</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967926979065</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981137275696</v>
+        <v>3.03981184959412</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>2.84775376319885</v>
+        <v>2.84775400161743</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772723197937</v>
+        <v>2.91772770881653</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="n">
-        <v>2.92308616638184</v>
+        <v>2.92308592796326</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093470573425</v>
+        <v>2.89093494415283</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897274971008</v>
+        <v>2.8989725112915</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.82395339012146</v>
+        <v>2.82395315170288</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.83333086967468</v>
+        <v>2.83333039283752</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.76768827438354</v>
+        <v>2.76768803596497</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="n">
-        <v>2.66989517211914</v>
+        <v>2.66989541053772</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>2.6993670463562</v>
+        <v>2.69936728477478</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68731045722961</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>2.67257452011108</v>
+        <v>2.67257404327393</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="n">
-        <v>2.70204639434814</v>
+        <v>2.70204615592957</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G376" t="n">
-        <v>2.6672158241272</v>
+        <v>2.66721558570862</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649843215942</v>
+        <v>2.65649890899658</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>2.56942224502563</v>
+        <v>2.56942248344421</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="n">
-        <v>2.53727149963379</v>
+        <v>2.53727126121521</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.74625444412231</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="n">
-        <v>2.72214078903198</v>
+        <v>2.72214102745056</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946144104004</v>
+        <v>2.7194619178772</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68731045722961</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63238549232483</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="n">
-        <v>2.64310216903687</v>
+        <v>2.64310193061829</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.63104581832886</v>
+        <v>2.63104557991028</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>2.60961127281189</v>
+        <v>2.60961103439331</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381908416748</v>
+        <v>2.65381932258606</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="n">
-        <v>2.67257452011108</v>
+        <v>2.67257404327393</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G410" t="n">
-        <v>2.6672158241272</v>
+        <v>2.66721558570862</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.5613842010498</v>
+        <v>2.56138443946838</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459143638611</v>
+        <v>2.53459191322327</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172306060791</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47162890434265</v>
+        <v>2.47162914276123</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G431" t="n">
-        <v>2.58951663970947</v>
+        <v>2.58951687812805</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189608573914</v>
+        <v>2.81189632415771</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.8534255027771</v>
+        <v>2.85342526435852</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="n">
-        <v>2.8869161605835</v>
+        <v>2.88691592216492</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="n">
-        <v>2.90165209770203</v>
+        <v>2.90165185928345</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136843681335</v>
+        <v>2.84136867523193</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682200431824</v>
+        <v>2.8668212890625</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682200431824</v>
+        <v>2.8668212890625</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.74625444412231</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>2.74625444412231</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868932723999</v>
+        <v>2.83868908882141</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567111968994</v>
+        <v>2.90567088127136</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.8869161605835</v>
+        <v>2.88691592216492</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.8400285243988</v>
+        <v>2.84002876281738</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710518836975</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710518836975</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>2.9257652759552</v>
+        <v>2.92576551437378</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88155722618103</v>
+        <v>2.88155746459961</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370868682861</v>
+        <v>2.91370892524719</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>2.90835046768188</v>
+        <v>2.90835070610046</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.88557648658752</v>
+        <v>2.8855767250061</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031242370605</v>
+        <v>2.90031218528748</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270763397217</v>
+        <v>2.84270834922791</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314136505127</v>
+        <v>2.79314184188843</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76232981681824</v>
+        <v>2.76233005523682</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300777435303</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G487" t="n">
-        <v>2.63238549232483</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6658763885498</v>
+        <v>2.66587615013123</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266867637634</v>
+        <v>2.69266891479492</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927265167236</v>
+        <v>2.67927217483521</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.63238549232483</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300777435303</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.5613842010498</v>
+        <v>2.56138443946838</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51315760612488</v>
+        <v>2.51315784454346</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449728012085</v>
+        <v>2.51449704170227</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.50846886634827</v>
+        <v>2.50846838951111</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884692192078</v>
+        <v>2.58884716033936</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526186943054</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50512003898621</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>2.54195976257324</v>
+        <v>2.54195952415466</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.52856373786926</v>
+        <v>2.52856349945068</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578175544739</v>
+        <v>2.64578151702881</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.57879972457886</v>
+        <v>2.57879948616028</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50512003898621</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172306060791</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51851606369019</v>
+        <v>2.51851630210876</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526186943054</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.54865789413452</v>
+        <v>2.5486581325531</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G539" t="n">
-        <v>2.5218653678894</v>
+        <v>2.52186512947083</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50512003898621</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G541" t="n">
-        <v>2.44818496704102</v>
+        <v>2.44818520545959</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488357543945</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.46158146858215</v>
+        <v>2.46158170700073</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G546" t="n">
-        <v>2.44818496704102</v>
+        <v>2.44818520545959</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.4046471118927</v>
+        <v>2.40464687347412</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G548" t="n">
-        <v>2.39125061035156</v>
+        <v>2.39125037193298</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>2.39794898033142</v>
+        <v>2.39794874191284</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>2.37115621566772</v>
+        <v>2.37115573883057</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>2.26398539543152</v>
+        <v>2.26398515701294</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.24389052391052</v>
+        <v>2.2438907623291</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700312614441</v>
+        <v>2.19700336456299</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365429878235</v>
+        <v>2.19365453720093</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695640563965</v>
+        <v>2.18695616722107</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.25728726387024</v>
+        <v>2.25728678703308</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.25058913230896</v>
+        <v>2.25058889389038</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24389052391052</v>
+        <v>2.2438907623291</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.33096694946289</v>
+        <v>2.33096742630005</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483590126038</v>
+        <v>2.44483613967896</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.4381377696991</v>
+        <v>2.43813800811768</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804361343384</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>2.4381377696991</v>
+        <v>2.43813800811768</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.4381377696991</v>
+        <v>2.43813800811768</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>2.4381377696991</v>
+        <v>2.43813800811768</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.42474174499512</v>
+        <v>2.42474150657654</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804361343384</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804361343384</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G586" t="n">
-        <v>2.44818496704102</v>
+        <v>2.44818520545959</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172306060791</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50512003898621</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="n">
-        <v>2.48837423324585</v>
+        <v>2.48837447166443</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46158146858215</v>
+        <v>2.46158170700073</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488357543945</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="n">
-        <v>2.54028511047363</v>
+        <v>2.54028534889221</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.43702149391174</v>
+        <v>2.43702125549316</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.3199896812439</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310534477234</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393607139587</v>
+        <v>2.23393654823303</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>2.26491546630859</v>
+        <v>2.26491570472717</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737812042236</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737812042236</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770522117615</v>
+        <v>2.24770498275757</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>2.32687377929688</v>
+        <v>2.3268735408783</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34408450126648</v>
+        <v>2.3440842628479</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>2.39571595191956</v>
+        <v>2.39571642875671</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>2.39571595191956</v>
+        <v>2.39571642875671</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G630" t="n">
-        <v>2.34752631187439</v>
+        <v>2.34752655029297</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212594985962</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915776252747</v>
+        <v>2.39915800094604</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473679542542</v>
+        <v>2.36473703384399</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310534477234</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.29933667182922</v>
+        <v>2.2993369102478</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30277895927429</v>
+        <v>2.30277872085571</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.3062207698822</v>
+        <v>2.30622100830078</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.3199896812439</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082088470459</v>
+        <v>2.24082112312317</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.17886257171631</v>
+        <v>2.17886233329773</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>2.19263052940369</v>
+        <v>2.19263076782227</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607305526733</v>
+        <v>2.19607329368591</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.1444411277771</v>
+        <v>2.14444136619568</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393607139587</v>
+        <v>2.23393654823303</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="n">
-        <v>2.29933667182922</v>
+        <v>2.2993369102478</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.3062207698822</v>
+        <v>2.30622100830078</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11002039909363</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099884033203</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690449714661</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690449714661</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099884033203</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378883361816</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="n">
-        <v>2.21672558784485</v>
+        <v>2.21672582626343</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.21672558784485</v>
+        <v>2.21672582626343</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099884033203</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512461662292</v>
+        <v>1.95512449741364</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168268680573</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841895103455</v>
+        <v>1.84841883182526</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.8828399181366</v>
+        <v>1.88283979892731</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070317268372</v>
+        <v>1.92070341110229</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.90349268913269</v>
+        <v>1.90349292755127</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414557933807</v>
+        <v>1.92414569854736</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921943664551</v>
+        <v>1.97921907901764</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298799037933</v>
+        <v>1.99298787117004</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610353469849</v>
+        <v>1.98610377311707</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429365158081</v>
+        <v>2.03429341316223</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="n">
-        <v>2.05838847160339</v>
+        <v>2.05838823318481</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.07559871673584</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099884033203</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.09625172615051</v>
+        <v>2.09625148773193</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>2.04806160926819</v>
+        <v>2.04806184768677</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.07559871673584</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889293193817</v>
+        <v>1.96889317035675</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168268680573</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758774757385</v>
+        <v>1.92758738994598</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200895309448</v>
+        <v>1.96200883388519</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="n">
-        <v>2.09625172615051</v>
+        <v>2.09625148773193</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="n">
-        <v>2.21672558784485</v>
+        <v>2.21672582626343</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378883361816</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212594985962</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="n">
-        <v>2.33375787734985</v>
+        <v>2.33375763893127</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.34408450126648</v>
+        <v>2.3440842628479</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.49209570884705</v>
+        <v>2.49209547042847</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832727432251</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046354293823</v>
+        <v>2.44046378135681</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.52651691436768</v>
+        <v>2.5265166759491</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274800300598</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307462692261</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307462692261</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274800300598</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093764305115</v>
+        <v>2.56093788146973</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="n">
-        <v>2.60568571090698</v>
+        <v>2.6056854724884</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945366859436</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="n">
-        <v>2.67108583450317</v>
+        <v>2.67108607292175</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67796993255615</v>
+        <v>2.67797017097473</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945366859436</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G791" t="n">
-        <v>2.56782221794128</v>
+        <v>2.56782197952271</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G792" t="n">
-        <v>2.57470631599426</v>
+        <v>2.57470655441284</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224318504333</v>
+        <v>2.60224342346191</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.56782221794128</v>
+        <v>2.56782197952271</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535932540894</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G796" t="n">
-        <v>2.56782221794128</v>
+        <v>2.56782197952271</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601185798645</v>
+        <v>2.61601161956787</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>2.65731716156006</v>
+        <v>2.65731692314148</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G801" t="n">
-        <v>2.69862270355225</v>
+        <v>2.69862294197083</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>2.70206451416016</v>
+        <v>2.70206475257874</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>2.68485403060913</v>
+        <v>2.68485426902771</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>4</v>
       </c>
       <c r="G805" t="n">
-        <v>2.75369668006897</v>
+        <v>2.75369644165039</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090740203857</v>
+        <v>2.77090716362</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.71239137649536</v>
+        <v>2.7123908996582</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681234359741</v>
+        <v>2.74681210517883</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>2.72615933418274</v>
+        <v>2.72615957260132</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>2.76746487617493</v>
+        <v>2.76746511459351</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304414749146</v>
+        <v>2.73304390907288</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>2.69518041610718</v>
+        <v>2.69518065452576</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535932540894</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>2.56782221794128</v>
+        <v>2.56782197952271</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G832" t="n">
-        <v>2.57470631599426</v>
+        <v>2.57470655441284</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="n">
-        <v>2.51619005203247</v>
+        <v>2.51619029045105</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.42669558525085</v>
+        <v>2.42669534683228</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357944488525</v>
+        <v>2.43357968330383</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.505863904953</v>
+        <v>2.50586414337158</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.52651691436768</v>
+        <v>2.5265166759491</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013739585876</v>
+        <v>2.43013715744019</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="n">
-        <v>2.38883185386658</v>
+        <v>2.38883209228516</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031606674194</v>
+        <v>2.33031582832336</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11002039909363</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.07559871673584</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085112571716</v>
+        <v>2.03085136413574</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G861" t="n">
-        <v>2.04117751121521</v>
+        <v>2.04117774963379</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>2.1374819278717</v>
+        <v>2.13748216629028</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06153130531311</v>
+        <v>2.06153106689453</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026313304901</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.94217920303345</v>
+        <v>1.94217908382416</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026313304901</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>1.94579601287842</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026277542114</v>
+        <v>1.96026313304901</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834634780884</v>
+        <v>1.97834622859955</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94579601287842</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>1.93132889270782</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G886" t="n">
-        <v>1.89154541492462</v>
+        <v>1.89154517650604</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.89154541492462</v>
+        <v>1.89154517650604</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.880695104599</v>
+        <v>1.88069486618042</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324543952942</v>
+        <v>1.91324555873871</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93132889270782</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.83006083965302</v>
+        <v>1.8300609588623</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.880695104599</v>
+        <v>1.88069486618042</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.90239536762238</v>
+        <v>1.90239560604095</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324543952942</v>
+        <v>1.91324555873871</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.86261165142059</v>
+        <v>1.86261141300201</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389381408691</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431167602539</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474400520325</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389381408691</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730844974518</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199149608612</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327377796173</v>
+        <v>1.57327365875244</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.6636917591095</v>
+        <v>1.66369163990021</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.62029111385345</v>
+        <v>1.62029099464417</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.57689046859741</v>
+        <v>1.57689034938812</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.59859085083008</v>
+        <v>1.59859073162079</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G930" t="n">
-        <v>1.58412384986877</v>
+        <v>1.58412408828735</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007506847382</v>
+        <v>1.66007518768311</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944080352783</v>
+        <v>1.60944092273712</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645813941956</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730844974518</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305773258209</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G950" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.62029111385345</v>
+        <v>1.62029099464417</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64560830593109</v>
+        <v>1.64560806751251</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.69985902309418</v>
+        <v>1.69985890388489</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199149608612</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G959" t="n">
-        <v>1.63475811481476</v>
+        <v>1.63475799560547</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944080352783</v>
+        <v>1.60944092273712</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837492465973</v>
+        <v>1.63837480545044</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900895118713</v>
+        <v>1.68900871276855</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.6962423324585</v>
+        <v>1.69624245166779</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815864086151</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092537879944</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730844974518</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G980" t="n">
-        <v>1.79751026630402</v>
+        <v>1.7975105047226</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134300231934</v>
+        <v>1.7613433599472</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070921421051</v>
+        <v>1.71070909500122</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666031360626</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666031360626</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G996" t="n">
-        <v>2.01451396942139</v>
+        <v>2.01451373100281</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.9349457025528</v>
+        <v>1.93494582176208</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196303844452</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.06153130531311</v>
+        <v>2.06153106689453</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.05429792404175</v>
+        <v>2.05429768562317</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.03621411323547</v>
+        <v>2.03621387481689</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.00366377830505</v>
+        <v>2.00366353988647</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.01813054084778</v>
+        <v>2.01813077926636</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196303844452</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281334877014</v>
+        <v>1.99281346797943</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387946605682</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387946605682</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.94579601287842</v>
+        <v>1.94579613208771</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.93132889270782</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324543952942</v>
+        <v>1.91324555873871</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814465045929</v>
+        <v>1.84814453125</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728034973145</v>
+        <v>2.00728058815002</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.98557996749878</v>
+        <v>1.98557984828949</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387946605682</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.98557996749878</v>
+        <v>1.98557984828949</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431167602539</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.87707841396332</v>
+        <v>1.87707829475403</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474400520325</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964273929596</v>
+        <v>1.73964297771454</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899472236633</v>
+        <v>1.85899484157562</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.87707841396332</v>
+        <v>1.87707829475403</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644414901733</v>
+        <v>1.82644426822662</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176134109497</v>
+        <v>1.85176122188568</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.77942669391632</v>
+        <v>1.77942681312561</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645813941956</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645813941956</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.60582423210144</v>
+        <v>1.60582411289215</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965708732605</v>
+        <v>1.56965696811676</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.51178932189941</v>
+        <v>1.5117894411087</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366825580597</v>
+        <v>1.43366813659668</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448095321655</v>
+        <v>1.38448083400726</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.35120713710785</v>
+        <v>1.35120701789856</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412868499756</v>
+        <v>1.01412856578827</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00400197505951</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.985194861888885</v>
+        <v>0.98519492149353</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.23547208309174</v>
+        <v>1.23547196388245</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.25861895084381</v>
+        <v>1.2586190700531</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.17760455608368</v>
+        <v>1.1776043176651</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.18194448947906</v>
+        <v>1.18194437026978</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968518733978</v>
+        <v>1.22968530654907</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.19351804256439</v>
+        <v>1.19351780414581</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.18194448947906</v>
+        <v>1.18194437026978</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.2427054643631</v>
+        <v>1.24270534515381</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100508213043</v>
+        <v>1.22100496292114</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.14288377761841</v>
+        <v>1.1428838968277</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.15156388282776</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570223808289</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.02714896202087</v>
+        <v>1.02714884281158</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.00978851318359</v>
+        <v>1.00978863239288</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.982301592826843</v>
+        <v>0.982301533222198</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.985194861888885</v>
+        <v>0.98519492149353</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428183555603</v>
+        <v>0.992428243160248</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04306244850159</v>
+        <v>1.0430623292923</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.02859568595886</v>
+        <v>1.02859544754028</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.18917810916901</v>
+        <v>1.18917787075043</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.09658980369568</v>
+        <v>1.09658992290497</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212304115295</v>
+        <v>1.08212292194366</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.12263035774231</v>
+        <v>1.12263023853302</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382318496704</v>
+        <v>1.10382330417633</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237658023834</v>
+        <v>1.10237669944763</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05608260631561</v>
+        <v>1.0560827255249</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.15156388282776</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476271152496</v>
+        <v>1.06476283073425</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501648902893</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501648902893</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.07488965988159</v>
+        <v>1.0748895406723</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595589637756</v>
+        <v>1.04595577716827</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.99098151922226</v>
+        <v>0.990981698036194</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088369369507</v>
+        <v>0.988088190555573</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.00400197505951</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088369369507</v>
+        <v>0.988088190555573</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.985194861888885</v>
+        <v>0.98519492149353</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.97217470407486</v>
+        <v>0.972174525260925</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387927532196</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387927532196</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387927532196</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.967834711074829</v>
+        <v>0.96783459186554</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047755718231</v>
+        <v>0.962047934532166</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880670547485</v>
+        <v>0.925880610942841</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.930220663547516</v>
+        <v>0.930220603942871</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.930220663547516</v>
+        <v>0.930220603942871</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.921540498733521</v>
+        <v>0.921540439128876</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.891160011291504</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093894004822</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901286959648132</v>
+        <v>0.901286900043488</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.88971334695816</v>
+        <v>0.889713406562805</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093894004822</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928774058818817</v>
+        <v>0.928773999214172</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748257160187</v>
+        <v>0.983748197555542</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951921045780182</v>
+        <v>0.951920986175537</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753841400146</v>
+        <v>0.915753960609436</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246584415436</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013083934784</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.817379057407379</v>
+        <v>0.817378997802734</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.826059103012085</v>
+        <v>0.82605904340744</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.828952491283417</v>
+        <v>0.828952550888062</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024312019348</v>
+        <v>0.732024371623993</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.772531688213348</v>
+        <v>0.772531628608704</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211793422699</v>
+        <v>0.781211853027344</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.833292543888092</v>
+        <v>0.833292603492737</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079320430756</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799800872803</v>
+        <v>0.873799741268158</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901286959648132</v>
+        <v>0.901286900043488</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967124462128</v>
+        <v>0.909967005252838</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.89405345916748</v>
+        <v>0.894053399562836</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.88971334695816</v>
+        <v>0.889713406562805</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693189144135</v>
+        <v>0.876693308353424</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013083934784</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013083934784</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119814872742</v>
+        <v>0.865119755268097</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246584415436</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.88537335395813</v>
+        <v>0.885373294353485</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779762268066</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459807872772</v>
+        <v>0.869459748268127</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946907043457</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.891160011291504</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.881033360958099</v>
+        <v>0.88103324174881</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013083934784</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.854992926120758</v>
+        <v>0.854992985725403</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779762268066</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206149578094</v>
+        <v>0.849206209182739</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079320430756</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.843419313430786</v>
+        <v>0.843419373035431</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.836185932159424</v>
+        <v>0.836185991764069</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.826059103012085</v>
+        <v>0.82605904340744</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845879554749</v>
+        <v>0.831845819950104</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312701702118</v>
+        <v>0.846312761306763</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119814872742</v>
+        <v>0.865119755268097</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799800872803</v>
+        <v>0.873799741268158</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.982301592826843</v>
+        <v>0.982301533222198</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.00978851318359</v>
+        <v>1.00978863239288</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.982301592826843</v>
+        <v>0.982301533222198</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408085346222</v>
+        <v>0.979408025741577</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748257160187</v>
+        <v>0.983748197555542</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.0575293302536</v>
+        <v>1.05752921104431</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570223808289</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.02136206626892</v>
+        <v>1.02136194705963</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768534183502</v>
+        <v>0.996768414974213</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748257160187</v>
+        <v>0.983748197555542</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570223808289</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884910583496</v>
+        <v>1.04884934425354</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.17037105560303</v>
+        <v>1.17037093639374</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.17037105560303</v>
+        <v>1.17037093639374</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458427906036</v>
+        <v>1.16458415985107</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.19351804256439</v>
+        <v>1.19351780414581</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.14288377761841</v>
+        <v>1.1428838968277</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049776554108</v>
+        <v>1.18049788475037</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.17037105560303</v>
+        <v>1.17037093639374</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.18339109420776</v>
+        <v>1.18339121341705</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.15156388282776</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.26440572738647</v>
+        <v>1.26440560817719</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491292476654</v>
+        <v>1.30491304397583</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.27453243732452</v>
+        <v>1.27453255653381</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.2918928861618</v>
+        <v>1.29189276695251</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.33674025535583</v>
+        <v>1.33674013614655</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.46115529537201</v>
+        <v>1.4611554145813</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030522346497</v>
+        <v>1.45030546188354</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.42932820320129</v>
+        <v>1.429328083992</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.39750111103058</v>
+        <v>1.39750123023987</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537173748016</v>
+        <v>1.45537161827087</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.30761826038361</v>
+        <v>1.30761814117432</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.29432046413422</v>
+        <v>1.29432058334351</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.18646037578583</v>
+        <v>1.18646025657654</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.21305596828461</v>
+        <v>1.2130560874939</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.21896612644196</v>
+        <v>1.21896600723267</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.19384813308716</v>
+        <v>1.19384801387787</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.1672523021698</v>
+        <v>1.16725242137909</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.28250014781952</v>
+        <v>1.28250002861023</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.42582106590271</v>
+        <v>1.42582094669342</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.42582106590271</v>
+        <v>1.42582094669342</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.27511250972748</v>
+        <v>1.27511239051819</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.24408435821533</v>
+        <v>1.24408423900604</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.28545522689819</v>
+        <v>1.28545534610748</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.39479267597198</v>
+        <v>1.39479279518127</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.39627039432526</v>
+        <v>1.39627027511597</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.37115216255188</v>
+        <v>1.37115204334259</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.55879890918732</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.55879890918732</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.34898912906647</v>
+        <v>1.34898924827576</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.37115216255188</v>
+        <v>1.37115204334259</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.51816713809967</v>
+        <v>1.51816701889038</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.4812285900116</v>
+        <v>1.48122870922089</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.47605717182159</v>
+        <v>1.4760570526123</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.51816713809967</v>
+        <v>1.51816701889038</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.54402363300323</v>
+        <v>1.54402375221252</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.39627039432526</v>
+        <v>1.39627027511597</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.39627039432526</v>
+        <v>1.39627027511597</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.39479267597198</v>
+        <v>1.39479279518127</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.41252315044403</v>
+        <v>1.41252303123474</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.43320870399475</v>
+        <v>1.43320882320404</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.42286586761475</v>
+        <v>1.42286598682404</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.34898912906647</v>
+        <v>1.34898924827576</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.28545522689819</v>
+        <v>1.28545534610748</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862329006195</v>
+        <v>1.20862340927124</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.21305596828461</v>
+        <v>1.2130560874939</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.28545522689819</v>
+        <v>1.28545534610748</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.26476967334747</v>
+        <v>1.26476979255676</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.33864653110504</v>
+        <v>1.33864641189575</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.48492240905762</v>
+        <v>1.48492228984833</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.65853261947632</v>
+        <v>1.65853273868561</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.69177722930908</v>
+        <v>1.69177711009979</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.69916498661041</v>
+        <v>1.69916486740112</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.70655262470245</v>
+        <v>1.70655274391174</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.70655262470245</v>
+        <v>1.70655274391174</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.69547116756439</v>
+        <v>1.69547128677368</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.65114498138428</v>
+        <v>1.65114486217499</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.55879890918732</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.59573757648468</v>
+        <v>1.59573769569397</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.64006352424622</v>
+        <v>1.64006340503693</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.63380634784698</v>
+        <v>1.6338062286377</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.64986348152161</v>
+        <v>1.64986336231232</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.64986348152161</v>
+        <v>1.64986336231232</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.62979197502136</v>
+        <v>1.62979209423065</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.61373496055603</v>
+        <v>1.61373484134674</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.37448465824127</v>
+        <v>1.37448477745056</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609040737152</v>
+        <v>1.37609028816223</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.27814221382141</v>
+        <v>1.2781423330307</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="n">
-        <v>1.4210501909256</v>
+        <v>1.42105007171631</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082710266113</v>
+        <v>1.47082698345184</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.35200488567352</v>
+        <v>1.35200476646423</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.28295946121216</v>
+        <v>1.28295958042145</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.13684010505676</v>
+        <v>1.13684022426605</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741084575653</v>
+        <v>1.29741072654724</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>1.67799997329712</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.34718751907349</v>
+        <v>1.34718763828278</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.31989073753357</v>
+        <v>1.31989061832428</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.31346774101257</v>
+        <v>1.31346786022186</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.28938221931458</v>
+        <v>1.28938210010529</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.2685079574585</v>
+        <v>1.26850807666779</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.23799979686737</v>
+        <v>1.23799967765808</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.25084519386292</v>
+        <v>1.2508453130722</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.18822276592255</v>
+        <v>1.18822264671326</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.18822276592255</v>
+        <v>1.18822264671326</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.1866170167923</v>
+        <v>1.18661713600159</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.19946253299713</v>
+        <v>1.19946265220642</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.25084519386292</v>
+        <v>1.2508453130722</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.2540568113327</v>
+        <v>1.25405669212341</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.3937531709671</v>
+        <v>1.39375305175781</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.41141593456268</v>
+        <v>1.41141581535339</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.3937531709671</v>
+        <v>1.39375305175781</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.40338742733002</v>
+        <v>1.40338730812073</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828486919403</v>
+        <v>1.31828498840332</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.49009549617767</v>
+        <v>1.49009537696838</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.51418101787567</v>
+        <v>1.51418113708496</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.47885549068451</v>
+        <v>1.4788556098938</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.49009549617767</v>
+        <v>1.49009537696838</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.51096963882446</v>
+        <v>1.51096975803375</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>2.06500005722046</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>91109</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>2.11500000953674</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>2.09500002861023</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85730123519897</v>
+        <v>2.85730147361755</v>
       </c>
       <c r="H2" t="n">
         <v>30003</v>
@@ -456,7 +456,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86872529983521</v>
+        <v>2.86872553825378</v>
       </c>
       <c r="H3" t="n">
         <v>20338</v>
@@ -485,7 +485,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525851249695</v>
+        <v>2.80525827407837</v>
       </c>
       <c r="H4" t="n">
         <v>23828</v>
@@ -543,7 +543,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7709858417511</v>
+        <v>2.77098608016968</v>
       </c>
       <c r="H6" t="n">
         <v>24790</v>
@@ -601,7 +601,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G8" t="n">
-        <v>2.732905626297</v>
+        <v>2.73290514945984</v>
       </c>
       <c r="H8" t="n">
         <v>58587</v>
@@ -688,7 +688,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928339958191</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H11" t="n">
         <v>96501</v>
@@ -717,7 +717,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408214569092</v>
+        <v>2.56408190727234</v>
       </c>
       <c r="H12" t="n">
         <v>52586</v>
@@ -775,7 +775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.50061464309692</v>
+        <v>2.5006148815155</v>
       </c>
       <c r="H14" t="n">
         <v>75440</v>
@@ -804,7 +804,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H15" t="n">
         <v>65925</v>
@@ -833,7 +833,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66436052322388</v>
+        <v>2.6643602848053</v>
       </c>
       <c r="H16" t="n">
         <v>61532</v>
@@ -862,7 +862,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915950775146</v>
+        <v>2.56915926933289</v>
       </c>
       <c r="H17" t="n">
         <v>32766</v>
@@ -891,7 +891,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138850212097</v>
+        <v>2.55138874053955</v>
       </c>
       <c r="H18" t="n">
         <v>16747</v>
@@ -920,7 +920,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56281304359436</v>
+        <v>2.56281280517578</v>
       </c>
       <c r="H19" t="n">
         <v>19201</v>
@@ -949,7 +949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965475082397</v>
+        <v>2.51965498924255</v>
       </c>
       <c r="H20" t="n">
         <v>43026</v>
@@ -1007,7 +1007,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662106513977</v>
+        <v>2.56662082672119</v>
       </c>
       <c r="H22" t="n">
         <v>34521</v>
@@ -1065,7 +1065,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696134567261</v>
+        <v>2.50696110725403</v>
       </c>
       <c r="H24" t="n">
         <v>32795</v>
@@ -1094,7 +1094,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107881546021</v>
+        <v>2.53107905387878</v>
       </c>
       <c r="H25" t="n">
         <v>32107</v>
@@ -1123,7 +1123,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H26" t="n">
         <v>40968</v>
@@ -1152,7 +1152,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349384307861</v>
+        <v>2.44349408149719</v>
       </c>
       <c r="H27" t="n">
         <v>83462</v>
@@ -1181,7 +1181,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2860951423645</v>
+        <v>2.28609490394592</v>
       </c>
       <c r="H28" t="n">
         <v>109730</v>
@@ -1268,7 +1268,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135806083679</v>
+        <v>2.22135829925537</v>
       </c>
       <c r="H31" t="n">
         <v>155211</v>
@@ -1297,7 +1297,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36098670959473</v>
+        <v>2.36098623275757</v>
       </c>
       <c r="H32" t="n">
         <v>97681</v>
@@ -1326,7 +1326,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798337936401</v>
+        <v>2.32798385620117</v>
       </c>
       <c r="H33" t="n">
         <v>39970</v>
@@ -1355,7 +1355,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.48665165901184</v>
+        <v>2.48665189743042</v>
       </c>
       <c r="H34" t="n">
         <v>72475</v>
@@ -1384,7 +1384,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.61866402626038</v>
+        <v>2.61866426467896</v>
       </c>
       <c r="H35" t="n">
         <v>117716</v>
@@ -1413,7 +1413,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.55519652366638</v>
+        <v>2.55519676208496</v>
       </c>
       <c r="H36" t="n">
         <v>17078</v>
@@ -1442,7 +1442,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928339958191</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H37" t="n">
         <v>45626</v>
@@ -1500,7 +1500,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49553728103638</v>
+        <v>2.4955370426178</v>
       </c>
       <c r="H39" t="n">
         <v>77760</v>
@@ -1529,7 +1529,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H40" t="n">
         <v>22658</v>
@@ -1732,7 +1732,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G47" t="n">
-        <v>2.68086171150208</v>
+        <v>2.68086194992065</v>
       </c>
       <c r="H47" t="n">
         <v>42015</v>
@@ -1761,7 +1761,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213129043579</v>
+        <v>2.68213105201721</v>
       </c>
       <c r="H48" t="n">
         <v>40006</v>
@@ -1790,7 +1790,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6935555934906</v>
+        <v>2.69355511665344</v>
       </c>
       <c r="H49" t="n">
         <v>25946</v>
@@ -1906,7 +1906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.74179077148438</v>
+        <v>2.74179100990295</v>
       </c>
       <c r="H53" t="n">
         <v>42603</v>
@@ -1935,7 +1935,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84333801269531</v>
+        <v>2.84333872795105</v>
       </c>
       <c r="H54" t="n">
         <v>63652</v>
@@ -1993,7 +1993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853974342346</v>
+        <v>2.9385392665863</v>
       </c>
       <c r="H56" t="n">
         <v>170803</v>
@@ -2051,7 +2051,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169708251953</v>
+        <v>2.98169755935669</v>
       </c>
       <c r="H58" t="n">
         <v>45732</v>
@@ -2109,7 +2109,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>2.94869422912598</v>
+        <v>2.94869470596313</v>
       </c>
       <c r="H60" t="n">
         <v>43744</v>
@@ -2138,7 +2138,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835394859314</v>
+        <v>3.00835371017456</v>
       </c>
       <c r="H61" t="n">
         <v>91726</v>
@@ -2167,7 +2167,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104759216309</v>
+        <v>3.02104783058167</v>
       </c>
       <c r="H62" t="n">
         <v>71653</v>
@@ -2225,7 +2225,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566030502319</v>
+        <v>2.99566006660461</v>
       </c>
       <c r="H64" t="n">
         <v>46851</v>
@@ -2341,7 +2341,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711520195007</v>
+        <v>2.92711544036865</v>
       </c>
       <c r="H68" t="n">
         <v>58634</v>
@@ -2370,7 +2370,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819922447205</v>
+        <v>2.99819874763489</v>
       </c>
       <c r="H69" t="n">
         <v>75222</v>
@@ -2457,7 +2457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182097434998</v>
+        <v>3.07182145118713</v>
       </c>
       <c r="H72" t="n">
         <v>136484</v>
@@ -2573,7 +2573,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702175140381</v>
+        <v>3.16702198982239</v>
       </c>
       <c r="H76" t="n">
         <v>114194</v>
@@ -2602,7 +2602,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702175140381</v>
+        <v>3.16702198982239</v>
       </c>
       <c r="H77" t="n">
         <v>122410</v>
@@ -2689,7 +2689,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798188209534</v>
+        <v>3.14798164367676</v>
       </c>
       <c r="H80" t="n">
         <v>29895</v>
@@ -2747,7 +2747,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244034767151</v>
+        <v>3.11244010925293</v>
       </c>
       <c r="H82" t="n">
         <v>32834</v>
@@ -2805,7 +2805,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959245681763</v>
+        <v>3.08959221839905</v>
       </c>
       <c r="H84" t="n">
         <v>34327</v>
@@ -2834,7 +2834,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547451019287</v>
+        <v>3.06547427177429</v>
       </c>
       <c r="H85" t="n">
         <v>37849</v>
@@ -2979,7 +2979,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053998947144</v>
+        <v>3.03053951263428</v>
       </c>
       <c r="H90" t="n">
         <v>50752</v>
@@ -3008,7 +3008,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>2.96696162223816</v>
+        <v>2.96696209907532</v>
       </c>
       <c r="H91" t="n">
         <v>62212</v>
@@ -3037,7 +3037,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>2.93384861946106</v>
+        <v>2.93384885787964</v>
       </c>
       <c r="H92" t="n">
         <v>77806</v>
@@ -3066,7 +3066,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H93" t="n">
         <v>86004</v>
@@ -3153,7 +3153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H96" t="n">
         <v>54946</v>
@@ -3182,7 +3182,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92722630500793</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H97" t="n">
         <v>13594</v>
@@ -3269,7 +3269,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941554069519</v>
+        <v>3.09941577911377</v>
       </c>
       <c r="H100" t="n">
         <v>95435</v>
@@ -3298,7 +3298,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G101" t="n">
-        <v>3.07822322845459</v>
+        <v>3.07822299003601</v>
       </c>
       <c r="H101" t="n">
         <v>47757</v>
@@ -3327,7 +3327,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577412605286</v>
+        <v>3.14577436447144</v>
       </c>
       <c r="H102" t="n">
         <v>86451</v>
@@ -3356,7 +3356,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140504837036</v>
+        <v>3.20140528678894</v>
       </c>
       <c r="H103" t="n">
         <v>92445</v>
@@ -3443,7 +3443,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584294319153</v>
+        <v>3.23584318161011</v>
       </c>
       <c r="H106" t="n">
         <v>124255</v>
@@ -3501,7 +3501,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610714912415</v>
+        <v>3.19610667228699</v>
       </c>
       <c r="H108" t="n">
         <v>19558</v>
@@ -3530,7 +3530,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802783966064</v>
+        <v>3.20802760124207</v>
       </c>
       <c r="H109" t="n">
         <v>23367</v>
@@ -3559,7 +3559,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829180717468</v>
+        <v>3.1682915687561</v>
       </c>
       <c r="H110" t="n">
         <v>37625</v>
@@ -3617,7 +3617,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133623123169</v>
+        <v>3.11133670806885</v>
       </c>
       <c r="H112" t="n">
         <v>10926</v>
@@ -3733,7 +3733,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516845703125</v>
+        <v>2.73516821861267</v>
       </c>
       <c r="H116" t="n">
         <v>77740</v>
@@ -3762,7 +3762,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G117" t="n">
-        <v>2.69543242454529</v>
+        <v>2.69543218612671</v>
       </c>
       <c r="H117" t="n">
         <v>51280</v>
@@ -3907,7 +3907,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398048400879</v>
       </c>
       <c r="H122" t="n">
         <v>31647</v>
@@ -3936,7 +3936,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060279846191</v>
+        <v>2.92060327529907</v>
       </c>
       <c r="H123" t="n">
         <v>44363</v>
@@ -3965,7 +3965,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596493721008</v>
+        <v>2.81596517562866</v>
       </c>
       <c r="H124" t="n">
         <v>67252</v>
@@ -4023,7 +4023,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841356277466</v>
+        <v>2.74841332435608</v>
       </c>
       <c r="H126" t="n">
         <v>44702</v>
@@ -4052,7 +4052,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907841682434</v>
+        <v>2.84907793998718</v>
       </c>
       <c r="H127" t="n">
         <v>171545</v>
@@ -4139,7 +4139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047117233276</v>
+        <v>2.94047093391418</v>
       </c>
       <c r="H130" t="n">
         <v>49672</v>
@@ -4226,7 +4226,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152704238892</v>
+        <v>2.78152656555176</v>
       </c>
       <c r="H133" t="n">
         <v>40862</v>
@@ -4255,7 +4255,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>2.90073561668396</v>
+        <v>2.90073537826538</v>
       </c>
       <c r="H134" t="n">
         <v>104347</v>
@@ -4313,7 +4313,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802254676819</v>
+        <v>3.00802230834961</v>
       </c>
       <c r="H136" t="n">
         <v>190152</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>2.96696162223816</v>
+        <v>2.96696209907532</v>
       </c>
       <c r="H137" t="n">
         <v>193814</v>
@@ -4400,7 +4400,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.91530513763428</v>
+        <v>2.9153048992157</v>
       </c>
       <c r="H139" t="n">
         <v>337397</v>
@@ -4458,7 +4458,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="n">
-        <v>2.63715243339539</v>
+        <v>2.63715267181396</v>
       </c>
       <c r="H141" t="n">
         <v>384878</v>
@@ -4487,7 +4487,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397542953491</v>
+        <v>2.71397590637207</v>
       </c>
       <c r="H142" t="n">
         <v>293231</v>
@@ -4516,7 +4516,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H143" t="n">
         <v>206630</v>
@@ -4545,7 +4545,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="n">
-        <v>2.69940590858459</v>
+        <v>2.69940567016602</v>
       </c>
       <c r="H144" t="n">
         <v>154876</v>
@@ -4603,7 +4603,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112591743469</v>
+        <v>2.64112615585327</v>
       </c>
       <c r="H146" t="n">
         <v>91785</v>
@@ -4661,7 +4661,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H148" t="n">
         <v>77302</v>
@@ -4690,7 +4690,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112591743469</v>
+        <v>2.64112615585327</v>
       </c>
       <c r="H149" t="n">
         <v>58696</v>
@@ -4806,7 +4806,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>2.68218684196472</v>
+        <v>2.6821870803833</v>
       </c>
       <c r="H153" t="n">
         <v>379608</v>
@@ -4864,7 +4864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245057106018</v>
+        <v>2.64245080947876</v>
       </c>
       <c r="H155" t="n">
         <v>131874</v>
@@ -4893,7 +4893,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>2.67556405067444</v>
+        <v>2.67556381225586</v>
       </c>
       <c r="H156" t="n">
         <v>71701</v>
@@ -4922,7 +4922,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7219226360321</v>
+        <v>2.72192287445068</v>
       </c>
       <c r="H157" t="n">
         <v>1740457</v>
@@ -5009,7 +5009,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H160" t="n">
         <v>69314</v>
@@ -5067,7 +5067,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702080726624</v>
+        <v>2.65702056884766</v>
       </c>
       <c r="H162" t="n">
         <v>133837</v>
@@ -5125,7 +5125,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G164" t="n">
-        <v>2.69543242454529</v>
+        <v>2.69543218612671</v>
       </c>
       <c r="H164" t="n">
         <v>253678</v>
@@ -5270,7 +5270,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6186089515686</v>
+        <v>2.61860871315002</v>
       </c>
       <c r="H169" t="n">
         <v>113605</v>
@@ -5357,7 +5357,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.63582801818848</v>
+        <v>2.6358277797699</v>
       </c>
       <c r="H172" t="n">
         <v>149122</v>
@@ -5386,7 +5386,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801267623901</v>
+        <v>2.60801243782043</v>
       </c>
       <c r="H173" t="n">
         <v>90282</v>
@@ -5444,7 +5444,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>2.56430268287659</v>
+        <v>2.56430315971375</v>
       </c>
       <c r="H175" t="n">
         <v>202259</v>
@@ -5473,7 +5473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H176" t="n">
         <v>133924</v>
@@ -5502,7 +5502,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H177" t="n">
         <v>178815</v>
@@ -5531,7 +5531,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H178" t="n">
         <v>66133</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979644775391</v>
+        <v>2.43979668617249</v>
       </c>
       <c r="H180" t="n">
         <v>95436</v>
@@ -5618,7 +5618,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.41198086738586</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H181" t="n">
         <v>140968</v>
@@ -5734,7 +5734,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761226654053</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H185" t="n">
         <v>109363</v>
@@ -5763,7 +5763,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>2.45039319992065</v>
+        <v>2.4503927230835</v>
       </c>
       <c r="H186" t="n">
         <v>71603</v>
@@ -5792,7 +5792,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992855072021</v>
+        <v>2.41992807388306</v>
       </c>
       <c r="H187" t="n">
         <v>58946</v>
@@ -5850,7 +5850,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="n">
-        <v>2.2782027721405</v>
+        <v>2.27820301055908</v>
       </c>
       <c r="H189" t="n">
         <v>134521</v>
@@ -5908,7 +5908,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.25303649902344</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H191" t="n">
         <v>98350</v>
@@ -5937,7 +5937,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>2.27158045768738</v>
+        <v>2.27158069610596</v>
       </c>
       <c r="H192" t="n">
         <v>124936</v>
@@ -5966,7 +5966,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="n">
-        <v>2.24641418457031</v>
+        <v>2.24641370773315</v>
       </c>
       <c r="H193" t="n">
         <v>167793</v>
@@ -6024,7 +6024,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.45039319992065</v>
+        <v>2.4503927230835</v>
       </c>
       <c r="H195" t="n">
         <v>439465</v>
@@ -6053,7 +6053,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="n">
-        <v>2.43449878692627</v>
+        <v>2.43449807167053</v>
       </c>
       <c r="H196" t="n">
         <v>224328</v>
@@ -6082,7 +6082,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.42655086517334</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H197" t="n">
         <v>94547</v>
@@ -6169,7 +6169,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741110801697</v>
+        <v>2.39741134643555</v>
       </c>
       <c r="H200" t="n">
         <v>83817</v>
@@ -6198,7 +6198,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H201" t="n">
         <v>67052</v>
@@ -6227,7 +6227,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="n">
-        <v>2.34575462341309</v>
+        <v>2.34575486183167</v>
       </c>
       <c r="H202" t="n">
         <v>176806</v>
@@ -6256,7 +6256,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211344718933</v>
+        <v>2.39211320877075</v>
       </c>
       <c r="H203" t="n">
         <v>79415</v>
@@ -6285,7 +6285,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.42655086517334</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H204" t="n">
         <v>55166</v>
@@ -6314,7 +6314,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.45833992958069</v>
+        <v>2.45834040641785</v>
       </c>
       <c r="H205" t="n">
         <v>124627</v>
@@ -6372,7 +6372,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.4543662071228</v>
+        <v>2.45436644554138</v>
       </c>
       <c r="H207" t="n">
         <v>152563</v>
@@ -6430,7 +6430,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>2.44376993179321</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H209" t="n">
         <v>84077</v>
@@ -6488,7 +6488,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.45039319992065</v>
+        <v>2.4503927230835</v>
       </c>
       <c r="H211" t="n">
         <v>66822</v>
@@ -6517,7 +6517,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="n">
-        <v>2.48350596427917</v>
+        <v>2.48350620269775</v>
       </c>
       <c r="H212" t="n">
         <v>273607</v>
@@ -6546,7 +6546,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503106117249</v>
+        <v>2.55503129959106</v>
       </c>
       <c r="H213" t="n">
         <v>339678</v>
@@ -6575,7 +6575,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H214" t="n">
         <v>119773</v>
@@ -6633,7 +6633,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>2.54443502426147</v>
+        <v>2.5444347858429</v>
       </c>
       <c r="H216" t="n">
         <v>93617</v>
@@ -6778,7 +6778,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496272087097</v>
+        <v>2.46496248245239</v>
       </c>
       <c r="H221" t="n">
         <v>80797</v>
@@ -6807,7 +6807,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48085737228394</v>
+        <v>2.48085713386536</v>
       </c>
       <c r="H222" t="n">
         <v>144428</v>
@@ -6836,7 +6836,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="n">
-        <v>2.45171713829041</v>
+        <v>2.45171737670898</v>
       </c>
       <c r="H223" t="n">
         <v>48476</v>
@@ -6923,7 +6923,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G226" t="n">
-        <v>2.34442949295044</v>
+        <v>2.34442973136902</v>
       </c>
       <c r="H226" t="n">
         <v>92193</v>
@@ -6952,7 +6952,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.33780717849731</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H227" t="n">
         <v>189301</v>
@@ -6981,7 +6981,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.33780717849731</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H228" t="n">
         <v>112606</v>
@@ -7068,7 +7068,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.25303649902344</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H231" t="n">
         <v>105323</v>
@@ -7097,7 +7097,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098394393921</v>
+        <v>2.26098370552063</v>
       </c>
       <c r="H232" t="n">
         <v>54749</v>
@@ -7126,7 +7126,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495742797852</v>
+        <v>2.26495766639709</v>
       </c>
       <c r="H233" t="n">
         <v>33872</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>2.22522163391113</v>
+        <v>2.22522139549255</v>
       </c>
       <c r="H234" t="n">
         <v>82103</v>
@@ -7184,7 +7184,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="n">
-        <v>2.22389698028564</v>
+        <v>2.22389721870422</v>
       </c>
       <c r="H235" t="n">
         <v>107495</v>
@@ -7213,7 +7213,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25303649902344</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H236" t="n">
         <v>166280</v>
@@ -7242,7 +7242,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482604026794</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H237" t="n">
         <v>48104</v>
@@ -7300,7 +7300,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>2.25171232223511</v>
+        <v>2.25171208381653</v>
       </c>
       <c r="H239" t="n">
         <v>111810</v>
@@ -7358,7 +7358,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H241" t="n">
         <v>218337</v>
@@ -7387,7 +7387,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608669281006</v>
+        <v>2.39608693122864</v>
       </c>
       <c r="H242" t="n">
         <v>275325</v>
@@ -7416,7 +7416,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="n">
-        <v>2.40668296813965</v>
+        <v>2.40668320655823</v>
       </c>
       <c r="H243" t="n">
         <v>104163</v>
@@ -7445,7 +7445,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="n">
-        <v>2.41198086738586</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H244" t="n">
         <v>143146</v>
@@ -7532,7 +7532,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="n">
-        <v>2.48350596427917</v>
+        <v>2.48350620269775</v>
       </c>
       <c r="H247" t="n">
         <v>122320</v>
@@ -7590,7 +7590,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.45039319992065</v>
+        <v>2.4503927230835</v>
       </c>
       <c r="H249" t="n">
         <v>141900</v>
@@ -7735,7 +7735,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="n">
-        <v>2.50204968452454</v>
+        <v>2.50204992294312</v>
       </c>
       <c r="H254" t="n">
         <v>103937</v>
@@ -7764,7 +7764,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H255" t="n">
         <v>71140</v>
@@ -7851,7 +7851,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="n">
-        <v>2.54708409309387</v>
+        <v>2.54708385467529</v>
       </c>
       <c r="H258" t="n">
         <v>159203</v>
@@ -7880,7 +7880,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H259" t="n">
         <v>160972</v>
@@ -7909,7 +7909,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H260" t="n">
         <v>231873</v>
@@ -8083,7 +8083,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="n">
-        <v>2.50204968452454</v>
+        <v>2.50204992294312</v>
       </c>
       <c r="H266" t="n">
         <v>156717</v>
@@ -8141,7 +8141,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.53648734092712</v>
+        <v>2.5364875793457</v>
       </c>
       <c r="H268" t="n">
         <v>422771</v>
@@ -8228,7 +8228,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165361404419</v>
+        <v>2.56165385246277</v>
       </c>
       <c r="H271" t="n">
         <v>288062</v>
@@ -8286,7 +8286,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.5205934047699</v>
+        <v>2.52059292793274</v>
       </c>
       <c r="H273" t="n">
         <v>263075</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363830566406</v>
+        <v>2.46363806724548</v>
       </c>
       <c r="H275" t="n">
         <v>198253</v>
@@ -8373,7 +8373,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.44376993179321</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H276" t="n">
         <v>157304</v>
@@ -8402,7 +8402,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="n">
-        <v>2.42390203475952</v>
+        <v>2.42390179634094</v>
       </c>
       <c r="H277" t="n">
         <v>129770</v>
@@ -8431,7 +8431,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138483047485</v>
+        <v>2.40138459205627</v>
       </c>
       <c r="H278" t="n">
         <v>362112</v>
@@ -8460,7 +8460,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>2.37092065811157</v>
+        <v>2.37092041969299</v>
       </c>
       <c r="H279" t="n">
         <v>309995</v>
@@ -8489,7 +8489,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356972694397</v>
+        <v>2.37356948852539</v>
       </c>
       <c r="H280" t="n">
         <v>114037</v>
@@ -8518,7 +8518,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="n">
-        <v>2.34310555458069</v>
+        <v>2.34310531616211</v>
       </c>
       <c r="H281" t="n">
         <v>266394</v>
@@ -8547,7 +8547,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="n">
-        <v>2.42257738113403</v>
+        <v>2.42257761955261</v>
       </c>
       <c r="H282" t="n">
         <v>228893</v>
@@ -8576,7 +8576,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019275665283</v>
+        <v>2.38019227981567</v>
       </c>
       <c r="H283" t="n">
         <v>99628</v>
@@ -8605,7 +8605,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.3656222820282</v>
+        <v>2.36562252044678</v>
       </c>
       <c r="H284" t="n">
         <v>69136</v>
@@ -8634,7 +8634,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>2.36164879798889</v>
+        <v>2.36164855957031</v>
       </c>
       <c r="H285" t="n">
         <v>138083</v>
@@ -8663,7 +8663,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="n">
-        <v>2.32853555679321</v>
+        <v>2.32853531837463</v>
       </c>
       <c r="H286" t="n">
         <v>143452</v>
@@ -8721,7 +8721,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985997200012</v>
+        <v>2.32985973358154</v>
       </c>
       <c r="H288" t="n">
         <v>130996</v>
@@ -8779,7 +8779,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476203918457</v>
+        <v>2.39476251602173</v>
       </c>
       <c r="H290" t="n">
         <v>374020</v>
@@ -8837,7 +8837,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H292" t="n">
         <v>129497</v>
@@ -8866,7 +8866,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006017684937</v>
+        <v>2.40006041526794</v>
       </c>
       <c r="H293" t="n">
         <v>70534</v>
@@ -8895,7 +8895,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886786460876</v>
+        <v>2.37886762619019</v>
       </c>
       <c r="H294" t="n">
         <v>84182</v>
@@ -8924,7 +8924,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.40403389930725</v>
+        <v>2.40403437614441</v>
       </c>
       <c r="H295" t="n">
         <v>126484</v>
@@ -8953,7 +8953,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35767483711243</v>
+        <v>2.35767531394958</v>
       </c>
       <c r="H296" t="n">
         <v>190410</v>
@@ -8982,7 +8982,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999207496643</v>
+        <v>2.30999183654785</v>
       </c>
       <c r="H297" t="n">
         <v>327861</v>
@@ -9011,7 +9011,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="n">
-        <v>2.34575462341309</v>
+        <v>2.34575486183167</v>
       </c>
       <c r="H298" t="n">
         <v>65455</v>
@@ -9040,7 +9040,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.36429786682129</v>
+        <v>2.36429762840271</v>
       </c>
       <c r="H299" t="n">
         <v>92767</v>
@@ -9069,7 +9069,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H300" t="n">
         <v>154051</v>
@@ -9127,7 +9127,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="n">
-        <v>2.50469875335693</v>
+        <v>2.50469899177551</v>
       </c>
       <c r="H302" t="n">
         <v>283293</v>
@@ -9156,7 +9156,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761226654053</v>
+        <v>2.46761202812195</v>
       </c>
       <c r="H303" t="n">
         <v>262776</v>
@@ -9214,7 +9214,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.54973292350769</v>
+        <v>2.54973316192627</v>
       </c>
       <c r="H305" t="n">
         <v>523792</v>
@@ -9272,7 +9272,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622361183167</v>
+        <v>2.57622385025024</v>
       </c>
       <c r="H307" t="n">
         <v>428054</v>
@@ -9388,7 +9388,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63185429573059</v>
+        <v>2.63185453414917</v>
       </c>
       <c r="H311" t="n">
         <v>305933</v>
@@ -9417,7 +9417,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.70073008537292</v>
+        <v>2.7007303237915</v>
       </c>
       <c r="H312" t="n">
         <v>590494</v>
@@ -9533,7 +9533,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252396583557</v>
+        <v>2.93252420425415</v>
       </c>
       <c r="H316" t="n">
         <v>857622</v>
@@ -9562,7 +9562,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.06497740745544</v>
+        <v>3.0649778842926</v>
       </c>
       <c r="H317" t="n">
         <v>1978795</v>
@@ -9591,7 +9591,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02789092063904</v>
+        <v>3.02789068222046</v>
       </c>
       <c r="H318" t="n">
         <v>1098038</v>
@@ -9649,7 +9649,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907841682434</v>
+        <v>2.84907793998718</v>
       </c>
       <c r="H320" t="n">
         <v>786928</v>
@@ -9707,7 +9707,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444489479065</v>
+        <v>2.94444513320923</v>
       </c>
       <c r="H322" t="n">
         <v>480186</v>
@@ -9736,7 +9736,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="n">
-        <v>2.93914723396301</v>
+        <v>2.93914699554443</v>
       </c>
       <c r="H323" t="n">
         <v>302239</v>
@@ -9765,7 +9765,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H324" t="n">
         <v>228643</v>
@@ -9794,7 +9794,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.99212861061096</v>
+        <v>2.99212837219238</v>
       </c>
       <c r="H325" t="n">
         <v>565930</v>
@@ -9823,7 +9823,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.99477696418762</v>
+        <v>2.9947772026062</v>
       </c>
       <c r="H326" t="n">
         <v>373530</v>
@@ -9852,7 +9852,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="n">
-        <v>3.04510951042175</v>
+        <v>3.04510974884033</v>
       </c>
       <c r="H327" t="n">
         <v>348998</v>
@@ -9881,7 +9881,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G328" t="n">
-        <v>3.05040788650513</v>
+        <v>3.05040764808655</v>
       </c>
       <c r="H328" t="n">
         <v>187071</v>
@@ -9910,7 +9910,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848695755005</v>
+        <v>3.03848648071289</v>
       </c>
       <c r="H329" t="n">
         <v>242448</v>
@@ -10055,7 +10055,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>2.92722630500793</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H334" t="n">
         <v>171240</v>
@@ -10084,7 +10084,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G335" t="n">
-        <v>2.8821918964386</v>
+        <v>2.88219165802002</v>
       </c>
       <c r="H335" t="n">
         <v>311784</v>
@@ -10113,7 +10113,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97226023674011</v>
+        <v>2.97225975990295</v>
       </c>
       <c r="H336" t="n">
         <v>271824</v>
@@ -10171,7 +10171,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067185401917</v>
+        <v>3.01067209243774</v>
       </c>
       <c r="H338" t="n">
         <v>333907</v>
@@ -10258,7 +10258,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967998504639</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H341" t="n">
         <v>486269</v>
@@ -10287,7 +10287,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="n">
-        <v>3.09146857261658</v>
+        <v>3.09146881103516</v>
       </c>
       <c r="H342" t="n">
         <v>699107</v>
@@ -10316,7 +10316,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173230171204</v>
+        <v>3.05173206329346</v>
       </c>
       <c r="H343" t="n">
         <v>351338</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484601974487</v>
+        <v>3.08484554290771</v>
       </c>
       <c r="H344" t="n">
         <v>309892</v>
@@ -10403,7 +10403,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637063980103</v>
+        <v>3.15637040138245</v>
       </c>
       <c r="H346" t="n">
         <v>987482</v>
@@ -10461,7 +10461,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.00669813156128</v>
+        <v>3.00669836997986</v>
       </c>
       <c r="H348" t="n">
         <v>392406</v>
@@ -10490,7 +10490,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967998504639</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H349" t="n">
         <v>335842</v>
@@ -10519,7 +10519,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981161117554</v>
+        <v>3.03981184959412</v>
       </c>
       <c r="H350" t="n">
         <v>361444</v>
@@ -10577,7 +10577,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159514427185</v>
+        <v>2.87159538269043</v>
       </c>
       <c r="H352" t="n">
         <v>379734</v>
@@ -10635,7 +10635,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H354" t="n">
         <v>462237</v>
@@ -10693,7 +10693,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887811660767</v>
+        <v>2.87887787818909</v>
       </c>
       <c r="H356" t="n">
         <v>535677</v>
@@ -10722,7 +10722,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="n">
-        <v>2.89227437973022</v>
+        <v>2.8922746181488</v>
       </c>
       <c r="H357" t="n">
         <v>254418</v>
@@ -10838,7 +10838,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.8989725112915</v>
+        <v>2.89897298812866</v>
       </c>
       <c r="H361" t="n">
         <v>217176</v>
@@ -10896,7 +10896,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.82395339012146</v>
+        <v>2.82395315170288</v>
       </c>
       <c r="H363" t="n">
         <v>342599</v>
@@ -10954,7 +10954,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644347190857</v>
+        <v>2.78644323348999</v>
       </c>
       <c r="H365" t="n">
         <v>82995</v>
@@ -11099,7 +11099,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>2.6993670463562</v>
+        <v>2.69936728477478</v>
       </c>
       <c r="H370" t="n">
         <v>299134</v>
@@ -11128,7 +11128,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>2.68731045722961</v>
+        <v>2.68730998039246</v>
       </c>
       <c r="H371" t="n">
         <v>152197</v>
@@ -11186,7 +11186,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="n">
-        <v>2.64846086502075</v>
+        <v>2.64846062660217</v>
       </c>
       <c r="H373" t="n">
         <v>468185</v>
@@ -11215,7 +11215,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="n">
-        <v>2.72080087661743</v>
+        <v>2.72080111503601</v>
       </c>
       <c r="H374" t="n">
         <v>862681</v>
@@ -11244,7 +11244,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="n">
-        <v>2.70204591751099</v>
+        <v>2.70204615592957</v>
       </c>
       <c r="H375" t="n">
         <v>271668</v>
@@ -11302,7 +11302,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H377" t="n">
         <v>218952</v>
@@ -11331,7 +11331,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649890899658</v>
+        <v>2.656498670578</v>
       </c>
       <c r="H378" t="n">
         <v>194294</v>
@@ -11418,7 +11418,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>2.64846086502075</v>
+        <v>2.64846062660217</v>
       </c>
       <c r="H381" t="n">
         <v>281322</v>
@@ -11447,7 +11447,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568688392639</v>
+        <v>2.62568712234497</v>
       </c>
       <c r="H382" t="n">
         <v>194044</v>
@@ -11476,7 +11476,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621477127075</v>
+        <v>2.59621500968933</v>
       </c>
       <c r="H383" t="n">
         <v>275930</v>
@@ -11534,7 +11534,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61229062080383</v>
+        <v>2.61229038238525</v>
       </c>
       <c r="H385" t="n">
         <v>222513</v>
@@ -11563,7 +11563,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291337966919</v>
       </c>
       <c r="H386" t="n">
         <v>259728</v>
@@ -11621,7 +11621,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G388" t="n">
-        <v>2.53727126121521</v>
+        <v>2.53727102279663</v>
       </c>
       <c r="H388" t="n">
         <v>249188</v>
@@ -11650,7 +11650,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H389" t="n">
         <v>213962</v>
@@ -11795,7 +11795,7 @@
         <v>4.06400012969971</v>
       </c>
       <c r="G394" t="n">
-        <v>2.72214078903198</v>
+        <v>2.72214102745056</v>
       </c>
       <c r="H394" t="n">
         <v>226635</v>
@@ -11853,7 +11853,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="n">
-        <v>2.68731045722961</v>
+        <v>2.68730998039246</v>
       </c>
       <c r="H396" t="n">
         <v>85342</v>
@@ -11969,7 +11969,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.63104557991028</v>
+        <v>2.6310453414917</v>
       </c>
       <c r="H400" t="n">
         <v>109092</v>
@@ -11998,7 +11998,7 @@
         <v>3.92199993133545</v>
       </c>
       <c r="G401" t="n">
-        <v>2.62702655792236</v>
+        <v>2.62702631950378</v>
       </c>
       <c r="H401" t="n">
         <v>93407</v>
@@ -12027,7 +12027,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H402" t="n">
         <v>129322</v>
@@ -12114,7 +12114,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H405" t="n">
         <v>195865</v>
@@ -12143,7 +12143,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381932258606</v>
+        <v>2.65381908416748</v>
       </c>
       <c r="H406" t="n">
         <v>110887</v>
@@ -12317,7 +12317,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H412" t="n">
         <v>148944</v>
@@ -12346,7 +12346,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291337966919</v>
       </c>
       <c r="H413" t="n">
         <v>90682</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H414" t="n">
         <v>196816</v>
@@ -12433,7 +12433,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H416" t="n">
         <v>50142</v>
@@ -12462,7 +12462,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344150543213</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H417" t="n">
         <v>103218</v>
@@ -12491,7 +12491,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="n">
-        <v>2.51181793212891</v>
+        <v>2.51181769371033</v>
       </c>
       <c r="H418" t="n">
         <v>297656</v>
@@ -12520,7 +12520,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459191322327</v>
+        <v>2.53459167480469</v>
       </c>
       <c r="H419" t="n">
         <v>215549</v>
@@ -12549,7 +12549,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="n">
-        <v>2.5225350856781</v>
+        <v>2.52253484725952</v>
       </c>
       <c r="H420" t="n">
         <v>95268</v>
@@ -12578,7 +12578,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325223922729</v>
+        <v>2.53325200080872</v>
       </c>
       <c r="H421" t="n">
         <v>130865</v>
@@ -12607,7 +12607,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H422" t="n">
         <v>133276</v>
@@ -12665,7 +12665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H424" t="n">
         <v>51012</v>
@@ -12723,7 +12723,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G426" t="n">
-        <v>2.48770475387573</v>
+        <v>2.48770451545715</v>
       </c>
       <c r="H426" t="n">
         <v>80945</v>
@@ -12752,7 +12752,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56004452705383</v>
+        <v>2.56004476547241</v>
       </c>
       <c r="H427" t="n">
         <v>193537</v>
@@ -12810,7 +12810,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157370567322</v>
+        <v>2.60157346725464</v>
       </c>
       <c r="H429" t="n">
         <v>130021</v>
@@ -12839,7 +12839,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200719833374</v>
+        <v>2.55200695991516</v>
       </c>
       <c r="H430" t="n">
         <v>130300</v>
@@ -12926,7 +12926,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.71678256988525</v>
+        <v>2.71678233146667</v>
       </c>
       <c r="H433" t="n">
         <v>449341</v>
@@ -12955,7 +12955,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189632415771</v>
+        <v>2.81189656257629</v>
       </c>
       <c r="H434" t="n">
         <v>677293</v>
@@ -12984,7 +12984,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323552131653</v>
       </c>
       <c r="H435" t="n">
         <v>606578</v>
@@ -13013,7 +13013,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85342526435852</v>
+        <v>2.85342574119568</v>
       </c>
       <c r="H436" t="n">
         <v>325483</v>
@@ -13100,7 +13100,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94719982147217</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H439" t="n">
         <v>359505</v>
@@ -13129,7 +13129,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>2.92040705680847</v>
+        <v>2.92040681838989</v>
       </c>
       <c r="H440" t="n">
         <v>311701</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>2.88021779060364</v>
+        <v>2.8802182674408</v>
       </c>
       <c r="H442" t="n">
         <v>440312</v>
@@ -13216,7 +13216,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136867523193</v>
+        <v>2.84136843681335</v>
       </c>
       <c r="H443" t="n">
         <v>279165</v>
@@ -13245,7 +13245,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H444" t="n">
         <v>227702</v>
@@ -13274,7 +13274,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682152748108</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H445" t="n">
         <v>208778</v>
@@ -13303,7 +13303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323552131653</v>
       </c>
       <c r="H446" t="n">
         <v>218622</v>
@@ -13332,7 +13332,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="n">
-        <v>2.85744404792786</v>
+        <v>2.85744380950928</v>
       </c>
       <c r="H447" t="n">
         <v>204402</v>
@@ -13361,7 +13361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682152748108</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H448" t="n">
         <v>119126</v>
@@ -13390,7 +13390,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H449" t="n">
         <v>292316</v>
@@ -13506,7 +13506,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663226127625</v>
+        <v>2.82663249969482</v>
       </c>
       <c r="H453" t="n">
         <v>1050600</v>
@@ -13564,7 +13564,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887811660767</v>
+        <v>2.87887787818909</v>
       </c>
       <c r="H455" t="n">
         <v>244063</v>
@@ -13622,7 +13622,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567088127136</v>
+        <v>2.90567111968994</v>
       </c>
       <c r="H457" t="n">
         <v>257517</v>
@@ -13651,7 +13651,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H458" t="n">
         <v>354316</v>
@@ -13709,7 +13709,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.84002876281738</v>
+        <v>2.84002828598022</v>
       </c>
       <c r="H460" t="n">
         <v>234215</v>
@@ -13738,7 +13738,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="n">
-        <v>2.86280274391174</v>
+        <v>2.86280250549316</v>
       </c>
       <c r="H461" t="n">
         <v>278042</v>
@@ -13767,7 +13767,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H462" t="n">
         <v>461987</v>
@@ -13825,7 +13825,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916177749634</v>
+        <v>2.93916201591492</v>
       </c>
       <c r="H464" t="n">
         <v>296201</v>
@@ -13854,7 +13854,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92040705680847</v>
+        <v>2.92040681838989</v>
       </c>
       <c r="H465" t="n">
         <v>172474</v>
@@ -13883,7 +13883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94719982147217</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H466" t="n">
         <v>276862</v>
@@ -13941,7 +13941,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>2.92576599121094</v>
+        <v>2.92576551437378</v>
       </c>
       <c r="H468" t="n">
         <v>376809</v>
@@ -13970,7 +13970,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88155770301819</v>
+        <v>2.88155722618103</v>
       </c>
       <c r="H469" t="n">
         <v>246783</v>
@@ -14028,7 +14028,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648242950439</v>
+        <v>2.93648266792297</v>
       </c>
       <c r="H471" t="n">
         <v>136035</v>
@@ -14057,7 +14057,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.93246340751648</v>
+        <v>2.93246364593506</v>
       </c>
       <c r="H472" t="n">
         <v>142444</v>
@@ -14086,7 +14086,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>2.90835022926331</v>
+        <v>2.90834999084473</v>
       </c>
       <c r="H473" t="n">
         <v>172391</v>
@@ -14144,7 +14144,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8855767250061</v>
+        <v>2.88557648658752</v>
       </c>
       <c r="H475" t="n">
         <v>113109</v>
@@ -14173,7 +14173,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031218528748</v>
+        <v>2.90031242370605</v>
       </c>
       <c r="H476" t="n">
         <v>293657</v>
@@ -14202,7 +14202,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>2.88021779060364</v>
+        <v>2.8802182674408</v>
       </c>
       <c r="H477" t="n">
         <v>371178</v>
@@ -14231,7 +14231,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270834922791</v>
+        <v>2.84270787239075</v>
       </c>
       <c r="H478" t="n">
         <v>266545</v>
@@ -14318,7 +14318,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.64042282104492</v>
+        <v>2.64042329788208</v>
       </c>
       <c r="H481" t="n">
         <v>1595732</v>
@@ -14347,7 +14347,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.61229062080383</v>
+        <v>2.61229038238525</v>
       </c>
       <c r="H482" t="n">
         <v>381717</v>
@@ -14376,7 +14376,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.58817744255066</v>
+        <v>2.58817720413208</v>
       </c>
       <c r="H483" t="n">
         <v>299109</v>
@@ -14434,7 +14434,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H485" t="n">
         <v>239693</v>
@@ -14463,7 +14463,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H486" t="n">
         <v>174243</v>
@@ -14666,7 +14666,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H493" t="n">
         <v>248344</v>
@@ -14724,7 +14724,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H495" t="n">
         <v>459746</v>
@@ -14782,7 +14782,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62970590591431</v>
+        <v>2.62970638275146</v>
       </c>
       <c r="H497" t="n">
         <v>169752</v>
@@ -14898,7 +14898,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344150543213</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H501" t="n">
         <v>511482</v>
@@ -14956,7 +14956,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344150543213</v>
+        <v>2.57344102859497</v>
       </c>
       <c r="H503" t="n">
         <v>442866</v>
@@ -14985,7 +14985,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H504" t="n">
         <v>308246</v>
@@ -15014,7 +15014,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51315760612488</v>
+        <v>2.51315784454346</v>
       </c>
       <c r="H505" t="n">
         <v>239707</v>
@@ -15043,7 +15043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H506" t="n">
         <v>188484</v>
@@ -15072,7 +15072,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325223922729</v>
+        <v>2.53325200080872</v>
       </c>
       <c r="H507" t="n">
         <v>155274</v>
@@ -15101,7 +15101,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057289123535</v>
+        <v>2.53057265281677</v>
       </c>
       <c r="H508" t="n">
         <v>166223</v>
@@ -15159,7 +15159,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119541168213</v>
+        <v>2.52119517326355</v>
       </c>
       <c r="H510" t="n">
         <v>181112</v>
@@ -15188,7 +15188,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H511" t="n">
         <v>183688</v>
@@ -15217,7 +15217,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G512" t="n">
-        <v>2.46894955635071</v>
+        <v>2.46894979476929</v>
       </c>
       <c r="H512" t="n">
         <v>202096</v>
@@ -15246,7 +15246,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H513" t="n">
         <v>248411</v>
@@ -15304,7 +15304,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.57210183143616</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H515" t="n">
         <v>481721</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.57210183143616</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H517" t="n">
         <v>342428</v>
@@ -15420,7 +15420,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H519" t="n">
         <v>422125</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H520" t="n">
         <v>236775</v>
@@ -15478,7 +15478,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>2.54195952415466</v>
+        <v>2.54196000099182</v>
       </c>
       <c r="H521" t="n">
         <v>308599</v>
@@ -15565,7 +15565,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.52856349945068</v>
+        <v>2.5285632610321</v>
       </c>
       <c r="H524" t="n">
         <v>208864</v>
@@ -15594,7 +15594,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H525" t="n">
         <v>259926</v>
@@ -15652,7 +15652,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578151702881</v>
+        <v>2.64578175544739</v>
       </c>
       <c r="H527" t="n">
         <v>344329</v>
@@ -15739,7 +15739,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>2.61229062080383</v>
+        <v>2.61229038238525</v>
       </c>
       <c r="H530" t="n">
         <v>222183</v>
@@ -15768,7 +15768,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="n">
-        <v>2.57545042037964</v>
+        <v>2.5754508972168</v>
       </c>
       <c r="H531" t="n">
         <v>188683</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H532" t="n">
         <v>266372</v>
@@ -15826,7 +15826,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H533" t="n">
         <v>272113</v>
@@ -15884,7 +15884,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.57210183143616</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H535" t="n">
         <v>657310</v>
@@ -15913,7 +15913,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H536" t="n">
         <v>753926</v>
@@ -15971,7 +15971,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.54865789413452</v>
+        <v>2.5486581325531</v>
       </c>
       <c r="H538" t="n">
         <v>187640</v>
@@ -16029,7 +16029,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H540" t="n">
         <v>333031</v>
@@ -16087,7 +16087,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148659706116</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H542" t="n">
         <v>168325</v>
@@ -16116,7 +16116,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.45488309860229</v>
+        <v>2.45488333702087</v>
       </c>
       <c r="H543" t="n">
         <v>168193</v>
@@ -16174,7 +16174,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H545" t="n">
         <v>205807</v>
@@ -16261,7 +16261,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G548" t="n">
-        <v>2.39125037193298</v>
+        <v>2.39125061035156</v>
       </c>
       <c r="H548" t="n">
         <v>225604</v>
@@ -16290,7 +16290,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>2.39794898033142</v>
+        <v>2.39794874191284</v>
       </c>
       <c r="H549" t="n">
         <v>151085</v>
@@ -16377,7 +16377,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>2.37115573883057</v>
+        <v>2.37115621566772</v>
       </c>
       <c r="H552" t="n">
         <v>210013</v>
@@ -16493,7 +16493,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>2.14676713943481</v>
+        <v>2.14676690101624</v>
       </c>
       <c r="H556" t="n">
         <v>427000</v>
@@ -16551,7 +16551,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>2.2271454334259</v>
+        <v>2.22714519500732</v>
       </c>
       <c r="H558" t="n">
         <v>273606</v>
@@ -16580,7 +16580,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G559" t="n">
-        <v>2.24723982810974</v>
+        <v>2.24723958969116</v>
       </c>
       <c r="H559" t="n">
         <v>293372</v>
@@ -16638,7 +16638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700336456299</v>
+        <v>2.19700312614441</v>
       </c>
       <c r="H561" t="n">
         <v>269006</v>
@@ -16667,7 +16667,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365453720093</v>
+        <v>2.19365429878235</v>
       </c>
       <c r="H562" t="n">
         <v>397917</v>
@@ -16696,7 +16696,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337063789368</v>
+        <v>2.13337087631226</v>
       </c>
       <c r="H563" t="n">
         <v>656760</v>
@@ -16754,7 +16754,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695616722107</v>
+        <v>2.18695640563965</v>
       </c>
       <c r="H565" t="n">
         <v>2292967</v>
@@ -16783,7 +16783,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="n">
-        <v>2.34436345100403</v>
+        <v>2.34436368942261</v>
       </c>
       <c r="H566" t="n">
         <v>1700593</v>
@@ -16812,7 +16812,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.2572865486145</v>
+        <v>2.25728678703308</v>
       </c>
       <c r="H567" t="n">
         <v>535502</v>
@@ -16841,7 +16841,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>2.27403259277344</v>
+        <v>2.27403211593628</v>
       </c>
       <c r="H568" t="n">
         <v>278538</v>
@@ -16957,7 +16957,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.4113450050354</v>
+        <v>2.41134524345398</v>
       </c>
       <c r="H572" t="n">
         <v>584347</v>
@@ -16986,7 +16986,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.38455247879028</v>
+        <v>2.3845522403717</v>
       </c>
       <c r="H573" t="n">
         <v>439152</v>
@@ -17015,7 +17015,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483637809753</v>
+        <v>2.44483613967896</v>
       </c>
       <c r="H574" t="n">
         <v>662269</v>
@@ -17044,7 +17044,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="n">
-        <v>2.46493053436279</v>
+        <v>2.46493101119995</v>
       </c>
       <c r="H575" t="n">
         <v>419566</v>
@@ -17073,7 +17073,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43813800811768</v>
+        <v>2.43813824653625</v>
       </c>
       <c r="H576" t="n">
         <v>366638</v>
@@ -17131,7 +17131,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>2.43813800811768</v>
+        <v>2.43813824653625</v>
       </c>
       <c r="H578" t="n">
         <v>231016</v>
@@ -17160,7 +17160,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.43813800811768</v>
+        <v>2.43813824653625</v>
       </c>
       <c r="H579" t="n">
         <v>244165</v>
@@ -17189,7 +17189,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148659706116</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H580" t="n">
         <v>207497</v>
@@ -17218,7 +17218,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>2.43813800811768</v>
+        <v>2.43813824653625</v>
       </c>
       <c r="H581" t="n">
         <v>150530</v>
@@ -17334,7 +17334,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.45153427124023</v>
+        <v>2.45153403282166</v>
       </c>
       <c r="H585" t="n">
         <v>145222</v>
@@ -17392,7 +17392,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507212638855</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H587" t="n">
         <v>277880</v>
@@ -17421,7 +17421,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H588" t="n">
         <v>131179</v>
@@ -17450,7 +17450,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H589" t="n">
         <v>121975</v>
@@ -17479,7 +17479,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172329902649</v>
+        <v>2.49172353744507</v>
       </c>
       <c r="H590" t="n">
         <v>91101</v>
@@ -17508,7 +17508,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H591" t="n">
         <v>51454</v>
@@ -17537,7 +17537,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="n">
-        <v>2.51181793212891</v>
+        <v>2.51181769371033</v>
       </c>
       <c r="H592" t="n">
         <v>172383</v>
@@ -17566,7 +17566,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="n">
-        <v>2.45153427124023</v>
+        <v>2.45153403282166</v>
       </c>
       <c r="H593" t="n">
         <v>194484</v>
@@ -17595,7 +17595,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511980056763</v>
+        <v>2.50511956214905</v>
       </c>
       <c r="H594" t="n">
         <v>142722</v>
@@ -17624,7 +17624,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="n">
-        <v>2.50177049636841</v>
+        <v>2.50177025794983</v>
       </c>
       <c r="H595" t="n">
         <v>206947</v>
@@ -17653,7 +17653,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="n">
-        <v>2.48837423324585</v>
+        <v>2.48837447166443</v>
       </c>
       <c r="H596" t="n">
         <v>218613</v>
@@ -17682,7 +17682,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507212638855</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H597" t="n">
         <v>234943</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H598" t="n">
         <v>111857</v>
@@ -17740,7 +17740,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H599" t="n">
         <v>150521</v>
@@ -17769,7 +17769,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>2.45488309860229</v>
+        <v>2.45488333702087</v>
       </c>
       <c r="H600" t="n">
         <v>114328</v>
@@ -17798,7 +17798,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="n">
-        <v>2.46493053436279</v>
+        <v>2.46493101119995</v>
       </c>
       <c r="H601" t="n">
         <v>180468</v>
@@ -17827,7 +17827,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832727432251</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H602" t="n">
         <v>187716</v>
@@ -17885,7 +17885,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.43702125549316</v>
+        <v>2.43702173233032</v>
       </c>
       <c r="H604" t="n">
         <v>438968</v>
@@ -17914,7 +17914,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.31998896598816</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H605" t="n">
         <v>1262853</v>
@@ -18001,7 +18001,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>2.26491546630859</v>
+        <v>2.26491522789001</v>
       </c>
       <c r="H608" t="n">
         <v>241172</v>
@@ -18059,7 +18059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.22360992431641</v>
+        <v>2.22360968589783</v>
       </c>
       <c r="H610" t="n">
         <v>258239</v>
@@ -18146,7 +18146,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H613" t="n">
         <v>279124</v>
@@ -18175,7 +18175,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H614" t="n">
         <v>249358</v>
@@ -18262,7 +18262,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H617" t="n">
         <v>287908</v>
@@ -18349,7 +18349,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H620" t="n">
         <v>204163</v>
@@ -18436,7 +18436,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770498275757</v>
+        <v>2.24770522117615</v>
       </c>
       <c r="H623" t="n">
         <v>57699</v>
@@ -18465,7 +18465,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589486122131</v>
       </c>
       <c r="H624" t="n">
         <v>191609</v>
@@ -18523,7 +18523,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408402442932</v>
       </c>
       <c r="H626" t="n">
         <v>133097</v>
@@ -18552,7 +18552,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>2.35441064834595</v>
+        <v>2.35441088676453</v>
       </c>
       <c r="H627" t="n">
         <v>289153</v>
@@ -18668,7 +18668,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212594985962</v>
       </c>
       <c r="H631" t="n">
         <v>206647</v>
@@ -18726,7 +18726,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473703384399</v>
+        <v>2.36473679542542</v>
       </c>
       <c r="H633" t="n">
         <v>866249</v>
@@ -18842,7 +18842,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.35785293579102</v>
+        <v>2.35785269737244</v>
       </c>
       <c r="H637" t="n">
         <v>276596</v>
@@ -18900,7 +18900,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.33720016479492</v>
+        <v>2.33719992637634</v>
       </c>
       <c r="H639" t="n">
         <v>136440</v>
@@ -18987,7 +18987,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.31998896598816</v>
+        <v>2.31998920440674</v>
       </c>
       <c r="H642" t="n">
         <v>44838</v>
@@ -19016,7 +19016,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589462280273</v>
+        <v>2.29589486122131</v>
       </c>
       <c r="H643" t="n">
         <v>117183</v>
@@ -19045,7 +19045,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H644" t="n">
         <v>158331</v>
@@ -19103,7 +19103,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082088470459</v>
+        <v>2.24082064628601</v>
       </c>
       <c r="H646" t="n">
         <v>138242</v>
@@ -19161,7 +19161,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H648" t="n">
         <v>204541</v>
@@ -19190,7 +19190,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>2.1995153427124</v>
+        <v>2.19951510429382</v>
       </c>
       <c r="H649" t="n">
         <v>159276</v>
@@ -19219,7 +19219,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.17886257171631</v>
+        <v>2.17886233329773</v>
       </c>
       <c r="H650" t="n">
         <v>98263</v>
@@ -19277,7 +19277,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H652" t="n">
         <v>43938</v>
@@ -19335,7 +19335,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="n">
-        <v>2.1995153427124</v>
+        <v>2.19951510429382</v>
       </c>
       <c r="H654" t="n">
         <v>79584</v>
@@ -19393,7 +19393,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H656" t="n">
         <v>94908</v>
@@ -19422,7 +19422,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15821003913879</v>
+        <v>2.15820980072021</v>
       </c>
       <c r="H657" t="n">
         <v>127746</v>
@@ -19451,7 +19451,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.22360992431641</v>
+        <v>2.22360968589783</v>
       </c>
       <c r="H658" t="n">
         <v>79691</v>
@@ -19509,7 +19509,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.22016787528992</v>
+        <v>2.2201681137085</v>
       </c>
       <c r="H660" t="n">
         <v>72516</v>
@@ -19596,7 +19596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H663" t="n">
         <v>128498</v>
@@ -19712,7 +19712,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H667" t="n">
         <v>147403</v>
@@ -19799,7 +19799,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20639944076538</v>
+        <v>2.2063992023468</v>
       </c>
       <c r="H670" t="n">
         <v>234133</v>
@@ -19828,7 +19828,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H671" t="n">
         <v>122606</v>
@@ -19886,7 +19886,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H673" t="n">
         <v>87561</v>
@@ -20031,7 +20031,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>2.12034606933594</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H678" t="n">
         <v>97627</v>
@@ -20060,7 +20060,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11001968383789</v>
       </c>
       <c r="H679" t="n">
         <v>147813</v>
@@ -20089,7 +20089,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H680" t="n">
         <v>72566</v>
@@ -20118,7 +20118,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H681" t="n">
         <v>90219</v>
@@ -20147,7 +20147,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H682" t="n">
         <v>38146</v>
@@ -20176,7 +20176,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690449714661</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H683" t="n">
         <v>89809</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.1065776348114</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H684" t="n">
         <v>106959</v>
@@ -20263,7 +20263,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>2.13067245483398</v>
+        <v>2.13067293167114</v>
       </c>
       <c r="H686" t="n">
         <v>92024</v>
@@ -20292,7 +20292,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690449714661</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H687" t="n">
         <v>150304</v>
@@ -20321,7 +20321,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H688" t="n">
         <v>283824</v>
@@ -20379,7 +20379,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>2.12034606933594</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H690" t="n">
         <v>188909</v>
@@ -20437,7 +20437,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H692" t="n">
         <v>87021</v>
@@ -20524,7 +20524,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>2.13067245483398</v>
+        <v>2.13067293167114</v>
       </c>
       <c r="H695" t="n">
         <v>137482</v>
@@ -20553,7 +20553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.1065776348114</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H696" t="n">
         <v>205834</v>
@@ -20611,7 +20611,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H698" t="n">
         <v>474404</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H701" t="n">
         <v>280938</v>
@@ -20756,7 +20756,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>2.05150413513184</v>
+        <v>2.05150389671326</v>
       </c>
       <c r="H703" t="n">
         <v>500439</v>
@@ -20785,7 +20785,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H704" t="n">
         <v>153586</v>
@@ -20843,7 +20843,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H706" t="n">
         <v>108391</v>
@@ -20872,7 +20872,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H707" t="n">
         <v>102562</v>
@@ -20930,7 +20930,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643039703369</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H709" t="n">
         <v>235805</v>
@@ -20988,7 +20988,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168256759644</v>
       </c>
       <c r="H711" t="n">
         <v>98948</v>
@@ -21017,7 +21017,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.94135630130768</v>
+        <v>1.94135618209839</v>
       </c>
       <c r="H712" t="n">
         <v>74593</v>
@@ -21220,7 +21220,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="n">
-        <v>1.81399726867676</v>
+        <v>1.81399750709534</v>
       </c>
       <c r="H719" t="n">
         <v>170042</v>
@@ -21307,7 +21307,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070353031158</v>
+        <v>1.92070341110229</v>
       </c>
       <c r="H722" t="n">
         <v>277130</v>
@@ -21336,7 +21336,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.90349292755127</v>
+        <v>1.90349316596985</v>
       </c>
       <c r="H723" t="n">
         <v>172278</v>
@@ -21365,7 +21365,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414569854736</v>
+        <v>1.92414557933807</v>
       </c>
       <c r="H724" t="n">
         <v>125557</v>
@@ -21394,7 +21394,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921919822693</v>
+        <v>1.97921943664551</v>
       </c>
       <c r="H725" t="n">
         <v>62710</v>
@@ -21481,7 +21481,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429341316223</v>
+        <v>2.03429365158081</v>
       </c>
       <c r="H728" t="n">
         <v>85910</v>
@@ -21510,7 +21510,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="n">
-        <v>2.05838799476624</v>
+        <v>2.05838823318481</v>
       </c>
       <c r="H729" t="n">
         <v>113777</v>
@@ -21539,7 +21539,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H730" t="n">
         <v>98831</v>
@@ -21568,7 +21568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099884033203</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H731" t="n">
         <v>181838</v>
@@ -21655,7 +21655,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H734" t="n">
         <v>134624</v>
@@ -21713,7 +21713,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.06183004379272</v>
+        <v>2.0618302822113</v>
       </c>
       <c r="H736" t="n">
         <v>119731</v>
@@ -21742,7 +21742,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H737" t="n">
         <v>129394</v>
@@ -21771,7 +21771,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889305114746</v>
+        <v>1.96889269351959</v>
       </c>
       <c r="H738" t="n">
         <v>161205</v>
@@ -21800,7 +21800,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168256759644</v>
       </c>
       <c r="H739" t="n">
         <v>264586</v>
@@ -21829,7 +21829,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758750915527</v>
+        <v>1.92758774757385</v>
       </c>
       <c r="H740" t="n">
         <v>177737</v>
@@ -21945,7 +21945,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>2.20639944076538</v>
+        <v>2.2063992023468</v>
       </c>
       <c r="H744" t="n">
         <v>196223</v>
@@ -22119,7 +22119,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918871879578</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H750" t="n">
         <v>204318</v>
@@ -22148,7 +22148,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H751" t="n">
         <v>49394</v>
@@ -22206,7 +22206,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.08936715126038</v>
+        <v>2.08936762809753</v>
       </c>
       <c r="H753" t="n">
         <v>238366</v>
@@ -22235,7 +22235,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509389877319</v>
+        <v>2.16509413719177</v>
       </c>
       <c r="H754" t="n">
         <v>409359</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H759" t="n">
         <v>342700</v>
@@ -22409,7 +22409,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212594985962</v>
       </c>
       <c r="H760" t="n">
         <v>297330</v>
@@ -22467,7 +22467,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.3440842628479</v>
+        <v>2.34408402442932</v>
       </c>
       <c r="H762" t="n">
         <v>257956</v>
@@ -22496,7 +22496,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G763" t="n">
-        <v>2.35785293579102</v>
+        <v>2.35785269737244</v>
       </c>
       <c r="H763" t="n">
         <v>242878</v>
@@ -22583,7 +22583,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="n">
-        <v>2.4198112487793</v>
+        <v>2.41981101036072</v>
       </c>
       <c r="H766" t="n">
         <v>344369</v>
@@ -22612,7 +22612,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H767" t="n">
         <v>205883</v>
@@ -22641,7 +22641,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H768" t="n">
         <v>360249</v>
@@ -22670,7 +22670,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H769" t="n">
         <v>456800</v>
@@ -22699,7 +22699,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H770" t="n">
         <v>203705</v>
@@ -22728,7 +22728,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H771" t="n">
         <v>431119</v>
@@ -22786,7 +22786,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H773" t="n">
         <v>383952</v>
@@ -22815,7 +22815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H774" t="n">
         <v>376439</v>
@@ -22873,7 +22873,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274847984314</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H776" t="n">
         <v>426695</v>
@@ -22931,7 +22931,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H778" t="n">
         <v>296450</v>
@@ -22960,7 +22960,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>2.50242185592651</v>
+        <v>2.50242161750793</v>
       </c>
       <c r="H779" t="n">
         <v>334437</v>
@@ -22989,7 +22989,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307415008545</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H780" t="n">
         <v>192769</v>
@@ -23018,7 +23018,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307415008545</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H781" t="n">
         <v>177735</v>
@@ -23047,7 +23047,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274847984314</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H782" t="n">
         <v>217858</v>
@@ -23134,7 +23134,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H785" t="n">
         <v>236542</v>
@@ -23163,7 +23163,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.6435489654541</v>
+        <v>2.64354872703552</v>
       </c>
       <c r="H786" t="n">
         <v>412937</v>
@@ -23221,7 +23221,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G788" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H788" t="n">
         <v>315628</v>
@@ -23250,7 +23250,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67797017097473</v>
+        <v>2.67796993255615</v>
       </c>
       <c r="H789" t="n">
         <v>248259</v>
@@ -23279,7 +23279,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H790" t="n">
         <v>328656</v>
@@ -23366,7 +23366,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224342346191</v>
+        <v>2.60224318504333</v>
       </c>
       <c r="H793" t="n">
         <v>285918</v>
@@ -23482,7 +23482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601161956787</v>
+        <v>2.61601185798645</v>
       </c>
       <c r="H797" t="n">
         <v>367842</v>
@@ -23511,7 +23511,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880137443542</v>
+        <v>2.59880113601685</v>
       </c>
       <c r="H798" t="n">
         <v>105895</v>
@@ -23540,7 +23540,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>2.56437969207764</v>
+        <v>2.56437993049622</v>
       </c>
       <c r="H799" t="n">
         <v>201471</v>
@@ -23627,7 +23627,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.69173860549927</v>
+        <v>2.69173884391785</v>
       </c>
       <c r="H802" t="n">
         <v>302710</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>2.68485426902771</v>
+        <v>2.68485403060913</v>
       </c>
       <c r="H804" t="n">
         <v>170162</v>
@@ -23772,7 +23772,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.71239137649536</v>
+        <v>2.7123908996582</v>
       </c>
       <c r="H807" t="n">
         <v>271085</v>
@@ -23859,7 +23859,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="n">
-        <v>2.72960162162781</v>
+        <v>2.72960186004639</v>
       </c>
       <c r="H810" t="n">
         <v>150232</v>
@@ -23917,7 +23917,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.72960162162781</v>
+        <v>2.72960186004639</v>
       </c>
       <c r="H812" t="n">
         <v>131490</v>
@@ -23946,7 +23946,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>2.7261598110199</v>
+        <v>2.72615957260132</v>
       </c>
       <c r="H813" t="n">
         <v>104400</v>
@@ -24033,7 +24033,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>2.76058125495911</v>
+        <v>2.76058101654053</v>
       </c>
       <c r="H816" t="n">
         <v>220094</v>
@@ -24062,7 +24062,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>2.76746511459351</v>
+        <v>2.76746535301208</v>
       </c>
       <c r="H817" t="n">
         <v>265414</v>
@@ -24091,7 +24091,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304390907288</v>
+        <v>2.73304414749146</v>
       </c>
       <c r="H818" t="n">
         <v>216455</v>
@@ -24178,7 +24178,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G821" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H821" t="n">
         <v>429072</v>
@@ -24207,7 +24207,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.61256957054138</v>
+        <v>2.61256980895996</v>
       </c>
       <c r="H822" t="n">
         <v>177668</v>
@@ -24265,7 +24265,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H824" t="n">
         <v>459248</v>
@@ -24294,7 +24294,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H825" t="n">
         <v>305118</v>
@@ -24352,7 +24352,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G827" t="n">
-        <v>2.66075921058655</v>
+        <v>2.66075944900513</v>
       </c>
       <c r="H827" t="n">
         <v>287574</v>
@@ -24381,7 +24381,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912799835205</v>
       </c>
       <c r="H828" t="n">
         <v>412011</v>
@@ -24410,7 +24410,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322257995605</v>
+        <v>2.63322234153748</v>
       </c>
       <c r="H829" t="n">
         <v>67486</v>
@@ -24584,7 +24584,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H835" t="n">
         <v>355578</v>
@@ -24613,7 +24613,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.4266951084137</v>
+        <v>2.42669534683228</v>
       </c>
       <c r="H836" t="n">
         <v>233626</v>
@@ -24642,7 +24642,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423245429993</v>
+        <v>2.45423221588135</v>
       </c>
       <c r="H837" t="n">
         <v>108607</v>
@@ -24671,7 +24671,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>2.4439058303833</v>
+        <v>2.44390606880188</v>
       </c>
       <c r="H838" t="n">
         <v>182231</v>
@@ -24758,7 +24758,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357968330383</v>
+        <v>2.43357944488525</v>
       </c>
       <c r="H841" t="n">
         <v>124221</v>
@@ -24787,7 +24787,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="n">
-        <v>2.4198112487793</v>
+        <v>2.41981101036072</v>
       </c>
       <c r="H842" t="n">
         <v>263155</v>
@@ -24845,7 +24845,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H844" t="n">
         <v>59749</v>
@@ -24874,7 +24874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50586414337158</v>
+        <v>2.50586438179016</v>
       </c>
       <c r="H845" t="n">
         <v>222012</v>
@@ -24961,7 +24961,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>2.49897956848145</v>
+        <v>2.49897980690002</v>
       </c>
       <c r="H848" t="n">
         <v>191698</v>
@@ -24990,7 +24990,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013739585876</v>
+        <v>2.43013715744019</v>
       </c>
       <c r="H849" t="n">
         <v>115219</v>
@@ -25019,7 +25019,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.35441064834595</v>
+        <v>2.35441088676453</v>
       </c>
       <c r="H850" t="n">
         <v>388754</v>
@@ -25048,7 +25048,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="n">
-        <v>2.38883185386658</v>
+        <v>2.388831615448</v>
       </c>
       <c r="H851" t="n">
         <v>289904</v>
@@ -25077,7 +25077,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>2.31654739379883</v>
+        <v>2.31654715538025</v>
       </c>
       <c r="H852" t="n">
         <v>227097</v>
@@ -25106,7 +25106,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031582832336</v>
+        <v>2.33031606674194</v>
       </c>
       <c r="H853" t="n">
         <v>221581</v>
@@ -25222,7 +25222,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11001968383789</v>
       </c>
       <c r="H857" t="n">
         <v>429648</v>
@@ -25251,7 +25251,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>2.07904076576233</v>
+        <v>2.07904100418091</v>
       </c>
       <c r="H858" t="n">
         <v>179861</v>
@@ -25280,7 +25280,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.075599193573</v>
+        <v>2.07559895515442</v>
       </c>
       <c r="H859" t="n">
         <v>251246</v>
@@ -25309,7 +25309,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085160255432</v>
+        <v>2.03085112571716</v>
       </c>
       <c r="H860" t="n">
         <v>287672</v>
@@ -25367,7 +25367,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643039703369</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H862" t="n">
         <v>284968</v>
@@ -25454,7 +25454,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.9964302778244</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H865" t="n">
         <v>416439</v>
@@ -25483,7 +25483,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H866" t="n">
         <v>194008</v>
@@ -25541,7 +25541,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.94217908382416</v>
+        <v>1.94217920303345</v>
       </c>
       <c r="H868" t="n">
         <v>234747</v>
@@ -25570,7 +25570,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.95302951335907</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H869" t="n">
         <v>222484</v>
@@ -25599,7 +25599,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H870" t="n">
         <v>404038</v>
@@ -25628,7 +25628,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H871" t="n">
         <v>377733</v>
@@ -25715,7 +25715,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H874" t="n">
         <v>251629</v>
@@ -25744,7 +25744,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.9964302778244</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H875" t="n">
         <v>184992</v>
@@ -25773,7 +25773,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026289463043</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H876" t="n">
         <v>239841</v>
@@ -25802,7 +25802,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834634780884</v>
+        <v>1.97834658622742</v>
       </c>
       <c r="H877" t="n">
         <v>247637</v>
@@ -25831,7 +25831,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.95302951335907</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H878" t="n">
         <v>109838</v>
@@ -25889,7 +25889,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H880" t="n">
         <v>284652</v>
@@ -25947,7 +25947,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H882" t="n">
         <v>279659</v>
@@ -25976,7 +25976,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>1.93132925033569</v>
+        <v>1.9313291311264</v>
       </c>
       <c r="H883" t="n">
         <v>1099479</v>
@@ -26005,7 +26005,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601170063019</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H884" t="n">
         <v>286493</v>
@@ -26150,7 +26150,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H889" t="n">
         <v>274027</v>
@@ -26179,7 +26179,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069486618042</v>
+        <v>1.88069498538971</v>
       </c>
       <c r="H890" t="n">
         <v>170084</v>
@@ -26208,7 +26208,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601170063019</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H891" t="n">
         <v>279577</v>
@@ -26324,7 +26324,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.95302951335907</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H895" t="n">
         <v>800354</v>
@@ -26353,7 +26353,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H896" t="n">
         <v>911289</v>
@@ -26411,7 +26411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>2.07238125801086</v>
+        <v>2.07238149642944</v>
       </c>
       <c r="H898" t="n">
         <v>924209</v>
@@ -26440,7 +26440,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.03259754180908</v>
+        <v>2.0325973033905</v>
       </c>
       <c r="H899" t="n">
         <v>626504</v>
@@ -26469,7 +26469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.9964302778244</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H900" t="n">
         <v>386888</v>
@@ -26527,7 +26527,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93132925033569</v>
+        <v>1.9313291311264</v>
       </c>
       <c r="H902" t="n">
         <v>257125</v>
@@ -26556,7 +26556,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H903" t="n">
         <v>353686</v>
@@ -26585,7 +26585,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8300609588623</v>
+        <v>1.83006107807159</v>
       </c>
       <c r="H904" t="n">
         <v>909668</v>
@@ -26614,7 +26614,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069486618042</v>
+        <v>1.88069498538971</v>
       </c>
       <c r="H905" t="n">
         <v>562530</v>
@@ -26672,7 +26672,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601170063019</v>
+        <v>1.90601193904877</v>
       </c>
       <c r="H907" t="n">
         <v>228173</v>
@@ -26730,7 +26730,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.86261117458344</v>
+        <v>1.86261165142059</v>
       </c>
       <c r="H909" t="n">
         <v>371388</v>
@@ -26759,7 +26759,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H910" t="n">
         <v>493642</v>
@@ -26788,7 +26788,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792824745178</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H911" t="n">
         <v>261392</v>
@@ -26817,7 +26817,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431179523468</v>
       </c>
       <c r="H912" t="n">
         <v>465653</v>
@@ -26846,7 +26846,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474388599396</v>
       </c>
       <c r="H913" t="n">
         <v>618635</v>
@@ -26875,7 +26875,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H914" t="n">
         <v>465588</v>
@@ -26933,7 +26933,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H916" t="n">
         <v>862579</v>
@@ -26962,7 +26962,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199125766754</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H917" t="n">
         <v>497518</v>
@@ -27049,7 +27049,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H920" t="n">
         <v>347469</v>
@@ -27078,7 +27078,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327365875244</v>
+        <v>1.57327353954315</v>
       </c>
       <c r="H921" t="n">
         <v>763177</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.66369163990021</v>
+        <v>1.6636917591095</v>
       </c>
       <c r="H922" t="n">
         <v>294260</v>
@@ -27136,7 +27136,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H923" t="n">
         <v>378459</v>
@@ -27165,7 +27165,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>1.61667418479919</v>
+        <v>1.61667442321777</v>
       </c>
       <c r="H924" t="n">
         <v>432209</v>
@@ -27194,7 +27194,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.62029087543488</v>
+        <v>1.62029111385345</v>
       </c>
       <c r="H925" t="n">
         <v>696992</v>
@@ -27223,7 +27223,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>1.61667418479919</v>
+        <v>1.61667442321777</v>
       </c>
       <c r="H926" t="n">
         <v>277933</v>
@@ -27252,7 +27252,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.57689046859741</v>
+        <v>1.5768905878067</v>
       </c>
       <c r="H927" t="n">
         <v>526312</v>
@@ -27281,7 +27281,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.59135735034943</v>
+        <v>1.59135723114014</v>
       </c>
       <c r="H928" t="n">
         <v>250086</v>
@@ -27310,7 +27310,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.59859073162079</v>
+        <v>1.59859085083008</v>
       </c>
       <c r="H929" t="n">
         <v>220719</v>
@@ -27339,7 +27339,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G930" t="n">
-        <v>1.58412408828735</v>
+        <v>1.58412384986877</v>
       </c>
       <c r="H930" t="n">
         <v>987694</v>
@@ -27426,7 +27426,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>1.59497380256653</v>
+        <v>1.59497404098511</v>
       </c>
       <c r="H933" t="n">
         <v>252676</v>
@@ -27455,7 +27455,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305785179138</v>
       </c>
       <c r="H934" t="n">
         <v>287211</v>
@@ -27484,7 +27484,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645813941956</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H935" t="n">
         <v>361760</v>
@@ -27542,7 +27542,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H937" t="n">
         <v>332384</v>
@@ -27600,7 +27600,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G939" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517609596252</v>
       </c>
       <c r="H939" t="n">
         <v>258542</v>
@@ -27658,7 +27658,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G941" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H941" t="n">
         <v>345682</v>
@@ -27745,7 +27745,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H944" t="n">
         <v>336528</v>
@@ -27774,7 +27774,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H945" t="n">
         <v>255600</v>
@@ -27803,7 +27803,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H946" t="n">
         <v>241984</v>
@@ -27861,7 +27861,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305785179138</v>
       </c>
       <c r="H948" t="n">
         <v>774848</v>
@@ -27890,7 +27890,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>1.6130576133728</v>
+        <v>1.61305785179138</v>
       </c>
       <c r="H949" t="n">
         <v>404180</v>
@@ -27919,7 +27919,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G950" t="n">
-        <v>1.61667418479919</v>
+        <v>1.61667442321777</v>
       </c>
       <c r="H950" t="n">
         <v>294932</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.62029087543488</v>
+        <v>1.62029111385345</v>
       </c>
       <c r="H951" t="n">
         <v>262964</v>
@@ -27977,7 +27977,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64560806751251</v>
+        <v>1.6456081867218</v>
       </c>
       <c r="H952" t="n">
         <v>114952</v>
@@ -28122,7 +28122,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H957" t="n">
         <v>183628</v>
@@ -28151,7 +28151,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199125766754</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H958" t="n">
         <v>141207</v>
@@ -28180,7 +28180,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G959" t="n">
-        <v>1.63475799560547</v>
+        <v>1.63475811481476</v>
       </c>
       <c r="H959" t="n">
         <v>198189</v>
@@ -28238,7 +28238,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837480545044</v>
+        <v>1.63837468624115</v>
       </c>
       <c r="H961" t="n">
         <v>175327</v>
@@ -28267,7 +28267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H962" t="n">
         <v>546781</v>
@@ -28325,7 +28325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H964" t="n">
         <v>258696</v>
@@ -28354,7 +28354,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H965" t="n">
         <v>412054</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H966" t="n">
         <v>445642</v>
@@ -28470,7 +28470,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624245166779</v>
+        <v>1.69624209403992</v>
       </c>
       <c r="H969" t="n">
         <v>150403</v>
@@ -28499,7 +28499,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H970" t="n">
         <v>116106</v>
@@ -28528,7 +28528,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H971" t="n">
         <v>185489</v>
@@ -28557,7 +28557,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H972" t="n">
         <v>278746</v>
@@ -28586,7 +28586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815864086151</v>
       </c>
       <c r="H973" t="n">
         <v>190802</v>
@@ -28615,7 +28615,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G974" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H974" t="n">
         <v>161117</v>
@@ -28644,7 +28644,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H975" t="n">
         <v>145445</v>
@@ -28673,7 +28673,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H976" t="n">
         <v>145725</v>
@@ -28731,7 +28731,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H978" t="n">
         <v>456317</v>
@@ -28818,7 +28818,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772666931152</v>
+        <v>1.75772655010223</v>
       </c>
       <c r="H981" t="n">
         <v>635657</v>
@@ -28934,7 +28934,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134324073792</v>
+        <v>1.76134312152863</v>
       </c>
       <c r="H985" t="n">
         <v>462415</v>
@@ -28963,7 +28963,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G986" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517609596252</v>
       </c>
       <c r="H986" t="n">
         <v>235688</v>
@@ -29021,7 +29021,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H988" t="n">
         <v>321015</v>
@@ -29224,7 +29224,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H995" t="n">
         <v>1295316</v>
@@ -29282,7 +29282,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H997" t="n">
         <v>989644</v>
@@ -29311,7 +29311,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.93494582176208</v>
+        <v>1.9349457025528</v>
       </c>
       <c r="H998" t="n">
         <v>1204470</v>
@@ -29340,7 +29340,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G999" t="n">
-        <v>1.91686224937439</v>
+        <v>1.9168621301651</v>
       </c>
       <c r="H999" t="n">
         <v>662234</v>
@@ -29369,7 +29369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1000" t="n">
         <v>951588</v>
@@ -29398,7 +29398,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196315765381</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1001" t="n">
         <v>659632</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1002" t="n">
         <v>591585</v>
@@ -29456,7 +29456,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1003" t="n">
         <v>552967</v>
@@ -29543,7 +29543,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.03621387481689</v>
+        <v>2.03621435165405</v>
       </c>
       <c r="H1006" t="n">
         <v>950508</v>
@@ -29601,7 +29601,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.04344773292542</v>
+        <v>2.04344749450684</v>
       </c>
       <c r="H1008" t="n">
         <v>410384</v>
@@ -29659,7 +29659,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H1010" t="n">
         <v>295623</v>
@@ -29688,7 +29688,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919689655304</v>
+        <v>1.98919653892517</v>
       </c>
       <c r="H1011" t="n">
         <v>341025</v>
@@ -29717,7 +29717,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196315765381</v>
+        <v>1.98196339607239</v>
       </c>
       <c r="H1012" t="n">
         <v>244318</v>
@@ -29746,7 +29746,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281322956085</v>
+        <v>1.99281358718872</v>
       </c>
       <c r="H1013" t="n">
         <v>183722</v>
@@ -29775,7 +29775,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.9964302778244</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H1014" t="n">
         <v>219712</v>
@@ -29833,7 +29833,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H1016" t="n">
         <v>238710</v>
@@ -29891,7 +29891,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.93856263160706</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1018" t="n">
         <v>371965</v>
@@ -29949,7 +29949,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.93132925033569</v>
+        <v>1.9313291311264</v>
       </c>
       <c r="H1020" t="n">
         <v>417414</v>
@@ -29978,7 +29978,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664620399475</v>
       </c>
       <c r="H1021" t="n">
         <v>243379</v>
@@ -30007,7 +30007,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.93856263160706</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1022" t="n">
         <v>218394</v>
@@ -30065,7 +30065,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346148490906</v>
+        <v>1.87346172332764</v>
       </c>
       <c r="H1024" t="n">
         <v>368919</v>
@@ -30094,7 +30094,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814453125</v>
+        <v>1.84814476966858</v>
       </c>
       <c r="H1025" t="n">
         <v>225576</v>
@@ -30123,7 +30123,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H1026" t="n">
         <v>271070</v>
@@ -30152,7 +30152,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.93856263160706</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1027" t="n">
         <v>619856</v>
@@ -30181,7 +30181,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728034973145</v>
+        <v>2.00728011131287</v>
       </c>
       <c r="H1028" t="n">
         <v>978677</v>
@@ -30210,7 +30210,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.98557984828949</v>
+        <v>1.98557996749878</v>
       </c>
       <c r="H1029" t="n">
         <v>431020</v>
@@ -30297,7 +30297,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.98557984828949</v>
+        <v>1.98557996749878</v>
       </c>
       <c r="H1032" t="n">
         <v>263186</v>
@@ -30326,7 +30326,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984491348267</v>
       </c>
       <c r="H1033" t="n">
         <v>665587</v>
@@ -30355,7 +30355,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431179523468</v>
       </c>
       <c r="H1034" t="n">
         <v>562475</v>
@@ -30413,7 +30413,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474388599396</v>
       </c>
       <c r="H1036" t="n">
         <v>595397</v>
@@ -30442,7 +30442,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517609596252</v>
       </c>
       <c r="H1037" t="n">
         <v>749348</v>
@@ -30529,7 +30529,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77581012248993</v>
+        <v>1.77581024169922</v>
       </c>
       <c r="H1040" t="n">
         <v>435901</v>
@@ -30558,7 +30558,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.79027688503265</v>
+        <v>1.79027700424194</v>
       </c>
       <c r="H1041" t="n">
         <v>444570</v>
@@ -30616,7 +30616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.76496005058289</v>
+        <v>1.7649599313736</v>
       </c>
       <c r="H1043" t="n">
         <v>116889</v>
@@ -30674,7 +30674,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.81559407711029</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1045" t="n">
         <v>215954</v>
@@ -30703,7 +30703,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899484157562</v>
+        <v>1.85899448394775</v>
       </c>
       <c r="H1046" t="n">
         <v>633060</v>
@@ -30790,7 +30790,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644438743591</v>
+        <v>1.82644426822662</v>
       </c>
       <c r="H1049" t="n">
         <v>268233</v>
@@ -30819,7 +30819,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176122188568</v>
+        <v>1.85176134109497</v>
       </c>
       <c r="H1050" t="n">
         <v>328554</v>
@@ -30848,7 +30848,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.81559407711029</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1051" t="n">
         <v>301333</v>
@@ -30906,7 +30906,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H1053" t="n">
         <v>578759</v>
@@ -30935,7 +30935,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645813941956</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H1054" t="n">
         <v>345112</v>
@@ -30964,7 +30964,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645813941956</v>
+        <v>1.65645825862885</v>
       </c>
       <c r="H1055" t="n">
         <v>555769</v>
@@ -31022,7 +31022,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965696811676</v>
+        <v>1.56965708732605</v>
       </c>
       <c r="H1057" t="n">
         <v>544343</v>
@@ -31051,7 +31051,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.5117894411087</v>
+        <v>1.51178932189941</v>
       </c>
       <c r="H1058" t="n">
         <v>534309</v>
@@ -31080,7 +31080,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285579681396</v>
+        <v>1.48285567760468</v>
       </c>
       <c r="H1059" t="n">
         <v>394349</v>
@@ -31109,7 +31109,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366813659668</v>
+        <v>1.43366837501526</v>
       </c>
       <c r="H1060" t="n">
         <v>342436</v>
@@ -31167,7 +31167,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.35120701789856</v>
+        <v>1.35120713710785</v>
       </c>
       <c r="H1062" t="n">
         <v>475900</v>
@@ -31312,7 +31312,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.07922947406769</v>
+        <v>1.07922959327698</v>
       </c>
       <c r="H1067" t="n">
         <v>643441</v>
@@ -31399,7 +31399,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.00834178924561</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1070" t="n">
         <v>205387</v>
@@ -31573,7 +31573,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.25861895084381</v>
+        <v>1.2586190700531</v>
       </c>
       <c r="H1076" t="n">
         <v>129270</v>
@@ -31631,7 +31631,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.1776043176651</v>
+        <v>1.17760443687439</v>
       </c>
       <c r="H1078" t="n">
         <v>204338</v>
@@ -31718,7 +31718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968530654907</v>
+        <v>1.22968518733978</v>
       </c>
       <c r="H1081" t="n">
         <v>100009</v>
@@ -31747,7 +31747,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1082" t="n">
         <v>144468</v>
@@ -32008,7 +32008,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.20653820037842</v>
+        <v>1.20653831958771</v>
       </c>
       <c r="H1091" t="n">
         <v>97285</v>
@@ -32037,7 +32037,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.24270534515381</v>
+        <v>1.2427054643631</v>
       </c>
       <c r="H1092" t="n">
         <v>149538</v>
@@ -32095,7 +32095,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100496292114</v>
+        <v>1.22100508213043</v>
       </c>
       <c r="H1094" t="n">
         <v>124832</v>
@@ -32153,7 +32153,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.20075130462646</v>
+        <v>1.20075154304504</v>
       </c>
       <c r="H1096" t="n">
         <v>153500</v>
@@ -32298,7 +32298,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.1428838968277</v>
+        <v>1.14288401603699</v>
       </c>
       <c r="H1101" t="n">
         <v>111460</v>
@@ -32443,7 +32443,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1106" t="n">
         <v>214071</v>
@@ -32472,7 +32472,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318927764893</v>
+        <v>1.05318915843964</v>
       </c>
       <c r="H1107" t="n">
         <v>149211</v>
@@ -32530,7 +32530,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.02570223808289</v>
+        <v>1.0257021188736</v>
       </c>
       <c r="H1109" t="n">
         <v>171022</v>
@@ -32704,7 +32704,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04306244850159</v>
+        <v>1.0430623292923</v>
       </c>
       <c r="H1115" t="n">
         <v>194795</v>
@@ -32733,7 +32733,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.02859544754028</v>
+        <v>1.02859556674957</v>
       </c>
       <c r="H1116" t="n">
         <v>310163</v>
@@ -32791,7 +32791,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.06910288333893</v>
+        <v>1.06910264492035</v>
       </c>
       <c r="H1118" t="n">
         <v>324190</v>
@@ -32820,7 +32820,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.0589759349823</v>
+        <v>1.05897605419159</v>
       </c>
       <c r="H1119" t="n">
         <v>276892</v>
@@ -32849,7 +32849,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1120" t="n">
         <v>352921</v>
@@ -32907,7 +32907,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011727809906</v>
+        <v>1.15011751651764</v>
       </c>
       <c r="H1122" t="n">
         <v>444295</v>
@@ -32994,7 +32994,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1125" t="n">
         <v>636837</v>
@@ -33052,7 +33052,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.18917787075043</v>
+        <v>1.18917798995972</v>
       </c>
       <c r="H1127" t="n">
         <v>341827</v>
@@ -33110,7 +33110,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212292194366</v>
+        <v>1.08212304115295</v>
       </c>
       <c r="H1129" t="n">
         <v>419381</v>
@@ -33139,7 +33139,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1130" t="n">
         <v>250136</v>
@@ -33226,7 +33226,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1133" t="n">
         <v>140955</v>
@@ -33255,7 +33255,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.12263023853302</v>
+        <v>1.12263035774231</v>
       </c>
       <c r="H1134" t="n">
         <v>364632</v>
@@ -33284,7 +33284,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382330417633</v>
+        <v>1.10382354259491</v>
       </c>
       <c r="H1135" t="n">
         <v>163559</v>
@@ -33371,7 +33371,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237669944763</v>
+        <v>1.10237658023834</v>
       </c>
       <c r="H1138" t="n">
         <v>192526</v>
@@ -33487,7 +33487,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.0589759349823</v>
+        <v>1.05897605419159</v>
       </c>
       <c r="H1142" t="n">
         <v>271139</v>
@@ -33574,7 +33574,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1145" t="n">
         <v>289061</v>
@@ -33632,7 +33632,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1147" t="n">
         <v>313392</v>
@@ -33661,7 +33661,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476283073425</v>
+        <v>1.06476271152496</v>
       </c>
       <c r="H1148" t="n">
         <v>229091</v>
@@ -33690,7 +33690,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1149" t="n">
         <v>255277</v>
@@ -33748,7 +33748,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.07054960727692</v>
+        <v>1.07054948806763</v>
       </c>
       <c r="H1151" t="n">
         <v>175817</v>
@@ -33777,7 +33777,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935630321503</v>
       </c>
       <c r="H1152" t="n">
         <v>149121</v>
@@ -33806,7 +33806,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1153" t="n">
         <v>146621</v>
@@ -33835,7 +33835,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1154" t="n">
         <v>63350</v>
@@ -33864,7 +33864,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1155" t="n">
         <v>121530</v>
@@ -33893,7 +33893,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1156" t="n">
         <v>244507</v>
@@ -33980,7 +33980,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595577716827</v>
+        <v>1.04595589637756</v>
       </c>
       <c r="H1159" t="n">
         <v>160290</v>
@@ -34009,7 +34009,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846873760223</v>
+        <v>1.01846861839294</v>
       </c>
       <c r="H1160" t="n">
         <v>289771</v>
@@ -34038,7 +34038,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1161" t="n">
         <v>162875</v>
@@ -34067,7 +34067,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981578826904</v>
+        <v>0.990981698036194</v>
       </c>
       <c r="H1162" t="n">
         <v>183349</v>
@@ -34096,7 +34096,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.00689506530762</v>
+        <v>1.00689518451691</v>
       </c>
       <c r="H1163" t="n">
         <v>202296</v>
@@ -34125,7 +34125,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088309764862</v>
       </c>
       <c r="H1164" t="n">
         <v>137388</v>
@@ -34241,7 +34241,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.00834178924561</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1168" t="n">
         <v>267115</v>
@@ -34270,7 +34270,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088309764862</v>
       </c>
       <c r="H1169" t="n">
         <v>318607</v>
@@ -34299,7 +34299,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321750640869</v>
+        <v>0.995321691036224</v>
       </c>
       <c r="H1170" t="n">
         <v>284109</v>
@@ -34415,7 +34415,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.00834178924561</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1174" t="n">
         <v>183078</v>
@@ -34502,7 +34502,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.976514756679535</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1177" t="n">
         <v>195958</v>
@@ -34560,7 +34560,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1179" t="n">
         <v>235988</v>
@@ -34589,7 +34589,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1180" t="n">
         <v>341818</v>
@@ -34618,7 +34618,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.966387867927551</v>
+        <v>0.966387808322906</v>
       </c>
       <c r="H1181" t="n">
         <v>515945</v>
@@ -34647,7 +34647,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.96783459186554</v>
+        <v>0.967834651470184</v>
       </c>
       <c r="H1182" t="n">
         <v>267761</v>
@@ -34676,7 +34676,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1183" t="n">
         <v>281167</v>
@@ -34705,7 +34705,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047934532166</v>
+        <v>0.962047874927521</v>
       </c>
       <c r="H1184" t="n">
         <v>241006</v>
@@ -34734,7 +34734,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.963494539260864</v>
+        <v>0.963494658470154</v>
       </c>
       <c r="H1185" t="n">
         <v>283085</v>
@@ -34792,7 +34792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880610942841</v>
+        <v>0.925880670547485</v>
       </c>
       <c r="H1187" t="n">
         <v>573190</v>
@@ -34821,7 +34821,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1188" t="n">
         <v>555967</v>
@@ -34850,7 +34850,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687604904175</v>
+        <v>0.944687724113464</v>
       </c>
       <c r="H1189" t="n">
         <v>485261</v>
@@ -34879,7 +34879,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687604904175</v>
+        <v>0.944687724113464</v>
       </c>
       <c r="H1190" t="n">
         <v>152429</v>
@@ -34908,7 +34908,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.937454044818878</v>
+        <v>0.937454164028168</v>
       </c>
       <c r="H1191" t="n">
         <v>312695</v>
@@ -34937,7 +34937,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900768756866</v>
+        <v>0.938900828361511</v>
       </c>
       <c r="H1192" t="n">
         <v>194055</v>
@@ -35024,7 +35024,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.921540439128876</v>
+        <v>0.92154061794281</v>
       </c>
       <c r="H1195" t="n">
         <v>289851</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.898393571376801</v>
+        <v>0.898393452167511</v>
       </c>
       <c r="H1196" t="n">
         <v>406491</v>
@@ -35082,7 +35082,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1197" t="n">
         <v>192408</v>
@@ -35198,7 +35198,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1201" t="n">
         <v>504293</v>
@@ -35227,7 +35227,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.937454044818878</v>
+        <v>0.937454164028168</v>
       </c>
       <c r="H1202" t="n">
         <v>519628</v>
@@ -35256,7 +35256,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1203" t="n">
         <v>394327</v>
@@ -35285,7 +35285,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1204" t="n">
         <v>232364</v>
@@ -35314,7 +35314,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1205" t="n">
         <v>119791</v>
@@ -35372,7 +35372,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1207" t="n">
         <v>363479</v>
@@ -35488,7 +35488,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1211" t="n">
         <v>668739</v>
@@ -35517,7 +35517,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.976514756679535</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1212" t="n">
         <v>642364</v>
@@ -35604,7 +35604,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951921105384827</v>
+        <v>0.951920986175537</v>
       </c>
       <c r="H1215" t="n">
         <v>224463</v>
@@ -35633,7 +35633,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.918647170066833</v>
+        <v>0.918647110462189</v>
       </c>
       <c r="H1216" t="n">
         <v>231495</v>
@@ -35662,7 +35662,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753841400146</v>
+        <v>0.915753901004791</v>
       </c>
       <c r="H1217" t="n">
         <v>178785</v>
@@ -35691,7 +35691,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246644020081</v>
       </c>
       <c r="H1218" t="n">
         <v>276978</v>
@@ -35720,7 +35720,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1219" t="n">
         <v>154359</v>
@@ -35749,7 +35749,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1220" t="n">
         <v>238072</v>
@@ -35778,7 +35778,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013083934784</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1221" t="n">
         <v>219329</v>
@@ -35836,7 +35836,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.817378997802734</v>
+        <v>0.817379057407379</v>
       </c>
       <c r="H1223" t="n">
         <v>171062</v>
@@ -35865,7 +35865,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.824612498283386</v>
+        <v>0.824612379074097</v>
       </c>
       <c r="H1224" t="n">
         <v>195845</v>
@@ -35923,7 +35923,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.828952550888062</v>
+        <v>0.828952491283417</v>
       </c>
       <c r="H1226" t="n">
         <v>322984</v>
@@ -35952,7 +35952,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871740818024</v>
+        <v>0.776871681213379</v>
       </c>
       <c r="H1227" t="n">
         <v>366061</v>
@@ -36010,7 +36010,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024371623993</v>
+        <v>0.732024431228638</v>
       </c>
       <c r="H1229" t="n">
         <v>446350</v>
@@ -36039,7 +36039,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.77108496427536</v>
+        <v>0.771085023880005</v>
       </c>
       <c r="H1230" t="n">
         <v>254758</v>
@@ -36068,7 +36068,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.772531628608704</v>
+        <v>0.772531569004059</v>
       </c>
       <c r="H1231" t="n">
         <v>205732</v>
@@ -36213,7 +36213,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.833292603492737</v>
+        <v>0.833292484283447</v>
       </c>
       <c r="H1236" t="n">
         <v>491269</v>
@@ -36242,7 +36242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079320430756</v>
       </c>
       <c r="H1237" t="n">
         <v>399300</v>
@@ -36271,7 +36271,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.850652754306793</v>
+        <v>0.850652873516083</v>
       </c>
       <c r="H1238" t="n">
         <v>314246</v>
@@ -36300,7 +36300,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799741268158</v>
+        <v>0.873799860477448</v>
       </c>
       <c r="H1239" t="n">
         <v>463886</v>
@@ -36329,7 +36329,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1240" t="n">
         <v>465758</v>
@@ -36358,7 +36358,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1241" t="n">
         <v>475088</v>
@@ -36387,7 +36387,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1242" t="n">
         <v>529118</v>
@@ -36445,7 +36445,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1244" t="n">
         <v>350164</v>
@@ -36474,7 +36474,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1245" t="n">
         <v>371270</v>
@@ -36561,7 +36561,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967005252838</v>
+        <v>0.909967064857483</v>
       </c>
       <c r="H1248" t="n">
         <v>283507</v>
@@ -36619,7 +36619,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.863673031330109</v>
+        <v>0.863673090934753</v>
       </c>
       <c r="H1250" t="n">
         <v>2118508</v>
@@ -36677,7 +36677,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1252" t="n">
         <v>343874</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693367958069</v>
+        <v>0.876693189144135</v>
       </c>
       <c r="H1258" t="n">
         <v>265557</v>
@@ -36880,7 +36880,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013083934784</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1259" t="n">
         <v>258243</v>
@@ -36909,7 +36909,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013083934784</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1260" t="n">
         <v>250978</v>
@@ -36938,7 +36938,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119755268097</v>
+        <v>0.865119636058807</v>
       </c>
       <c r="H1261" t="n">
         <v>73429</v>
@@ -36967,7 +36967,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246644020081</v>
       </c>
       <c r="H1262" t="n">
         <v>261444</v>
@@ -36996,7 +36996,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1263" t="n">
         <v>171832</v>
@@ -37054,7 +37054,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.862226366996765</v>
+        <v>0.86222630739212</v>
       </c>
       <c r="H1265" t="n">
         <v>389130</v>
@@ -37083,7 +37083,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1266" t="n">
         <v>174813</v>
@@ -37112,7 +37112,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459748268127</v>
+        <v>0.869459688663483</v>
       </c>
       <c r="H1267" t="n">
         <v>207362</v>
@@ -37141,7 +37141,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1268" t="n">
         <v>362696</v>
@@ -37170,7 +37170,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1269" t="n">
         <v>264575</v>
@@ -37228,7 +37228,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1271" t="n">
         <v>357067</v>
@@ -37257,7 +37257,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1272" t="n">
         <v>196824</v>
@@ -37315,7 +37315,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733683586121</v>
+        <v>0.902733564376831</v>
       </c>
       <c r="H1274" t="n">
         <v>125768</v>
@@ -37402,7 +37402,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013083934784</v>
+        <v>0.868013143539429</v>
       </c>
       <c r="H1277" t="n">
         <v>273169</v>
@@ -37460,7 +37460,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1279" t="n">
         <v>178958</v>
@@ -37489,7 +37489,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206209182739</v>
+        <v>0.849206149578094</v>
       </c>
       <c r="H1280" t="n">
         <v>159959</v>
@@ -37518,7 +37518,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079320430756</v>
       </c>
       <c r="H1281" t="n">
         <v>188343</v>
@@ -37576,7 +37576,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.843419373035431</v>
+        <v>0.843419313430786</v>
       </c>
       <c r="H1283" t="n">
         <v>381437</v>
@@ -37605,7 +37605,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.852099537849426</v>
+        <v>0.852099478244781</v>
       </c>
       <c r="H1284" t="n">
         <v>176033</v>
@@ -37634,7 +37634,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.836185991764069</v>
+        <v>0.836185932159424</v>
       </c>
       <c r="H1285" t="n">
         <v>383548</v>
@@ -37692,7 +37692,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.853546261787415</v>
+        <v>0.853546142578125</v>
       </c>
       <c r="H1287" t="n">
         <v>307350</v>
@@ -37721,7 +37721,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1288" t="n">
         <v>234994</v>
@@ -37750,7 +37750,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.853546261787415</v>
+        <v>0.853546142578125</v>
       </c>
       <c r="H1289" t="n">
         <v>211199</v>
@@ -37779,7 +37779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845819950104</v>
+        <v>0.831845879554749</v>
       </c>
       <c r="H1290" t="n">
         <v>153639</v>
@@ -37808,7 +37808,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866037368774</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1291" t="n">
         <v>84133</v>
@@ -37837,7 +37837,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312701702118</v>
+        <v>0.846312761306763</v>
       </c>
       <c r="H1292" t="n">
         <v>193484</v>
@@ -37866,7 +37866,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119755268097</v>
+        <v>0.865119636058807</v>
       </c>
       <c r="H1293" t="n">
         <v>395877</v>
@@ -37895,7 +37895,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799741268158</v>
+        <v>0.873799860477448</v>
       </c>
       <c r="H1294" t="n">
         <v>252193</v>
@@ -37953,7 +37953,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.946134328842163</v>
+        <v>0.946134209632874</v>
       </c>
       <c r="H1296" t="n">
         <v>1951196</v>
@@ -38069,7 +38069,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1300" t="n">
         <v>440904</v>
@@ -38156,7 +38156,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408144950867</v>
+        <v>0.979408204555511</v>
       </c>
       <c r="H1303" t="n">
         <v>386487</v>
@@ -38272,7 +38272,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.05752921104431</v>
+        <v>1.0575293302536</v>
       </c>
       <c r="H1307" t="n">
         <v>670651</v>
@@ -38301,7 +38301,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778298854828</v>
+        <v>1.07778310775757</v>
       </c>
       <c r="H1308" t="n">
         <v>656005</v>
@@ -38359,7 +38359,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1310" t="n">
         <v>750423</v>
@@ -38388,7 +38388,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.02280879020691</v>
+        <v>1.02280867099762</v>
       </c>
       <c r="H1311" t="n">
         <v>213190</v>
@@ -38417,7 +38417,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.02570223808289</v>
+        <v>1.0257021188736</v>
       </c>
       <c r="H1312" t="n">
         <v>192416</v>
@@ -38475,7 +38475,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768414974213</v>
+        <v>0.996768355369568</v>
       </c>
       <c r="H1314" t="n">
         <v>379948</v>
@@ -38562,7 +38562,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.02570223808289</v>
+        <v>1.0257021188736</v>
       </c>
       <c r="H1317" t="n">
         <v>330734</v>
@@ -38591,7 +38591,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884934425354</v>
+        <v>1.04884922504425</v>
       </c>
       <c r="H1318" t="n">
         <v>602483</v>
@@ -38649,7 +38649,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.03872227668762</v>
+        <v>1.03872239589691</v>
       </c>
       <c r="H1320" t="n">
         <v>177744</v>
@@ -38678,7 +38678,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.07922947406769</v>
+        <v>1.07922959327698</v>
       </c>
       <c r="H1321" t="n">
         <v>786626</v>
@@ -38707,7 +38707,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935630321503</v>
       </c>
       <c r="H1322" t="n">
         <v>506082</v>
@@ -38736,7 +38736,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.07344281673431</v>
+        <v>1.0734429359436</v>
       </c>
       <c r="H1323" t="n">
         <v>261172</v>
@@ -38823,7 +38823,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1326" t="n">
         <v>1612557</v>
@@ -38852,7 +38852,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037117481232</v>
       </c>
       <c r="H1327" t="n">
         <v>582330</v>
@@ -38881,7 +38881,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037117481232</v>
       </c>
       <c r="H1328" t="n">
         <v>411680</v>
@@ -38910,7 +38910,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.1587975025177</v>
+        <v>1.15879738330841</v>
       </c>
       <c r="H1329" t="n">
         <v>259241</v>
@@ -38939,7 +38939,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458427906036</v>
+        <v>1.16458415985107</v>
       </c>
       <c r="H1330" t="n">
         <v>469768</v>
@@ -39084,7 +39084,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.1428838968277</v>
+        <v>1.14288401603699</v>
       </c>
       <c r="H1335" t="n">
         <v>251813</v>
@@ -39142,7 +39142,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037117481232</v>
       </c>
       <c r="H1337" t="n">
         <v>823456</v>
@@ -39171,7 +39171,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.16892433166504</v>
+        <v>1.16892445087433</v>
       </c>
       <c r="H1338" t="n">
         <v>336802</v>
@@ -39229,7 +39229,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.18339121341705</v>
+        <v>1.18339109420776</v>
       </c>
       <c r="H1340" t="n">
         <v>415370</v>
@@ -39403,7 +39403,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.26440560817719</v>
+        <v>1.26440572738647</v>
       </c>
       <c r="H1346" t="n">
         <v>1836829</v>
@@ -39519,7 +39519,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.2745326757431</v>
+        <v>1.27453255653381</v>
       </c>
       <c r="H1350" t="n">
         <v>314905</v>
@@ -39548,7 +39548,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057299137115</v>
+        <v>1.30057287216187</v>
       </c>
       <c r="H1351" t="n">
         <v>318670</v>
@@ -39606,7 +39606,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.29189264774323</v>
+        <v>1.29189276695251</v>
       </c>
       <c r="H1353" t="n">
         <v>274547</v>
@@ -39635,7 +39635,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912638664246</v>
       </c>
       <c r="H1354" t="n">
         <v>744694</v>
@@ -39693,7 +39693,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912638664246</v>
       </c>
       <c r="H1356" t="n">
         <v>193651</v>
@@ -39722,7 +39722,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635976791382</v>
+        <v>1.30635964870453</v>
       </c>
       <c r="H1357" t="n">
         <v>181760</v>
@@ -39780,7 +39780,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1359" t="n">
         <v>1365631</v>
@@ -39809,7 +39809,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1360" t="n">
         <v>612054</v>
@@ -39838,7 +39838,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.4611554145813</v>
+        <v>1.46115529537201</v>
       </c>
       <c r="H1361" t="n">
         <v>730836</v>
@@ -39867,7 +39867,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030546188354</v>
+        <v>1.45030534267426</v>
       </c>
       <c r="H1362" t="n">
         <v>734134</v>
@@ -39896,7 +39896,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.47562229633331</v>
+        <v>1.47562217712402</v>
       </c>
       <c r="H1363" t="n">
         <v>690935</v>
@@ -39925,7 +39925,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.429328083992</v>
+        <v>1.42932820320129</v>
       </c>
       <c r="H1364" t="n">
         <v>2260128</v>
@@ -39954,7 +39954,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.40762782096863</v>
+        <v>1.40762794017792</v>
       </c>
       <c r="H1365" t="n">
         <v>1106457</v>
@@ -39983,7 +39983,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.39750123023987</v>
+        <v>1.39750111103058</v>
       </c>
       <c r="H1366" t="n">
         <v>375019</v>
@@ -40012,7 +40012,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.39894771575928</v>
+        <v>1.39894783496857</v>
       </c>
       <c r="H1367" t="n">
         <v>239547</v>
@@ -40128,7 +40128,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1371" t="n">
         <v>196035</v>
@@ -40157,7 +40157,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.36376440525055</v>
+        <v>1.36376452445984</v>
       </c>
       <c r="H1372" t="n">
         <v>346170</v>
@@ -40273,7 +40273,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.37706243991852</v>
+        <v>1.37706232070923</v>
       </c>
       <c r="H1376" t="n">
         <v>173905</v>
@@ -40360,7 +40360,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.43911874294281</v>
+        <v>1.4391188621521</v>
       </c>
       <c r="H1379" t="n">
         <v>239859</v>
@@ -40389,7 +40389,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.44502890110016</v>
+        <v>1.44502902030945</v>
       </c>
       <c r="H1380" t="n">
         <v>213603</v>
@@ -40418,7 +40418,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1381" t="n">
         <v>159305</v>
@@ -40447,7 +40447,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980441570282</v>
       </c>
       <c r="H1382" t="n">
         <v>287514</v>
@@ -40476,7 +40476,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537173748016</v>
+        <v>1.45537161827087</v>
       </c>
       <c r="H1383" t="n">
         <v>131183</v>
@@ -40534,7 +40534,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1385" t="n">
         <v>278517</v>
@@ -40563,7 +40563,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.42877602577209</v>
+        <v>1.42877614498138</v>
       </c>
       <c r="H1386" t="n">
         <v>161882</v>
@@ -40592,7 +40592,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.41991090774536</v>
+        <v>1.41991102695465</v>
       </c>
       <c r="H1387" t="n">
         <v>150398</v>
@@ -40621,7 +40621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.3667197227478</v>
+        <v>1.36671960353851</v>
       </c>
       <c r="H1388" t="n">
         <v>291702</v>
@@ -40766,7 +40766,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1393" t="n">
         <v>166696</v>
@@ -40882,7 +40882,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.25294947624207</v>
+        <v>1.25294935703278</v>
       </c>
       <c r="H1397" t="n">
         <v>236575</v>
@@ -40969,7 +40969,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.22635364532471</v>
+        <v>1.22635388374329</v>
       </c>
       <c r="H1400" t="n">
         <v>215998</v>
@@ -41085,7 +41085,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1404" t="n">
         <v>172154</v>
@@ -41114,7 +41114,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.21896612644196</v>
+        <v>1.21896600723267</v>
       </c>
       <c r="H1405" t="n">
         <v>286470</v>
@@ -41172,7 +41172,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.19384801387787</v>
+        <v>1.19384813308716</v>
       </c>
       <c r="H1407" t="n">
         <v>147880</v>
@@ -41201,7 +41201,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.18498289585114</v>
+        <v>1.18498277664185</v>
       </c>
       <c r="H1408" t="n">
         <v>330749</v>
@@ -41288,7 +41288,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.16725242137909</v>
+        <v>1.16725254058838</v>
       </c>
       <c r="H1411" t="n">
         <v>286124</v>
@@ -41346,7 +41346,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.16577482223511</v>
+        <v>1.1657749414444</v>
       </c>
       <c r="H1413" t="n">
         <v>116151</v>
@@ -41375,7 +41375,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.19237041473389</v>
+        <v>1.19237053394318</v>
       </c>
       <c r="H1414" t="n">
         <v>75348</v>
@@ -41404,7 +41404,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.1406569480896</v>
+        <v>1.14065682888031</v>
       </c>
       <c r="H1415" t="n">
         <v>566131</v>
@@ -41549,7 +41549,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H1420" t="n">
         <v>399404</v>
@@ -41578,7 +41578,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.27954518795013</v>
+        <v>1.27954506874084</v>
       </c>
       <c r="H1421" t="n">
         <v>855837</v>
@@ -41607,7 +41607,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.27067983150482</v>
+        <v>1.27067995071411</v>
       </c>
       <c r="H1422" t="n">
         <v>523160</v>
@@ -41694,7 +41694,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.25738215446472</v>
+        <v>1.25738203525543</v>
       </c>
       <c r="H1425" t="n">
         <v>180384</v>
@@ -41723,7 +41723,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.27806770801544</v>
+        <v>1.27806746959686</v>
       </c>
       <c r="H1426" t="n">
         <v>138463</v>
@@ -41839,7 +41839,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.24260663986206</v>
+        <v>1.24260675907135</v>
       </c>
       <c r="H1430" t="n">
         <v>100163</v>
@@ -41897,7 +41897,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.26624715328217</v>
+        <v>1.26624727249146</v>
       </c>
       <c r="H1432" t="n">
         <v>266829</v>
@@ -41984,7 +41984,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1435" t="n">
         <v>261431</v>
@@ -42013,7 +42013,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614078044891</v>
+        <v>1.30614066123962</v>
       </c>
       <c r="H1436" t="n">
         <v>371377</v>
@@ -42042,7 +42042,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.42582106590271</v>
+        <v>1.42582094669342</v>
       </c>
       <c r="H1437" t="n">
         <v>1482976</v>
@@ -42071,7 +42071,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.42582106590271</v>
+        <v>1.42582094669342</v>
       </c>
       <c r="H1438" t="n">
         <v>541084</v>
@@ -42100,7 +42100,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.41991090774536</v>
+        <v>1.41991102695465</v>
       </c>
       <c r="H1439" t="n">
         <v>194067</v>
@@ -42158,7 +42158,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.37706243991852</v>
+        <v>1.37706232070923</v>
       </c>
       <c r="H1441" t="n">
         <v>121208</v>
@@ -42187,7 +42187,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1442" t="n">
         <v>230453</v>
@@ -42216,7 +42216,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.3667197227478</v>
+        <v>1.36671960353851</v>
       </c>
       <c r="H1443" t="n">
         <v>203945</v>
@@ -42303,7 +42303,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.31500577926636</v>
+        <v>1.31500589847565</v>
       </c>
       <c r="H1446" t="n">
         <v>188716</v>
@@ -42332,7 +42332,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1447" t="n">
         <v>140764</v>
@@ -42419,7 +42419,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.35785448551178</v>
+        <v>1.35785436630249</v>
       </c>
       <c r="H1450" t="n">
         <v>148858</v>
@@ -42593,7 +42593,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.25738215446472</v>
+        <v>1.25738203525543</v>
       </c>
       <c r="H1456" t="n">
         <v>404235</v>
@@ -42622,7 +42622,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.27954518795013</v>
+        <v>1.27954506874084</v>
       </c>
       <c r="H1457" t="n">
         <v>374481</v>
@@ -42767,7 +42767,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.26624715328217</v>
+        <v>1.26624727249146</v>
       </c>
       <c r="H1462" t="n">
         <v>172321</v>
@@ -42796,7 +42796,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.27511239051819</v>
+        <v>1.27511250972748</v>
       </c>
       <c r="H1463" t="n">
         <v>188738</v>
@@ -42825,7 +42825,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.27954518795013</v>
+        <v>1.27954506874084</v>
       </c>
       <c r="H1464" t="n">
         <v>82983</v>
@@ -42941,7 +42941,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.27806770801544</v>
+        <v>1.27806746959686</v>
       </c>
       <c r="H1468" t="n">
         <v>132333</v>
@@ -43115,7 +43115,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1474" t="n">
         <v>136320</v>
@@ -43260,7 +43260,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1479" t="n">
         <v>88402</v>
@@ -43347,7 +43347,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1482" t="n">
         <v>129778</v>
@@ -43376,7 +43376,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1483" t="n">
         <v>191991</v>
@@ -43405,7 +43405,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.38297259807587</v>
+        <v>1.38297247886658</v>
       </c>
       <c r="H1484" t="n">
         <v>183001</v>
@@ -43579,7 +43579,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.43911874294281</v>
+        <v>1.4391188621521</v>
       </c>
       <c r="H1490" t="n">
         <v>184337</v>
@@ -43637,7 +43637,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.54771769046783</v>
+        <v>1.54771757125854</v>
       </c>
       <c r="H1492" t="n">
         <v>586422</v>
@@ -43869,7 +43869,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980441570282</v>
       </c>
       <c r="H1500" t="n">
         <v>271549</v>
@@ -43898,7 +43898,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.44502890110016</v>
+        <v>1.44502902030945</v>
       </c>
       <c r="H1501" t="n">
         <v>177494</v>
@@ -43927,7 +43927,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.42877602577209</v>
+        <v>1.42877614498138</v>
       </c>
       <c r="H1502" t="n">
         <v>182464</v>
@@ -43956,7 +43956,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1503" t="n">
         <v>551023</v>
@@ -43985,7 +43985,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1504" t="n">
         <v>165387</v>
@@ -44014,7 +44014,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.33716893196106</v>
+        <v>1.33716881275177</v>
       </c>
       <c r="H1505" t="n">
         <v>248601</v>
@@ -44043,7 +44043,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36376440525055</v>
+        <v>1.36376452445984</v>
       </c>
       <c r="H1506" t="n">
         <v>133446</v>
@@ -44072,7 +44072,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1507" t="n">
         <v>204317</v>
@@ -44159,7 +44159,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.34455668926239</v>
+        <v>1.3445565700531</v>
       </c>
       <c r="H1510" t="n">
         <v>116822</v>
@@ -44188,7 +44188,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1511" t="n">
         <v>138621</v>
@@ -44246,7 +44246,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.34898924827576</v>
+        <v>1.34898912906647</v>
       </c>
       <c r="H1513" t="n">
         <v>216613</v>
@@ -44275,7 +44275,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1514" t="n">
         <v>106604</v>
@@ -44333,7 +44333,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1516" t="n">
         <v>156869</v>
@@ -44362,7 +44362,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.34455668926239</v>
+        <v>1.3445565700531</v>
       </c>
       <c r="H1517" t="n">
         <v>89004</v>
@@ -44507,7 +44507,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980441570282</v>
       </c>
       <c r="H1522" t="n">
         <v>604333</v>
@@ -44594,7 +44594,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816689968109</v>
       </c>
       <c r="H1525" t="n">
         <v>301193</v>
@@ -44797,7 +44797,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.48861622810364</v>
+        <v>1.48861634731293</v>
       </c>
       <c r="H1532" t="n">
         <v>153042</v>
@@ -44826,7 +44826,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1533" t="n">
         <v>132143</v>
@@ -44855,7 +44855,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816689968109</v>
       </c>
       <c r="H1534" t="n">
         <v>108707</v>
@@ -44884,7 +44884,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.48861622810364</v>
+        <v>1.48861634731293</v>
       </c>
       <c r="H1535" t="n">
         <v>47904</v>
@@ -45058,7 +45058,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1541" t="n">
         <v>253545</v>
@@ -45377,7 +45377,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1552" t="n">
         <v>137743</v>
@@ -45464,7 +45464,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.43320882320404</v>
+        <v>1.43320870399475</v>
       </c>
       <c r="H1555" t="n">
         <v>187316</v>
@@ -45493,7 +45493,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.42138850688934</v>
+        <v>1.42138838768005</v>
       </c>
       <c r="H1556" t="n">
         <v>116333</v>
@@ -45551,7 +45551,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.42286598682404</v>
+        <v>1.42286586761475</v>
       </c>
       <c r="H1558" t="n">
         <v>168182</v>
@@ -45580,7 +45580,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.41695582866669</v>
+        <v>1.4169557094574</v>
       </c>
       <c r="H1559" t="n">
         <v>112669</v>
@@ -45609,7 +45609,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1560" t="n">
         <v>118655</v>
@@ -45667,7 +45667,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.34898924827576</v>
+        <v>1.34898912906647</v>
       </c>
       <c r="H1562" t="n">
         <v>264942</v>
@@ -45696,7 +45696,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.32978117465973</v>
+        <v>1.32978129386902</v>
       </c>
       <c r="H1563" t="n">
         <v>314147</v>
@@ -45725,7 +45725,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.33716893196106</v>
+        <v>1.33716881275177</v>
       </c>
       <c r="H1564" t="n">
         <v>219956</v>
@@ -45754,7 +45754,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.27659010887146</v>
+        <v>1.27658998966217</v>
       </c>
       <c r="H1565" t="n">
         <v>563690</v>
@@ -45841,7 +45841,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.24260663986206</v>
+        <v>1.24260675907135</v>
       </c>
       <c r="H1568" t="n">
         <v>179629</v>
@@ -45870,7 +45870,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.21601104736328</v>
+        <v>1.21601116657257</v>
       </c>
       <c r="H1569" t="n">
         <v>186496</v>
@@ -45899,7 +45899,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862340927124</v>
+        <v>1.20862329006195</v>
       </c>
       <c r="H1570" t="n">
         <v>195940</v>
@@ -46044,7 +46044,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.22635364532471</v>
+        <v>1.22635388374329</v>
       </c>
       <c r="H1575" t="n">
         <v>95606</v>
@@ -46073,7 +46073,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1576" t="n">
         <v>144426</v>
@@ -46131,7 +46131,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.26624715328217</v>
+        <v>1.26624727249146</v>
       </c>
       <c r="H1578" t="n">
         <v>184608</v>
@@ -46189,7 +46189,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.27954518795013</v>
+        <v>1.27954506874084</v>
       </c>
       <c r="H1580" t="n">
         <v>74635</v>
@@ -46218,7 +46218,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.26476967334747</v>
+        <v>1.26476979255676</v>
       </c>
       <c r="H1581" t="n">
         <v>115514</v>
@@ -46276,7 +46276,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1583" t="n">
         <v>145426</v>
@@ -46392,7 +46392,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.51447319984436</v>
+        <v>1.51447308063507</v>
       </c>
       <c r="H1587" t="n">
         <v>2303043</v>
@@ -46421,7 +46421,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.54771769046783</v>
+        <v>1.54771757125854</v>
       </c>
       <c r="H1588" t="n">
         <v>1110225</v>
@@ -46450,7 +46450,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.62528824806213</v>
+        <v>1.62528812885284</v>
       </c>
       <c r="H1589" t="n">
         <v>1203439</v>
@@ -46508,7 +46508,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.6363697052002</v>
+        <v>1.63636958599091</v>
       </c>
       <c r="H1591" t="n">
         <v>519821</v>
@@ -46537,7 +46537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1592" t="n">
         <v>488837</v>
@@ -46566,7 +46566,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.65483868122101</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1593" t="n">
         <v>358597</v>
@@ -46653,7 +46653,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.69177711009979</v>
+        <v>1.69177722930908</v>
       </c>
       <c r="H1596" t="n">
         <v>513055</v>
@@ -46682,7 +46682,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.68438971042633</v>
+        <v>1.68438947200775</v>
       </c>
       <c r="H1597" t="n">
         <v>455707</v>
@@ -46711,7 +46711,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1598" t="n">
         <v>516825</v>
@@ -46740,7 +46740,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1599" t="n">
         <v>358721</v>
@@ -46798,7 +46798,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1601" t="n">
         <v>293308</v>
@@ -46827,7 +46827,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.72132790088654</v>
+        <v>1.72132802009583</v>
       </c>
       <c r="H1602" t="n">
         <v>313832</v>
@@ -46856,7 +46856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.70655274391174</v>
+        <v>1.70655250549316</v>
       </c>
       <c r="H1603" t="n">
         <v>292128</v>
@@ -46885,7 +46885,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.70655274391174</v>
+        <v>1.70655250549316</v>
       </c>
       <c r="H1604" t="n">
         <v>457156</v>
@@ -46914,7 +46914,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.71024656295776</v>
+        <v>1.71024644374847</v>
       </c>
       <c r="H1605" t="n">
         <v>285312</v>
@@ -46943,7 +46943,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1606" t="n">
         <v>652953</v>
@@ -46972,7 +46972,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.69547128677368</v>
+        <v>1.69547116756439</v>
       </c>
       <c r="H1607" t="n">
         <v>254784</v>
@@ -47001,7 +47001,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.65114486217499</v>
+        <v>1.65114498138428</v>
       </c>
       <c r="H1608" t="n">
         <v>219912</v>
@@ -47088,7 +47088,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.66222655773163</v>
+        <v>1.66222667694092</v>
       </c>
       <c r="H1611" t="n">
         <v>68045</v>
@@ -47146,7 +47146,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.6363697052002</v>
+        <v>1.63636958599091</v>
       </c>
       <c r="H1613" t="n">
         <v>180456</v>
@@ -47175,7 +47175,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.60681903362274</v>
+        <v>1.60681879520416</v>
       </c>
       <c r="H1614" t="n">
         <v>227809</v>
@@ -47204,7 +47204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924835681915</v>
+        <v>1.52924847602844</v>
       </c>
       <c r="H1615" t="n">
         <v>245261</v>
@@ -47262,7 +47262,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.59573769569397</v>
+        <v>1.59573757648468</v>
       </c>
       <c r="H1617" t="n">
         <v>312009</v>
@@ -47291,7 +47291,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420667171478</v>
+        <v>1.61420679092407</v>
       </c>
       <c r="H1618" t="n">
         <v>173191</v>
@@ -47378,7 +47378,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.65483868122101</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1621" t="n">
         <v>179258</v>
@@ -47407,7 +47407,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.67700183391571</v>
+        <v>1.677001953125</v>
       </c>
       <c r="H1622" t="n">
         <v>296489</v>
@@ -47436,7 +47436,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1623" t="n">
         <v>712219</v>
@@ -47958,7 +47958,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1641" t="n">
         <v>199201</v>
@@ -48016,7 +48016,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1643" t="n">
         <v>247724</v>
@@ -48190,7 +48190,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1649" t="n">
         <v>141025</v>
@@ -48248,7 +48248,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1651" t="n">
         <v>56456</v>
@@ -48277,7 +48277,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609028816223</v>
+        <v>1.37609040737152</v>
       </c>
       <c r="H1652" t="n">
         <v>83408</v>
@@ -48335,7 +48335,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.37769603729248</v>
+        <v>1.37769615650177</v>
       </c>
       <c r="H1654" t="n">
         <v>136685</v>
@@ -48364,7 +48364,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1655" t="n">
         <v>31246</v>
@@ -48451,7 +48451,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1658" t="n">
         <v>87013</v>
@@ -48509,7 +48509,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1660" t="n">
         <v>103532</v>
@@ -48567,7 +48567,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.27653658390045</v>
+        <v>1.27653670310974</v>
       </c>
       <c r="H1662" t="n">
         <v>62267</v>
@@ -48683,7 +48683,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688399791718</v>
+        <v>1.48688411712646</v>
       </c>
       <c r="H1666" t="n">
         <v>370783</v>
@@ -48886,7 +48886,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1673" t="n">
         <v>316953</v>
@@ -48944,7 +48944,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082710266113</v>
+        <v>1.47082698345184</v>
       </c>
       <c r="H1675" t="n">
         <v>352968</v>
@@ -49089,7 +49089,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820443630219</v>
+        <v>1.40820455551147</v>
       </c>
       <c r="H1680" t="n">
         <v>95443</v>
@@ -49147,7 +49147,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1682" t="n">
         <v>66535</v>
@@ -49176,7 +49176,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1683" t="n">
         <v>260032</v>
@@ -49234,7 +49234,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1685" t="n">
         <v>224610</v>
@@ -49263,7 +49263,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1686" t="n">
         <v>210620</v>
@@ -49408,7 +49408,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558188915253</v>
+        <v>1.34558200836182</v>
       </c>
       <c r="H1691" t="n">
         <v>192296</v>
@@ -49524,7 +49524,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1695" t="n">
         <v>180799</v>
@@ -49582,7 +49582,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1697" t="n">
         <v>151485</v>
@@ -49872,7 +49872,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1707" t="n">
         <v>328393</v>
@@ -50075,7 +50075,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.15129148960114</v>
+        <v>1.15129160881042</v>
       </c>
       <c r="H1714" t="n">
         <v>239109</v>
@@ -50365,7 +50365,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1724" t="n">
         <v>195897</v>
@@ -50394,7 +50394,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267403125763</v>
+        <v>1.20267415046692</v>
       </c>
       <c r="H1725" t="n">
         <v>200716</v>
@@ -50481,7 +50481,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1728" t="n">
         <v>106830</v>
@@ -50510,7 +50510,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1729" t="n">
         <v>337931</v>
@@ -50539,7 +50539,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1730" t="n">
         <v>107088</v>
@@ -50597,7 +50597,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741072654724</v>
+        <v>1.29741084575653</v>
       </c>
       <c r="H1732" t="n">
         <v>220981</v>
@@ -50626,7 +50626,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1733" t="n">
         <v>162741</v>
@@ -50655,7 +50655,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1734" t="n">
         <v>122962</v>
@@ -50684,7 +50684,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.33273613452911</v>
+        <v>1.3327362537384</v>
       </c>
       <c r="H1735" t="n">
         <v>209163</v>
@@ -50829,7 +50829,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383348464966</v>
+        <v>1.30383360385895</v>
       </c>
       <c r="H1740" t="n">
         <v>63847</v>
@@ -50858,7 +50858,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1741" t="n">
         <v>362136</v>
@@ -50887,7 +50887,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1742" t="n">
         <v>126434</v>
@@ -51235,7 +51235,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1754" t="n">
         <v>268250</v>
@@ -51496,7 +51496,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1763" t="n">
         <v>180397</v>
@@ -51641,7 +51641,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1768" t="n">
         <v>44622</v>
@@ -51670,7 +51670,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1769" t="n">
         <v>310689</v>
@@ -51728,7 +51728,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1771" t="n">
         <v>224093</v>
@@ -51815,7 +51815,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1774" t="n">
         <v>131817</v>
@@ -51844,7 +51844,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1775" t="n">
         <v>99387</v>
@@ -51902,7 +51902,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1777" t="n">
         <v>83493</v>
@@ -51931,7 +51931,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1778" t="n">
         <v>95141</v>
@@ -51960,7 +51960,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.18661713600159</v>
+        <v>1.1866170167923</v>
       </c>
       <c r="H1779" t="n">
         <v>103412</v>
@@ -51989,7 +51989,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1780" t="n">
         <v>171787</v>
@@ -52163,7 +52163,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1786" t="n">
         <v>102156</v>
@@ -52279,7 +52279,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1790" t="n">
         <v>295350</v>
@@ -53236,7 +53236,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1823" t="n">
         <v>229481</v>
@@ -53381,7 +53381,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1828" t="n">
         <v>60503</v>
@@ -53497,7 +53497,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1832" t="n">
         <v>160687</v>
@@ -53526,7 +53526,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1833" t="n">
         <v>313479</v>
@@ -53584,7 +53584,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1835" t="n">
         <v>126203</v>
@@ -53613,7 +53613,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1836" t="n">
         <v>104258</v>
@@ -53642,7 +53642,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1837" t="n">
         <v>137726</v>
@@ -53671,7 +53671,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828498840332</v>
+        <v>1.31828486919403</v>
       </c>
       <c r="H1838" t="n">
         <v>268207</v>
@@ -53729,7 +53729,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1840" t="n">
         <v>380640</v>
@@ -53903,7 +53903,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206686973572</v>
+        <v>1.48206698894501</v>
       </c>
       <c r="H1846" t="n">
         <v>230147</v>
@@ -54193,7 +54193,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1856" t="n">
         <v>136076</v>
@@ -54280,7 +54280,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.4788556098938</v>
+        <v>1.47885572910309</v>
       </c>
       <c r="H1859" t="n">
         <v>185027</v>
@@ -54309,7 +54309,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.50294125080109</v>
+        <v>1.5029411315918</v>
       </c>
       <c r="H1860" t="n">
         <v>288447</v>
@@ -54831,7 +54831,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.45958697795868</v>
+        <v>1.45958709716797</v>
       </c>
       <c r="H1878" t="n">
         <v>118811</v>
@@ -54918,7 +54918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1881" t="n">
         <v>411337</v>
@@ -79980,6 +79980,35 @@
         <v>332065</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>2.02500009536743</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>171344</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -514,7 +514,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717758178711</v>
       </c>
       <c r="H5" t="n">
         <v>103885</v>
@@ -543,7 +543,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.77098608016968</v>
+        <v>2.7709858417511</v>
       </c>
       <c r="H6" t="n">
         <v>24790</v>
@@ -572,7 +572,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832279205322</v>
       </c>
       <c r="H7" t="n">
         <v>64928</v>
@@ -601,7 +601,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G8" t="n">
-        <v>2.732905626297</v>
+        <v>2.73290538787842</v>
       </c>
       <c r="H8" t="n">
         <v>58587</v>
@@ -630,7 +630,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832279205322</v>
       </c>
       <c r="H9" t="n">
         <v>36066</v>
@@ -688,7 +688,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928292274475</v>
       </c>
       <c r="H11" t="n">
         <v>96501</v>
@@ -717,7 +717,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408214569092</v>
+        <v>2.56408190727234</v>
       </c>
       <c r="H12" t="n">
         <v>52586</v>
@@ -746,7 +746,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G13" t="n">
-        <v>2.546311378479</v>
+        <v>2.54631114006042</v>
       </c>
       <c r="H13" t="n">
         <v>34257</v>
@@ -804,7 +804,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H15" t="n">
         <v>65925</v>
@@ -833,7 +833,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6643602848053</v>
+        <v>2.66436052322388</v>
       </c>
       <c r="H16" t="n">
         <v>61532</v>
@@ -891,7 +891,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138850212097</v>
+        <v>2.55138826370239</v>
       </c>
       <c r="H18" t="n">
         <v>16747</v>
@@ -949,7 +949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965498924255</v>
+        <v>2.51965475082397</v>
       </c>
       <c r="H20" t="n">
         <v>43026</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.53869485855103</v>
+        <v>2.53869533538818</v>
       </c>
       <c r="H21" t="n">
         <v>27727</v>
@@ -1036,7 +1036,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G23" t="n">
-        <v>2.53361773490906</v>
+        <v>2.53361797332764</v>
       </c>
       <c r="H23" t="n">
         <v>25182</v>
@@ -1065,7 +1065,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696158409119</v>
+        <v>2.50696134567261</v>
       </c>
       <c r="H24" t="n">
         <v>32795</v>
@@ -1123,7 +1123,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H26" t="n">
         <v>40968</v>
@@ -1152,7 +1152,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349431991577</v>
+        <v>2.44349384307861</v>
       </c>
       <c r="H27" t="n">
         <v>83462</v>
@@ -1210,7 +1210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482556343079</v>
+        <v>2.28482532501221</v>
       </c>
       <c r="H29" t="n">
         <v>103231</v>
@@ -1239,7 +1239,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.13885045051575</v>
+        <v>2.13885068893433</v>
       </c>
       <c r="H30" t="n">
         <v>81897</v>
@@ -1268,7 +1268,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135877609253</v>
+        <v>2.22135829925537</v>
       </c>
       <c r="H31" t="n">
         <v>155211</v>
@@ -1326,7 +1326,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798337936401</v>
+        <v>2.32798361778259</v>
       </c>
       <c r="H33" t="n">
         <v>39970</v>
@@ -1413,7 +1413,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5551962852478</v>
+        <v>2.55519676208496</v>
       </c>
       <c r="H36" t="n">
         <v>17078</v>
@@ -1442,7 +1442,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928316116333</v>
+        <v>2.65928292274475</v>
       </c>
       <c r="H37" t="n">
         <v>45626</v>
@@ -1500,7 +1500,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49553751945496</v>
+        <v>2.49553728103638</v>
       </c>
       <c r="H39" t="n">
         <v>77760</v>
@@ -1529,7 +1529,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600145339966</v>
+        <v>2.52600193023682</v>
       </c>
       <c r="H40" t="n">
         <v>22658</v>
@@ -1616,7 +1616,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>2.6783230304718</v>
+        <v>2.67832279205322</v>
       </c>
       <c r="H43" t="n">
         <v>55902</v>
@@ -1645,7 +1645,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66055274009705</v>
+        <v>2.66055226325989</v>
       </c>
       <c r="H44" t="n">
         <v>83690</v>
@@ -1703,7 +1703,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658999443054</v>
+        <v>2.64658975601196</v>
       </c>
       <c r="H46" t="n">
         <v>17636</v>
@@ -1877,7 +1877,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G52" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717758178711</v>
       </c>
       <c r="H52" t="n">
         <v>124017</v>
@@ -1964,7 +1964,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172839164734</v>
+        <v>2.90172863006592</v>
       </c>
       <c r="H55" t="n">
         <v>82307</v>
@@ -1993,7 +1993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853998184204</v>
+        <v>2.93853974342346</v>
       </c>
       <c r="H56" t="n">
         <v>170803</v>
@@ -2022,7 +2022,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95757985115051</v>
+        <v>2.95757937431335</v>
       </c>
       <c r="H57" t="n">
         <v>81691</v>
@@ -2051,7 +2051,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169755935669</v>
+        <v>2.98169732093811</v>
       </c>
       <c r="H58" t="n">
         <v>45732</v>
@@ -2080,7 +2080,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504093170166</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H59" t="n">
         <v>62635</v>
@@ -2138,7 +2138,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835371017456</v>
+        <v>3.00835347175598</v>
       </c>
       <c r="H61" t="n">
         <v>91726</v>
@@ -2196,7 +2196,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423624038696</v>
+        <v>2.98423600196838</v>
       </c>
       <c r="H63" t="n">
         <v>32830</v>
@@ -2225,7 +2225,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566030502319</v>
+        <v>2.99566006660461</v>
       </c>
       <c r="H64" t="n">
         <v>46851</v>
@@ -2254,7 +2254,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327634811401</v>
       </c>
       <c r="H65" t="n">
         <v>28745</v>
@@ -2283,7 +2283,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200748443604</v>
+        <v>3.00200700759888</v>
       </c>
       <c r="H66" t="n">
         <v>39511</v>
@@ -2312,7 +2312,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.91949939727783</v>
+        <v>2.91949915885925</v>
       </c>
       <c r="H67" t="n">
         <v>33763</v>
@@ -2341,7 +2341,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711520195007</v>
+        <v>2.92711591720581</v>
       </c>
       <c r="H68" t="n">
         <v>58634</v>
@@ -2370,7 +2370,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819874763489</v>
+        <v>2.99819922447205</v>
       </c>
       <c r="H69" t="n">
         <v>75222</v>
@@ -2428,7 +2428,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>2.98931336402893</v>
+        <v>2.98931360244751</v>
       </c>
       <c r="H71" t="n">
         <v>92895</v>
@@ -2457,7 +2457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182121276855</v>
+        <v>3.07182145118713</v>
       </c>
       <c r="H72" t="n">
         <v>136484</v>
@@ -2486,7 +2486,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H73" t="n">
         <v>94926</v>
@@ -2515,7 +2515,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>3.10990190505981</v>
+        <v>3.10990142822266</v>
       </c>
       <c r="H74" t="n">
         <v>109632</v>
@@ -2573,7 +2573,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702222824097</v>
       </c>
       <c r="H76" t="n">
         <v>114194</v>
@@ -2602,7 +2602,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702222824097</v>
       </c>
       <c r="H77" t="n">
         <v>122410</v>
@@ -2631,7 +2631,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.10990190505981</v>
+        <v>3.10990142822266</v>
       </c>
       <c r="H78" t="n">
         <v>61569</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.10990190505981</v>
+        <v>3.10990142822266</v>
       </c>
       <c r="H79" t="n">
         <v>45242</v>
@@ -2689,7 +2689,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798164367676</v>
+        <v>3.14798212051392</v>
       </c>
       <c r="H80" t="n">
         <v>29895</v>
@@ -2718,7 +2718,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.09847736358643</v>
+        <v>3.09847712516785</v>
       </c>
       <c r="H81" t="n">
         <v>94591</v>
@@ -2776,7 +2776,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086108207703</v>
+        <v>3.09086155891418</v>
       </c>
       <c r="H83" t="n">
         <v>44802</v>
@@ -2805,7 +2805,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959197998047</v>
+        <v>3.08959221839905</v>
       </c>
       <c r="H84" t="n">
         <v>34327</v>
@@ -2834,7 +2834,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547427177429</v>
+        <v>3.06547403335571</v>
       </c>
       <c r="H85" t="n">
         <v>37849</v>
@@ -2863,7 +2863,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374099731445</v>
+        <v>3.03374075889587</v>
       </c>
       <c r="H86" t="n">
         <v>46370</v>
@@ -2892,7 +2892,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327610969543</v>
+        <v>3.00327634811401</v>
       </c>
       <c r="H87" t="n">
         <v>120760</v>
@@ -2950,7 +2950,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.04643416404724</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H89" t="n">
         <v>55991</v>
@@ -2979,7 +2979,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053998947144</v>
+        <v>3.03053951263428</v>
       </c>
       <c r="H90" t="n">
         <v>50752</v>
@@ -3008,7 +3008,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H91" t="n">
         <v>62212</v>
@@ -3095,7 +3095,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974303245544</v>
+        <v>2.94974327087402</v>
       </c>
       <c r="H94" t="n">
         <v>22389</v>
@@ -3124,7 +3124,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424445152283</v>
+        <v>2.87424492835999</v>
       </c>
       <c r="H95" t="n">
         <v>67830</v>
@@ -3211,7 +3211,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G98" t="n">
-        <v>3.08881950378418</v>
+        <v>3.0888192653656</v>
       </c>
       <c r="H98" t="n">
         <v>155937</v>
@@ -3269,7 +3269,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941530227661</v>
+        <v>3.09941601753235</v>
       </c>
       <c r="H100" t="n">
         <v>95435</v>
@@ -3298,7 +3298,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G101" t="n">
-        <v>3.07822299003601</v>
+        <v>3.07822275161743</v>
       </c>
       <c r="H101" t="n">
         <v>47757</v>
@@ -3327,7 +3327,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577436447144</v>
+        <v>3.14577460289001</v>
       </c>
       <c r="H102" t="n">
         <v>86451</v>
@@ -3356,7 +3356,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140528678894</v>
+        <v>3.20140552520752</v>
       </c>
       <c r="H103" t="n">
         <v>92445</v>
@@ -3385,7 +3385,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.17888784408569</v>
+        <v>3.17888808250427</v>
       </c>
       <c r="H104" t="n">
         <v>49257</v>
@@ -3414,7 +3414,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>3.19213342666626</v>
+        <v>3.19213318824768</v>
       </c>
       <c r="H105" t="n">
         <v>39452</v>
@@ -3472,7 +3472,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.23186945915222</v>
+        <v>3.23186922073364</v>
       </c>
       <c r="H107" t="n">
         <v>38634</v>
@@ -3501,7 +3501,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610714912415</v>
+        <v>3.19610738754272</v>
       </c>
       <c r="H108" t="n">
         <v>19558</v>
@@ -3530,7 +3530,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802760124207</v>
+        <v>3.20802783966064</v>
       </c>
       <c r="H109" t="n">
         <v>23367</v>
@@ -3588,7 +3588,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.15901970863342</v>
+        <v>3.15901947021484</v>
       </c>
       <c r="H111" t="n">
         <v>31915</v>
@@ -3617,7 +3617,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133670806885</v>
+        <v>3.11133646965027</v>
       </c>
       <c r="H112" t="n">
         <v>10926</v>
@@ -3646,7 +3646,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G113" t="n">
-        <v>3.08881950378418</v>
+        <v>3.0888192653656</v>
       </c>
       <c r="H113" t="n">
         <v>13735</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H114" t="n">
         <v>34326</v>
@@ -3733,7 +3733,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516798019409</v>
+        <v>2.73516845703125</v>
       </c>
       <c r="H116" t="n">
         <v>77740</v>
@@ -3791,7 +3791,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69278311729431</v>
+        <v>2.69278264045715</v>
       </c>
       <c r="H118" t="n">
         <v>84374</v>
@@ -3849,7 +3849,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.86762166023254</v>
+        <v>2.86762142181396</v>
       </c>
       <c r="H120" t="n">
         <v>86220</v>
@@ -3878,7 +3878,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91133165359497</v>
+        <v>2.91133117675781</v>
       </c>
       <c r="H121" t="n">
         <v>23520</v>
@@ -3936,7 +3936,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060303688049</v>
+        <v>2.92060279846191</v>
       </c>
       <c r="H123" t="n">
         <v>44363</v>
@@ -3965,7 +3965,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596517562866</v>
+        <v>2.81596493721008</v>
       </c>
       <c r="H124" t="n">
         <v>67252</v>
@@ -3994,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H125" t="n">
         <v>48500</v>
@@ -4052,7 +4052,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907865524292</v>
       </c>
       <c r="H127" t="n">
         <v>171545</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H128" t="n">
         <v>87090</v>
@@ -4110,7 +4110,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H129" t="n">
         <v>113855</v>
@@ -4139,7 +4139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047093391418</v>
+        <v>2.94047141075134</v>
       </c>
       <c r="H130" t="n">
         <v>49672</v>
@@ -4168,7 +4168,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G131" t="n">
-        <v>2.75636100769043</v>
+        <v>2.75636076927185</v>
       </c>
       <c r="H131" t="n">
         <v>51557</v>
@@ -4197,7 +4197,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708867073059</v>
+        <v>2.74708890914917</v>
       </c>
       <c r="H132" t="n">
         <v>64127</v>
@@ -4226,7 +4226,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152680397034</v>
+        <v>2.78152656555176</v>
       </c>
       <c r="H133" t="n">
         <v>40862</v>
@@ -4284,7 +4284,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709396362305</v>
+        <v>2.94709372520447</v>
       </c>
       <c r="H135" t="n">
         <v>222212</v>
@@ -4313,7 +4313,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802206993103</v>
+        <v>3.00802278518677</v>
       </c>
       <c r="H136" t="n">
         <v>190152</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H137" t="n">
         <v>193814</v>
@@ -4371,7 +4371,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>2.95371651649475</v>
+        <v>2.95371699333191</v>
       </c>
       <c r="H138" t="n">
         <v>257080</v>
@@ -4487,7 +4487,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397566795349</v>
+        <v>2.71397542953491</v>
       </c>
       <c r="H142" t="n">
         <v>293231</v>
@@ -4516,7 +4516,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364336013794</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H143" t="n">
         <v>206630</v>
@@ -4545,7 +4545,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="n">
-        <v>2.69940567016602</v>
+        <v>2.69940590858459</v>
       </c>
       <c r="H144" t="n">
         <v>154876</v>
@@ -4574,7 +4574,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H145" t="n">
         <v>151529</v>
@@ -4719,7 +4719,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60138964653015</v>
+        <v>2.60139012336731</v>
       </c>
       <c r="H150" t="n">
         <v>119099</v>
@@ -4777,7 +4777,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152222633362</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H152" t="n">
         <v>427637</v>
@@ -4835,7 +4835,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159008979797</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H154" t="n">
         <v>972279</v>
@@ -4864,7 +4864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245057106018</v>
+        <v>2.64245080947876</v>
       </c>
       <c r="H155" t="n">
         <v>131874</v>
@@ -4922,7 +4922,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.72192287445068</v>
+        <v>2.72192239761353</v>
       </c>
       <c r="H157" t="n">
         <v>1740457</v>
@@ -5009,7 +5009,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364336013794</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H160" t="n">
         <v>69314</v>
@@ -5038,7 +5038,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="n">
-        <v>2.66496753692627</v>
+        <v>2.66496801376343</v>
       </c>
       <c r="H161" t="n">
         <v>161383</v>
@@ -5067,7 +5067,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702056884766</v>
+        <v>2.65702080726624</v>
       </c>
       <c r="H162" t="n">
         <v>133837</v>
@@ -5096,7 +5096,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H163" t="n">
         <v>149720</v>
@@ -5154,7 +5154,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159008979797</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H165" t="n">
         <v>235127</v>
@@ -5183,7 +5183,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.66231846809387</v>
+        <v>2.66231870651245</v>
       </c>
       <c r="H166" t="n">
         <v>89589</v>
@@ -5212,7 +5212,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H167" t="n">
         <v>122138</v>
@@ -5241,7 +5241,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H168" t="n">
         <v>78296</v>
@@ -5270,7 +5270,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="n">
-        <v>2.61860871315002</v>
+        <v>2.6186089515686</v>
       </c>
       <c r="H169" t="n">
         <v>113605</v>
@@ -5328,7 +5328,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907288551331</v>
+        <v>2.64907312393188</v>
       </c>
       <c r="H171" t="n">
         <v>338607</v>
@@ -5444,7 +5444,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>2.56430292129517</v>
+        <v>2.56430268287659</v>
       </c>
       <c r="H175" t="n">
         <v>202259</v>
@@ -5560,7 +5560,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675178527832</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H179" t="n">
         <v>130197</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979644775391</v>
+        <v>2.43979620933533</v>
       </c>
       <c r="H180" t="n">
         <v>95436</v>
@@ -5647,7 +5647,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G182" t="n">
-        <v>2.3682713508606</v>
+        <v>2.36827158927917</v>
       </c>
       <c r="H182" t="n">
         <v>465300</v>
@@ -5676,7 +5676,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40270924568176</v>
+        <v>2.40270948410034</v>
       </c>
       <c r="H183" t="n">
         <v>219710</v>
@@ -5705,7 +5705,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="n">
-        <v>2.46893620491028</v>
+        <v>2.46893644332886</v>
       </c>
       <c r="H184" t="n">
         <v>131854</v>
@@ -5763,7 +5763,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H186" t="n">
         <v>71603</v>
@@ -5792,7 +5792,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992807388306</v>
+        <v>2.41992855072021</v>
       </c>
       <c r="H187" t="n">
         <v>58946</v>
@@ -5821,7 +5821,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H188" t="n">
         <v>97323</v>
@@ -5850,7 +5850,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="n">
-        <v>2.27820348739624</v>
+        <v>2.27820324897766</v>
       </c>
       <c r="H189" t="n">
         <v>134521</v>
@@ -5908,7 +5908,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H191" t="n">
         <v>98350</v>
@@ -5937,7 +5937,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>2.2715802192688</v>
+        <v>2.27158045768738</v>
       </c>
       <c r="H192" t="n">
         <v>124936</v>
@@ -5966,7 +5966,7 @@
         <v>3.39199995994568</v>
       </c>
       <c r="G193" t="n">
-        <v>2.24641394615173</v>
+        <v>2.24641418457031</v>
       </c>
       <c r="H193" t="n">
         <v>167793</v>
@@ -5995,7 +5995,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.2861499786377</v>
+        <v>2.28615021705627</v>
       </c>
       <c r="H194" t="n">
         <v>121567</v>
@@ -6024,7 +6024,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H195" t="n">
         <v>439465</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078855514526</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H199" t="n">
         <v>102816</v>
@@ -6256,7 +6256,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211320877075</v>
+        <v>2.39211297035217</v>
       </c>
       <c r="H203" t="n">
         <v>79415</v>
@@ -6372,7 +6372,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.45436668395996</v>
+        <v>2.45436644554138</v>
       </c>
       <c r="H207" t="n">
         <v>152563</v>
@@ -6401,7 +6401,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="n">
-        <v>2.45304155349731</v>
+        <v>2.45304203033447</v>
       </c>
       <c r="H208" t="n">
         <v>115572</v>
@@ -6488,7 +6488,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H211" t="n">
         <v>66822</v>
@@ -6546,7 +6546,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503153800964</v>
+        <v>2.55503106117249</v>
       </c>
       <c r="H213" t="n">
         <v>339678</v>
@@ -6604,7 +6604,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152222633362</v>
+        <v>2.58152174949646</v>
       </c>
       <c r="H215" t="n">
         <v>116199</v>
@@ -6633,7 +6633,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>2.5444347858429</v>
+        <v>2.54443502426147</v>
       </c>
       <c r="H216" t="n">
         <v>93617</v>
@@ -6662,7 +6662,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G217" t="n">
-        <v>2.48483085632324</v>
+        <v>2.48483061790466</v>
       </c>
       <c r="H217" t="n">
         <v>121095</v>
@@ -6691,7 +6691,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264572143555</v>
       </c>
       <c r="H218" t="n">
         <v>53331</v>
@@ -6749,7 +6749,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>2.51661944389343</v>
+        <v>2.51661968231201</v>
       </c>
       <c r="H220" t="n">
         <v>40199</v>
@@ -6778,7 +6778,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496248245239</v>
+        <v>2.46496272087097</v>
       </c>
       <c r="H221" t="n">
         <v>80797</v>
@@ -6807,7 +6807,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48085713386536</v>
+        <v>2.48085689544678</v>
       </c>
       <c r="H222" t="n">
         <v>144428</v>
@@ -6865,7 +6865,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G224" t="n">
-        <v>2.47026062011719</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H224" t="n">
         <v>24480</v>
@@ -6952,7 +6952,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.33780694007874</v>
+        <v>2.33780717849731</v>
       </c>
       <c r="H227" t="n">
         <v>189301</v>
@@ -6981,7 +6981,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.33780694007874</v>
+        <v>2.33780717849731</v>
       </c>
       <c r="H228" t="n">
         <v>112606</v>
@@ -7010,7 +7010,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.2450897693634</v>
+        <v>2.24509000778198</v>
       </c>
       <c r="H229" t="n">
         <v>112233</v>
@@ -7039,7 +7039,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.2450897693634</v>
+        <v>2.24509000778198</v>
       </c>
       <c r="H230" t="n">
         <v>154519</v>
@@ -7068,7 +7068,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H231" t="n">
         <v>105323</v>
@@ -7184,7 +7184,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="n">
-        <v>2.22389721870422</v>
+        <v>2.22389698028564</v>
       </c>
       <c r="H235" t="n">
         <v>107495</v>
@@ -7213,7 +7213,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25303673744202</v>
+        <v>2.2530369758606</v>
       </c>
       <c r="H236" t="n">
         <v>166280</v>
@@ -7242,7 +7242,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482580184937</v>
+        <v>2.28482556343079</v>
       </c>
       <c r="H237" t="n">
         <v>48104</v>
@@ -7387,7 +7387,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608669281006</v>
+        <v>2.39608693122864</v>
       </c>
       <c r="H242" t="n">
         <v>275325</v>
@@ -7416,7 +7416,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G243" t="n">
-        <v>2.40668320655823</v>
+        <v>2.40668296813965</v>
       </c>
       <c r="H243" t="n">
         <v>104163</v>
@@ -7561,7 +7561,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46893620491028</v>
+        <v>2.46893644332886</v>
       </c>
       <c r="H248" t="n">
         <v>101059</v>
@@ -7590,7 +7590,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.4503927230835</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H249" t="n">
         <v>141900</v>
@@ -7619,7 +7619,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.47026062011719</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H250" t="n">
         <v>259270</v>
@@ -7677,7 +7677,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="n">
-        <v>2.49145340919495</v>
+        <v>2.49145364761353</v>
       </c>
       <c r="H252" t="n">
         <v>110793</v>
@@ -7706,7 +7706,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.47026062011719</v>
+        <v>2.47026085853577</v>
       </c>
       <c r="H253" t="n">
         <v>44412</v>
@@ -7764,7 +7764,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734758377075</v>
       </c>
       <c r="H255" t="n">
         <v>71140</v>
@@ -7793,7 +7793,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675178527832</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H256" t="n">
         <v>116308</v>
@@ -7851,7 +7851,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="n">
-        <v>2.54708409309387</v>
+        <v>2.54708385467529</v>
       </c>
       <c r="H258" t="n">
         <v>159203</v>
@@ -7880,7 +7880,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.54973316192627</v>
+        <v>2.54973292350769</v>
       </c>
       <c r="H259" t="n">
         <v>160972</v>
@@ -7909,7 +7909,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734806060791</v>
+        <v>2.50734758377075</v>
       </c>
       <c r="H260" t="n">
         <v>231873</v>
@@ -7938,7 +7938,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.53251385688782</v>
+        <v>2.5325140953064</v>
       </c>
       <c r="H261" t="n">
         <v>223968</v>
@@ -7967,7 +7967,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G262" t="n">
-        <v>2.53118968009949</v>
+        <v>2.53118944168091</v>
       </c>
       <c r="H262" t="n">
         <v>57795</v>
@@ -7996,7 +7996,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264572143555</v>
       </c>
       <c r="H263" t="n">
         <v>153807</v>
@@ -8025,7 +8025,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G264" t="n">
-        <v>2.48483085632324</v>
+        <v>2.48483061790466</v>
       </c>
       <c r="H264" t="n">
         <v>174948</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675178527832</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H265" t="n">
         <v>182001</v>
@@ -8170,7 +8170,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960105895996</v>
+        <v>2.56960129737854</v>
       </c>
       <c r="H269" t="n">
         <v>280634</v>
@@ -8228,7 +8228,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165385246277</v>
+        <v>2.56165361404419</v>
       </c>
       <c r="H271" t="n">
         <v>288062</v>
@@ -8286,7 +8286,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059316635132</v>
+        <v>2.52059292793274</v>
       </c>
       <c r="H273" t="n">
         <v>263075</v>
@@ -8315,7 +8315,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072526931763</v>
+        <v>2.50072503089905</v>
       </c>
       <c r="H274" t="n">
         <v>488841</v>
@@ -8489,7 +8489,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356948852539</v>
+        <v>2.37356996536255</v>
       </c>
       <c r="H280" t="n">
         <v>114037</v>
@@ -8518,7 +8518,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G281" t="n">
-        <v>2.34310531616211</v>
+        <v>2.34310555458069</v>
       </c>
       <c r="H281" t="n">
         <v>266394</v>
@@ -8576,7 +8576,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019227981567</v>
+        <v>2.38019251823425</v>
       </c>
       <c r="H283" t="n">
         <v>99628</v>
@@ -8605,7 +8605,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G284" t="n">
-        <v>2.3656222820282</v>
+        <v>2.36562252044678</v>
       </c>
       <c r="H284" t="n">
         <v>69136</v>
@@ -8692,7 +8692,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>2.32191252708435</v>
+        <v>2.32191276550293</v>
       </c>
       <c r="H287" t="n">
         <v>77908</v>
@@ -8721,7 +8721,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985973358154</v>
+        <v>2.32985997200012</v>
       </c>
       <c r="H288" t="n">
         <v>130996</v>
@@ -8808,7 +8808,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.41727924346924</v>
+        <v>2.4172797203064</v>
       </c>
       <c r="H291" t="n">
         <v>96839</v>
@@ -8866,7 +8866,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006065368652</v>
+        <v>2.4000608921051</v>
       </c>
       <c r="H293" t="n">
         <v>70534</v>
@@ -8895,7 +8895,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886786460876</v>
+        <v>2.37886762619019</v>
       </c>
       <c r="H294" t="n">
         <v>84182</v>
@@ -8924,7 +8924,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.40403437614441</v>
+        <v>2.40403413772583</v>
       </c>
       <c r="H295" t="n">
         <v>126484</v>
@@ -8953,7 +8953,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35767531394958</v>
+        <v>2.35767483711243</v>
       </c>
       <c r="H296" t="n">
         <v>190410</v>
@@ -8982,7 +8982,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999159812927</v>
+        <v>2.30999183654785</v>
       </c>
       <c r="H297" t="n">
         <v>327861</v>
@@ -9098,7 +9098,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807596206665</v>
+        <v>2.49807620048523</v>
       </c>
       <c r="H301" t="n">
         <v>292122</v>
@@ -9185,7 +9185,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49145340919495</v>
+        <v>2.49145364761353</v>
       </c>
       <c r="H304" t="n">
         <v>215004</v>
@@ -9214,7 +9214,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.54973316192627</v>
+        <v>2.54973292350769</v>
       </c>
       <c r="H305" t="n">
         <v>523792</v>
@@ -9272,7 +9272,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622361183167</v>
+        <v>2.57622385025024</v>
       </c>
       <c r="H307" t="n">
         <v>428054</v>
@@ -9330,7 +9330,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211826324463</v>
+        <v>2.59211850166321</v>
       </c>
       <c r="H309" t="n">
         <v>248866</v>
@@ -9388,7 +9388,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63185453414917</v>
+        <v>2.63185429573059</v>
       </c>
       <c r="H311" t="n">
         <v>305933</v>
@@ -9417,7 +9417,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.70073008537292</v>
+        <v>2.7007303237915</v>
       </c>
       <c r="H312" t="n">
         <v>590494</v>
@@ -9475,7 +9475,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.82126307487488</v>
+        <v>2.82126355171204</v>
       </c>
       <c r="H314" t="n">
         <v>1620852</v>
@@ -9504,7 +9504,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642910957336</v>
+        <v>2.84642887115479</v>
       </c>
       <c r="H315" t="n">
         <v>839292</v>
@@ -9533,7 +9533,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252420425415</v>
+        <v>2.93252372741699</v>
       </c>
       <c r="H316" t="n">
         <v>857622</v>
@@ -9591,7 +9591,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02789068222046</v>
+        <v>3.02789092063904</v>
       </c>
       <c r="H318" t="n">
         <v>1098038</v>
@@ -9620,7 +9620,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709396362305</v>
+        <v>2.94709372520447</v>
       </c>
       <c r="H319" t="n">
         <v>973140</v>
@@ -9649,7 +9649,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907865524292</v>
       </c>
       <c r="H320" t="n">
         <v>786928</v>
@@ -9765,7 +9765,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H324" t="n">
         <v>228643</v>
@@ -9823,7 +9823,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.9947772026062</v>
+        <v>2.99477744102478</v>
       </c>
       <c r="H326" t="n">
         <v>373530</v>
@@ -9910,7 +9910,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848671913147</v>
+        <v>3.03848695755005</v>
       </c>
       <c r="H329" t="n">
         <v>242448</v>
@@ -9939,7 +9939,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.00404858589172</v>
+        <v>3.00404930114746</v>
       </c>
       <c r="H330" t="n">
         <v>261526</v>
@@ -9968,7 +9968,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504140853882</v>
+        <v>2.95504117012024</v>
       </c>
       <c r="H331" t="n">
         <v>188931</v>
@@ -9997,7 +9997,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90868258476257</v>
+        <v>2.90868210792542</v>
       </c>
       <c r="H332" t="n">
         <v>360673</v>
@@ -10026,7 +10026,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093605995178</v>
+        <v>2.97093558311462</v>
       </c>
       <c r="H333" t="n">
         <v>261603</v>
@@ -10142,7 +10142,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H337" t="n">
         <v>335332</v>
@@ -10171,7 +10171,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067185401917</v>
+        <v>3.01067161560059</v>
       </c>
       <c r="H338" t="n">
         <v>333907</v>
@@ -10200,7 +10200,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="n">
-        <v>2.99875068664551</v>
+        <v>2.99875092506409</v>
       </c>
       <c r="H339" t="n">
         <v>201579</v>
@@ -10229,7 +10229,7 @@
         <v>4.5</v>
       </c>
       <c r="G340" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H340" t="n">
         <v>224232</v>
@@ -10316,7 +10316,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173230171204</v>
+        <v>3.05173254013062</v>
       </c>
       <c r="H343" t="n">
         <v>351338</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484578132629</v>
+        <v>3.08484601974487</v>
       </c>
       <c r="H344" t="n">
         <v>309892</v>
@@ -10548,7 +10548,7 @@
         <v>4.5</v>
       </c>
       <c r="G351" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H351" t="n">
         <v>622537</v>
@@ -10577,7 +10577,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159514427185</v>
+        <v>2.87159562110901</v>
       </c>
       <c r="H352" t="n">
         <v>379734</v>
@@ -10606,7 +10606,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>2.84775400161743</v>
+        <v>2.84775352478027</v>
       </c>
       <c r="H353" t="n">
         <v>660590</v>
@@ -10635,7 +10635,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782234191895</v>
+        <v>2.93782210350037</v>
       </c>
       <c r="H354" t="n">
         <v>462237</v>
@@ -10664,7 +10664,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="n">
-        <v>2.95121836662292</v>
+        <v>2.9512186050415</v>
       </c>
       <c r="H355" t="n">
         <v>365296</v>
@@ -10693,7 +10693,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887787818909</v>
+        <v>2.87887859344482</v>
       </c>
       <c r="H356" t="n">
         <v>535677</v>
@@ -10780,7 +10780,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="n">
-        <v>2.92308592796326</v>
+        <v>2.92308616638184</v>
       </c>
       <c r="H359" t="n">
         <v>298337</v>
@@ -10809,7 +10809,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093494415283</v>
+        <v>2.89093470573425</v>
       </c>
       <c r="H360" t="n">
         <v>173469</v>
@@ -10838,7 +10838,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897274971008</v>
+        <v>2.89897298812866</v>
       </c>
       <c r="H361" t="n">
         <v>217176</v>
@@ -10896,7 +10896,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.8239529132843</v>
+        <v>2.82395339012146</v>
       </c>
       <c r="H363" t="n">
         <v>342599</v>
@@ -10925,7 +10925,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.83333086967468</v>
+        <v>2.8333306312561</v>
       </c>
       <c r="H364" t="n">
         <v>80574</v>
@@ -10954,7 +10954,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644299507141</v>
+        <v>2.78644323348999</v>
       </c>
       <c r="H365" t="n">
         <v>82995</v>
@@ -10983,7 +10983,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="n">
-        <v>2.79448127746582</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H366" t="n">
         <v>170095</v>
@@ -11012,7 +11012,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.7676887512207</v>
+        <v>2.76768851280212</v>
       </c>
       <c r="H367" t="n">
         <v>132754</v>
@@ -11041,7 +11041,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276330947876</v>
       </c>
       <c r="H368" t="n">
         <v>291905</v>
@@ -11070,7 +11070,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="n">
-        <v>2.66989517211914</v>
+        <v>2.66989469528198</v>
       </c>
       <c r="H369" t="n">
         <v>430652</v>
@@ -11128,7 +11128,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G371" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68731045722961</v>
       </c>
       <c r="H371" t="n">
         <v>152197</v>
@@ -11157,7 +11157,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>2.67257452011108</v>
+        <v>2.6725742816925</v>
       </c>
       <c r="H372" t="n">
         <v>256578</v>
@@ -11302,7 +11302,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H377" t="n">
         <v>218952</v>
@@ -11331,7 +11331,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.656498670578</v>
+        <v>2.65649819374084</v>
       </c>
       <c r="H378" t="n">
         <v>194294</v>
@@ -11389,7 +11389,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="n">
-        <v>2.66855549812317</v>
+        <v>2.66855525970459</v>
       </c>
       <c r="H380" t="n">
         <v>368830</v>
@@ -11505,7 +11505,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>2.56942200660706</v>
+        <v>2.56942224502563</v>
       </c>
       <c r="H384" t="n">
         <v>134122</v>
@@ -11563,7 +11563,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291290283203</v>
       </c>
       <c r="H386" t="n">
         <v>259728</v>
@@ -11650,7 +11650,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H389" t="n">
         <v>213962</v>
@@ -11708,7 +11708,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G391" t="n">
-        <v>2.55334687232971</v>
+        <v>2.55334639549255</v>
       </c>
       <c r="H391" t="n">
         <v>152367</v>
@@ -11824,7 +11824,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946144104004</v>
+        <v>2.71946120262146</v>
       </c>
       <c r="H395" t="n">
         <v>107839</v>
@@ -11853,7 +11853,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G396" t="n">
-        <v>2.68731021881104</v>
+        <v>2.68731045722961</v>
       </c>
       <c r="H396" t="n">
         <v>85342</v>
@@ -11969,7 +11969,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G400" t="n">
-        <v>2.6310453414917</v>
+        <v>2.63104557991028</v>
       </c>
       <c r="H400" t="n">
         <v>109092</v>
@@ -12027,7 +12027,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H402" t="n">
         <v>129322</v>
@@ -12085,7 +12085,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095094680786</v>
+        <v>2.61095118522644</v>
       </c>
       <c r="H404" t="n">
         <v>112728</v>
@@ -12114,7 +12114,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H405" t="n">
         <v>195865</v>
@@ -12143,7 +12143,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381908416748</v>
+        <v>2.65381932258606</v>
       </c>
       <c r="H406" t="n">
         <v>110887</v>
@@ -12172,7 +12172,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="n">
-        <v>2.66319727897644</v>
+        <v>2.6631965637207</v>
       </c>
       <c r="H407" t="n">
         <v>149523</v>
@@ -12201,7 +12201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="n">
-        <v>2.67257452011108</v>
+        <v>2.6725742816925</v>
       </c>
       <c r="H408" t="n">
         <v>128788</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338582992554</v>
+        <v>2.70338559150696</v>
       </c>
       <c r="H411" t="n">
         <v>157359</v>
@@ -12317,7 +12317,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H412" t="n">
         <v>148944</v>
@@ -12346,7 +12346,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291290283203</v>
       </c>
       <c r="H413" t="n">
         <v>90682</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H414" t="n">
         <v>196816</v>
@@ -12433,7 +12433,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H416" t="n">
         <v>50142</v>
@@ -12520,7 +12520,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459167480469</v>
+        <v>2.53459143638611</v>
       </c>
       <c r="H419" t="n">
         <v>215549</v>
@@ -12607,7 +12607,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H422" t="n">
         <v>133276</v>
@@ -12665,7 +12665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.48502540588379</v>
+        <v>2.48502516746521</v>
       </c>
       <c r="H424" t="n">
         <v>51012</v>
@@ -12781,7 +12781,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="n">
-        <v>2.5975546836853</v>
+        <v>2.59755492210388</v>
       </c>
       <c r="H428" t="n">
         <v>217980</v>
@@ -12810,7 +12810,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157346725464</v>
+        <v>2.60157370567322</v>
       </c>
       <c r="H429" t="n">
         <v>130021</v>
@@ -12839,7 +12839,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200672149658</v>
+        <v>2.55200695991516</v>
       </c>
       <c r="H430" t="n">
         <v>130300</v>
@@ -12897,7 +12897,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095094680786</v>
+        <v>2.61095118522644</v>
       </c>
       <c r="H432" t="n">
         <v>63021</v>
@@ -12926,7 +12926,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.71678233146667</v>
+        <v>2.71678256988525</v>
       </c>
       <c r="H433" t="n">
         <v>449341</v>
@@ -12955,7 +12955,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189656257629</v>
+        <v>2.81189632415771</v>
       </c>
       <c r="H434" t="n">
         <v>677293</v>
@@ -13042,7 +13042,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="n">
-        <v>2.8869161605835</v>
+        <v>2.88691592216492</v>
       </c>
       <c r="H437" t="n">
         <v>435459</v>
@@ -13100,7 +13100,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94719982147217</v>
+        <v>2.94719958305359</v>
       </c>
       <c r="H439" t="n">
         <v>359505</v>
@@ -13216,7 +13216,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136867523193</v>
+        <v>2.84136819839478</v>
       </c>
       <c r="H443" t="n">
         <v>279165</v>
@@ -13245,7 +13245,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>2.86012315750122</v>
+        <v>2.8601233959198</v>
       </c>
       <c r="H444" t="n">
         <v>227702</v>
@@ -13274,7 +13274,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682200431824</v>
       </c>
       <c r="H445" t="n">
         <v>208778</v>
@@ -13361,7 +13361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682200431824</v>
       </c>
       <c r="H448" t="n">
         <v>119126</v>
@@ -13390,7 +13390,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>2.82663249969482</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H449" t="n">
         <v>292316</v>
@@ -13419,7 +13419,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>2.79448127746582</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H450" t="n">
         <v>261468</v>
@@ -13506,7 +13506,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G453" t="n">
-        <v>2.82663249969482</v>
+        <v>2.82663226127625</v>
       </c>
       <c r="H453" t="n">
         <v>1050600</v>
@@ -13535,7 +13535,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868908882141</v>
+        <v>2.83868932723999</v>
       </c>
       <c r="H454" t="n">
         <v>379887</v>
@@ -13564,7 +13564,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887787818909</v>
+        <v>2.87887859344482</v>
       </c>
       <c r="H455" t="n">
         <v>244063</v>
@@ -13593,7 +13593,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="n">
-        <v>2.95523762702942</v>
+        <v>2.955237865448</v>
       </c>
       <c r="H456" t="n">
         <v>621450</v>
@@ -13651,7 +13651,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>2.86012315750122</v>
+        <v>2.8601233959198</v>
       </c>
       <c r="H458" t="n">
         <v>354316</v>
@@ -13680,7 +13680,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.8869161605835</v>
+        <v>2.88691592216492</v>
       </c>
       <c r="H459" t="n">
         <v>240063</v>
@@ -13767,7 +13767,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>2.86012315750122</v>
+        <v>2.8601233959198</v>
       </c>
       <c r="H462" t="n">
         <v>461987</v>
@@ -13796,7 +13796,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710518836975</v>
+        <v>2.92710471153259</v>
       </c>
       <c r="H463" t="n">
         <v>290532</v>
@@ -13825,7 +13825,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916201591492</v>
+        <v>2.93916177749634</v>
       </c>
       <c r="H464" t="n">
         <v>296201</v>
@@ -13883,7 +13883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94719982147217</v>
+        <v>2.94719958305359</v>
       </c>
       <c r="H466" t="n">
         <v>276862</v>
@@ -13912,7 +13912,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710518836975</v>
+        <v>2.92710471153259</v>
       </c>
       <c r="H467" t="n">
         <v>1298241</v>
@@ -13999,7 +13999,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370868682861</v>
+        <v>2.91370844841003</v>
       </c>
       <c r="H470" t="n">
         <v>103518</v>
@@ -14028,7 +14028,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648266792297</v>
+        <v>2.93648242950439</v>
       </c>
       <c r="H471" t="n">
         <v>136035</v>
@@ -14057,7 +14057,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.93246364593506</v>
+        <v>2.93246340751648</v>
       </c>
       <c r="H472" t="n">
         <v>142444</v>
@@ -14115,7 +14115,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G474" t="n">
-        <v>2.89629340171814</v>
+        <v>2.89629364013672</v>
       </c>
       <c r="H474" t="n">
         <v>607080</v>
@@ -14231,7 +14231,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270787239075</v>
+        <v>2.84270811080933</v>
       </c>
       <c r="H478" t="n">
         <v>266545</v>
@@ -14260,7 +14260,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314160346985</v>
+        <v>2.79314136505127</v>
       </c>
       <c r="H479" t="n">
         <v>317272</v>
@@ -14289,7 +14289,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.7623302936554</v>
+        <v>2.76233005523682</v>
       </c>
       <c r="H480" t="n">
         <v>456143</v>
@@ -14318,7 +14318,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H481" t="n">
         <v>1595732</v>
@@ -14376,7 +14376,7 @@
         <v>3.86400008201599</v>
       </c>
       <c r="G483" t="n">
-        <v>2.58817744255066</v>
+        <v>2.58817720413208</v>
       </c>
       <c r="H483" t="n">
         <v>299109</v>
@@ -14434,7 +14434,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H485" t="n">
         <v>239693</v>
@@ -14463,7 +14463,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H486" t="n">
         <v>174243</v>
@@ -14608,7 +14608,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266867637634</v>
+        <v>2.69266891479492</v>
       </c>
       <c r="H491" t="n">
         <v>413905</v>
@@ -14637,7 +14637,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927241325378</v>
+        <v>2.67927265167236</v>
       </c>
       <c r="H492" t="n">
         <v>427250</v>
@@ -14666,7 +14666,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908362388611</v>
       </c>
       <c r="H493" t="n">
         <v>248344</v>
@@ -14695,7 +14695,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="n">
-        <v>2.64980053901672</v>
+        <v>2.64980006217957</v>
       </c>
       <c r="H494" t="n">
         <v>168528</v>
@@ -14724,7 +14724,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>2.67525339126587</v>
+        <v>2.67525362968445</v>
       </c>
       <c r="H495" t="n">
         <v>459746</v>
@@ -14840,7 +14840,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276354789734</v>
+        <v>2.71276330947876</v>
       </c>
       <c r="H499" t="n">
         <v>464341</v>
@@ -14985,7 +14985,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H504" t="n">
         <v>308246</v>
@@ -15014,7 +15014,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51315784454346</v>
+        <v>2.51315760612488</v>
       </c>
       <c r="H505" t="n">
         <v>239707</v>
@@ -15043,7 +15043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H506" t="n">
         <v>188484</v>
@@ -15101,7 +15101,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057289123535</v>
+        <v>2.53057312965393</v>
       </c>
       <c r="H508" t="n">
         <v>166223</v>
@@ -15130,7 +15130,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449728012085</v>
+        <v>2.51449751853943</v>
       </c>
       <c r="H509" t="n">
         <v>151770</v>
@@ -15159,7 +15159,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119517326355</v>
+        <v>2.52119565010071</v>
       </c>
       <c r="H510" t="n">
         <v>181112</v>
@@ -15188,7 +15188,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>2.48502540588379</v>
+        <v>2.48502516746521</v>
       </c>
       <c r="H511" t="n">
         <v>183688</v>
@@ -15217,7 +15217,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G512" t="n">
-        <v>2.46894979476929</v>
+        <v>2.46894955635071</v>
       </c>
       <c r="H512" t="n">
         <v>202096</v>
@@ -15246,7 +15246,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.48502540588379</v>
+        <v>2.48502516746521</v>
       </c>
       <c r="H513" t="n">
         <v>248411</v>
@@ -15275,7 +15275,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.50846862792969</v>
+        <v>2.50846886634827</v>
       </c>
       <c r="H514" t="n">
         <v>345941</v>
@@ -15304,7 +15304,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H515" t="n">
         <v>481721</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H517" t="n">
         <v>342428</v>
@@ -15391,7 +15391,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526163101196</v>
+        <v>2.53526186943054</v>
       </c>
       <c r="H518" t="n">
         <v>296465</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.54530882835388</v>
+        <v>2.5453085899353</v>
       </c>
       <c r="H520" t="n">
         <v>236775</v>
@@ -15536,7 +15536,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5386106967926</v>
+        <v>2.53861045837402</v>
       </c>
       <c r="H523" t="n">
         <v>500528</v>
@@ -15565,7 +15565,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.5285632610321</v>
+        <v>2.52856349945068</v>
       </c>
       <c r="H524" t="n">
         <v>208864</v>
@@ -15594,7 +15594,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H525" t="n">
         <v>259926</v>
@@ -15652,7 +15652,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578151702881</v>
+        <v>2.64578175544739</v>
       </c>
       <c r="H527" t="n">
         <v>344329</v>
@@ -15681,7 +15681,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.57879948616028</v>
+        <v>2.57879972457886</v>
       </c>
       <c r="H528" t="n">
         <v>219606</v>
@@ -15768,7 +15768,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="n">
-        <v>2.5754508972168</v>
+        <v>2.57545065879822</v>
       </c>
       <c r="H531" t="n">
         <v>188683</v>
@@ -15826,7 +15826,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H533" t="n">
         <v>272113</v>
@@ -15855,7 +15855,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51851582527161</v>
+        <v>2.51851606369019</v>
       </c>
       <c r="H534" t="n">
         <v>180644</v>
@@ -15884,7 +15884,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.572101354599</v>
+        <v>2.57210159301758</v>
       </c>
       <c r="H535" t="n">
         <v>657310</v>
@@ -15913,7 +15913,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219622612</v>
+        <v>2.59219598770142</v>
       </c>
       <c r="H536" t="n">
         <v>753926</v>
@@ -15942,7 +15942,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526163101196</v>
+        <v>2.53526186943054</v>
       </c>
       <c r="H537" t="n">
         <v>618411</v>
@@ -16087,7 +16087,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148707389832</v>
+        <v>2.44148683547974</v>
       </c>
       <c r="H542" t="n">
         <v>168325</v>
@@ -16116,7 +16116,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.45488309860229</v>
+        <v>2.45488333702087</v>
       </c>
       <c r="H543" t="n">
         <v>168193</v>
@@ -16145,7 +16145,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827960014343</v>
+        <v>2.46827983856201</v>
       </c>
       <c r="H544" t="n">
         <v>133388</v>
@@ -16174,7 +16174,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G545" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H545" t="n">
         <v>205807</v>
@@ -16232,7 +16232,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.40464687347412</v>
+        <v>2.4046471118927</v>
       </c>
       <c r="H547" t="n">
         <v>141963</v>
@@ -16290,7 +16290,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>2.39794874191284</v>
+        <v>2.39794898033142</v>
       </c>
       <c r="H549" t="n">
         <v>151085</v>
@@ -16348,7 +16348,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="n">
-        <v>2.38120317459106</v>
+        <v>2.38120341300964</v>
       </c>
       <c r="H551" t="n">
         <v>177056</v>
@@ -16377,7 +16377,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>2.37115621566772</v>
+        <v>2.37115597724915</v>
       </c>
       <c r="H552" t="n">
         <v>210013</v>
@@ -16551,7 +16551,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G558" t="n">
-        <v>2.2271454334259</v>
+        <v>2.22714519500732</v>
       </c>
       <c r="H558" t="n">
         <v>273606</v>
@@ -16580,7 +16580,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G559" t="n">
-        <v>2.24723958969116</v>
+        <v>2.24723982810974</v>
       </c>
       <c r="H559" t="n">
         <v>293372</v>
@@ -16609,7 +16609,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.24389028549194</v>
+        <v>2.2438907623291</v>
       </c>
       <c r="H560" t="n">
         <v>289529</v>
@@ -16638,7 +16638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700336456299</v>
+        <v>2.19700312614441</v>
       </c>
       <c r="H561" t="n">
         <v>269006</v>
@@ -16725,7 +16725,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.27738165855408</v>
+        <v>2.27738189697266</v>
       </c>
       <c r="H564" t="n">
         <v>859120</v>
@@ -16754,7 +16754,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695640563965</v>
+        <v>2.18695616722107</v>
       </c>
       <c r="H565" t="n">
         <v>2292967</v>
@@ -16783,7 +16783,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="n">
-        <v>2.34436368942261</v>
+        <v>2.34436345100403</v>
       </c>
       <c r="H566" t="n">
         <v>1700593</v>
@@ -16812,7 +16812,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.25728678703308</v>
+        <v>2.25728702545166</v>
       </c>
       <c r="H567" t="n">
         <v>535502</v>
@@ -16841,7 +16841,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>2.27403235435486</v>
+        <v>2.27403259277344</v>
       </c>
       <c r="H568" t="n">
         <v>278538</v>
@@ -16870,7 +16870,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.25058889389038</v>
+        <v>2.2505886554718</v>
       </c>
       <c r="H569" t="n">
         <v>201800</v>
@@ -16899,7 +16899,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.24389028549194</v>
+        <v>2.2438907623291</v>
       </c>
       <c r="H570" t="n">
         <v>280790</v>
@@ -17015,7 +17015,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483590126038</v>
+        <v>2.44483613967896</v>
       </c>
       <c r="H574" t="n">
         <v>662269</v>
@@ -17102,7 +17102,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804361343384</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H577" t="n">
         <v>339561</v>
@@ -17189,7 +17189,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148707389832</v>
+        <v>2.44148683547974</v>
       </c>
       <c r="H580" t="n">
         <v>207497</v>
@@ -17247,7 +17247,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.42474150657654</v>
+        <v>2.42474126815796</v>
       </c>
       <c r="H582" t="n">
         <v>212044</v>
@@ -17276,7 +17276,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804361343384</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H583" t="n">
         <v>185158</v>
@@ -17305,7 +17305,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804361343384</v>
+        <v>2.41804337501526</v>
       </c>
       <c r="H584" t="n">
         <v>89113</v>
@@ -17334,7 +17334,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.45153427124023</v>
+        <v>2.45153450965881</v>
       </c>
       <c r="H585" t="n">
         <v>145222</v>
@@ -17392,7 +17392,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H587" t="n">
         <v>277880</v>
@@ -17450,7 +17450,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.48502540588379</v>
+        <v>2.48502516746521</v>
       </c>
       <c r="H589" t="n">
         <v>121975</v>
@@ -17479,7 +17479,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H590" t="n">
         <v>91101</v>
@@ -17566,7 +17566,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="n">
-        <v>2.45153427124023</v>
+        <v>2.45153450965881</v>
       </c>
       <c r="H593" t="n">
         <v>194484</v>
@@ -17682,7 +17682,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507260322571</v>
+        <v>2.49507236480713</v>
       </c>
       <c r="H597" t="n">
         <v>234943</v>
@@ -17740,7 +17740,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.46158123016357</v>
+        <v>2.46158146858215</v>
       </c>
       <c r="H599" t="n">
         <v>150521</v>
@@ -17769,7 +17769,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>2.45488309860229</v>
+        <v>2.45488333702087</v>
       </c>
       <c r="H600" t="n">
         <v>114328</v>
@@ -17885,7 +17885,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.43702149391174</v>
+        <v>2.43702125549316</v>
       </c>
       <c r="H604" t="n">
         <v>438968</v>
@@ -17914,7 +17914,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G605" t="n">
-        <v>2.31998920440674</v>
+        <v>2.31998944282532</v>
       </c>
       <c r="H605" t="n">
         <v>1262853</v>
@@ -17943,7 +17943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310486793518</v>
       </c>
       <c r="H606" t="n">
         <v>447106</v>
@@ -18030,7 +18030,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556799888611</v>
       </c>
       <c r="H609" t="n">
         <v>162895</v>
@@ -18088,7 +18088,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="n">
-        <v>2.23737859725952</v>
+        <v>2.23737835884094</v>
       </c>
       <c r="H611" t="n">
         <v>302598</v>
@@ -18146,7 +18146,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H613" t="n">
         <v>279124</v>
@@ -18175,7 +18175,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H614" t="n">
         <v>249358</v>
@@ -18204,7 +18204,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G615" t="n">
-        <v>2.1616518497467</v>
+        <v>2.16165208816528</v>
       </c>
       <c r="H615" t="n">
         <v>293231</v>
@@ -18233,7 +18233,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G616" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H616" t="n">
         <v>325512</v>
@@ -18291,7 +18291,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G618" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H618" t="n">
         <v>111257</v>
@@ -18378,7 +18378,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="n">
-        <v>2.23737859725952</v>
+        <v>2.23737835884094</v>
       </c>
       <c r="H621" t="n">
         <v>102223</v>
@@ -18407,7 +18407,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G622" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H622" t="n">
         <v>208980</v>
@@ -18436,7 +18436,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770522117615</v>
+        <v>2.24770498275757</v>
       </c>
       <c r="H623" t="n">
         <v>57699</v>
@@ -18552,7 +18552,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>2.35441088676453</v>
+        <v>2.35441064834595</v>
       </c>
       <c r="H627" t="n">
         <v>289153</v>
@@ -18668,7 +18668,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212642669678</v>
       </c>
       <c r="H631" t="n">
         <v>206647</v>
@@ -18697,7 +18697,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915823936462</v>
+        <v>2.39915800094604</v>
       </c>
       <c r="H632" t="n">
         <v>997504</v>
@@ -18726,7 +18726,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473679542542</v>
+        <v>2.36473703384399</v>
       </c>
       <c r="H633" t="n">
         <v>866249</v>
@@ -18755,7 +18755,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310486793518</v>
       </c>
       <c r="H634" t="n">
         <v>291169</v>
@@ -18842,7 +18842,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G637" t="n">
-        <v>2.35785293579102</v>
+        <v>2.35785269737244</v>
       </c>
       <c r="H637" t="n">
         <v>276596</v>
@@ -18871,7 +18871,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30277872085571</v>
+        <v>2.30277895927429</v>
       </c>
       <c r="H638" t="n">
         <v>143372</v>
@@ -18929,7 +18929,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556823730469</v>
+        <v>2.28556799888611</v>
       </c>
       <c r="H640" t="n">
         <v>188973</v>
@@ -18958,7 +18958,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.30622053146362</v>
+        <v>2.30622100830078</v>
       </c>
       <c r="H641" t="n">
         <v>66001</v>
@@ -18987,7 +18987,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>2.31998920440674</v>
+        <v>2.31998944282532</v>
       </c>
       <c r="H642" t="n">
         <v>44838</v>
@@ -19045,7 +19045,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245209693909</v>
       </c>
       <c r="H644" t="n">
         <v>158331</v>
@@ -19074,7 +19074,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H645" t="n">
         <v>204003</v>
@@ -19132,7 +19132,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H647" t="n">
         <v>91283</v>
@@ -19161,7 +19161,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H648" t="n">
         <v>204541</v>
@@ -19364,7 +19364,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.14444136619568</v>
+        <v>2.1444411277771</v>
       </c>
       <c r="H655" t="n">
         <v>109564</v>
@@ -19393,7 +19393,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>2.14788341522217</v>
+        <v>2.14788317680359</v>
       </c>
       <c r="H656" t="n">
         <v>94908</v>
@@ -19422,7 +19422,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15820980072021</v>
+        <v>2.15820956230164</v>
       </c>
       <c r="H657" t="n">
         <v>127746</v>
@@ -19480,7 +19480,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23049402236938</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H659" t="n">
         <v>89642</v>
@@ -19538,7 +19538,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H661" t="n">
         <v>58784</v>
@@ -19596,7 +19596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245209693909</v>
       </c>
       <c r="H663" t="n">
         <v>128498</v>
@@ -19654,7 +19654,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G665" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H665" t="n">
         <v>518570</v>
@@ -19683,7 +19683,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.30622053146362</v>
+        <v>2.30622100830078</v>
       </c>
       <c r="H666" t="n">
         <v>427892</v>
@@ -19712,7 +19712,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245209693909</v>
       </c>
       <c r="H667" t="n">
         <v>147403</v>
@@ -19741,7 +19741,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>2.2442626953125</v>
+        <v>2.24426293373108</v>
       </c>
       <c r="H668" t="n">
         <v>79510</v>
@@ -19770,7 +19770,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G669" t="n">
-        <v>2.25803136825562</v>
+        <v>2.25803112983704</v>
       </c>
       <c r="H669" t="n">
         <v>49943</v>
@@ -19799,7 +19799,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20639967918396</v>
+        <v>2.20639944076538</v>
       </c>
       <c r="H670" t="n">
         <v>234133</v>
@@ -19828,7 +19828,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H671" t="n">
         <v>122606</v>
@@ -19857,7 +19857,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G672" t="n">
-        <v>2.1616518497467</v>
+        <v>2.16165208816528</v>
       </c>
       <c r="H672" t="n">
         <v>76727</v>
@@ -19886,7 +19886,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H673" t="n">
         <v>87561</v>
@@ -19915,7 +19915,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H674" t="n">
         <v>127368</v>
@@ -19944,7 +19944,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H675" t="n">
         <v>54391</v>
@@ -19973,7 +19973,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H676" t="n">
         <v>182359</v>
@@ -20031,7 +20031,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>2.12034630775452</v>
+        <v>2.1203465461731</v>
       </c>
       <c r="H678" t="n">
         <v>97627</v>
@@ -20060,7 +20060,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001968383789</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H679" t="n">
         <v>147813</v>
@@ -20089,7 +20089,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H680" t="n">
         <v>72566</v>
@@ -20118,7 +20118,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H681" t="n">
         <v>90219</v>
@@ -20147,7 +20147,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="n">
-        <v>2.14788341522217</v>
+        <v>2.14788317680359</v>
       </c>
       <c r="H682" t="n">
         <v>38146</v>
@@ -20176,7 +20176,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690402030945</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H683" t="n">
         <v>89809</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H684" t="n">
         <v>106959</v>
@@ -20263,7 +20263,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>2.13067293167114</v>
+        <v>2.13067245483398</v>
       </c>
       <c r="H686" t="n">
         <v>92024</v>
@@ -20292,7 +20292,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690402030945</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H687" t="n">
         <v>150304</v>
@@ -20321,7 +20321,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H688" t="n">
         <v>283824</v>
@@ -20350,7 +20350,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G689" t="n">
-        <v>2.1616518497467</v>
+        <v>2.16165208816528</v>
       </c>
       <c r="H689" t="n">
         <v>92233</v>
@@ -20379,7 +20379,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>2.12034630775452</v>
+        <v>2.1203465461731</v>
       </c>
       <c r="H690" t="n">
         <v>188909</v>
@@ -20408,7 +20408,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H691" t="n">
         <v>98598</v>
@@ -20437,7 +20437,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.1375572681427</v>
+        <v>2.13755702972412</v>
       </c>
       <c r="H692" t="n">
         <v>87021</v>
@@ -20495,7 +20495,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378835678101</v>
       </c>
       <c r="H694" t="n">
         <v>310317</v>
@@ -20524,7 +20524,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>2.13067293167114</v>
+        <v>2.13067245483398</v>
       </c>
       <c r="H695" t="n">
         <v>137482</v>
@@ -20553,7 +20553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H696" t="n">
         <v>205834</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H697" t="n">
         <v>159262</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H701" t="n">
         <v>280938</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H702" t="n">
         <v>120044</v>
@@ -20756,7 +20756,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>2.05150413513184</v>
+        <v>2.05150365829468</v>
       </c>
       <c r="H703" t="n">
         <v>500439</v>
@@ -20785,7 +20785,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H704" t="n">
         <v>153586</v>
@@ -20843,7 +20843,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H706" t="n">
         <v>108391</v>
@@ -20901,7 +20901,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>1.98266160488129</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H708" t="n">
         <v>124414</v>
@@ -20930,7 +20930,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H709" t="n">
         <v>235805</v>
@@ -20988,7 +20988,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H711" t="n">
         <v>98948</v>
@@ -21046,7 +21046,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>1.98266160488129</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H713" t="n">
         <v>101638</v>
@@ -21075,7 +21075,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>1.98266160488129</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H714" t="n">
         <v>78349</v>
@@ -21104,7 +21104,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.95856666564941</v>
+        <v>1.95856690406799</v>
       </c>
       <c r="H715" t="n">
         <v>70649</v>
@@ -21133,7 +21133,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726112365723</v>
       </c>
       <c r="H716" t="n">
         <v>173384</v>
@@ -21162,7 +21162,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726112365723</v>
       </c>
       <c r="H717" t="n">
         <v>97454</v>
@@ -21191,7 +21191,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841859340668</v>
+        <v>1.84841871261597</v>
       </c>
       <c r="H718" t="n">
         <v>92562</v>
@@ -21249,7 +21249,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726112365723</v>
       </c>
       <c r="H720" t="n">
         <v>126796</v>
@@ -21278,7 +21278,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.88283967971802</v>
+        <v>1.8828399181366</v>
       </c>
       <c r="H721" t="n">
         <v>101180</v>
@@ -21307,7 +21307,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070341110229</v>
+        <v>1.92070353031158</v>
       </c>
       <c r="H722" t="n">
         <v>277130</v>
@@ -21336,7 +21336,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.90349268913269</v>
+        <v>1.90349280834198</v>
       </c>
       <c r="H723" t="n">
         <v>172278</v>
@@ -21365,7 +21365,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414557933807</v>
+        <v>1.92414546012878</v>
       </c>
       <c r="H724" t="n">
         <v>125557</v>
@@ -21394,7 +21394,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921943664551</v>
+        <v>1.97921967506409</v>
       </c>
       <c r="H725" t="n">
         <v>62710</v>
@@ -21452,7 +21452,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610377311707</v>
+        <v>1.98610353469849</v>
       </c>
       <c r="H727" t="n">
         <v>75372</v>
@@ -21481,7 +21481,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429317474365</v>
+        <v>2.03429341316223</v>
       </c>
       <c r="H728" t="n">
         <v>85910</v>
@@ -21510,7 +21510,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G729" t="n">
-        <v>2.05838823318481</v>
+        <v>2.05838799476624</v>
       </c>
       <c r="H729" t="n">
         <v>113777</v>
@@ -21568,7 +21568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099931716919</v>
+        <v>2.14099907875061</v>
       </c>
       <c r="H731" t="n">
         <v>181838</v>
@@ -21800,7 +21800,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168244838715</v>
       </c>
       <c r="H739" t="n">
         <v>264586</v>
@@ -21858,7 +21858,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200859546661</v>
+        <v>1.9620087146759</v>
       </c>
       <c r="H741" t="n">
         <v>248184</v>
@@ -21916,7 +21916,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H743" t="n">
         <v>238713</v>
@@ -21945,7 +21945,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>2.20639967918396</v>
+        <v>2.20639944076538</v>
       </c>
       <c r="H744" t="n">
         <v>196223</v>
@@ -22003,7 +22003,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="n">
-        <v>2.23049402236938</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H746" t="n">
         <v>326895</v>
@@ -22032,7 +22032,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H747" t="n">
         <v>206720</v>
@@ -22061,7 +22061,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.20984148979187</v>
+        <v>2.20984172821045</v>
       </c>
       <c r="H748" t="n">
         <v>177494</v>
@@ -22090,7 +22090,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H749" t="n">
         <v>156319</v>
@@ -22148,7 +22148,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H751" t="n">
         <v>49394</v>
@@ -22235,7 +22235,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509366035461</v>
       </c>
       <c r="H754" t="n">
         <v>409359</v>
@@ -22264,7 +22264,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15476751327515</v>
+        <v>2.15476775169373</v>
       </c>
       <c r="H755" t="n">
         <v>162636</v>
@@ -22293,7 +22293,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378835678101</v>
       </c>
       <c r="H756" t="n">
         <v>149343</v>
@@ -22351,7 +22351,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="n">
-        <v>2.17197847366333</v>
+        <v>2.17197799682617</v>
       </c>
       <c r="H758" t="n">
         <v>265608</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245209693909</v>
       </c>
       <c r="H759" t="n">
         <v>342700</v>
@@ -22409,7 +22409,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.2821261882782</v>
+        <v>2.28212642669678</v>
       </c>
       <c r="H760" t="n">
         <v>297330</v>
@@ -22496,7 +22496,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G763" t="n">
-        <v>2.35785293579102</v>
+        <v>2.35785269737244</v>
       </c>
       <c r="H763" t="n">
         <v>242878</v>
@@ -22554,7 +22554,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.49209547042847</v>
+        <v>2.49209523200989</v>
       </c>
       <c r="H765" t="n">
         <v>207696</v>
@@ -22583,7 +22583,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="n">
-        <v>2.41981101036072</v>
+        <v>2.41981053352356</v>
       </c>
       <c r="H766" t="n">
         <v>344369</v>
@@ -22670,7 +22670,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832703590393</v>
+        <v>2.47832679748535</v>
       </c>
       <c r="H769" t="n">
         <v>456800</v>
@@ -22699,7 +22699,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144269943237</v>
       </c>
       <c r="H770" t="n">
         <v>203705</v>
@@ -22728,7 +22728,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H771" t="n">
         <v>431119</v>
@@ -22757,7 +22757,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046354293823</v>
+        <v>2.44046378135681</v>
       </c>
       <c r="H772" t="n">
         <v>369438</v>
@@ -22786,7 +22786,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144269943237</v>
       </c>
       <c r="H773" t="n">
         <v>383952</v>
@@ -22815,7 +22815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144269943237</v>
       </c>
       <c r="H774" t="n">
         <v>376439</v>
@@ -22844,7 +22844,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.52651691436768</v>
+        <v>2.5265166759491</v>
       </c>
       <c r="H775" t="n">
         <v>412613</v>
@@ -22873,7 +22873,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274800300598</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H776" t="n">
         <v>426695</v>
@@ -22902,7 +22902,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>2.53684282302856</v>
+        <v>2.53684306144714</v>
       </c>
       <c r="H777" t="n">
         <v>356598</v>
@@ -22931,7 +22931,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H778" t="n">
         <v>296450</v>
@@ -22960,7 +22960,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>2.50242185592651</v>
+        <v>2.50242161750793</v>
       </c>
       <c r="H779" t="n">
         <v>334437</v>
@@ -22989,7 +22989,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307415008545</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H780" t="n">
         <v>192769</v>
@@ -23018,7 +23018,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307415008545</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H781" t="n">
         <v>177735</v>
@@ -23047,7 +23047,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274800300598</v>
+        <v>2.51274824142456</v>
       </c>
       <c r="H782" t="n">
         <v>217858</v>
@@ -23105,7 +23105,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="n">
-        <v>2.6056854724884</v>
+        <v>2.60568571090698</v>
       </c>
       <c r="H784" t="n">
         <v>273170</v>
@@ -23134,7 +23134,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945414543152</v>
+        <v>2.61945390701294</v>
       </c>
       <c r="H785" t="n">
         <v>236542</v>
@@ -23163,7 +23163,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.64354848861694</v>
+        <v>2.64354872703552</v>
       </c>
       <c r="H786" t="n">
         <v>412937</v>
@@ -23192,7 +23192,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="n">
-        <v>2.67108607292175</v>
+        <v>2.67108583450317</v>
       </c>
       <c r="H787" t="n">
         <v>308241</v>
@@ -23279,7 +23279,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945414543152</v>
+        <v>2.61945390701294</v>
       </c>
       <c r="H790" t="n">
         <v>328656</v>
@@ -23366,7 +23366,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224318504333</v>
+        <v>2.60224342346191</v>
       </c>
       <c r="H793" t="n">
         <v>285918</v>
@@ -23482,7 +23482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601185798645</v>
+        <v>2.61601161956787</v>
       </c>
       <c r="H797" t="n">
         <v>367842</v>
@@ -23540,7 +23540,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>2.56438016891479</v>
+        <v>2.56437993049622</v>
       </c>
       <c r="H799" t="n">
         <v>201471</v>
@@ -23627,7 +23627,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.69173884391785</v>
+        <v>2.69173860549927</v>
       </c>
       <c r="H802" t="n">
         <v>302710</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>2.68485450744629</v>
+        <v>2.68485426902771</v>
       </c>
       <c r="H804" t="n">
         <v>170162</v>
@@ -23743,7 +23743,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090764045715</v>
+        <v>2.77090740203857</v>
       </c>
       <c r="H806" t="n">
         <v>284595</v>
@@ -23772,7 +23772,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.71239113807678</v>
+        <v>2.71239137649536</v>
       </c>
       <c r="H807" t="n">
         <v>271085</v>
@@ -23801,7 +23801,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>2.73992824554443</v>
+        <v>2.73992800712585</v>
       </c>
       <c r="H808" t="n">
         <v>191242</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681258201599</v>
+        <v>2.74681210517883</v>
       </c>
       <c r="H811" t="n">
         <v>215954</v>
@@ -23975,7 +23975,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.7055070400238</v>
+        <v>2.70550680160522</v>
       </c>
       <c r="H814" t="n">
         <v>151157</v>
@@ -24033,7 +24033,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>2.76058125495911</v>
+        <v>2.76058101654053</v>
       </c>
       <c r="H816" t="n">
         <v>220094</v>
@@ -24091,7 +24091,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304390907288</v>
+        <v>2.73304414749146</v>
       </c>
       <c r="H818" t="n">
         <v>216455</v>
@@ -24120,7 +24120,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.7055070400238</v>
+        <v>2.70550680160522</v>
       </c>
       <c r="H819" t="n">
         <v>173539</v>
@@ -24149,7 +24149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>2.69518065452576</v>
+        <v>2.69518089294434</v>
       </c>
       <c r="H820" t="n">
         <v>209313</v>
@@ -24236,7 +24236,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>2.66420149803162</v>
+        <v>2.66420125961304</v>
       </c>
       <c r="H823" t="n">
         <v>229565</v>
@@ -24265,7 +24265,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H824" t="n">
         <v>459248</v>
@@ -24294,7 +24294,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H825" t="n">
         <v>305118</v>
@@ -24381,7 +24381,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H828" t="n">
         <v>412011</v>
@@ -24410,7 +24410,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322257995605</v>
+        <v>2.63322234153748</v>
       </c>
       <c r="H829" t="n">
         <v>67486</v>
@@ -24555,7 +24555,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G834" t="n">
-        <v>2.51619005203247</v>
+        <v>2.51619029045105</v>
       </c>
       <c r="H834" t="n">
         <v>155975</v>
@@ -24613,7 +24613,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.42669534683228</v>
+        <v>2.4266951084137</v>
       </c>
       <c r="H836" t="n">
         <v>233626</v>
@@ -24642,7 +24642,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423197746277</v>
+        <v>2.45423221588135</v>
       </c>
       <c r="H837" t="n">
         <v>108607</v>
@@ -24700,7 +24700,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>2.45079016685486</v>
+        <v>2.45078992843628</v>
       </c>
       <c r="H839" t="n">
         <v>177889</v>
@@ -24729,7 +24729,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734764099121</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H840" t="n">
         <v>102179</v>
@@ -24787,7 +24787,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="n">
-        <v>2.41981101036072</v>
+        <v>2.41981053352356</v>
       </c>
       <c r="H842" t="n">
         <v>263155</v>
@@ -24816,7 +24816,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734764099121</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H843" t="n">
         <v>82236</v>
@@ -24845,7 +24845,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="n">
-        <v>2.47144246101379</v>
+        <v>2.47144269943237</v>
       </c>
       <c r="H844" t="n">
         <v>59749</v>
@@ -24874,7 +24874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.505863904953</v>
+        <v>2.50586414337158</v>
       </c>
       <c r="H845" t="n">
         <v>222012</v>
@@ -24903,7 +24903,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.52651691436768</v>
+        <v>2.5265166759491</v>
       </c>
       <c r="H846" t="n">
         <v>296447</v>
@@ -24990,7 +24990,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013715744019</v>
+        <v>2.43013739585876</v>
       </c>
       <c r="H849" t="n">
         <v>115219</v>
@@ -25019,7 +25019,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.35441088676453</v>
+        <v>2.35441064834595</v>
       </c>
       <c r="H850" t="n">
         <v>388754</v>
@@ -25048,7 +25048,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G851" t="n">
-        <v>2.388831615448</v>
+        <v>2.38883209228516</v>
       </c>
       <c r="H851" t="n">
         <v>289904</v>
@@ -25077,7 +25077,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>2.31654715538025</v>
+        <v>2.31654739379883</v>
       </c>
       <c r="H852" t="n">
         <v>227097</v>
@@ -25106,7 +25106,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031582832336</v>
+        <v>2.33031558990479</v>
       </c>
       <c r="H853" t="n">
         <v>221581</v>
@@ -25222,7 +25222,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001968383789</v>
+        <v>2.11001992225647</v>
       </c>
       <c r="H857" t="n">
         <v>429648</v>
@@ -25309,7 +25309,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085160255432</v>
+        <v>2.03085112571716</v>
       </c>
       <c r="H860" t="n">
         <v>287672</v>
@@ -25367,7 +25367,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H862" t="n">
         <v>284968</v>
@@ -25396,7 +25396,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G863" t="n">
-        <v>2.1374819278717</v>
+        <v>2.13748216629028</v>
       </c>
       <c r="H863" t="n">
         <v>253019</v>
@@ -25454,7 +25454,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H865" t="n">
         <v>416439</v>
@@ -25512,7 +25512,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472953796387</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H867" t="n">
         <v>171746</v>
@@ -25599,7 +25599,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H870" t="n">
         <v>404038</v>
@@ -25686,7 +25686,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H873" t="n">
         <v>227376</v>
@@ -25715,7 +25715,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H874" t="n">
         <v>251629</v>
@@ -25744,7 +25744,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H875" t="n">
         <v>184992</v>
@@ -25889,7 +25889,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H880" t="n">
         <v>284652</v>
@@ -25918,7 +25918,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H881" t="n">
         <v>276051</v>
@@ -25947,7 +25947,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H882" t="n">
         <v>279659</v>
@@ -26005,7 +26005,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H884" t="n">
         <v>286493</v>
@@ -26121,7 +26121,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.90962898731232</v>
+        <v>1.90962886810303</v>
       </c>
       <c r="H888" t="n">
         <v>107626</v>
@@ -26150,7 +26150,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792812824249</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H889" t="n">
         <v>274027</v>
@@ -26179,7 +26179,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069498538971</v>
+        <v>1.88069474697113</v>
       </c>
       <c r="H890" t="n">
         <v>170084</v>
@@ -26208,7 +26208,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H891" t="n">
         <v>279577</v>
@@ -26237,7 +26237,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324532032013</v>
       </c>
       <c r="H892" t="n">
         <v>470871</v>
@@ -26295,7 +26295,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8987785577774</v>
+        <v>1.89877843856812</v>
       </c>
       <c r="H894" t="n">
         <v>237876</v>
@@ -26353,7 +26353,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H896" t="n">
         <v>911289</v>
@@ -26382,7 +26382,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472953796387</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H897" t="n">
         <v>805951</v>
@@ -26440,7 +26440,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.0325973033905</v>
+        <v>2.03259706497192</v>
       </c>
       <c r="H899" t="n">
         <v>626504</v>
@@ -26469,7 +26469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H900" t="n">
         <v>386888</v>
@@ -26498,7 +26498,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472953796387</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H901" t="n">
         <v>318897</v>
@@ -26556,7 +26556,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792812824249</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H903" t="n">
         <v>353686</v>
@@ -26614,7 +26614,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069498538971</v>
+        <v>1.88069474697113</v>
       </c>
       <c r="H905" t="n">
         <v>562530</v>
@@ -26672,7 +26672,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H907" t="n">
         <v>228173</v>
@@ -26701,7 +26701,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324532032013</v>
       </c>
       <c r="H908" t="n">
         <v>91411</v>
@@ -26788,7 +26788,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792812824249</v>
+        <v>1.88792836666107</v>
       </c>
       <c r="H911" t="n">
         <v>261392</v>
@@ -26817,7 +26817,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H912" t="n">
         <v>465653</v>
@@ -26846,7 +26846,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474388599396</v>
       </c>
       <c r="H913" t="n">
         <v>618635</v>
@@ -26904,7 +26904,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H915" t="n">
         <v>1785650</v>
@@ -26962,7 +26962,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199149608612</v>
       </c>
       <c r="H917" t="n">
         <v>497518</v>
@@ -26991,7 +26991,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G918" t="n">
-        <v>1.68177545070648</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H918" t="n">
         <v>629139</v>
@@ -27020,7 +27020,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.62752461433411</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H919" t="n">
         <v>393031</v>
@@ -27049,7 +27049,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H920" t="n">
         <v>347469</v>
@@ -27078,7 +27078,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327365875244</v>
+        <v>1.57327353954315</v>
       </c>
       <c r="H921" t="n">
         <v>763177</v>
@@ -27136,7 +27136,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H923" t="n">
         <v>378459</v>
@@ -27252,7 +27252,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.5768905878067</v>
+        <v>1.57689046859741</v>
       </c>
       <c r="H927" t="n">
         <v>526312</v>
@@ -27339,7 +27339,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G930" t="n">
-        <v>1.58412396907806</v>
+        <v>1.58412384986877</v>
       </c>
       <c r="H930" t="n">
         <v>987694</v>
@@ -27368,7 +27368,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007518768311</v>
+        <v>1.66007483005524</v>
       </c>
       <c r="H931" t="n">
         <v>679589</v>
@@ -27397,7 +27397,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944104194641</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H932" t="n">
         <v>532189</v>
@@ -27542,7 +27542,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454183101654</v>
       </c>
       <c r="H937" t="n">
         <v>332384</v>
@@ -27658,7 +27658,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G941" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H941" t="n">
         <v>345682</v>
@@ -27745,7 +27745,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H944" t="n">
         <v>336528</v>
@@ -27803,7 +27803,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H946" t="n">
         <v>241984</v>
@@ -27832,7 +27832,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.62752461433411</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H947" t="n">
         <v>1680843</v>
@@ -27977,7 +27977,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64560806751251</v>
+        <v>1.6456081867218</v>
       </c>
       <c r="H952" t="n">
         <v>114952</v>
@@ -28006,7 +28006,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.6998587846756</v>
+        <v>1.69985902309418</v>
       </c>
       <c r="H953" t="n">
         <v>409767</v>
@@ -28035,7 +28035,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G954" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H954" t="n">
         <v>542414</v>
@@ -28064,7 +28064,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.62752461433411</v>
+        <v>1.62752449512482</v>
       </c>
       <c r="H955" t="n">
         <v>414852</v>
@@ -28122,7 +28122,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390780448914</v>
+        <v>1.62390768527985</v>
       </c>
       <c r="H957" t="n">
         <v>183628</v>
@@ -28151,7 +28151,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199137687683</v>
+        <v>1.64199149608612</v>
       </c>
       <c r="H958" t="n">
         <v>141207</v>
@@ -28209,7 +28209,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944104194641</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H960" t="n">
         <v>254516</v>
@@ -28267,7 +28267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H962" t="n">
         <v>546781</v>
@@ -28296,7 +28296,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G963" t="n">
-        <v>1.68177545070648</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H963" t="n">
         <v>286763</v>
@@ -28325,7 +28325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H964" t="n">
         <v>258696</v>
@@ -28354,7 +28354,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H965" t="n">
         <v>412054</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815840244293</v>
       </c>
       <c r="H966" t="n">
         <v>445642</v>
@@ -28412,7 +28412,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900883197784</v>
+        <v>1.68900871276855</v>
       </c>
       <c r="H967" t="n">
         <v>205808</v>
@@ -28470,7 +28470,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624245166779</v>
+        <v>1.69624209403992</v>
       </c>
       <c r="H969" t="n">
         <v>150403</v>
@@ -28499,7 +28499,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H970" t="n">
         <v>116106</v>
@@ -28528,7 +28528,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815840244293</v>
       </c>
       <c r="H971" t="n">
         <v>185489</v>
@@ -28557,7 +28557,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H972" t="n">
         <v>278746</v>
@@ -28586,7 +28586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815852165222</v>
+        <v>1.67815840244293</v>
       </c>
       <c r="H973" t="n">
         <v>190802</v>
@@ -28615,7 +28615,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G974" t="n">
-        <v>1.67454206943512</v>
+        <v>1.67454183101654</v>
       </c>
       <c r="H974" t="n">
         <v>161117</v>
@@ -28644,7 +28644,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092537879944</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H975" t="n">
         <v>145445</v>
@@ -28702,7 +28702,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G977" t="n">
-        <v>1.68177545070648</v>
+        <v>1.68177533149719</v>
       </c>
       <c r="H977" t="n">
         <v>135253</v>
@@ -28731,7 +28731,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H978" t="n">
         <v>456317</v>
@@ -28789,7 +28789,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G980" t="n">
-        <v>1.79751038551331</v>
+        <v>1.79751026630402</v>
       </c>
       <c r="H980" t="n">
         <v>683548</v>
@@ -28818,7 +28818,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772666931152</v>
+        <v>1.75772643089294</v>
       </c>
       <c r="H981" t="n">
         <v>635657</v>
@@ -28905,7 +28905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.77219355106354</v>
+        <v>1.77219331264496</v>
       </c>
       <c r="H984" t="n">
         <v>304114</v>
@@ -28934,7 +28934,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134312152863</v>
+        <v>1.76134300231934</v>
       </c>
       <c r="H985" t="n">
         <v>462415</v>
@@ -29021,7 +29021,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>1.70709252357483</v>
+        <v>1.70709228515625</v>
       </c>
       <c r="H988" t="n">
         <v>321015</v>
@@ -29050,7 +29050,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H989" t="n">
         <v>290573</v>
@@ -29108,7 +29108,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>1.71432590484619</v>
+        <v>1.7143257856369</v>
       </c>
       <c r="H991" t="n">
         <v>218713</v>
@@ -29166,7 +29166,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666031360626</v>
+        <v>1.78666019439697</v>
       </c>
       <c r="H993" t="n">
         <v>380638</v>
@@ -29195,7 +29195,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666031360626</v>
+        <v>1.78666019439697</v>
       </c>
       <c r="H994" t="n">
         <v>337289</v>
@@ -29224,7 +29224,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984515190125</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H995" t="n">
         <v>1295316</v>
@@ -29253,7 +29253,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G996" t="n">
-        <v>2.01451373100281</v>
+        <v>2.01451349258423</v>
       </c>
       <c r="H996" t="n">
         <v>2489093</v>
@@ -29311,7 +29311,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.93494594097137</v>
+        <v>1.9349457025528</v>
       </c>
       <c r="H998" t="n">
         <v>1204470</v>
@@ -29340,7 +29340,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G999" t="n">
-        <v>1.9168621301651</v>
+        <v>1.91686224937439</v>
       </c>
       <c r="H999" t="n">
         <v>662234</v>
@@ -29369,7 +29369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1000" t="n">
         <v>951588</v>
@@ -29398,7 +29398,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196315765381</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1001" t="n">
         <v>659632</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1002" t="n">
         <v>591585</v>
@@ -29456,7 +29456,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1003" t="n">
         <v>552967</v>
@@ -29514,7 +29514,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.05429768562317</v>
+        <v>2.05429792404175</v>
       </c>
       <c r="H1005" t="n">
         <v>604497</v>
@@ -29572,7 +29572,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.0036633014679</v>
+        <v>2.00366353988647</v>
       </c>
       <c r="H1007" t="n">
         <v>828831</v>
@@ -29601,7 +29601,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.04344773292542</v>
+        <v>2.04344749450684</v>
       </c>
       <c r="H1008" t="n">
         <v>410384</v>
@@ -29630,7 +29630,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.0181303024292</v>
+        <v>2.01813054084778</v>
       </c>
       <c r="H1009" t="n">
         <v>304169</v>
@@ -29688,7 +29688,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1011" t="n">
         <v>341025</v>
@@ -29717,7 +29717,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196315765381</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1012" t="n">
         <v>244318</v>
@@ -29775,7 +29775,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H1014" t="n">
         <v>219712</v>
@@ -29804,7 +29804,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1015" t="n">
         <v>196502</v>
@@ -29862,7 +29862,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1017" t="n">
         <v>308613</v>
@@ -29891,7 +29891,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.93856275081635</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1018" t="n">
         <v>371965</v>
@@ -29978,7 +29978,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H1021" t="n">
         <v>243379</v>
@@ -30007,7 +30007,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.93856275081635</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1022" t="n">
         <v>218394</v>
@@ -30036,7 +30036,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324532032013</v>
       </c>
       <c r="H1023" t="n">
         <v>212691</v>
@@ -30123,7 +30123,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984515190125</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H1026" t="n">
         <v>271070</v>
@@ -30152,7 +30152,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.93856275081635</v>
+        <v>1.93856251239777</v>
       </c>
       <c r="H1027" t="n">
         <v>619856</v>
@@ -30239,7 +30239,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1030" t="n">
         <v>334352</v>
@@ -30268,7 +30268,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H1031" t="n">
         <v>346362</v>
@@ -30326,7 +30326,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984515190125</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H1033" t="n">
         <v>665587</v>
@@ -30355,7 +30355,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H1034" t="n">
         <v>562475</v>
@@ -30413,7 +30413,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474376678467</v>
+        <v>1.80474388599396</v>
       </c>
       <c r="H1036" t="n">
         <v>595397</v>
@@ -30471,7 +30471,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964297771454</v>
+        <v>1.73964285850525</v>
       </c>
       <c r="H1038" t="n">
         <v>332631</v>
@@ -30500,7 +30500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.77219355106354</v>
+        <v>1.77219331264496</v>
       </c>
       <c r="H1039" t="n">
         <v>337490</v>
@@ -30529,7 +30529,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77581012248993</v>
+        <v>1.77581000328064</v>
       </c>
       <c r="H1040" t="n">
         <v>435901</v>
@@ -30674,7 +30674,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.81559407711029</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1045" t="n">
         <v>215954</v>
@@ -30703,7 +30703,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899484157562</v>
+        <v>1.85899448394775</v>
       </c>
       <c r="H1046" t="n">
         <v>633060</v>
@@ -30761,7 +30761,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.81921064853668</v>
+        <v>1.81921076774597</v>
       </c>
       <c r="H1048" t="n">
         <v>428986</v>
@@ -30790,7 +30790,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644438743591</v>
+        <v>1.82644426822662</v>
       </c>
       <c r="H1049" t="n">
         <v>268233</v>
@@ -30819,7 +30819,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176122188568</v>
+        <v>1.85176110267639</v>
       </c>
       <c r="H1050" t="n">
         <v>328554</v>
@@ -30848,7 +30848,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.81559407711029</v>
+        <v>1.815593957901</v>
       </c>
       <c r="H1051" t="n">
         <v>301333</v>
@@ -30906,7 +30906,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H1053" t="n">
         <v>578759</v>
@@ -31022,7 +31022,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965696811676</v>
+        <v>1.56965708732605</v>
       </c>
       <c r="H1057" t="n">
         <v>544343</v>
@@ -31051,7 +31051,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.51178956031799</v>
+        <v>1.5117894411087</v>
       </c>
       <c r="H1058" t="n">
         <v>534309</v>
@@ -31080,7 +31080,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285579681396</v>
+        <v>1.48285567760468</v>
       </c>
       <c r="H1059" t="n">
         <v>394349</v>
@@ -31109,7 +31109,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366825580597</v>
+        <v>1.43366837501526</v>
       </c>
       <c r="H1060" t="n">
         <v>342436</v>
@@ -31138,7 +31138,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448083400726</v>
+        <v>1.38448107242584</v>
       </c>
       <c r="H1061" t="n">
         <v>581654</v>
@@ -31167,7 +31167,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.35120701789856</v>
+        <v>1.35120713710785</v>
       </c>
       <c r="H1062" t="n">
         <v>475900</v>
@@ -31254,7 +31254,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.18628454208374</v>
+        <v>1.18628442287445</v>
       </c>
       <c r="H1065" t="n">
         <v>545776</v>
@@ -31283,7 +31283,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412868499756</v>
+        <v>1.01412844657898</v>
       </c>
       <c r="H1066" t="n">
         <v>500114</v>
@@ -31341,7 +31341,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00400173664093</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1068" t="n">
         <v>418504</v>
@@ -31370,7 +31370,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1069" t="n">
         <v>281501</v>
@@ -31428,7 +31428,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1071" t="n">
         <v>337483</v>
@@ -31457,7 +31457,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.13854384422302</v>
+        <v>1.13854396343231</v>
       </c>
       <c r="H1072" t="n">
         <v>440163</v>
@@ -31486,7 +31486,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.22679197788239</v>
+        <v>1.22679173946381</v>
       </c>
       <c r="H1073" t="n">
         <v>282057</v>
@@ -31573,7 +31573,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.2586190700531</v>
+        <v>1.25861895084381</v>
       </c>
       <c r="H1076" t="n">
         <v>129270</v>
@@ -31602,7 +31602,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.22679197788239</v>
+        <v>1.22679173946381</v>
       </c>
       <c r="H1077" t="n">
         <v>359736</v>
@@ -31631,7 +31631,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.1776043176651</v>
+        <v>1.17760443687439</v>
       </c>
       <c r="H1078" t="n">
         <v>204338</v>
@@ -31660,7 +31660,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.13854384422302</v>
+        <v>1.13854396343231</v>
       </c>
       <c r="H1079" t="n">
         <v>243445</v>
@@ -31747,7 +31747,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1082" t="n">
         <v>144468</v>
@@ -31834,7 +31834,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.2947860956192</v>
+        <v>1.29478621482849</v>
       </c>
       <c r="H1085" t="n">
         <v>332626</v>
@@ -31921,7 +31921,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.17181766033173</v>
+        <v>1.17181777954102</v>
       </c>
       <c r="H1088" t="n">
         <v>216163</v>
@@ -31979,7 +31979,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.20509147644043</v>
+        <v>1.20509159564972</v>
       </c>
       <c r="H1090" t="n">
         <v>122954</v>
@@ -32066,7 +32066,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1093" t="n">
         <v>222649</v>
@@ -32095,7 +32095,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100496292114</v>
+        <v>1.22100508213043</v>
       </c>
       <c r="H1094" t="n">
         <v>124832</v>
@@ -32182,7 +32182,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1097" t="n">
         <v>97350</v>
@@ -32211,7 +32211,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1098" t="n">
         <v>241005</v>
@@ -32269,7 +32269,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.17181766033173</v>
+        <v>1.17181777954102</v>
       </c>
       <c r="H1100" t="n">
         <v>41271</v>
@@ -32356,7 +32356,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.15590417385101</v>
+        <v>1.15590405464172</v>
       </c>
       <c r="H1103" t="n">
         <v>128118</v>
@@ -32385,7 +32385,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.15590417385101</v>
+        <v>1.15590405464172</v>
       </c>
       <c r="H1104" t="n">
         <v>105864</v>
@@ -32414,7 +32414,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.12407696247101</v>
+        <v>1.1240770816803</v>
       </c>
       <c r="H1105" t="n">
         <v>152349</v>
@@ -32443,7 +32443,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1106" t="n">
         <v>214071</v>
@@ -32472,7 +32472,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318927764893</v>
+        <v>1.05318915843964</v>
       </c>
       <c r="H1107" t="n">
         <v>149211</v>
@@ -32501,7 +32501,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1108" t="n">
         <v>254021</v>
@@ -32559,7 +32559,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.02714884281158</v>
+        <v>1.02714896202087</v>
       </c>
       <c r="H1110" t="n">
         <v>107166</v>
@@ -32617,7 +32617,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301473617554</v>
       </c>
       <c r="H1112" t="n">
         <v>157009</v>
@@ -32646,7 +32646,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1113" t="n">
         <v>128951</v>
@@ -32675,7 +32675,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428362369537</v>
+        <v>0.992428243160248</v>
       </c>
       <c r="H1114" t="n">
         <v>168726</v>
@@ -32704,7 +32704,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04306244850159</v>
+        <v>1.0430623292923</v>
       </c>
       <c r="H1115" t="n">
         <v>194795</v>
@@ -32762,7 +32762,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.06186938285828</v>
+        <v>1.06186926364899</v>
       </c>
       <c r="H1117" t="n">
         <v>1781957</v>
@@ -32878,7 +32878,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.157350897789</v>
+        <v>1.15735077857971</v>
       </c>
       <c r="H1121" t="n">
         <v>630215</v>
@@ -32907,7 +32907,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011727809906</v>
+        <v>1.15011739730835</v>
       </c>
       <c r="H1122" t="n">
         <v>444295</v>
@@ -32936,7 +32936,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.13565063476562</v>
+        <v>1.13565051555634</v>
       </c>
       <c r="H1123" t="n">
         <v>441474</v>
@@ -32965,7 +32965,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.17181766033173</v>
+        <v>1.17181777954102</v>
       </c>
       <c r="H1124" t="n">
         <v>675402</v>
@@ -32994,7 +32994,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1125" t="n">
         <v>636837</v>
@@ -33023,7 +33023,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.19641137123108</v>
+        <v>1.19641149044037</v>
       </c>
       <c r="H1126" t="n">
         <v>400827</v>
@@ -33081,7 +33081,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.09658992290497</v>
+        <v>1.09658980369568</v>
       </c>
       <c r="H1128" t="n">
         <v>569514</v>
@@ -33110,7 +33110,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212292194366</v>
+        <v>1.08212304115295</v>
       </c>
       <c r="H1129" t="n">
         <v>419381</v>
@@ -33139,7 +33139,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1130" t="n">
         <v>250136</v>
@@ -33168,7 +33168,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14867079257965</v>
+        <v>1.14867067337036</v>
       </c>
       <c r="H1131" t="n">
         <v>335721</v>
@@ -33313,7 +33313,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.12552356719971</v>
+        <v>1.125523686409</v>
       </c>
       <c r="H1136" t="n">
         <v>207095</v>
@@ -33342,7 +33342,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.09514319896698</v>
+        <v>1.09514331817627</v>
       </c>
       <c r="H1137" t="n">
         <v>145504</v>
@@ -33371,7 +33371,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237658023834</v>
+        <v>1.10237669944763</v>
       </c>
       <c r="H1138" t="n">
         <v>192526</v>
@@ -33429,7 +33429,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.076336145401</v>
+        <v>1.07633626461029</v>
       </c>
       <c r="H1140" t="n">
         <v>134302</v>
@@ -33458,7 +33458,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.060422539711</v>
+        <v>1.06042265892029</v>
       </c>
       <c r="H1141" t="n">
         <v>213541</v>
@@ -33545,7 +33545,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1144" t="n">
         <v>205530</v>
@@ -33603,7 +33603,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.08790981769562</v>
+        <v>1.08790969848633</v>
       </c>
       <c r="H1146" t="n">
         <v>227859</v>
@@ -33632,7 +33632,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1147" t="n">
         <v>313392</v>
@@ -33777,7 +33777,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.08935642242432</v>
+        <v>1.08935654163361</v>
       </c>
       <c r="H1152" t="n">
         <v>149121</v>
@@ -33806,7 +33806,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.09224987030029</v>
+        <v>1.092249751091</v>
       </c>
       <c r="H1153" t="n">
         <v>146621</v>
@@ -33922,7 +33922,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.07488942146301</v>
+        <v>1.0748895406723</v>
       </c>
       <c r="H1157" t="n">
         <v>172984</v>
@@ -33951,7 +33951,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.06186938285828</v>
+        <v>1.06186926364899</v>
       </c>
       <c r="H1158" t="n">
         <v>208272</v>
@@ -33980,7 +33980,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595577716827</v>
+        <v>1.04595589637756</v>
       </c>
       <c r="H1159" t="n">
         <v>160290</v>
@@ -34009,7 +34009,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846873760223</v>
+        <v>1.01846861839294</v>
       </c>
       <c r="H1160" t="n">
         <v>289771</v>
@@ -34067,7 +34067,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981578826904</v>
+        <v>0.990981638431549</v>
       </c>
       <c r="H1162" t="n">
         <v>183349</v>
@@ -34125,7 +34125,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088369369507</v>
       </c>
       <c r="H1164" t="n">
         <v>137388</v>
@@ -34154,7 +34154,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.975068151950836</v>
+        <v>0.975068032741547</v>
       </c>
       <c r="H1165" t="n">
         <v>149823</v>
@@ -34183,7 +34183,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.00400173664093</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1166" t="n">
         <v>268517</v>
@@ -34212,7 +34212,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.01702201366425</v>
+        <v>1.01702213287354</v>
       </c>
       <c r="H1167" t="n">
         <v>307311</v>
@@ -34270,7 +34270,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088369369507</v>
       </c>
       <c r="H1169" t="n">
         <v>318607</v>
@@ -34299,7 +34299,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321691036224</v>
+        <v>0.995321750640869</v>
       </c>
       <c r="H1170" t="n">
         <v>284109</v>
@@ -34357,7 +34357,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.01702201366425</v>
+        <v>1.01702213287354</v>
       </c>
       <c r="H1172" t="n">
         <v>246499</v>
@@ -34444,7 +34444,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.986641466617584</v>
+        <v>0.986641585826874</v>
       </c>
       <c r="H1175" t="n">
         <v>123963</v>
@@ -34473,7 +34473,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1176" t="n">
         <v>165512</v>
@@ -34531,7 +34531,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.972174644470215</v>
+        <v>0.97217470407486</v>
       </c>
       <c r="H1178" t="n">
         <v>90569</v>
@@ -34676,7 +34676,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1183" t="n">
         <v>281167</v>
@@ -34792,7 +34792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880610942841</v>
+        <v>0.925880551338196</v>
       </c>
       <c r="H1187" t="n">
         <v>573190</v>
@@ -34821,7 +34821,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1188" t="n">
         <v>555967</v>
@@ -34850,7 +34850,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468754529953</v>
       </c>
       <c r="H1189" t="n">
         <v>485261</v>
@@ -34879,7 +34879,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468754529953</v>
       </c>
       <c r="H1190" t="n">
         <v>152429</v>
@@ -34908,7 +34908,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.937454104423523</v>
+        <v>0.937454164028168</v>
       </c>
       <c r="H1191" t="n">
         <v>312695</v>
@@ -34937,7 +34937,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900828361511</v>
+        <v>0.938900887966156</v>
       </c>
       <c r="H1192" t="n">
         <v>194055</v>
@@ -35024,7 +35024,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.921540558338165</v>
+        <v>0.921540677547455</v>
       </c>
       <c r="H1195" t="n">
         <v>289851</v>
@@ -35053,7 +35053,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.898393511772156</v>
+        <v>0.898393571376801</v>
       </c>
       <c r="H1196" t="n">
         <v>406491</v>
@@ -35111,7 +35111,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1198" t="n">
         <v>368604</v>
@@ -35140,7 +35140,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.886820018291473</v>
+        <v>0.886820077896118</v>
       </c>
       <c r="H1199" t="n">
         <v>2193562</v>
@@ -35169,7 +35169,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1200" t="n">
         <v>628275</v>
@@ -35198,7 +35198,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1201" t="n">
         <v>504293</v>
@@ -35227,7 +35227,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.937454104423523</v>
+        <v>0.937454164028168</v>
       </c>
       <c r="H1202" t="n">
         <v>519628</v>
@@ -35256,7 +35256,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1203" t="n">
         <v>394327</v>
@@ -35314,7 +35314,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1205" t="n">
         <v>119791</v>
@@ -35372,7 +35372,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1207" t="n">
         <v>363479</v>
@@ -35459,7 +35459,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928773999214172</v>
+        <v>0.928774118423462</v>
       </c>
       <c r="H1210" t="n">
         <v>89660</v>
@@ -35488,7 +35488,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601031780243</v>
+        <v>0.960601091384888</v>
       </c>
       <c r="H1211" t="n">
         <v>668739</v>
@@ -35575,7 +35575,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1214" t="n">
         <v>432837</v>
@@ -35604,7 +35604,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951921105384827</v>
+        <v>0.951920986175537</v>
       </c>
       <c r="H1215" t="n">
         <v>224463</v>
@@ -35633,7 +35633,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.918647170066833</v>
+        <v>0.918647110462189</v>
       </c>
       <c r="H1216" t="n">
         <v>231495</v>
@@ -35662,7 +35662,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753841400146</v>
+        <v>0.915753781795502</v>
       </c>
       <c r="H1217" t="n">
         <v>178785</v>
@@ -35691,7 +35691,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246465206146</v>
       </c>
       <c r="H1218" t="n">
         <v>276978</v>
@@ -35807,7 +35807,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.840525984764099</v>
+        <v>0.840525925159454</v>
       </c>
       <c r="H1222" t="n">
         <v>361515</v>
@@ -35865,7 +35865,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.824612438678741</v>
+        <v>0.824612379074097</v>
       </c>
       <c r="H1224" t="n">
         <v>195845</v>
@@ -35894,7 +35894,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1225" t="n">
         <v>209693</v>
@@ -35952,7 +35952,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871800422668</v>
+        <v>0.776871740818024</v>
       </c>
       <c r="H1227" t="n">
         <v>366061</v>
@@ -36010,7 +36010,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024431228638</v>
+        <v>0.732024371623993</v>
       </c>
       <c r="H1229" t="n">
         <v>446350</v>
@@ -36068,7 +36068,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.772531569004059</v>
+        <v>0.772531628608704</v>
       </c>
       <c r="H1231" t="n">
         <v>205732</v>
@@ -36097,7 +36097,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211853027344</v>
+        <v>0.781211793422699</v>
       </c>
       <c r="H1232" t="n">
         <v>238451</v>
@@ -36126,7 +36126,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191635608673</v>
+        <v>0.768191576004028</v>
       </c>
       <c r="H1233" t="n">
         <v>672823</v>
@@ -36184,7 +36184,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.805805563926697</v>
+        <v>0.805805444717407</v>
       </c>
       <c r="H1235" t="n">
         <v>493728</v>
@@ -36242,7 +36242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079201221466</v>
       </c>
       <c r="H1237" t="n">
         <v>399300</v>
@@ -36271,7 +36271,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.850652813911438</v>
+        <v>0.850652873516083</v>
       </c>
       <c r="H1238" t="n">
         <v>314246</v>
@@ -36300,7 +36300,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799741268158</v>
+        <v>0.873799860477448</v>
       </c>
       <c r="H1239" t="n">
         <v>463886</v>
@@ -36329,7 +36329,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520340919495</v>
       </c>
       <c r="H1240" t="n">
         <v>465758</v>
@@ -36387,7 +36387,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520340919495</v>
       </c>
       <c r="H1242" t="n">
         <v>529118</v>
@@ -36416,7 +36416,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.895500183105469</v>
+        <v>0.895500302314758</v>
       </c>
       <c r="H1243" t="n">
         <v>309302</v>
@@ -36445,7 +36445,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901286959648132</v>
       </c>
       <c r="H1244" t="n">
         <v>350164</v>
@@ -36474,7 +36474,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1245" t="n">
         <v>371270</v>
@@ -36561,7 +36561,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967064857483</v>
+        <v>0.909967184066772</v>
       </c>
       <c r="H1248" t="n">
         <v>283507</v>
@@ -36619,7 +36619,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.863673031330109</v>
+        <v>0.863672971725464</v>
       </c>
       <c r="H1250" t="n">
         <v>2118508</v>
@@ -36648,7 +36648,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.886820018291473</v>
+        <v>0.886820077896118</v>
       </c>
       <c r="H1251" t="n">
         <v>315281</v>
@@ -36706,7 +36706,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.895500183105469</v>
+        <v>0.895500302314758</v>
       </c>
       <c r="H1253" t="n">
         <v>276903</v>
@@ -36735,7 +36735,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.894053339958191</v>
+        <v>0.89405345916748</v>
       </c>
       <c r="H1254" t="n">
         <v>333750</v>
@@ -36793,7 +36793,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.886820018291473</v>
+        <v>0.886820077896118</v>
       </c>
       <c r="H1256" t="n">
         <v>196304</v>
@@ -36967,7 +36967,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246465206146</v>
       </c>
       <c r="H1262" t="n">
         <v>261444</v>
@@ -37025,7 +37025,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.88537323474884</v>
+        <v>0.885373294353485</v>
       </c>
       <c r="H1264" t="n">
         <v>229764</v>
@@ -37054,7 +37054,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.862226366996765</v>
+        <v>0.86222642660141</v>
       </c>
       <c r="H1265" t="n">
         <v>389130</v>
@@ -37083,7 +37083,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1266" t="n">
         <v>174813</v>
@@ -37112,7 +37112,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459688663483</v>
+        <v>0.869459807872772</v>
       </c>
       <c r="H1267" t="n">
         <v>207362</v>
@@ -37170,7 +37170,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520400524139</v>
+        <v>0.908520340919495</v>
       </c>
       <c r="H1269" t="n">
         <v>264575</v>
@@ -37257,7 +37257,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840295314789</v>
+        <v>0.899840176105499</v>
       </c>
       <c r="H1272" t="n">
         <v>196824</v>
@@ -37286,7 +37286,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073676586151</v>
       </c>
       <c r="H1273" t="n">
         <v>210846</v>
@@ -37315,7 +37315,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733623981476</v>
+        <v>0.902733683586121</v>
       </c>
       <c r="H1274" t="n">
         <v>125768</v>
@@ -37344,7 +37344,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1275" t="n">
         <v>199794</v>
@@ -37373,7 +37373,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.88103324174881</v>
+        <v>0.881033420562744</v>
       </c>
       <c r="H1276" t="n">
         <v>275751</v>
@@ -37431,7 +37431,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.854992985725403</v>
+        <v>0.854992926120758</v>
       </c>
       <c r="H1278" t="n">
         <v>195138</v>
@@ -37460,7 +37460,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1279" t="n">
         <v>178958</v>
@@ -37489,7 +37489,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206209182739</v>
+        <v>0.84920608997345</v>
       </c>
       <c r="H1280" t="n">
         <v>159959</v>
@@ -37518,7 +37518,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079260826111</v>
+        <v>0.839079201221466</v>
       </c>
       <c r="H1281" t="n">
         <v>188343</v>
@@ -37547,7 +37547,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.840525984764099</v>
+        <v>0.840525925159454</v>
       </c>
       <c r="H1282" t="n">
         <v>192827</v>
@@ -37663,7 +37663,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.82605904340744</v>
+        <v>0.826059103012085</v>
       </c>
       <c r="H1286" t="n">
         <v>345204</v>
@@ -37692,7 +37692,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.853546261787415</v>
+        <v>0.853546142578125</v>
       </c>
       <c r="H1287" t="n">
         <v>307350</v>
@@ -37750,7 +37750,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.853546261787415</v>
+        <v>0.853546142578125</v>
       </c>
       <c r="H1289" t="n">
         <v>211199</v>
@@ -37837,7 +37837,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312642097473</v>
+        <v>0.846312701702118</v>
       </c>
       <c r="H1292" t="n">
         <v>193484</v>
@@ -37895,7 +37895,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799741268158</v>
+        <v>0.873799860477448</v>
       </c>
       <c r="H1294" t="n">
         <v>252193</v>
@@ -37924,7 +37924,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.878139913082123</v>
+        <v>0.878139853477478</v>
       </c>
       <c r="H1295" t="n">
         <v>546482</v>
@@ -37953,7 +37953,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.946134209632874</v>
+        <v>0.946134388446808</v>
       </c>
       <c r="H1296" t="n">
         <v>1951196</v>
@@ -37982,7 +37982,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.975068151950836</v>
+        <v>0.975068032741547</v>
       </c>
       <c r="H1297" t="n">
         <v>1511134</v>
@@ -38040,7 +38040,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301473617554</v>
       </c>
       <c r="H1299" t="n">
         <v>514735</v>
@@ -38127,7 +38127,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301473617554</v>
       </c>
       <c r="H1302" t="n">
         <v>468329</v>
@@ -38214,7 +38214,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1305" t="n">
         <v>460160</v>
@@ -38243,7 +38243,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.06186938285828</v>
+        <v>1.06186926364899</v>
       </c>
       <c r="H1306" t="n">
         <v>1146881</v>
@@ -38301,7 +38301,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778298854828</v>
+        <v>1.07778286933899</v>
       </c>
       <c r="H1308" t="n">
         <v>656005</v>
@@ -38388,7 +38388,7 @@
         <v>1.41400003433228</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.0228089094162</v>
+        <v>1.02280879020691</v>
       </c>
       <c r="H1311" t="n">
         <v>213190</v>
@@ -38475,7 +38475,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768474578857</v>
+        <v>0.996768295764923</v>
       </c>
       <c r="H1314" t="n">
         <v>379948</v>
@@ -38504,7 +38504,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748257160187</v>
       </c>
       <c r="H1315" t="n">
         <v>436542</v>
@@ -38591,7 +38591,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884922504425</v>
+        <v>1.04884910583496</v>
       </c>
       <c r="H1318" t="n">
         <v>602483</v>
@@ -38620,7 +38620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.04161584377289</v>
+        <v>1.0416157245636</v>
       </c>
       <c r="H1319" t="n">
         <v>236404</v>
@@ -38707,7 +38707,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.08935642242432</v>
+        <v>1.08935654163361</v>
       </c>
       <c r="H1322" t="n">
         <v>506082</v>
@@ -38736,7 +38736,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.0734429359436</v>
+        <v>1.07344281673431</v>
       </c>
       <c r="H1323" t="n">
         <v>261172</v>
@@ -38765,7 +38765,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1324" t="n">
         <v>701728</v>
@@ -38794,7 +38794,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.21955847740173</v>
+        <v>1.21955835819244</v>
       </c>
       <c r="H1325" t="n">
         <v>3022164</v>
@@ -38823,7 +38823,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1326" t="n">
         <v>1612557</v>
@@ -39055,7 +39055,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.14433073997498</v>
+        <v>1.1443305015564</v>
       </c>
       <c r="H1334" t="n">
         <v>246192</v>
@@ -39113,7 +39113,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049788475037</v>
+        <v>1.18049776554108</v>
       </c>
       <c r="H1336" t="n">
         <v>648102</v>
@@ -39258,7 +39258,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.17181766033173</v>
+        <v>1.17181777954102</v>
       </c>
       <c r="H1341" t="n">
         <v>170083</v>
@@ -39345,7 +39345,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.18628454208374</v>
+        <v>1.18628442287445</v>
       </c>
       <c r="H1344" t="n">
         <v>178324</v>
@@ -39461,7 +39461,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.30201959609985</v>
+        <v>1.30201971530914</v>
       </c>
       <c r="H1348" t="n">
         <v>408190</v>
@@ -39490,7 +39490,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491316318512</v>
+        <v>1.30491292476654</v>
       </c>
       <c r="H1349" t="n">
         <v>305433</v>
@@ -39519,7 +39519,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.2745326757431</v>
+        <v>1.27453255653381</v>
       </c>
       <c r="H1350" t="n">
         <v>314905</v>
@@ -39548,7 +39548,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057299137115</v>
+        <v>1.30057287216187</v>
       </c>
       <c r="H1351" t="n">
         <v>318670</v>
@@ -39606,7 +39606,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.2918928861618</v>
+        <v>1.29189276695251</v>
       </c>
       <c r="H1353" t="n">
         <v>274547</v>
@@ -39635,7 +39635,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912614822388</v>
       </c>
       <c r="H1354" t="n">
         <v>744694</v>
@@ -39693,7 +39693,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912614822388</v>
       </c>
       <c r="H1356" t="n">
         <v>193651</v>
@@ -39751,7 +39751,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.33674013614655</v>
+        <v>1.33674025535583</v>
       </c>
       <c r="H1358" t="n">
         <v>368618</v>
@@ -39780,7 +39780,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1359" t="n">
         <v>1365631</v>
@@ -39809,7 +39809,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1360" t="n">
         <v>612054</v>
@@ -39896,7 +39896,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.47562217712402</v>
+        <v>1.47562229633331</v>
       </c>
       <c r="H1363" t="n">
         <v>690935</v>
@@ -39925,7 +39925,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.429328083992</v>
+        <v>1.42932820320129</v>
       </c>
       <c r="H1364" t="n">
         <v>2260128</v>
@@ -39954,7 +39954,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.40762794017792</v>
+        <v>1.40762782096863</v>
       </c>
       <c r="H1365" t="n">
         <v>1106457</v>
@@ -39983,7 +39983,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.39750099182129</v>
+        <v>1.39750111103058</v>
       </c>
       <c r="H1366" t="n">
         <v>375019</v>
@@ -40070,7 +40070,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1369" t="n">
         <v>249082</v>
@@ -40128,7 +40128,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1371" t="n">
         <v>196035</v>
@@ -40157,7 +40157,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.36376440525055</v>
+        <v>1.36376464366913</v>
       </c>
       <c r="H1372" t="n">
         <v>346170</v>
@@ -40215,7 +40215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.38149499893188</v>
+        <v>1.3814948797226</v>
       </c>
       <c r="H1374" t="n">
         <v>236076</v>
@@ -40244,7 +40244,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.38444995880127</v>
+        <v>1.38445007801056</v>
       </c>
       <c r="H1375" t="n">
         <v>300280</v>
@@ -40331,7 +40331,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1378" t="n">
         <v>217402</v>
@@ -40389,7 +40389,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.44502902030945</v>
+        <v>1.44502890110016</v>
       </c>
       <c r="H1380" t="n">
         <v>213603</v>
@@ -40418,7 +40418,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1381" t="n">
         <v>159305</v>
@@ -40476,7 +40476,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537161827087</v>
+        <v>1.45537173748016</v>
       </c>
       <c r="H1383" t="n">
         <v>131183</v>
@@ -40534,7 +40534,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1385" t="n">
         <v>278517</v>
@@ -40621,7 +40621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.36671960353851</v>
+        <v>1.36671948432922</v>
       </c>
       <c r="H1388" t="n">
         <v>291702</v>
@@ -40650,7 +40650,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.38444995880127</v>
+        <v>1.38445007801056</v>
       </c>
       <c r="H1389" t="n">
         <v>136346</v>
@@ -40737,7 +40737,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.33273637294769</v>
+        <v>1.3327362537384</v>
       </c>
       <c r="H1392" t="n">
         <v>230681</v>
@@ -40795,7 +40795,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.29432046413422</v>
+        <v>1.29432034492493</v>
       </c>
       <c r="H1394" t="n">
         <v>728450</v>
@@ -40824,7 +40824,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.26181471347809</v>
+        <v>1.2618145942688</v>
       </c>
       <c r="H1395" t="n">
         <v>555187</v>
@@ -40882,7 +40882,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.25294947624207</v>
+        <v>1.25294935703278</v>
       </c>
       <c r="H1397" t="n">
         <v>236575</v>
@@ -40911,7 +40911,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.2381739616394</v>
+        <v>1.23817408084869</v>
       </c>
       <c r="H1398" t="n">
         <v>288738</v>
@@ -40998,7 +40998,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.22192120552063</v>
+        <v>1.22192132472992</v>
       </c>
       <c r="H1401" t="n">
         <v>230579</v>
@@ -41143,7 +41143,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.21157848834991</v>
+        <v>1.21157836914062</v>
       </c>
       <c r="H1406" t="n">
         <v>146658</v>
@@ -41172,7 +41172,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.19384801387787</v>
+        <v>1.19384813308716</v>
       </c>
       <c r="H1407" t="n">
         <v>147880</v>
@@ -41201,7 +41201,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.18498289585114</v>
+        <v>1.18498277664185</v>
       </c>
       <c r="H1408" t="n">
         <v>330749</v>
@@ -41259,7 +41259,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.13622426986694</v>
+        <v>1.13622415065765</v>
       </c>
       <c r="H1410" t="n">
         <v>139750</v>
@@ -41317,7 +41317,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.16134238243103</v>
+        <v>1.16134226322174</v>
       </c>
       <c r="H1412" t="n">
         <v>106478</v>
@@ -41433,7 +41433,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.12588143348694</v>
+        <v>1.12588155269623</v>
       </c>
       <c r="H1416" t="n">
         <v>229887</v>
@@ -41462,7 +41462,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.12588143348694</v>
+        <v>1.12588155269623</v>
       </c>
       <c r="H1417" t="n">
         <v>205128</v>
@@ -41491,7 +41491,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.13622426986694</v>
+        <v>1.13622415065765</v>
       </c>
       <c r="H1418" t="n">
         <v>323570</v>
@@ -41549,7 +41549,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H1420" t="n">
         <v>399404</v>
@@ -41723,7 +41723,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.27806758880615</v>
+        <v>1.27806746959686</v>
       </c>
       <c r="H1426" t="n">
         <v>138463</v>
@@ -41868,7 +41868,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.26181471347809</v>
+        <v>1.2618145942688</v>
       </c>
       <c r="H1431" t="n">
         <v>118584</v>
@@ -41926,7 +41926,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.26772463321686</v>
+        <v>1.26772475242615</v>
       </c>
       <c r="H1433" t="n">
         <v>186872</v>
@@ -41984,7 +41984,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.32830369472504</v>
+        <v>1.32830357551575</v>
       </c>
       <c r="H1435" t="n">
         <v>261431</v>
@@ -42013,7 +42013,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614078044891</v>
+        <v>1.30614066123962</v>
       </c>
       <c r="H1436" t="n">
         <v>371377</v>
@@ -42187,7 +42187,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1442" t="n">
         <v>230453</v>
@@ -42216,7 +42216,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.36671960353851</v>
+        <v>1.36671948432922</v>
       </c>
       <c r="H1443" t="n">
         <v>203945</v>
@@ -42332,7 +42332,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.32830369472504</v>
+        <v>1.32830357551575</v>
       </c>
       <c r="H1447" t="n">
         <v>140764</v>
@@ -42419,7 +42419,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.35785448551178</v>
+        <v>1.35785436630249</v>
       </c>
       <c r="H1450" t="n">
         <v>148858</v>
@@ -42506,7 +42506,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.24556183815002</v>
+        <v>1.24556171894073</v>
       </c>
       <c r="H1453" t="n">
         <v>671330</v>
@@ -42564,7 +42564,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.24112915992737</v>
+        <v>1.24112904071808</v>
       </c>
       <c r="H1455" t="n">
         <v>333161</v>
@@ -42709,7 +42709,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.25885951519012</v>
+        <v>1.25885963439941</v>
       </c>
       <c r="H1460" t="n">
         <v>250808</v>
@@ -42941,7 +42941,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.27806758880615</v>
+        <v>1.27806746959686</v>
       </c>
       <c r="H1468" t="n">
         <v>132333</v>
@@ -43057,7 +43057,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.41400074958801</v>
+        <v>1.4140008687973</v>
       </c>
       <c r="H1472" t="n">
         <v>435343</v>
@@ -43086,7 +43086,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1473" t="n">
         <v>224203</v>
@@ -43173,7 +43173,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.38444995880127</v>
+        <v>1.38445007801056</v>
       </c>
       <c r="H1476" t="n">
         <v>264903</v>
@@ -43202,7 +43202,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.40513551235199</v>
+        <v>1.40513563156128</v>
       </c>
       <c r="H1477" t="n">
         <v>185218</v>
@@ -43347,7 +43347,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1482" t="n">
         <v>129778</v>
@@ -43376,7 +43376,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1483" t="n">
         <v>191991</v>
@@ -43434,7 +43434,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.37558484077454</v>
+        <v>1.37558495998383</v>
       </c>
       <c r="H1485" t="n">
         <v>148734</v>
@@ -43492,7 +43492,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.3785400390625</v>
+        <v>1.37853991985321</v>
       </c>
       <c r="H1487" t="n">
         <v>393472</v>
@@ -43695,7 +43695,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.58096218109131</v>
+        <v>1.5809623003006</v>
       </c>
       <c r="H1494" t="n">
         <v>291825</v>
@@ -43753,7 +43753,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.53663611412048</v>
+        <v>1.53663599491119</v>
       </c>
       <c r="H1496" t="n">
         <v>505426</v>
@@ -43898,7 +43898,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.44502902030945</v>
+        <v>1.44502890110016</v>
       </c>
       <c r="H1501" t="n">
         <v>177494</v>
@@ -43956,7 +43956,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1503" t="n">
         <v>551023</v>
@@ -43985,7 +43985,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1504" t="n">
         <v>165387</v>
@@ -44043,7 +44043,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36376440525055</v>
+        <v>1.36376464366913</v>
       </c>
       <c r="H1506" t="n">
         <v>133446</v>
@@ -44072,7 +44072,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.35046684741974</v>
+        <v>1.35046672821045</v>
       </c>
       <c r="H1507" t="n">
         <v>204317</v>
@@ -44159,7 +44159,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.3445565700531</v>
+        <v>1.34455668926239</v>
       </c>
       <c r="H1510" t="n">
         <v>116822</v>
@@ -44275,7 +44275,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.32830369472504</v>
+        <v>1.32830357551575</v>
       </c>
       <c r="H1514" t="n">
         <v>106604</v>
@@ -44362,7 +44362,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.3445565700531</v>
+        <v>1.34455668926239</v>
       </c>
       <c r="H1517" t="n">
         <v>89004</v>
@@ -44449,7 +44449,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.38444995880127</v>
+        <v>1.38445007801056</v>
       </c>
       <c r="H1520" t="n">
         <v>141490</v>
@@ -44594,7 +44594,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.51816689968109</v>
+        <v>1.51816701889038</v>
       </c>
       <c r="H1525" t="n">
         <v>301193</v>
@@ -44855,7 +44855,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.51816689968109</v>
+        <v>1.51816701889038</v>
       </c>
       <c r="H1534" t="n">
         <v>108707</v>
@@ -45116,7 +45116,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1543" t="n">
         <v>303306</v>
@@ -45174,7 +45174,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.40513551235199</v>
+        <v>1.40513563156128</v>
       </c>
       <c r="H1545" t="n">
         <v>140913</v>
@@ -45261,7 +45261,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.41400074958801</v>
+        <v>1.4140008687973</v>
       </c>
       <c r="H1548" t="n">
         <v>110404</v>
@@ -45377,7 +45377,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.36819708347321</v>
+        <v>1.3681972026825</v>
       </c>
       <c r="H1552" t="n">
         <v>137743</v>
@@ -45435,7 +45435,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.41252303123474</v>
+        <v>1.41252315044403</v>
       </c>
       <c r="H1554" t="n">
         <v>115911</v>
@@ -45551,7 +45551,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.42286598682404</v>
+        <v>1.42286586761475</v>
       </c>
       <c r="H1558" t="n">
         <v>168182</v>
@@ -45638,7 +45638,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37558484077454</v>
+        <v>1.37558495998383</v>
       </c>
       <c r="H1561" t="n">
         <v>147702</v>
@@ -45812,7 +45812,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.24112915992737</v>
+        <v>1.24112904071808</v>
       </c>
       <c r="H1567" t="n">
         <v>290390</v>
@@ -45899,7 +45899,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862340927124</v>
+        <v>1.20862352848053</v>
       </c>
       <c r="H1570" t="n">
         <v>195940</v>
@@ -45928,7 +45928,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.142134308815</v>
+        <v>1.14213442802429</v>
       </c>
       <c r="H1571" t="n">
         <v>312535</v>
@@ -45986,7 +45986,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.21157848834991</v>
+        <v>1.21157836914062</v>
       </c>
       <c r="H1573" t="n">
         <v>417935</v>
@@ -46015,7 +46015,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.24556183815002</v>
+        <v>1.24556171894073</v>
       </c>
       <c r="H1574" t="n">
         <v>232917</v>
@@ -46276,7 +46276,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.33864641189575</v>
+        <v>1.33864653110504</v>
       </c>
       <c r="H1583" t="n">
         <v>145426</v>
@@ -46363,7 +46363,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.48492228984833</v>
+        <v>1.48492240905762</v>
       </c>
       <c r="H1586" t="n">
         <v>1535158</v>
@@ -46479,7 +46479,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.65853273868561</v>
+        <v>1.65853261947632</v>
       </c>
       <c r="H1590" t="n">
         <v>853412</v>
@@ -46508,7 +46508,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.63636958599091</v>
+        <v>1.63636946678162</v>
       </c>
       <c r="H1591" t="n">
         <v>519821</v>
@@ -46595,7 +46595,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.62159430980682</v>
+        <v>1.62159419059753</v>
       </c>
       <c r="H1594" t="n">
         <v>308615</v>
@@ -46624,7 +46624,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.62159430980682</v>
+        <v>1.62159419059753</v>
       </c>
       <c r="H1595" t="n">
         <v>268063</v>
@@ -46682,7 +46682,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.68438959121704</v>
+        <v>1.68438947200775</v>
       </c>
       <c r="H1597" t="n">
         <v>455707</v>
@@ -46711,7 +46711,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.70285880565643</v>
+        <v>1.70285868644714</v>
       </c>
       <c r="H1598" t="n">
         <v>516825</v>
@@ -46740,7 +46740,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.70285880565643</v>
+        <v>1.70285868644714</v>
       </c>
       <c r="H1599" t="n">
         <v>358721</v>
@@ -46798,7 +46798,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.70285880565643</v>
+        <v>1.70285868644714</v>
       </c>
       <c r="H1601" t="n">
         <v>293308</v>
@@ -46827,7 +46827,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.72132802009583</v>
+        <v>1.72132778167725</v>
       </c>
       <c r="H1602" t="n">
         <v>313832</v>
@@ -46856,7 +46856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.70655274391174</v>
+        <v>1.70655250549316</v>
       </c>
       <c r="H1603" t="n">
         <v>292128</v>
@@ -46885,7 +46885,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.70655274391174</v>
+        <v>1.70655250549316</v>
       </c>
       <c r="H1604" t="n">
         <v>457156</v>
@@ -46914,7 +46914,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.71024656295776</v>
+        <v>1.71024632453918</v>
       </c>
       <c r="H1605" t="n">
         <v>285312</v>
@@ -46943,7 +46943,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.70285880565643</v>
+        <v>1.70285868644714</v>
       </c>
       <c r="H1606" t="n">
         <v>652953</v>
@@ -46972,7 +46972,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.69547116756439</v>
+        <v>1.69547092914581</v>
       </c>
       <c r="H1607" t="n">
         <v>254784</v>
@@ -47059,7 +47059,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64375746250153</v>
+        <v>1.64375722408295</v>
       </c>
       <c r="H1610" t="n">
         <v>91769</v>
@@ -47088,7 +47088,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.66222667694092</v>
+        <v>1.66222655773163</v>
       </c>
       <c r="H1611" t="n">
         <v>68045</v>
@@ -47117,7 +47117,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.64375746250153</v>
+        <v>1.64375722408295</v>
       </c>
       <c r="H1612" t="n">
         <v>180712</v>
@@ -47146,7 +47146,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.63636958599091</v>
+        <v>1.63636946678162</v>
       </c>
       <c r="H1613" t="n">
         <v>180456</v>
@@ -47175,7 +47175,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.60681891441345</v>
+        <v>1.60681879520416</v>
       </c>
       <c r="H1614" t="n">
         <v>227809</v>
@@ -47204,7 +47204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924835681915</v>
+        <v>1.52924847602844</v>
       </c>
       <c r="H1615" t="n">
         <v>245261</v>
@@ -47291,7 +47291,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420667171478</v>
+        <v>1.61420655250549</v>
       </c>
       <c r="H1618" t="n">
         <v>173191</v>
@@ -47320,7 +47320,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.63267600536346</v>
+        <v>1.63267588615417</v>
       </c>
       <c r="H1619" t="n">
         <v>160173</v>
@@ -47407,7 +47407,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.67700183391571</v>
+        <v>1.677001953125</v>
       </c>
       <c r="H1622" t="n">
         <v>296489</v>
@@ -47958,7 +47958,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1641" t="n">
         <v>199201</v>
@@ -48016,7 +48016,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1643" t="n">
         <v>247724</v>
@@ -48190,7 +48190,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1649" t="n">
         <v>141025</v>
@@ -48248,7 +48248,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1651" t="n">
         <v>56456</v>
@@ -48277,7 +48277,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609028816223</v>
+        <v>1.37609040737152</v>
       </c>
       <c r="H1652" t="n">
         <v>83408</v>
@@ -48335,7 +48335,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.37769603729248</v>
+        <v>1.37769615650177</v>
       </c>
       <c r="H1654" t="n">
         <v>136685</v>
@@ -48364,7 +48364,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1655" t="n">
         <v>31246</v>
@@ -48451,7 +48451,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1658" t="n">
         <v>87013</v>
@@ -48509,7 +48509,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1660" t="n">
         <v>103532</v>
@@ -48567,7 +48567,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.27653658390045</v>
+        <v>1.27653670310974</v>
       </c>
       <c r="H1662" t="n">
         <v>62267</v>
@@ -48683,7 +48683,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688399791718</v>
+        <v>1.48688411712646</v>
       </c>
       <c r="H1666" t="n">
         <v>370783</v>
@@ -48886,7 +48886,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1673" t="n">
         <v>316953</v>
@@ -48944,7 +48944,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082710266113</v>
+        <v>1.47082698345184</v>
       </c>
       <c r="H1675" t="n">
         <v>352968</v>
@@ -49089,7 +49089,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820443630219</v>
+        <v>1.40820455551147</v>
       </c>
       <c r="H1680" t="n">
         <v>95443</v>
@@ -49147,7 +49147,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1682" t="n">
         <v>66535</v>
@@ -49176,7 +49176,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1683" t="n">
         <v>260032</v>
@@ -49234,7 +49234,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1685" t="n">
         <v>224610</v>
@@ -49263,7 +49263,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1686" t="n">
         <v>210620</v>
@@ -49408,7 +49408,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558188915253</v>
+        <v>1.34558200836182</v>
       </c>
       <c r="H1691" t="n">
         <v>192296</v>
@@ -49524,7 +49524,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1695" t="n">
         <v>180799</v>
@@ -49582,7 +49582,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1697" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1697" t="n">
         <v>151485</v>
@@ -49872,7 +49872,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1707" t="n">
         <v>328393</v>
@@ -50075,7 +50075,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.15129148960114</v>
+        <v>1.15129160881042</v>
       </c>
       <c r="H1714" t="n">
         <v>239109</v>
@@ -50365,7 +50365,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1724" t="n">
         <v>195897</v>
@@ -50394,7 +50394,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267403125763</v>
+        <v>1.20267415046692</v>
       </c>
       <c r="H1725" t="n">
         <v>200716</v>
@@ -50481,7 +50481,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1728" t="n">
         <v>106830</v>
@@ -50510,7 +50510,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1729" t="n">
         <v>337931</v>
@@ -50539,7 +50539,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1730" t="n">
         <v>107088</v>
@@ -50597,7 +50597,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741072654724</v>
+        <v>1.29741084575653</v>
       </c>
       <c r="H1732" t="n">
         <v>220981</v>
@@ -50626,7 +50626,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1733" t="n">
         <v>162741</v>
@@ -50655,7 +50655,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1734" t="n">
         <v>122962</v>
@@ -50684,7 +50684,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.33273613452911</v>
+        <v>1.3327362537384</v>
       </c>
       <c r="H1735" t="n">
         <v>209163</v>
@@ -50829,7 +50829,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383348464966</v>
+        <v>1.30383360385895</v>
       </c>
       <c r="H1740" t="n">
         <v>63847</v>
@@ -50858,7 +50858,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1741" t="n">
         <v>362136</v>
@@ -50887,7 +50887,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1742" t="n">
         <v>126434</v>
@@ -51235,7 +51235,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1754" t="n">
         <v>268250</v>
@@ -51496,7 +51496,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1763" t="n">
         <v>180397</v>
@@ -51641,7 +51641,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1768" t="n">
         <v>44622</v>
@@ -51670,7 +51670,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1769" t="n">
         <v>310689</v>
@@ -51728,7 +51728,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1771" t="n">
         <v>224093</v>
@@ -51815,7 +51815,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1774" t="n">
         <v>131817</v>
@@ -51844,7 +51844,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1775" t="n">
         <v>99387</v>
@@ -51902,7 +51902,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1777" t="n">
         <v>83493</v>
@@ -51931,7 +51931,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.19303977489471</v>
+        <v>1.193039894104</v>
       </c>
       <c r="H1778" t="n">
         <v>95141</v>
@@ -51960,7 +51960,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.18661713600159</v>
+        <v>1.1866170167923</v>
       </c>
       <c r="H1779" t="n">
         <v>103412</v>
@@ -51989,7 +51989,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1780" t="n">
         <v>171787</v>
@@ -52163,7 +52163,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1786" t="n">
         <v>102156</v>
@@ -52279,7 +52279,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.22836530208588</v>
+        <v>1.22836542129517</v>
       </c>
       <c r="H1790" t="n">
         <v>295350</v>
@@ -53236,7 +53236,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1823" t="n">
         <v>229481</v>
@@ -53381,7 +53381,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1828" t="n">
         <v>60503</v>
@@ -53497,7 +53497,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1832" t="n">
         <v>160687</v>
@@ -53526,7 +53526,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1833" t="n">
         <v>313479</v>
@@ -53584,7 +53584,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1835" t="n">
         <v>126203</v>
@@ -53613,7 +53613,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1836" t="n">
         <v>104258</v>
@@ -53642,7 +53642,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1837" t="n">
         <v>137726</v>
@@ -53671,7 +53671,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828498840332</v>
+        <v>1.31828486919403</v>
       </c>
       <c r="H1838" t="n">
         <v>268207</v>
@@ -53729,7 +53729,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.39214742183685</v>
+        <v>1.39214730262756</v>
       </c>
       <c r="H1840" t="n">
         <v>380640</v>
@@ -53903,7 +53903,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206686973572</v>
+        <v>1.48206698894501</v>
       </c>
       <c r="H1846" t="n">
         <v>230147</v>
@@ -54193,7 +54193,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1856" t="n">
         <v>136076</v>
@@ -54280,7 +54280,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.4788556098938</v>
+        <v>1.47885572910309</v>
       </c>
       <c r="H1859" t="n">
         <v>185027</v>
@@ -54309,7 +54309,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.50294125080109</v>
+        <v>1.5029411315918</v>
       </c>
       <c r="H1860" t="n">
         <v>288447</v>
@@ -54831,7 +54831,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.45958697795868</v>
+        <v>1.45958709716797</v>
       </c>
       <c r="H1878" t="n">
         <v>118811</v>
@@ -54918,7 +54918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1881" t="n">
         <v>411337</v>
@@ -80067,6 +80067,35 @@
         <v>128921</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>65735</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8573009967804</v>
+        <v>2.85730123519897</v>
       </c>
       <c r="H2" t="n">
         <v>30003</v>
@@ -456,7 +456,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86872553825378</v>
+        <v>2.86872529983521</v>
       </c>
       <c r="H3" t="n">
         <v>20338</v>
@@ -485,7 +485,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525827407837</v>
+        <v>2.80525803565979</v>
       </c>
       <c r="H4" t="n">
         <v>23828</v>
@@ -514,7 +514,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76717758178711</v>
+        <v>2.76717829704285</v>
       </c>
       <c r="H5" t="n">
         <v>103885</v>
@@ -543,7 +543,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7709858417511</v>
+        <v>2.77098608016968</v>
       </c>
       <c r="H6" t="n">
         <v>24790</v>
@@ -572,7 +572,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67832279205322</v>
+        <v>2.6783230304718</v>
       </c>
       <c r="H7" t="n">
         <v>64928</v>
@@ -630,7 +630,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G9" t="n">
-        <v>2.67832279205322</v>
+        <v>2.6783230304718</v>
       </c>
       <c r="H9" t="n">
         <v>36066</v>
@@ -659,7 +659,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H10" t="n">
         <v>108431</v>
@@ -688,7 +688,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65928292274475</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H11" t="n">
         <v>96501</v>
@@ -746,7 +746,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54631114006042</v>
+        <v>2.546311378479</v>
       </c>
       <c r="H13" t="n">
         <v>34257</v>
@@ -775,7 +775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5006148815155</v>
+        <v>2.50061464309692</v>
       </c>
       <c r="H14" t="n">
         <v>75440</v>
@@ -804,7 +804,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H15" t="n">
         <v>65925</v>
@@ -862,7 +862,7 @@
         <v>4.0479998588562</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56915926933289</v>
+        <v>2.56915950775146</v>
       </c>
       <c r="H17" t="n">
         <v>32766</v>
@@ -891,7 +891,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138826370239</v>
+        <v>2.55138874053955</v>
       </c>
       <c r="H18" t="n">
         <v>16747</v>
@@ -920,7 +920,7 @@
         <v>4.03800010681152</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56281304359436</v>
+        <v>2.56281328201294</v>
       </c>
       <c r="H19" t="n">
         <v>19201</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.53869533538818</v>
+        <v>2.5386950969696</v>
       </c>
       <c r="H21" t="n">
         <v>27727</v>
@@ -1094,7 +1094,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107905387878</v>
+        <v>2.53107857704163</v>
       </c>
       <c r="H25" t="n">
         <v>32107</v>
@@ -1123,7 +1123,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H26" t="n">
         <v>40968</v>
@@ -1210,7 +1210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482532501221</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H29" t="n">
         <v>103231</v>
@@ -1239,7 +1239,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.13885068893433</v>
+        <v>2.13885045051575</v>
       </c>
       <c r="H30" t="n">
         <v>81897</v>
@@ -1326,7 +1326,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798361778259</v>
+        <v>2.32798337936401</v>
       </c>
       <c r="H33" t="n">
         <v>39970</v>
@@ -1355,7 +1355,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.48665189743042</v>
+        <v>2.48665165901184</v>
       </c>
       <c r="H34" t="n">
         <v>72475</v>
@@ -1384,7 +1384,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6186637878418</v>
+        <v>2.61866402626038</v>
       </c>
       <c r="H35" t="n">
         <v>117716</v>
@@ -1413,7 +1413,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.55519676208496</v>
+        <v>2.55519604682922</v>
       </c>
       <c r="H36" t="n">
         <v>17078</v>
@@ -1442,7 +1442,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G37" t="n">
-        <v>2.65928292274475</v>
+        <v>2.65928316116333</v>
       </c>
       <c r="H37" t="n">
         <v>45626</v>
@@ -1529,7 +1529,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600193023682</v>
+        <v>2.52600169181824</v>
       </c>
       <c r="H40" t="n">
         <v>22658</v>
@@ -1558,7 +1558,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H41" t="n">
         <v>29241</v>
@@ -1587,7 +1587,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G42" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H42" t="n">
         <v>49765</v>
@@ -1616,7 +1616,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>2.67832279205322</v>
+        <v>2.6783230304718</v>
       </c>
       <c r="H43" t="n">
         <v>55902</v>
@@ -1703,7 +1703,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658975601196</v>
+        <v>2.64658999443054</v>
       </c>
       <c r="H46" t="n">
         <v>17636</v>
@@ -1790,7 +1790,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.69355535507202</v>
+        <v>2.6935555934906</v>
       </c>
       <c r="H49" t="n">
         <v>25946</v>
@@ -1819,7 +1819,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G50" t="n">
-        <v>2.65039777755737</v>
+        <v>2.65039801597595</v>
       </c>
       <c r="H50" t="n">
         <v>43154</v>
@@ -1848,7 +1848,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G51" t="n">
-        <v>2.7392520904541</v>
+        <v>2.73925185203552</v>
       </c>
       <c r="H51" t="n">
         <v>198987</v>
@@ -1877,7 +1877,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G52" t="n">
-        <v>2.76717758178711</v>
+        <v>2.76717829704285</v>
       </c>
       <c r="H52" t="n">
         <v>124017</v>
@@ -1906,7 +1906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.74179077148438</v>
+        <v>2.7417905330658</v>
       </c>
       <c r="H53" t="n">
         <v>42603</v>
@@ -1935,7 +1935,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84333872795105</v>
+        <v>2.84333848953247</v>
       </c>
       <c r="H54" t="n">
         <v>63652</v>
@@ -2022,7 +2022,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95757937431335</v>
+        <v>2.95757961273193</v>
       </c>
       <c r="H57" t="n">
         <v>81691</v>
@@ -2051,7 +2051,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169732093811</v>
+        <v>2.98169755935669</v>
       </c>
       <c r="H58" t="n">
         <v>45732</v>
@@ -2138,7 +2138,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835347175598</v>
+        <v>3.00835371017456</v>
       </c>
       <c r="H61" t="n">
         <v>91726</v>
@@ -2167,7 +2167,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104735374451</v>
+        <v>3.02104711532593</v>
       </c>
       <c r="H62" t="n">
         <v>71653</v>
@@ -2196,7 +2196,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423600196838</v>
+        <v>2.98423624038696</v>
       </c>
       <c r="H63" t="n">
         <v>32830</v>
@@ -2225,7 +2225,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566006660461</v>
+        <v>2.99566030502319</v>
       </c>
       <c r="H64" t="n">
         <v>46851</v>
@@ -2283,7 +2283,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200700759888</v>
+        <v>3.00200748443604</v>
       </c>
       <c r="H66" t="n">
         <v>39511</v>
@@ -2312,7 +2312,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.91949915885925</v>
+        <v>2.91949939727783</v>
       </c>
       <c r="H67" t="n">
         <v>33763</v>
@@ -2341,7 +2341,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711591720581</v>
+        <v>2.92711544036865</v>
       </c>
       <c r="H68" t="n">
         <v>58634</v>
@@ -2370,7 +2370,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819922447205</v>
+        <v>2.99819874763489</v>
       </c>
       <c r="H69" t="n">
         <v>75222</v>
@@ -2399,7 +2399,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G70" t="n">
-        <v>3.06039690971375</v>
+        <v>3.0603973865509</v>
       </c>
       <c r="H70" t="n">
         <v>458291</v>
@@ -2428,7 +2428,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>2.98931360244751</v>
+        <v>2.98931336402893</v>
       </c>
       <c r="H71" t="n">
         <v>92895</v>
@@ -2457,7 +2457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182145118713</v>
+        <v>3.07182097434998</v>
       </c>
       <c r="H72" t="n">
         <v>136484</v>
@@ -2515,7 +2515,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H74" t="n">
         <v>109632</v>
@@ -2573,7 +2573,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702222824097</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H76" t="n">
         <v>114194</v>
@@ -2602,7 +2602,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702222824097</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H77" t="n">
         <v>122410</v>
@@ -2631,7 +2631,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H78" t="n">
         <v>61569</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H79" t="n">
         <v>45242</v>
@@ -2689,7 +2689,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798212051392</v>
+        <v>3.14798188209534</v>
       </c>
       <c r="H80" t="n">
         <v>29895</v>
@@ -2718,7 +2718,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.09847712516785</v>
+        <v>3.098477602005</v>
       </c>
       <c r="H81" t="n">
         <v>94591</v>
@@ -2747,7 +2747,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244034767151</v>
+        <v>3.11244058609009</v>
       </c>
       <c r="H82" t="n">
         <v>32834</v>
@@ -2776,7 +2776,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086155891418</v>
+        <v>3.09086108207703</v>
       </c>
       <c r="H83" t="n">
         <v>44802</v>
@@ -2805,7 +2805,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959221839905</v>
+        <v>3.08959197998047</v>
       </c>
       <c r="H84" t="n">
         <v>34327</v>
@@ -2834,7 +2834,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547403335571</v>
+        <v>3.06547427177429</v>
       </c>
       <c r="H85" t="n">
         <v>37849</v>
@@ -2863,7 +2863,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374075889587</v>
+        <v>3.03374099731445</v>
       </c>
       <c r="H86" t="n">
         <v>46370</v>
@@ -2979,7 +2979,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053951263428</v>
+        <v>3.03053998947144</v>
       </c>
       <c r="H90" t="n">
         <v>50752</v>
@@ -3037,7 +3037,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>2.93384861946106</v>
+        <v>2.93384838104248</v>
       </c>
       <c r="H92" t="n">
         <v>77806</v>
@@ -3066,7 +3066,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398096084595</v>
       </c>
       <c r="H93" t="n">
         <v>86004</v>
@@ -3095,7 +3095,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974327087402</v>
+        <v>2.94974303245544</v>
       </c>
       <c r="H94" t="n">
         <v>22389</v>
@@ -3124,7 +3124,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424492835999</v>
+        <v>2.87424468994141</v>
       </c>
       <c r="H95" t="n">
         <v>67830</v>
@@ -3153,7 +3153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398096084595</v>
       </c>
       <c r="H96" t="n">
         <v>54946</v>
@@ -3182,7 +3182,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92722606658936</v>
+        <v>2.92722582817078</v>
       </c>
       <c r="H97" t="n">
         <v>13594</v>
@@ -3211,7 +3211,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G98" t="n">
-        <v>3.0888192653656</v>
+        <v>3.08881974220276</v>
       </c>
       <c r="H98" t="n">
         <v>155937</v>
@@ -3269,7 +3269,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941601753235</v>
+        <v>3.09941554069519</v>
       </c>
       <c r="H100" t="n">
         <v>95435</v>
@@ -3327,7 +3327,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577460289001</v>
+        <v>3.14577436447144</v>
       </c>
       <c r="H102" t="n">
         <v>86451</v>
@@ -3356,7 +3356,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140552520752</v>
+        <v>3.20140504837036</v>
       </c>
       <c r="H103" t="n">
         <v>92445</v>
@@ -3443,7 +3443,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584318161011</v>
+        <v>3.23584270477295</v>
       </c>
       <c r="H106" t="n">
         <v>124255</v>
@@ -3472,7 +3472,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.23186922073364</v>
+        <v>3.2318696975708</v>
       </c>
       <c r="H107" t="n">
         <v>38634</v>
@@ -3501,7 +3501,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610738754272</v>
+        <v>3.1961076259613</v>
       </c>
       <c r="H108" t="n">
         <v>19558</v>
@@ -3559,7 +3559,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829133033752</v>
+        <v>3.16829180717468</v>
       </c>
       <c r="H110" t="n">
         <v>37625</v>
@@ -3588,7 +3588,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.15901947021484</v>
+        <v>3.159019947052</v>
       </c>
       <c r="H111" t="n">
         <v>31915</v>
@@ -3617,7 +3617,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133646965027</v>
+        <v>3.11133694648743</v>
       </c>
       <c r="H112" t="n">
         <v>10926</v>
@@ -3646,7 +3646,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G113" t="n">
-        <v>3.0888192653656</v>
+        <v>3.08881974220276</v>
       </c>
       <c r="H113" t="n">
         <v>13735</v>
@@ -3733,7 +3733,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516845703125</v>
+        <v>2.73516821861267</v>
       </c>
       <c r="H116" t="n">
         <v>77740</v>
@@ -3791,7 +3791,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69278264045715</v>
+        <v>2.69278311729431</v>
       </c>
       <c r="H118" t="n">
         <v>84374</v>
@@ -3878,7 +3878,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91133117675781</v>
+        <v>2.91133141517639</v>
       </c>
       <c r="H121" t="n">
         <v>23520</v>
@@ -3907,7 +3907,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398072242737</v>
+        <v>2.91398096084595</v>
       </c>
       <c r="H122" t="n">
         <v>31647</v>
@@ -3936,7 +3936,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060279846191</v>
+        <v>2.92060327529907</v>
       </c>
       <c r="H123" t="n">
         <v>44363</v>
@@ -3965,7 +3965,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596493721008</v>
+        <v>2.81596446037292</v>
       </c>
       <c r="H124" t="n">
         <v>67252</v>
@@ -3994,7 +3994,7 @@
         <v>4</v>
       </c>
       <c r="G125" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H125" t="n">
         <v>48500</v>
@@ -4023,7 +4023,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841356277466</v>
+        <v>2.74841380119324</v>
       </c>
       <c r="H126" t="n">
         <v>44702</v>
@@ -4052,7 +4052,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907865524292</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H127" t="n">
         <v>171545</v>
@@ -4139,7 +4139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047141075134</v>
+        <v>2.94047117233276</v>
       </c>
       <c r="H130" t="n">
         <v>49672</v>
@@ -4197,7 +4197,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708890914917</v>
+        <v>2.74708867073059</v>
       </c>
       <c r="H132" t="n">
         <v>64127</v>
@@ -4226,7 +4226,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152656555176</v>
+        <v>2.78152680397034</v>
       </c>
       <c r="H133" t="n">
         <v>40862</v>
@@ -4255,7 +4255,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G134" t="n">
-        <v>2.90073537826538</v>
+        <v>2.9007351398468</v>
       </c>
       <c r="H134" t="n">
         <v>104347</v>
@@ -4284,7 +4284,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H135" t="n">
         <v>222212</v>
@@ -4371,7 +4371,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>2.95371699333191</v>
+        <v>2.95371651649475</v>
       </c>
       <c r="H138" t="n">
         <v>257080</v>
@@ -4400,7 +4400,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.91530513763428</v>
+        <v>2.9153048992157</v>
       </c>
       <c r="H139" t="n">
         <v>337397</v>
@@ -4429,7 +4429,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G140" t="n">
-        <v>2.74179077148438</v>
+        <v>2.7417905330658</v>
       </c>
       <c r="H140" t="n">
         <v>939291</v>
@@ -4458,7 +4458,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="n">
-        <v>2.63715243339539</v>
+        <v>2.63715267181396</v>
       </c>
       <c r="H141" t="n">
         <v>384878</v>
@@ -4487,7 +4487,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397542953491</v>
+        <v>2.71397566795349</v>
       </c>
       <c r="H142" t="n">
         <v>293231</v>
@@ -4545,7 +4545,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="n">
-        <v>2.69940590858459</v>
+        <v>2.69940567016602</v>
       </c>
       <c r="H144" t="n">
         <v>154876</v>
@@ -4574,7 +4574,7 @@
         <v>4</v>
       </c>
       <c r="G145" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H145" t="n">
         <v>151529</v>
@@ -4603,7 +4603,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112591743469</v>
+        <v>2.64112615585327</v>
       </c>
       <c r="H146" t="n">
         <v>91785</v>
@@ -4632,7 +4632,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="n">
-        <v>2.67291498184204</v>
+        <v>2.67291474342346</v>
       </c>
       <c r="H147" t="n">
         <v>156041</v>
@@ -4690,7 +4690,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112591743469</v>
+        <v>2.64112615585327</v>
       </c>
       <c r="H149" t="n">
         <v>58696</v>
@@ -4719,7 +4719,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60139012336731</v>
+        <v>2.60138988494873</v>
       </c>
       <c r="H150" t="n">
         <v>119099</v>
@@ -4777,7 +4777,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G152" t="n">
-        <v>2.58152174949646</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H152" t="n">
         <v>427637</v>
@@ -4864,7 +4864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245080947876</v>
+        <v>2.64245057106018</v>
       </c>
       <c r="H155" t="n">
         <v>131874</v>
@@ -4922,7 +4922,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.72192239761353</v>
+        <v>2.7219226360321</v>
       </c>
       <c r="H157" t="n">
         <v>1740457</v>
@@ -4951,7 +4951,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71529984474182</v>
       </c>
       <c r="H158" t="n">
         <v>518886</v>
@@ -4980,7 +4980,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G159" t="n">
-        <v>2.73384356498718</v>
+        <v>2.7338433265686</v>
       </c>
       <c r="H159" t="n">
         <v>133278</v>
@@ -5067,7 +5067,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702080726624</v>
+        <v>2.65702056884766</v>
       </c>
       <c r="H162" t="n">
         <v>133837</v>
@@ -5096,7 +5096,7 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H163" t="n">
         <v>149720</v>
@@ -5212,7 +5212,7 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H167" t="n">
         <v>122138</v>
@@ -5241,7 +5241,7 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H168" t="n">
         <v>78296</v>
@@ -5328,7 +5328,7 @@
         <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>2.64907312393188</v>
+        <v>2.64907336235046</v>
       </c>
       <c r="H171" t="n">
         <v>338607</v>
@@ -5386,7 +5386,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801243782043</v>
+        <v>2.60801291465759</v>
       </c>
       <c r="H173" t="n">
         <v>90282</v>
@@ -5415,7 +5415,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754826545715</v>
+        <v>2.57754850387573</v>
       </c>
       <c r="H174" t="n">
         <v>111504</v>
@@ -5444,7 +5444,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>2.56430268287659</v>
+        <v>2.56430292129517</v>
       </c>
       <c r="H175" t="n">
         <v>202259</v>
@@ -5473,7 +5473,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G176" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H176" t="n">
         <v>133924</v>
@@ -5502,7 +5502,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G177" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H177" t="n">
         <v>178815</v>
@@ -5531,7 +5531,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G178" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H178" t="n">
         <v>66133</v>
@@ -5560,7 +5560,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H179" t="n">
         <v>130197</v>
@@ -5618,7 +5618,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.41198134422302</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H181" t="n">
         <v>140968</v>
@@ -5705,7 +5705,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H184" t="n">
         <v>131854</v>
@@ -5734,7 +5734,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761202812195</v>
+        <v>2.46761178970337</v>
       </c>
       <c r="H185" t="n">
         <v>109363</v>
@@ -5792,7 +5792,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992855072021</v>
+        <v>2.41992831230164</v>
       </c>
       <c r="H187" t="n">
         <v>58946</v>
@@ -5821,7 +5821,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078831672668</v>
       </c>
       <c r="H188" t="n">
         <v>97323</v>
@@ -5850,7 +5850,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="n">
-        <v>2.27820324897766</v>
+        <v>2.2782027721405</v>
       </c>
       <c r="H189" t="n">
         <v>134521</v>
@@ -5879,7 +5879,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="n">
-        <v>2.27290487289429</v>
+        <v>2.27290463447571</v>
       </c>
       <c r="H190" t="n">
         <v>106587</v>
@@ -5908,7 +5908,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H191" t="n">
         <v>98350</v>
@@ -5937,7 +5937,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>2.27158045768738</v>
+        <v>2.2715802192688</v>
       </c>
       <c r="H192" t="n">
         <v>124936</v>
@@ -6053,7 +6053,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="n">
-        <v>2.43449831008911</v>
+        <v>2.43449854850769</v>
       </c>
       <c r="H196" t="n">
         <v>224328</v>
@@ -6082,7 +6082,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655110359192</v>
       </c>
       <c r="H197" t="n">
         <v>94547</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078831672668</v>
       </c>
       <c r="H199" t="n">
         <v>102816</v>
@@ -6169,7 +6169,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741134643555</v>
+        <v>2.39741110801697</v>
       </c>
       <c r="H200" t="n">
         <v>83817</v>
@@ -6198,7 +6198,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092089653015</v>
       </c>
       <c r="H201" t="n">
         <v>67052</v>
@@ -6256,7 +6256,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211297035217</v>
+        <v>2.39211320877075</v>
       </c>
       <c r="H203" t="n">
         <v>79415</v>
@@ -6285,7 +6285,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.4265513420105</v>
+        <v>2.42655110359192</v>
       </c>
       <c r="H204" t="n">
         <v>55166</v>
@@ -6314,7 +6314,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.45833992958069</v>
+        <v>2.45834016799927</v>
       </c>
       <c r="H205" t="n">
         <v>124627</v>
@@ -6343,7 +6343,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337433815002</v>
       </c>
       <c r="H206" t="n">
         <v>103757</v>
@@ -6372,7 +6372,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.45436644554138</v>
+        <v>2.45436668395996</v>
       </c>
       <c r="H207" t="n">
         <v>152563</v>
@@ -6401,7 +6401,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="n">
-        <v>2.45304203033447</v>
+        <v>2.45304179191589</v>
       </c>
       <c r="H208" t="n">
         <v>115572</v>
@@ -6517,7 +6517,7 @@
         <v>3.75</v>
       </c>
       <c r="G212" t="n">
-        <v>2.48350620269775</v>
+        <v>2.48350644111633</v>
       </c>
       <c r="H212" t="n">
         <v>273607</v>
@@ -6575,7 +6575,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>2.58284640312195</v>
+        <v>2.58284664154053</v>
       </c>
       <c r="H214" t="n">
         <v>119773</v>
@@ -6604,7 +6604,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G215" t="n">
-        <v>2.58152174949646</v>
+        <v>2.58152198791504</v>
       </c>
       <c r="H215" t="n">
         <v>116199</v>
@@ -6633,7 +6633,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>2.54443502426147</v>
+        <v>2.54443454742432</v>
       </c>
       <c r="H216" t="n">
         <v>93617</v>
@@ -6691,7 +6691,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="n">
-        <v>2.51264572143555</v>
+        <v>2.51264595985413</v>
       </c>
       <c r="H218" t="n">
         <v>53331</v>
@@ -6720,7 +6720,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324199676514</v>
       </c>
       <c r="H219" t="n">
         <v>63266</v>
@@ -6807,7 +6807,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G222" t="n">
-        <v>2.48085689544678</v>
+        <v>2.48085713386536</v>
       </c>
       <c r="H222" t="n">
         <v>144428</v>
@@ -6836,7 +6836,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="n">
-        <v>2.45171737670898</v>
+        <v>2.45171713829041</v>
       </c>
       <c r="H223" t="n">
         <v>48476</v>
@@ -6894,7 +6894,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416576385498</v>
+        <v>2.38416600227356</v>
       </c>
       <c r="H225" t="n">
         <v>57912</v>
@@ -7010,7 +7010,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24509000778198</v>
+        <v>2.24508953094482</v>
       </c>
       <c r="H229" t="n">
         <v>112233</v>
@@ -7039,7 +7039,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24509000778198</v>
+        <v>2.24508953094482</v>
       </c>
       <c r="H230" t="n">
         <v>154519</v>
@@ -7068,7 +7068,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H231" t="n">
         <v>105323</v>
@@ -7213,7 +7213,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H236" t="n">
         <v>166280</v>
@@ -7242,7 +7242,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482556343079</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H237" t="n">
         <v>48104</v>
@@ -7271,7 +7271,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548536300659</v>
+        <v>2.18548560142517</v>
       </c>
       <c r="H238" t="n">
         <v>189002</v>
@@ -7329,7 +7329,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237717628479</v>
+        <v>2.35237669944763</v>
       </c>
       <c r="H240" t="n">
         <v>374448</v>
@@ -7358,7 +7358,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092089653015</v>
       </c>
       <c r="H241" t="n">
         <v>218337</v>
@@ -7445,7 +7445,7 @@
         <v>3.64199995994568</v>
       </c>
       <c r="G244" t="n">
-        <v>2.41198134422302</v>
+        <v>2.41198110580444</v>
       </c>
       <c r="H244" t="n">
         <v>143146</v>
@@ -7503,7 +7503,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="n">
-        <v>2.44906830787659</v>
+        <v>2.44906806945801</v>
       </c>
       <c r="H246" t="n">
         <v>149566</v>
@@ -7532,7 +7532,7 @@
         <v>3.75</v>
       </c>
       <c r="G247" t="n">
-        <v>2.48350620269775</v>
+        <v>2.48350644111633</v>
       </c>
       <c r="H247" t="n">
         <v>122320</v>
@@ -7561,7 +7561,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H248" t="n">
         <v>101059</v>
@@ -7677,7 +7677,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G252" t="n">
-        <v>2.49145364761353</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H252" t="n">
         <v>110793</v>
@@ -7735,7 +7735,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G254" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204944610596</v>
       </c>
       <c r="H254" t="n">
         <v>103937</v>
@@ -7764,7 +7764,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734758377075</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H255" t="n">
         <v>71140</v>
@@ -7793,7 +7793,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H256" t="n">
         <v>116308</v>
@@ -7822,7 +7822,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324199676514</v>
       </c>
       <c r="H257" t="n">
         <v>138168</v>
@@ -7909,7 +7909,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734758377075</v>
+        <v>2.50734782218933</v>
       </c>
       <c r="H260" t="n">
         <v>231873</v>
@@ -7996,7 +7996,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="n">
-        <v>2.51264572143555</v>
+        <v>2.51264595985413</v>
       </c>
       <c r="H263" t="n">
         <v>153807</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675154685974</v>
+        <v>2.49675178527832</v>
       </c>
       <c r="H265" t="n">
         <v>182001</v>
@@ -8083,7 +8083,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G266" t="n">
-        <v>2.50204992294312</v>
+        <v>2.50204944610596</v>
       </c>
       <c r="H266" t="n">
         <v>156717</v>
@@ -8112,7 +8112,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337433815002</v>
       </c>
       <c r="H267" t="n">
         <v>244491</v>
@@ -8141,7 +8141,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.53648781776428</v>
+        <v>2.5364875793457</v>
       </c>
       <c r="H268" t="n">
         <v>422771</v>
@@ -8170,7 +8170,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960129737854</v>
+        <v>2.56960105895996</v>
       </c>
       <c r="H269" t="n">
         <v>280634</v>
@@ -8228,7 +8228,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165361404419</v>
+        <v>2.56165385246277</v>
       </c>
       <c r="H271" t="n">
         <v>288062</v>
@@ -8286,7 +8286,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059292793274</v>
+        <v>2.5205934047699</v>
       </c>
       <c r="H273" t="n">
         <v>263075</v>
@@ -8315,7 +8315,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072503089905</v>
+        <v>2.50072526931763</v>
       </c>
       <c r="H274" t="n">
         <v>488841</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363806724548</v>
+        <v>2.46363830566406</v>
       </c>
       <c r="H275" t="n">
         <v>198253</v>
@@ -8431,7 +8431,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138483047485</v>
+        <v>2.40138506889343</v>
       </c>
       <c r="H278" t="n">
         <v>362112</v>
@@ -8460,7 +8460,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092089653015</v>
       </c>
       <c r="H279" t="n">
         <v>309995</v>
@@ -8489,7 +8489,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356996536255</v>
+        <v>2.37356948852539</v>
       </c>
       <c r="H280" t="n">
         <v>114037</v>
@@ -8547,7 +8547,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G282" t="n">
-        <v>2.42257738113403</v>
+        <v>2.42257785797119</v>
       </c>
       <c r="H282" t="n">
         <v>228893</v>
@@ -8634,7 +8634,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>2.36164855957031</v>
+        <v>2.36164879798889</v>
       </c>
       <c r="H285" t="n">
         <v>138083</v>
@@ -8721,7 +8721,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985997200012</v>
+        <v>2.32985973358154</v>
       </c>
       <c r="H288" t="n">
         <v>130996</v>
@@ -8866,7 +8866,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.4000608921051</v>
+        <v>2.40006041526794</v>
       </c>
       <c r="H293" t="n">
         <v>70534</v>
@@ -8924,7 +8924,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.40403413772583</v>
+        <v>2.40403389930725</v>
       </c>
       <c r="H295" t="n">
         <v>126484</v>
@@ -8953,7 +8953,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35767483711243</v>
+        <v>2.35767507553101</v>
       </c>
       <c r="H296" t="n">
         <v>190410</v>
@@ -9098,7 +9098,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807620048523</v>
+        <v>2.49807596206665</v>
       </c>
       <c r="H301" t="n">
         <v>292122</v>
@@ -9127,7 +9127,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G302" t="n">
-        <v>2.50469875335693</v>
+        <v>2.50469899177551</v>
       </c>
       <c r="H302" t="n">
         <v>283293</v>
@@ -9156,7 +9156,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761202812195</v>
+        <v>2.46761178970337</v>
       </c>
       <c r="H303" t="n">
         <v>262776</v>
@@ -9185,7 +9185,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G304" t="n">
-        <v>2.49145364761353</v>
+        <v>2.49145340919495</v>
       </c>
       <c r="H304" t="n">
         <v>215004</v>
@@ -9243,7 +9243,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>2.56297850608826</v>
+        <v>2.56297826766968</v>
       </c>
       <c r="H306" t="n">
         <v>615974</v>
@@ -9301,7 +9301,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.6000657081604</v>
+        <v>2.60006546974182</v>
       </c>
       <c r="H308" t="n">
         <v>263459</v>
@@ -9330,7 +9330,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211850166321</v>
+        <v>2.59211826324463</v>
       </c>
       <c r="H309" t="n">
         <v>248866</v>
@@ -9388,7 +9388,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63185429573059</v>
+        <v>2.63185405731201</v>
       </c>
       <c r="H311" t="n">
         <v>305933</v>
@@ -9417,7 +9417,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>2.7007303237915</v>
+        <v>2.70073008537292</v>
       </c>
       <c r="H312" t="n">
         <v>590494</v>
@@ -9446,7 +9446,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71529984474182</v>
       </c>
       <c r="H313" t="n">
         <v>428736</v>
@@ -9475,7 +9475,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.82126355171204</v>
+        <v>2.82126307487488</v>
       </c>
       <c r="H314" t="n">
         <v>1620852</v>
@@ -9504,7 +9504,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642887115479</v>
+        <v>2.84642934799194</v>
       </c>
       <c r="H315" t="n">
         <v>839292</v>
@@ -9562,7 +9562,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.0649778842926</v>
+        <v>3.06497716903687</v>
       </c>
       <c r="H317" t="n">
         <v>1978795</v>
@@ -9591,7 +9591,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02789092063904</v>
+        <v>3.02789068222046</v>
       </c>
       <c r="H318" t="n">
         <v>1098038</v>
@@ -9620,7 +9620,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709372520447</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H319" t="n">
         <v>973140</v>
@@ -9649,7 +9649,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907865524292</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H320" t="n">
         <v>786928</v>
@@ -9736,7 +9736,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="n">
-        <v>2.93914699554443</v>
+        <v>2.93914675712585</v>
       </c>
       <c r="H323" t="n">
         <v>302239</v>
@@ -9765,7 +9765,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H324" t="n">
         <v>228643</v>
@@ -9794,7 +9794,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.99212837219238</v>
+        <v>2.9921281337738</v>
       </c>
       <c r="H325" t="n">
         <v>565930</v>
@@ -9823,7 +9823,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.99477744102478</v>
+        <v>2.99477696418762</v>
       </c>
       <c r="H326" t="n">
         <v>373530</v>
@@ -9939,7 +9939,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.00404930114746</v>
+        <v>3.00404858589172</v>
       </c>
       <c r="H330" t="n">
         <v>261526</v>
@@ -9968,7 +9968,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504117012024</v>
+        <v>2.95504093170166</v>
       </c>
       <c r="H331" t="n">
         <v>188931</v>
@@ -9997,7 +9997,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90868210792542</v>
+        <v>2.90868258476257</v>
       </c>
       <c r="H332" t="n">
         <v>360673</v>
@@ -10026,7 +10026,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093558311462</v>
+        <v>2.9709358215332</v>
       </c>
       <c r="H333" t="n">
         <v>261603</v>
@@ -10055,7 +10055,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>2.92722606658936</v>
+        <v>2.92722582817078</v>
       </c>
       <c r="H334" t="n">
         <v>171240</v>
@@ -10113,7 +10113,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97225975990295</v>
+        <v>2.97226047515869</v>
       </c>
       <c r="H336" t="n">
         <v>271824</v>
@@ -10171,7 +10171,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067161560059</v>
+        <v>3.01067209243774</v>
       </c>
       <c r="H338" t="n">
         <v>333907</v>
@@ -10200,7 +10200,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="n">
-        <v>2.99875092506409</v>
+        <v>2.99875116348267</v>
       </c>
       <c r="H339" t="n">
         <v>201579</v>
@@ -10258,7 +10258,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H341" t="n">
         <v>486269</v>
@@ -10316,7 +10316,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173254013062</v>
+        <v>3.05173230171204</v>
       </c>
       <c r="H343" t="n">
         <v>351338</v>
@@ -10461,7 +10461,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.00669836997986</v>
+        <v>3.00669813156128</v>
       </c>
       <c r="H348" t="n">
         <v>392406</v>
@@ -10490,7 +10490,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H349" t="n">
         <v>335842</v>
@@ -10519,7 +10519,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981161117554</v>
+        <v>3.03981137275696</v>
       </c>
       <c r="H350" t="n">
         <v>361444</v>
@@ -10577,7 +10577,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159562110901</v>
+        <v>2.87159538269043</v>
       </c>
       <c r="H352" t="n">
         <v>379734</v>
@@ -10606,7 +10606,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>2.84775352478027</v>
+        <v>2.84775424003601</v>
       </c>
       <c r="H353" t="n">
         <v>660590</v>
@@ -10635,7 +10635,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H354" t="n">
         <v>462237</v>
@@ -10664,7 +10664,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="n">
-        <v>2.9512186050415</v>
+        <v>2.95121836662292</v>
       </c>
       <c r="H355" t="n">
         <v>365296</v>
@@ -10693,7 +10693,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G356" t="n">
-        <v>2.87887859344482</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H356" t="n">
         <v>535677</v>
@@ -10722,7 +10722,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="n">
-        <v>2.8922746181488</v>
+        <v>2.89227437973022</v>
       </c>
       <c r="H357" t="n">
         <v>254418</v>
@@ -10751,7 +10751,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772770881653</v>
+        <v>2.91772747039795</v>
       </c>
       <c r="H358" t="n">
         <v>201245</v>
@@ -10838,7 +10838,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897298812866</v>
+        <v>2.89897274971008</v>
       </c>
       <c r="H361" t="n">
         <v>217176</v>
@@ -10867,7 +10867,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G362" t="n">
-        <v>2.85476469993591</v>
+        <v>2.85476493835449</v>
       </c>
       <c r="H362" t="n">
         <v>288132</v>
@@ -10983,7 +10983,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="n">
-        <v>2.79448103904724</v>
+        <v>2.79448127746582</v>
       </c>
       <c r="H366" t="n">
         <v>170095</v>
@@ -11012,7 +11012,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.76768851280212</v>
+        <v>2.76768827438354</v>
       </c>
       <c r="H367" t="n">
         <v>132754</v>
@@ -11041,7 +11041,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H368" t="n">
         <v>291905</v>
@@ -11070,7 +11070,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="n">
-        <v>2.66989469528198</v>
+        <v>2.66989517211914</v>
       </c>
       <c r="H369" t="n">
         <v>430652</v>
@@ -11186,7 +11186,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="n">
-        <v>2.64846062660217</v>
+        <v>2.64846086502075</v>
       </c>
       <c r="H373" t="n">
         <v>468185</v>
@@ -11215,7 +11215,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G374" t="n">
-        <v>2.72080111503601</v>
+        <v>2.72080087661743</v>
       </c>
       <c r="H374" t="n">
         <v>862681</v>
@@ -11244,7 +11244,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G375" t="n">
-        <v>2.70204615592957</v>
+        <v>2.70204639434814</v>
       </c>
       <c r="H375" t="n">
         <v>271668</v>
@@ -11331,7 +11331,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649819374084</v>
+        <v>2.656498670578</v>
       </c>
       <c r="H378" t="n">
         <v>194294</v>
@@ -11418,7 +11418,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>2.64846062660217</v>
+        <v>2.64846086502075</v>
       </c>
       <c r="H381" t="n">
         <v>281322</v>
@@ -11447,7 +11447,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568712234497</v>
+        <v>2.62568688392639</v>
       </c>
       <c r="H382" t="n">
         <v>194044</v>
@@ -11476,7 +11476,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621500968933</v>
+        <v>2.59621477127075</v>
       </c>
       <c r="H383" t="n">
         <v>275930</v>
@@ -11534,7 +11534,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H385" t="n">
         <v>222513</v>
@@ -11563,7 +11563,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="n">
-        <v>2.60291290283203</v>
+        <v>2.60291314125061</v>
       </c>
       <c r="H386" t="n">
         <v>259728</v>
@@ -11650,7 +11650,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870485305786</v>
       </c>
       <c r="H389" t="n">
         <v>213962</v>
@@ -11708,7 +11708,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G391" t="n">
-        <v>2.55334639549255</v>
+        <v>2.55334687232971</v>
       </c>
       <c r="H391" t="n">
         <v>152367</v>
@@ -11737,7 +11737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H392" t="n">
         <v>689944</v>
@@ -11766,7 +11766,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G393" t="n">
-        <v>2.7154426574707</v>
+        <v>2.71544241905212</v>
       </c>
       <c r="H393" t="n">
         <v>325361</v>
@@ -11824,7 +11824,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946120262146</v>
+        <v>2.71946167945862</v>
       </c>
       <c r="H395" t="n">
         <v>107839</v>
@@ -11940,7 +11940,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G399" t="n">
-        <v>2.60693192481995</v>
+        <v>2.6069324016571</v>
       </c>
       <c r="H399" t="n">
         <v>99666</v>
@@ -12027,7 +12027,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H402" t="n">
         <v>129322</v>
@@ -12114,7 +12114,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.64042282104492</v>
+        <v>2.6404230594635</v>
       </c>
       <c r="H405" t="n">
         <v>195865</v>
@@ -12172,7 +12172,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="n">
-        <v>2.6631965637207</v>
+        <v>2.66319680213928</v>
       </c>
       <c r="H407" t="n">
         <v>149523</v>
@@ -12230,7 +12230,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G409" t="n">
-        <v>2.67391395568848</v>
+        <v>2.67391419410706</v>
       </c>
       <c r="H409" t="n">
         <v>148113</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338559150696</v>
+        <v>2.70338582992554</v>
       </c>
       <c r="H411" t="n">
         <v>157359</v>
@@ -12317,7 +12317,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H412" t="n">
         <v>148944</v>
@@ -12346,7 +12346,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="n">
-        <v>2.60291290283203</v>
+        <v>2.60291314125061</v>
       </c>
       <c r="H413" t="n">
         <v>90682</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H414" t="n">
         <v>196816</v>
@@ -12433,7 +12433,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H416" t="n">
         <v>50142</v>
@@ -12462,7 +12462,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344126701355</v>
       </c>
       <c r="H417" t="n">
         <v>103218</v>
@@ -12491,7 +12491,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H418" t="n">
         <v>297656</v>
@@ -12520,7 +12520,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459143638611</v>
+        <v>2.53459167480469</v>
       </c>
       <c r="H419" t="n">
         <v>215549</v>
@@ -12549,7 +12549,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="n">
-        <v>2.5225350856781</v>
+        <v>2.52253484725952</v>
       </c>
       <c r="H420" t="n">
         <v>95268</v>
@@ -12578,7 +12578,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H421" t="n">
         <v>130865</v>
@@ -12636,7 +12636,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G423" t="n">
-        <v>2.48636484146118</v>
+        <v>2.48636507987976</v>
       </c>
       <c r="H423" t="n">
         <v>72576</v>
@@ -12665,7 +12665,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H424" t="n">
         <v>51012</v>
@@ -12694,7 +12694,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47162890434265</v>
+        <v>2.47162914276123</v>
       </c>
       <c r="H425" t="n">
         <v>188856</v>
@@ -12752,7 +12752,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56004476547241</v>
+        <v>2.56004452705383</v>
       </c>
       <c r="H427" t="n">
         <v>193537</v>
@@ -12781,7 +12781,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G428" t="n">
-        <v>2.59755492210388</v>
+        <v>2.5975546836853</v>
       </c>
       <c r="H428" t="n">
         <v>217980</v>
@@ -12810,7 +12810,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157370567322</v>
+        <v>2.60157346725464</v>
       </c>
       <c r="H429" t="n">
         <v>130021</v>
@@ -12926,7 +12926,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.71678256988525</v>
+        <v>2.71678233146667</v>
       </c>
       <c r="H433" t="n">
         <v>449341</v>
@@ -12955,7 +12955,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189632415771</v>
+        <v>2.81189656257629</v>
       </c>
       <c r="H434" t="n">
         <v>677293</v>
@@ -12984,7 +12984,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H435" t="n">
         <v>606578</v>
@@ -13013,7 +13013,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.8534255027771</v>
+        <v>2.85342526435852</v>
       </c>
       <c r="H436" t="n">
         <v>325483</v>
@@ -13071,7 +13071,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="n">
-        <v>2.90165185928345</v>
+        <v>2.90165209770203</v>
       </c>
       <c r="H438" t="n">
         <v>438391</v>
@@ -13100,7 +13100,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H439" t="n">
         <v>359505</v>
@@ -13129,7 +13129,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G440" t="n">
-        <v>2.92040681838989</v>
+        <v>2.92040705680847</v>
       </c>
       <c r="H440" t="n">
         <v>311701</v>
@@ -13158,7 +13158,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>2.91504883766174</v>
+        <v>2.91504859924316</v>
       </c>
       <c r="H441" t="n">
         <v>331954</v>
@@ -13216,7 +13216,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136819839478</v>
+        <v>2.84136843681335</v>
       </c>
       <c r="H443" t="n">
         <v>279165</v>
@@ -13245,7 +13245,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H444" t="n">
         <v>227702</v>
@@ -13274,7 +13274,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682200431824</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H445" t="n">
         <v>208778</v>
@@ -13303,7 +13303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H446" t="n">
         <v>218622</v>
@@ -13332,7 +13332,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="n">
-        <v>2.85744380950928</v>
+        <v>2.85744428634644</v>
       </c>
       <c r="H447" t="n">
         <v>204402</v>
@@ -13361,7 +13361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682200431824</v>
+        <v>2.86682176589966</v>
       </c>
       <c r="H448" t="n">
         <v>119126</v>
@@ -13419,7 +13419,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>2.79448103904724</v>
+        <v>2.79448127746582</v>
       </c>
       <c r="H450" t="n">
         <v>261468</v>
@@ -13448,7 +13448,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H451" t="n">
         <v>306011</v>
@@ -13477,7 +13477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H452" t="n">
         <v>174105</v>
@@ -13535,7 +13535,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868932723999</v>
+        <v>2.83868885040283</v>
       </c>
       <c r="H454" t="n">
         <v>379887</v>
@@ -13564,7 +13564,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G455" t="n">
-        <v>2.87887859344482</v>
+        <v>2.87887835502625</v>
       </c>
       <c r="H455" t="n">
         <v>244063</v>
@@ -13593,7 +13593,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="n">
-        <v>2.955237865448</v>
+        <v>2.95523738861084</v>
       </c>
       <c r="H456" t="n">
         <v>621450</v>
@@ -13622,7 +13622,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567111968994</v>
+        <v>2.90567088127136</v>
       </c>
       <c r="H457" t="n">
         <v>257517</v>
@@ -13651,7 +13651,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G458" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H458" t="n">
         <v>354316</v>
@@ -13709,7 +13709,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.8400285243988</v>
+        <v>2.84002876281738</v>
       </c>
       <c r="H460" t="n">
         <v>234215</v>
@@ -13767,7 +13767,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G462" t="n">
-        <v>2.8601233959198</v>
+        <v>2.86012315750122</v>
       </c>
       <c r="H462" t="n">
         <v>461987</v>
@@ -13796,7 +13796,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710471153259</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H463" t="n">
         <v>290532</v>
@@ -13825,7 +13825,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916177749634</v>
+        <v>2.93916201591492</v>
       </c>
       <c r="H464" t="n">
         <v>296201</v>
@@ -13854,7 +13854,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G465" t="n">
-        <v>2.92040681838989</v>
+        <v>2.92040705680847</v>
       </c>
       <c r="H465" t="n">
         <v>172474</v>
@@ -13883,7 +13883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94720005989075</v>
       </c>
       <c r="H466" t="n">
         <v>276862</v>
@@ -13912,7 +13912,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710471153259</v>
+        <v>2.92710518836975</v>
       </c>
       <c r="H467" t="n">
         <v>1298241</v>
@@ -13941,7 +13941,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>2.92576551437378</v>
+        <v>2.92576575279236</v>
       </c>
       <c r="H468" t="n">
         <v>376809</v>
@@ -13970,7 +13970,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88155746459961</v>
+        <v>2.88155722618103</v>
       </c>
       <c r="H469" t="n">
         <v>246783</v>
@@ -13999,7 +13999,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370844841003</v>
+        <v>2.91370868682861</v>
       </c>
       <c r="H470" t="n">
         <v>103518</v>
@@ -14057,7 +14057,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.93246340751648</v>
+        <v>2.93246364593506</v>
       </c>
       <c r="H472" t="n">
         <v>142444</v>
@@ -14086,7 +14086,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G473" t="n">
-        <v>2.90835022926331</v>
+        <v>2.90834999084473</v>
       </c>
       <c r="H473" t="n">
         <v>172391</v>
@@ -14115,7 +14115,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G474" t="n">
-        <v>2.89629364013672</v>
+        <v>2.89629340171814</v>
       </c>
       <c r="H474" t="n">
         <v>607080</v>
@@ -14173,7 +14173,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031242370605</v>
+        <v>2.9003119468689</v>
       </c>
       <c r="H476" t="n">
         <v>293657</v>
@@ -14260,7 +14260,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314136505127</v>
+        <v>2.79314184188843</v>
       </c>
       <c r="H479" t="n">
         <v>317272</v>
@@ -14289,7 +14289,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76233005523682</v>
+        <v>2.7623302936554</v>
       </c>
       <c r="H480" t="n">
         <v>456143</v>
@@ -14318,7 +14318,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.64042282104492</v>
+        <v>2.6404230594635</v>
       </c>
       <c r="H481" t="n">
         <v>1595732</v>
@@ -14347,7 +14347,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H482" t="n">
         <v>381717</v>
@@ -14405,7 +14405,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300777435303</v>
       </c>
       <c r="H484" t="n">
         <v>183394</v>
@@ -14463,7 +14463,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H486" t="n">
         <v>174243</v>
@@ -14521,7 +14521,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.66587615013123</v>
+        <v>2.66587591171265</v>
       </c>
       <c r="H488" t="n">
         <v>291126</v>
@@ -14637,7 +14637,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927265167236</v>
+        <v>2.67927241325378</v>
       </c>
       <c r="H492" t="n">
         <v>427250</v>
@@ -14666,7 +14666,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908362388611</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H493" t="n">
         <v>248344</v>
@@ -14695,7 +14695,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="n">
-        <v>2.64980006217957</v>
+        <v>2.6498007774353</v>
       </c>
       <c r="H494" t="n">
         <v>168528</v>
@@ -14782,7 +14782,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62970614433289</v>
+        <v>2.62970590591431</v>
       </c>
       <c r="H497" t="n">
         <v>169752</v>
@@ -14811,7 +14811,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.62434768676758</v>
+        <v>2.624347448349</v>
       </c>
       <c r="H498" t="n">
         <v>109452</v>
@@ -14840,7 +14840,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H499" t="n">
         <v>464341</v>
@@ -14869,7 +14869,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300753593445</v>
+        <v>2.62300777435303</v>
       </c>
       <c r="H500" t="n">
         <v>412188</v>
@@ -14898,7 +14898,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344126701355</v>
       </c>
       <c r="H501" t="n">
         <v>511482</v>
@@ -14956,7 +14956,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344102859497</v>
+        <v>2.57344126701355</v>
       </c>
       <c r="H503" t="n">
         <v>442866</v>
@@ -14985,7 +14985,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H504" t="n">
         <v>308246</v>
@@ -15043,7 +15043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H506" t="n">
         <v>188484</v>
@@ -15072,7 +15072,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H507" t="n">
         <v>155274</v>
@@ -15101,7 +15101,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057312965393</v>
+        <v>2.53057265281677</v>
       </c>
       <c r="H508" t="n">
         <v>166223</v>
@@ -15130,7 +15130,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449751853943</v>
+        <v>2.51449728012085</v>
       </c>
       <c r="H509" t="n">
         <v>151770</v>
@@ -15159,7 +15159,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119565010071</v>
+        <v>2.52119541168213</v>
       </c>
       <c r="H510" t="n">
         <v>181112</v>
@@ -15188,7 +15188,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G511" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H511" t="n">
         <v>183688</v>
@@ -15246,7 +15246,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H513" t="n">
         <v>248411</v>
@@ -15275,7 +15275,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.50846886634827</v>
+        <v>2.50846862792969</v>
       </c>
       <c r="H514" t="n">
         <v>345941</v>
@@ -15333,7 +15333,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884692192078</v>
+        <v>2.58884716033936</v>
       </c>
       <c r="H516" t="n">
         <v>358297</v>
@@ -15391,7 +15391,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526186943054</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H518" t="n">
         <v>296465</v>
@@ -15420,7 +15420,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H519" t="n">
         <v>422125</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.5453085899353</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H520" t="n">
         <v>236775</v>
@@ -15478,7 +15478,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G521" t="n">
-        <v>2.54196000099182</v>
+        <v>2.54195952415466</v>
       </c>
       <c r="H521" t="n">
         <v>308599</v>
@@ -15536,7 +15536,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.53861045837402</v>
+        <v>2.5386106967926</v>
       </c>
       <c r="H523" t="n">
         <v>500528</v>
@@ -15565,7 +15565,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.52856349945068</v>
+        <v>2.52856373786926</v>
       </c>
       <c r="H524" t="n">
         <v>208864</v>
@@ -15594,7 +15594,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870485305786</v>
       </c>
       <c r="H525" t="n">
         <v>259926</v>
@@ -15652,7 +15652,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578175544739</v>
+        <v>2.64578151702881</v>
       </c>
       <c r="H527" t="n">
         <v>344329</v>
@@ -15739,7 +15739,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H530" t="n">
         <v>222183</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H532" t="n">
         <v>266372</v>
@@ -15913,7 +15913,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219574928284</v>
       </c>
       <c r="H536" t="n">
         <v>753926</v>
@@ -15942,7 +15942,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526186943054</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H537" t="n">
         <v>618411</v>
@@ -15971,7 +15971,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.5486581325531</v>
+        <v>2.54865789413452</v>
       </c>
       <c r="H538" t="n">
         <v>187640</v>
@@ -16029,7 +16029,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H540" t="n">
         <v>333031</v>
@@ -16087,7 +16087,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148683547974</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H542" t="n">
         <v>168325</v>
@@ -16116,7 +16116,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G543" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488357543945</v>
       </c>
       <c r="H543" t="n">
         <v>168193</v>
@@ -16145,7 +16145,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827983856201</v>
+        <v>2.46828007698059</v>
       </c>
       <c r="H544" t="n">
         <v>133388</v>
@@ -16232,7 +16232,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.4046471118927</v>
+        <v>2.40464687347412</v>
       </c>
       <c r="H547" t="n">
         <v>141963</v>
@@ -16609,7 +16609,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389028549194</v>
       </c>
       <c r="H560" t="n">
         <v>289529</v>
@@ -16638,7 +16638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700312614441</v>
+        <v>2.19700336456299</v>
       </c>
       <c r="H561" t="n">
         <v>269006</v>
@@ -16696,7 +16696,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337087631226</v>
+        <v>2.1333703994751</v>
       </c>
       <c r="H563" t="n">
         <v>656760</v>
@@ -16725,7 +16725,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G564" t="n">
-        <v>2.27738189697266</v>
+        <v>2.2773814201355</v>
       </c>
       <c r="H564" t="n">
         <v>859120</v>
@@ -16841,7 +16841,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>2.27403259277344</v>
+        <v>2.27403235435486</v>
       </c>
       <c r="H568" t="n">
         <v>278538</v>
@@ -16870,7 +16870,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.2505886554718</v>
+        <v>2.25058889389038</v>
       </c>
       <c r="H569" t="n">
         <v>201800</v>
@@ -16899,7 +16899,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389028549194</v>
       </c>
       <c r="H570" t="n">
         <v>280790</v>
@@ -17015,7 +17015,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G574" t="n">
-        <v>2.44483613967896</v>
+        <v>2.44483637809753</v>
       </c>
       <c r="H574" t="n">
         <v>662269</v>
@@ -17102,7 +17102,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H577" t="n">
         <v>339561</v>
@@ -17189,7 +17189,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148683547974</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H580" t="n">
         <v>207497</v>
@@ -17276,7 +17276,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H583" t="n">
         <v>185158</v>
@@ -17305,7 +17305,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H584" t="n">
         <v>89113</v>
@@ -17450,7 +17450,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>2.48502516746521</v>
+        <v>2.48502492904663</v>
       </c>
       <c r="H589" t="n">
         <v>121975</v>
@@ -17537,7 +17537,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181793212891</v>
       </c>
       <c r="H592" t="n">
         <v>172383</v>
@@ -17595,7 +17595,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H594" t="n">
         <v>142722</v>
@@ -17624,7 +17624,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="n">
-        <v>2.50177073478699</v>
+        <v>2.50177049636841</v>
       </c>
       <c r="H595" t="n">
         <v>206947</v>
@@ -17769,7 +17769,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>2.45488333702087</v>
+        <v>2.45488357543945</v>
       </c>
       <c r="H600" t="n">
         <v>114328</v>
@@ -17856,7 +17856,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="n">
-        <v>2.54028511047363</v>
+        <v>2.54028534889221</v>
       </c>
       <c r="H603" t="n">
         <v>178403</v>
@@ -17885,7 +17885,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.43702125549316</v>
+        <v>2.43702149391174</v>
       </c>
       <c r="H604" t="n">
         <v>438968</v>
@@ -17943,7 +17943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H606" t="n">
         <v>447106</v>
@@ -18030,7 +18030,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556799888611</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H609" t="n">
         <v>162895</v>
@@ -18088,7 +18088,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737859725952</v>
       </c>
       <c r="H611" t="n">
         <v>302598</v>
@@ -18117,7 +18117,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295715332031</v>
       </c>
       <c r="H612" t="n">
         <v>208784</v>
@@ -18146,7 +18146,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H613" t="n">
         <v>279124</v>
@@ -18175,7 +18175,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H614" t="n">
         <v>249358</v>
@@ -18320,7 +18320,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295715332031</v>
       </c>
       <c r="H619" t="n">
         <v>271778</v>
@@ -18378,7 +18378,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737859725952</v>
       </c>
       <c r="H621" t="n">
         <v>102223</v>
@@ -18465,7 +18465,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589438438416</v>
+        <v>2.29589462280273</v>
       </c>
       <c r="H624" t="n">
         <v>191609</v>
@@ -18668,7 +18668,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28212642669678</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H631" t="n">
         <v>206647</v>
@@ -18697,7 +18697,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915800094604</v>
+        <v>2.39915823936462</v>
       </c>
       <c r="H632" t="n">
         <v>997504</v>
@@ -18726,7 +18726,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473703384399</v>
+        <v>2.36473679542542</v>
       </c>
       <c r="H633" t="n">
         <v>866249</v>
@@ -18755,7 +18755,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H634" t="n">
         <v>291169</v>
@@ -18929,7 +18929,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556799888611</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H640" t="n">
         <v>188973</v>
@@ -18958,7 +18958,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.30622100830078</v>
+        <v>2.30622053146362</v>
       </c>
       <c r="H641" t="n">
         <v>66001</v>
@@ -19016,7 +19016,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589438438416</v>
+        <v>2.29589462280273</v>
       </c>
       <c r="H643" t="n">
         <v>117183</v>
@@ -19045,7 +19045,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245209693909</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H644" t="n">
         <v>158331</v>
@@ -19074,7 +19074,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H645" t="n">
         <v>204003</v>
@@ -19103,7 +19103,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082064628601</v>
+        <v>2.24082088470459</v>
       </c>
       <c r="H646" t="n">
         <v>138242</v>
@@ -19132,7 +19132,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H647" t="n">
         <v>91283</v>
@@ -19190,7 +19190,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>2.19951510429382</v>
+        <v>2.19951486587524</v>
       </c>
       <c r="H649" t="n">
         <v>159276</v>
@@ -19219,7 +19219,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.17886233329773</v>
+        <v>2.17886281013489</v>
       </c>
       <c r="H650" t="n">
         <v>98263</v>
@@ -19248,7 +19248,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>2.19263100624084</v>
+        <v>2.19263076782227</v>
       </c>
       <c r="H651" t="n">
         <v>112998</v>
@@ -19277,7 +19277,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918895721436</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H652" t="n">
         <v>43938</v>
@@ -19306,7 +19306,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607305526733</v>
+        <v>2.19607329368591</v>
       </c>
       <c r="H653" t="n">
         <v>33141</v>
@@ -19335,7 +19335,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="n">
-        <v>2.19951510429382</v>
+        <v>2.19951486587524</v>
       </c>
       <c r="H654" t="n">
         <v>79584</v>
@@ -19364,7 +19364,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.1444411277771</v>
+        <v>2.14444136619568</v>
       </c>
       <c r="H655" t="n">
         <v>109564</v>
@@ -19422,7 +19422,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15820956230164</v>
+        <v>2.15820980072021</v>
       </c>
       <c r="H657" t="n">
         <v>127746</v>
@@ -19538,7 +19538,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328353881836</v>
+        <v>2.21328377723694</v>
       </c>
       <c r="H661" t="n">
         <v>58784</v>
@@ -19596,7 +19596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245209693909</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H663" t="n">
         <v>128498</v>
@@ -19683,7 +19683,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.30622100830078</v>
+        <v>2.30622053146362</v>
       </c>
       <c r="H666" t="n">
         <v>427892</v>
@@ -19712,7 +19712,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245209693909</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H667" t="n">
         <v>147403</v>
@@ -19741,7 +19741,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>2.24426293373108</v>
+        <v>2.2442626953125</v>
       </c>
       <c r="H668" t="n">
         <v>79510</v>
@@ -19915,7 +19915,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328353881836</v>
+        <v>2.21328377723694</v>
       </c>
       <c r="H674" t="n">
         <v>127368</v>
@@ -20031,7 +20031,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>2.1203465461731</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H678" t="n">
         <v>97627</v>
@@ -20060,7 +20060,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11002016067505</v>
       </c>
       <c r="H679" t="n">
         <v>147813</v>
@@ -20118,7 +20118,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509366035461</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H681" t="n">
         <v>90219</v>
@@ -20176,7 +20176,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690402030945</v>
       </c>
       <c r="H683" t="n">
         <v>89809</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H684" t="n">
         <v>106959</v>
@@ -20263,7 +20263,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>2.13067245483398</v>
+        <v>2.13067269325256</v>
       </c>
       <c r="H686" t="n">
         <v>92024</v>
@@ -20292,7 +20292,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690402030945</v>
       </c>
       <c r="H687" t="n">
         <v>150304</v>
@@ -20379,7 +20379,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>2.1203465461731</v>
+        <v>2.12034630775452</v>
       </c>
       <c r="H690" t="n">
         <v>188909</v>
@@ -20437,7 +20437,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H692" t="n">
         <v>87021</v>
@@ -20495,7 +20495,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378835678101</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H694" t="n">
         <v>310317</v>
@@ -20524,7 +20524,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G695" t="n">
-        <v>2.13067245483398</v>
+        <v>2.13067269325256</v>
       </c>
       <c r="H695" t="n">
         <v>137482</v>
@@ -20553,7 +20553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657787322998</v>
+        <v>2.10657811164856</v>
       </c>
       <c r="H696" t="n">
         <v>205834</v>
@@ -20611,7 +20611,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918895721436</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H698" t="n">
         <v>474404</v>
@@ -20756,7 +20756,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>2.05150365829468</v>
+        <v>2.05150389671326</v>
       </c>
       <c r="H703" t="n">
         <v>500439</v>
@@ -20785,7 +20785,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H704" t="n">
         <v>153586</v>
@@ -20843,7 +20843,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494618415833</v>
+        <v>2.05494594573975</v>
       </c>
       <c r="H706" t="n">
         <v>108391</v>
@@ -20930,7 +20930,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H709" t="n">
         <v>235805</v>
@@ -20959,7 +20959,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512461662292</v>
+        <v>1.95512473583221</v>
       </c>
       <c r="H710" t="n">
         <v>129165</v>
@@ -20988,7 +20988,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H711" t="n">
         <v>98948</v>
@@ -21104,7 +21104,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.95856690406799</v>
+        <v>1.95856666564941</v>
       </c>
       <c r="H715" t="n">
         <v>70649</v>
@@ -21133,7 +21133,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.91726112365723</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H716" t="n">
         <v>173384</v>
@@ -21162,7 +21162,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.91726112365723</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H717" t="n">
         <v>97454</v>
@@ -21220,7 +21220,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G719" t="n">
-        <v>1.81399762630463</v>
+        <v>1.81399774551392</v>
       </c>
       <c r="H719" t="n">
         <v>170042</v>
@@ -21249,7 +21249,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.91726112365723</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H720" t="n">
         <v>126796</v>
@@ -21278,7 +21278,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.8828399181366</v>
+        <v>1.88284027576447</v>
       </c>
       <c r="H721" t="n">
         <v>101180</v>
@@ -21307,7 +21307,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070353031158</v>
+        <v>1.92070329189301</v>
       </c>
       <c r="H722" t="n">
         <v>277130</v>
@@ -21336,7 +21336,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.90349280834198</v>
+        <v>1.90349268913269</v>
       </c>
       <c r="H723" t="n">
         <v>172278</v>
@@ -21394,7 +21394,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921967506409</v>
+        <v>1.97921919822693</v>
       </c>
       <c r="H725" t="n">
         <v>62710</v>
@@ -21423,7 +21423,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298799037933</v>
+        <v>1.99298787117004</v>
       </c>
       <c r="H726" t="n">
         <v>108169</v>
@@ -21452,7 +21452,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610353469849</v>
+        <v>1.98610365390778</v>
       </c>
       <c r="H727" t="n">
         <v>75372</v>
@@ -21481,7 +21481,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>2.03429341316223</v>
+        <v>2.03429317474365</v>
       </c>
       <c r="H728" t="n">
         <v>85910</v>
@@ -21771,7 +21771,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889269351959</v>
+        <v>1.96889317035675</v>
       </c>
       <c r="H738" t="n">
         <v>161205</v>
@@ -21800,7 +21800,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H739" t="n">
         <v>264586</v>
@@ -21858,7 +21858,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.9620087146759</v>
+        <v>1.96200895309448</v>
       </c>
       <c r="H741" t="n">
         <v>248184</v>
@@ -22032,7 +22032,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328353881836</v>
+        <v>2.21328377723694</v>
       </c>
       <c r="H747" t="n">
         <v>206720</v>
@@ -22090,7 +22090,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>2.22705221176147</v>
+        <v>2.2270519733429</v>
       </c>
       <c r="H749" t="n">
         <v>156319</v>
@@ -22119,7 +22119,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918895721436</v>
+        <v>2.18918871879578</v>
       </c>
       <c r="H750" t="n">
         <v>204318</v>
@@ -22148,7 +22148,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509366035461</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H751" t="n">
         <v>49394</v>
@@ -22206,7 +22206,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.08936738967896</v>
+        <v>2.08936762809753</v>
       </c>
       <c r="H753" t="n">
         <v>238366</v>
@@ -22235,7 +22235,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509366035461</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H754" t="n">
         <v>409359</v>
@@ -22293,7 +22293,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378835678101</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H756" t="n">
         <v>149343</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245209693909</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H759" t="n">
         <v>342700</v>
@@ -22409,7 +22409,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.28212642669678</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H760" t="n">
         <v>297330</v>
@@ -22438,7 +22438,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="n">
-        <v>2.33375811576843</v>
+        <v>2.33375787734985</v>
       </c>
       <c r="H761" t="n">
         <v>787607</v>
@@ -22583,7 +22583,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="n">
-        <v>2.41981053352356</v>
+        <v>2.41981077194214</v>
       </c>
       <c r="H766" t="n">
         <v>344369</v>
@@ -22670,7 +22670,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G769" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H769" t="n">
         <v>456800</v>
@@ -22699,7 +22699,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H770" t="n">
         <v>203705</v>
@@ -22757,7 +22757,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046378135681</v>
+        <v>2.44046354293823</v>
       </c>
       <c r="H772" t="n">
         <v>369438</v>
@@ -22786,7 +22786,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H773" t="n">
         <v>383952</v>
@@ -22815,7 +22815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H774" t="n">
         <v>376439</v>
@@ -22844,7 +22844,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H775" t="n">
         <v>412613</v>
@@ -22873,7 +22873,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274847984314</v>
       </c>
       <c r="H776" t="n">
         <v>426695</v>
@@ -22902,7 +22902,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>2.53684306144714</v>
+        <v>2.53684329986572</v>
       </c>
       <c r="H777" t="n">
         <v>356598</v>
@@ -22989,7 +22989,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307462692261</v>
       </c>
       <c r="H780" t="n">
         <v>192769</v>
@@ -23018,7 +23018,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307438850403</v>
+        <v>2.52307462692261</v>
       </c>
       <c r="H781" t="n">
         <v>177735</v>
@@ -23047,7 +23047,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274847984314</v>
       </c>
       <c r="H782" t="n">
         <v>217858</v>
@@ -23105,7 +23105,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G784" t="n">
-        <v>2.60568571090698</v>
+        <v>2.6056854724884</v>
       </c>
       <c r="H784" t="n">
         <v>273170</v>
@@ -23366,7 +23366,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224342346191</v>
+        <v>2.60224366188049</v>
       </c>
       <c r="H793" t="n">
         <v>285918</v>
@@ -23424,7 +23424,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535932540894</v>
       </c>
       <c r="H795" t="n">
         <v>139076</v>
@@ -23482,7 +23482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601161956787</v>
+        <v>2.61601185798645</v>
       </c>
       <c r="H797" t="n">
         <v>367842</v>
@@ -23511,7 +23511,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880113601685</v>
+        <v>2.598801612854</v>
       </c>
       <c r="H798" t="n">
         <v>105895</v>
@@ -23743,7 +23743,7 @@
         <v>4.02500009536743</v>
       </c>
       <c r="G806" t="n">
-        <v>2.77090740203857</v>
+        <v>2.77090716362</v>
       </c>
       <c r="H806" t="n">
         <v>284595</v>
@@ -23772,7 +23772,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.71239137649536</v>
+        <v>2.71239113807678</v>
       </c>
       <c r="H807" t="n">
         <v>271085</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681210517883</v>
+        <v>2.74681234359741</v>
       </c>
       <c r="H811" t="n">
         <v>215954</v>
@@ -23946,7 +23946,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G813" t="n">
-        <v>2.72615957260132</v>
+        <v>2.7261598110199</v>
       </c>
       <c r="H813" t="n">
         <v>104400</v>
@@ -23975,7 +23975,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H814" t="n">
         <v>151157</v>
@@ -24120,7 +24120,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H819" t="n">
         <v>173539</v>
@@ -24149,7 +24149,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>2.69518089294434</v>
+        <v>2.6951801776886</v>
       </c>
       <c r="H820" t="n">
         <v>209313</v>
@@ -24207,7 +24207,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.61256980895996</v>
+        <v>2.61256957054138</v>
       </c>
       <c r="H822" t="n">
         <v>177668</v>
@@ -24323,7 +24323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535932540894</v>
       </c>
       <c r="H826" t="n">
         <v>159624</v>
@@ -24439,7 +24439,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>2.65387511253357</v>
+        <v>2.65387535095215</v>
       </c>
       <c r="H830" t="n">
         <v>99250</v>
@@ -24613,7 +24613,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>2.4266951084137</v>
+        <v>2.42669534683228</v>
       </c>
       <c r="H836" t="n">
         <v>233626</v>
@@ -24729,7 +24729,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H840" t="n">
         <v>102179</v>
@@ -24787,7 +24787,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="n">
-        <v>2.41981053352356</v>
+        <v>2.41981077194214</v>
       </c>
       <c r="H842" t="n">
         <v>263155</v>
@@ -24816,7 +24816,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734811782837</v>
+        <v>2.44734787940979</v>
       </c>
       <c r="H843" t="n">
         <v>82236</v>
@@ -24845,7 +24845,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144246101379</v>
       </c>
       <c r="H844" t="n">
         <v>59749</v>
@@ -24874,7 +24874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50586414337158</v>
+        <v>2.505863904953</v>
       </c>
       <c r="H845" t="n">
         <v>222012</v>
@@ -24903,7 +24903,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H846" t="n">
         <v>296447</v>
@@ -24932,7 +24932,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="n">
-        <v>2.49553775787354</v>
+        <v>2.49553751945496</v>
       </c>
       <c r="H847" t="n">
         <v>157082</v>
@@ -24961,7 +24961,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>2.49897980690002</v>
+        <v>2.49897956848145</v>
       </c>
       <c r="H848" t="n">
         <v>191698</v>
@@ -24990,7 +24990,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013739585876</v>
+        <v>2.43013715744019</v>
       </c>
       <c r="H849" t="n">
         <v>115219</v>
@@ -25077,7 +25077,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G852" t="n">
-        <v>2.31654739379883</v>
+        <v>2.31654763221741</v>
       </c>
       <c r="H852" t="n">
         <v>227097</v>
@@ -25106,7 +25106,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031558990479</v>
+        <v>2.33031582832336</v>
       </c>
       <c r="H853" t="n">
         <v>221581</v>
@@ -25164,7 +25164,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G855" t="n">
-        <v>2.20295739173889</v>
+        <v>2.20295715332031</v>
       </c>
       <c r="H855" t="n">
         <v>358436</v>
@@ -25222,7 +25222,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11001992225647</v>
+        <v>2.11002016067505</v>
       </c>
       <c r="H857" t="n">
         <v>429648</v>
@@ -25251,7 +25251,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>2.07904100418091</v>
+        <v>2.07904076576233</v>
       </c>
       <c r="H858" t="n">
         <v>179861</v>
@@ -25309,7 +25309,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085112571716</v>
+        <v>2.03085136413574</v>
       </c>
       <c r="H860" t="n">
         <v>287672</v>
@@ -25367,7 +25367,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H862" t="n">
         <v>284968</v>
@@ -25454,7 +25454,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H865" t="n">
         <v>416439</v>
@@ -25512,7 +25512,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H867" t="n">
         <v>171746</v>
@@ -25541,7 +25541,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.94217920303345</v>
+        <v>1.94217908382416</v>
       </c>
       <c r="H868" t="n">
         <v>234747</v>
@@ -25570,7 +25570,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302951335907</v>
       </c>
       <c r="H869" t="n">
         <v>222484</v>
@@ -25599,7 +25599,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664584636688</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H870" t="n">
         <v>404038</v>
@@ -25686,7 +25686,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H873" t="n">
         <v>227376</v>
@@ -25715,7 +25715,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H874" t="n">
         <v>251629</v>
@@ -25744,7 +25744,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H875" t="n">
         <v>184992</v>
@@ -25802,7 +25802,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834634780884</v>
+        <v>1.97834646701813</v>
       </c>
       <c r="H877" t="n">
         <v>247637</v>
@@ -25831,7 +25831,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302951335907</v>
       </c>
       <c r="H878" t="n">
         <v>109838</v>
@@ -25889,7 +25889,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664584636688</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H880" t="n">
         <v>284652</v>
@@ -25918,7 +25918,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H881" t="n">
         <v>276051</v>
@@ -25947,7 +25947,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H882" t="n">
         <v>279659</v>
@@ -26005,7 +26005,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601241588593</v>
       </c>
       <c r="H884" t="n">
         <v>286493</v>
@@ -26034,7 +26034,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239548683167</v>
       </c>
       <c r="H885" t="n">
         <v>94780</v>
@@ -26063,7 +26063,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G886" t="n">
-        <v>1.89154517650604</v>
+        <v>1.89154529571533</v>
       </c>
       <c r="H886" t="n">
         <v>286669</v>
@@ -26092,7 +26092,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.89154517650604</v>
+        <v>1.89154529571533</v>
       </c>
       <c r="H887" t="n">
         <v>146747</v>
@@ -26121,7 +26121,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.90962886810303</v>
+        <v>1.90962898731232</v>
       </c>
       <c r="H888" t="n">
         <v>107626</v>
@@ -26150,7 +26150,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792836666107</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H889" t="n">
         <v>274027</v>
@@ -26179,7 +26179,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069474697113</v>
+        <v>1.88069498538971</v>
       </c>
       <c r="H890" t="n">
         <v>170084</v>
@@ -26208,7 +26208,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601241588593</v>
       </c>
       <c r="H891" t="n">
         <v>279577</v>
@@ -26237,7 +26237,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324532032013</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H892" t="n">
         <v>470871</v>
@@ -26266,7 +26266,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239548683167</v>
       </c>
       <c r="H893" t="n">
         <v>291178</v>
@@ -26295,7 +26295,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.89877843856812</v>
+        <v>1.89877867698669</v>
       </c>
       <c r="H894" t="n">
         <v>237876</v>
@@ -26324,7 +26324,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.95302939414978</v>
+        <v>1.95302951335907</v>
       </c>
       <c r="H895" t="n">
         <v>800354</v>
@@ -26353,7 +26353,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664584636688</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H896" t="n">
         <v>911289</v>
@@ -26382,7 +26382,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H897" t="n">
         <v>805951</v>
@@ -26411,7 +26411,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G898" t="n">
-        <v>2.07238125801086</v>
+        <v>2.07238101959229</v>
       </c>
       <c r="H898" t="n">
         <v>924209</v>
@@ -26440,7 +26440,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.03259706497192</v>
+        <v>2.0325973033905</v>
       </c>
       <c r="H899" t="n">
         <v>626504</v>
@@ -26469,7 +26469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H900" t="n">
         <v>386888</v>
@@ -26498,7 +26498,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472965717316</v>
+        <v>1.97472977638245</v>
       </c>
       <c r="H901" t="n">
         <v>318897</v>
@@ -26556,7 +26556,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792836666107</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H903" t="n">
         <v>353686</v>
@@ -26585,7 +26585,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.83006083965302</v>
+        <v>1.83006107807159</v>
       </c>
       <c r="H904" t="n">
         <v>909668</v>
@@ -26614,7 +26614,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069474697113</v>
+        <v>1.88069498538971</v>
       </c>
       <c r="H905" t="n">
         <v>562530</v>
@@ -26643,7 +26643,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239548683167</v>
       </c>
       <c r="H906" t="n">
         <v>234433</v>
@@ -26672,7 +26672,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601205825806</v>
+        <v>1.90601241588593</v>
       </c>
       <c r="H907" t="n">
         <v>228173</v>
@@ -26701,7 +26701,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324532032013</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H908" t="n">
         <v>91411</v>
@@ -26788,7 +26788,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792836666107</v>
+        <v>1.88792848587036</v>
       </c>
       <c r="H911" t="n">
         <v>261392</v>
@@ -26817,7 +26817,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431191444397</v>
+        <v>1.8843115568161</v>
       </c>
       <c r="H912" t="n">
         <v>465653</v>
@@ -26846,7 +26846,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474364757538</v>
       </c>
       <c r="H913" t="n">
         <v>618635</v>
@@ -26933,7 +26933,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H916" t="n">
         <v>862579</v>
@@ -26962,7 +26962,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>1.64199149608612</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H917" t="n">
         <v>497518</v>
@@ -26991,7 +26991,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G918" t="n">
-        <v>1.68177533149719</v>
+        <v>1.6817752122879</v>
       </c>
       <c r="H918" t="n">
         <v>629139</v>
@@ -27020,7 +27020,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.62752449512482</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H919" t="n">
         <v>393031</v>
@@ -27078,7 +27078,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327353954315</v>
+        <v>1.57327377796173</v>
       </c>
       <c r="H921" t="n">
         <v>763177</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.6636917591095</v>
+        <v>1.66369152069092</v>
       </c>
       <c r="H922" t="n">
         <v>294260</v>
@@ -27136,7 +27136,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H923" t="n">
         <v>378459</v>
@@ -27194,7 +27194,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.62029099464417</v>
+        <v>1.62029111385345</v>
       </c>
       <c r="H925" t="n">
         <v>696992</v>
@@ -27281,7 +27281,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G928" t="n">
-        <v>1.59135723114014</v>
+        <v>1.59135746955872</v>
       </c>
       <c r="H928" t="n">
         <v>250086</v>
@@ -27310,7 +27310,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G929" t="n">
-        <v>1.59859085083008</v>
+        <v>1.59859073162079</v>
       </c>
       <c r="H929" t="n">
         <v>220719</v>
@@ -27368,7 +27368,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007483005524</v>
+        <v>1.66007506847382</v>
       </c>
       <c r="H931" t="n">
         <v>679589</v>
@@ -27426,7 +27426,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G933" t="n">
-        <v>1.59497392177582</v>
+        <v>1.5949741601944</v>
       </c>
       <c r="H933" t="n">
         <v>252676</v>
@@ -27484,7 +27484,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H935" t="n">
         <v>361760</v>
@@ -27513,7 +27513,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H936" t="n">
         <v>357964</v>
@@ -27542,7 +27542,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G937" t="n">
-        <v>1.67454183101654</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H937" t="n">
         <v>332384</v>
@@ -27571,7 +27571,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H938" t="n">
         <v>298104</v>
@@ -27600,7 +27600,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G939" t="n">
-        <v>1.72517585754395</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H939" t="n">
         <v>258542</v>
@@ -27629,7 +27629,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H940" t="n">
         <v>372190</v>
@@ -27658,7 +27658,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G941" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H941" t="n">
         <v>345682</v>
@@ -27687,7 +27687,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.74687623977661</v>
+        <v>1.7468763589859</v>
       </c>
       <c r="H942" t="n">
         <v>316432</v>
@@ -27716,7 +27716,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H943" t="n">
         <v>343096</v>
@@ -27774,7 +27774,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H945" t="n">
         <v>255600</v>
@@ -27832,7 +27832,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.62752449512482</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H947" t="n">
         <v>1680843</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.62029099464417</v>
+        <v>1.62029111385345</v>
       </c>
       <c r="H951" t="n">
         <v>262964</v>
@@ -28006,7 +28006,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.69985902309418</v>
+        <v>1.69985890388489</v>
       </c>
       <c r="H953" t="n">
         <v>409767</v>
@@ -28064,7 +28064,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.62752449512482</v>
+        <v>1.6275247335434</v>
       </c>
       <c r="H955" t="n">
         <v>414852</v>
@@ -28093,7 +28093,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G956" t="n">
-        <v>1.63114130496979</v>
+        <v>1.63114154338837</v>
       </c>
       <c r="H956" t="n">
         <v>272469</v>
@@ -28151,7 +28151,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G958" t="n">
-        <v>1.64199149608612</v>
+        <v>1.64199137687683</v>
       </c>
       <c r="H958" t="n">
         <v>141207</v>
@@ -28267,7 +28267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H962" t="n">
         <v>546781</v>
@@ -28296,7 +28296,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G963" t="n">
-        <v>1.68177533149719</v>
+        <v>1.6817752122879</v>
       </c>
       <c r="H963" t="n">
         <v>286763</v>
@@ -28325,7 +28325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H964" t="n">
         <v>258696</v>
@@ -28354,7 +28354,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H965" t="n">
         <v>412054</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815840244293</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H966" t="n">
         <v>445642</v>
@@ -28412,7 +28412,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900871276855</v>
+        <v>1.68900883197784</v>
       </c>
       <c r="H967" t="n">
         <v>205808</v>
@@ -28441,7 +28441,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H968" t="n">
         <v>103141</v>
@@ -28470,7 +28470,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.69624209403992</v>
+        <v>1.6962423324585</v>
       </c>
       <c r="H969" t="n">
         <v>150403</v>
@@ -28499,7 +28499,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H970" t="n">
         <v>116106</v>
@@ -28528,7 +28528,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815840244293</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H971" t="n">
         <v>185489</v>
@@ -28586,7 +28586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815840244293</v>
+        <v>1.67815852165222</v>
       </c>
       <c r="H973" t="n">
         <v>190802</v>
@@ -28615,7 +28615,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G974" t="n">
-        <v>1.67454183101654</v>
+        <v>1.67454195022583</v>
       </c>
       <c r="H974" t="n">
         <v>161117</v>
@@ -28673,7 +28673,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730844974518</v>
+        <v>1.66730868816376</v>
       </c>
       <c r="H976" t="n">
         <v>145725</v>
@@ -28702,7 +28702,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G977" t="n">
-        <v>1.68177533149719</v>
+        <v>1.6817752122879</v>
       </c>
       <c r="H977" t="n">
         <v>135253</v>
@@ -28731,7 +28731,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H978" t="n">
         <v>456317</v>
@@ -28760,7 +28760,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.77942669391632</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H979" t="n">
         <v>1130319</v>
@@ -28818,7 +28818,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772643089294</v>
+        <v>1.75772666931152</v>
       </c>
       <c r="H981" t="n">
         <v>635657</v>
@@ -28847,7 +28847,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347571372986</v>
       </c>
       <c r="H982" t="n">
         <v>825785</v>
@@ -28876,7 +28876,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G983" t="n">
-        <v>1.74325954914093</v>
+        <v>1.74325966835022</v>
       </c>
       <c r="H983" t="n">
         <v>346060</v>
@@ -28905,7 +28905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.77219331264496</v>
+        <v>1.77219343185425</v>
       </c>
       <c r="H984" t="n">
         <v>304114</v>
@@ -28934,7 +28934,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134300231934</v>
+        <v>1.76134324073792</v>
       </c>
       <c r="H985" t="n">
         <v>462415</v>
@@ -28963,7 +28963,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G986" t="n">
-        <v>1.72517585754395</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H986" t="n">
         <v>235688</v>
@@ -28992,7 +28992,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>1.7287929058075</v>
+        <v>1.72879278659821</v>
       </c>
       <c r="H987" t="n">
         <v>462399</v>
@@ -29021,7 +29021,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H988" t="n">
         <v>321015</v>
@@ -29079,7 +29079,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070909500122</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H990" t="n">
         <v>404717</v>
@@ -29137,7 +29137,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.77942669391632</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H992" t="n">
         <v>947214</v>
@@ -29166,7 +29166,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666019439697</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H993" t="n">
         <v>380638</v>
@@ -29195,7 +29195,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666019439697</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H994" t="n">
         <v>337289</v>
@@ -29224,7 +29224,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H995" t="n">
         <v>1295316</v>
@@ -29253,7 +29253,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G996" t="n">
-        <v>2.01451349258423</v>
+        <v>2.01451373100281</v>
       </c>
       <c r="H996" t="n">
         <v>2489093</v>
@@ -29311,7 +29311,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.9349457025528</v>
+        <v>1.93494582176208</v>
       </c>
       <c r="H998" t="n">
         <v>1204470</v>
@@ -29369,7 +29369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1000" t="n">
         <v>951588</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1002" t="n">
         <v>591585</v>
@@ -29456,7 +29456,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1003" t="n">
         <v>552967</v>
@@ -29514,7 +29514,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.05429792404175</v>
+        <v>2.05429768562317</v>
       </c>
       <c r="H1005" t="n">
         <v>604497</v>
@@ -29572,7 +29572,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.00366353988647</v>
+        <v>2.0036633014679</v>
       </c>
       <c r="H1007" t="n">
         <v>828831</v>
@@ -29630,7 +29630,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.01813054084778</v>
+        <v>2.0181303024292</v>
       </c>
       <c r="H1009" t="n">
         <v>304169</v>
@@ -29688,7 +29688,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1011" t="n">
         <v>341025</v>
@@ -29746,7 +29746,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281334877014</v>
+        <v>1.99281346797943</v>
       </c>
       <c r="H1013" t="n">
         <v>183722</v>
@@ -29775,7 +29775,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99643003940582</v>
+        <v>1.99643015861511</v>
       </c>
       <c r="H1014" t="n">
         <v>219712</v>
@@ -29891,7 +29891,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856239318848</v>
       </c>
       <c r="H1018" t="n">
         <v>371965</v>
@@ -29978,7 +29978,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664584636688</v>
+        <v>1.95664608478546</v>
       </c>
       <c r="H1021" t="n">
         <v>243379</v>
@@ -30007,7 +30007,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856239318848</v>
       </c>
       <c r="H1022" t="n">
         <v>218394</v>
@@ -30036,7 +30036,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324532032013</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H1023" t="n">
         <v>212691</v>
@@ -30065,7 +30065,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346148490906</v>
+        <v>1.87346136569977</v>
       </c>
       <c r="H1024" t="n">
         <v>368919</v>
@@ -30123,7 +30123,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H1026" t="n">
         <v>271070</v>
@@ -30152,7 +30152,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856239318848</v>
       </c>
       <c r="H1027" t="n">
         <v>619856</v>
@@ -30181,7 +30181,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728011131287</v>
+        <v>2.00728034973145</v>
       </c>
       <c r="H1028" t="n">
         <v>978677</v>
@@ -30210,7 +30210,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.9855797290802</v>
+        <v>1.98558020591736</v>
       </c>
       <c r="H1029" t="n">
         <v>431020</v>
@@ -30268,7 +30268,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H1031" t="n">
         <v>346362</v>
@@ -30297,7 +30297,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.9855797290802</v>
+        <v>1.98558020591736</v>
       </c>
       <c r="H1032" t="n">
         <v>263186</v>
@@ -30326,7 +30326,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984503269196</v>
+        <v>1.86984479427338</v>
       </c>
       <c r="H1033" t="n">
         <v>665587</v>
@@ -30355,7 +30355,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431191444397</v>
+        <v>1.8843115568161</v>
       </c>
       <c r="H1034" t="n">
         <v>562475</v>
@@ -30413,7 +30413,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474364757538</v>
       </c>
       <c r="H1036" t="n">
         <v>595397</v>
@@ -30442,7 +30442,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.72517585754395</v>
+        <v>1.72517597675323</v>
       </c>
       <c r="H1037" t="n">
         <v>749348</v>
@@ -30500,7 +30500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.77219331264496</v>
+        <v>1.77219343185425</v>
       </c>
       <c r="H1039" t="n">
         <v>337490</v>
@@ -30558,7 +30558,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.79027688503265</v>
+        <v>1.79027700424194</v>
       </c>
       <c r="H1041" t="n">
         <v>444570</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.77942669391632</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1042" t="n">
         <v>282267</v>
@@ -30616,7 +30616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.7649599313736</v>
+        <v>1.76496005058289</v>
       </c>
       <c r="H1043" t="n">
         <v>116889</v>
@@ -30645,7 +30645,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77942669391632</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1044" t="n">
         <v>331929</v>
@@ -30674,7 +30674,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1045" t="n">
         <v>215954</v>
@@ -30703,7 +30703,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899448394775</v>
+        <v>1.85899472236633</v>
       </c>
       <c r="H1046" t="n">
         <v>633060</v>
@@ -30761,7 +30761,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.81921076774597</v>
+        <v>1.81921088695526</v>
       </c>
       <c r="H1048" t="n">
         <v>428986</v>
@@ -30790,7 +30790,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644426822662</v>
+        <v>1.82644438743591</v>
       </c>
       <c r="H1049" t="n">
         <v>268233</v>
@@ -30819,7 +30819,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176110267639</v>
+        <v>1.85176134109497</v>
       </c>
       <c r="H1050" t="n">
         <v>328554</v>
@@ -30848,7 +30848,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1051" t="n">
         <v>301333</v>
@@ -30877,7 +30877,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.77942669391632</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1052" t="n">
         <v>278255</v>
@@ -30906,7 +30906,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262540340424</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H1053" t="n">
         <v>578759</v>
@@ -30935,7 +30935,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1054" t="n">
         <v>345112</v>
@@ -30964,7 +30964,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1055" t="n">
         <v>555769</v>
@@ -30993,7 +30993,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.60582423210144</v>
+        <v>1.60582411289215</v>
       </c>
       <c r="H1056" t="n">
         <v>441535</v>
@@ -31109,7 +31109,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366837501526</v>
+        <v>1.43366825580597</v>
       </c>
       <c r="H1060" t="n">
         <v>342436</v>
@@ -31138,7 +31138,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448107242584</v>
+        <v>1.38448095321655</v>
       </c>
       <c r="H1061" t="n">
         <v>581654</v>
@@ -31196,7 +31196,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.2441520690918</v>
+        <v>1.24415218830109</v>
       </c>
       <c r="H1063" t="n">
         <v>710228</v>
@@ -31283,7 +31283,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412844657898</v>
+        <v>1.01412856578827</v>
       </c>
       <c r="H1066" t="n">
         <v>500114</v>
@@ -31370,7 +31370,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.985194742679596</v>
+        <v>0.985194802284241</v>
       </c>
       <c r="H1069" t="n">
         <v>281501</v>
@@ -31399,7 +31399,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.0083419084549</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1070" t="n">
         <v>205387</v>
@@ -31428,7 +31428,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.0242555141449</v>
+        <v>1.02425539493561</v>
       </c>
       <c r="H1071" t="n">
         <v>337483</v>
@@ -31457,7 +31457,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.13854396343231</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1072" t="n">
         <v>440163</v>
@@ -31486,7 +31486,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.22679173946381</v>
+        <v>1.2267918586731</v>
       </c>
       <c r="H1073" t="n">
         <v>282057</v>
@@ -31544,7 +31544,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.2441520690918</v>
+        <v>1.24415218830109</v>
       </c>
       <c r="H1075" t="n">
         <v>387433</v>
@@ -31602,7 +31602,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.22679173946381</v>
+        <v>1.2267918586731</v>
       </c>
       <c r="H1077" t="n">
         <v>359736</v>
@@ -31631,7 +31631,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.17760443687439</v>
+        <v>1.1776043176651</v>
       </c>
       <c r="H1078" t="n">
         <v>204338</v>
@@ -31660,7 +31660,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.13854396343231</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1079" t="n">
         <v>243445</v>
@@ -31747,7 +31747,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1082" t="n">
         <v>144468</v>
@@ -31776,7 +31776,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1083" t="n">
         <v>108764</v>
@@ -31921,7 +31921,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1088" t="n">
         <v>216163</v>
@@ -31979,7 +31979,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.20509159564972</v>
+        <v>1.20509147644043</v>
       </c>
       <c r="H1090" t="n">
         <v>122954</v>
@@ -32008,7 +32008,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.20653820037842</v>
+        <v>1.20653831958771</v>
       </c>
       <c r="H1091" t="n">
         <v>97285</v>
@@ -32269,7 +32269,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1100" t="n">
         <v>41271</v>
@@ -32327,7 +32327,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.15156400203705</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1102" t="n">
         <v>88940</v>
@@ -32414,7 +32414,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.1240770816803</v>
+        <v>1.12407696247101</v>
       </c>
       <c r="H1105" t="n">
         <v>152349</v>
@@ -32443,7 +32443,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1106" t="n">
         <v>214071</v>
@@ -32472,7 +32472,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318915843964</v>
+        <v>1.05318903923035</v>
       </c>
       <c r="H1107" t="n">
         <v>149211</v>
@@ -32501,7 +32501,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.0242555141449</v>
+        <v>1.02425539493561</v>
       </c>
       <c r="H1108" t="n">
         <v>254021</v>
@@ -32559,7 +32559,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.02714896202087</v>
+        <v>1.02714884281158</v>
       </c>
       <c r="H1110" t="n">
         <v>107166</v>
@@ -32646,7 +32646,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.985194742679596</v>
+        <v>0.985194802284241</v>
       </c>
       <c r="H1113" t="n">
         <v>128951</v>
@@ -32675,7 +32675,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428243160248</v>
+        <v>0.992428302764893</v>
       </c>
       <c r="H1114" t="n">
         <v>168726</v>
@@ -32704,7 +32704,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.0430623292923</v>
+        <v>1.04306244850159</v>
       </c>
       <c r="H1115" t="n">
         <v>194795</v>
@@ -32762,7 +32762,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186950206757</v>
       </c>
       <c r="H1117" t="n">
         <v>1781957</v>
@@ -32849,7 +32849,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1120" t="n">
         <v>352921</v>
@@ -32907,7 +32907,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011739730835</v>
+        <v>1.15011727809906</v>
       </c>
       <c r="H1122" t="n">
         <v>444295</v>
@@ -32965,7 +32965,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1124" t="n">
         <v>675402</v>
@@ -32994,7 +32994,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1125" t="n">
         <v>636837</v>
@@ -33023,7 +33023,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.19641149044037</v>
+        <v>1.19641137123108</v>
       </c>
       <c r="H1126" t="n">
         <v>400827</v>
@@ -33052,7 +33052,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.18917798995972</v>
+        <v>1.18917787075043</v>
       </c>
       <c r="H1127" t="n">
         <v>341827</v>
@@ -33081,7 +33081,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.09658980369568</v>
+        <v>1.09658992290497</v>
       </c>
       <c r="H1128" t="n">
         <v>569514</v>
@@ -33110,7 +33110,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08212304115295</v>
+        <v>1.08212292194366</v>
       </c>
       <c r="H1129" t="n">
         <v>419381</v>
@@ -33139,7 +33139,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1130" t="n">
         <v>250136</v>
@@ -33226,7 +33226,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1133" t="n">
         <v>140955</v>
@@ -33255,7 +33255,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.12263035774231</v>
+        <v>1.1226304769516</v>
       </c>
       <c r="H1134" t="n">
         <v>364632</v>
@@ -33284,7 +33284,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382330417633</v>
+        <v>1.10382342338562</v>
       </c>
       <c r="H1135" t="n">
         <v>163559</v>
@@ -33313,7 +33313,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.125523686409</v>
+        <v>1.12552356719971</v>
       </c>
       <c r="H1136" t="n">
         <v>207095</v>
@@ -33342,7 +33342,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.09514331817627</v>
+        <v>1.09514319896698</v>
       </c>
       <c r="H1137" t="n">
         <v>145504</v>
@@ -33371,7 +33371,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237669944763</v>
+        <v>1.10237658023834</v>
       </c>
       <c r="H1138" t="n">
         <v>192526</v>
@@ -33400,7 +33400,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.05608260631561</v>
+        <v>1.0560827255249</v>
       </c>
       <c r="H1139" t="n">
         <v>310095</v>
@@ -33429,7 +33429,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.07633626461029</v>
+        <v>1.076336145401</v>
       </c>
       <c r="H1140" t="n">
         <v>134302</v>
@@ -33458,7 +33458,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.06042265892029</v>
+        <v>1.060422539711</v>
       </c>
       <c r="H1141" t="n">
         <v>213541</v>
@@ -33516,7 +33516,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.15156400203705</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1143" t="n">
         <v>651459</v>
@@ -33574,7 +33574,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.11395013332367</v>
+        <v>1.11395001411438</v>
       </c>
       <c r="H1145" t="n">
         <v>289061</v>
@@ -33632,7 +33632,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1147" t="n">
         <v>313392</v>
@@ -33661,7 +33661,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476283073425</v>
+        <v>1.06476259231567</v>
       </c>
       <c r="H1148" t="n">
         <v>229091</v>
@@ -33777,7 +33777,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1152" t="n">
         <v>149121</v>
@@ -33806,7 +33806,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1153" t="n">
         <v>146621</v>
@@ -33922,7 +33922,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.0748895406723</v>
+        <v>1.07488965988159</v>
       </c>
       <c r="H1157" t="n">
         <v>172984</v>
@@ -33951,7 +33951,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186950206757</v>
       </c>
       <c r="H1158" t="n">
         <v>208272</v>
@@ -33980,7 +33980,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595589637756</v>
+        <v>1.04595565795898</v>
       </c>
       <c r="H1159" t="n">
         <v>160290</v>
@@ -34125,7 +34125,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088369369507</v>
+        <v>0.988088250160217</v>
       </c>
       <c r="H1164" t="n">
         <v>137388</v>
@@ -34154,7 +34154,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.975068032741547</v>
+        <v>0.975068092346191</v>
       </c>
       <c r="H1165" t="n">
         <v>149823</v>
@@ -34212,7 +34212,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.01702213287354</v>
+        <v>1.01702201366425</v>
       </c>
       <c r="H1167" t="n">
         <v>307311</v>
@@ -34241,7 +34241,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.0083419084549</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1168" t="n">
         <v>267115</v>
@@ -34270,7 +34270,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088369369507</v>
+        <v>0.988088250160217</v>
       </c>
       <c r="H1169" t="n">
         <v>318607</v>
@@ -34299,7 +34299,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321750640869</v>
+        <v>0.995321810245514</v>
       </c>
       <c r="H1170" t="n">
         <v>284109</v>
@@ -34328,7 +34328,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1171" t="n">
         <v>267333</v>
@@ -34357,7 +34357,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.01702213287354</v>
+        <v>1.01702201366425</v>
       </c>
       <c r="H1172" t="n">
         <v>246499</v>
@@ -34386,7 +34386,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1173" t="n">
         <v>251274</v>
@@ -34415,7 +34415,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.0083419084549</v>
+        <v>1.00834202766418</v>
       </c>
       <c r="H1174" t="n">
         <v>183078</v>
@@ -34444,7 +34444,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.986641585826874</v>
+        <v>0.986641526222229</v>
       </c>
       <c r="H1175" t="n">
         <v>123963</v>
@@ -34473,7 +34473,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.985194742679596</v>
+        <v>0.985194802284241</v>
       </c>
       <c r="H1176" t="n">
         <v>165512</v>
@@ -34502,7 +34502,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.97651469707489</v>
+        <v>0.976514756679535</v>
       </c>
       <c r="H1177" t="n">
         <v>195958</v>
@@ -34647,7 +34647,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.967834532260895</v>
+        <v>0.967834711074829</v>
       </c>
       <c r="H1182" t="n">
         <v>267761</v>
@@ -34676,7 +34676,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1183" t="n">
         <v>281167</v>
@@ -34705,7 +34705,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047874927521</v>
+        <v>0.962047815322876</v>
       </c>
       <c r="H1184" t="n">
         <v>241006</v>
@@ -34792,7 +34792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880551338196</v>
+        <v>0.925880670547485</v>
       </c>
       <c r="H1187" t="n">
         <v>573190</v>
@@ -34821,7 +34821,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1188" t="n">
         <v>555967</v>
@@ -34850,7 +34850,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.94468754529953</v>
+        <v>0.944687604904175</v>
       </c>
       <c r="H1189" t="n">
         <v>485261</v>
@@ -34879,7 +34879,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.94468754529953</v>
+        <v>0.944687604904175</v>
       </c>
       <c r="H1190" t="n">
         <v>152429</v>
@@ -34937,7 +34937,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900887966156</v>
+        <v>0.938900828361511</v>
       </c>
       <c r="H1192" t="n">
         <v>194055</v>
@@ -34966,7 +34966,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.930220723152161</v>
+        <v>0.930220663547516</v>
       </c>
       <c r="H1193" t="n">
         <v>285073</v>
@@ -34995,7 +34995,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.930220723152161</v>
+        <v>0.930220663547516</v>
       </c>
       <c r="H1194" t="n">
         <v>248063</v>
@@ -35024,7 +35024,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.921540677547455</v>
+        <v>0.921540558338165</v>
       </c>
       <c r="H1195" t="n">
         <v>289851</v>
@@ -35111,7 +35111,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.891160130500793</v>
+        <v>0.891160070896149</v>
       </c>
       <c r="H1198" t="n">
         <v>368604</v>
@@ -35198,7 +35198,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093834400177</v>
+        <v>0.920093953609467</v>
       </c>
       <c r="H1201" t="n">
         <v>504293</v>
@@ -35285,7 +35285,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1204" t="n">
         <v>232364</v>
@@ -35343,7 +35343,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.88971334695816</v>
+        <v>0.88971346616745</v>
       </c>
       <c r="H1206" t="n">
         <v>196518</v>
@@ -35372,7 +35372,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093834400177</v>
+        <v>0.920093953609467</v>
       </c>
       <c r="H1207" t="n">
         <v>363479</v>
@@ -35401,7 +35401,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1208" t="n">
         <v>255998</v>
@@ -35430,7 +35430,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1209" t="n">
         <v>107552</v>
@@ -35459,7 +35459,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928774118423462</v>
+        <v>0.928773999214172</v>
       </c>
       <c r="H1210" t="n">
         <v>89660</v>
@@ -35488,7 +35488,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601091384888</v>
+        <v>0.960601150989532</v>
       </c>
       <c r="H1211" t="n">
         <v>668739</v>
@@ -35517,7 +35517,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.97651469707489</v>
+        <v>0.976514756679535</v>
       </c>
       <c r="H1212" t="n">
         <v>642364</v>
@@ -35546,7 +35546,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.989534854888916</v>
+        <v>0.98953503370285</v>
       </c>
       <c r="H1213" t="n">
         <v>306233</v>
@@ -35633,7 +35633,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.918647110462189</v>
+        <v>0.918647229671478</v>
       </c>
       <c r="H1216" t="n">
         <v>231495</v>
@@ -35662,7 +35662,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753781795502</v>
+        <v>0.915753841400146</v>
       </c>
       <c r="H1217" t="n">
         <v>178785</v>
@@ -35691,7 +35691,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246465206146</v>
+        <v>0.875246644020081</v>
       </c>
       <c r="H1218" t="n">
         <v>276978</v>
@@ -35720,7 +35720,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1219" t="n">
         <v>154359</v>
@@ -35749,7 +35749,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1220" t="n">
         <v>238072</v>
@@ -35807,7 +35807,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.840525925159454</v>
+        <v>0.840525984764099</v>
       </c>
       <c r="H1222" t="n">
         <v>361515</v>
@@ -35865,7 +35865,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.824612379074097</v>
+        <v>0.824612498283386</v>
       </c>
       <c r="H1224" t="n">
         <v>195845</v>
@@ -35894,7 +35894,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.826059103012085</v>
+        <v>0.826058983802795</v>
       </c>
       <c r="H1225" t="n">
         <v>209693</v>
@@ -35952,7 +35952,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871740818024</v>
+        <v>0.776871681213379</v>
       </c>
       <c r="H1227" t="n">
         <v>366061</v>
@@ -36039,7 +36039,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.77108496427536</v>
+        <v>0.771084904670715</v>
       </c>
       <c r="H1230" t="n">
         <v>254758</v>
@@ -36097,7 +36097,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211793422699</v>
+        <v>0.781211733818054</v>
       </c>
       <c r="H1232" t="n">
         <v>238451</v>
@@ -36126,7 +36126,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191576004028</v>
+        <v>0.768191695213318</v>
       </c>
       <c r="H1233" t="n">
         <v>672823</v>
@@ -36184,7 +36184,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.805805444717407</v>
+        <v>0.805805504322052</v>
       </c>
       <c r="H1235" t="n">
         <v>493728</v>
@@ -36242,7 +36242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079201221466</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1237" t="n">
         <v>399300</v>
@@ -36271,7 +36271,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.850652873516083</v>
+        <v>0.850652813911438</v>
       </c>
       <c r="H1238" t="n">
         <v>314246</v>
@@ -36300,7 +36300,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799681663513</v>
       </c>
       <c r="H1239" t="n">
         <v>463886</v>
@@ -36329,7 +36329,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1240" t="n">
         <v>465758</v>
@@ -36387,7 +36387,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1242" t="n">
         <v>529118</v>
@@ -36416,7 +36416,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.895500302314758</v>
+        <v>0.895500242710114</v>
       </c>
       <c r="H1243" t="n">
         <v>309302</v>
@@ -36561,7 +36561,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967184066772</v>
+        <v>0.909967005252838</v>
       </c>
       <c r="H1248" t="n">
         <v>283507</v>
@@ -36619,7 +36619,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.863672971725464</v>
+        <v>0.863673090934753</v>
       </c>
       <c r="H1250" t="n">
         <v>2118508</v>
@@ -36677,7 +36677,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1252" t="n">
         <v>343874</v>
@@ -36706,7 +36706,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.895500302314758</v>
+        <v>0.895500242710114</v>
       </c>
       <c r="H1253" t="n">
         <v>276903</v>
@@ -36735,7 +36735,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.89405345916748</v>
+        <v>0.894053339958191</v>
       </c>
       <c r="H1254" t="n">
         <v>333750</v>
@@ -36764,7 +36764,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.879586637020111</v>
+        <v>0.879586517810822</v>
       </c>
       <c r="H1255" t="n">
         <v>304340</v>
@@ -36822,7 +36822,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.88971334695816</v>
+        <v>0.88971346616745</v>
       </c>
       <c r="H1257" t="n">
         <v>276597</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693308353424</v>
+        <v>0.876693189144135</v>
       </c>
       <c r="H1258" t="n">
         <v>265557</v>
@@ -36967,7 +36967,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246465206146</v>
+        <v>0.875246644020081</v>
       </c>
       <c r="H1262" t="n">
         <v>261444</v>
@@ -36996,7 +36996,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1263" t="n">
         <v>171832</v>
@@ -37025,7 +37025,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.885373294353485</v>
+        <v>0.88537323474884</v>
       </c>
       <c r="H1264" t="n">
         <v>229764</v>
@@ -37054,7 +37054,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.86222642660141</v>
+        <v>0.86222630739212</v>
       </c>
       <c r="H1265" t="n">
         <v>389130</v>
@@ -37170,7 +37170,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1269" t="n">
         <v>264575</v>
@@ -37315,7 +37315,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733683586121</v>
+        <v>0.902733743190765</v>
       </c>
       <c r="H1274" t="n">
         <v>125768</v>
@@ -37344,7 +37344,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.891160130500793</v>
+        <v>0.891160070896149</v>
       </c>
       <c r="H1275" t="n">
         <v>199794</v>
@@ -37373,7 +37373,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.881033420562744</v>
+        <v>0.881033360958099</v>
       </c>
       <c r="H1276" t="n">
         <v>275751</v>
@@ -37489,7 +37489,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.84920608997345</v>
+        <v>0.849206149578094</v>
       </c>
       <c r="H1280" t="n">
         <v>159959</v>
@@ -37518,7 +37518,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079201221466</v>
+        <v>0.839079260826111</v>
       </c>
       <c r="H1281" t="n">
         <v>188343</v>
@@ -37547,7 +37547,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.840525925159454</v>
+        <v>0.840525984764099</v>
       </c>
       <c r="H1282" t="n">
         <v>192827</v>
@@ -37576,7 +37576,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.843419373035431</v>
+        <v>0.843419432640076</v>
       </c>
       <c r="H1283" t="n">
         <v>381437</v>
@@ -37634,7 +37634,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.836185991764069</v>
+        <v>0.836186051368713</v>
       </c>
       <c r="H1285" t="n">
         <v>383548</v>
@@ -37663,7 +37663,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.826059103012085</v>
+        <v>0.826058983802795</v>
       </c>
       <c r="H1286" t="n">
         <v>345204</v>
@@ -37692,7 +37692,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1287" t="n">
         <v>307350</v>
@@ -37721,7 +37721,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1288" t="n">
         <v>234994</v>
@@ -37750,7 +37750,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1289" t="n">
         <v>211199</v>
@@ -37779,7 +37779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845879554749</v>
+        <v>0.831845760345459</v>
       </c>
       <c r="H1290" t="n">
         <v>153639</v>
@@ -37808,7 +37808,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1291" t="n">
         <v>84133</v>
@@ -37837,7 +37837,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312701702118</v>
+        <v>0.846312761306763</v>
       </c>
       <c r="H1292" t="n">
         <v>193484</v>
@@ -37895,7 +37895,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799681663513</v>
       </c>
       <c r="H1294" t="n">
         <v>252193</v>
@@ -37924,7 +37924,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.878139853477478</v>
+        <v>0.878139913082123</v>
       </c>
       <c r="H1295" t="n">
         <v>546482</v>
@@ -37953,7 +37953,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.946134388446808</v>
+        <v>0.946134209632874</v>
       </c>
       <c r="H1296" t="n">
         <v>1951196</v>
@@ -37982,7 +37982,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.975068032741547</v>
+        <v>0.975068092346191</v>
       </c>
       <c r="H1297" t="n">
         <v>1511134</v>
@@ -38011,7 +38011,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.01991534233093</v>
+        <v>1.01991546154022</v>
       </c>
       <c r="H1298" t="n">
         <v>959878</v>
@@ -38156,7 +38156,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408204555511</v>
+        <v>0.979408144950867</v>
       </c>
       <c r="H1303" t="n">
         <v>386487</v>
@@ -38243,7 +38243,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186950206757</v>
       </c>
       <c r="H1306" t="n">
         <v>1146881</v>
@@ -38330,7 +38330,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.05029582977295</v>
+        <v>1.05029594898224</v>
       </c>
       <c r="H1309" t="n">
         <v>555685</v>
@@ -38533,7 +38533,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.989534854888916</v>
+        <v>0.98953503370285</v>
       </c>
       <c r="H1316" t="n">
         <v>242430</v>
@@ -38620,7 +38620,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.0416157245636</v>
+        <v>1.04161560535431</v>
       </c>
       <c r="H1319" t="n">
         <v>236404</v>
@@ -38707,7 +38707,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1322" t="n">
         <v>506082</v>
@@ -38823,7 +38823,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1326" t="n">
         <v>1612557</v>
@@ -38910,7 +38910,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.1587975025177</v>
+        <v>1.15879762172699</v>
       </c>
       <c r="H1329" t="n">
         <v>259241</v>
@@ -38939,7 +38939,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458427906036</v>
+        <v>1.16458439826965</v>
       </c>
       <c r="H1330" t="n">
         <v>469768</v>
@@ -38968,7 +38968,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1331" t="n">
         <v>534133</v>
@@ -38997,7 +38997,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16603088378906</v>
+        <v>1.16603076457977</v>
       </c>
       <c r="H1332" t="n">
         <v>471250</v>
@@ -39200,7 +39200,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1339" t="n">
         <v>508534</v>
@@ -39229,7 +39229,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.18339133262634</v>
+        <v>1.18339121341705</v>
       </c>
       <c r="H1340" t="n">
         <v>415370</v>
@@ -39258,7 +39258,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1341" t="n">
         <v>170083</v>
@@ -39287,7 +39287,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.16603088378906</v>
+        <v>1.16603076457977</v>
       </c>
       <c r="H1342" t="n">
         <v>257345</v>
@@ -39316,7 +39316,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1343" t="n">
         <v>476067</v>
@@ -39374,7 +39374,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.15156400203705</v>
+        <v>1.15156412124634</v>
       </c>
       <c r="H1345" t="n">
         <v>402831</v>
@@ -39490,7 +39490,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.30491292476654</v>
+        <v>1.30491304397583</v>
       </c>
       <c r="H1349" t="n">
         <v>305433</v>
@@ -39635,7 +39635,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912614822388</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1354" t="n">
         <v>744694</v>
@@ -39693,7 +39693,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912614822388</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1356" t="n">
         <v>193651</v>
@@ -39722,7 +39722,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635976791382</v>
+        <v>1.30635964870453</v>
       </c>
       <c r="H1357" t="n">
         <v>181760</v>
@@ -39780,7 +39780,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1359" t="n">
         <v>1365631</v>
@@ -39809,7 +39809,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1360" t="n">
         <v>612054</v>
@@ -39867,7 +39867,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.45030534267426</v>
+        <v>1.45030522346497</v>
       </c>
       <c r="H1362" t="n">
         <v>734134</v>
@@ -39925,7 +39925,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.42932820320129</v>
+        <v>1.429328083992</v>
       </c>
       <c r="H1364" t="n">
         <v>2260128</v>
@@ -39954,7 +39954,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.40762782096863</v>
+        <v>1.40762794017792</v>
       </c>
       <c r="H1365" t="n">
         <v>1106457</v>
@@ -40012,7 +40012,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.39894783496857</v>
+        <v>1.39894771575928</v>
       </c>
       <c r="H1367" t="n">
         <v>239547</v>
@@ -40070,7 +40070,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1369" t="n">
         <v>249082</v>
@@ -40157,7 +40157,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.36376464366913</v>
+        <v>1.36376452445984</v>
       </c>
       <c r="H1372" t="n">
         <v>346170</v>
@@ -40215,7 +40215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.3814948797226</v>
+        <v>1.38149499893188</v>
       </c>
       <c r="H1374" t="n">
         <v>236076</v>
@@ -40331,7 +40331,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1378" t="n">
         <v>217402</v>
@@ -40360,7 +40360,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.4391188621521</v>
+        <v>1.43911874294281</v>
       </c>
       <c r="H1379" t="n">
         <v>239859</v>
@@ -40418,7 +40418,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1381" t="n">
         <v>159305</v>
@@ -40447,7 +40447,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1382" t="n">
         <v>287514</v>
@@ -40476,7 +40476,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537173748016</v>
+        <v>1.45537161827087</v>
       </c>
       <c r="H1383" t="n">
         <v>131183</v>
@@ -40505,7 +40505,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.45684921741486</v>
+        <v>1.45684933662415</v>
       </c>
       <c r="H1384" t="n">
         <v>91908</v>
@@ -40534,7 +40534,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1385" t="n">
         <v>278517</v>
@@ -40592,7 +40592,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.41991102695465</v>
+        <v>1.41991090774536</v>
       </c>
       <c r="H1387" t="n">
         <v>150398</v>
@@ -40621,7 +40621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.36671948432922</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1388" t="n">
         <v>291702</v>
@@ -40679,7 +40679,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.34160149097443</v>
+        <v>1.34160161018372</v>
       </c>
       <c r="H1390" t="n">
         <v>161663</v>
@@ -40737,7 +40737,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.3327362537384</v>
+        <v>1.33273637294769</v>
       </c>
       <c r="H1392" t="n">
         <v>230681</v>
@@ -40795,7 +40795,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.29432034492493</v>
+        <v>1.29432046413422</v>
       </c>
       <c r="H1394" t="n">
         <v>728450</v>
@@ -40882,7 +40882,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.25294935703278</v>
+        <v>1.25294947624207</v>
       </c>
       <c r="H1397" t="n">
         <v>236575</v>
@@ -40911,7 +40911,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.23817408084869</v>
+        <v>1.23817420005798</v>
       </c>
       <c r="H1398" t="n">
         <v>288738</v>
@@ -41027,7 +41027,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.18646037578583</v>
+        <v>1.18646049499512</v>
       </c>
       <c r="H1402" t="n">
         <v>319571</v>
@@ -41114,7 +41114,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.21896600723267</v>
+        <v>1.21896612644196</v>
       </c>
       <c r="H1405" t="n">
         <v>286470</v>
@@ -41143,7 +41143,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.21157836914062</v>
+        <v>1.21157848834991</v>
       </c>
       <c r="H1406" t="n">
         <v>146658</v>
@@ -41259,7 +41259,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622403144836</v>
       </c>
       <c r="H1410" t="n">
         <v>139750</v>
@@ -41288,7 +41288,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.16725254058838</v>
+        <v>1.16725242137909</v>
       </c>
       <c r="H1411" t="n">
         <v>286124</v>
@@ -41317,7 +41317,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.16134226322174</v>
+        <v>1.16134238243103</v>
       </c>
       <c r="H1412" t="n">
         <v>106478</v>
@@ -41491,7 +41491,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622403144836</v>
       </c>
       <c r="H1418" t="n">
         <v>323570</v>
@@ -41578,7 +41578,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.27954506874084</v>
+        <v>1.27954494953156</v>
       </c>
       <c r="H1421" t="n">
         <v>855837</v>
@@ -41607,7 +41607,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.27067983150482</v>
+        <v>1.27067995071411</v>
       </c>
       <c r="H1422" t="n">
         <v>523160</v>
@@ -41694,7 +41694,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.25738203525543</v>
+        <v>1.25738215446472</v>
       </c>
       <c r="H1425" t="n">
         <v>180384</v>
@@ -41723,7 +41723,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.27806746959686</v>
+        <v>1.27806758880615</v>
       </c>
       <c r="H1426" t="n">
         <v>138463</v>
@@ -41752,7 +41752,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.28250002861023</v>
+        <v>1.28250014781952</v>
       </c>
       <c r="H1427" t="n">
         <v>384014</v>
@@ -41781,7 +41781,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.2839777469635</v>
+        <v>1.28397762775421</v>
       </c>
       <c r="H1428" t="n">
         <v>139450</v>
@@ -41810,7 +41810,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.24851679801941</v>
+        <v>1.2485169172287</v>
       </c>
       <c r="H1429" t="n">
         <v>265485</v>
@@ -41955,7 +41955,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1434" t="n">
         <v>300625</v>
@@ -42013,7 +42013,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614066123962</v>
+        <v>1.30614078044891</v>
       </c>
       <c r="H1436" t="n">
         <v>371377</v>
@@ -42100,7 +42100,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.41991102695465</v>
+        <v>1.41991090774536</v>
       </c>
       <c r="H1439" t="n">
         <v>194067</v>
@@ -42129,7 +42129,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.39183759689331</v>
+        <v>1.3918377161026</v>
       </c>
       <c r="H1440" t="n">
         <v>280527</v>
@@ -42216,7 +42216,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.36671948432922</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1443" t="n">
         <v>203945</v>
@@ -42274,7 +42274,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682621479034</v>
       </c>
       <c r="H1445" t="n">
         <v>537192</v>
@@ -42506,7 +42506,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.24556171894073</v>
+        <v>1.24556183815002</v>
       </c>
       <c r="H1453" t="n">
         <v>671330</v>
@@ -42535,7 +42535,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.24703931808472</v>
+        <v>1.24703919887543</v>
       </c>
       <c r="H1454" t="n">
         <v>311006</v>
@@ -42564,7 +42564,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.24112904071808</v>
+        <v>1.24112915992737</v>
       </c>
       <c r="H1455" t="n">
         <v>333161</v>
@@ -42593,7 +42593,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.25738203525543</v>
+        <v>1.25738215446472</v>
       </c>
       <c r="H1456" t="n">
         <v>404235</v>
@@ -42622,7 +42622,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.27954506874084</v>
+        <v>1.27954494953156</v>
       </c>
       <c r="H1457" t="n">
         <v>374481</v>
@@ -42796,7 +42796,7 @@
         <v>1.72599995136261</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.27511250972748</v>
+        <v>1.27511239051819</v>
       </c>
       <c r="H1463" t="n">
         <v>188738</v>
@@ -42825,7 +42825,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.27954506874084</v>
+        <v>1.27954494953156</v>
       </c>
       <c r="H1464" t="n">
         <v>82983</v>
@@ -42854,7 +42854,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.2839777469635</v>
+        <v>1.28397762775421</v>
       </c>
       <c r="H1465" t="n">
         <v>181638</v>
@@ -42941,7 +42941,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.27806746959686</v>
+        <v>1.27806758880615</v>
       </c>
       <c r="H1468" t="n">
         <v>132333</v>
@@ -42999,7 +42999,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.34160149097443</v>
+        <v>1.34160161018372</v>
       </c>
       <c r="H1470" t="n">
         <v>398939</v>
@@ -43086,7 +43086,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1473" t="n">
         <v>224203</v>
@@ -43115,7 +43115,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.39036023616791</v>
+        <v>1.39036011695862</v>
       </c>
       <c r="H1474" t="n">
         <v>136320</v>
@@ -43202,7 +43202,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.40513563156128</v>
+        <v>1.40513551235199</v>
       </c>
       <c r="H1477" t="n">
         <v>185218</v>
@@ -43260,7 +43260,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.39036023616791</v>
+        <v>1.39036011695862</v>
       </c>
       <c r="H1479" t="n">
         <v>88402</v>
@@ -43434,7 +43434,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558484077454</v>
       </c>
       <c r="H1485" t="n">
         <v>148734</v>
@@ -43492,7 +43492,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.37853991985321</v>
+        <v>1.3785400390625</v>
       </c>
       <c r="H1487" t="n">
         <v>393472</v>
@@ -43579,7 +43579,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.4391188621521</v>
+        <v>1.43911874294281</v>
       </c>
       <c r="H1490" t="n">
         <v>184337</v>
@@ -43608,7 +43608,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.52186071872711</v>
+        <v>1.5218608379364</v>
       </c>
       <c r="H1491" t="n">
         <v>963778</v>
@@ -43637,7 +43637,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.54771757125854</v>
+        <v>1.54771769046783</v>
       </c>
       <c r="H1492" t="n">
         <v>586422</v>
@@ -43666,7 +43666,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.55879902839661</v>
+        <v>1.5587991476059</v>
       </c>
       <c r="H1493" t="n">
         <v>728617</v>
@@ -43724,7 +43724,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.55879902839661</v>
+        <v>1.5587991476059</v>
       </c>
       <c r="H1495" t="n">
         <v>407217</v>
@@ -43811,7 +43811,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.44798409938812</v>
+        <v>1.44798398017883</v>
       </c>
       <c r="H1498" t="n">
         <v>355414</v>
@@ -43840,7 +43840,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.4627593755722</v>
+        <v>1.46275949478149</v>
       </c>
       <c r="H1499" t="n">
         <v>297409</v>
@@ -43869,7 +43869,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1500" t="n">
         <v>271549</v>
@@ -44043,7 +44043,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.36376464366913</v>
+        <v>1.36376452445984</v>
       </c>
       <c r="H1506" t="n">
         <v>133446</v>
@@ -44101,7 +44101,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682621479034</v>
       </c>
       <c r="H1508" t="n">
         <v>153178</v>
@@ -44130,7 +44130,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.34160149097443</v>
+        <v>1.34160161018372</v>
       </c>
       <c r="H1509" t="n">
         <v>120342</v>
@@ -44159,7 +44159,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.34455668926239</v>
+        <v>1.3445565700531</v>
       </c>
       <c r="H1510" t="n">
         <v>116822</v>
@@ -44304,7 +44304,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682621479034</v>
       </c>
       <c r="H1515" t="n">
         <v>144985</v>
@@ -44362,7 +44362,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.34455668926239</v>
+        <v>1.3445565700531</v>
       </c>
       <c r="H1517" t="n">
         <v>89004</v>
@@ -44478,7 +44478,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1521" t="n">
         <v>187418</v>
@@ -44507,7 +44507,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.45980429649353</v>
+        <v>1.45980417728424</v>
       </c>
       <c r="H1522" t="n">
         <v>604333</v>
@@ -44942,7 +44942,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.54402375221252</v>
+        <v>1.54402363300323</v>
       </c>
       <c r="H1537" t="n">
         <v>294711</v>
@@ -45000,7 +45000,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.52186071872711</v>
+        <v>1.5218608379364</v>
       </c>
       <c r="H1539" t="n">
         <v>145076</v>
@@ -45116,7 +45116,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1543" t="n">
         <v>303306</v>
@@ -45174,7 +45174,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.40513563156128</v>
+        <v>1.40513551235199</v>
       </c>
       <c r="H1545" t="n">
         <v>140913</v>
@@ -45232,7 +45232,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1547" t="n">
         <v>154493</v>
@@ -45290,7 +45290,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1549" t="n">
         <v>136807</v>
@@ -45348,7 +45348,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.39183759689331</v>
+        <v>1.3918377161026</v>
       </c>
       <c r="H1551" t="n">
         <v>99853</v>
@@ -45493,7 +45493,7 @@
         <v>1.92400002479553</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.42138838768005</v>
+        <v>1.42138850688934</v>
       </c>
       <c r="H1556" t="n">
         <v>116333</v>
@@ -45580,7 +45580,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.4169557094574</v>
+        <v>1.41695582866669</v>
       </c>
       <c r="H1559" t="n">
         <v>112669</v>
@@ -45609,7 +45609,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.39036023616791</v>
+        <v>1.39036011695862</v>
       </c>
       <c r="H1560" t="n">
         <v>118655</v>
@@ -45638,7 +45638,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558484077454</v>
       </c>
       <c r="H1561" t="n">
         <v>147702</v>
@@ -45754,7 +45754,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.27659010887146</v>
+        <v>1.27658998966217</v>
       </c>
       <c r="H1565" t="n">
         <v>563690</v>
@@ -45812,7 +45812,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.24112904071808</v>
+        <v>1.24112915992737</v>
       </c>
       <c r="H1567" t="n">
         <v>290390</v>
@@ -45986,7 +45986,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.21157836914062</v>
+        <v>1.21157848834991</v>
       </c>
       <c r="H1573" t="n">
         <v>417935</v>
@@ -46015,7 +46015,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.24556171894073</v>
+        <v>1.24556183815002</v>
       </c>
       <c r="H1574" t="n">
         <v>232917</v>
@@ -46189,7 +46189,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.27954506874084</v>
+        <v>1.27954494953156</v>
       </c>
       <c r="H1580" t="n">
         <v>74635</v>
@@ -46305,7 +46305,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682621479034</v>
       </c>
       <c r="H1584" t="n">
         <v>111356</v>
@@ -46334,7 +46334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1585" t="n">
         <v>261659</v>
@@ -46421,7 +46421,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.54771757125854</v>
+        <v>1.54771769046783</v>
       </c>
       <c r="H1588" t="n">
         <v>1110225</v>
@@ -46479,7 +46479,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.65853261947632</v>
+        <v>1.65853250026703</v>
       </c>
       <c r="H1590" t="n">
         <v>853412</v>
@@ -46508,7 +46508,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.63636946678162</v>
+        <v>1.63636958599091</v>
       </c>
       <c r="H1591" t="n">
         <v>519821</v>
@@ -46537,7 +46537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.64745128154755</v>
+        <v>1.64745104312897</v>
       </c>
       <c r="H1592" t="n">
         <v>488837</v>
@@ -46653,7 +46653,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.69177722930908</v>
+        <v>1.69177711009979</v>
       </c>
       <c r="H1596" t="n">
         <v>513055</v>
@@ -46711,7 +46711,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1598" t="n">
         <v>516825</v>
@@ -46740,7 +46740,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1599" t="n">
         <v>358721</v>
@@ -46798,7 +46798,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1601" t="n">
         <v>293308</v>
@@ -46914,7 +46914,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.71024632453918</v>
+        <v>1.71024644374847</v>
       </c>
       <c r="H1605" t="n">
         <v>285312</v>
@@ -46943,7 +46943,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.70285868644714</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1606" t="n">
         <v>652953</v>
@@ -46972,7 +46972,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.69547092914581</v>
+        <v>1.6954710483551</v>
       </c>
       <c r="H1607" t="n">
         <v>254784</v>
@@ -47146,7 +47146,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.63636946678162</v>
+        <v>1.63636958599091</v>
       </c>
       <c r="H1613" t="n">
         <v>180456</v>
@@ -47204,7 +47204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924847602844</v>
+        <v>1.52924835681915</v>
       </c>
       <c r="H1615" t="n">
         <v>245261</v>
@@ -47233,7 +47233,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.55879902839661</v>
+        <v>1.5587991476059</v>
       </c>
       <c r="H1616" t="n">
         <v>147876</v>
@@ -47349,7 +47349,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.64006352424622</v>
+        <v>1.64006340503693</v>
       </c>
       <c r="H1620" t="n">
         <v>229999</v>
@@ -47407,7 +47407,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.677001953125</v>
+        <v>1.67700171470642</v>
       </c>
       <c r="H1622" t="n">
         <v>296489</v>
@@ -47436,7 +47436,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.64745128154755</v>
+        <v>1.64745104312897</v>
       </c>
       <c r="H1623" t="n">
         <v>712219</v>
@@ -47523,7 +47523,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.61774921417236</v>
+        <v>1.61774933338165</v>
       </c>
       <c r="H1626" t="n">
         <v>295022</v>
@@ -47610,7 +47610,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.63380634784698</v>
+        <v>1.6338062286377</v>
       </c>
       <c r="H1629" t="n">
         <v>180001</v>
@@ -47755,7 +47755,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.62979197502136</v>
+        <v>1.62979209423065</v>
       </c>
       <c r="H1634" t="n">
         <v>134212</v>
@@ -47900,7 +47900,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.44834721088409</v>
+        <v>1.4483470916748</v>
       </c>
       <c r="H1639" t="n">
         <v>363994</v>
@@ -47958,7 +47958,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1641" t="n">
         <v>199201</v>
@@ -48016,7 +48016,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1643" t="n">
         <v>247724</v>
@@ -48132,7 +48132,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1647" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1647" t="n">
         <v>128790</v>
@@ -48161,7 +48161,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.37448465824127</v>
+        <v>1.37448477745056</v>
       </c>
       <c r="H1648" t="n">
         <v>89430</v>
@@ -48219,7 +48219,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1650" t="n">
         <v>62063</v>
@@ -48277,7 +48277,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609040737152</v>
+        <v>1.37609028816223</v>
       </c>
       <c r="H1652" t="n">
         <v>83408</v>
@@ -48335,7 +48335,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.37769615650177</v>
+        <v>1.37769603729248</v>
       </c>
       <c r="H1654" t="n">
         <v>136685</v>
@@ -48393,7 +48393,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1656" t="n">
-        <v>1.31186211109161</v>
+        <v>1.31186199188232</v>
       </c>
       <c r="H1656" t="n">
         <v>150236</v>
@@ -48451,7 +48451,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1658" t="n">
         <v>87013</v>
@@ -48509,7 +48509,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1660" t="n">
         <v>103532</v>
@@ -48538,7 +48538,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.27814221382141</v>
+        <v>1.2781423330307</v>
       </c>
       <c r="H1661" t="n">
         <v>79903</v>
@@ -48567,7 +48567,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.27653670310974</v>
+        <v>1.27653658390045</v>
       </c>
       <c r="H1662" t="n">
         <v>62267</v>
@@ -48712,7 +48712,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.44834721088409</v>
+        <v>1.4483470916748</v>
       </c>
       <c r="H1667" t="n">
         <v>287992</v>
@@ -48770,7 +48770,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.44353008270264</v>
+        <v>1.44352996349335</v>
       </c>
       <c r="H1669" t="n">
         <v>190612</v>
@@ -48828,7 +48828,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1671" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1671" t="n">
         <v>154813</v>
@@ -48886,7 +48886,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1673" t="n">
         <v>316953</v>
@@ -48915,7 +48915,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.49170136451721</v>
+        <v>1.49170124530792</v>
       </c>
       <c r="H1674" t="n">
         <v>418301</v>
@@ -49089,7 +49089,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820455551147</v>
+        <v>1.40820443630219</v>
       </c>
       <c r="H1680" t="n">
         <v>95443</v>
@@ -49118,7 +49118,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.39696455001831</v>
+        <v>1.3969646692276</v>
       </c>
       <c r="H1681" t="n">
         <v>119133</v>
@@ -49234,7 +49234,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1685" t="n">
         <v>224610</v>
@@ -49350,7 +49350,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1689" t="n">
         <v>287007</v>
@@ -49379,7 +49379,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.33434200286865</v>
+        <v>1.33434188365936</v>
       </c>
       <c r="H1690" t="n">
         <v>143753</v>
@@ -49408,7 +49408,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558200836182</v>
+        <v>1.34558188915253</v>
       </c>
       <c r="H1691" t="n">
         <v>192296</v>
@@ -49437,7 +49437,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.32791912555695</v>
+        <v>1.32791924476624</v>
       </c>
       <c r="H1692" t="n">
         <v>174564</v>
@@ -49495,7 +49495,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1694" t="n">
-        <v>1.27011382579803</v>
+        <v>1.27011370658875</v>
       </c>
       <c r="H1694" t="n">
         <v>206788</v>
@@ -49611,7 +49611,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.22997117042542</v>
+        <v>1.22997105121613</v>
       </c>
       <c r="H1698" t="n">
         <v>108022</v>
@@ -49640,7 +49640,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.22675967216492</v>
+        <v>1.22675979137421</v>
       </c>
       <c r="H1699" t="n">
         <v>58118</v>
@@ -49785,7 +49785,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.28295946121216</v>
+        <v>1.28295958042145</v>
       </c>
       <c r="H1704" t="n">
         <v>252692</v>
@@ -49814,7 +49814,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.25566232204437</v>
+        <v>1.25566244125366</v>
       </c>
       <c r="H1705" t="n">
         <v>432498</v>
@@ -49872,7 +49872,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1707" t="n">
         <v>328393</v>
@@ -49901,7 +49901,7 @@
         <v>1.5</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1708" t="n">
         <v>261982</v>
@@ -49959,7 +49959,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.14968574047089</v>
+        <v>1.14968585968018</v>
       </c>
       <c r="H1710" t="n">
         <v>182259</v>
@@ -49988,7 +49988,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.16895425319672</v>
+        <v>1.16895413398743</v>
       </c>
       <c r="H1711" t="n">
         <v>296443</v>
@@ -50017,7 +50017,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.16895425319672</v>
+        <v>1.16895413398743</v>
       </c>
       <c r="H1712" t="n">
         <v>115921</v>
@@ -50075,7 +50075,7 @@
         <v>1.43400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.15129160881042</v>
+        <v>1.15129148960114</v>
       </c>
       <c r="H1714" t="n">
         <v>239109</v>
@@ -50133,7 +50133,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.13684010505676</v>
+        <v>1.13684022426605</v>
       </c>
       <c r="H1716" t="n">
         <v>505238</v>
@@ -50191,7 +50191,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.13362872600555</v>
+        <v>1.13362860679626</v>
       </c>
       <c r="H1718" t="n">
         <v>137061</v>
@@ -50220,7 +50220,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.17216563224792</v>
+        <v>1.17216575145721</v>
       </c>
       <c r="H1719" t="n">
         <v>125543</v>
@@ -50249,7 +50249,7 @@
         <v>1.5</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1720" t="n">
         <v>173250</v>
@@ -50336,7 +50336,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.23318254947662</v>
+        <v>1.23318243026733</v>
       </c>
       <c r="H1723" t="n">
         <v>118046</v>
@@ -50394,7 +50394,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267415046692</v>
+        <v>1.20267403125763</v>
       </c>
       <c r="H1725" t="n">
         <v>200716</v>
@@ -50423,7 +50423,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.1593199968338</v>
+        <v>1.15932011604309</v>
       </c>
       <c r="H1726" t="n">
         <v>154513</v>
@@ -50452,7 +50452,7 @@
         <v>1.5</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1727" t="n">
         <v>63252</v>
@@ -50481,7 +50481,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1728" t="n">
         <v>106830</v>
@@ -50539,7 +50539,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1730" t="n">
         <v>107088</v>
@@ -50597,7 +50597,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741084575653</v>
+        <v>1.29741072654724</v>
       </c>
       <c r="H1732" t="n">
         <v>220981</v>
@@ -50655,7 +50655,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1734" t="n">
         <v>122962</v>
@@ -50771,7 +50771,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1738" t="n">
         <v>72837</v>
@@ -50829,7 +50829,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383360385895</v>
+        <v>1.30383348464966</v>
       </c>
       <c r="H1740" t="n">
         <v>63847</v>
@@ -50858,7 +50858,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1741" t="n">
         <v>362136</v>
@@ -50887,7 +50887,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.3022278547287</v>
+        <v>1.30222773551941</v>
       </c>
       <c r="H1742" t="n">
         <v>126434</v>
@@ -50916,7 +50916,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.3054393529892</v>
+        <v>1.30543947219849</v>
       </c>
       <c r="H1743" t="n">
         <v>128541</v>
@@ -50974,7 +50974,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1745" t="n">
         <v>56326</v>
@@ -51032,7 +51032,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1747" t="n">
         <v>209049</v>
@@ -51119,7 +51119,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.28938221931458</v>
+        <v>1.28938210010529</v>
       </c>
       <c r="H1750" t="n">
         <v>292273</v>
@@ -51177,7 +51177,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.23478829860687</v>
+        <v>1.23478817939758</v>
       </c>
       <c r="H1752" t="n">
         <v>120642</v>
@@ -51235,7 +51235,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1754" t="n">
         <v>268250</v>
@@ -51293,7 +51293,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1756" t="n">
         <v>58942</v>
@@ -51380,7 +51380,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1759" t="n">
         <v>207138</v>
@@ -51438,7 +51438,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.22997117042542</v>
+        <v>1.22997105121613</v>
       </c>
       <c r="H1761" t="n">
         <v>76152</v>
@@ -51467,7 +51467,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1762" t="n">
         <v>195165</v>
@@ -51525,7 +51525,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.25084519386292</v>
+        <v>1.2508453130722</v>
       </c>
       <c r="H1764" t="n">
         <v>152406</v>
@@ -51583,7 +51583,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1766" t="n">
         <v>177051</v>
@@ -51641,7 +51641,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.2139139175415</v>
+        <v>1.21391403675079</v>
       </c>
       <c r="H1768" t="n">
         <v>44622</v>
@@ -51670,7 +51670,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1769" t="n">
         <v>310689</v>
@@ -51699,7 +51699,7 @@
         <v>1.52799999713898</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.22675967216492</v>
+        <v>1.22675979137421</v>
       </c>
       <c r="H1770" t="n">
         <v>588847</v>
@@ -51728,7 +51728,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1771" t="n">
         <v>224093</v>
@@ -51757,7 +51757,7 @@
         <v>1.5</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.20427978038788</v>
+        <v>1.20427989959717</v>
       </c>
       <c r="H1772" t="n">
         <v>183258</v>
@@ -51786,7 +51786,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.18822276592255</v>
+        <v>1.18822264671326</v>
       </c>
       <c r="H1773" t="n">
         <v>267161</v>
@@ -51815,7 +51815,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1774" t="n">
         <v>131817</v>
@@ -51844,7 +51844,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18179988861084</v>
+        <v>1.18180000782013</v>
       </c>
       <c r="H1775" t="n">
         <v>99387</v>
@@ -51873,7 +51873,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.18822276592255</v>
+        <v>1.18822264671326</v>
       </c>
       <c r="H1776" t="n">
         <v>806694</v>
@@ -51902,7 +51902,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1777" t="n">
         <v>83493</v>
@@ -51931,7 +51931,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.193039894104</v>
+        <v>1.19303977489471</v>
       </c>
       <c r="H1778" t="n">
         <v>95141</v>
@@ -51960,7 +51960,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.1866170167923</v>
+        <v>1.18661713600159</v>
       </c>
       <c r="H1779" t="n">
         <v>103412</v>
@@ -51989,7 +51989,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1780" t="n">
         <v>171787</v>
@@ -52047,7 +52047,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1782" t="n">
-        <v>1.19464552402496</v>
+        <v>1.19464564323425</v>
       </c>
       <c r="H1782" t="n">
         <v>97441</v>
@@ -52105,7 +52105,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1784" t="n">
         <v>259226</v>
@@ -52163,7 +52163,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.217125415802</v>
+        <v>1.21712553501129</v>
       </c>
       <c r="H1786" t="n">
         <v>102156</v>
@@ -52221,7 +52221,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.25084519386292</v>
+        <v>1.2508453130722</v>
       </c>
       <c r="H1788" t="n">
         <v>267155</v>
@@ -52424,7 +52424,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.24923944473267</v>
+        <v>1.24923956394196</v>
       </c>
       <c r="H1795" t="n">
         <v>224358</v>
@@ -52453,7 +52453,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.247633934021</v>
+        <v>1.24763381481171</v>
       </c>
       <c r="H1796" t="n">
         <v>158009</v>
@@ -52540,7 +52540,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.23318254947662</v>
+        <v>1.23318243026733</v>
       </c>
       <c r="H1799" t="n">
         <v>58960</v>
@@ -52627,7 +52627,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.27332508563995</v>
+        <v>1.27332520484924</v>
       </c>
       <c r="H1802" t="n">
         <v>330416</v>
@@ -52656,7 +52656,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.33434200286865</v>
+        <v>1.33434188365936</v>
       </c>
       <c r="H1803" t="n">
         <v>1159198</v>
@@ -52714,7 +52714,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470762729645</v>
       </c>
       <c r="H1805" t="n">
         <v>309868</v>
@@ -52743,7 +52743,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1806" t="n">
         <v>302074</v>
@@ -52859,7 +52859,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.42586731910706</v>
+        <v>1.42586719989777</v>
       </c>
       <c r="H1810" t="n">
         <v>259535</v>
@@ -52946,7 +52946,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.41302168369293</v>
+        <v>1.41302156448364</v>
       </c>
       <c r="H1813" t="n">
         <v>305237</v>
@@ -52975,7 +52975,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G1814" t="n">
-        <v>1.41141593456268</v>
+        <v>1.41141581535339</v>
       </c>
       <c r="H1814" t="n">
         <v>102231</v>
@@ -53004,7 +53004,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.42907857894897</v>
+        <v>1.42907869815826</v>
       </c>
       <c r="H1815" t="n">
         <v>261500</v>
@@ -53033,7 +53033,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.41302168369293</v>
+        <v>1.41302156448364</v>
       </c>
       <c r="H1816" t="n">
         <v>158773</v>
@@ -53323,7 +53323,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1826" t="n">
         <v>66052</v>
@@ -53381,7 +53381,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1828" t="n">
         <v>60503</v>
@@ -53439,7 +53439,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1830" t="n">
         <v>142891</v>
@@ -53468,7 +53468,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1831" t="n">
         <v>169426</v>
@@ -53497,7 +53497,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1832" t="n">
         <v>160687</v>
@@ -53526,7 +53526,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1833" t="n">
         <v>313479</v>
@@ -53555,7 +53555,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1834" t="n">
         <v>89373</v>
@@ -53584,7 +53584,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1835" t="n">
         <v>126203</v>
@@ -53613,7 +53613,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704510211945</v>
+        <v>1.30704498291016</v>
       </c>
       <c r="H1836" t="n">
         <v>104258</v>
@@ -53642,7 +53642,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1837" t="n">
         <v>137726</v>
@@ -53671,7 +53671,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.31828486919403</v>
+        <v>1.31828498840332</v>
       </c>
       <c r="H1838" t="n">
         <v>268207</v>
@@ -53729,7 +53729,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.39214730262756</v>
+        <v>1.39214742183685</v>
       </c>
       <c r="H1840" t="n">
         <v>380640</v>
@@ -53758,7 +53758,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.43389570713043</v>
+        <v>1.43389582633972</v>
       </c>
       <c r="H1841" t="n">
         <v>519268</v>
@@ -53787,7 +53787,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.44353008270264</v>
+        <v>1.44352996349335</v>
       </c>
       <c r="H1842" t="n">
         <v>694559</v>
@@ -53845,7 +53845,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.42907857894897</v>
+        <v>1.42907869815826</v>
       </c>
       <c r="H1844" t="n">
         <v>214215</v>
@@ -53903,7 +53903,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206698894501</v>
+        <v>1.48206686973572</v>
       </c>
       <c r="H1846" t="n">
         <v>230147</v>
@@ -54077,7 +54077,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.49009549617767</v>
+        <v>1.49009537696838</v>
       </c>
       <c r="H1852" t="n">
         <v>100715</v>
@@ -54193,7 +54193,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1856" t="n">
         <v>136076</v>
@@ -54280,7 +54280,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.47885572910309</v>
+        <v>1.4788556098938</v>
       </c>
       <c r="H1859" t="n">
         <v>185027</v>
@@ -54570,7 +54570,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.49009549617767</v>
+        <v>1.49009537696838</v>
       </c>
       <c r="H1869" t="n">
         <v>96052</v>
@@ -54715,7 +54715,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.51096963882446</v>
+        <v>1.51096975803375</v>
       </c>
       <c r="H1874" t="n">
         <v>154060</v>
@@ -54831,7 +54831,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.45958709716797</v>
+        <v>1.45958697795868</v>
       </c>
       <c r="H1878" t="n">
         <v>118811</v>
@@ -54860,7 +54860,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.46279847621918</v>
+        <v>1.46279859542847</v>
       </c>
       <c r="H1879" t="n">
         <v>148220</v>
@@ -54918,7 +54918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330687522888</v>
+        <v>1.49330699443817</v>
       </c>
       <c r="H1881" t="n">
         <v>411337</v>
@@ -55063,7 +55063,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.43476319313049</v>
+        <v>1.43476331233978</v>
       </c>
       <c r="H1886" t="n">
         <v>536461</v>
@@ -55208,7 +55208,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.42955851554871</v>
+        <v>1.429558634758</v>
       </c>
       <c r="H1891" t="n">
         <v>91752</v>
@@ -55324,7 +55324,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1895" t="n">
         <v>155465</v>
@@ -55469,7 +55469,7 @@
         <v>1.75</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.51803839206696</v>
+        <v>1.51803851127625</v>
       </c>
       <c r="H1900" t="n">
         <v>98091</v>
@@ -55527,7 +55527,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1902" t="n">
         <v>209046</v>
@@ -55614,7 +55614,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.41220951080322</v>
+        <v>1.41220963001251</v>
       </c>
       <c r="H1905" t="n">
         <v>123981</v>
@@ -55672,7 +55672,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.43129336833954</v>
+        <v>1.43129348754883</v>
       </c>
       <c r="H1907" t="n">
         <v>105330</v>
@@ -55730,7 +55730,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.43302822113037</v>
+        <v>1.43302834033966</v>
       </c>
       <c r="H1909" t="n">
         <v>141549</v>
@@ -55846,7 +55846,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.43823301792145</v>
+        <v>1.43823313713074</v>
       </c>
       <c r="H1913" t="n">
         <v>242905</v>
@@ -55904,7 +55904,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.43476319313049</v>
+        <v>1.43476331233978</v>
       </c>
       <c r="H1915" t="n">
         <v>75897</v>
@@ -56020,7 +56020,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H1919" t="n">
         <v>73204</v>
@@ -56078,7 +56078,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H1921" t="n">
         <v>105790</v>
@@ -56107,7 +56107,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.47119605541229</v>
+        <v>1.47119617462158</v>
       </c>
       <c r="H1922" t="n">
         <v>167278</v>
@@ -56136,7 +56136,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.46946120262146</v>
+        <v>1.46946132183075</v>
       </c>
       <c r="H1923" t="n">
         <v>75490</v>
@@ -56194,7 +56194,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1925" t="n">
         <v>85670</v>
@@ -56223,7 +56223,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1926" t="n">
         <v>130688</v>
@@ -56252,7 +56252,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1927" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1927" t="n">
         <v>168473</v>
@@ -56310,7 +56310,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.50415921211243</v>
+        <v>1.50415933132172</v>
       </c>
       <c r="H1929" t="n">
         <v>283646</v>
@@ -56368,7 +56368,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.50762903690338</v>
+        <v>1.50762915611267</v>
       </c>
       <c r="H1931" t="n">
         <v>280427</v>
@@ -56397,7 +56397,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.51456868648529</v>
+        <v>1.51456880569458</v>
       </c>
       <c r="H1932" t="n">
         <v>194466</v>
@@ -56455,7 +56455,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1934" t="n">
-        <v>1.51456868648529</v>
+        <v>1.51456880569458</v>
       </c>
       <c r="H1934" t="n">
         <v>127399</v>
@@ -56484,7 +56484,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1935" t="n">
         <v>224620</v>
@@ -56542,7 +56542,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1937" t="n">
         <v>331903</v>
@@ -56600,7 +56600,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.40353512763977</v>
+        <v>1.40353500843048</v>
       </c>
       <c r="H1939" t="n">
         <v>88869</v>
@@ -56658,7 +56658,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.4226188659668</v>
+        <v>1.42261898517609</v>
       </c>
       <c r="H1941" t="n">
         <v>129872</v>
@@ -56716,7 +56716,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.40180027484894</v>
+        <v>1.40180015563965</v>
       </c>
       <c r="H1943" t="n">
         <v>113302</v>
@@ -56803,7 +56803,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.4226188659668</v>
+        <v>1.42261898517609</v>
       </c>
       <c r="H1946" t="n">
         <v>144857</v>
@@ -56832,7 +56832,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.42088401317596</v>
+        <v>1.42088413238525</v>
       </c>
       <c r="H1947" t="n">
         <v>128877</v>
@@ -57151,7 +57151,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37924647331238</v>
+        <v>1.37924635410309</v>
       </c>
       <c r="H1958" t="n">
         <v>186765</v>
@@ -57383,7 +57383,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.42088401317596</v>
+        <v>1.42088413238525</v>
       </c>
       <c r="H1966" t="n">
         <v>255864</v>
@@ -57441,7 +57441,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.40353512763977</v>
+        <v>1.40353500843048</v>
       </c>
       <c r="H1968" t="n">
         <v>58263</v>
@@ -57702,7 +57702,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.38098132610321</v>
+        <v>1.38098120689392</v>
       </c>
       <c r="H1977" t="n">
         <v>161060</v>
@@ -57847,7 +57847,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1982" t="n">
         <v>151373</v>
@@ -57876,7 +57876,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1983" t="n">
         <v>104614</v>
@@ -57905,7 +57905,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1984" t="n">
         <v>112284</v>
@@ -57934,7 +57934,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1985" t="n">
         <v>38175</v>
@@ -57963,7 +57963,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1986" t="n">
         <v>158425</v>
@@ -57992,7 +57992,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1987" t="n">
         <v>143196</v>
@@ -58021,7 +58021,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1988" t="n">
         <v>121532</v>
@@ -58137,7 +58137,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1992" t="n">
         <v>99504</v>
@@ -58369,7 +58369,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.43302822113037</v>
+        <v>1.43302834033966</v>
       </c>
       <c r="H2000" t="n">
         <v>91033</v>
@@ -58456,7 +58456,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.42955851554871</v>
+        <v>1.429558634758</v>
       </c>
       <c r="H2003" t="n">
         <v>437597</v>
@@ -58485,7 +58485,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H2004" t="n">
         <v>396696</v>
@@ -58630,7 +58630,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.4781357049942</v>
+        <v>1.47813582420349</v>
       </c>
       <c r="H2009" t="n">
         <v>120373</v>
@@ -58659,7 +58659,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2010" t="n">
         <v>78064</v>
@@ -58688,7 +58688,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G2011" t="n">
-        <v>1.4781357049942</v>
+        <v>1.47813582420349</v>
       </c>
       <c r="H2011" t="n">
         <v>106739</v>
@@ -58746,7 +58746,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2013" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2013" t="n">
         <v>46060</v>
@@ -58862,7 +58862,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H2017" t="n">
         <v>211706</v>
@@ -58920,7 +58920,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2019" t="n">
         <v>74724</v>
@@ -58949,7 +58949,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.46946120262146</v>
+        <v>1.46946132183075</v>
       </c>
       <c r="H2020" t="n">
         <v>63283</v>
@@ -59007,7 +59007,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.47640085220337</v>
+        <v>1.47640097141266</v>
       </c>
       <c r="H2022" t="n">
         <v>155094</v>
@@ -59036,7 +59036,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H2023" t="n">
         <v>24585</v>
@@ -59123,7 +59123,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.47119605541229</v>
+        <v>1.47119617462158</v>
       </c>
       <c r="H2026" t="n">
         <v>101853</v>
@@ -59239,7 +59239,7 @@
         <v>1.75</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.51803839206696</v>
+        <v>1.51803851127625</v>
       </c>
       <c r="H2030" t="n">
         <v>141811</v>
@@ -59326,7 +59326,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2033" t="n">
         <v>261156</v>
@@ -59355,7 +59355,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2034" t="n">
         <v>289476</v>
@@ -59413,7 +59413,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2036" t="n">
         <v>222362</v>
@@ -59819,7 +59819,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.55794131755829</v>
+        <v>1.557941198349</v>
       </c>
       <c r="H2050" t="n">
         <v>242753</v>
@@ -59993,7 +59993,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2056" t="n">
         <v>183238</v>
@@ -60022,7 +60022,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2057" t="n">
         <v>159596</v>
@@ -60080,7 +60080,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2059" t="n">
         <v>166315</v>
@@ -60138,7 +60138,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2061" t="n">
         <v>245729</v>
@@ -60167,7 +60167,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G2062" t="n">
-        <v>1.55794131755829</v>
+        <v>1.557941198349</v>
       </c>
       <c r="H2062" t="n">
         <v>101478</v>
@@ -60312,7 +60312,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2067" t="n">
         <v>176828</v>
@@ -60428,7 +60428,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.58916938304901</v>
+        <v>1.5891695022583</v>
       </c>
       <c r="H2071" t="n">
         <v>202349</v>
@@ -60544,7 +60544,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2075" t="n">
         <v>165697</v>
@@ -60602,7 +60602,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2077" t="n">
         <v>182533</v>
@@ -60631,7 +60631,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2078" t="n">
         <v>124929</v>
@@ -60747,7 +60747,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2082" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2082" t="n">
         <v>478181</v>
@@ -60776,7 +60776,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2083" t="n">
         <v>218213</v>
@@ -60805,7 +60805,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.55967617034912</v>
+        <v>1.55967605113983</v>
       </c>
       <c r="H2084" t="n">
         <v>164927</v>
@@ -60950,7 +60950,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.55967617034912</v>
+        <v>1.55967605113983</v>
       </c>
       <c r="H2089" t="n">
         <v>237737</v>
@@ -61298,7 +61298,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2101" t="n">
-        <v>1.83465802669525</v>
+        <v>1.83465790748596</v>
       </c>
       <c r="H2101" t="n">
         <v>399372</v>
@@ -61327,7 +61327,7 @@
         <v>2.125</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2102" t="n">
         <v>614339</v>
@@ -61443,7 +61443,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.94308936595917</v>
+        <v>1.94308924674988</v>
       </c>
       <c r="H2106" t="n">
         <v>1986166</v>
@@ -61501,7 +61501,7 @@
         <v>2.125</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2108" t="n">
         <v>629582</v>
@@ -61646,7 +61646,7 @@
         <v>2.125</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2113" t="n">
         <v>238974</v>
@@ -61704,7 +61704,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.87369334697723</v>
+        <v>1.87369322776794</v>
       </c>
       <c r="H2115" t="n">
         <v>183920</v>
@@ -61849,7 +61849,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.87369334697723</v>
+        <v>1.87369322776794</v>
       </c>
       <c r="H2120" t="n">
         <v>272405</v>
@@ -61878,7 +61878,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.89104235172272</v>
+        <v>1.89104223251343</v>
       </c>
       <c r="H2121" t="n">
         <v>113831</v>
@@ -61907,7 +61907,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.89104235172272</v>
+        <v>1.89104223251343</v>
       </c>
       <c r="H2122" t="n">
         <v>172869</v>
@@ -62110,7 +62110,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.20766162872314</v>
+        <v>2.20766186714172</v>
       </c>
       <c r="H2129" t="n">
         <v>392842</v>
@@ -62342,7 +62342,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G2137" t="n">
-        <v>2.07754421234131</v>
+        <v>2.07754397392273</v>
       </c>
       <c r="H2137" t="n">
         <v>1128604</v>
@@ -80096,6 +80096,35 @@
         <v>65735</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>2.06500005722046</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>82313</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85730123519897</v>
+        <v>2.85730147361755</v>
       </c>
       <c r="H2" t="n">
         <v>30003</v>
@@ -485,7 +485,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525803565979</v>
+        <v>2.80525827407837</v>
       </c>
       <c r="H4" t="n">
         <v>23828</v>
@@ -514,7 +514,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717758178711</v>
       </c>
       <c r="H5" t="n">
         <v>103885</v>
@@ -543,7 +543,7 @@
         <v>4.36600017547607</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7709858417511</v>
+        <v>2.77098608016968</v>
       </c>
       <c r="H6" t="n">
         <v>24790</v>
@@ -572,7 +572,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67832326889038</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H7" t="n">
         <v>64928</v>
@@ -601,7 +601,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G8" t="n">
-        <v>2.732905626297</v>
+        <v>2.73290538787842</v>
       </c>
       <c r="H8" t="n">
         <v>58587</v>
@@ -630,7 +630,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G9" t="n">
-        <v>2.67832326889038</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H9" t="n">
         <v>36066</v>
@@ -659,7 +659,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H10" t="n">
         <v>108431</v>
@@ -717,7 +717,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408190727234</v>
+        <v>2.56408214569092</v>
       </c>
       <c r="H12" t="n">
         <v>52586</v>
@@ -775,7 +775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G14" t="n">
-        <v>2.50061464309692</v>
+        <v>2.5006148815155</v>
       </c>
       <c r="H14" t="n">
         <v>75440</v>
@@ -804,7 +804,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H15" t="n">
         <v>65925</v>
@@ -833,7 +833,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66436052322388</v>
+        <v>2.66436076164246</v>
       </c>
       <c r="H16" t="n">
         <v>61532</v>
@@ -891,7 +891,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138897895813</v>
+        <v>2.55138874053955</v>
       </c>
       <c r="H18" t="n">
         <v>16747</v>
@@ -949,7 +949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965522766113</v>
+        <v>2.51965498924255</v>
       </c>
       <c r="H20" t="n">
         <v>43026</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.53869533538818</v>
+        <v>2.5386950969696</v>
       </c>
       <c r="H21" t="n">
         <v>27727</v>
@@ -1007,7 +1007,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662058830261</v>
+        <v>2.56662106513977</v>
       </c>
       <c r="H22" t="n">
         <v>34521</v>
@@ -1036,7 +1036,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G23" t="n">
-        <v>2.53361773490906</v>
+        <v>2.53361797332764</v>
       </c>
       <c r="H23" t="n">
         <v>25182</v>
@@ -1065,7 +1065,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G24" t="n">
-        <v>2.50696110725403</v>
+        <v>2.50696158409119</v>
       </c>
       <c r="H24" t="n">
         <v>32795</v>
@@ -1123,7 +1123,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H26" t="n">
         <v>40968</v>
@@ -1152,7 +1152,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44349431991577</v>
+        <v>2.44349408149719</v>
       </c>
       <c r="H27" t="n">
         <v>83462</v>
@@ -1181,7 +1181,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2860951423645</v>
+        <v>2.28609490394592</v>
       </c>
       <c r="H28" t="n">
         <v>109730</v>
@@ -1210,7 +1210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28482532501221</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H29" t="n">
         <v>103231</v>
@@ -1268,7 +1268,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135829925537</v>
+        <v>2.22135806083679</v>
       </c>
       <c r="H31" t="n">
         <v>155211</v>
@@ -1326,7 +1326,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798337936401</v>
+        <v>2.32798361778259</v>
       </c>
       <c r="H33" t="n">
         <v>39970</v>
@@ -1500,7 +1500,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49553751945496</v>
+        <v>2.49553728103638</v>
       </c>
       <c r="H39" t="n">
         <v>77760</v>
@@ -1529,7 +1529,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52600169181824</v>
+        <v>2.52600145339966</v>
       </c>
       <c r="H40" t="n">
         <v>22658</v>
@@ -1558,7 +1558,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H41" t="n">
         <v>29241</v>
@@ -1587,7 +1587,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G42" t="n">
-        <v>2.60850930213928</v>
+        <v>2.6085090637207</v>
       </c>
       <c r="H42" t="n">
         <v>49765</v>
@@ -1616,7 +1616,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>2.67832326889038</v>
+        <v>2.67832350730896</v>
       </c>
       <c r="H43" t="n">
         <v>55902</v>
@@ -1645,7 +1645,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66055274009705</v>
+        <v>2.66055226325989</v>
       </c>
       <c r="H44" t="n">
         <v>83690</v>
@@ -1703,7 +1703,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.64658975601196</v>
+        <v>2.64658951759338</v>
       </c>
       <c r="H46" t="n">
         <v>17636</v>
@@ -1761,7 +1761,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213152885437</v>
+        <v>2.68213105201721</v>
       </c>
       <c r="H48" t="n">
         <v>40006</v>
@@ -1790,7 +1790,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6935555934906</v>
+        <v>2.69355535507202</v>
       </c>
       <c r="H49" t="n">
         <v>25946</v>
@@ -1819,7 +1819,7 @@
         <v>4.17600011825562</v>
       </c>
       <c r="G50" t="n">
-        <v>2.65039753913879</v>
+        <v>2.65039777755737</v>
       </c>
       <c r="H50" t="n">
         <v>43154</v>
@@ -1848,7 +1848,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G51" t="n">
-        <v>2.7392520904541</v>
+        <v>2.73925185203552</v>
       </c>
       <c r="H51" t="n">
         <v>198987</v>
@@ -1877,7 +1877,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G52" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717758178711</v>
       </c>
       <c r="H52" t="n">
         <v>124017</v>
@@ -1906,7 +1906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.74179100990295</v>
+        <v>2.74179077148438</v>
       </c>
       <c r="H53" t="n">
         <v>42603</v>
@@ -1935,7 +1935,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>2.84333872795105</v>
+        <v>2.84333825111389</v>
       </c>
       <c r="H54" t="n">
         <v>63652</v>
@@ -1964,7 +1964,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172863006592</v>
+        <v>2.90172839164734</v>
       </c>
       <c r="H55" t="n">
         <v>82307</v>
@@ -1993,7 +1993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853974342346</v>
+        <v>2.93853998184204</v>
       </c>
       <c r="H56" t="n">
         <v>170803</v>
@@ -2022,7 +2022,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95757961273193</v>
+        <v>2.95757985115051</v>
       </c>
       <c r="H57" t="n">
         <v>81691</v>
@@ -2051,7 +2051,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169708251953</v>
+        <v>2.98169732093811</v>
       </c>
       <c r="H58" t="n">
         <v>45732</v>
@@ -2080,7 +2080,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504117012024</v>
+        <v>2.95504093170166</v>
       </c>
       <c r="H59" t="n">
         <v>62635</v>
@@ -2138,7 +2138,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835371017456</v>
+        <v>3.00835347175598</v>
       </c>
       <c r="H61" t="n">
         <v>91726</v>
@@ -2167,7 +2167,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G62" t="n">
-        <v>3.02104759216309</v>
+        <v>3.02104735374451</v>
       </c>
       <c r="H62" t="n">
         <v>71653</v>
@@ -2196,7 +2196,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423624038696</v>
+        <v>2.9842369556427</v>
       </c>
       <c r="H63" t="n">
         <v>32830</v>
@@ -2225,7 +2225,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566030502319</v>
+        <v>2.99566006660461</v>
       </c>
       <c r="H64" t="n">
         <v>46851</v>
@@ -2254,7 +2254,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327634811401</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H65" t="n">
         <v>28745</v>
@@ -2283,7 +2283,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.00200748443604</v>
+        <v>3.00200700759888</v>
       </c>
       <c r="H66" t="n">
         <v>39511</v>
@@ -2312,7 +2312,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.91949915885925</v>
+        <v>2.91949963569641</v>
       </c>
       <c r="H67" t="n">
         <v>33763</v>
@@ -2341,7 +2341,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92711520195007</v>
+        <v>2.92711544036865</v>
       </c>
       <c r="H68" t="n">
         <v>58634</v>
@@ -2457,7 +2457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182145118713</v>
+        <v>3.07182097434998</v>
       </c>
       <c r="H72" t="n">
         <v>136484</v>
@@ -2515,7 +2515,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G74" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H74" t="n">
         <v>109632</v>
@@ -2573,7 +2573,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702222824097</v>
       </c>
       <c r="H76" t="n">
         <v>114194</v>
@@ -2602,7 +2602,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702198982239</v>
+        <v>3.16702222824097</v>
       </c>
       <c r="H77" t="n">
         <v>122410</v>
@@ -2631,7 +2631,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H78" t="n">
         <v>61569</v>
@@ -2660,7 +2660,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>3.10990142822266</v>
+        <v>3.10990166664124</v>
       </c>
       <c r="H79" t="n">
         <v>45242</v>
@@ -2689,7 +2689,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798164367676</v>
+        <v>3.14798212051392</v>
       </c>
       <c r="H80" t="n">
         <v>29895</v>
@@ -2747,7 +2747,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11244034767151</v>
+        <v>3.11243987083435</v>
       </c>
       <c r="H82" t="n">
         <v>32834</v>
@@ -2805,7 +2805,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959197998047</v>
+        <v>3.08959174156189</v>
       </c>
       <c r="H84" t="n">
         <v>34327</v>
@@ -2834,7 +2834,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547451019287</v>
+        <v>3.06547474861145</v>
       </c>
       <c r="H85" t="n">
         <v>37849</v>
@@ -2863,7 +2863,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G86" t="n">
-        <v>3.03374075889587</v>
+        <v>3.03374099731445</v>
       </c>
       <c r="H86" t="n">
         <v>46370</v>
@@ -2892,7 +2892,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327634811401</v>
+        <v>3.00327587127686</v>
       </c>
       <c r="H87" t="n">
         <v>120760</v>
@@ -2979,7 +2979,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053975105286</v>
+        <v>3.03053951263428</v>
       </c>
       <c r="H90" t="n">
         <v>50752</v>
@@ -3037,7 +3037,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G92" t="n">
-        <v>2.93384861946106</v>
+        <v>2.93384838104248</v>
       </c>
       <c r="H92" t="n">
         <v>77806</v>
@@ -3066,7 +3066,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H93" t="n">
         <v>86004</v>
@@ -3095,7 +3095,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G94" t="n">
-        <v>2.94974303245544</v>
+        <v>2.94974279403687</v>
       </c>
       <c r="H94" t="n">
         <v>22389</v>
@@ -3124,7 +3124,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424468994141</v>
+        <v>2.87424445152283</v>
       </c>
       <c r="H95" t="n">
         <v>67830</v>
@@ -3153,7 +3153,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H96" t="n">
         <v>54946</v>
@@ -3298,7 +3298,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G101" t="n">
-        <v>3.07822346687317</v>
+        <v>3.07822275161743</v>
       </c>
       <c r="H101" t="n">
         <v>47757</v>
@@ -3327,7 +3327,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577436447144</v>
+        <v>3.14577460289001</v>
       </c>
       <c r="H102" t="n">
         <v>86451</v>
@@ -3356,7 +3356,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140504837036</v>
+        <v>3.20140528678894</v>
       </c>
       <c r="H103" t="n">
         <v>92445</v>
@@ -3385,7 +3385,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.17888784408569</v>
+        <v>3.17888808250427</v>
       </c>
       <c r="H104" t="n">
         <v>49257</v>
@@ -3472,7 +3472,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.23186922073364</v>
+        <v>3.23186945915222</v>
       </c>
       <c r="H107" t="n">
         <v>38634</v>
@@ -3501,7 +3501,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610691070557</v>
+        <v>3.19610714912415</v>
       </c>
       <c r="H108" t="n">
         <v>19558</v>
@@ -3530,7 +3530,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802783966064</v>
+        <v>3.20802736282349</v>
       </c>
       <c r="H109" t="n">
         <v>23367</v>
@@ -3559,7 +3559,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.16829180717468</v>
+        <v>3.16829133033752</v>
       </c>
       <c r="H110" t="n">
         <v>37625</v>
@@ -3588,7 +3588,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>3.15901947021484</v>
+        <v>3.15901970863342</v>
       </c>
       <c r="H111" t="n">
         <v>31915</v>
@@ -3617,7 +3617,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133623123169</v>
+        <v>3.11133646965027</v>
       </c>
       <c r="H112" t="n">
         <v>10926</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H114" t="n">
         <v>34326</v>
@@ -3704,7 +3704,7 @@
         <v>4.25</v>
       </c>
       <c r="G115" t="n">
-        <v>2.81464004516602</v>
+        <v>2.81464028358459</v>
       </c>
       <c r="H115" t="n">
         <v>47164</v>
@@ -3733,7 +3733,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516821861267</v>
+        <v>2.73516798019409</v>
       </c>
       <c r="H116" t="n">
         <v>77740</v>
@@ -3820,7 +3820,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85040283203125</v>
+        <v>2.85040235519409</v>
       </c>
       <c r="H119" t="n">
         <v>114293</v>
@@ -3849,7 +3849,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>2.86762166023254</v>
+        <v>2.86762142181396</v>
       </c>
       <c r="H120" t="n">
         <v>86220</v>
@@ -3878,7 +3878,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91133141517639</v>
+        <v>2.91133165359497</v>
       </c>
       <c r="H121" t="n">
         <v>23520</v>
@@ -3907,7 +3907,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.91398048400879</v>
+        <v>2.91398072242737</v>
       </c>
       <c r="H122" t="n">
         <v>31647</v>
@@ -4023,7 +4023,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841356277466</v>
+        <v>2.74841380119324</v>
       </c>
       <c r="H126" t="n">
         <v>44702</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H128" t="n">
         <v>87090</v>
@@ -4110,7 +4110,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H129" t="n">
         <v>113855</v>
@@ -4139,7 +4139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047164916992</v>
+        <v>2.94047117233276</v>
       </c>
       <c r="H130" t="n">
         <v>49672</v>
@@ -4226,7 +4226,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152656555176</v>
+        <v>2.78152704238892</v>
       </c>
       <c r="H133" t="n">
         <v>40862</v>
@@ -4313,7 +4313,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802278518677</v>
+        <v>3.00802254676819</v>
       </c>
       <c r="H136" t="n">
         <v>190152</v>
@@ -4371,7 +4371,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>2.95371675491333</v>
+        <v>2.95371651649475</v>
       </c>
       <c r="H138" t="n">
         <v>257080</v>
@@ -4400,7 +4400,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.91530513763428</v>
+        <v>2.91530466079712</v>
       </c>
       <c r="H139" t="n">
         <v>337397</v>
@@ -4458,7 +4458,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G141" t="n">
-        <v>2.63715267181396</v>
+        <v>2.63715243339539</v>
       </c>
       <c r="H141" t="n">
         <v>384878</v>
@@ -4545,7 +4545,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G144" t="n">
-        <v>2.69940590858459</v>
+        <v>2.69940567016602</v>
       </c>
       <c r="H144" t="n">
         <v>154876</v>
@@ -4632,7 +4632,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="n">
-        <v>2.67291450500488</v>
+        <v>2.67291474342346</v>
       </c>
       <c r="H147" t="n">
         <v>156041</v>
@@ -4719,7 +4719,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60138988494873</v>
+        <v>2.60139012336731</v>
       </c>
       <c r="H150" t="n">
         <v>119099</v>
@@ -4748,7 +4748,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.5417857170105</v>
+        <v>2.54178595542908</v>
       </c>
       <c r="H151" t="n">
         <v>586648</v>
@@ -4835,7 +4835,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159008979797</v>
       </c>
       <c r="H154" t="n">
         <v>972279</v>
@@ -4864,7 +4864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245057106018</v>
+        <v>2.64245080947876</v>
       </c>
       <c r="H155" t="n">
         <v>131874</v>
@@ -4893,7 +4893,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G156" t="n">
-        <v>2.67556357383728</v>
+        <v>2.67556405067444</v>
       </c>
       <c r="H156" t="n">
         <v>71701</v>
@@ -4922,7 +4922,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.7219226360321</v>
+        <v>2.72192287445068</v>
       </c>
       <c r="H157" t="n">
         <v>1740457</v>
@@ -4951,7 +4951,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71529984474182</v>
       </c>
       <c r="H158" t="n">
         <v>518886</v>
@@ -5038,7 +5038,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="n">
-        <v>2.66496801376343</v>
+        <v>2.66496777534485</v>
       </c>
       <c r="H161" t="n">
         <v>161383</v>
@@ -5067,7 +5067,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702033042908</v>
+        <v>2.65702080726624</v>
       </c>
       <c r="H162" t="n">
         <v>133837</v>
@@ -5154,7 +5154,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159008979797</v>
       </c>
       <c r="H165" t="n">
         <v>235127</v>
@@ -5299,7 +5299,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="n">
-        <v>2.56562781333923</v>
+        <v>2.56562757492065</v>
       </c>
       <c r="H170" t="n">
         <v>215835</v>
@@ -5386,7 +5386,7 @@
         <v>3.93799996376038</v>
       </c>
       <c r="G173" t="n">
-        <v>2.60801243782043</v>
+        <v>2.60801267623901</v>
       </c>
       <c r="H173" t="n">
         <v>90282</v>
@@ -5415,7 +5415,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754874229431</v>
+        <v>2.57754826545715</v>
       </c>
       <c r="H174" t="n">
         <v>111504</v>
@@ -5444,7 +5444,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G175" t="n">
-        <v>2.56430292129517</v>
+        <v>2.56430268287659</v>
       </c>
       <c r="H175" t="n">
         <v>202259</v>
@@ -5560,7 +5560,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H179" t="n">
         <v>130197</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979668617249</v>
+        <v>2.43979644775391</v>
       </c>
       <c r="H180" t="n">
         <v>95436</v>
@@ -5676,7 +5676,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40270948410034</v>
+        <v>2.40270924568176</v>
       </c>
       <c r="H183" t="n">
         <v>219710</v>
@@ -5734,7 +5734,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G185" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761155128479</v>
       </c>
       <c r="H185" t="n">
         <v>109363</v>
@@ -5763,7 +5763,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G186" t="n">
-        <v>2.45039296150208</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H186" t="n">
         <v>71603</v>
@@ -5792,7 +5792,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G187" t="n">
-        <v>2.41992855072021</v>
+        <v>2.41992831230164</v>
       </c>
       <c r="H187" t="n">
         <v>58946</v>
@@ -5821,7 +5821,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078831672668</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H188" t="n">
         <v>97323</v>
@@ -5937,7 +5937,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G192" t="n">
-        <v>2.27158069610596</v>
+        <v>2.2715802192688</v>
       </c>
       <c r="H192" t="n">
         <v>124936</v>
@@ -5995,7 +5995,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.28615021705627</v>
+        <v>2.28615045547485</v>
       </c>
       <c r="H194" t="n">
         <v>121567</v>
@@ -6024,7 +6024,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G195" t="n">
-        <v>2.45039296150208</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H195" t="n">
         <v>439465</v>
@@ -6053,7 +6053,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G196" t="n">
-        <v>2.43449807167053</v>
+        <v>2.43449831008911</v>
       </c>
       <c r="H196" t="n">
         <v>224328</v>
@@ -6082,7 +6082,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.42655110359192</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H197" t="n">
         <v>94547</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078831672668</v>
+        <v>2.39078879356384</v>
       </c>
       <c r="H199" t="n">
         <v>102816</v>
@@ -6198,7 +6198,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H201" t="n">
         <v>67052</v>
@@ -6227,7 +6227,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G202" t="n">
-        <v>2.34575438499451</v>
+        <v>2.34575414657593</v>
       </c>
       <c r="H202" t="n">
         <v>176806</v>
@@ -6256,7 +6256,7 @@
         <v>3.61199998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>2.39211344718933</v>
+        <v>2.39211297035217</v>
       </c>
       <c r="H203" t="n">
         <v>79415</v>
@@ -6285,7 +6285,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.42655110359192</v>
+        <v>2.4265513420105</v>
       </c>
       <c r="H204" t="n">
         <v>55166</v>
@@ -6372,7 +6372,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.45436668395996</v>
+        <v>2.45436644554138</v>
       </c>
       <c r="H207" t="n">
         <v>152563</v>
@@ -6401,7 +6401,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G208" t="n">
-        <v>2.45304179191589</v>
+        <v>2.45304155349731</v>
       </c>
       <c r="H208" t="n">
         <v>115572</v>
@@ -6430,7 +6430,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>2.44377040863037</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H209" t="n">
         <v>84077</v>
@@ -6459,7 +6459,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="n">
-        <v>2.4477436542511</v>
+        <v>2.44774389266968</v>
       </c>
       <c r="H210" t="n">
         <v>57237</v>
@@ -6488,7 +6488,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.45039296150208</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H211" t="n">
         <v>66822</v>
@@ -6546,7 +6546,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G213" t="n">
-        <v>2.55503082275391</v>
+        <v>2.55503106117249</v>
       </c>
       <c r="H213" t="n">
         <v>339678</v>
@@ -6720,7 +6720,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324247360229</v>
       </c>
       <c r="H219" t="n">
         <v>63266</v>
@@ -6749,7 +6749,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G220" t="n">
-        <v>2.51661944389343</v>
+        <v>2.51661968231201</v>
       </c>
       <c r="H220" t="n">
         <v>40199</v>
@@ -6778,7 +6778,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496248245239</v>
+        <v>2.46496272087097</v>
       </c>
       <c r="H221" t="n">
         <v>80797</v>
@@ -6894,7 +6894,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416600227356</v>
+        <v>2.38416576385498</v>
       </c>
       <c r="H225" t="n">
         <v>57912</v>
@@ -6952,7 +6952,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.33780741691589</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H227" t="n">
         <v>189301</v>
@@ -6981,7 +6981,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.33780741691589</v>
+        <v>2.33780694007874</v>
       </c>
       <c r="H228" t="n">
         <v>112606</v>
@@ -7010,7 +7010,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H229" t="n">
         <v>112233</v>
@@ -7039,7 +7039,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H230" t="n">
         <v>154519</v>
@@ -7097,7 +7097,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098394393921</v>
+        <v>2.26098442077637</v>
       </c>
       <c r="H232" t="n">
         <v>54749</v>
@@ -7126,7 +7126,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G233" t="n">
-        <v>2.26495790481567</v>
+        <v>2.26495766639709</v>
       </c>
       <c r="H233" t="n">
         <v>33872</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>2.22522139549255</v>
+        <v>2.22522163391113</v>
       </c>
       <c r="H234" t="n">
         <v>82103</v>
@@ -7242,7 +7242,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482556343079</v>
+        <v>2.28482604026794</v>
       </c>
       <c r="H237" t="n">
         <v>48104</v>
@@ -7271,7 +7271,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548536300659</v>
+        <v>2.18548512458801</v>
       </c>
       <c r="H238" t="n">
         <v>189002</v>
@@ -7300,7 +7300,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G239" t="n">
-        <v>2.25171232223511</v>
+        <v>2.25171256065369</v>
       </c>
       <c r="H239" t="n">
         <v>111810</v>
@@ -7329,7 +7329,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237717628479</v>
+        <v>2.35237693786621</v>
       </c>
       <c r="H240" t="n">
         <v>374448</v>
@@ -7358,7 +7358,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H241" t="n">
         <v>218337</v>
@@ -7387,7 +7387,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608693122864</v>
+        <v>2.39608669281006</v>
       </c>
       <c r="H242" t="n">
         <v>275325</v>
@@ -7474,7 +7474,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="n">
-        <v>2.4477436542511</v>
+        <v>2.44774389266968</v>
       </c>
       <c r="H245" t="n">
         <v>152191</v>
@@ -7590,7 +7590,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.45039296150208</v>
+        <v>2.45039248466492</v>
       </c>
       <c r="H249" t="n">
         <v>141900</v>
@@ -7793,7 +7793,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G256" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H256" t="n">
         <v>116308</v>
@@ -7822,7 +7822,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324223518372</v>
+        <v>2.52324247360229</v>
       </c>
       <c r="H257" t="n">
         <v>138168</v>
@@ -7851,7 +7851,7 @@
         <v>3.84599995613098</v>
       </c>
       <c r="G258" t="n">
-        <v>2.54708409309387</v>
+        <v>2.54708385467529</v>
       </c>
       <c r="H258" t="n">
         <v>159203</v>
@@ -7967,7 +7967,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G262" t="n">
-        <v>2.53118968009949</v>
+        <v>2.53118944168091</v>
       </c>
       <c r="H262" t="n">
         <v>57795</v>
@@ -8054,7 +8054,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G265" t="n">
-        <v>2.49675130844116</v>
+        <v>2.49675154685974</v>
       </c>
       <c r="H265" t="n">
         <v>182001</v>
@@ -8141,7 +8141,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.53648734092712</v>
+        <v>2.5364875793457</v>
       </c>
       <c r="H268" t="n">
         <v>422771</v>
@@ -8170,7 +8170,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960105895996</v>
+        <v>2.56960129737854</v>
       </c>
       <c r="H269" t="n">
         <v>280634</v>
@@ -8199,7 +8199,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5576798915863</v>
+        <v>2.55768013000488</v>
       </c>
       <c r="H270" t="n">
         <v>132299</v>
@@ -8228,7 +8228,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165385246277</v>
+        <v>2.56165409088135</v>
       </c>
       <c r="H271" t="n">
         <v>288062</v>
@@ -8257,7 +8257,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5576798915863</v>
+        <v>2.55768013000488</v>
       </c>
       <c r="H272" t="n">
         <v>301942</v>
@@ -8286,7 +8286,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G273" t="n">
-        <v>2.52059316635132</v>
+        <v>2.5205934047699</v>
       </c>
       <c r="H273" t="n">
         <v>263075</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.46363806724548</v>
+        <v>2.46363830566406</v>
       </c>
       <c r="H275" t="n">
         <v>198253</v>
@@ -8373,7 +8373,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>2.44377040863037</v>
+        <v>2.44377017021179</v>
       </c>
       <c r="H276" t="n">
         <v>157304</v>
@@ -8402,7 +8402,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="n">
-        <v>2.42390179634094</v>
+        <v>2.4239022731781</v>
       </c>
       <c r="H277" t="n">
         <v>129770</v>
@@ -8431,7 +8431,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138483047485</v>
+        <v>2.40138459205627</v>
       </c>
       <c r="H278" t="n">
         <v>362112</v>
@@ -8460,7 +8460,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H279" t="n">
         <v>309995</v>
@@ -8489,7 +8489,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356948852539</v>
+        <v>2.37356996536255</v>
       </c>
       <c r="H280" t="n">
         <v>114037</v>
@@ -8576,7 +8576,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019251823425</v>
+        <v>2.38019227981567</v>
       </c>
       <c r="H283" t="n">
         <v>99628</v>
@@ -8634,7 +8634,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G285" t="n">
-        <v>2.36164879798889</v>
+        <v>2.36164855957031</v>
       </c>
       <c r="H285" t="n">
         <v>138083</v>
@@ -8663,7 +8663,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G286" t="n">
-        <v>2.32853531837463</v>
+        <v>2.32853555679321</v>
       </c>
       <c r="H286" t="n">
         <v>143452</v>
@@ -8750,7 +8750,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="n">
-        <v>2.35502600669861</v>
+        <v>2.35502624511719</v>
       </c>
       <c r="H289" t="n">
         <v>119547</v>
@@ -8779,7 +8779,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476227760315</v>
+        <v>2.39476180076599</v>
       </c>
       <c r="H290" t="n">
         <v>374020</v>
@@ -8808,7 +8808,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G291" t="n">
-        <v>2.41727924346924</v>
+        <v>2.41727900505066</v>
       </c>
       <c r="H291" t="n">
         <v>96839</v>
@@ -8895,7 +8895,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886786460876</v>
+        <v>2.37886762619019</v>
       </c>
       <c r="H294" t="n">
         <v>84182</v>
@@ -8982,7 +8982,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999159812927</v>
+        <v>2.30999183654785</v>
       </c>
       <c r="H297" t="n">
         <v>327861</v>
@@ -9011,7 +9011,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G298" t="n">
-        <v>2.34575438499451</v>
+        <v>2.34575414657593</v>
       </c>
       <c r="H298" t="n">
         <v>65455</v>
@@ -9098,7 +9098,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807596206665</v>
+        <v>2.49807620048523</v>
       </c>
       <c r="H301" t="n">
         <v>292122</v>
@@ -9156,7 +9156,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G303" t="n">
-        <v>2.46761178970337</v>
+        <v>2.46761155128479</v>
       </c>
       <c r="H303" t="n">
         <v>262776</v>
@@ -9272,7 +9272,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622408866882</v>
+        <v>2.57622385025024</v>
       </c>
       <c r="H307" t="n">
         <v>428054</v>
@@ -9359,7 +9359,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.60271430015564</v>
+        <v>2.6027147769928</v>
       </c>
       <c r="H310" t="n">
         <v>178260</v>
@@ -9388,7 +9388,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63185429573059</v>
+        <v>2.63185405731201</v>
       </c>
       <c r="H311" t="n">
         <v>305933</v>
@@ -9446,7 +9446,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.7153000831604</v>
+        <v>2.71529984474182</v>
       </c>
       <c r="H313" t="n">
         <v>428736</v>
@@ -9475,7 +9475,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G314" t="n">
-        <v>2.82126331329346</v>
+        <v>2.82126379013062</v>
       </c>
       <c r="H314" t="n">
         <v>1620852</v>
@@ -9504,7 +9504,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G315" t="n">
-        <v>2.84642887115479</v>
+        <v>2.84642934799194</v>
       </c>
       <c r="H315" t="n">
         <v>839292</v>
@@ -9533,7 +9533,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252348899841</v>
+        <v>2.93252396583557</v>
       </c>
       <c r="H316" t="n">
         <v>857622</v>
@@ -9562,7 +9562,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.06497740745544</v>
+        <v>3.06497764587402</v>
       </c>
       <c r="H317" t="n">
         <v>1978795</v>
@@ -9591,7 +9591,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G318" t="n">
-        <v>3.02789092063904</v>
+        <v>3.02789068222046</v>
       </c>
       <c r="H318" t="n">
         <v>1098038</v>
@@ -9736,7 +9736,7 @@
         <v>4.43800020217896</v>
       </c>
       <c r="G323" t="n">
-        <v>2.93914699554443</v>
+        <v>2.93914651870728</v>
       </c>
       <c r="H323" t="n">
         <v>302239</v>
@@ -9794,7 +9794,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.99212837219238</v>
+        <v>2.9921281337738</v>
       </c>
       <c r="H325" t="n">
         <v>565930</v>
@@ -9823,7 +9823,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.99477672576904</v>
+        <v>2.9947772026062</v>
       </c>
       <c r="H326" t="n">
         <v>373530</v>
@@ -9910,7 +9910,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848648071289</v>
+        <v>3.03848719596863</v>
       </c>
       <c r="H329" t="n">
         <v>242448</v>
@@ -9939,7 +9939,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.00404906272888</v>
+        <v>3.0040488243103</v>
       </c>
       <c r="H330" t="n">
         <v>261526</v>
@@ -9997,7 +9997,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90868234634399</v>
+        <v>2.90868258476257</v>
       </c>
       <c r="H332" t="n">
         <v>360673</v>
@@ -10026,7 +10026,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.9709358215332</v>
+        <v>2.97093558311462</v>
       </c>
       <c r="H333" t="n">
         <v>261603</v>
@@ -10084,7 +10084,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G335" t="n">
-        <v>2.8821918964386</v>
+        <v>2.88219165802002</v>
       </c>
       <c r="H335" t="n">
         <v>311784</v>
@@ -10113,7 +10113,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G336" t="n">
-        <v>2.97225999832153</v>
+        <v>2.97225975990295</v>
       </c>
       <c r="H336" t="n">
         <v>271824</v>
@@ -10142,7 +10142,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H337" t="n">
         <v>335332</v>
@@ -10171,7 +10171,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067209243774</v>
+        <v>3.01067161560059</v>
       </c>
       <c r="H338" t="n">
         <v>333907</v>
@@ -10200,7 +10200,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G339" t="n">
-        <v>2.99875116348267</v>
+        <v>2.99875068664551</v>
       </c>
       <c r="H339" t="n">
         <v>201579</v>
@@ -10229,7 +10229,7 @@
         <v>4.5</v>
       </c>
       <c r="G340" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H340" t="n">
         <v>224232</v>
@@ -10258,7 +10258,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G341" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H341" t="n">
         <v>486269</v>
@@ -10287,7 +10287,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="n">
-        <v>3.09146881103516</v>
+        <v>3.09146904945374</v>
       </c>
       <c r="H342" t="n">
         <v>699107</v>
@@ -10316,7 +10316,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G343" t="n">
-        <v>3.05173206329346</v>
+        <v>3.05173230171204</v>
       </c>
       <c r="H343" t="n">
         <v>351338</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484601974487</v>
+        <v>3.08484554290771</v>
       </c>
       <c r="H344" t="n">
         <v>309892</v>
@@ -10374,7 +10374,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10471415519714</v>
+        <v>3.10471439361572</v>
       </c>
       <c r="H345" t="n">
         <v>353071</v>
@@ -10403,7 +10403,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637111663818</v>
+        <v>3.1563708782196</v>
       </c>
       <c r="H346" t="n">
         <v>987482</v>
@@ -10461,7 +10461,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.0066978931427</v>
+        <v>3.00669813156128</v>
       </c>
       <c r="H348" t="n">
         <v>392406</v>
@@ -10490,7 +10490,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G349" t="n">
-        <v>3.05967950820923</v>
+        <v>3.05967974662781</v>
       </c>
       <c r="H349" t="n">
         <v>335842</v>
@@ -10519,7 +10519,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G350" t="n">
-        <v>3.03981184959412</v>
+        <v>3.03981161117554</v>
       </c>
       <c r="H350" t="n">
         <v>361444</v>
@@ -10548,7 +10548,7 @@
         <v>4.5</v>
       </c>
       <c r="G351" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H351" t="n">
         <v>622537</v>
@@ -10577,7 +10577,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159562110901</v>
+        <v>2.87159538269043</v>
       </c>
       <c r="H352" t="n">
         <v>379734</v>
@@ -10664,7 +10664,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G355" t="n">
-        <v>2.9512186050415</v>
+        <v>2.95121884346008</v>
       </c>
       <c r="H355" t="n">
         <v>365296</v>
@@ -10751,7 +10751,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772770881653</v>
+        <v>2.91772794723511</v>
       </c>
       <c r="H358" t="n">
         <v>201245</v>
@@ -10780,7 +10780,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G359" t="n">
-        <v>2.92308616638184</v>
+        <v>2.92308592796326</v>
       </c>
       <c r="H359" t="n">
         <v>298337</v>
@@ -10809,7 +10809,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093518257141</v>
+        <v>2.89093494415283</v>
       </c>
       <c r="H360" t="n">
         <v>173469</v>
@@ -10896,7 +10896,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G363" t="n">
-        <v>2.82395315170288</v>
+        <v>2.82395339012146</v>
       </c>
       <c r="H363" t="n">
         <v>342599</v>
@@ -10925,7 +10925,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.8333306312561</v>
+        <v>2.83333039283752</v>
       </c>
       <c r="H364" t="n">
         <v>80574</v>
@@ -10954,7 +10954,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>2.78644347190857</v>
+        <v>2.78644323348999</v>
       </c>
       <c r="H365" t="n">
         <v>82995</v>
@@ -10983,7 +10983,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="n">
-        <v>2.79448080062866</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H366" t="n">
         <v>170095</v>
@@ -11012,7 +11012,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.76768827438354</v>
+        <v>2.76768851280212</v>
       </c>
       <c r="H367" t="n">
         <v>132754</v>
@@ -11041,7 +11041,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H368" t="n">
         <v>291905</v>
@@ -11157,7 +11157,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>2.6725742816925</v>
+        <v>2.67257404327393</v>
       </c>
       <c r="H372" t="n">
         <v>256578</v>
@@ -11331,7 +11331,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649843215942</v>
+        <v>2.656498670578</v>
       </c>
       <c r="H378" t="n">
         <v>194294</v>
@@ -11360,7 +11360,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>2.65247964859009</v>
+        <v>2.65247988700867</v>
       </c>
       <c r="H379" t="n">
         <v>150080</v>
@@ -11389,7 +11389,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G380" t="n">
-        <v>2.66855502128601</v>
+        <v>2.66855549812317</v>
       </c>
       <c r="H380" t="n">
         <v>368830</v>
@@ -11447,7 +11447,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568712234497</v>
+        <v>2.62568688392639</v>
       </c>
       <c r="H382" t="n">
         <v>194044</v>
@@ -11476,7 +11476,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621500968933</v>
+        <v>2.59621477127075</v>
       </c>
       <c r="H383" t="n">
         <v>275930</v>
@@ -11505,7 +11505,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>2.56942224502563</v>
+        <v>2.56942200660706</v>
       </c>
       <c r="H384" t="n">
         <v>134122</v>
@@ -11534,7 +11534,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G385" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H385" t="n">
         <v>222513</v>
@@ -11563,7 +11563,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G386" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291290283203</v>
       </c>
       <c r="H386" t="n">
         <v>259728</v>
@@ -11592,7 +11592,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="n">
-        <v>2.59487557411194</v>
+        <v>2.59487533569336</v>
       </c>
       <c r="H387" t="n">
         <v>168180</v>
@@ -11650,7 +11650,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870532989502</v>
       </c>
       <c r="H389" t="n">
         <v>213962</v>
@@ -11737,7 +11737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.74625396728516</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H392" t="n">
         <v>689944</v>
@@ -11911,7 +11911,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G398" t="n">
-        <v>2.64310216903687</v>
+        <v>2.64310240745544</v>
       </c>
       <c r="H398" t="n">
         <v>179459</v>
@@ -12056,7 +12056,7 @@
         <v>3.89599990844727</v>
       </c>
       <c r="G403" t="n">
-        <v>2.60961151123047</v>
+        <v>2.60961127281189</v>
       </c>
       <c r="H403" t="n">
         <v>128306</v>
@@ -12085,7 +12085,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H404" t="n">
         <v>112728</v>
@@ -12143,7 +12143,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.65381956100464</v>
+        <v>2.65381932258606</v>
       </c>
       <c r="H406" t="n">
         <v>110887</v>
@@ -12201,7 +12201,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G408" t="n">
-        <v>2.6725742816925</v>
+        <v>2.67257404327393</v>
       </c>
       <c r="H408" t="n">
         <v>128788</v>
@@ -12230,7 +12230,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G409" t="n">
-        <v>2.67391419410706</v>
+        <v>2.67391395568848</v>
       </c>
       <c r="H409" t="n">
         <v>148113</v>
@@ -12288,7 +12288,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G411" t="n">
-        <v>2.70338559150696</v>
+        <v>2.70338582992554</v>
       </c>
       <c r="H411" t="n">
         <v>157359</v>
@@ -12317,7 +12317,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H412" t="n">
         <v>148944</v>
@@ -12346,7 +12346,7 @@
         <v>3.88599991798401</v>
       </c>
       <c r="G413" t="n">
-        <v>2.60291314125061</v>
+        <v>2.60291290283203</v>
       </c>
       <c r="H413" t="n">
         <v>90682</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H414" t="n">
         <v>196816</v>
@@ -12404,7 +12404,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.56138443946838</v>
+        <v>2.56138467788696</v>
       </c>
       <c r="H415" t="n">
         <v>116446</v>
@@ -12462,7 +12462,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H417" t="n">
         <v>103218</v>
@@ -12491,7 +12491,7 @@
         <v>3.75</v>
       </c>
       <c r="G418" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181817054749</v>
       </c>
       <c r="H418" t="n">
         <v>297656</v>
@@ -12520,7 +12520,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459191322327</v>
+        <v>2.53459167480469</v>
       </c>
       <c r="H419" t="n">
         <v>215549</v>
@@ -12549,7 +12549,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G420" t="n">
-        <v>2.5225350856781</v>
+        <v>2.52253484725952</v>
       </c>
       <c r="H420" t="n">
         <v>95268</v>
@@ -12578,7 +12578,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325223922729</v>
+        <v>2.53325200080872</v>
       </c>
       <c r="H421" t="n">
         <v>130865</v>
@@ -12723,7 +12723,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G426" t="n">
-        <v>2.48770475387573</v>
+        <v>2.48770451545715</v>
       </c>
       <c r="H426" t="n">
         <v>80945</v>
@@ -12752,7 +12752,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56004500389099</v>
+        <v>2.56004476547241</v>
       </c>
       <c r="H427" t="n">
         <v>193537</v>
@@ -12810,7 +12810,7 @@
         <v>3.8840000629425</v>
       </c>
       <c r="G429" t="n">
-        <v>2.60157370567322</v>
+        <v>2.60157346725464</v>
       </c>
       <c r="H429" t="n">
         <v>130021</v>
@@ -12839,7 +12839,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200719833374</v>
+        <v>2.55200672149658</v>
       </c>
       <c r="H430" t="n">
         <v>130300</v>
@@ -12897,7 +12897,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H432" t="n">
         <v>63021</v>
@@ -12955,7 +12955,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G434" t="n">
-        <v>2.81189632415771</v>
+        <v>2.81189656257629</v>
       </c>
       <c r="H434" t="n">
         <v>677293</v>
@@ -12984,7 +12984,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323623657227</v>
       </c>
       <c r="H435" t="n">
         <v>606578</v>
@@ -13071,7 +13071,7 @@
         <v>4.33199977874756</v>
       </c>
       <c r="G438" t="n">
-        <v>2.90165209770203</v>
+        <v>2.90165185928345</v>
       </c>
       <c r="H438" t="n">
         <v>438391</v>
@@ -13100,7 +13100,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H439" t="n">
         <v>359505</v>
@@ -13158,7 +13158,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>2.91504859924316</v>
+        <v>2.91504883766174</v>
       </c>
       <c r="H441" t="n">
         <v>331954</v>
@@ -13216,7 +13216,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136843681335</v>
+        <v>2.84136867523193</v>
       </c>
       <c r="H443" t="n">
         <v>279165</v>
@@ -13303,7 +13303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323575973511</v>
+        <v>2.81323623657227</v>
       </c>
       <c r="H446" t="n">
         <v>218622</v>
@@ -13419,7 +13419,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>2.79448080062866</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H450" t="n">
         <v>261468</v>
@@ -13448,7 +13448,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.74625396728516</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H451" t="n">
         <v>306011</v>
@@ -13477,7 +13477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>2.74625396728516</v>
+        <v>2.74625420570374</v>
       </c>
       <c r="H452" t="n">
         <v>174105</v>
@@ -13535,7 +13535,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G454" t="n">
-        <v>2.83868932723999</v>
+        <v>2.83868908882141</v>
       </c>
       <c r="H454" t="n">
         <v>379887</v>
@@ -13738,7 +13738,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="n">
-        <v>2.86280274391174</v>
+        <v>2.86280250549316</v>
       </c>
       <c r="H461" t="n">
         <v>278042</v>
@@ -13796,7 +13796,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G463" t="n">
-        <v>2.92710542678833</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H463" t="n">
         <v>290532</v>
@@ -13825,7 +13825,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916177749634</v>
+        <v>2.93916153907776</v>
       </c>
       <c r="H464" t="n">
         <v>296201</v>
@@ -13883,7 +13883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94719958305359</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H466" t="n">
         <v>276862</v>
@@ -13912,7 +13912,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>2.92710542678833</v>
+        <v>2.92710494995117</v>
       </c>
       <c r="H467" t="n">
         <v>1298241</v>
@@ -13999,7 +13999,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370868682861</v>
+        <v>2.91370844841003</v>
       </c>
       <c r="H470" t="n">
         <v>103518</v>
@@ -14028,7 +14028,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648266792297</v>
+        <v>2.93648242950439</v>
       </c>
       <c r="H471" t="n">
         <v>136035</v>
@@ -14144,7 +14144,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.88557648658752</v>
+        <v>2.8855767250061</v>
       </c>
       <c r="H475" t="n">
         <v>113109</v>
@@ -14173,7 +14173,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031218528748</v>
+        <v>2.90031242370605</v>
       </c>
       <c r="H476" t="n">
         <v>293657</v>
@@ -14231,7 +14231,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270834922791</v>
+        <v>2.84270811080933</v>
       </c>
       <c r="H478" t="n">
         <v>266545</v>
@@ -14289,7 +14289,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76232981681824</v>
+        <v>2.76233005523682</v>
       </c>
       <c r="H480" t="n">
         <v>456143</v>
@@ -14347,7 +14347,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H482" t="n">
         <v>381717</v>
@@ -14463,7 +14463,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H486" t="n">
         <v>174243</v>
@@ -14521,7 +14521,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G488" t="n">
-        <v>2.66587615013123</v>
+        <v>2.6658763885498</v>
       </c>
       <c r="H488" t="n">
         <v>291126</v>
@@ -14550,7 +14550,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="n">
-        <v>2.59487557411194</v>
+        <v>2.59487533569336</v>
       </c>
       <c r="H489" t="n">
         <v>256882</v>
@@ -14579,7 +14579,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>2.65247964859009</v>
+        <v>2.65247988700867</v>
       </c>
       <c r="H490" t="n">
         <v>191291</v>
@@ -14637,7 +14637,7 @@
         <v>4</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67927265167236</v>
+        <v>2.67927241325378</v>
       </c>
       <c r="H492" t="n">
         <v>427250</v>
@@ -14666,7 +14666,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908338546753</v>
+        <v>2.63908314704895</v>
       </c>
       <c r="H493" t="n">
         <v>248344</v>
@@ -14811,7 +14811,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.62434697151184</v>
+        <v>2.624347448349</v>
       </c>
       <c r="H498" t="n">
         <v>109452</v>
@@ -14840,7 +14840,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H499" t="n">
         <v>464341</v>
@@ -14898,7 +14898,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H501" t="n">
         <v>511482</v>
@@ -14927,7 +14927,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.56138443946838</v>
+        <v>2.56138467788696</v>
       </c>
       <c r="H502" t="n">
         <v>215962</v>
@@ -14956,7 +14956,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H503" t="n">
         <v>442866</v>
@@ -14985,7 +14985,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H504" t="n">
         <v>308246</v>
@@ -15014,7 +15014,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51315760612488</v>
+        <v>2.51315784454346</v>
       </c>
       <c r="H505" t="n">
         <v>239707</v>
@@ -15043,7 +15043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H506" t="n">
         <v>188484</v>
@@ -15072,7 +15072,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325223922729</v>
+        <v>2.53325200080872</v>
       </c>
       <c r="H507" t="n">
         <v>155274</v>
@@ -15130,7 +15130,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449728012085</v>
+        <v>2.51449751853943</v>
       </c>
       <c r="H509" t="n">
         <v>151770</v>
@@ -15275,7 +15275,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.50846886634827</v>
+        <v>2.50846838951111</v>
       </c>
       <c r="H514" t="n">
         <v>345941</v>
@@ -15333,7 +15333,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884692192078</v>
+        <v>2.58884716033936</v>
       </c>
       <c r="H516" t="n">
         <v>358297</v>
@@ -15391,7 +15391,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G518" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H518" t="n">
         <v>296465</v>
@@ -15420,7 +15420,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G519" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H519" t="n">
         <v>422125</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H520" t="n">
         <v>236775</v>
@@ -15536,7 +15536,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.53861093521118</v>
+        <v>2.5386106967926</v>
       </c>
       <c r="H523" t="n">
         <v>500528</v>
@@ -15594,7 +15594,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870509147644</v>
+        <v>2.55870532989502</v>
       </c>
       <c r="H525" t="n">
         <v>259926</v>
@@ -15681,7 +15681,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G528" t="n">
-        <v>2.57879948616028</v>
+        <v>2.57879972457886</v>
       </c>
       <c r="H528" t="n">
         <v>219606</v>
@@ -15739,7 +15739,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>2.61229085922241</v>
+        <v>2.61229062080383</v>
       </c>
       <c r="H530" t="n">
         <v>222183</v>
@@ -15768,7 +15768,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="n">
-        <v>2.57545065879822</v>
+        <v>2.57545113563538</v>
       </c>
       <c r="H531" t="n">
         <v>188683</v>
@@ -15797,7 +15797,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G532" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H532" t="n">
         <v>266372</v>
@@ -15855,7 +15855,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51851582527161</v>
+        <v>2.51851606369019</v>
       </c>
       <c r="H534" t="n">
         <v>180644</v>
@@ -15942,7 +15942,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>2.53526139259338</v>
+        <v>2.53526163101196</v>
       </c>
       <c r="H537" t="n">
         <v>618411</v>
@@ -15971,7 +15971,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G538" t="n">
-        <v>2.54865789413452</v>
+        <v>2.5486581325531</v>
       </c>
       <c r="H538" t="n">
         <v>187640</v>
@@ -16029,7 +16029,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G540" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H540" t="n">
         <v>333031</v>
@@ -16232,7 +16232,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G547" t="n">
-        <v>2.40464735031128</v>
+        <v>2.4046471118927</v>
       </c>
       <c r="H547" t="n">
         <v>141963</v>
@@ -16290,7 +16290,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>2.39794874191284</v>
+        <v>2.39794898033142</v>
       </c>
       <c r="H549" t="n">
         <v>151085</v>
@@ -16348,7 +16348,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G551" t="n">
-        <v>2.38120341300964</v>
+        <v>2.38120365142822</v>
       </c>
       <c r="H551" t="n">
         <v>177056</v>
@@ -16406,7 +16406,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.38790130615234</v>
+        <v>2.38790154457092</v>
       </c>
       <c r="H553" t="n">
         <v>261710</v>
@@ -16435,7 +16435,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G554" t="n">
-        <v>2.26398515701294</v>
+        <v>2.26398539543152</v>
       </c>
       <c r="H554" t="n">
         <v>968278</v>
@@ -16609,7 +16609,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G560" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H560" t="n">
         <v>289529</v>
@@ -16638,7 +16638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700336456299</v>
+        <v>2.19700312614441</v>
       </c>
       <c r="H561" t="n">
         <v>269006</v>
@@ -16667,7 +16667,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365429878235</v>
+        <v>2.19365453720093</v>
       </c>
       <c r="H562" t="n">
         <v>397917</v>
@@ -16696,7 +16696,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337087631226</v>
+        <v>2.13337063789368</v>
       </c>
       <c r="H563" t="n">
         <v>656760</v>
@@ -16754,7 +16754,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695592880249</v>
+        <v>2.18695640563965</v>
       </c>
       <c r="H565" t="n">
         <v>2292967</v>
@@ -16812,7 +16812,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G567" t="n">
-        <v>2.25728702545166</v>
+        <v>2.25728678703308</v>
       </c>
       <c r="H567" t="n">
         <v>535502</v>
@@ -16870,7 +16870,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.2505886554718</v>
+        <v>2.25058913230896</v>
       </c>
       <c r="H569" t="n">
         <v>201800</v>
@@ -16899,7 +16899,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G570" t="n">
-        <v>2.2438907623291</v>
+        <v>2.24389052391052</v>
       </c>
       <c r="H570" t="n">
         <v>280790</v>
@@ -16928,7 +16928,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G571" t="n">
-        <v>2.33096718788147</v>
+        <v>2.33096694946289</v>
       </c>
       <c r="H571" t="n">
         <v>730410</v>
@@ -16957,7 +16957,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.4113450050354</v>
+        <v>2.41134524345398</v>
       </c>
       <c r="H572" t="n">
         <v>584347</v>
@@ -16986,7 +16986,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.38455247879028</v>
+        <v>2.38455271720886</v>
       </c>
       <c r="H573" t="n">
         <v>439152</v>
@@ -17044,7 +17044,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H575" t="n">
         <v>419566</v>
@@ -17073,7 +17073,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H576" t="n">
         <v>366638</v>
@@ -17102,7 +17102,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H577" t="n">
         <v>339561</v>
@@ -17131,7 +17131,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G578" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H578" t="n">
         <v>231016</v>
@@ -17160,7 +17160,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G579" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H579" t="n">
         <v>244165</v>
@@ -17218,7 +17218,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>2.43813800811768</v>
+        <v>2.4381377696991</v>
       </c>
       <c r="H581" t="n">
         <v>150530</v>
@@ -17276,7 +17276,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H583" t="n">
         <v>185158</v>
@@ -17305,7 +17305,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H584" t="n">
         <v>89113</v>
@@ -17334,7 +17334,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G585" t="n">
-        <v>2.45153403282166</v>
+        <v>2.45153427124023</v>
       </c>
       <c r="H585" t="n">
         <v>145222</v>
@@ -17392,7 +17392,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G587" t="n">
-        <v>2.49507236480713</v>
+        <v>2.49507212638855</v>
       </c>
       <c r="H587" t="n">
         <v>277880</v>
@@ -17421,7 +17421,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832751274109</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H588" t="n">
         <v>131179</v>
@@ -17508,7 +17508,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832751274109</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H591" t="n">
         <v>51454</v>
@@ -17537,7 +17537,7 @@
         <v>3.75</v>
       </c>
       <c r="G592" t="n">
-        <v>2.51181769371033</v>
+        <v>2.51181817054749</v>
       </c>
       <c r="H592" t="n">
         <v>172383</v>
@@ -17566,7 +17566,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G593" t="n">
-        <v>2.45153403282166</v>
+        <v>2.45153427124023</v>
       </c>
       <c r="H593" t="n">
         <v>194484</v>
@@ -17595,7 +17595,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G594" t="n">
-        <v>2.50511956214905</v>
+        <v>2.50511980056763</v>
       </c>
       <c r="H594" t="n">
         <v>142722</v>
@@ -17653,7 +17653,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="n">
-        <v>2.48837399482727</v>
+        <v>2.48837423324585</v>
       </c>
       <c r="H596" t="n">
         <v>218613</v>
@@ -17682,7 +17682,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>2.49507236480713</v>
+        <v>2.49507212638855</v>
       </c>
       <c r="H597" t="n">
         <v>234943</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832751274109</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H598" t="n">
         <v>111857</v>
@@ -17798,7 +17798,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H601" t="n">
         <v>180468</v>
@@ -17827,7 +17827,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832751274109</v>
+        <v>2.47832703590393</v>
       </c>
       <c r="H602" t="n">
         <v>187716</v>
@@ -17856,7 +17856,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G603" t="n">
-        <v>2.54028558731079</v>
+        <v>2.54028534889221</v>
       </c>
       <c r="H603" t="n">
         <v>178403</v>
@@ -17943,7 +17943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310534477234</v>
       </c>
       <c r="H606" t="n">
         <v>447106</v>
@@ -17972,7 +17972,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H607" t="n">
         <v>439315</v>
@@ -18030,7 +18030,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G609" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H609" t="n">
         <v>162895</v>
@@ -18059,7 +18059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.22361016273499</v>
+        <v>2.22360992431641</v>
       </c>
       <c r="H610" t="n">
         <v>258239</v>
@@ -18088,7 +18088,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737859725952</v>
       </c>
       <c r="H611" t="n">
         <v>302598</v>
@@ -18146,7 +18146,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H613" t="n">
         <v>279124</v>
@@ -18175,7 +18175,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H614" t="n">
         <v>249358</v>
@@ -18204,7 +18204,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G615" t="n">
-        <v>2.16165208816528</v>
+        <v>2.1616518497467</v>
       </c>
       <c r="H615" t="n">
         <v>293231</v>
@@ -18262,7 +18262,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>2.22016787528992</v>
+        <v>2.22016763687134</v>
       </c>
       <c r="H617" t="n">
         <v>287908</v>
@@ -18349,7 +18349,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>2.22016787528992</v>
+        <v>2.22016763687134</v>
       </c>
       <c r="H620" t="n">
         <v>204163</v>
@@ -18378,7 +18378,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="n">
-        <v>2.23737835884094</v>
+        <v>2.23737859725952</v>
       </c>
       <c r="H621" t="n">
         <v>102223</v>
@@ -18523,7 +18523,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34408402442932</v>
+        <v>2.3440842628479</v>
       </c>
       <c r="H626" t="n">
         <v>133097</v>
@@ -18552,7 +18552,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>2.35441088676453</v>
+        <v>2.35441040992737</v>
       </c>
       <c r="H627" t="n">
         <v>289153</v>
@@ -18581,7 +18581,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H628" t="n">
         <v>104749</v>
@@ -18610,7 +18610,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>2.39571619033813</v>
+        <v>2.39571595191956</v>
       </c>
       <c r="H629" t="n">
         <v>232962</v>
@@ -18697,7 +18697,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915823936462</v>
+        <v>2.39915800094604</v>
       </c>
       <c r="H632" t="n">
         <v>997504</v>
@@ -18726,7 +18726,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473727226257</v>
+        <v>2.36473703384399</v>
       </c>
       <c r="H633" t="n">
         <v>866249</v>
@@ -18755,7 +18755,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310510635376</v>
+        <v>2.31310534477234</v>
       </c>
       <c r="H634" t="n">
         <v>291169</v>
@@ -18784,7 +18784,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.29933643341064</v>
+        <v>2.2993369102478</v>
       </c>
       <c r="H635" t="n">
         <v>210570</v>
@@ -18813,7 +18813,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27524185180664</v>
+        <v>2.27524209022522</v>
       </c>
       <c r="H636" t="n">
         <v>402407</v>
@@ -18929,7 +18929,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.28556847572327</v>
+        <v>2.28556823730469</v>
       </c>
       <c r="H640" t="n">
         <v>188973</v>
@@ -18958,7 +18958,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>2.30622053146362</v>
+        <v>2.3062207698822</v>
       </c>
       <c r="H641" t="n">
         <v>66001</v>
@@ -19045,7 +19045,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H644" t="n">
         <v>158331</v>
@@ -19074,7 +19074,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G645" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H645" t="n">
         <v>204003</v>
@@ -19103,7 +19103,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G646" t="n">
-        <v>2.24082088470459</v>
+        <v>2.24082064628601</v>
       </c>
       <c r="H646" t="n">
         <v>138242</v>
@@ -19132,7 +19132,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G647" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H647" t="n">
         <v>91283</v>
@@ -19161,7 +19161,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H648" t="n">
         <v>204541</v>
@@ -19190,7 +19190,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>2.19951510429382</v>
+        <v>2.1995153427124</v>
       </c>
       <c r="H649" t="n">
         <v>159276</v>
@@ -19219,7 +19219,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G650" t="n">
-        <v>2.17886257171631</v>
+        <v>2.17886233329773</v>
       </c>
       <c r="H650" t="n">
         <v>98263</v>
@@ -19306,7 +19306,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G653" t="n">
-        <v>2.19607329368591</v>
+        <v>2.19607281684875</v>
       </c>
       <c r="H653" t="n">
         <v>33141</v>
@@ -19335,7 +19335,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="n">
-        <v>2.19951510429382</v>
+        <v>2.1995153427124</v>
       </c>
       <c r="H654" t="n">
         <v>79584</v>
@@ -19364,7 +19364,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.14444160461426</v>
+        <v>2.14444136619568</v>
       </c>
       <c r="H655" t="n">
         <v>109564</v>
@@ -19422,7 +19422,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15820956230164</v>
+        <v>2.15820980072021</v>
       </c>
       <c r="H657" t="n">
         <v>127746</v>
@@ -19451,7 +19451,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.22361016273499</v>
+        <v>2.22360992431641</v>
       </c>
       <c r="H658" t="n">
         <v>79691</v>
@@ -19509,7 +19509,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.22016787528992</v>
+        <v>2.22016763687134</v>
       </c>
       <c r="H660" t="n">
         <v>72516</v>
@@ -19538,7 +19538,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H661" t="n">
         <v>58784</v>
@@ -19567,7 +19567,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393654823303</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H662" t="n">
         <v>94242</v>
@@ -19596,7 +19596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H663" t="n">
         <v>128498</v>
@@ -19625,7 +19625,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="n">
-        <v>2.29933643341064</v>
+        <v>2.2993369102478</v>
       </c>
       <c r="H664" t="n">
         <v>149672</v>
@@ -19683,7 +19683,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>2.30622053146362</v>
+        <v>2.3062207698822</v>
       </c>
       <c r="H666" t="n">
         <v>427892</v>
@@ -19712,7 +19712,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H667" t="n">
         <v>147403</v>
@@ -19741,7 +19741,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>2.2442626953125</v>
+        <v>2.24426293373108</v>
       </c>
       <c r="H668" t="n">
         <v>79510</v>
@@ -19799,7 +19799,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>2.20639967918396</v>
+        <v>2.2063992023468</v>
       </c>
       <c r="H670" t="n">
         <v>234133</v>
@@ -19828,7 +19828,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H671" t="n">
         <v>122606</v>
@@ -19857,7 +19857,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G672" t="n">
-        <v>2.16165208816528</v>
+        <v>2.1616518497467</v>
       </c>
       <c r="H672" t="n">
         <v>76727</v>
@@ -19886,7 +19886,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574643135071</v>
+        <v>2.18574666976929</v>
       </c>
       <c r="H673" t="n">
         <v>87561</v>
@@ -19915,7 +19915,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H674" t="n">
         <v>127368</v>
@@ -19973,7 +19973,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G676" t="n">
-        <v>2.15476775169373</v>
+        <v>2.1547679901123</v>
       </c>
       <c r="H676" t="n">
         <v>182359</v>
@@ -20031,7 +20031,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G678" t="n">
-        <v>2.12034630775452</v>
+        <v>2.1203465461731</v>
       </c>
       <c r="H678" t="n">
         <v>97627</v>
@@ -20060,7 +20060,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G679" t="n">
-        <v>2.11002039909363</v>
+        <v>2.11002016067505</v>
       </c>
       <c r="H679" t="n">
         <v>147813</v>
@@ -20089,7 +20089,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H680" t="n">
         <v>72566</v>
@@ -20176,7 +20176,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690449714661</v>
       </c>
       <c r="H683" t="n">
         <v>89809</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H684" t="n">
         <v>106959</v>
@@ -20292,7 +20292,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690425872803</v>
+        <v>2.11690449714661</v>
       </c>
       <c r="H687" t="n">
         <v>150304</v>
@@ -20321,7 +20321,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G688" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H688" t="n">
         <v>283824</v>
@@ -20350,7 +20350,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G689" t="n">
-        <v>2.16165208816528</v>
+        <v>2.1616518497467</v>
       </c>
       <c r="H689" t="n">
         <v>92233</v>
@@ -20379,7 +20379,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>2.12034630775452</v>
+        <v>2.1203465461731</v>
       </c>
       <c r="H690" t="n">
         <v>188909</v>
@@ -20408,7 +20408,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H691" t="n">
         <v>98598</v>
@@ -20437,7 +20437,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H692" t="n">
         <v>87021</v>
@@ -20495,7 +20495,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378835678101</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H694" t="n">
         <v>310317</v>
@@ -20553,7 +20553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H696" t="n">
         <v>205834</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H697" t="n">
         <v>159262</v>
@@ -20640,7 +20640,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H699" t="n">
         <v>101472</v>
@@ -20669,7 +20669,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H700" t="n">
         <v>104775</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H701" t="n">
         <v>280938</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.11346197128296</v>
+        <v>2.11346220970154</v>
       </c>
       <c r="H702" t="n">
         <v>120044</v>
@@ -20785,7 +20785,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H704" t="n">
         <v>153586</v>
@@ -20843,7 +20843,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H706" t="n">
         <v>108391</v>
@@ -20872,7 +20872,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G707" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H707" t="n">
         <v>102562</v>
@@ -20901,7 +20901,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>1.98266172409058</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H708" t="n">
         <v>124414</v>
@@ -20959,7 +20959,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512449741364</v>
+        <v>1.95512461662292</v>
       </c>
       <c r="H710" t="n">
         <v>129165</v>
@@ -20988,7 +20988,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H711" t="n">
         <v>98948</v>
@@ -21017,7 +21017,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.94135618209839</v>
+        <v>1.9413560628891</v>
       </c>
       <c r="H712" t="n">
         <v>74593</v>
@@ -21046,7 +21046,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>1.98266172409058</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H713" t="n">
         <v>101638</v>
@@ -21075,7 +21075,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>1.98266172409058</v>
+        <v>1.982661485672</v>
       </c>
       <c r="H714" t="n">
         <v>78349</v>
@@ -21104,7 +21104,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.95856690406799</v>
+        <v>1.95856666564941</v>
       </c>
       <c r="H715" t="n">
         <v>70649</v>
@@ -21133,7 +21133,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H716" t="n">
         <v>173384</v>
@@ -21162,7 +21162,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H717" t="n">
         <v>97454</v>
@@ -21191,7 +21191,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G718" t="n">
-        <v>1.84841883182526</v>
+        <v>1.84841859340668</v>
       </c>
       <c r="H718" t="n">
         <v>92562</v>
@@ -21249,7 +21249,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.91726124286652</v>
+        <v>1.9172614812851</v>
       </c>
       <c r="H720" t="n">
         <v>126796</v>
@@ -21278,7 +21278,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G721" t="n">
-        <v>1.88284003734589</v>
+        <v>1.8828399181366</v>
       </c>
       <c r="H721" t="n">
         <v>101180</v>
@@ -21365,7 +21365,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>1.92414569854736</v>
+        <v>1.92414557933807</v>
       </c>
       <c r="H724" t="n">
         <v>125557</v>
@@ -21394,7 +21394,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921931743622</v>
+        <v>1.97921979427338</v>
       </c>
       <c r="H725" t="n">
         <v>62710</v>
@@ -21423,7 +21423,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298810958862</v>
+        <v>1.99298787117004</v>
       </c>
       <c r="H726" t="n">
         <v>108169</v>
@@ -21452,7 +21452,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610377311707</v>
+        <v>1.98610365390778</v>
       </c>
       <c r="H727" t="n">
         <v>75372</v>
@@ -21568,7 +21568,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G731" t="n">
-        <v>2.14099907875061</v>
+        <v>2.14099931716919</v>
       </c>
       <c r="H731" t="n">
         <v>181838</v>
@@ -21597,7 +21597,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H732" t="n">
         <v>149126</v>
@@ -21684,7 +21684,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G735" t="n">
-        <v>2.04461979866028</v>
+        <v>2.04462003707886</v>
       </c>
       <c r="H735" t="n">
         <v>174458</v>
@@ -21713,7 +21713,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.06183004379272</v>
+        <v>2.0618302822113</v>
       </c>
       <c r="H736" t="n">
         <v>119731</v>
@@ -21742,7 +21742,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G737" t="n">
-        <v>2.00331449508667</v>
+        <v>2.00331425666809</v>
       </c>
       <c r="H737" t="n">
         <v>129394</v>
@@ -21771,7 +21771,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889305114746</v>
+        <v>1.96889293193817</v>
       </c>
       <c r="H738" t="n">
         <v>161205</v>
@@ -21800,7 +21800,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168244838715</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H739" t="n">
         <v>264586</v>
@@ -21829,7 +21829,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.92758738994598</v>
+        <v>1.92758750915527</v>
       </c>
       <c r="H740" t="n">
         <v>177737</v>
@@ -21858,7 +21858,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G741" t="n">
-        <v>1.96200883388519</v>
+        <v>1.96200907230377</v>
       </c>
       <c r="H741" t="n">
         <v>248184</v>
@@ -21887,7 +21887,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G742" t="n">
-        <v>2.09625148773193</v>
+        <v>2.09625172615051</v>
       </c>
       <c r="H742" t="n">
         <v>343613</v>
@@ -21916,7 +21916,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G743" t="n">
-        <v>2.15476775169373</v>
+        <v>2.1547679901123</v>
       </c>
       <c r="H743" t="n">
         <v>238713</v>
@@ -21945,7 +21945,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>2.20639967918396</v>
+        <v>2.2063992023468</v>
       </c>
       <c r="H744" t="n">
         <v>196223</v>
@@ -21974,7 +21974,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H745" t="n">
         <v>209439</v>
@@ -22032,7 +22032,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H747" t="n">
         <v>206720</v>
@@ -22090,7 +22090,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>2.2270519733429</v>
+        <v>2.22705221176147</v>
       </c>
       <c r="H749" t="n">
         <v>156319</v>
@@ -22206,7 +22206,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.08936738967896</v>
+        <v>2.08936762809753</v>
       </c>
       <c r="H753" t="n">
         <v>238366</v>
@@ -22264,7 +22264,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G755" t="n">
-        <v>2.15476775169373</v>
+        <v>2.1547679901123</v>
       </c>
       <c r="H755" t="n">
         <v>162636</v>
@@ -22293,7 +22293,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378835678101</v>
+        <v>2.12378859519958</v>
       </c>
       <c r="H756" t="n">
         <v>149343</v>
@@ -22351,7 +22351,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="n">
-        <v>2.17197847366333</v>
+        <v>2.17197823524475</v>
       </c>
       <c r="H758" t="n">
         <v>265608</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245257377625</v>
+        <v>2.29245233535767</v>
       </c>
       <c r="H759" t="n">
         <v>342700</v>
@@ -22438,7 +22438,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="n">
-        <v>2.33375787734985</v>
+        <v>2.33375811576843</v>
       </c>
       <c r="H761" t="n">
         <v>787607</v>
@@ -22467,7 +22467,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.34408402442932</v>
+        <v>2.3440842628479</v>
       </c>
       <c r="H762" t="n">
         <v>257956</v>
@@ -22554,7 +22554,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.49209523200989</v>
+        <v>2.49209570884705</v>
       </c>
       <c r="H765" t="n">
         <v>207696</v>
@@ -22612,7 +22612,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>2.44390559196472</v>
+        <v>2.4439058303833</v>
       </c>
       <c r="H767" t="n">
         <v>205883</v>
@@ -22641,7 +22641,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G768" t="n">
-        <v>2.44390559196472</v>
+        <v>2.4439058303833</v>
       </c>
       <c r="H768" t="n">
         <v>360249</v>
@@ -22728,7 +22728,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H771" t="n">
         <v>431119</v>
@@ -22757,7 +22757,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046378135681</v>
+        <v>2.44046354293823</v>
       </c>
       <c r="H772" t="n">
         <v>369438</v>
@@ -22844,7 +22844,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H775" t="n">
         <v>412613</v>
@@ -22873,7 +22873,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G776" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H776" t="n">
         <v>426695</v>
@@ -22902,7 +22902,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>2.53684282302856</v>
+        <v>2.53684306144714</v>
       </c>
       <c r="H777" t="n">
         <v>356598</v>
@@ -22931,7 +22931,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455860137939</v>
+        <v>2.46455836296082</v>
       </c>
       <c r="H778" t="n">
         <v>296450</v>
@@ -22989,7 +22989,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307462692261</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H780" t="n">
         <v>192769</v>
@@ -23018,7 +23018,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307462692261</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H781" t="n">
         <v>177735</v>
@@ -23047,7 +23047,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>2.51274824142456</v>
+        <v>2.51274800300598</v>
       </c>
       <c r="H782" t="n">
         <v>217858</v>
@@ -23076,7 +23076,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093788146973</v>
+        <v>2.56093764305115</v>
       </c>
       <c r="H783" t="n">
         <v>259927</v>
@@ -23163,7 +23163,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.64354848861694</v>
+        <v>2.64354872703552</v>
       </c>
       <c r="H786" t="n">
         <v>412937</v>
@@ -23192,7 +23192,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="n">
-        <v>2.67108607292175</v>
+        <v>2.67108583450317</v>
       </c>
       <c r="H787" t="n">
         <v>308241</v>
@@ -23250,7 +23250,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G789" t="n">
-        <v>2.67797017097473</v>
+        <v>2.67796993255615</v>
       </c>
       <c r="H789" t="n">
         <v>248259</v>
@@ -23482,7 +23482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601185798645</v>
+        <v>2.61601161956787</v>
       </c>
       <c r="H797" t="n">
         <v>367842</v>
@@ -23511,7 +23511,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880113601685</v>
+        <v>2.59880137443542</v>
       </c>
       <c r="H798" t="n">
         <v>105895</v>
@@ -23540,7 +23540,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G799" t="n">
-        <v>2.56438016891479</v>
+        <v>2.56437993049622</v>
       </c>
       <c r="H799" t="n">
         <v>201471</v>
@@ -23627,7 +23627,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G802" t="n">
-        <v>2.69173860549927</v>
+        <v>2.69173836708069</v>
       </c>
       <c r="H802" t="n">
         <v>302710</v>
@@ -23685,7 +23685,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G804" t="n">
-        <v>2.68485450744629</v>
+        <v>2.68485426902771</v>
       </c>
       <c r="H804" t="n">
         <v>170162</v>
@@ -23714,7 +23714,7 @@
         <v>4</v>
       </c>
       <c r="G805" t="n">
-        <v>2.75369668006897</v>
+        <v>2.75369644165039</v>
       </c>
       <c r="H805" t="n">
         <v>533089</v>
@@ -23830,7 +23830,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G809" t="n">
-        <v>2.74337005615234</v>
+        <v>2.74337029457092</v>
       </c>
       <c r="H809" t="n">
         <v>143894</v>
@@ -23859,7 +23859,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="n">
-        <v>2.72960186004639</v>
+        <v>2.72960162162781</v>
       </c>
       <c r="H810" t="n">
         <v>150232</v>
@@ -23917,7 +23917,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.72960186004639</v>
+        <v>2.72960162162781</v>
       </c>
       <c r="H812" t="n">
         <v>131490</v>
@@ -23975,7 +23975,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.70550680160522</v>
+        <v>2.70550656318665</v>
       </c>
       <c r="H814" t="n">
         <v>151157</v>
@@ -24004,7 +24004,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G815" t="n">
-        <v>2.74337005615234</v>
+        <v>2.74337029457092</v>
       </c>
       <c r="H815" t="n">
         <v>126338</v>
@@ -24033,7 +24033,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>2.76058101654053</v>
+        <v>2.76058125495911</v>
       </c>
       <c r="H816" t="n">
         <v>220094</v>
@@ -24091,7 +24091,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304414749146</v>
+        <v>2.73304390907288</v>
       </c>
       <c r="H818" t="n">
         <v>216455</v>
@@ -24120,7 +24120,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.70550680160522</v>
+        <v>2.70550656318665</v>
       </c>
       <c r="H819" t="n">
         <v>173539</v>
@@ -24207,7 +24207,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>2.61256957054138</v>
+        <v>2.61256980895996</v>
       </c>
       <c r="H822" t="n">
         <v>177668</v>
@@ -24265,7 +24265,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H824" t="n">
         <v>459248</v>
@@ -24294,7 +24294,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H825" t="n">
         <v>305118</v>
@@ -24381,7 +24381,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>2.60912775993347</v>
+        <v>2.60912752151489</v>
       </c>
       <c r="H828" t="n">
         <v>412011</v>
@@ -24410,7 +24410,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322257995605</v>
+        <v>2.63322234153748</v>
       </c>
       <c r="H829" t="n">
         <v>67486</v>
@@ -24526,7 +24526,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G833" t="n">
-        <v>2.51963210105896</v>
+        <v>2.51963257789612</v>
       </c>
       <c r="H833" t="n">
         <v>219045</v>
@@ -24584,7 +24584,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G835" t="n">
-        <v>2.44390559196472</v>
+        <v>2.4439058303833</v>
       </c>
       <c r="H835" t="n">
         <v>355578</v>
@@ -24642,7 +24642,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423221588135</v>
+        <v>2.45423245429993</v>
       </c>
       <c r="H837" t="n">
         <v>108607</v>
@@ -24671,7 +24671,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G838" t="n">
-        <v>2.44390559196472</v>
+        <v>2.4439058303833</v>
       </c>
       <c r="H838" t="n">
         <v>182231</v>
@@ -24700,7 +24700,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>2.4507896900177</v>
+        <v>2.45078992843628</v>
       </c>
       <c r="H839" t="n">
         <v>177889</v>
@@ -24729,7 +24729,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G840" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H840" t="n">
         <v>102179</v>
@@ -24758,7 +24758,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357968330383</v>
+        <v>2.43357944488525</v>
       </c>
       <c r="H841" t="n">
         <v>124221</v>
@@ -24816,7 +24816,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G843" t="n">
-        <v>2.44734787940979</v>
+        <v>2.44734811782837</v>
       </c>
       <c r="H843" t="n">
         <v>82236</v>
@@ -24874,7 +24874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50586414337158</v>
+        <v>2.505863904953</v>
       </c>
       <c r="H845" t="n">
         <v>222012</v>
@@ -24903,7 +24903,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H846" t="n">
         <v>296447</v>
@@ -24932,7 +24932,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="n">
-        <v>2.49553775787354</v>
+        <v>2.49553751945496</v>
       </c>
       <c r="H847" t="n">
         <v>157082</v>
@@ -24961,7 +24961,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>2.49897980690002</v>
+        <v>2.49897956848145</v>
       </c>
       <c r="H848" t="n">
         <v>191698</v>
@@ -24990,7 +24990,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013715744019</v>
+        <v>2.43013739585876</v>
       </c>
       <c r="H849" t="n">
         <v>115219</v>
@@ -25019,7 +25019,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>2.35441088676453</v>
+        <v>2.35441040992737</v>
       </c>
       <c r="H850" t="n">
         <v>388754</v>
@@ -25106,7 +25106,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>2.33031582832336</v>
+        <v>2.33031558990479</v>
       </c>
       <c r="H853" t="n">
         <v>221581</v>
@@ -25222,7 +25222,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G857" t="n">
-        <v>2.11002039909363</v>
+        <v>2.11002016067505</v>
       </c>
       <c r="H857" t="n">
         <v>429648</v>
@@ -25309,7 +25309,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03085136413574</v>
+        <v>2.03085112571716</v>
       </c>
       <c r="H860" t="n">
         <v>287672</v>
@@ -25425,7 +25425,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06153106689453</v>
+        <v>2.06153130531311</v>
       </c>
       <c r="H864" t="n">
         <v>233373</v>
@@ -25454,7 +25454,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99642980098724</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H865" t="n">
         <v>416439</v>
@@ -25483,7 +25483,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>1.96026313304901</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H866" t="n">
         <v>194008</v>
@@ -25512,7 +25512,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472989559174</v>
       </c>
       <c r="H867" t="n">
         <v>171746</v>
@@ -25570,7 +25570,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G869" t="n">
-        <v>1.95302927494049</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H869" t="n">
         <v>222484</v>
@@ -25599,7 +25599,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664632320404</v>
       </c>
       <c r="H870" t="n">
         <v>404038</v>
@@ -25628,7 +25628,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>1.96026313304901</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H871" t="n">
         <v>377733</v>
@@ -25657,7 +25657,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G872" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579577445984</v>
       </c>
       <c r="H872" t="n">
         <v>155594</v>
@@ -25686,7 +25686,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H873" t="n">
         <v>227376</v>
@@ -25715,7 +25715,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H874" t="n">
         <v>251629</v>
@@ -25744,7 +25744,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99642980098724</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H875" t="n">
         <v>184992</v>
@@ -25773,7 +25773,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>1.96026313304901</v>
+        <v>1.96026301383972</v>
       </c>
       <c r="H876" t="n">
         <v>239841</v>
@@ -25802,7 +25802,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>1.97834658622742</v>
+        <v>1.97834634780884</v>
       </c>
       <c r="H877" t="n">
         <v>247637</v>
@@ -25831,7 +25831,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.95302927494049</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H878" t="n">
         <v>109838</v>
@@ -25860,7 +25860,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G879" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579577445984</v>
       </c>
       <c r="H879" t="n">
         <v>155683</v>
@@ -25889,7 +25889,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664632320404</v>
       </c>
       <c r="H880" t="n">
         <v>284652</v>
@@ -25918,7 +25918,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H881" t="n">
         <v>276051</v>
@@ -25947,7 +25947,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H882" t="n">
         <v>279659</v>
@@ -25976,7 +25976,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>1.93132901191711</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H883" t="n">
         <v>1099479</v>
@@ -26005,7 +26005,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H884" t="n">
         <v>286493</v>
@@ -26121,7 +26121,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G888" t="n">
-        <v>1.90962898731232</v>
+        <v>1.90962874889374</v>
       </c>
       <c r="H888" t="n">
         <v>107626</v>
@@ -26150,7 +26150,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.88792848587036</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H889" t="n">
         <v>274027</v>
@@ -26208,7 +26208,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H891" t="n">
         <v>279577</v>
@@ -26237,7 +26237,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H892" t="n">
         <v>470871</v>
@@ -26295,7 +26295,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.8987785577774</v>
+        <v>1.89877867698669</v>
       </c>
       <c r="H894" t="n">
         <v>237876</v>
@@ -26324,7 +26324,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G895" t="n">
-        <v>1.95302927494049</v>
+        <v>1.95302939414978</v>
       </c>
       <c r="H895" t="n">
         <v>800354</v>
@@ -26353,7 +26353,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664632320404</v>
       </c>
       <c r="H896" t="n">
         <v>911289</v>
@@ -26382,7 +26382,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472989559174</v>
       </c>
       <c r="H897" t="n">
         <v>805951</v>
@@ -26440,7 +26440,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.03259706497192</v>
+        <v>2.0325973033905</v>
       </c>
       <c r="H899" t="n">
         <v>626504</v>
@@ -26469,7 +26469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99642980098724</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H900" t="n">
         <v>386888</v>
@@ -26498,7 +26498,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472989559174</v>
       </c>
       <c r="H901" t="n">
         <v>318897</v>
@@ -26527,7 +26527,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>1.93132901191711</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H902" t="n">
         <v>257125</v>
@@ -26556,7 +26556,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>1.88792848587036</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H903" t="n">
         <v>353686</v>
@@ -26585,7 +26585,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.8300609588623</v>
+        <v>1.83006107807159</v>
       </c>
       <c r="H904" t="n">
         <v>909668</v>
@@ -26672,7 +26672,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601193904877</v>
+        <v>1.90601205825806</v>
       </c>
       <c r="H907" t="n">
         <v>228173</v>
@@ -26701,7 +26701,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H908" t="n">
         <v>91411</v>
@@ -26759,7 +26759,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H910" t="n">
         <v>493642</v>
@@ -26788,7 +26788,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G911" t="n">
-        <v>1.88792848587036</v>
+        <v>1.88792860507965</v>
       </c>
       <c r="H911" t="n">
         <v>261392</v>
@@ -26817,7 +26817,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H912" t="n">
         <v>465653</v>
@@ -26846,7 +26846,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H913" t="n">
         <v>618635</v>
@@ -26875,7 +26875,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389357566833</v>
+        <v>1.79389381408691</v>
       </c>
       <c r="H914" t="n">
         <v>465588</v>
@@ -26904,7 +26904,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G915" t="n">
-        <v>1.71432566642761</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H915" t="n">
         <v>1785650</v>
@@ -26991,7 +26991,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G918" t="n">
-        <v>1.68177533149719</v>
+        <v>1.68177545070648</v>
       </c>
       <c r="H918" t="n">
         <v>629139</v>
@@ -27049,7 +27049,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G920" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H920" t="n">
         <v>347469</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.66369163990021</v>
+        <v>1.6636917591095</v>
       </c>
       <c r="H922" t="n">
         <v>294260</v>
@@ -27136,7 +27136,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H923" t="n">
         <v>378459</v>
@@ -27165,7 +27165,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G924" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H924" t="n">
         <v>432209</v>
@@ -27223,7 +27223,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H926" t="n">
         <v>277933</v>
@@ -27397,7 +27397,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944080352783</v>
+        <v>1.60944068431854</v>
       </c>
       <c r="H932" t="n">
         <v>532189</v>
@@ -27484,7 +27484,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H935" t="n">
         <v>361760</v>
@@ -27513,7 +27513,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G936" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347595214844</v>
       </c>
       <c r="H936" t="n">
         <v>357964</v>
@@ -27571,7 +27571,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.7107093334198</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H938" t="n">
         <v>298104</v>
@@ -27600,7 +27600,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G939" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H939" t="n">
         <v>258542</v>
@@ -27629,7 +27629,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.7107093334198</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H940" t="n">
         <v>372190</v>
@@ -27687,7 +27687,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>1.74687612056732</v>
+        <v>1.7468763589859</v>
       </c>
       <c r="H942" t="n">
         <v>316432</v>
@@ -27716,7 +27716,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.7107093334198</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H943" t="n">
         <v>343096</v>
@@ -27745,7 +27745,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H944" t="n">
         <v>336528</v>
@@ -27803,7 +27803,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H946" t="n">
         <v>241984</v>
@@ -27919,7 +27919,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G950" t="n">
-        <v>1.61667430400848</v>
+        <v>1.61667418479919</v>
       </c>
       <c r="H950" t="n">
         <v>294932</v>
@@ -27977,7 +27977,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.6456081867218</v>
+        <v>1.64560830593109</v>
       </c>
       <c r="H952" t="n">
         <v>114952</v>
@@ -28006,7 +28006,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G953" t="n">
-        <v>1.69985902309418</v>
+        <v>1.69985890388489</v>
       </c>
       <c r="H953" t="n">
         <v>409767</v>
@@ -28035,7 +28035,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G954" t="n">
-        <v>1.71432566642761</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H954" t="n">
         <v>542414</v>
@@ -28093,7 +28093,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G956" t="n">
-        <v>1.63114130496979</v>
+        <v>1.63114142417908</v>
       </c>
       <c r="H956" t="n">
         <v>272469</v>
@@ -28122,7 +28122,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G957" t="n">
-        <v>1.62390768527985</v>
+        <v>1.62390780448914</v>
       </c>
       <c r="H957" t="n">
         <v>183628</v>
@@ -28209,7 +28209,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944080352783</v>
+        <v>1.60944068431854</v>
       </c>
       <c r="H960" t="n">
         <v>254516</v>
@@ -28267,7 +28267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H962" t="n">
         <v>546781</v>
@@ -28296,7 +28296,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G963" t="n">
-        <v>1.68177533149719</v>
+        <v>1.68177545070648</v>
       </c>
       <c r="H963" t="n">
         <v>286763</v>
@@ -28325,7 +28325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H964" t="n">
         <v>258696</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H966" t="n">
         <v>445642</v>
@@ -28412,7 +28412,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>1.68900871276855</v>
+        <v>1.68900883197784</v>
       </c>
       <c r="H967" t="n">
         <v>205808</v>
@@ -28441,7 +28441,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G968" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347595214844</v>
       </c>
       <c r="H968" t="n">
         <v>103141</v>
@@ -28499,7 +28499,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H970" t="n">
         <v>116106</v>
@@ -28528,7 +28528,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H971" t="n">
         <v>185489</v>
@@ -28557,7 +28557,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H972" t="n">
         <v>278746</v>
@@ -28586,7 +28586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H973" t="n">
         <v>190802</v>
@@ -28644,7 +28644,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092514038086</v>
+        <v>1.67092525959015</v>
       </c>
       <c r="H975" t="n">
         <v>145445</v>
@@ -28702,7 +28702,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G977" t="n">
-        <v>1.68177533149719</v>
+        <v>1.68177545070648</v>
       </c>
       <c r="H977" t="n">
         <v>135253</v>
@@ -28789,7 +28789,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G980" t="n">
-        <v>1.79751026630402</v>
+        <v>1.79751038551331</v>
       </c>
       <c r="H980" t="n">
         <v>683548</v>
@@ -28847,7 +28847,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G982" t="n">
-        <v>1.70347559452057</v>
+        <v>1.70347595214844</v>
       </c>
       <c r="H982" t="n">
         <v>825785</v>
@@ -28876,7 +28876,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G983" t="n">
-        <v>1.74325966835022</v>
+        <v>1.74325942993164</v>
       </c>
       <c r="H983" t="n">
         <v>346060</v>
@@ -28963,7 +28963,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G986" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H986" t="n">
         <v>235688</v>
@@ -28992,7 +28992,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G987" t="n">
-        <v>1.72879266738892</v>
+        <v>1.7287929058075</v>
       </c>
       <c r="H987" t="n">
         <v>462399</v>
@@ -29050,7 +29050,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G989" t="n">
-        <v>1.71432566642761</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H989" t="n">
         <v>290573</v>
@@ -29079,7 +29079,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.7107093334198</v>
+        <v>1.71070921421051</v>
       </c>
       <c r="H990" t="n">
         <v>404717</v>
@@ -29108,7 +29108,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G991" t="n">
-        <v>1.71432566642761</v>
+        <v>1.71432590484619</v>
       </c>
       <c r="H991" t="n">
         <v>218713</v>
@@ -29166,7 +29166,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666043281555</v>
+        <v>1.78666019439697</v>
       </c>
       <c r="H993" t="n">
         <v>380638</v>
@@ -29195,7 +29195,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666043281555</v>
+        <v>1.78666019439697</v>
       </c>
       <c r="H994" t="n">
         <v>337289</v>
@@ -29253,7 +29253,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G996" t="n">
-        <v>2.01451373100281</v>
+        <v>2.01451396942139</v>
       </c>
       <c r="H996" t="n">
         <v>2489093</v>
@@ -29282,7 +29282,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H997" t="n">
         <v>989644</v>
@@ -29311,7 +29311,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>1.93494582176208</v>
+        <v>1.9349457025528</v>
       </c>
       <c r="H998" t="n">
         <v>1204470</v>
@@ -29340,7 +29340,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G999" t="n">
-        <v>1.91686224937439</v>
+        <v>1.91686236858368</v>
       </c>
       <c r="H999" t="n">
         <v>662234</v>
@@ -29369,7 +29369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1000" t="n">
         <v>951588</v>
@@ -29398,7 +29398,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196315765381</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1001" t="n">
         <v>659632</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1002" t="n">
         <v>591585</v>
@@ -29456,7 +29456,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1003" t="n">
         <v>552967</v>
@@ -29485,7 +29485,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.06153106689453</v>
+        <v>2.06153130531311</v>
       </c>
       <c r="H1004" t="n">
         <v>981209</v>
@@ -29601,7 +29601,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.04344773292542</v>
+        <v>2.04344749450684</v>
       </c>
       <c r="H1008" t="n">
         <v>410384</v>
@@ -29630,7 +29630,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.01813054084778</v>
+        <v>2.0181303024292</v>
       </c>
       <c r="H1009" t="n">
         <v>304169</v>
@@ -29659,7 +29659,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H1010" t="n">
         <v>295623</v>
@@ -29688,7 +29688,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919665813446</v>
+        <v>1.98919689655304</v>
       </c>
       <c r="H1011" t="n">
         <v>341025</v>
@@ -29717,7 +29717,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196315765381</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1012" t="n">
         <v>244318</v>
@@ -29746,7 +29746,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281370639801</v>
+        <v>1.99281358718872</v>
       </c>
       <c r="H1013" t="n">
         <v>183722</v>
@@ -29775,7 +29775,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99642980098724</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H1014" t="n">
         <v>219712</v>
@@ -29804,7 +29804,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1015" t="n">
         <v>196502</v>
@@ -29833,7 +29833,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.01089715957642</v>
+        <v>2.01089692115784</v>
       </c>
       <c r="H1016" t="n">
         <v>238710</v>
@@ -29862,7 +29862,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1017" t="n">
         <v>308613</v>
@@ -29920,7 +29920,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.94579613208771</v>
+        <v>1.94579577445984</v>
       </c>
       <c r="H1019" t="n">
         <v>213742</v>
@@ -29949,7 +29949,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.93132901191711</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H1020" t="n">
         <v>417414</v>
@@ -29978,7 +29978,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664608478546</v>
+        <v>1.95664632320404</v>
       </c>
       <c r="H1021" t="n">
         <v>243379</v>
@@ -30036,7 +30036,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324555873871</v>
+        <v>1.91324543952942</v>
       </c>
       <c r="H1023" t="n">
         <v>212691</v>
@@ -30065,7 +30065,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346172332764</v>
+        <v>1.87346148490906</v>
       </c>
       <c r="H1024" t="n">
         <v>368919</v>
@@ -30181,7 +30181,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G1028" t="n">
-        <v>2.00728034973145</v>
+        <v>2.00728058815002</v>
       </c>
       <c r="H1028" t="n">
         <v>978677</v>
@@ -30210,7 +30210,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.98557984828949</v>
+        <v>1.9855797290802</v>
       </c>
       <c r="H1029" t="n">
         <v>431020</v>
@@ -30239,7 +30239,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387934684753</v>
+        <v>1.96387958526611</v>
       </c>
       <c r="H1030" t="n">
         <v>334352</v>
@@ -30268,7 +30268,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111320495605</v>
+        <v>1.97111296653748</v>
       </c>
       <c r="H1031" t="n">
         <v>346362</v>
@@ -30297,7 +30297,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.98557984828949</v>
+        <v>1.9855797290802</v>
       </c>
       <c r="H1032" t="n">
         <v>263186</v>
@@ -30355,7 +30355,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431167602539</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H1034" t="n">
         <v>562475</v>
@@ -30384,7 +30384,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1035" t="n">
         <v>361531</v>
@@ -30413,7 +30413,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474388599396</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H1036" t="n">
         <v>595397</v>
@@ -30442,7 +30442,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.72517597675323</v>
+        <v>1.72517585754395</v>
       </c>
       <c r="H1037" t="n">
         <v>749348</v>
@@ -30471,7 +30471,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964297771454</v>
+        <v>1.73964285850525</v>
       </c>
       <c r="H1038" t="n">
         <v>332631</v>
@@ -30558,7 +30558,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.79027712345123</v>
+        <v>1.79027688503265</v>
       </c>
       <c r="H1041" t="n">
         <v>444570</v>
@@ -30616,7 +30616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.76496005058289</v>
+        <v>1.7649599313736</v>
       </c>
       <c r="H1043" t="n">
         <v>116889</v>
@@ -30703,7 +30703,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.85899460315704</v>
+        <v>1.85899472236633</v>
       </c>
       <c r="H1046" t="n">
         <v>633060</v>
@@ -30732,7 +30732,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1047" t="n">
         <v>448193</v>
@@ -30790,7 +30790,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.82644426822662</v>
+        <v>1.82644438743591</v>
       </c>
       <c r="H1049" t="n">
         <v>268233</v>
@@ -30819,7 +30819,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.85176122188568</v>
+        <v>1.85176134109497</v>
       </c>
       <c r="H1050" t="n">
         <v>328554</v>
@@ -30906,7 +30906,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262552261353</v>
+        <v>1.69262540340424</v>
       </c>
       <c r="H1053" t="n">
         <v>578759</v>
@@ -30935,7 +30935,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1054" t="n">
         <v>345112</v>
@@ -30964,7 +30964,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.65645825862885</v>
+        <v>1.65645837783813</v>
       </c>
       <c r="H1055" t="n">
         <v>555769</v>
@@ -31022,7 +31022,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.56965720653534</v>
+        <v>1.56965696811676</v>
       </c>
       <c r="H1057" t="n">
         <v>544343</v>
@@ -31080,7 +31080,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285555839539</v>
+        <v>1.48285567760468</v>
       </c>
       <c r="H1059" t="n">
         <v>394349</v>
@@ -31109,7 +31109,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43366837501526</v>
+        <v>1.43366825580597</v>
       </c>
       <c r="H1060" t="n">
         <v>342436</v>
@@ -31138,7 +31138,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.38448083400726</v>
+        <v>1.38448095321655</v>
       </c>
       <c r="H1061" t="n">
         <v>581654</v>
@@ -31196,7 +31196,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1063" t="n">
         <v>710228</v>
@@ -31254,7 +31254,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.18628442287445</v>
+        <v>1.18628454208374</v>
       </c>
       <c r="H1065" t="n">
         <v>545776</v>
@@ -31283,7 +31283,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412856578827</v>
+        <v>1.01412868499756</v>
       </c>
       <c r="H1066" t="n">
         <v>500114</v>
@@ -31312,7 +31312,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.07922971248627</v>
+        <v>1.07922959327698</v>
       </c>
       <c r="H1067" t="n">
         <v>643441</v>
@@ -31341,7 +31341,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00400197505951</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1068" t="n">
         <v>418504</v>
@@ -31370,7 +31370,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.98519492149353</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1069" t="n">
         <v>281501</v>
@@ -31428,7 +31428,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1071" t="n">
         <v>337483</v>
@@ -31457,7 +31457,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.13854396343231</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1072" t="n">
         <v>440163</v>
@@ -31486,7 +31486,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.22679173946381</v>
+        <v>1.2267918586731</v>
       </c>
       <c r="H1073" t="n">
         <v>282057</v>
@@ -31544,7 +31544,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.24415218830109</v>
+        <v>1.2441520690918</v>
       </c>
       <c r="H1075" t="n">
         <v>387433</v>
@@ -31602,7 +31602,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.22679173946381</v>
+        <v>1.2267918586731</v>
       </c>
       <c r="H1077" t="n">
         <v>359736</v>
@@ -31631,7 +31631,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.1776043176651</v>
+        <v>1.17760443687439</v>
       </c>
       <c r="H1078" t="n">
         <v>204338</v>
@@ -31660,7 +31660,7 @@
         <v>1.57400000095367</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.13854396343231</v>
+        <v>1.13854384422302</v>
       </c>
       <c r="H1079" t="n">
         <v>243445</v>
@@ -31718,7 +31718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968518733978</v>
+        <v>1.22968530654907</v>
       </c>
       <c r="H1081" t="n">
         <v>100009</v>
@@ -31747,7 +31747,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1082" t="n">
         <v>144468</v>
@@ -31776,7 +31776,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1083" t="n">
         <v>108764</v>
@@ -31834,7 +31834,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.2947860956192</v>
+        <v>1.29478621482849</v>
       </c>
       <c r="H1085" t="n">
         <v>332626</v>
@@ -31921,7 +31921,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1088" t="n">
         <v>216163</v>
@@ -32037,7 +32037,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.2427054643631</v>
+        <v>1.24270558357239</v>
       </c>
       <c r="H1092" t="n">
         <v>149538</v>
@@ -32066,7 +32066,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1093" t="n">
         <v>222649</v>
@@ -32153,7 +32153,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.20075154304504</v>
+        <v>1.20075142383575</v>
       </c>
       <c r="H1096" t="n">
         <v>153500</v>
@@ -32182,7 +32182,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1097" t="n">
         <v>97350</v>
@@ -32211,7 +32211,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798492431641</v>
+        <v>1.20798480510712</v>
       </c>
       <c r="H1098" t="n">
         <v>241005</v>
@@ -32269,7 +32269,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1100" t="n">
         <v>41271</v>
@@ -32298,7 +32298,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.14288401603699</v>
+        <v>1.1428838968277</v>
       </c>
       <c r="H1101" t="n">
         <v>111460</v>
@@ -32327,7 +32327,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1102" t="n">
         <v>88940</v>
@@ -32443,7 +32443,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1106" t="n">
         <v>214071</v>
@@ -32501,7 +32501,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.02425539493561</v>
+        <v>1.0242555141449</v>
       </c>
       <c r="H1108" t="n">
         <v>254021</v>
@@ -32530,7 +32530,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1109" t="n">
         <v>171022</v>
@@ -32588,7 +32588,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978851318359</v>
       </c>
       <c r="H1111" t="n">
         <v>304217</v>
@@ -32617,7 +32617,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1112" t="n">
         <v>157009</v>
@@ -32646,7 +32646,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.98519492149353</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1113" t="n">
         <v>128951</v>
@@ -32675,7 +32675,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428243160248</v>
+        <v>0.992428302764893</v>
       </c>
       <c r="H1114" t="n">
         <v>168726</v>
@@ -32704,7 +32704,7 @@
         <v>1.44200003147125</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04306244850159</v>
+        <v>1.04306256771088</v>
       </c>
       <c r="H1115" t="n">
         <v>194795</v>
@@ -32791,7 +32791,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.06910288333893</v>
+        <v>1.06910276412964</v>
       </c>
       <c r="H1118" t="n">
         <v>324190</v>
@@ -32820,7 +32820,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1119" t="n">
         <v>276892</v>
@@ -32936,7 +32936,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.13565051555634</v>
+        <v>1.13565039634705</v>
       </c>
       <c r="H1123" t="n">
         <v>441474</v>
@@ -32965,7 +32965,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1124" t="n">
         <v>675402</v>
@@ -32994,7 +32994,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1125" t="n">
         <v>636837</v>
@@ -33139,7 +33139,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1130" t="n">
         <v>250136</v>
@@ -33168,7 +33168,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.14867079257965</v>
+        <v>1.14867067337036</v>
       </c>
       <c r="H1131" t="n">
         <v>335721</v>
@@ -33255,7 +33255,7 @@
         <v>1.55200004577637</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.12263023853302</v>
+        <v>1.12263035774231</v>
       </c>
       <c r="H1134" t="n">
         <v>364632</v>
@@ -33342,7 +33342,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.09514319896698</v>
+        <v>1.09514307975769</v>
       </c>
       <c r="H1137" t="n">
         <v>145504</v>
@@ -33371,7 +33371,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237658023834</v>
+        <v>1.10237669944763</v>
       </c>
       <c r="H1138" t="n">
         <v>192526</v>
@@ -33458,7 +33458,7 @@
         <v>1.46599996089935</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.060422539711</v>
+        <v>1.06042277812958</v>
       </c>
       <c r="H1141" t="n">
         <v>213541</v>
@@ -33487,7 +33487,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1142" t="n">
         <v>271139</v>
@@ -33516,7 +33516,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1143" t="n">
         <v>651459</v>
@@ -33545,7 +33545,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1144" t="n">
         <v>205530</v>
@@ -33603,7 +33603,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.08790969848633</v>
+        <v>1.08790957927704</v>
       </c>
       <c r="H1146" t="n">
         <v>227859</v>
@@ -33632,7 +33632,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1147" t="n">
         <v>313392</v>
@@ -33661,7 +33661,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476271152496</v>
+        <v>1.06476259231567</v>
       </c>
       <c r="H1148" t="n">
         <v>229091</v>
@@ -33690,7 +33690,7 @@
         <v>1.5</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1149" t="n">
         <v>255277</v>
@@ -33748,7 +33748,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.07054960727692</v>
+        <v>1.07054948806763</v>
       </c>
       <c r="H1151" t="n">
         <v>175817</v>
@@ -33777,7 +33777,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1152" t="n">
         <v>149121</v>
@@ -33806,7 +33806,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.092249751091</v>
+        <v>1.09224987030029</v>
       </c>
       <c r="H1153" t="n">
         <v>146621</v>
@@ -33835,7 +33835,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1154" t="n">
         <v>63350</v>
@@ -33864,7 +33864,7 @@
         <v>1.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.08501625061035</v>
+        <v>1.08501636981964</v>
       </c>
       <c r="H1155" t="n">
         <v>121530</v>
@@ -33893,7 +33893,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1156" t="n">
         <v>244507</v>
@@ -33922,7 +33922,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.0748895406723</v>
+        <v>1.07488942146301</v>
       </c>
       <c r="H1157" t="n">
         <v>172984</v>
@@ -33980,7 +33980,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.04595577716827</v>
+        <v>1.04595565795898</v>
       </c>
       <c r="H1159" t="n">
         <v>160290</v>
@@ -34009,7 +34009,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846861839294</v>
+        <v>1.01846873760223</v>
       </c>
       <c r="H1160" t="n">
         <v>289771</v>
@@ -34038,7 +34038,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1161" t="n">
         <v>162875</v>
@@ -34067,7 +34067,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981578826904</v>
+        <v>0.990981638431549</v>
       </c>
       <c r="H1162" t="n">
         <v>183349</v>
@@ -34125,7 +34125,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088309764862</v>
       </c>
       <c r="H1164" t="n">
         <v>137388</v>
@@ -34183,7 +34183,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.00400197505951</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1166" t="n">
         <v>268517</v>
@@ -34270,7 +34270,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.988088190555573</v>
+        <v>0.988088309764862</v>
       </c>
       <c r="H1169" t="n">
         <v>318607</v>
@@ -34444,7 +34444,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.986641585826874</v>
+        <v>0.986641645431519</v>
       </c>
       <c r="H1175" t="n">
         <v>123963</v>
@@ -34473,7 +34473,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.98519492149353</v>
+        <v>0.985194742679596</v>
       </c>
       <c r="H1176" t="n">
         <v>165512</v>
@@ -34502,7 +34502,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.976514637470245</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1177" t="n">
         <v>195958</v>
@@ -34531,7 +34531,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.972174763679504</v>
+        <v>0.972174644470215</v>
       </c>
       <c r="H1178" t="n">
         <v>90569</v>
@@ -34647,7 +34647,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.96783447265625</v>
+        <v>0.967834532260895</v>
       </c>
       <c r="H1182" t="n">
         <v>267761</v>
@@ -34676,7 +34676,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1183" t="n">
         <v>281167</v>
@@ -34705,7 +34705,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047934532166</v>
+        <v>0.962047815322876</v>
       </c>
       <c r="H1184" t="n">
         <v>241006</v>
@@ -34734,7 +34734,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.963494539260864</v>
+        <v>0.963494598865509</v>
       </c>
       <c r="H1185" t="n">
         <v>283085</v>
@@ -34763,7 +34763,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.950474381446838</v>
+        <v>0.950474441051483</v>
       </c>
       <c r="H1186" t="n">
         <v>250204</v>
@@ -34792,7 +34792,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.925880610942841</v>
+        <v>0.925880670547485</v>
       </c>
       <c r="H1187" t="n">
         <v>573190</v>
@@ -34821,7 +34821,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1188" t="n">
         <v>555967</v>
@@ -34850,7 +34850,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468754529953</v>
       </c>
       <c r="H1189" t="n">
         <v>485261</v>
@@ -34879,7 +34879,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468754529953</v>
       </c>
       <c r="H1190" t="n">
         <v>152429</v>
@@ -34908,7 +34908,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454044818878</v>
       </c>
       <c r="H1191" t="n">
         <v>312695</v>
@@ -34937,7 +34937,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900768756866</v>
+        <v>0.938900828361511</v>
       </c>
       <c r="H1192" t="n">
         <v>194055</v>
@@ -35082,7 +35082,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1197" t="n">
         <v>192408</v>
@@ -35169,7 +35169,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073557376862</v>
       </c>
       <c r="H1200" t="n">
         <v>628275</v>
@@ -35198,7 +35198,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1201" t="n">
         <v>504293</v>
@@ -35227,7 +35227,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454044818878</v>
       </c>
       <c r="H1202" t="n">
         <v>519628</v>
@@ -35256,7 +35256,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901287078857422</v>
       </c>
       <c r="H1203" t="n">
         <v>394327</v>
@@ -35285,7 +35285,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1204" t="n">
         <v>232364</v>
@@ -35372,7 +35372,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093894004822</v>
+        <v>0.920093834400177</v>
       </c>
       <c r="H1207" t="n">
         <v>363479</v>
@@ -35401,7 +35401,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413788795471</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1208" t="n">
         <v>255998</v>
@@ -35430,7 +35430,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413788795471</v>
+        <v>0.911413729190826</v>
       </c>
       <c r="H1209" t="n">
         <v>107552</v>
@@ -35459,7 +35459,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928773999214172</v>
+        <v>0.928774058818817</v>
       </c>
       <c r="H1210" t="n">
         <v>89660</v>
@@ -35488,7 +35488,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1211" t="n">
         <v>668739</v>
@@ -35517,7 +35517,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.976514637470245</v>
+        <v>0.97651469707489</v>
       </c>
       <c r="H1212" t="n">
         <v>642364</v>
@@ -35575,7 +35575,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1214" t="n">
         <v>432837</v>
@@ -35604,7 +35604,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951921105384827</v>
+        <v>0.951921045780182</v>
       </c>
       <c r="H1215" t="n">
         <v>224463</v>
@@ -35662,7 +35662,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753841400146</v>
+        <v>0.915753722190857</v>
       </c>
       <c r="H1217" t="n">
         <v>178785</v>
@@ -35691,7 +35691,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1218" t="n">
         <v>276978</v>
@@ -35720,7 +35720,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1219" t="n">
         <v>154359</v>
@@ -35749,7 +35749,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1220" t="n">
         <v>238072</v>
@@ -35923,7 +35923,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.828952491283417</v>
+        <v>0.828952550888062</v>
       </c>
       <c r="H1226" t="n">
         <v>322984</v>
@@ -35952,7 +35952,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871681213379</v>
+        <v>0.776871740818024</v>
       </c>
       <c r="H1227" t="n">
         <v>366061</v>
@@ -36010,7 +36010,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.732024371623993</v>
+        <v>0.732024312019348</v>
       </c>
       <c r="H1229" t="n">
         <v>446350</v>
@@ -36039,7 +36039,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.771084904670715</v>
+        <v>0.77108496427536</v>
       </c>
       <c r="H1230" t="n">
         <v>254758</v>
@@ -36097,7 +36097,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211853027344</v>
+        <v>0.781211733818054</v>
       </c>
       <c r="H1232" t="n">
         <v>238451</v>
@@ -36126,7 +36126,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.768191695213318</v>
+        <v>0.768191576004028</v>
       </c>
       <c r="H1233" t="n">
         <v>672823</v>
@@ -36155,7 +36155,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.759511470794678</v>
+        <v>0.759511411190033</v>
       </c>
       <c r="H1234" t="n">
         <v>160813</v>
@@ -36213,7 +36213,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.833292484283447</v>
+        <v>0.833292543888092</v>
       </c>
       <c r="H1236" t="n">
         <v>491269</v>
@@ -36242,7 +36242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079260826111</v>
+        <v>0.8390793800354</v>
       </c>
       <c r="H1237" t="n">
         <v>399300</v>
@@ -36300,7 +36300,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1239" t="n">
         <v>463886</v>
@@ -36329,7 +36329,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1240" t="n">
         <v>465758</v>
@@ -36358,7 +36358,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1241" t="n">
         <v>475088</v>
@@ -36387,7 +36387,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1242" t="n">
         <v>529118</v>
@@ -36445,7 +36445,7 @@
         <v>1.24600005149841</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.901287019252777</v>
+        <v>0.901287078857422</v>
       </c>
       <c r="H1244" t="n">
         <v>350164</v>
@@ -36503,7 +36503,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.914307177066803</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1246" t="n">
         <v>599351</v>
@@ -36532,7 +36532,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.914307177066803</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1247" t="n">
         <v>474055</v>
@@ -36590,7 +36590,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.914307177066803</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1249" t="n">
         <v>208821</v>
@@ -36677,7 +36677,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1252" t="n">
         <v>343874</v>
@@ -36764,7 +36764,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.879586637020111</v>
+        <v>0.879586577415466</v>
       </c>
       <c r="H1255" t="n">
         <v>304340</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693308353424</v>
+        <v>0.876693189144135</v>
       </c>
       <c r="H1258" t="n">
         <v>265557</v>
@@ -36938,7 +36938,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119636058807</v>
+        <v>0.865119695663452</v>
       </c>
       <c r="H1261" t="n">
         <v>73429</v>
@@ -36967,7 +36967,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246644020081</v>
+        <v>0.875246524810791</v>
       </c>
       <c r="H1262" t="n">
         <v>261444</v>
@@ -36996,7 +36996,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.882480025291443</v>
+        <v>0.882479965686798</v>
       </c>
       <c r="H1263" t="n">
         <v>171832</v>
@@ -37025,7 +37025,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.88537335395813</v>
+        <v>0.885373413562775</v>
       </c>
       <c r="H1264" t="n">
         <v>229764</v>
@@ -37054,7 +37054,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.862226366996765</v>
+        <v>0.86222642660141</v>
       </c>
       <c r="H1265" t="n">
         <v>389130</v>
@@ -37083,7 +37083,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1266" t="n">
         <v>174813</v>
@@ -37112,7 +37112,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459807872772</v>
+        <v>0.869459867477417</v>
       </c>
       <c r="H1267" t="n">
         <v>207362</v>
@@ -37141,7 +37141,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1268" t="n">
         <v>362696</v>
@@ -37170,7 +37170,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520340919495</v>
+        <v>0.908520460128784</v>
       </c>
       <c r="H1269" t="n">
         <v>264575</v>
@@ -37199,7 +37199,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.914307177066803</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1270" t="n">
         <v>297896</v>
@@ -37228,7 +37228,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946787834167</v>
+        <v>0.896946907043457</v>
       </c>
       <c r="H1271" t="n">
         <v>357067</v>
@@ -37286,7 +37286,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.907073616981506</v>
+        <v>0.907073557376862</v>
       </c>
       <c r="H1273" t="n">
         <v>210846</v>
@@ -37431,7 +37431,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.854992926120758</v>
+        <v>0.854992985725403</v>
       </c>
       <c r="H1278" t="n">
         <v>195138</v>
@@ -37460,7 +37460,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779762268066</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1279" t="n">
         <v>178958</v>
@@ -37489,7 +37489,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206149578094</v>
+        <v>0.849206209182739</v>
       </c>
       <c r="H1280" t="n">
         <v>159959</v>
@@ -37518,7 +37518,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079260826111</v>
+        <v>0.8390793800354</v>
       </c>
       <c r="H1281" t="n">
         <v>188343</v>
@@ -37605,7 +37605,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.852099597454071</v>
+        <v>0.852099478244781</v>
       </c>
       <c r="H1284" t="n">
         <v>176033</v>
@@ -37721,7 +37721,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1288" t="n">
         <v>234994</v>
@@ -37779,7 +37779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845819950104</v>
+        <v>0.831845879554749</v>
       </c>
       <c r="H1290" t="n">
         <v>153639</v>
@@ -37808,7 +37808,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866096973419</v>
+        <v>0.844866037368774</v>
       </c>
       <c r="H1291" t="n">
         <v>84133</v>
@@ -37837,7 +37837,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312761306763</v>
+        <v>0.846312701702118</v>
       </c>
       <c r="H1292" t="n">
         <v>193484</v>
@@ -37866,7 +37866,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119636058807</v>
+        <v>0.865119695663452</v>
       </c>
       <c r="H1293" t="n">
         <v>395877</v>
@@ -37895,7 +37895,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.873799860477448</v>
+        <v>0.873799800872803</v>
       </c>
       <c r="H1294" t="n">
         <v>252193</v>
@@ -37924,7 +37924,7 @@
         <v>1.21399998664856</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.878139913082123</v>
+        <v>0.878139853477478</v>
       </c>
       <c r="H1295" t="n">
         <v>546482</v>
@@ -38040,7 +38040,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1299" t="n">
         <v>514735</v>
@@ -38069,7 +38069,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1300" t="n">
         <v>440904</v>
@@ -38098,7 +38098,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978851318359</v>
       </c>
       <c r="H1301" t="n">
         <v>487433</v>
@@ -38127,7 +38127,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.982301533222198</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1302" t="n">
         <v>468329</v>
@@ -38185,7 +38185,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.950474381446838</v>
+        <v>0.950474441051483</v>
       </c>
       <c r="H1304" t="n">
         <v>534039</v>
@@ -38214,7 +38214,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1305" t="n">
         <v>460160</v>
@@ -38330,7 +38330,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.05029582977295</v>
+        <v>1.05029594898224</v>
       </c>
       <c r="H1309" t="n">
         <v>555685</v>
@@ -38359,7 +38359,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.00544857978821</v>
+        <v>1.00544846057892</v>
       </c>
       <c r="H1310" t="n">
         <v>750423</v>
@@ -38417,7 +38417,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1312" t="n">
         <v>192416</v>
@@ -38446,7 +38446,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.02136206626892</v>
+        <v>1.02136194705963</v>
       </c>
       <c r="H1313" t="n">
         <v>246366</v>
@@ -38475,7 +38475,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.996768414974213</v>
+        <v>0.996768355369568</v>
       </c>
       <c r="H1314" t="n">
         <v>379948</v>
@@ -38504,7 +38504,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1315" t="n">
         <v>436542</v>
@@ -38562,7 +38562,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1317" t="n">
         <v>330734</v>
@@ -38591,7 +38591,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884922504425</v>
+        <v>1.04884910583496</v>
       </c>
       <c r="H1318" t="n">
         <v>602483</v>
@@ -38649,7 +38649,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.03872239589691</v>
+        <v>1.03872227668762</v>
       </c>
       <c r="H1320" t="n">
         <v>177744</v>
@@ -38678,7 +38678,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.07922971248627</v>
+        <v>1.07922959327698</v>
       </c>
       <c r="H1321" t="n">
         <v>786626</v>
@@ -38707,7 +38707,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.08935654163361</v>
+        <v>1.08935642242432</v>
       </c>
       <c r="H1322" t="n">
         <v>506082</v>
@@ -38736,7 +38736,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.07344281673431</v>
+        <v>1.0734429359436</v>
       </c>
       <c r="H1323" t="n">
         <v>261172</v>
@@ -38765,7 +38765,7 @@
         <v>1.52199995517731</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.10092997550964</v>
+        <v>1.10092985630035</v>
       </c>
       <c r="H1324" t="n">
         <v>701728</v>
@@ -38823,7 +38823,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785809516907</v>
+        <v>1.19785797595978</v>
       </c>
       <c r="H1326" t="n">
         <v>1612557</v>
@@ -38910,7 +38910,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.1587975025177</v>
+        <v>1.15879738330841</v>
       </c>
       <c r="H1329" t="n">
         <v>259241</v>
@@ -38939,7 +38939,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.16458415985107</v>
+        <v>1.16458427906036</v>
       </c>
       <c r="H1330" t="n">
         <v>469768</v>
@@ -38968,7 +38968,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.1935179233551</v>
+        <v>1.19351804256439</v>
       </c>
       <c r="H1331" t="n">
         <v>534133</v>
@@ -38997,7 +38997,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1332" t="n">
         <v>471250</v>
@@ -39055,7 +39055,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.1443305015564</v>
+        <v>1.14433062076569</v>
       </c>
       <c r="H1334" t="n">
         <v>246192</v>
@@ -39084,7 +39084,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.14288401603699</v>
+        <v>1.1428838968277</v>
       </c>
       <c r="H1335" t="n">
         <v>251813</v>
@@ -39113,7 +39113,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049788475037</v>
+        <v>1.18049776554108</v>
       </c>
       <c r="H1336" t="n">
         <v>648102</v>
@@ -39200,7 +39200,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1339" t="n">
         <v>508534</v>
@@ -39258,7 +39258,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.17181777954102</v>
+        <v>1.17181766033173</v>
       </c>
       <c r="H1341" t="n">
         <v>170083</v>
@@ -39287,7 +39287,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.16603076457977</v>
+        <v>1.16603088378906</v>
       </c>
       <c r="H1342" t="n">
         <v>257345</v>
@@ -39316,7 +39316,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.17905116081238</v>
+        <v>1.17905104160309</v>
       </c>
       <c r="H1343" t="n">
         <v>476067</v>
@@ -39345,7 +39345,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.18628442287445</v>
+        <v>1.18628454208374</v>
       </c>
       <c r="H1344" t="n">
         <v>178324</v>
@@ -39374,7 +39374,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1345" t="n">
         <v>402831</v>
@@ -39461,7 +39461,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.30201959609985</v>
+        <v>1.30201971530914</v>
       </c>
       <c r="H1348" t="n">
         <v>408190</v>
@@ -39548,7 +39548,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057299137115</v>
+        <v>1.30057287216187</v>
       </c>
       <c r="H1351" t="n">
         <v>318670</v>
@@ -39577,7 +39577,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.29623281955719</v>
+        <v>1.29623305797577</v>
       </c>
       <c r="H1352" t="n">
         <v>344858</v>
@@ -39606,7 +39606,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.29189276695251</v>
+        <v>1.2918928861618</v>
       </c>
       <c r="H1353" t="n">
         <v>274547</v>
@@ -39635,7 +39635,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1354" t="n">
         <v>744694</v>
@@ -39693,7 +39693,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912638664246</v>
+        <v>1.29912626743317</v>
       </c>
       <c r="H1356" t="n">
         <v>193651</v>
@@ -39722,7 +39722,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635976791382</v>
+        <v>1.30635964870453</v>
       </c>
       <c r="H1357" t="n">
         <v>181760</v>
@@ -39780,7 +39780,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1359" t="n">
         <v>1365631</v>
@@ -39809,7 +39809,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341459751129</v>
+        <v>1.41341471672058</v>
       </c>
       <c r="H1360" t="n">
         <v>612054</v>
@@ -39838,7 +39838,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.46115529537201</v>
+        <v>1.4611554145813</v>
       </c>
       <c r="H1361" t="n">
         <v>730836</v>
@@ -40070,7 +40070,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1369" t="n">
         <v>249082</v>
@@ -40215,7 +40215,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.38149499893188</v>
+        <v>1.3814948797226</v>
       </c>
       <c r="H1374" t="n">
         <v>236076</v>
@@ -40273,7 +40273,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.37706243991852</v>
+        <v>1.37706232070923</v>
       </c>
       <c r="H1376" t="n">
         <v>173905</v>
@@ -40302,7 +40302,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.38592755794525</v>
+        <v>1.38592767715454</v>
       </c>
       <c r="H1377" t="n">
         <v>224156</v>
@@ -40331,7 +40331,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1378" t="n">
         <v>217402</v>
@@ -40360,7 +40360,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.4391188621521</v>
+        <v>1.43911874294281</v>
       </c>
       <c r="H1379" t="n">
         <v>239859</v>
@@ -40418,7 +40418,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1381" t="n">
         <v>159305</v>
@@ -40476,7 +40476,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537161827087</v>
+        <v>1.45537173748016</v>
       </c>
       <c r="H1383" t="n">
         <v>131183</v>
@@ -40505,7 +40505,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.45684933662415</v>
+        <v>1.45684921741486</v>
       </c>
       <c r="H1384" t="n">
         <v>91908</v>
@@ -40534,7 +40534,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650650024414</v>
+        <v>1.44650638103485</v>
       </c>
       <c r="H1385" t="n">
         <v>278517</v>
@@ -40795,7 +40795,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.29432046413422</v>
+        <v>1.29432034492493</v>
       </c>
       <c r="H1394" t="n">
         <v>728450</v>
@@ -40853,7 +40853,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.25442695617676</v>
+        <v>1.25442683696747</v>
       </c>
       <c r="H1396" t="n">
         <v>333027</v>
@@ -40882,7 +40882,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.25294935703278</v>
+        <v>1.25294947624207</v>
       </c>
       <c r="H1397" t="n">
         <v>236575</v>
@@ -40911,7 +40911,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.23817420005798</v>
+        <v>1.2381739616394</v>
       </c>
       <c r="H1398" t="n">
         <v>288738</v>
@@ -40940,7 +40940,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.26033711433411</v>
+        <v>1.26033699512482</v>
       </c>
       <c r="H1399" t="n">
         <v>195621</v>
@@ -40969,7 +40969,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1400" t="n">
         <v>215998</v>
@@ -40998,7 +40998,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.22192120552063</v>
+        <v>1.22192132472992</v>
       </c>
       <c r="H1401" t="n">
         <v>230579</v>
@@ -41027,7 +41027,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.18646025657654</v>
+        <v>1.18646037578583</v>
       </c>
       <c r="H1402" t="n">
         <v>319571</v>
@@ -41085,7 +41085,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1404" t="n">
         <v>172154</v>
@@ -41143,7 +41143,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.21157836914062</v>
+        <v>1.2115786075592</v>
       </c>
       <c r="H1406" t="n">
         <v>146658</v>
@@ -41201,7 +41201,7 @@
         <v>1.60399997234344</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.18498277664185</v>
+        <v>1.18498289585114</v>
       </c>
       <c r="H1408" t="n">
         <v>330749</v>
@@ -41259,7 +41259,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622426986694</v>
       </c>
       <c r="H1410" t="n">
         <v>139750</v>
@@ -41317,7 +41317,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.16134226322174</v>
+        <v>1.16134238243103</v>
       </c>
       <c r="H1412" t="n">
         <v>106478</v>
@@ -41346,7 +41346,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.1657749414444</v>
+        <v>1.16577482223511</v>
       </c>
       <c r="H1413" t="n">
         <v>116151</v>
@@ -41375,7 +41375,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.19237041473389</v>
+        <v>1.19237053394318</v>
       </c>
       <c r="H1414" t="n">
         <v>75348</v>
@@ -41491,7 +41491,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622426986694</v>
       </c>
       <c r="H1418" t="n">
         <v>323570</v>
@@ -41520,7 +41520,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.18350529670715</v>
+        <v>1.18350541591644</v>
       </c>
       <c r="H1419" t="n">
         <v>385901</v>
@@ -41607,7 +41607,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.27067995071411</v>
+        <v>1.27067983150482</v>
       </c>
       <c r="H1422" t="n">
         <v>523160</v>
@@ -41636,7 +41636,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.26033711433411</v>
+        <v>1.26033699512482</v>
       </c>
       <c r="H1423" t="n">
         <v>241029</v>
@@ -41665,7 +41665,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.26033711433411</v>
+        <v>1.26033699512482</v>
       </c>
       <c r="H1424" t="n">
         <v>260328</v>
@@ -41694,7 +41694,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.25738203525543</v>
+        <v>1.25738215446472</v>
       </c>
       <c r="H1425" t="n">
         <v>180384</v>
@@ -41781,7 +41781,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.28397762775421</v>
+        <v>1.2839777469635</v>
       </c>
       <c r="H1428" t="n">
         <v>139450</v>
@@ -41839,7 +41839,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.24260663986206</v>
+        <v>1.24260675907135</v>
       </c>
       <c r="H1430" t="n">
         <v>100163</v>
@@ -41897,7 +41897,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1432" t="n">
         <v>266829</v>
@@ -41955,7 +41955,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1434" t="n">
         <v>300625</v>
@@ -41984,7 +41984,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1435" t="n">
         <v>261431</v>
@@ -42013,7 +42013,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614066123962</v>
+        <v>1.30614078044891</v>
       </c>
       <c r="H1436" t="n">
         <v>371377</v>
@@ -42129,7 +42129,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.39183759689331</v>
+        <v>1.3918377161026</v>
       </c>
       <c r="H1440" t="n">
         <v>280527</v>
@@ -42158,7 +42158,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.37706243991852</v>
+        <v>1.37706232070923</v>
       </c>
       <c r="H1441" t="n">
         <v>121208</v>
@@ -42274,7 +42274,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.32682633399963</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1445" t="n">
         <v>537192</v>
@@ -42332,7 +42332,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1447" t="n">
         <v>140764</v>
@@ -42361,7 +42361,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.32387101650238</v>
+        <v>1.32387113571167</v>
       </c>
       <c r="H1448" t="n">
         <v>172595</v>
@@ -42419,7 +42419,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.35785448551178</v>
+        <v>1.35785436630249</v>
       </c>
       <c r="H1450" t="n">
         <v>148858</v>
@@ -42448,7 +42448,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.3194385766983</v>
+        <v>1.31943845748901</v>
       </c>
       <c r="H1451" t="n">
         <v>263587</v>
@@ -42477,7 +42477,7 @@
         <v>1.75</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.29284274578094</v>
+        <v>1.29284286499023</v>
       </c>
       <c r="H1452" t="n">
         <v>270867</v>
@@ -42564,7 +42564,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.24112904071808</v>
+        <v>1.24112927913666</v>
       </c>
       <c r="H1455" t="n">
         <v>333161</v>
@@ -42593,7 +42593,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.25738203525543</v>
+        <v>1.25738215446472</v>
       </c>
       <c r="H1456" t="n">
         <v>404235</v>
@@ -42651,7 +42651,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.28102254867554</v>
+        <v>1.28102266788483</v>
       </c>
       <c r="H1458" t="n">
         <v>335681</v>
@@ -42680,7 +42680,7 @@
         <v>1.75</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.29284274578094</v>
+        <v>1.29284286499023</v>
       </c>
       <c r="H1459" t="n">
         <v>436418</v>
@@ -42709,7 +42709,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.25885951519012</v>
+        <v>1.25885963439941</v>
       </c>
       <c r="H1460" t="n">
         <v>250808</v>
@@ -42738,7 +42738,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.236696600914</v>
+        <v>1.23669648170471</v>
       </c>
       <c r="H1461" t="n">
         <v>302646</v>
@@ -42767,7 +42767,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1462" t="n">
         <v>172321</v>
@@ -42854,7 +42854,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.28397762775421</v>
+        <v>1.2839777469635</v>
       </c>
       <c r="H1465" t="n">
         <v>181638</v>
@@ -42883,7 +42883,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.24408435821533</v>
+        <v>1.24408423900604</v>
       </c>
       <c r="H1466" t="n">
         <v>137068</v>
@@ -42912,7 +42912,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.26033711433411</v>
+        <v>1.26033699512482</v>
       </c>
       <c r="H1467" t="n">
         <v>124843</v>
@@ -43028,7 +43028,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479291439056</v>
       </c>
       <c r="H1471" t="n">
         <v>1009740</v>
@@ -43086,7 +43086,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1473" t="n">
         <v>224203</v>
@@ -43115,7 +43115,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1474" t="n">
         <v>136320</v>
@@ -43144,7 +43144,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.40218043327332</v>
+        <v>1.4021805524826</v>
       </c>
       <c r="H1475" t="n">
         <v>161915</v>
@@ -43260,7 +43260,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1479" t="n">
         <v>88402</v>
@@ -43405,7 +43405,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.38297247886658</v>
+        <v>1.38297235965729</v>
       </c>
       <c r="H1484" t="n">
         <v>183001</v>
@@ -43434,7 +43434,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558472156525</v>
       </c>
       <c r="H1485" t="n">
         <v>148734</v>
@@ -43492,7 +43492,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.37853991985321</v>
+        <v>1.3785400390625</v>
       </c>
       <c r="H1487" t="n">
         <v>393472</v>
@@ -43521,7 +43521,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.40365791320801</v>
+        <v>1.4036580324173</v>
       </c>
       <c r="H1488" t="n">
         <v>290587</v>
@@ -43550,7 +43550,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.4524165391922</v>
+        <v>1.45241665840149</v>
       </c>
       <c r="H1489" t="n">
         <v>481854</v>
@@ -43579,7 +43579,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.4391188621521</v>
+        <v>1.43911874294281</v>
       </c>
       <c r="H1490" t="n">
         <v>184337</v>
@@ -43695,7 +43695,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.58096218109131</v>
+        <v>1.5809623003006</v>
       </c>
       <c r="H1494" t="n">
         <v>291825</v>
@@ -43782,7 +43782,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.49230992794037</v>
+        <v>1.49231004714966</v>
       </c>
       <c r="H1497" t="n">
         <v>91048</v>
@@ -43811,7 +43811,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.44798409938812</v>
+        <v>1.44798398017883</v>
       </c>
       <c r="H1498" t="n">
         <v>355414</v>
@@ -44101,7 +44101,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.32682633399963</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1508" t="n">
         <v>153178</v>
@@ -44217,7 +44217,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.35194432735443</v>
+        <v>1.35194420814514</v>
       </c>
       <c r="H1512" t="n">
         <v>91587</v>
@@ -44275,7 +44275,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.32830381393433</v>
+        <v>1.32830369472504</v>
       </c>
       <c r="H1514" t="n">
         <v>106604</v>
@@ -44304,7 +44304,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.32682633399963</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1515" t="n">
         <v>144985</v>
@@ -44478,7 +44478,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1521" t="n">
         <v>187418</v>
@@ -44565,7 +44565,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.50339162349701</v>
+        <v>1.5033917427063</v>
       </c>
       <c r="H1524" t="n">
         <v>245135</v>
@@ -44710,7 +44710,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.4812285900116</v>
+        <v>1.48122870922089</v>
       </c>
       <c r="H1529" t="n">
         <v>115283</v>
@@ -44797,7 +44797,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.48861634731293</v>
+        <v>1.48861622810364</v>
       </c>
       <c r="H1532" t="n">
         <v>153042</v>
@@ -44884,7 +44884,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.48861634731293</v>
+        <v>1.48861622810364</v>
       </c>
       <c r="H1535" t="n">
         <v>47904</v>
@@ -44913,7 +44913,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.50339162349701</v>
+        <v>1.5033917427063</v>
       </c>
       <c r="H1536" t="n">
         <v>152395</v>
@@ -44942,7 +44942,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.54402375221252</v>
+        <v>1.54402363300323</v>
       </c>
       <c r="H1537" t="n">
         <v>294711</v>
@@ -45116,7 +45116,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.41104555130005</v>
+        <v>1.41104567050934</v>
       </c>
       <c r="H1543" t="n">
         <v>303306</v>
@@ -45232,7 +45232,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1547" t="n">
         <v>154493</v>
@@ -45290,7 +45290,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.40956819057465</v>
+        <v>1.40956807136536</v>
       </c>
       <c r="H1549" t="n">
         <v>136807</v>
@@ -45348,7 +45348,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.39183759689331</v>
+        <v>1.3918377161026</v>
       </c>
       <c r="H1551" t="n">
         <v>99853</v>
@@ -45406,7 +45406,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479291439056</v>
       </c>
       <c r="H1553" t="n">
         <v>222677</v>
@@ -45464,7 +45464,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.43320882320404</v>
+        <v>1.43320858478546</v>
       </c>
       <c r="H1555" t="n">
         <v>187316</v>
@@ -45551,7 +45551,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.42286586761475</v>
+        <v>1.42286598682404</v>
       </c>
       <c r="H1558" t="n">
         <v>168182</v>
@@ -45580,7 +45580,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.41695582866669</v>
+        <v>1.4169557094574</v>
       </c>
       <c r="H1559" t="n">
         <v>112669</v>
@@ -45609,7 +45609,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.39036011695862</v>
+        <v>1.39036023616791</v>
       </c>
       <c r="H1560" t="n">
         <v>118655</v>
@@ -45638,7 +45638,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558472156525</v>
       </c>
       <c r="H1561" t="n">
         <v>147702</v>
@@ -45754,7 +45754,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.27659010887146</v>
+        <v>1.27658998966217</v>
       </c>
       <c r="H1565" t="n">
         <v>563690</v>
@@ -45812,7 +45812,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.24112904071808</v>
+        <v>1.24112927913666</v>
       </c>
       <c r="H1567" t="n">
         <v>290390</v>
@@ -45841,7 +45841,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.24260663986206</v>
+        <v>1.24260675907135</v>
       </c>
       <c r="H1568" t="n">
         <v>179629</v>
@@ -45899,7 +45899,7 @@
         <v>1.6360000371933</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.20862340927124</v>
+        <v>1.20862329006195</v>
       </c>
       <c r="H1570" t="n">
         <v>195940</v>
@@ -45986,7 +45986,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.21157836914062</v>
+        <v>1.2115786075592</v>
       </c>
       <c r="H1573" t="n">
         <v>417935</v>
@@ -46044,7 +46044,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.22635388374329</v>
+        <v>1.226353764534</v>
       </c>
       <c r="H1575" t="n">
         <v>95606</v>
@@ -46073,7 +46073,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.2130560874939</v>
+        <v>1.21305596828461</v>
       </c>
       <c r="H1576" t="n">
         <v>144426</v>
@@ -46102,7 +46102,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.26920247077942</v>
+        <v>1.26920235157013</v>
       </c>
       <c r="H1577" t="n">
         <v>169945</v>
@@ -46131,7 +46131,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.26624727249146</v>
+        <v>1.26624715328217</v>
       </c>
       <c r="H1578" t="n">
         <v>184608</v>
@@ -46218,7 +46218,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.26476979255676</v>
+        <v>1.26476967334747</v>
       </c>
       <c r="H1581" t="n">
         <v>115514</v>
@@ -46305,7 +46305,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.32682633399963</v>
+        <v>1.32682609558105</v>
       </c>
       <c r="H1584" t="n">
         <v>111356</v>
@@ -46334,7 +46334,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.30023062229156</v>
+        <v>1.30023050308228</v>
       </c>
       <c r="H1585" t="n">
         <v>261659</v>
@@ -46363,7 +46363,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.48492228984833</v>
+        <v>1.48492240905762</v>
       </c>
       <c r="H1586" t="n">
         <v>1535158</v>
@@ -46537,7 +46537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.64745128154755</v>
+        <v>1.64745116233826</v>
       </c>
       <c r="H1592" t="n">
         <v>488837</v>
@@ -46566,7 +46566,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1593" t="n">
         <v>358597</v>
@@ -46595,7 +46595,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.62159442901611</v>
+        <v>1.62159419059753</v>
       </c>
       <c r="H1594" t="n">
         <v>308615</v>
@@ -46624,7 +46624,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.62159442901611</v>
+        <v>1.62159419059753</v>
       </c>
       <c r="H1595" t="n">
         <v>268063</v>
@@ -46653,7 +46653,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.69177722930908</v>
+        <v>1.69177734851837</v>
       </c>
       <c r="H1596" t="n">
         <v>513055</v>
@@ -46711,7 +46711,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1598" t="n">
         <v>516825</v>
@@ -46740,7 +46740,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1599" t="n">
         <v>358721</v>
@@ -46769,7 +46769,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.69916474819183</v>
+        <v>1.69916486740112</v>
       </c>
       <c r="H1600" t="n">
         <v>291517</v>
@@ -46798,7 +46798,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1601" t="n">
         <v>293308</v>
@@ -46827,7 +46827,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.72132802009583</v>
+        <v>1.72132813930511</v>
       </c>
       <c r="H1602" t="n">
         <v>313832</v>
@@ -46856,7 +46856,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.70655250549316</v>
+        <v>1.70655262470245</v>
       </c>
       <c r="H1603" t="n">
         <v>292128</v>
@@ -46885,7 +46885,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.70655250549316</v>
+        <v>1.70655262470245</v>
       </c>
       <c r="H1604" t="n">
         <v>457156</v>
@@ -46943,7 +46943,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.70285892486572</v>
+        <v>1.70285880565643</v>
       </c>
       <c r="H1606" t="n">
         <v>652953</v>
@@ -47030,7 +47030,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.66592037677765</v>
+        <v>1.66592049598694</v>
       </c>
       <c r="H1609" t="n">
         <v>120344</v>
@@ -47059,7 +47059,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1610" t="n">
         <v>91769</v>
@@ -47088,7 +47088,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.66222655773163</v>
+        <v>1.66222667694092</v>
       </c>
       <c r="H1611" t="n">
         <v>68045</v>
@@ -47117,7 +47117,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1612" t="n">
         <v>180712</v>
@@ -47204,7 +47204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924847602844</v>
+        <v>1.52924835681915</v>
       </c>
       <c r="H1615" t="n">
         <v>245261</v>
@@ -47262,7 +47262,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.59573769569397</v>
+        <v>1.59573745727539</v>
       </c>
       <c r="H1617" t="n">
         <v>312009</v>
@@ -47291,7 +47291,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420679092407</v>
+        <v>1.61420667171478</v>
       </c>
       <c r="H1618" t="n">
         <v>173191</v>
@@ -47349,7 +47349,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.64006352424622</v>
+        <v>1.64006364345551</v>
       </c>
       <c r="H1620" t="n">
         <v>229999</v>
@@ -47378,7 +47378,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.65483891963959</v>
+        <v>1.6548388004303</v>
       </c>
       <c r="H1621" t="n">
         <v>179258</v>
@@ -47407,7 +47407,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.677001953125</v>
+        <v>1.67700183391571</v>
       </c>
       <c r="H1622" t="n">
         <v>296489</v>
@@ -47436,7 +47436,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.64745128154755</v>
+        <v>1.64745116233826</v>
       </c>
       <c r="H1623" t="n">
         <v>712219</v>
@@ -47465,7 +47465,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.66592037677765</v>
+        <v>1.66592049598694</v>
       </c>
       <c r="H1624" t="n">
         <v>652663</v>
@@ -47494,7 +47494,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.66592049598694</v>
+        <v>1.66592037677765</v>
       </c>
       <c r="H1625" t="n">
         <v>863616</v>
@@ -47581,7 +47581,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.63782048225403</v>
+        <v>1.63782060146332</v>
       </c>
       <c r="H1628" t="n">
         <v>236334</v>
@@ -47668,7 +47668,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.63782048225403</v>
+        <v>1.63782060146332</v>
       </c>
       <c r="H1631" t="n">
         <v>218453</v>
@@ -47697,7 +47697,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.63782048225403</v>
+        <v>1.63782060146332</v>
       </c>
       <c r="H1632" t="n">
         <v>113564</v>
@@ -47784,7 +47784,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.63782048225403</v>
+        <v>1.63782060146332</v>
       </c>
       <c r="H1635" t="n">
         <v>133365</v>
@@ -47813,7 +47813,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.61373484134674</v>
+        <v>1.61373496055603</v>
       </c>
       <c r="H1636" t="n">
         <v>134639</v>
@@ -47958,7 +47958,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1641" t="n">
         <v>199201</v>
@@ -48016,7 +48016,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1643" t="n">
         <v>247724</v>
@@ -48161,7 +48161,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.37448477745056</v>
+        <v>1.37448465824127</v>
       </c>
       <c r="H1648" t="n">
         <v>89430</v>
@@ -48306,7 +48306,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.3841187953949</v>
+        <v>1.38411891460419</v>
       </c>
       <c r="H1653" t="n">
         <v>351494</v>
@@ -48364,7 +48364,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.36645615100861</v>
+        <v>1.3664562702179</v>
       </c>
       <c r="H1655" t="n">
         <v>31246</v>
@@ -48509,7 +48509,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1660" t="n">
         <v>103532</v>
@@ -48538,7 +48538,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.2781423330307</v>
+        <v>1.27814221382141</v>
       </c>
       <c r="H1661" t="n">
         <v>79903</v>
@@ -48683,7 +48683,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688411712646</v>
+        <v>1.48688399791718</v>
       </c>
       <c r="H1666" t="n">
         <v>370783</v>
@@ -48741,7 +48741,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.43871283531189</v>
+        <v>1.43871295452118</v>
       </c>
       <c r="H1668" t="n">
         <v>426769</v>
@@ -48770,7 +48770,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.44353008270264</v>
+        <v>1.44352996349335</v>
       </c>
       <c r="H1669" t="n">
         <v>190612</v>
@@ -48799,7 +48799,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.43871283531189</v>
+        <v>1.43871295452118</v>
       </c>
       <c r="H1670" t="n">
         <v>160424</v>
@@ -48944,7 +48944,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082698345184</v>
+        <v>1.47082710266113</v>
       </c>
       <c r="H1675" t="n">
         <v>352968</v>
@@ -49060,7 +49060,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.41783881187439</v>
+        <v>1.4178386926651</v>
       </c>
       <c r="H1679" t="n">
         <v>183162</v>
@@ -49089,7 +49089,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820455551147</v>
+        <v>1.40820443630219</v>
       </c>
       <c r="H1680" t="n">
         <v>95443</v>
@@ -49263,7 +49263,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.36645615100861</v>
+        <v>1.3664562702179</v>
       </c>
       <c r="H1686" t="n">
         <v>210620</v>
@@ -49350,7 +49350,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470786571503</v>
       </c>
       <c r="H1689" t="n">
         <v>287007</v>
@@ -49437,7 +49437,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.32791912555695</v>
+        <v>1.32791924476624</v>
       </c>
       <c r="H1692" t="n">
         <v>174564</v>
@@ -49466,7 +49466,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.29419922828674</v>
+        <v>1.29419934749603</v>
       </c>
       <c r="H1693" t="n">
         <v>143170</v>
@@ -49611,7 +49611,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.22997117042542</v>
+        <v>1.22997105121613</v>
       </c>
       <c r="H1698" t="n">
         <v>108022</v>
@@ -49872,7 +49872,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1707" t="n">
         <v>328393</v>
@@ -49959,7 +49959,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.14968574047089</v>
+        <v>1.14968585968018</v>
       </c>
       <c r="H1710" t="n">
         <v>182259</v>
@@ -50162,7 +50162,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.10472595691681</v>
+        <v>1.1047260761261</v>
       </c>
       <c r="H1717" t="n">
         <v>265221</v>
@@ -50336,7 +50336,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.23318254947662</v>
+        <v>1.23318243026733</v>
       </c>
       <c r="H1723" t="n">
         <v>118046</v>
@@ -50481,7 +50481,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1728" t="n">
         <v>106830</v>
@@ -50539,7 +50539,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515404224396</v>
+        <v>1.22515392303467</v>
       </c>
       <c r="H1730" t="n">
         <v>107088</v>
@@ -50655,7 +50655,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1734" t="n">
         <v>122962</v>
@@ -50858,7 +50858,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1741" t="n">
         <v>362136</v>
@@ -50974,7 +50974,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470786571503</v>
       </c>
       <c r="H1745" t="n">
         <v>56326</v>
@@ -51032,7 +51032,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470786571503</v>
       </c>
       <c r="H1747" t="n">
         <v>209049</v>
@@ -51061,7 +51061,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.34879326820374</v>
+        <v>1.34879338741302</v>
       </c>
       <c r="H1748" t="n">
         <v>394461</v>
@@ -51148,7 +51148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.26850807666779</v>
+        <v>1.2685079574585</v>
       </c>
       <c r="H1751" t="n">
         <v>336838</v>
@@ -51438,7 +51438,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.22997117042542</v>
+        <v>1.22997105121613</v>
       </c>
       <c r="H1761" t="n">
         <v>76152</v>
@@ -51989,7 +51989,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.1834055185318</v>
+        <v>1.18340563774109</v>
       </c>
       <c r="H1780" t="n">
         <v>171787</v>
@@ -52076,7 +52076,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.19946265220642</v>
+        <v>1.19946253299713</v>
       </c>
       <c r="H1783" t="n">
         <v>190112</v>
@@ -52308,7 +52308,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.24281680583954</v>
+        <v>1.24281668663025</v>
       </c>
       <c r="H1791" t="n">
         <v>163525</v>
@@ -52366,7 +52366,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.24281680583954</v>
+        <v>1.24281668663025</v>
       </c>
       <c r="H1793" t="n">
         <v>186386</v>
@@ -52540,7 +52540,7 @@
         <v>1.53600001335144</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.23318254947662</v>
+        <v>1.23318243026733</v>
       </c>
       <c r="H1799" t="n">
         <v>58960</v>
@@ -52569,7 +52569,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.24121105670929</v>
+        <v>1.2412109375</v>
       </c>
       <c r="H1800" t="n">
         <v>114006</v>
@@ -52685,7 +52685,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.31507349014282</v>
+        <v>1.31507360935211</v>
       </c>
       <c r="H1804" t="n">
         <v>568083</v>
@@ -52714,7 +52714,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1805" t="n">
-        <v>1.32470774650574</v>
+        <v>1.32470786571503</v>
       </c>
       <c r="H1805" t="n">
         <v>309868</v>
@@ -52801,7 +52801,7 @@
         <v>1.75</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.40499293804169</v>
+        <v>1.40499305725098</v>
       </c>
       <c r="H1808" t="n">
         <v>628014</v>
@@ -52830,7 +52830,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1809" t="n">
-        <v>1.39375305175781</v>
+        <v>1.3937531709671</v>
       </c>
       <c r="H1809" t="n">
         <v>291370</v>
@@ -53120,7 +53120,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.3841187953949</v>
+        <v>1.38411891460419</v>
       </c>
       <c r="H1819" t="n">
         <v>180097</v>
@@ -53207,7 +53207,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.34879326820374</v>
+        <v>1.34879338741302</v>
       </c>
       <c r="H1822" t="n">
         <v>112098</v>
@@ -53265,7 +53265,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.39375305175781</v>
+        <v>1.3937531709671</v>
       </c>
       <c r="H1824" t="n">
         <v>108877</v>
@@ -53294,7 +53294,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1825" t="n">
-        <v>1.40338730812073</v>
+        <v>1.40338742733002</v>
       </c>
       <c r="H1825" t="n">
         <v>98704</v>
@@ -53497,7 +53497,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163890361786</v>
+        <v>1.36163902282715</v>
       </c>
       <c r="H1832" t="n">
         <v>160687</v>
@@ -53526,7 +53526,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310199737549</v>
+        <v>1.32310211658478</v>
       </c>
       <c r="H1833" t="n">
         <v>313479</v>
@@ -53584,7 +53584,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1835" t="n">
         <v>126203</v>
@@ -53613,7 +53613,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.30704498291016</v>
+        <v>1.30704510211945</v>
       </c>
       <c r="H1836" t="n">
         <v>104258</v>
@@ -53642,7 +53642,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901659488678</v>
+        <v>1.29901647567749</v>
       </c>
       <c r="H1837" t="n">
         <v>137726</v>
@@ -53787,7 +53787,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.44353008270264</v>
+        <v>1.44352996349335</v>
       </c>
       <c r="H1842" t="n">
         <v>694559</v>
@@ -54222,7 +54222,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.52220976352692</v>
+        <v>1.52220964431763</v>
       </c>
       <c r="H1857" t="n">
         <v>84316</v>
@@ -54251,7 +54251,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1858" t="n">
         <v>58868</v>
@@ -54280,7 +54280,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.4788556098938</v>
+        <v>1.47885549068451</v>
       </c>
       <c r="H1859" t="n">
         <v>185027</v>
@@ -54628,7 +54628,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1871" t="n">
         <v>152966</v>
@@ -54657,7 +54657,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.51739263534546</v>
+        <v>1.51739251613617</v>
       </c>
       <c r="H1872" t="n">
         <v>111449</v>
@@ -54686,7 +54686,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.51899826526642</v>
+        <v>1.51899814605713</v>
       </c>
       <c r="H1873" t="n">
         <v>152075</v>
@@ -55063,7 +55063,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.43476319313049</v>
+        <v>1.43476331233978</v>
       </c>
       <c r="H1886" t="n">
         <v>536461</v>
@@ -55208,7 +55208,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.42955851554871</v>
+        <v>1.429558634758</v>
       </c>
       <c r="H1891" t="n">
         <v>91752</v>
@@ -55324,7 +55324,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1895" t="n">
         <v>155465</v>
@@ -55469,7 +55469,7 @@
         <v>1.75</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.51803839206696</v>
+        <v>1.51803851127625</v>
       </c>
       <c r="H1900" t="n">
         <v>98091</v>
@@ -55527,7 +55527,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1902" t="n">
         <v>209046</v>
@@ -55614,7 +55614,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.41220951080322</v>
+        <v>1.41220963001251</v>
       </c>
       <c r="H1905" t="n">
         <v>123981</v>
@@ -55672,7 +55672,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.43129336833954</v>
+        <v>1.43129348754883</v>
       </c>
       <c r="H1907" t="n">
         <v>105330</v>
@@ -55730,7 +55730,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.43302822113037</v>
+        <v>1.43302834033966</v>
       </c>
       <c r="H1909" t="n">
         <v>141549</v>
@@ -55846,7 +55846,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.43823301792145</v>
+        <v>1.43823313713074</v>
       </c>
       <c r="H1913" t="n">
         <v>242905</v>
@@ -55904,7 +55904,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.43476319313049</v>
+        <v>1.43476331233978</v>
       </c>
       <c r="H1915" t="n">
         <v>75897</v>
@@ -56020,7 +56020,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H1919" t="n">
         <v>73204</v>
@@ -56078,7 +56078,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H1921" t="n">
         <v>105790</v>
@@ -56107,7 +56107,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.47119605541229</v>
+        <v>1.47119617462158</v>
       </c>
       <c r="H1922" t="n">
         <v>167278</v>
@@ -56136,7 +56136,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.46946120262146</v>
+        <v>1.46946132183075</v>
       </c>
       <c r="H1923" t="n">
         <v>75490</v>
@@ -56194,7 +56194,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1925" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1925" t="n">
         <v>85670</v>
@@ -56223,7 +56223,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1926" t="n">
         <v>130688</v>
@@ -56252,7 +56252,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1927" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1927" t="n">
         <v>168473</v>
@@ -56310,7 +56310,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.50415921211243</v>
+        <v>1.50415933132172</v>
       </c>
       <c r="H1929" t="n">
         <v>283646</v>
@@ -56368,7 +56368,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.50762903690338</v>
+        <v>1.50762915611267</v>
       </c>
       <c r="H1931" t="n">
         <v>280427</v>
@@ -56397,7 +56397,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.51456868648529</v>
+        <v>1.51456880569458</v>
       </c>
       <c r="H1932" t="n">
         <v>194466</v>
@@ -56455,7 +56455,7 @@
         <v>1.74600005149841</v>
       </c>
       <c r="G1934" t="n">
-        <v>1.51456868648529</v>
+        <v>1.51456880569458</v>
       </c>
       <c r="H1934" t="n">
         <v>127399</v>
@@ -56484,7 +56484,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H1935" t="n">
         <v>224620</v>
@@ -56542,7 +56542,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1937" t="n">
         <v>331903</v>
@@ -56600,7 +56600,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.40353512763977</v>
+        <v>1.40353500843048</v>
       </c>
       <c r="H1939" t="n">
         <v>88869</v>
@@ -56658,7 +56658,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.4226188659668</v>
+        <v>1.42261898517609</v>
       </c>
       <c r="H1941" t="n">
         <v>129872</v>
@@ -56716,7 +56716,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.40180027484894</v>
+        <v>1.40180015563965</v>
       </c>
       <c r="H1943" t="n">
         <v>113302</v>
@@ -56803,7 +56803,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.4226188659668</v>
+        <v>1.42261898517609</v>
       </c>
       <c r="H1946" t="n">
         <v>144857</v>
@@ -56832,7 +56832,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.42088401317596</v>
+        <v>1.42088413238525</v>
       </c>
       <c r="H1947" t="n">
         <v>128877</v>
@@ -57151,7 +57151,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.37924647331238</v>
+        <v>1.37924635410309</v>
       </c>
       <c r="H1958" t="n">
         <v>186765</v>
@@ -57383,7 +57383,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.42088401317596</v>
+        <v>1.42088413238525</v>
       </c>
       <c r="H1966" t="n">
         <v>255864</v>
@@ -57441,7 +57441,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.40353512763977</v>
+        <v>1.40353500843048</v>
       </c>
       <c r="H1968" t="n">
         <v>58263</v>
@@ -57702,7 +57702,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.38098132610321</v>
+        <v>1.38098120689392</v>
       </c>
       <c r="H1977" t="n">
         <v>161060</v>
@@ -57847,7 +57847,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1982" t="n">
         <v>151373</v>
@@ -57876,7 +57876,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1983" t="n">
         <v>104614</v>
@@ -57905,7 +57905,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1984" t="n">
         <v>112284</v>
@@ -57934,7 +57934,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.3983302116394</v>
+        <v>1.39833033084869</v>
       </c>
       <c r="H1985" t="n">
         <v>38175</v>
@@ -57963,7 +57963,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1986" t="n">
         <v>158425</v>
@@ -57992,7 +57992,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1987" t="n">
         <v>143196</v>
@@ -58021,7 +58021,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1988" t="n">
         <v>121532</v>
@@ -58137,7 +58137,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.38965582847595</v>
+        <v>1.38965570926666</v>
       </c>
       <c r="H1992" t="n">
         <v>99504</v>
@@ -58369,7 +58369,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.43302822113037</v>
+        <v>1.43302834033966</v>
       </c>
       <c r="H2000" t="n">
         <v>91033</v>
@@ -58456,7 +58456,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.42955851554871</v>
+        <v>1.429558634758</v>
       </c>
       <c r="H2003" t="n">
         <v>437597</v>
@@ -58485,7 +58485,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H2004" t="n">
         <v>396696</v>
@@ -58630,7 +58630,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G2009" t="n">
-        <v>1.4781357049942</v>
+        <v>1.47813582420349</v>
       </c>
       <c r="H2009" t="n">
         <v>120373</v>
@@ -58659,7 +58659,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2010" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2010" t="n">
         <v>78064</v>
@@ -58688,7 +58688,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G2011" t="n">
-        <v>1.4781357049942</v>
+        <v>1.47813582420349</v>
       </c>
       <c r="H2011" t="n">
         <v>106739</v>
@@ -58746,7 +58746,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2013" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2013" t="n">
         <v>46060</v>
@@ -58862,7 +58862,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.45731687545776</v>
+        <v>1.45731699466705</v>
       </c>
       <c r="H2017" t="n">
         <v>211706</v>
@@ -58920,7 +58920,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.45905184745789</v>
+        <v>1.45905196666718</v>
       </c>
       <c r="H2019" t="n">
         <v>74724</v>
@@ -58949,7 +58949,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.46946120262146</v>
+        <v>1.46946132183075</v>
       </c>
       <c r="H2020" t="n">
         <v>63283</v>
@@ -59007,7 +59007,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.47640085220337</v>
+        <v>1.47640097141266</v>
       </c>
       <c r="H2022" t="n">
         <v>155094</v>
@@ -59036,7 +59036,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.46772634983063</v>
+        <v>1.46772646903992</v>
       </c>
       <c r="H2023" t="n">
         <v>24585</v>
@@ -59123,7 +59123,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.47119605541229</v>
+        <v>1.47119617462158</v>
       </c>
       <c r="H2026" t="n">
         <v>101853</v>
@@ -59239,7 +59239,7 @@
         <v>1.75</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.51803839206696</v>
+        <v>1.51803851127625</v>
       </c>
       <c r="H2030" t="n">
         <v>141811</v>
@@ -59326,7 +59326,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2033" t="n">
         <v>261156</v>
@@ -59355,7 +59355,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2034" t="n">
         <v>289476</v>
@@ -59413,7 +59413,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2036" t="n">
         <v>222362</v>
@@ -59819,7 +59819,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.55794131755829</v>
+        <v>1.557941198349</v>
       </c>
       <c r="H2050" t="n">
         <v>242753</v>
@@ -59993,7 +59993,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2056" t="n">
         <v>183238</v>
@@ -60022,7 +60022,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2057" t="n">
         <v>159596</v>
@@ -60080,7 +60080,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2059" t="n">
         <v>166315</v>
@@ -60138,7 +60138,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2061" t="n">
         <v>245729</v>
@@ -60167,7 +60167,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G2062" t="n">
-        <v>1.55794131755829</v>
+        <v>1.557941198349</v>
       </c>
       <c r="H2062" t="n">
         <v>101478</v>
@@ -60312,7 +60312,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.54232704639435</v>
+        <v>1.54232716560364</v>
       </c>
       <c r="H2067" t="n">
         <v>176828</v>
@@ -60428,7 +60428,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G2071" t="n">
-        <v>1.58916938304901</v>
+        <v>1.5891695022583</v>
       </c>
       <c r="H2071" t="n">
         <v>202349</v>
@@ -60544,7 +60544,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.56835067272186</v>
+        <v>1.56835055351257</v>
       </c>
       <c r="H2075" t="n">
         <v>165697</v>
@@ -60602,7 +60602,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2077" t="n">
         <v>182533</v>
@@ -60631,7 +60631,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2078" t="n">
         <v>124929</v>
@@ -60747,7 +60747,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2082" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2082" t="n">
         <v>478181</v>
@@ -60776,7 +60776,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G2083" t="n">
-        <v>1.55447137355804</v>
+        <v>1.55447149276733</v>
       </c>
       <c r="H2083" t="n">
         <v>218213</v>
@@ -60805,7 +60805,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2084" t="n">
-        <v>1.55967617034912</v>
+        <v>1.55967605113983</v>
       </c>
       <c r="H2084" t="n">
         <v>164927</v>
@@ -60950,7 +60950,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G2089" t="n">
-        <v>1.55967617034912</v>
+        <v>1.55967605113983</v>
       </c>
       <c r="H2089" t="n">
         <v>237737</v>
@@ -61298,7 +61298,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2101" t="n">
-        <v>1.83465802669525</v>
+        <v>1.83465790748596</v>
       </c>
       <c r="H2101" t="n">
         <v>399372</v>
@@ -61327,7 +61327,7 @@
         <v>2.125</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2102" t="n">
         <v>614339</v>
@@ -61443,7 +61443,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.94308936595917</v>
+        <v>1.94308924674988</v>
       </c>
       <c r="H2106" t="n">
         <v>1986166</v>
@@ -61501,7 +61501,7 @@
         <v>2.125</v>
       </c>
       <c r="G2108" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2108" t="n">
         <v>629582</v>
@@ -61646,7 +61646,7 @@
         <v>2.125</v>
       </c>
       <c r="G2113" t="n">
-        <v>1.84333252906799</v>
+        <v>1.8433324098587</v>
       </c>
       <c r="H2113" t="n">
         <v>238974</v>
@@ -61704,7 +61704,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.87369334697723</v>
+        <v>1.87369322776794</v>
       </c>
       <c r="H2115" t="n">
         <v>183920</v>
@@ -61849,7 +61849,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.87369334697723</v>
+        <v>1.87369322776794</v>
       </c>
       <c r="H2120" t="n">
         <v>272405</v>
@@ -61878,7 +61878,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.89104235172272</v>
+        <v>1.89104223251343</v>
       </c>
       <c r="H2121" t="n">
         <v>113831</v>
@@ -61907,7 +61907,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.89104235172272</v>
+        <v>1.89104223251343</v>
       </c>
       <c r="H2122" t="n">
         <v>172869</v>
@@ -62110,7 +62110,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.20766162872314</v>
+        <v>2.20766186714172</v>
       </c>
       <c r="H2129" t="n">
         <v>392842</v>
@@ -62342,7 +62342,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G2137" t="n">
-        <v>2.07754421234131</v>
+        <v>2.07754397392273</v>
       </c>
       <c r="H2137" t="n">
         <v>1128604</v>
@@ -80154,6 +80154,35 @@
         <v>63841</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>2.07500004768372</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>2.04500007629395</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>2.0550000667572</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>2.0550000667572</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>111971</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CAI.MI.xlsx
+++ b/data/CAI.MI.xlsx
@@ -427,7 +427,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G2" t="n">
-        <v>2.85730123519897</v>
+        <v>2.8573009967804</v>
       </c>
       <c r="H2" t="n">
         <v>30003</v>
@@ -485,7 +485,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80525803565979</v>
+        <v>2.80525827407837</v>
       </c>
       <c r="H4" t="n">
         <v>23828</v>
@@ -514,7 +514,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717805862427</v>
       </c>
       <c r="H5" t="n">
         <v>103885</v>
@@ -659,7 +659,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G10" t="n">
-        <v>2.60850954055786</v>
+        <v>2.60850930213928</v>
       </c>
       <c r="H10" t="n">
         <v>108431</v>
@@ -717,7 +717,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G12" t="n">
-        <v>2.56408214569092</v>
+        <v>2.56408190727234</v>
       </c>
       <c r="H12" t="n">
         <v>52586</v>
@@ -746,7 +746,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G13" t="n">
-        <v>2.546311378479</v>
+        <v>2.54631114006042</v>
       </c>
       <c r="H13" t="n">
         <v>34257</v>
@@ -833,7 +833,7 @@
         <v>4.19799995422363</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66436004638672</v>
+        <v>2.66436052322388</v>
       </c>
       <c r="H16" t="n">
         <v>61532</v>
@@ -891,7 +891,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55138850212097</v>
+        <v>2.55138874053955</v>
       </c>
       <c r="H18" t="n">
         <v>16747</v>
@@ -949,7 +949,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G20" t="n">
-        <v>2.51965498924255</v>
+        <v>2.51965522766113</v>
       </c>
       <c r="H20" t="n">
         <v>43026</v>
@@ -1007,7 +1007,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56662106513977</v>
+        <v>2.56662082672119</v>
       </c>
       <c r="H22" t="n">
         <v>34521</v>
@@ -1094,7 +1094,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G25" t="n">
-        <v>2.53107905387878</v>
+        <v>2.53107929229736</v>
       </c>
       <c r="H25" t="n">
         <v>32107</v>
@@ -1181,7 +1181,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G28" t="n">
-        <v>2.28609490394592</v>
+        <v>2.2860951423645</v>
       </c>
       <c r="H28" t="n">
         <v>109730</v>
@@ -1239,7 +1239,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G30" t="n">
-        <v>2.13885068893433</v>
+        <v>2.13885045051575</v>
       </c>
       <c r="H30" t="n">
         <v>81897</v>
@@ -1268,7 +1268,7 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22135853767395</v>
+        <v>2.22135806083679</v>
       </c>
       <c r="H31" t="n">
         <v>155211</v>
@@ -1297,7 +1297,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36098599433899</v>
+        <v>2.36098647117615</v>
       </c>
       <c r="H32" t="n">
         <v>97681</v>
@@ -1326,7 +1326,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G33" t="n">
-        <v>2.32798361778259</v>
+        <v>2.32798337936401</v>
       </c>
       <c r="H33" t="n">
         <v>39970</v>
@@ -1355,7 +1355,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G34" t="n">
-        <v>2.486652135849</v>
+        <v>2.48665189743042</v>
       </c>
       <c r="H34" t="n">
         <v>72475</v>
@@ -1384,7 +1384,7 @@
         <v>4.12599992752075</v>
       </c>
       <c r="G35" t="n">
-        <v>2.61866354942322</v>
+        <v>2.6186637878418</v>
       </c>
       <c r="H35" t="n">
         <v>117716</v>
@@ -1413,7 +1413,7 @@
         <v>4.02600002288818</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5551962852478</v>
+        <v>2.55519652366638</v>
       </c>
       <c r="H36" t="n">
         <v>17078</v>
@@ -1471,7 +1471,7 @@
         <v>4.07399988174438</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58566117286682</v>
+        <v>2.58566093444824</v>
       </c>
       <c r="H38" t="n">
         <v>18151</v>
@@ -1500,7 +1500,7 @@
         <v>3.93199992179871</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49553775787354</v>
+        <v>2.4955370426178</v>
       </c>
       <c r="H39" t="n">
         <v>77760</v>
@@ -1558,7 +1558,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G41" t="n">
-        <v>2.60850954055786</v>
+        <v>2.60850930213928</v>
       </c>
       <c r="H41" t="n">
         <v>29241</v>
@@ -1587,7 +1587,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G42" t="n">
-        <v>2.60850954055786</v>
+        <v>2.60850930213928</v>
       </c>
       <c r="H42" t="n">
         <v>49765</v>
@@ -1645,7 +1645,7 @@
         <v>4.19199991226196</v>
       </c>
       <c r="G44" t="n">
-        <v>2.66055226325989</v>
+        <v>2.66055250167847</v>
       </c>
       <c r="H44" t="n">
         <v>83690</v>
@@ -1761,7 +1761,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68213152885437</v>
+        <v>2.68213129043579</v>
       </c>
       <c r="H48" t="n">
         <v>40006</v>
@@ -1790,7 +1790,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>2.69355535507202</v>
+        <v>2.69355583190918</v>
       </c>
       <c r="H49" t="n">
         <v>25946</v>
@@ -1877,7 +1877,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G52" t="n">
-        <v>2.76717782020569</v>
+        <v>2.76717805862427</v>
       </c>
       <c r="H52" t="n">
         <v>124017</v>
@@ -1906,7 +1906,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G53" t="n">
-        <v>2.74179077148438</v>
+        <v>2.74179100990295</v>
       </c>
       <c r="H53" t="n">
         <v>42603</v>
@@ -1964,7 +1964,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G55" t="n">
-        <v>2.90172839164734</v>
+        <v>2.90172863006592</v>
       </c>
       <c r="H55" t="n">
         <v>82307</v>
@@ -1993,7 +1993,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G56" t="n">
-        <v>2.93853950500488</v>
+        <v>2.93853998184204</v>
       </c>
       <c r="H56" t="n">
         <v>170803</v>
@@ -2051,7 +2051,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G58" t="n">
-        <v>2.98169755935669</v>
+        <v>2.98169708251953</v>
       </c>
       <c r="H58" t="n">
         <v>45732</v>
@@ -2080,7 +2080,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G59" t="n">
-        <v>2.95504117012024</v>
+        <v>2.9550416469574</v>
       </c>
       <c r="H59" t="n">
         <v>62635</v>
@@ -2109,7 +2109,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G60" t="n">
-        <v>2.94869422912598</v>
+        <v>2.9486939907074</v>
       </c>
       <c r="H60" t="n">
         <v>43744</v>
@@ -2138,7 +2138,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G61" t="n">
-        <v>3.00835347175598</v>
+        <v>3.00835371017456</v>
       </c>
       <c r="H61" t="n">
         <v>91726</v>
@@ -2196,7 +2196,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G63" t="n">
-        <v>2.98423600196838</v>
+        <v>2.98423624038696</v>
       </c>
       <c r="H63" t="n">
         <v>32830</v>
@@ -2225,7 +2225,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>2.99566030502319</v>
+        <v>2.99566006660461</v>
       </c>
       <c r="H64" t="n">
         <v>46851</v>
@@ -2254,7 +2254,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G65" t="n">
-        <v>3.00327587127686</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H65" t="n">
         <v>28745</v>
@@ -2283,7 +2283,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>3.0020067691803</v>
+        <v>3.00200724601746</v>
       </c>
       <c r="H66" t="n">
         <v>39511</v>
@@ -2312,7 +2312,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.91949892044067</v>
+        <v>2.91949939727783</v>
       </c>
       <c r="H67" t="n">
         <v>33763</v>
@@ -2370,7 +2370,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G69" t="n">
-        <v>2.99819874763489</v>
+        <v>2.99819898605347</v>
       </c>
       <c r="H69" t="n">
         <v>75222</v>
@@ -2399,7 +2399,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G70" t="n">
-        <v>3.0603973865509</v>
+        <v>3.06039714813232</v>
       </c>
       <c r="H70" t="n">
         <v>458291</v>
@@ -2457,7 +2457,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G72" t="n">
-        <v>3.07182097434998</v>
+        <v>3.07182145118713</v>
       </c>
       <c r="H72" t="n">
         <v>136484</v>
@@ -2486,7 +2486,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.0464346408844</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H73" t="n">
         <v>94926</v>
@@ -2573,7 +2573,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G76" t="n">
-        <v>3.16702151298523</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H76" t="n">
         <v>114194</v>
@@ -2602,7 +2602,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16702151298523</v>
+        <v>3.16702175140381</v>
       </c>
       <c r="H77" t="n">
         <v>122410</v>
@@ -2689,7 +2689,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14798188209534</v>
+        <v>3.14798164367676</v>
       </c>
       <c r="H80" t="n">
         <v>29895</v>
@@ -2718,7 +2718,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G81" t="n">
-        <v>3.09847736358643</v>
+        <v>3.09847712516785</v>
       </c>
       <c r="H81" t="n">
         <v>94591</v>
@@ -2747,7 +2747,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G82" t="n">
-        <v>3.11243987083435</v>
+        <v>3.11244010925293</v>
       </c>
       <c r="H82" t="n">
         <v>32834</v>
@@ -2776,7 +2776,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.09086132049561</v>
+        <v>3.09086108207703</v>
       </c>
       <c r="H83" t="n">
         <v>44802</v>
@@ -2805,7 +2805,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G84" t="n">
-        <v>3.08959197998047</v>
+        <v>3.08959221839905</v>
       </c>
       <c r="H84" t="n">
         <v>34327</v>
@@ -2834,7 +2834,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>3.06547451019287</v>
+        <v>3.06547427177429</v>
       </c>
       <c r="H85" t="n">
         <v>37849</v>
@@ -2892,7 +2892,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G87" t="n">
-        <v>3.00327587127686</v>
+        <v>3.00327610969543</v>
       </c>
       <c r="H87" t="n">
         <v>120760</v>
@@ -2921,7 +2921,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G88" t="n">
-        <v>3.05912804603577</v>
+        <v>3.05912780761719</v>
       </c>
       <c r="H88" t="n">
         <v>145710</v>
@@ -2950,7 +2950,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.0464346408844</v>
+        <v>3.04643440246582</v>
       </c>
       <c r="H89" t="n">
         <v>55991</v>
@@ -2979,7 +2979,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G90" t="n">
-        <v>3.03053998947144</v>
+        <v>3.03053975105286</v>
       </c>
       <c r="H90" t="n">
         <v>50752</v>
@@ -3008,7 +3008,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H91" t="n">
         <v>62212</v>
@@ -3124,7 +3124,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87424421310425</v>
+        <v>2.87424468994141</v>
       </c>
       <c r="H95" t="n">
         <v>67830</v>
@@ -3182,7 +3182,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>2.92722582817078</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H97" t="n">
         <v>13594</v>
@@ -3240,7 +3240,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G99" t="n">
-        <v>3.1126606464386</v>
+        <v>3.11266112327576</v>
       </c>
       <c r="H99" t="n">
         <v>86375</v>
@@ -3269,7 +3269,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G100" t="n">
-        <v>3.09941530227661</v>
+        <v>3.09941554069519</v>
       </c>
       <c r="H100" t="n">
         <v>95435</v>
@@ -3298,7 +3298,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G101" t="n">
-        <v>3.07822299003601</v>
+        <v>3.07822322845459</v>
       </c>
       <c r="H101" t="n">
         <v>47757</v>
@@ -3327,7 +3327,7 @@
         <v>4.75</v>
       </c>
       <c r="G102" t="n">
-        <v>3.14577460289001</v>
+        <v>3.14577436447144</v>
       </c>
       <c r="H102" t="n">
         <v>86451</v>
@@ -3356,7 +3356,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G103" t="n">
-        <v>3.20140528678894</v>
+        <v>3.20140504837036</v>
       </c>
       <c r="H103" t="n">
         <v>92445</v>
@@ -3385,7 +3385,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.17888832092285</v>
+        <v>3.17888808250427</v>
       </c>
       <c r="H104" t="n">
         <v>49257</v>
@@ -3443,7 +3443,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G106" t="n">
-        <v>3.23584342002869</v>
+        <v>3.23584270477295</v>
       </c>
       <c r="H106" t="n">
         <v>124255</v>
@@ -3472,7 +3472,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>3.2318696975708</v>
+        <v>3.23186945915222</v>
       </c>
       <c r="H107" t="n">
         <v>38634</v>
@@ -3501,7 +3501,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G108" t="n">
-        <v>3.19610691070557</v>
+        <v>3.19610714912415</v>
       </c>
       <c r="H108" t="n">
         <v>19558</v>
@@ -3530,7 +3530,7 @@
         <v>4.8439998626709</v>
       </c>
       <c r="G109" t="n">
-        <v>3.20802783966064</v>
+        <v>3.20802760124207</v>
       </c>
       <c r="H109" t="n">
         <v>23367</v>
@@ -3559,7 +3559,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G110" t="n">
-        <v>3.1682915687561</v>
+        <v>3.16829180717468</v>
       </c>
       <c r="H110" t="n">
         <v>37625</v>
@@ -3617,7 +3617,7 @@
         <v>4.69799995422363</v>
       </c>
       <c r="G112" t="n">
-        <v>3.11133670806885</v>
+        <v>3.11133623123169</v>
       </c>
       <c r="H112" t="n">
         <v>10926</v>
@@ -3675,7 +3675,7 @@
         <v>4.5</v>
       </c>
       <c r="G114" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H114" t="n">
         <v>34326</v>
@@ -3733,7 +3733,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>2.73516821861267</v>
+        <v>2.73516845703125</v>
       </c>
       <c r="H116" t="n">
         <v>77740</v>
@@ -3791,7 +3791,7 @@
         <v>4.06599998474121</v>
       </c>
       <c r="G118" t="n">
-        <v>2.69278335571289</v>
+        <v>2.69278311729431</v>
       </c>
       <c r="H118" t="n">
         <v>84374</v>
@@ -3936,7 +3936,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G123" t="n">
-        <v>2.92060303688049</v>
+        <v>2.92060327529907</v>
       </c>
       <c r="H123" t="n">
         <v>44363</v>
@@ -3965,7 +3965,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81596493721008</v>
+        <v>2.81596517562866</v>
       </c>
       <c r="H124" t="n">
         <v>67252</v>
@@ -4023,7 +4023,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.74841332435608</v>
+        <v>2.74841356277466</v>
       </c>
       <c r="H126" t="n">
         <v>44702</v>
@@ -4052,7 +4052,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G127" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H127" t="n">
         <v>171545</v>
@@ -4081,7 +4081,7 @@
         <v>4.5</v>
       </c>
       <c r="G128" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H128" t="n">
         <v>87090</v>
@@ -4110,7 +4110,7 @@
         <v>4.5</v>
       </c>
       <c r="G129" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H129" t="n">
         <v>113855</v>
@@ -4139,7 +4139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G130" t="n">
-        <v>2.94047093391418</v>
+        <v>2.94047117233276</v>
       </c>
       <c r="H130" t="n">
         <v>49672</v>
@@ -4197,7 +4197,7 @@
         <v>4.14799976348877</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74708867073059</v>
+        <v>2.74708890914917</v>
       </c>
       <c r="H132" t="n">
         <v>64127</v>
@@ -4226,7 +4226,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78152656555176</v>
+        <v>2.78152680397034</v>
       </c>
       <c r="H133" t="n">
         <v>40862</v>
@@ -4284,7 +4284,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G135" t="n">
-        <v>2.94709420204163</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H135" t="n">
         <v>222212</v>
@@ -4313,7 +4313,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G136" t="n">
-        <v>3.00802206993103</v>
+        <v>3.00802278518677</v>
       </c>
       <c r="H136" t="n">
         <v>190152</v>
@@ -4342,7 +4342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G137" t="n">
-        <v>2.96696209907532</v>
+        <v>2.96696186065674</v>
       </c>
       <c r="H137" t="n">
         <v>193814</v>
@@ -4400,7 +4400,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G139" t="n">
-        <v>2.9153048992157</v>
+        <v>2.91530513763428</v>
       </c>
       <c r="H139" t="n">
         <v>337397</v>
@@ -4487,7 +4487,7 @@
         <v>4.09800004959106</v>
       </c>
       <c r="G142" t="n">
-        <v>2.71397590637207</v>
+        <v>2.71397566795349</v>
       </c>
       <c r="H142" t="n">
         <v>293231</v>
@@ -4516,7 +4516,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G143" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H143" t="n">
         <v>206630</v>
@@ -4603,7 +4603,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G146" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112639427185</v>
       </c>
       <c r="H146" t="n">
         <v>91785</v>
@@ -4632,7 +4632,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G147" t="n">
-        <v>2.67291498184204</v>
+        <v>2.67291474342346</v>
       </c>
       <c r="H147" t="n">
         <v>156041</v>
@@ -4661,7 +4661,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G148" t="n">
-        <v>2.6358277797699</v>
+        <v>2.63582801818848</v>
       </c>
       <c r="H148" t="n">
         <v>77302</v>
@@ -4690,7 +4690,7 @@
         <v>3.98799991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>2.64112615585327</v>
+        <v>2.64112639427185</v>
       </c>
       <c r="H149" t="n">
         <v>58696</v>
@@ -4719,7 +4719,7 @@
         <v>3.92799997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>2.60139012336731</v>
+        <v>2.60138988494873</v>
       </c>
       <c r="H150" t="n">
         <v>119099</v>
@@ -4748,7 +4748,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G151" t="n">
-        <v>2.54178595542908</v>
+        <v>2.5417857170105</v>
       </c>
       <c r="H151" t="n">
         <v>586648</v>
@@ -4806,7 +4806,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>2.68218684196472</v>
+        <v>2.68218660354614</v>
       </c>
       <c r="H153" t="n">
         <v>379608</v>
@@ -4835,7 +4835,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G154" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H154" t="n">
         <v>972279</v>
@@ -4864,7 +4864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G155" t="n">
-        <v>2.64245080947876</v>
+        <v>2.64245057106018</v>
       </c>
       <c r="H155" t="n">
         <v>131874</v>
@@ -4922,7 +4922,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G157" t="n">
-        <v>2.72192311286926</v>
+        <v>2.72192287445068</v>
       </c>
       <c r="H157" t="n">
         <v>1740457</v>
@@ -4951,7 +4951,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G158" t="n">
-        <v>2.71529984474182</v>
+        <v>2.71529960632324</v>
       </c>
       <c r="H158" t="n">
         <v>518886</v>
@@ -5009,7 +5009,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G160" t="n">
-        <v>2.66364312171936</v>
+        <v>2.66364288330078</v>
       </c>
       <c r="H160" t="n">
         <v>69314</v>
@@ -5038,7 +5038,7 @@
         <v>4.02400016784668</v>
       </c>
       <c r="G161" t="n">
-        <v>2.66496753692627</v>
+        <v>2.66496777534485</v>
       </c>
       <c r="H161" t="n">
         <v>161383</v>
@@ -5067,7 +5067,7 @@
         <v>4.01200008392334</v>
       </c>
       <c r="G162" t="n">
-        <v>2.65702056884766</v>
+        <v>2.65702033042908</v>
       </c>
       <c r="H162" t="n">
         <v>133837</v>
@@ -5154,7 +5154,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G165" t="n">
-        <v>2.67159032821655</v>
+        <v>2.67159056663513</v>
       </c>
       <c r="H165" t="n">
         <v>235127</v>
@@ -5183,7 +5183,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.66231822967529</v>
+        <v>2.66231870651245</v>
       </c>
       <c r="H166" t="n">
         <v>89589</v>
@@ -5270,7 +5270,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6186089515686</v>
+        <v>2.61860871315002</v>
       </c>
       <c r="H169" t="n">
         <v>113605</v>
@@ -5299,7 +5299,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G170" t="n">
-        <v>2.56562733650208</v>
+        <v>2.56562781333923</v>
       </c>
       <c r="H170" t="n">
         <v>215835</v>
@@ -5357,7 +5357,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.6358277797699</v>
+        <v>2.63582801818848</v>
       </c>
       <c r="H172" t="n">
         <v>149122</v>
@@ -5415,7 +5415,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G174" t="n">
-        <v>2.57754826545715</v>
+        <v>2.57754874229431</v>
       </c>
       <c r="H174" t="n">
         <v>111504</v>
@@ -5589,7 +5589,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G180" t="n">
-        <v>2.43979668617249</v>
+        <v>2.43979620933533</v>
       </c>
       <c r="H180" t="n">
         <v>95436</v>
@@ -5676,7 +5676,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40270924568176</v>
+        <v>2.40270948410034</v>
       </c>
       <c r="H183" t="n">
         <v>219710</v>
@@ -5705,7 +5705,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G184" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H184" t="n">
         <v>131854</v>
@@ -5821,7 +5821,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G188" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078855514526</v>
       </c>
       <c r="H188" t="n">
         <v>97323</v>
@@ -5850,7 +5850,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G189" t="n">
-        <v>2.27820301055908</v>
+        <v>2.27820324897766</v>
       </c>
       <c r="H189" t="n">
         <v>134521</v>
@@ -5879,7 +5879,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G190" t="n">
-        <v>2.27290463447571</v>
+        <v>2.27290487289429</v>
       </c>
       <c r="H190" t="n">
         <v>106587</v>
@@ -5908,7 +5908,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G191" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H191" t="n">
         <v>98350</v>
@@ -5995,7 +5995,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G194" t="n">
-        <v>2.2861499786377</v>
+        <v>2.28615021705627</v>
       </c>
       <c r="H194" t="n">
         <v>121567</v>
@@ -6082,7 +6082,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>2.42655110359192</v>
+        <v>2.42655086517334</v>
       </c>
       <c r="H197" t="n">
         <v>94547</v>
@@ -6111,7 +6111,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G198" t="n">
-        <v>2.36959600448608</v>
+        <v>2.36959624290466</v>
       </c>
       <c r="H198" t="n">
         <v>64077</v>
@@ -6140,7 +6140,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G199" t="n">
-        <v>2.39078879356384</v>
+        <v>2.39078855514526</v>
       </c>
       <c r="H199" t="n">
         <v>102816</v>
@@ -6169,7 +6169,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G200" t="n">
-        <v>2.39741134643555</v>
+        <v>2.39741110801697</v>
       </c>
       <c r="H200" t="n">
         <v>83817</v>
@@ -6198,7 +6198,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H201" t="n">
         <v>67052</v>
@@ -6285,7 +6285,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>2.42655110359192</v>
+        <v>2.42655086517334</v>
       </c>
       <c r="H204" t="n">
         <v>55166</v>
@@ -6343,7 +6343,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G206" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337433815002</v>
       </c>
       <c r="H206" t="n">
         <v>103757</v>
@@ -6372,7 +6372,7 @@
         <v>3.70600008964539</v>
       </c>
       <c r="G207" t="n">
-        <v>2.45436668395996</v>
+        <v>2.45436644554138</v>
       </c>
       <c r="H207" t="n">
         <v>152563</v>
@@ -6459,7 +6459,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G210" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H210" t="n">
         <v>57237</v>
@@ -6633,7 +6633,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>2.5444347858429</v>
+        <v>2.54443502426147</v>
       </c>
       <c r="H216" t="n">
         <v>93617</v>
@@ -6691,7 +6691,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G218" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264572143555</v>
       </c>
       <c r="H218" t="n">
         <v>53331</v>
@@ -6720,7 +6720,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G219" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H219" t="n">
         <v>63266</v>
@@ -6778,7 +6778,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G221" t="n">
-        <v>2.46496272087097</v>
+        <v>2.46496248245239</v>
       </c>
       <c r="H221" t="n">
         <v>80797</v>
@@ -6836,7 +6836,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G223" t="n">
-        <v>2.45171737670898</v>
+        <v>2.45171713829041</v>
       </c>
       <c r="H223" t="n">
         <v>48476</v>
@@ -6894,7 +6894,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>2.38416576385498</v>
+        <v>2.38416600227356</v>
       </c>
       <c r="H225" t="n">
         <v>57912</v>
@@ -6952,7 +6952,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.33780694007874</v>
+        <v>2.33780717849731</v>
       </c>
       <c r="H227" t="n">
         <v>189301</v>
@@ -6981,7 +6981,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.33780694007874</v>
+        <v>2.33780717849731</v>
       </c>
       <c r="H228" t="n">
         <v>112606</v>
@@ -7010,7 +7010,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G229" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H229" t="n">
         <v>112233</v>
@@ -7039,7 +7039,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G230" t="n">
-        <v>2.24508953094482</v>
+        <v>2.2450897693634</v>
       </c>
       <c r="H230" t="n">
         <v>154519</v>
@@ -7068,7 +7068,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G231" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H231" t="n">
         <v>105323</v>
@@ -7097,7 +7097,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G232" t="n">
-        <v>2.26098370552063</v>
+        <v>2.26098418235779</v>
       </c>
       <c r="H232" t="n">
         <v>54749</v>
@@ -7184,7 +7184,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G235" t="n">
-        <v>2.22389721870422</v>
+        <v>2.22389698028564</v>
       </c>
       <c r="H235" t="n">
         <v>107495</v>
@@ -7213,7 +7213,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G236" t="n">
-        <v>2.2530369758606</v>
+        <v>2.25303673744202</v>
       </c>
       <c r="H236" t="n">
         <v>166280</v>
@@ -7242,7 +7242,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G237" t="n">
-        <v>2.28482604026794</v>
+        <v>2.28482580184937</v>
       </c>
       <c r="H237" t="n">
         <v>48104</v>
@@ -7271,7 +7271,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>2.18548560142517</v>
+        <v>2.18548536300659</v>
       </c>
       <c r="H238" t="n">
         <v>189002</v>
@@ -7329,7 +7329,7 @@
         <v>3.55200004577637</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35237717628479</v>
+        <v>2.35237693786621</v>
       </c>
       <c r="H240" t="n">
         <v>374448</v>
@@ -7358,7 +7358,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H241" t="n">
         <v>218337</v>
@@ -7387,7 +7387,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>2.39608693122864</v>
+        <v>2.39608716964722</v>
       </c>
       <c r="H242" t="n">
         <v>275325</v>
@@ -7474,7 +7474,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G245" t="n">
-        <v>2.44774389266968</v>
+        <v>2.4477436542511</v>
       </c>
       <c r="H245" t="n">
         <v>152191</v>
@@ -7503,7 +7503,7 @@
         <v>3.69799995422363</v>
       </c>
       <c r="G246" t="n">
-        <v>2.44906806945801</v>
+        <v>2.44906783103943</v>
       </c>
       <c r="H246" t="n">
         <v>149566</v>
@@ -7561,7 +7561,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.46893644332886</v>
+        <v>2.46893620491028</v>
       </c>
       <c r="H248" t="n">
         <v>101059</v>
@@ -7764,7 +7764,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G255" t="n">
-        <v>2.50734782218933</v>
+        <v>2.50734806060791</v>
       </c>
       <c r="H255" t="n">
         <v>71140</v>
@@ -7822,7 +7822,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G257" t="n">
-        <v>2.52324247360229</v>
+        <v>2.52324223518372</v>
       </c>
       <c r="H257" t="n">
         <v>138168</v>
@@ -7909,7 +7909,7 @@
         <v>3.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>2.50734782218933</v>
+        <v>2.50734806060791</v>
       </c>
       <c r="H260" t="n">
         <v>231873</v>
@@ -7938,7 +7938,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G261" t="n">
-        <v>2.53251385688782</v>
+        <v>2.5325140953064</v>
       </c>
       <c r="H261" t="n">
         <v>223968</v>
@@ -7996,7 +7996,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G263" t="n">
-        <v>2.51264619827271</v>
+        <v>2.51264572143555</v>
       </c>
       <c r="H263" t="n">
         <v>153807</v>
@@ -8112,7 +8112,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G267" t="n">
-        <v>2.50337409973145</v>
+        <v>2.50337433815002</v>
       </c>
       <c r="H267" t="n">
         <v>244491</v>
@@ -8141,7 +8141,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>2.5364875793457</v>
+        <v>2.53648734092712</v>
       </c>
       <c r="H268" t="n">
         <v>422771</v>
@@ -8170,7 +8170,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>2.56960105895996</v>
+        <v>2.56960129737854</v>
       </c>
       <c r="H269" t="n">
         <v>280634</v>
@@ -8228,7 +8228,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G271" t="n">
-        <v>2.56165361404419</v>
+        <v>2.56165385246277</v>
       </c>
       <c r="H271" t="n">
         <v>288062</v>
@@ -8315,7 +8315,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G274" t="n">
-        <v>2.50072503089905</v>
+        <v>2.50072526931763</v>
       </c>
       <c r="H274" t="n">
         <v>488841</v>
@@ -8344,7 +8344,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G275" t="n">
-        <v>2.4636378288269</v>
+        <v>2.46363806724548</v>
       </c>
       <c r="H275" t="n">
         <v>198253</v>
@@ -8402,7 +8402,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G277" t="n">
-        <v>2.4239022731781</v>
+        <v>2.42390203475952</v>
       </c>
       <c r="H277" t="n">
         <v>129770</v>
@@ -8431,7 +8431,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G278" t="n">
-        <v>2.40138459205627</v>
+        <v>2.40138483047485</v>
       </c>
       <c r="H278" t="n">
         <v>362112</v>
@@ -8460,7 +8460,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>2.37092041969299</v>
+        <v>2.37092065811157</v>
       </c>
       <c r="H279" t="n">
         <v>309995</v>
@@ -8489,7 +8489,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G280" t="n">
-        <v>2.37356948852539</v>
+        <v>2.37356972694397</v>
       </c>
       <c r="H280" t="n">
         <v>114037</v>
@@ -8576,7 +8576,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G283" t="n">
-        <v>2.38019227981567</v>
+        <v>2.38019251823425</v>
       </c>
       <c r="H283" t="n">
         <v>99628</v>
@@ -8692,7 +8692,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G287" t="n">
-        <v>2.32191276550293</v>
+        <v>2.32191300392151</v>
       </c>
       <c r="H287" t="n">
         <v>77908</v>
@@ -8721,7 +8721,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G288" t="n">
-        <v>2.32985973358154</v>
+        <v>2.32985997200012</v>
       </c>
       <c r="H288" t="n">
         <v>130996</v>
@@ -8750,7 +8750,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G289" t="n">
-        <v>2.35502600669861</v>
+        <v>2.35502576828003</v>
       </c>
       <c r="H289" t="n">
         <v>119547</v>
@@ -8779,7 +8779,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G290" t="n">
-        <v>2.39476251602173</v>
+        <v>2.39476227760315</v>
       </c>
       <c r="H290" t="n">
         <v>374020</v>
@@ -8837,7 +8837,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G292" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H292" t="n">
         <v>129497</v>
@@ -8866,7 +8866,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G293" t="n">
-        <v>2.40006065368652</v>
+        <v>2.40006041526794</v>
       </c>
       <c r="H293" t="n">
         <v>70534</v>
@@ -8895,7 +8895,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G294" t="n">
-        <v>2.37886762619019</v>
+        <v>2.37886786460876</v>
       </c>
       <c r="H294" t="n">
         <v>84182</v>
@@ -8924,7 +8924,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.40403437614441</v>
+        <v>2.40403389930725</v>
       </c>
       <c r="H295" t="n">
         <v>126484</v>
@@ -8953,7 +8953,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G296" t="n">
-        <v>2.35767531394958</v>
+        <v>2.35767507553101</v>
       </c>
       <c r="H296" t="n">
         <v>190410</v>
@@ -8982,7 +8982,7 @@
         <v>3.48799991607666</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30999207496643</v>
+        <v>2.30999183654785</v>
       </c>
       <c r="H297" t="n">
         <v>327861</v>
@@ -9040,7 +9040,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G299" t="n">
-        <v>2.36429762840271</v>
+        <v>2.36429786682129</v>
       </c>
       <c r="H299" t="n">
         <v>92767</v>
@@ -9069,7 +9069,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G300" t="n">
-        <v>2.40933227539062</v>
+        <v>2.40933203697205</v>
       </c>
       <c r="H300" t="n">
         <v>154051</v>
@@ -9098,7 +9098,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G301" t="n">
-        <v>2.49807620048523</v>
+        <v>2.49807596206665</v>
       </c>
       <c r="H301" t="n">
         <v>292122</v>
@@ -9272,7 +9272,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G307" t="n">
-        <v>2.57622361183167</v>
+        <v>2.57622408866882</v>
       </c>
       <c r="H307" t="n">
         <v>428054</v>
@@ -9301,7 +9301,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G308" t="n">
-        <v>2.60006523132324</v>
+        <v>2.60006546974182</v>
       </c>
       <c r="H308" t="n">
         <v>263459</v>
@@ -9330,7 +9330,7 @@
         <v>3.91400003433228</v>
       </c>
       <c r="G309" t="n">
-        <v>2.59211850166321</v>
+        <v>2.59211826324463</v>
       </c>
       <c r="H309" t="n">
         <v>248866</v>
@@ -9388,7 +9388,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63185453414917</v>
+        <v>2.63185429573059</v>
       </c>
       <c r="H311" t="n">
         <v>305933</v>
@@ -9446,7 +9446,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G313" t="n">
-        <v>2.71529984474182</v>
+        <v>2.71529960632324</v>
       </c>
       <c r="H313" t="n">
         <v>428736</v>
@@ -9533,7 +9533,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G316" t="n">
-        <v>2.93252420425415</v>
+        <v>2.93252372741699</v>
       </c>
       <c r="H316" t="n">
         <v>857622</v>
@@ -9562,7 +9562,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G317" t="n">
-        <v>3.0649778842926</v>
+        <v>3.06497740745544</v>
       </c>
       <c r="H317" t="n">
         <v>1978795</v>
@@ -9620,7 +9620,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>2.94709420204163</v>
+        <v>2.94709396362305</v>
       </c>
       <c r="H319" t="n">
         <v>973140</v>
@@ -9649,7 +9649,7 @@
         <v>4.30200004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>2.84907793998718</v>
+        <v>2.84907817840576</v>
       </c>
       <c r="H320" t="n">
         <v>786928</v>
@@ -9678,7 +9678,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G321" t="n">
-        <v>2.86099910736084</v>
+        <v>2.86099934577942</v>
       </c>
       <c r="H321" t="n">
         <v>648156</v>
@@ -9707,7 +9707,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G322" t="n">
-        <v>2.94444513320923</v>
+        <v>2.94444489479065</v>
       </c>
       <c r="H322" t="n">
         <v>480186</v>
@@ -9765,7 +9765,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G324" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H324" t="n">
         <v>228643</v>
@@ -9794,7 +9794,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G325" t="n">
-        <v>2.99212837219238</v>
+        <v>2.9921281337738</v>
       </c>
       <c r="H325" t="n">
         <v>565930</v>
@@ -9823,7 +9823,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G326" t="n">
-        <v>2.9947772026062</v>
+        <v>2.99477696418762</v>
       </c>
       <c r="H326" t="n">
         <v>373530</v>
@@ -9852,7 +9852,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G327" t="n">
-        <v>3.04510974884033</v>
+        <v>3.04510998725891</v>
       </c>
       <c r="H327" t="n">
         <v>348998</v>
@@ -9910,7 +9910,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G329" t="n">
-        <v>3.03848695755005</v>
+        <v>3.03848671913147</v>
       </c>
       <c r="H329" t="n">
         <v>242448</v>
@@ -9939,7 +9939,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G330" t="n">
-        <v>3.0040488243103</v>
+        <v>3.00404906272888</v>
       </c>
       <c r="H330" t="n">
         <v>261526</v>
@@ -9968,7 +9968,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G331" t="n">
-        <v>2.95504140853882</v>
+        <v>2.95504093170166</v>
       </c>
       <c r="H331" t="n">
         <v>188931</v>
@@ -10026,7 +10026,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G333" t="n">
-        <v>2.97093605995178</v>
+        <v>2.97093534469604</v>
       </c>
       <c r="H333" t="n">
         <v>261603</v>
@@ -10055,7 +10055,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>2.92722582817078</v>
+        <v>2.92722606658936</v>
       </c>
       <c r="H334" t="n">
         <v>171240</v>
@@ -10142,7 +10142,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H337" t="n">
         <v>335332</v>
@@ -10171,7 +10171,7 @@
         <v>4.5460000038147</v>
       </c>
       <c r="G338" t="n">
-        <v>3.01067185401917</v>
+        <v>3.01067233085632</v>
       </c>
       <c r="H338" t="n">
         <v>333907</v>
@@ -10229,7 +10229,7 @@
         <v>4.5</v>
       </c>
       <c r="G340" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H340" t="n">
         <v>224232</v>
@@ -10287,7 +10287,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G342" t="n">
-        <v>3.09146881103516</v>
+        <v>3.09146857261658</v>
       </c>
       <c r="H342" t="n">
         <v>699107</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.08484554290771</v>
+        <v>3.08484625816345</v>
       </c>
       <c r="H344" t="n">
         <v>309892</v>
@@ -10374,7 +10374,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G345" t="n">
-        <v>3.10471391677856</v>
+        <v>3.10471439361572</v>
       </c>
       <c r="H345" t="n">
         <v>353071</v>
@@ -10403,7 +10403,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G346" t="n">
-        <v>3.15637063980103</v>
+        <v>3.1563708782196</v>
       </c>
       <c r="H346" t="n">
         <v>987482</v>
@@ -10432,7 +10432,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>3.11928367614746</v>
+        <v>3.11928391456604</v>
       </c>
       <c r="H347" t="n">
         <v>289662</v>
@@ -10461,7 +10461,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>3.00669836997986</v>
+        <v>3.0066978931427</v>
       </c>
       <c r="H348" t="n">
         <v>392406</v>
@@ -10548,7 +10548,7 @@
         <v>4.5</v>
       </c>
       <c r="G351" t="n">
-        <v>2.98020768165588</v>
+        <v>2.9802074432373</v>
       </c>
       <c r="H351" t="n">
         <v>622537</v>
@@ -10577,7 +10577,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G352" t="n">
-        <v>2.87159514427185</v>
+        <v>2.87159538269043</v>
       </c>
       <c r="H352" t="n">
         <v>379734</v>
@@ -10606,7 +10606,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G353" t="n">
-        <v>2.84775400161743</v>
+        <v>2.84775376319885</v>
       </c>
       <c r="H353" t="n">
         <v>660590</v>
@@ -10635,7 +10635,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G354" t="n">
-        <v>2.93782210350037</v>
+        <v>2.93782234191895</v>
       </c>
       <c r="H354" t="n">
         <v>462237</v>
@@ -10722,7 +10722,7 @@
         <v>4.31799983978271</v>
       </c>
       <c r="G357" t="n">
-        <v>2.8922746181488</v>
+        <v>2.89227414131165</v>
       </c>
       <c r="H357" t="n">
         <v>254418</v>
@@ -10751,7 +10751,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G358" t="n">
-        <v>2.91772747039795</v>
+        <v>2.91772794723511</v>
       </c>
       <c r="H358" t="n">
         <v>201245</v>
@@ -10809,7 +10809,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G360" t="n">
-        <v>2.89093494415283</v>
+        <v>2.89093470573425</v>
       </c>
       <c r="H360" t="n">
         <v>173469</v>
@@ -10838,7 +10838,7 @@
         <v>4.32800006866455</v>
       </c>
       <c r="G361" t="n">
-        <v>2.89897274971008</v>
+        <v>2.89897298812866</v>
       </c>
       <c r="H361" t="n">
         <v>217176</v>
@@ -10867,7 +10867,7 @@
         <v>4.26200008392334</v>
       </c>
       <c r="G362" t="n">
-        <v>2.85476469993591</v>
+        <v>2.85476493835449</v>
       </c>
       <c r="H362" t="n">
         <v>288132</v>
@@ -10925,7 +10925,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>2.8333306312561</v>
+        <v>2.83333086967468</v>
       </c>
       <c r="H364" t="n">
         <v>80574</v>
@@ -10983,7 +10983,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G366" t="n">
-        <v>2.79448127746582</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H366" t="n">
         <v>170095</v>
@@ -11012,7 +11012,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G367" t="n">
-        <v>2.76768851280212</v>
+        <v>2.76768827438354</v>
       </c>
       <c r="H367" t="n">
         <v>132754</v>
@@ -11041,7 +11041,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G368" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H368" t="n">
         <v>291905</v>
@@ -11070,7 +11070,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G369" t="n">
-        <v>2.66989493370056</v>
+        <v>2.66989517211914</v>
       </c>
       <c r="H369" t="n">
         <v>430652</v>
@@ -11099,7 +11099,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>2.69936728477478</v>
+        <v>2.6993670463562</v>
       </c>
       <c r="H370" t="n">
         <v>299134</v>
@@ -11186,7 +11186,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G373" t="n">
-        <v>2.64846062660217</v>
+        <v>2.64846086502075</v>
       </c>
       <c r="H373" t="n">
         <v>468185</v>
@@ -11273,7 +11273,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G376" t="n">
-        <v>2.66721606254578</v>
+        <v>2.6672158241272</v>
       </c>
       <c r="H376" t="n">
         <v>295268</v>
@@ -11302,7 +11302,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H377" t="n">
         <v>218952</v>
@@ -11331,7 +11331,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G378" t="n">
-        <v>2.65649890899658</v>
+        <v>2.656498670578</v>
       </c>
       <c r="H378" t="n">
         <v>194294</v>
@@ -11418,7 +11418,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G381" t="n">
-        <v>2.64846062660217</v>
+        <v>2.64846086502075</v>
       </c>
       <c r="H381" t="n">
         <v>281322</v>
@@ -11447,7 +11447,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G382" t="n">
-        <v>2.62568712234497</v>
+        <v>2.62568664550781</v>
       </c>
       <c r="H382" t="n">
         <v>194044</v>
@@ -11476,7 +11476,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G383" t="n">
-        <v>2.59621477127075</v>
+        <v>2.59621500968933</v>
       </c>
       <c r="H383" t="n">
         <v>275930</v>
@@ -11505,7 +11505,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G384" t="n">
-        <v>2.56942248344421</v>
+        <v>2.56942200660706</v>
       </c>
       <c r="H384" t="n">
         <v>134122</v>
@@ -11592,7 +11592,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G387" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H387" t="n">
         <v>168180</v>
@@ -11650,7 +11650,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G389" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H389" t="n">
         <v>213962</v>
@@ -11679,7 +11679,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G390" t="n">
-        <v>2.5654034614563</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H390" t="n">
         <v>82927</v>
@@ -11708,7 +11708,7 @@
         <v>3.81200003623962</v>
       </c>
       <c r="G391" t="n">
-        <v>2.55334687232971</v>
+        <v>2.55334663391113</v>
       </c>
       <c r="H391" t="n">
         <v>152367</v>
@@ -11737,7 +11737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H392" t="n">
         <v>689944</v>
@@ -11824,7 +11824,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G395" t="n">
-        <v>2.71946120262146</v>
+        <v>2.71946144104004</v>
       </c>
       <c r="H395" t="n">
         <v>107839</v>
@@ -11882,7 +11882,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G397" t="n">
-        <v>2.63238501548767</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H397" t="n">
         <v>178710</v>
@@ -11940,7 +11940,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G399" t="n">
-        <v>2.60693192481995</v>
+        <v>2.6069324016571</v>
       </c>
       <c r="H399" t="n">
         <v>99666</v>
@@ -12027,7 +12027,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H402" t="n">
         <v>129322</v>
@@ -12085,7 +12085,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G404" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H404" t="n">
         <v>112728</v>
@@ -12114,7 +12114,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G405" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H405" t="n">
         <v>195865</v>
@@ -12143,7 +12143,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G406" t="n">
-        <v>2.6538188457489</v>
+        <v>2.65381908416748</v>
       </c>
       <c r="H406" t="n">
         <v>110887</v>
@@ -12172,7 +12172,7 @@
         <v>3.9760000705719</v>
       </c>
       <c r="G407" t="n">
-        <v>2.66319680213928</v>
+        <v>2.66319704055786</v>
       </c>
       <c r="H407" t="n">
         <v>149523</v>
@@ -12259,7 +12259,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G410" t="n">
-        <v>2.66721606254578</v>
+        <v>2.6672158241272</v>
       </c>
       <c r="H410" t="n">
         <v>74641</v>
@@ -12317,7 +12317,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G412" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H412" t="n">
         <v>148944</v>
@@ -12375,7 +12375,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H414" t="n">
         <v>196816</v>
@@ -12404,7 +12404,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G415" t="n">
-        <v>2.56138443946838</v>
+        <v>2.56138467788696</v>
       </c>
       <c r="H415" t="n">
         <v>116446</v>
@@ -12433,7 +12433,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G416" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H416" t="n">
         <v>50142</v>
@@ -12462,7 +12462,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G417" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H417" t="n">
         <v>103218</v>
@@ -12520,7 +12520,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G419" t="n">
-        <v>2.53459191322327</v>
+        <v>2.53459167480469</v>
       </c>
       <c r="H419" t="n">
         <v>215549</v>
@@ -12578,7 +12578,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H421" t="n">
         <v>130865</v>
@@ -12607,7 +12607,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G422" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H422" t="n">
         <v>133276</v>
@@ -12839,7 +12839,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G430" t="n">
-        <v>2.55200672149658</v>
+        <v>2.55200719833374</v>
       </c>
       <c r="H430" t="n">
         <v>130300</v>
@@ -12868,7 +12868,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G431" t="n">
-        <v>2.58951663970947</v>
+        <v>2.58951687812805</v>
       </c>
       <c r="H431" t="n">
         <v>117425</v>
@@ -12897,7 +12897,7 @@
         <v>3.89800000190735</v>
       </c>
       <c r="G432" t="n">
-        <v>2.61095070838928</v>
+        <v>2.61095094680786</v>
       </c>
       <c r="H432" t="n">
         <v>63021</v>
@@ -12926,7 +12926,7 @@
         <v>4.05600023269653</v>
       </c>
       <c r="G433" t="n">
-        <v>2.71678233146667</v>
+        <v>2.71678256988525</v>
       </c>
       <c r="H433" t="n">
         <v>449341</v>
@@ -12984,7 +12984,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H435" t="n">
         <v>606578</v>
@@ -13013,7 +13013,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85342526435852</v>
+        <v>2.8534255027771</v>
       </c>
       <c r="H436" t="n">
         <v>325483</v>
@@ -13042,7 +13042,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G437" t="n">
-        <v>2.88691592216492</v>
+        <v>2.8869161605835</v>
       </c>
       <c r="H437" t="n">
         <v>435459</v>
@@ -13100,7 +13100,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G439" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H439" t="n">
         <v>359505</v>
@@ -13158,7 +13158,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G441" t="n">
-        <v>2.91504883766174</v>
+        <v>2.91504836082458</v>
       </c>
       <c r="H441" t="n">
         <v>331954</v>
@@ -13187,7 +13187,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>2.88021802902222</v>
+        <v>2.88021779060364</v>
       </c>
       <c r="H442" t="n">
         <v>440312</v>
@@ -13216,7 +13216,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G443" t="n">
-        <v>2.84136843681335</v>
+        <v>2.84136867523193</v>
       </c>
       <c r="H443" t="n">
         <v>279165</v>
@@ -13274,7 +13274,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G445" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682152748108</v>
       </c>
       <c r="H445" t="n">
         <v>208778</v>
@@ -13303,7 +13303,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>2.81323599815369</v>
+        <v>2.81323575973511</v>
       </c>
       <c r="H446" t="n">
         <v>218622</v>
@@ -13332,7 +13332,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G447" t="n">
-        <v>2.85744380950928</v>
+        <v>2.85744404792786</v>
       </c>
       <c r="H447" t="n">
         <v>204402</v>
@@ -13361,7 +13361,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G448" t="n">
-        <v>2.86682176589966</v>
+        <v>2.86682152748108</v>
       </c>
       <c r="H448" t="n">
         <v>119126</v>
@@ -13419,7 +13419,7 @@
         <v>4.17199993133545</v>
       </c>
       <c r="G450" t="n">
-        <v>2.79448127746582</v>
+        <v>2.79448103904724</v>
       </c>
       <c r="H450" t="n">
         <v>261468</v>
@@ -13448,7 +13448,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H451" t="n">
         <v>306011</v>
@@ -13477,7 +13477,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G452" t="n">
-        <v>2.74625420570374</v>
+        <v>2.74625396728516</v>
       </c>
       <c r="H452" t="n">
         <v>174105</v>
@@ -13593,7 +13593,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G456" t="n">
-        <v>2.95523762702942</v>
+        <v>2.95523738861084</v>
       </c>
       <c r="H456" t="n">
         <v>621450</v>
@@ -13622,7 +13622,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G457" t="n">
-        <v>2.90567111968994</v>
+        <v>2.90567064285278</v>
       </c>
       <c r="H457" t="n">
         <v>257517</v>
@@ -13680,7 +13680,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G459" t="n">
-        <v>2.88691592216492</v>
+        <v>2.8869161605835</v>
       </c>
       <c r="H459" t="n">
         <v>240063</v>
@@ -13709,7 +13709,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>2.8400285243988</v>
+        <v>2.84002876281738</v>
       </c>
       <c r="H460" t="n">
         <v>234215</v>
@@ -13738,7 +13738,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G461" t="n">
-        <v>2.86280250549316</v>
+        <v>2.86280274391174</v>
       </c>
       <c r="H461" t="n">
         <v>278042</v>
@@ -13825,7 +13825,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>2.93916201591492</v>
+        <v>2.93916177749634</v>
       </c>
       <c r="H464" t="n">
         <v>296201</v>
@@ -13883,7 +13883,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>2.94720005989075</v>
+        <v>2.94719982147217</v>
       </c>
       <c r="H466" t="n">
         <v>276862</v>
@@ -13999,7 +13999,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>2.91370868682861</v>
+        <v>2.91370844841003</v>
       </c>
       <c r="H470" t="n">
         <v>103518</v>
@@ -14028,7 +14028,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G471" t="n">
-        <v>2.93648266792297</v>
+        <v>2.93648242950439</v>
       </c>
       <c r="H471" t="n">
         <v>136035</v>
@@ -14057,7 +14057,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G472" t="n">
-        <v>2.93246364593506</v>
+        <v>2.93246388435364</v>
       </c>
       <c r="H472" t="n">
         <v>142444</v>
@@ -14144,7 +14144,7 @@
         <v>4.30800008773804</v>
       </c>
       <c r="G475" t="n">
-        <v>2.8855767250061</v>
+        <v>2.88557696342468</v>
       </c>
       <c r="H475" t="n">
         <v>113109</v>
@@ -14173,7 +14173,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90031266212463</v>
+        <v>2.90031218528748</v>
       </c>
       <c r="H476" t="n">
         <v>293657</v>
@@ -14202,7 +14202,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>2.88021802902222</v>
+        <v>2.88021779060364</v>
       </c>
       <c r="H477" t="n">
         <v>371178</v>
@@ -14231,7 +14231,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G478" t="n">
-        <v>2.84270811080933</v>
+        <v>2.84270834922791</v>
       </c>
       <c r="H478" t="n">
         <v>266545</v>
@@ -14260,7 +14260,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G479" t="n">
-        <v>2.79314184188843</v>
+        <v>2.79314160346985</v>
       </c>
       <c r="H479" t="n">
         <v>317272</v>
@@ -14289,7 +14289,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G480" t="n">
-        <v>2.76233005523682</v>
+        <v>2.76232981681824</v>
       </c>
       <c r="H480" t="n">
         <v>456143</v>
@@ -14318,7 +14318,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G481" t="n">
-        <v>2.6404230594635</v>
+        <v>2.64042282104492</v>
       </c>
       <c r="H481" t="n">
         <v>1595732</v>
@@ -14405,7 +14405,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G484" t="n">
-        <v>2.62300777435303</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H484" t="n">
         <v>183394</v>
@@ -14434,7 +14434,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G485" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H485" t="n">
         <v>239693</v>
@@ -14463,7 +14463,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G486" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H486" t="n">
         <v>174243</v>
@@ -14492,7 +14492,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G487" t="n">
-        <v>2.63238501548767</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H487" t="n">
         <v>257416</v>
@@ -14550,7 +14550,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G489" t="n">
-        <v>2.59487533569336</v>
+        <v>2.59487557411194</v>
       </c>
       <c r="H489" t="n">
         <v>256882</v>
@@ -14608,7 +14608,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69266867637634</v>
+        <v>2.69266891479492</v>
       </c>
       <c r="H491" t="n">
         <v>413905</v>
@@ -14666,7 +14666,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G493" t="n">
-        <v>2.63908314704895</v>
+        <v>2.63908338546753</v>
       </c>
       <c r="H493" t="n">
         <v>248344</v>
@@ -14695,7 +14695,7 @@
         <v>3.95600008964539</v>
       </c>
       <c r="G494" t="n">
-        <v>2.64980053901672</v>
+        <v>2.6498007774353</v>
       </c>
       <c r="H494" t="n">
         <v>168528</v>
@@ -14724,7 +14724,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>2.67525362968445</v>
+        <v>2.67525339126587</v>
       </c>
       <c r="H495" t="n">
         <v>459746</v>
@@ -14753,7 +14753,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.63238501548767</v>
+        <v>2.63238525390625</v>
       </c>
       <c r="H496" t="n">
         <v>159188</v>
@@ -14782,7 +14782,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G497" t="n">
-        <v>2.62970614433289</v>
+        <v>2.62970590591431</v>
       </c>
       <c r="H497" t="n">
         <v>169752</v>
@@ -14811,7 +14811,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.624347448349</v>
+        <v>2.62434720993042</v>
       </c>
       <c r="H498" t="n">
         <v>109452</v>
@@ -14840,7 +14840,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>2.71276330947876</v>
+        <v>2.71276354789734</v>
       </c>
       <c r="H499" t="n">
         <v>464341</v>
@@ -14869,7 +14869,7 @@
         <v>3.91599988937378</v>
       </c>
       <c r="G500" t="n">
-        <v>2.62300777435303</v>
+        <v>2.62300753593445</v>
       </c>
       <c r="H500" t="n">
         <v>412188</v>
@@ -14898,7 +14898,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H501" t="n">
         <v>511482</v>
@@ -14927,7 +14927,7 @@
         <v>3.82399988174438</v>
       </c>
       <c r="G502" t="n">
-        <v>2.56138443946838</v>
+        <v>2.56138467788696</v>
       </c>
       <c r="H502" t="n">
         <v>215962</v>
@@ -14956,7 +14956,7 @@
         <v>3.84200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>2.57344126701355</v>
+        <v>2.57344150543213</v>
       </c>
       <c r="H503" t="n">
         <v>442866</v>
@@ -14985,7 +14985,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H504" t="n">
         <v>308246</v>
@@ -15043,7 +15043,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H506" t="n">
         <v>188484</v>
@@ -15072,7 +15072,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G507" t="n">
-        <v>2.53325200080872</v>
+        <v>2.53325223922729</v>
       </c>
       <c r="H507" t="n">
         <v>155274</v>
@@ -15101,7 +15101,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G508" t="n">
-        <v>2.53057289123535</v>
+        <v>2.53057312965393</v>
       </c>
       <c r="H508" t="n">
         <v>166223</v>
@@ -15130,7 +15130,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G509" t="n">
-        <v>2.51449728012085</v>
+        <v>2.51449704170227</v>
       </c>
       <c r="H509" t="n">
         <v>151770</v>
@@ -15159,7 +15159,7 @@
         <v>3.76399993896484</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52119517326355</v>
+        <v>2.52119541168213</v>
       </c>
       <c r="H510" t="n">
         <v>181112</v>
@@ -15217,7 +15217,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G512" t="n">
-        <v>2.46894955635071</v>
+        <v>2.46894979476929</v>
       </c>
       <c r="H512" t="n">
         <v>202096</v>
@@ -15304,7 +15304,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H515" t="n">
         <v>481721</v>
@@ -15333,7 +15333,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G516" t="n">
-        <v>2.58884692192078</v>
+        <v>2.58884716033936</v>
       </c>
       <c r="H516" t="n">
         <v>358297</v>
@@ -15362,7 +15362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G517" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H517" t="n">
         <v>342428</v>
@@ -15449,7 +15449,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.54530906677246</v>
+        <v>2.54530882835388</v>
       </c>
       <c r="H520" t="n">
         <v>236775</v>
@@ -15507,7 +15507,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>2.51516723632812</v>
+        <v>2.5151674747467</v>
       </c>
       <c r="H522" t="n">
         <v>216962</v>
@@ -15536,7 +15536,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>2.5386106967926</v>
+        <v>2.53861045837402</v>
       </c>
       <c r="H523" t="n">
         <v>500528</v>
@@ -15594,7 +15594,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G525" t="n">
-        <v>2.55870532989502</v>
+        <v>2.55870509147644</v>
       </c>
       <c r="H525" t="n">
         <v>259926</v>
@@ -15623,7 +15623,7 @@
         <v>3.875</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59554529190063</v>
+        <v>2.59554505348206</v>
       </c>
       <c r="H526" t="n">
         <v>245440</v>
@@ -15652,7 +15652,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.64578175544739</v>
+        <v>2.64578151702881</v>
       </c>
       <c r="H527" t="n">
         <v>344329</v>
@@ -15710,7 +15710,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>2.5654034614563</v>
+        <v>2.56540322303772</v>
       </c>
       <c r="H529" t="n">
         <v>213566</v>
@@ -15768,7 +15768,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G531" t="n">
-        <v>2.5754508972168</v>
+        <v>2.57545113563538</v>
       </c>
       <c r="H531" t="n">
         <v>188683</v>
@@ -15826,7 +15826,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G533" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H533" t="n">
         <v>272113</v>
@@ -15855,7 +15855,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51851630210876</v>
+        <v>2.51851606369019</v>
       </c>
       <c r="H534" t="n">
         <v>180644</v>
@@ -15884,7 +15884,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G535" t="n">
-        <v>2.57210159301758</v>
+        <v>2.572101354599</v>
       </c>
       <c r="H535" t="n">
         <v>657310</v>
@@ -15913,7 +15913,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>2.59219598770142</v>
+        <v>2.59219622612</v>
       </c>
       <c r="H536" t="n">
         <v>753926</v>
@@ -16087,7 +16087,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G542" t="n">
-        <v>2.44148683547974</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H542" t="n">
         <v>168325</v>
@@ -16145,7 +16145,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.46827960014343</v>
+        <v>2.46827983856201</v>
       </c>
       <c r="H544" t="n">
         <v>133388</v>
@@ -16464,7 +16464,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G555" t="n">
-        <v>2.20705103874207</v>
+        <v>2.20705080032349</v>
       </c>
       <c r="H555" t="n">
         <v>552453</v>
@@ -16493,7 +16493,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>2.14676713943481</v>
+        <v>2.14676737785339</v>
       </c>
       <c r="H556" t="n">
         <v>427000</v>
@@ -16522,7 +16522,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G557" t="n">
-        <v>2.20705103874207</v>
+        <v>2.20705080032349</v>
       </c>
       <c r="H557" t="n">
         <v>320376</v>
@@ -16638,7 +16638,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.19700312614441</v>
+        <v>2.19700336456299</v>
       </c>
       <c r="H561" t="n">
         <v>269006</v>
@@ -16667,7 +16667,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>2.19365429878235</v>
+        <v>2.19365453720093</v>
       </c>
       <c r="H562" t="n">
         <v>397917</v>
@@ -16696,7 +16696,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G563" t="n">
-        <v>2.13337087631226</v>
+        <v>2.13337063789368</v>
       </c>
       <c r="H563" t="n">
         <v>656760</v>
@@ -16754,7 +16754,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G565" t="n">
-        <v>2.18695640563965</v>
+        <v>2.18695592880249</v>
       </c>
       <c r="H565" t="n">
         <v>2292967</v>
@@ -16783,7 +16783,7 @@
         <v>3.5</v>
       </c>
       <c r="G566" t="n">
-        <v>2.34436368942261</v>
+        <v>2.34436321258545</v>
       </c>
       <c r="H566" t="n">
         <v>1700593</v>
@@ -16841,7 +16841,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G568" t="n">
-        <v>2.27403211593628</v>
+        <v>2.27403259277344</v>
       </c>
       <c r="H568" t="n">
         <v>278538</v>
@@ -16870,7 +16870,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G569" t="n">
-        <v>2.2505886554718</v>
+        <v>2.25058889389038</v>
       </c>
       <c r="H569" t="n">
         <v>201800</v>
@@ -16957,7 +16957,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>2.4113450050354</v>
+        <v>2.41134524345398</v>
       </c>
       <c r="H572" t="n">
         <v>584347</v>
@@ -17044,7 +17044,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G575" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H575" t="n">
         <v>419566</v>
@@ -17102,7 +17102,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G577" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H577" t="n">
         <v>339561</v>
@@ -17189,7 +17189,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G580" t="n">
-        <v>2.44148683547974</v>
+        <v>2.44148707389832</v>
       </c>
       <c r="H580" t="n">
         <v>207497</v>
@@ -17276,7 +17276,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G583" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H583" t="n">
         <v>185158</v>
@@ -17305,7 +17305,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G584" t="n">
-        <v>2.41804337501526</v>
+        <v>2.41804313659668</v>
       </c>
       <c r="H584" t="n">
         <v>89113</v>
@@ -17421,7 +17421,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G588" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832727432251</v>
       </c>
       <c r="H588" t="n">
         <v>131179</v>
@@ -17479,7 +17479,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G590" t="n">
-        <v>2.49172353744507</v>
+        <v>2.49172329902649</v>
       </c>
       <c r="H590" t="n">
         <v>91101</v>
@@ -17508,7 +17508,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G591" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832727432251</v>
       </c>
       <c r="H591" t="n">
         <v>51454</v>
@@ -17624,7 +17624,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G595" t="n">
-        <v>2.50177049636841</v>
+        <v>2.50177073478699</v>
       </c>
       <c r="H595" t="n">
         <v>206947</v>
@@ -17653,7 +17653,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G596" t="n">
-        <v>2.48837423324585</v>
+        <v>2.48837399482727</v>
       </c>
       <c r="H596" t="n">
         <v>218613</v>
@@ -17711,7 +17711,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G598" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832727432251</v>
       </c>
       <c r="H598" t="n">
         <v>111857</v>
@@ -17798,7 +17798,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G601" t="n">
-        <v>2.46493077278137</v>
+        <v>2.46493053436279</v>
       </c>
       <c r="H601" t="n">
         <v>180468</v>
@@ -17827,7 +17827,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.47832679748535</v>
+        <v>2.47832727432251</v>
       </c>
       <c r="H602" t="n">
         <v>187716</v>
@@ -17943,7 +17943,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G606" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H606" t="n">
         <v>447106</v>
@@ -17972,7 +17972,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.23393607139587</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H607" t="n">
         <v>439315</v>
@@ -18001,7 +18001,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>2.26491546630859</v>
+        <v>2.26491522789001</v>
       </c>
       <c r="H608" t="n">
         <v>241172</v>
@@ -18059,7 +18059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.22360992431641</v>
+        <v>2.22361016273499</v>
       </c>
       <c r="H610" t="n">
         <v>258239</v>
@@ -18088,7 +18088,7 @@
         <v>3.25</v>
       </c>
       <c r="G611" t="n">
-        <v>2.23737859725952</v>
+        <v>2.23737835884094</v>
       </c>
       <c r="H611" t="n">
         <v>302598</v>
@@ -18146,7 +18146,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G613" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H613" t="n">
         <v>279124</v>
@@ -18175,7 +18175,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G614" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H614" t="n">
         <v>249358</v>
@@ -18378,7 +18378,7 @@
         <v>3.25</v>
       </c>
       <c r="G621" t="n">
-        <v>2.23737859725952</v>
+        <v>2.23737835884094</v>
       </c>
       <c r="H621" t="n">
         <v>102223</v>
@@ -18436,7 +18436,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G623" t="n">
-        <v>2.24770522117615</v>
+        <v>2.24770474433899</v>
       </c>
       <c r="H623" t="n">
         <v>57699</v>
@@ -18465,7 +18465,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G624" t="n">
-        <v>2.29589486122131</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H624" t="n">
         <v>191609</v>
@@ -18494,7 +18494,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>2.32687377929688</v>
+        <v>2.32687401771545</v>
       </c>
       <c r="H625" t="n">
         <v>147334</v>
@@ -18523,7 +18523,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G626" t="n">
-        <v>2.34408402442932</v>
+        <v>2.34408450126648</v>
       </c>
       <c r="H626" t="n">
         <v>133097</v>
@@ -18581,7 +18581,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>2.39571595191956</v>
+        <v>2.39571619033813</v>
       </c>
       <c r="H628" t="n">
         <v>104749</v>
@@ -18610,7 +18610,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>2.39571595191956</v>
+        <v>2.39571619033813</v>
       </c>
       <c r="H629" t="n">
         <v>232962</v>
@@ -18668,7 +18668,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>2.28212594985962</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H631" t="n">
         <v>206647</v>
@@ -18697,7 +18697,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G632" t="n">
-        <v>2.39915800094604</v>
+        <v>2.39915823936462</v>
       </c>
       <c r="H632" t="n">
         <v>997504</v>
@@ -18726,7 +18726,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G633" t="n">
-        <v>2.36473679542542</v>
+        <v>2.36473703384399</v>
       </c>
       <c r="H633" t="n">
         <v>866249</v>
@@ -18755,7 +18755,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G634" t="n">
-        <v>2.31310486793518</v>
+        <v>2.31310510635376</v>
       </c>
       <c r="H634" t="n">
         <v>291169</v>
@@ -18784,7 +18784,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G635" t="n">
-        <v>2.29933667182922</v>
+        <v>2.29933643341064</v>
       </c>
       <c r="H635" t="n">
         <v>210570</v>
@@ -18813,7 +18813,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27524185180664</v>
+        <v>2.27524209022522</v>
       </c>
       <c r="H636" t="n">
         <v>402407</v>
@@ -18871,7 +18871,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30277919769287</v>
+        <v>2.30277872085571</v>
       </c>
       <c r="H638" t="n">
         <v>143372</v>
@@ -18900,7 +18900,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>2.33719992637634</v>
+        <v>2.33720016479492</v>
       </c>
       <c r="H639" t="n">
         <v>136440</v>
@@ -19016,7 +19016,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>2.29589486122131</v>
+        <v>2.29589438438416</v>
       </c>
       <c r="H643" t="n">
         <v>117183</v>
@@ -19045,7 +19045,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H644" t="n">
         <v>158331</v>
@@ -19161,7 +19161,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G648" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H648" t="n">
         <v>204541</v>
@@ -19190,7 +19190,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G649" t="n">
-        <v>2.19951486587524</v>
+        <v>2.1995153427124</v>
       </c>
       <c r="H649" t="n">
         <v>159276</v>
@@ -19277,7 +19277,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G652" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H652" t="n">
         <v>43938</v>
@@ -19335,7 +19335,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G654" t="n">
-        <v>2.19951486587524</v>
+        <v>2.1995153427124</v>
       </c>
       <c r="H654" t="n">
         <v>79584</v>
@@ -19364,7 +19364,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G655" t="n">
-        <v>2.1444411277771</v>
+        <v>2.14444136619568</v>
       </c>
       <c r="H655" t="n">
         <v>109564</v>
@@ -19393,7 +19393,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H656" t="n">
         <v>94908</v>
@@ -19422,7 +19422,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G657" t="n">
-        <v>2.15820980072021</v>
+        <v>2.15820956230164</v>
       </c>
       <c r="H657" t="n">
         <v>127746</v>
@@ -19451,7 +19451,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G658" t="n">
-        <v>2.22360992431641</v>
+        <v>2.22361016273499</v>
       </c>
       <c r="H658" t="n">
         <v>79691</v>
@@ -19480,7 +19480,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G659" t="n">
-        <v>2.23049449920654</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H659" t="n">
         <v>89642</v>
@@ -19538,7 +19538,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H661" t="n">
         <v>58784</v>
@@ -19567,7 +19567,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>2.23393607139587</v>
+        <v>2.23393630981445</v>
       </c>
       <c r="H662" t="n">
         <v>94242</v>
@@ -19596,7 +19596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H663" t="n">
         <v>128498</v>
@@ -19625,7 +19625,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G664" t="n">
-        <v>2.29933667182922</v>
+        <v>2.29933643341064</v>
       </c>
       <c r="H664" t="n">
         <v>149672</v>
@@ -19712,7 +19712,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H667" t="n">
         <v>147403</v>
@@ -19741,7 +19741,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G668" t="n">
-        <v>2.24426293373108</v>
+        <v>2.2442626953125</v>
       </c>
       <c r="H668" t="n">
         <v>79510</v>
@@ -19828,7 +19828,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H671" t="n">
         <v>122606</v>
@@ -19886,7 +19886,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G673" t="n">
-        <v>2.18574666976929</v>
+        <v>2.18574643135071</v>
       </c>
       <c r="H673" t="n">
         <v>87561</v>
@@ -19915,7 +19915,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H674" t="n">
         <v>127368</v>
@@ -20118,7 +20118,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H681" t="n">
         <v>90219</v>
@@ -20147,7 +20147,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G682" t="n">
-        <v>2.14788317680359</v>
+        <v>2.14788341522217</v>
       </c>
       <c r="H682" t="n">
         <v>38146</v>
@@ -20176,7 +20176,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G683" t="n">
-        <v>2.11690402030945</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H683" t="n">
         <v>89809</v>
@@ -20205,7 +20205,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G684" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H684" t="n">
         <v>106959</v>
@@ -20292,7 +20292,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11690402030945</v>
+        <v>2.11690425872803</v>
       </c>
       <c r="H687" t="n">
         <v>150304</v>
@@ -20408,7 +20408,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G691" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H691" t="n">
         <v>98598</v>
@@ -20437,7 +20437,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>2.13755702972412</v>
+        <v>2.1375572681427</v>
       </c>
       <c r="H692" t="n">
         <v>87021</v>
@@ -20495,7 +20495,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378835678101</v>
       </c>
       <c r="H694" t="n">
         <v>310317</v>
@@ -20553,7 +20553,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G696" t="n">
-        <v>2.10657811164856</v>
+        <v>2.10657787322998</v>
       </c>
       <c r="H696" t="n">
         <v>205834</v>
@@ -20582,7 +20582,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G697" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H697" t="n">
         <v>159262</v>
@@ -20611,7 +20611,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G698" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H698" t="n">
         <v>474404</v>
@@ -20640,7 +20640,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G699" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H699" t="n">
         <v>101472</v>
@@ -20669,7 +20669,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G700" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H700" t="n">
         <v>104775</v>
@@ -20727,7 +20727,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>2.11346220970154</v>
+        <v>2.11346197128296</v>
       </c>
       <c r="H702" t="n">
         <v>120044</v>
@@ -20756,7 +20756,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G703" t="n">
-        <v>2.05150413513184</v>
+        <v>2.05150389671326</v>
       </c>
       <c r="H703" t="n">
         <v>500439</v>
@@ -20785,7 +20785,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H704" t="n">
         <v>153586</v>
@@ -20814,7 +20814,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G705" t="n">
-        <v>2.08248329162598</v>
+        <v>2.0824830532074</v>
       </c>
       <c r="H705" t="n">
         <v>173224</v>
@@ -20843,7 +20843,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G706" t="n">
-        <v>2.05494594573975</v>
+        <v>2.05494618415833</v>
       </c>
       <c r="H706" t="n">
         <v>108391</v>
@@ -20901,7 +20901,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G708" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266172409058</v>
       </c>
       <c r="H708" t="n">
         <v>124414</v>
@@ -20930,7 +20930,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>1.99643015861511</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H709" t="n">
         <v>235805</v>
@@ -20959,7 +20959,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G710" t="n">
-        <v>1.95512461662292</v>
+        <v>1.95512437820435</v>
       </c>
       <c r="H710" t="n">
         <v>129165</v>
@@ -20988,7 +20988,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H711" t="n">
         <v>98948</v>
@@ -21017,7 +21017,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.94135594367981</v>
+        <v>1.9413560628891</v>
       </c>
       <c r="H712" t="n">
         <v>74593</v>
@@ -21046,7 +21046,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G713" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266172409058</v>
       </c>
       <c r="H713" t="n">
         <v>101638</v>
@@ -21075,7 +21075,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G714" t="n">
-        <v>1.98266184329987</v>
+        <v>1.98266172409058</v>
       </c>
       <c r="H714" t="n">
         <v>78349</v>
@@ -21104,7 +21104,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G715" t="n">
-        <v>1.95856666564941</v>
+        <v>1.95856690406799</v>
       </c>
       <c r="H715" t="n">
         <v>70649</v>
@@ -21133,7 +21133,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H716" t="n">
         <v>173384</v>
@@ -21162,7 +21162,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H717" t="n">
         <v>97454</v>
@@ -21249,7 +21249,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G720" t="n">
-        <v>1.9172614812851</v>
+        <v>1.91726124286652</v>
       </c>
       <c r="H720" t="n">
         <v>126796</v>
@@ -21307,7 +21307,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>1.92070317268372</v>
+        <v>1.92070341110229</v>
       </c>
       <c r="H722" t="n">
         <v>277130</v>
@@ -21336,7 +21336,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.90349292755127</v>
+        <v>1.90349268913269</v>
       </c>
       <c r="H723" t="n">
         <v>172278</v>
@@ -21394,7 +21394,7 @@
         <v>2.875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.97921919822693</v>
+        <v>1.97921931743622</v>
       </c>
       <c r="H725" t="n">
         <v>62710</v>
@@ -21423,7 +21423,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G726" t="n">
-        <v>1.99298799037933</v>
+        <v>1.99298810958862</v>
       </c>
       <c r="H726" t="n">
         <v>108169</v>
@@ -21452,7 +21452,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G727" t="n">
-        <v>1.98610377311707</v>
+        <v>1.98610365390778</v>
       </c>
       <c r="H727" t="n">
         <v>75372</v>
@@ -21539,7 +21539,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G730" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H730" t="n">
         <v>98831</v>
@@ -21626,7 +21626,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>2.04806208610535</v>
+        <v>2.04806160926819</v>
       </c>
       <c r="H733" t="n">
         <v>103940</v>
@@ -21655,7 +21655,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G734" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H734" t="n">
         <v>134624</v>
@@ -21713,7 +21713,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.0618302822113</v>
+        <v>2.06183052062988</v>
       </c>
       <c r="H736" t="n">
         <v>119731</v>
@@ -21771,7 +21771,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G738" t="n">
-        <v>1.96889293193817</v>
+        <v>1.96889269351959</v>
       </c>
       <c r="H738" t="n">
         <v>161205</v>
@@ -21800,7 +21800,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.95168256759644</v>
+        <v>1.95168268680573</v>
       </c>
       <c r="H739" t="n">
         <v>264586</v>
@@ -21974,7 +21974,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G745" t="n">
-        <v>2.21672582626343</v>
+        <v>2.21672606468201</v>
       </c>
       <c r="H745" t="n">
         <v>209439</v>
@@ -22003,7 +22003,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G746" t="n">
-        <v>2.23049449920654</v>
+        <v>2.23049426078796</v>
       </c>
       <c r="H746" t="n">
         <v>326895</v>
@@ -22032,7 +22032,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>2.21328377723694</v>
+        <v>2.21328353881836</v>
       </c>
       <c r="H747" t="n">
         <v>206720</v>
@@ -22119,7 +22119,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G750" t="n">
-        <v>2.18918919563293</v>
+        <v>2.18918895721436</v>
       </c>
       <c r="H750" t="n">
         <v>204318</v>
@@ -22148,7 +22148,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H751" t="n">
         <v>49394</v>
@@ -22235,7 +22235,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G754" t="n">
-        <v>2.16509413719177</v>
+        <v>2.16509389877319</v>
       </c>
       <c r="H754" t="n">
         <v>409359</v>
@@ -22293,7 +22293,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>2.12378859519958</v>
+        <v>2.12378835678101</v>
       </c>
       <c r="H756" t="n">
         <v>149343</v>
@@ -22351,7 +22351,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G758" t="n">
-        <v>2.17197847366333</v>
+        <v>2.17197823524475</v>
       </c>
       <c r="H758" t="n">
         <v>265608</v>
@@ -22380,7 +22380,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>2.29245233535767</v>
+        <v>2.29245257377625</v>
       </c>
       <c r="H759" t="n">
         <v>342700</v>
@@ -22409,7 +22409,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G760" t="n">
-        <v>2.28212594985962</v>
+        <v>2.2821261882782</v>
       </c>
       <c r="H760" t="n">
         <v>297330</v>
@@ -22438,7 +22438,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G761" t="n">
-        <v>2.33375811576843</v>
+        <v>2.33375763893127</v>
       </c>
       <c r="H761" t="n">
         <v>787607</v>
@@ -22467,7 +22467,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G762" t="n">
-        <v>2.34408402442932</v>
+        <v>2.34408450126648</v>
       </c>
       <c r="H762" t="n">
         <v>257956</v>
@@ -22583,7 +22583,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G766" t="n">
-        <v>2.41981101036072</v>
+        <v>2.41981077194214</v>
       </c>
       <c r="H766" t="n">
         <v>344369</v>
@@ -22699,7 +22699,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G770" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144293785095</v>
       </c>
       <c r="H770" t="n">
         <v>203705</v>
@@ -22728,7 +22728,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G771" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H771" t="n">
         <v>431119</v>
@@ -22757,7 +22757,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G772" t="n">
-        <v>2.44046378135681</v>
+        <v>2.44046354293823</v>
       </c>
       <c r="H772" t="n">
         <v>369438</v>
@@ -22786,7 +22786,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G773" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144293785095</v>
       </c>
       <c r="H773" t="n">
         <v>383952</v>
@@ -22815,7 +22815,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G774" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144293785095</v>
       </c>
       <c r="H774" t="n">
         <v>376439</v>
@@ -22844,7 +22844,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H775" t="n">
         <v>412613</v>
@@ -22902,7 +22902,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>2.53684282302856</v>
+        <v>2.53684306144714</v>
       </c>
       <c r="H777" t="n">
         <v>356598</v>
@@ -22931,7 +22931,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G778" t="n">
-        <v>2.46455836296082</v>
+        <v>2.46455860137939</v>
       </c>
       <c r="H778" t="n">
         <v>296450</v>
@@ -22960,7 +22960,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G779" t="n">
-        <v>2.50242185592651</v>
+        <v>2.50242161750793</v>
       </c>
       <c r="H779" t="n">
         <v>334437</v>
@@ -22989,7 +22989,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G780" t="n">
-        <v>2.52307462692261</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H780" t="n">
         <v>192769</v>
@@ -23018,7 +23018,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>2.52307462692261</v>
+        <v>2.52307438850403</v>
       </c>
       <c r="H781" t="n">
         <v>177735</v>
@@ -23076,7 +23076,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G783" t="n">
-        <v>2.56093788146973</v>
+        <v>2.56093764305115</v>
       </c>
       <c r="H783" t="n">
         <v>259927</v>
@@ -23134,7 +23134,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G785" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H785" t="n">
         <v>236542</v>
@@ -23192,7 +23192,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G787" t="n">
-        <v>2.67108607292175</v>
+        <v>2.67108583450317</v>
       </c>
       <c r="H787" t="n">
         <v>308241</v>
@@ -23279,7 +23279,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G790" t="n">
-        <v>2.61945390701294</v>
+        <v>2.61945414543152</v>
       </c>
       <c r="H790" t="n">
         <v>328656</v>
@@ -23366,7 +23366,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>2.60224318504333</v>
+        <v>2.60224342346191</v>
       </c>
       <c r="H793" t="n">
         <v>285918</v>
@@ -23424,7 +23424,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535884857178</v>
       </c>
       <c r="H795" t="n">
         <v>139076</v>
@@ -23482,7 +23482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>2.61601185798645</v>
+        <v>2.61601161956787</v>
       </c>
       <c r="H797" t="n">
         <v>367842</v>
@@ -23511,7 +23511,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G798" t="n">
-        <v>2.59880113601685</v>
+        <v>2.59880137443542</v>
       </c>
       <c r="H798" t="n">
         <v>105895</v>
@@ -23656,7 +23656,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G803" t="n">
-        <v>2.70206499099731</v>
+        <v>2.70206451416016</v>
       </c>
       <c r="H803" t="n">
         <v>263421</v>
@@ -23772,7 +23772,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G807" t="n">
-        <v>2.7123908996582</v>
+        <v>2.71239137649536</v>
       </c>
       <c r="H807" t="n">
         <v>271085</v>
@@ -23859,7 +23859,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G810" t="n">
-        <v>2.72960162162781</v>
+        <v>2.72960186004639</v>
       </c>
       <c r="H810" t="n">
         <v>150232</v>
@@ -23888,7 +23888,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G811" t="n">
-        <v>2.74681234359741</v>
+        <v>2.74681258201599</v>
       </c>
       <c r="H811" t="n">
         <v>215954</v>
@@ -23917,7 +23917,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G812" t="n">
-        <v>2.72960162162781</v>
+        <v>2.72960186004639</v>
       </c>
       <c r="H812" t="n">
         <v>131490</v>
@@ -23975,7 +23975,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G814" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H814" t="n">
         <v>151157</v>
@@ -24033,7 +24033,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G816" t="n">
-        <v>2.76058125495911</v>
+        <v>2.76058101654053</v>
       </c>
       <c r="H816" t="n">
         <v>220094</v>
@@ -24091,7 +24091,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>2.73304390907288</v>
+        <v>2.73304414749146</v>
       </c>
       <c r="H818" t="n">
         <v>216455</v>
@@ -24120,7 +24120,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G819" t="n">
-        <v>2.70550680160522</v>
+        <v>2.7055070400238</v>
       </c>
       <c r="H819" t="n">
         <v>173539</v>
@@ -24236,7 +24236,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>2.66420125961304</v>
+        <v>2.66420149803162</v>
       </c>
       <c r="H823" t="n">
         <v>229565</v>
@@ -24323,7 +24323,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G826" t="n">
-        <v>2.59535908699036</v>
+        <v>2.59535884857178</v>
       </c>
       <c r="H826" t="n">
         <v>159624</v>
@@ -24410,7 +24410,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G829" t="n">
-        <v>2.63322257995605</v>
+        <v>2.63322234153748</v>
       </c>
       <c r="H829" t="n">
         <v>67486</v>
@@ -24439,7 +24439,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>2.65387535095215</v>
+        <v>2.65387558937073</v>
       </c>
       <c r="H830" t="n">
         <v>99250</v>
@@ -24642,7 +24642,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>2.45423197746277</v>
+        <v>2.45423221588135</v>
       </c>
       <c r="H837" t="n">
         <v>108607</v>
@@ -24700,7 +24700,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>2.45079016685486</v>
+        <v>2.45078992843628</v>
       </c>
       <c r="H839" t="n">
         <v>177889</v>
@@ -24758,7 +24758,7 @@
         <v>3.53500008583069</v>
       </c>
       <c r="G841" t="n">
-        <v>2.43357968330383</v>
+        <v>2.43357920646667</v>
       </c>
       <c r="H841" t="n">
         <v>124221</v>
@@ -24787,7 +24787,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G842" t="n">
-        <v>2.41981101036072</v>
+        <v>2.41981077194214</v>
       </c>
       <c r="H842" t="n">
         <v>263155</v>
@@ -24845,7 +24845,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G844" t="n">
-        <v>2.47144269943237</v>
+        <v>2.47144293785095</v>
       </c>
       <c r="H844" t="n">
         <v>59749</v>
@@ -24874,7 +24874,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G845" t="n">
-        <v>2.50586414337158</v>
+        <v>2.505863904953</v>
       </c>
       <c r="H845" t="n">
         <v>222012</v>
@@ -24903,7 +24903,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G846" t="n">
-        <v>2.5265166759491</v>
+        <v>2.52651691436768</v>
       </c>
       <c r="H846" t="n">
         <v>296447</v>
@@ -24932,7 +24932,7 @@
         <v>3.625</v>
       </c>
       <c r="G847" t="n">
-        <v>2.49553751945496</v>
+        <v>2.49553728103638</v>
       </c>
       <c r="H847" t="n">
         <v>157082</v>
@@ -24990,7 +24990,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G849" t="n">
-        <v>2.43013715744019</v>
+        <v>2.43013739585876</v>
       </c>
       <c r="H849" t="n">
         <v>115219</v>
@@ -25135,7 +25135,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>2.18230438232422</v>
+        <v>2.18230485916138</v>
       </c>
       <c r="H854" t="n">
         <v>464853</v>
@@ -25251,7 +25251,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G858" t="n">
-        <v>2.07904100418091</v>
+        <v>2.07904076576233</v>
       </c>
       <c r="H858" t="n">
         <v>179861</v>
@@ -25280,7 +25280,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G859" t="n">
-        <v>2.07559895515442</v>
+        <v>2.07559871673584</v>
       </c>
       <c r="H859" t="n">
         <v>251246</v>
@@ -25338,7 +25338,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G861" t="n">
-        <v>2.04117774963379</v>
+        <v>2.04117727279663</v>
       </c>
       <c r="H861" t="n">
         <v>179312</v>
@@ -25367,7 +25367,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G862" t="n">
-        <v>1.99643015861511</v>
+        <v>1.9964302778244</v>
       </c>
       <c r="H862" t="n">
         <v>284968</v>
@@ -25425,7 +25425,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G864" t="n">
-        <v>2.06153130531311</v>
+        <v>2.06153106689453</v>
       </c>
       <c r="H864" t="n">
         <v>233373</v>
@@ -25454,7 +25454,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G865" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H865" t="n">
         <v>416439</v>
@@ -25512,7 +25512,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H867" t="n">
         <v>171746</v>
@@ -25541,7 +25541,7 @@
         <v>2.68499994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.94217920303345</v>
+        <v>1.94217932224274</v>
       </c>
       <c r="H868" t="n">
         <v>234747</v>
@@ -25599,7 +25599,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G870" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H870" t="n">
         <v>404038</v>
@@ -25686,7 +25686,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G873" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H873" t="n">
         <v>227376</v>
@@ -25715,7 +25715,7 @@
         <v>2.75</v>
       </c>
       <c r="G874" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H874" t="n">
         <v>251629</v>
@@ -25744,7 +25744,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G875" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H875" t="n">
         <v>184992</v>
@@ -25889,7 +25889,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G880" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H880" t="n">
         <v>284652</v>
@@ -25918,7 +25918,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G881" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H881" t="n">
         <v>276051</v>
@@ -25947,7 +25947,7 @@
         <v>2.75</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H882" t="n">
         <v>279659</v>
@@ -25976,7 +25976,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G883" t="n">
-        <v>1.9313291311264</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H883" t="n">
         <v>1099479</v>
@@ -26005,7 +26005,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601181983948</v>
       </c>
       <c r="H884" t="n">
         <v>286493</v>
@@ -26034,7 +26034,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G885" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H885" t="n">
         <v>94780</v>
@@ -26063,7 +26063,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G886" t="n">
-        <v>1.89154541492462</v>
+        <v>1.89154529571533</v>
       </c>
       <c r="H886" t="n">
         <v>286669</v>
@@ -26092,7 +26092,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G887" t="n">
-        <v>1.89154541492462</v>
+        <v>1.89154529571533</v>
       </c>
       <c r="H887" t="n">
         <v>146747</v>
@@ -26179,7 +26179,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.88069498538971</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H890" t="n">
         <v>170084</v>
@@ -26208,7 +26208,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G891" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601181983948</v>
       </c>
       <c r="H891" t="n">
         <v>279577</v>
@@ -26237,7 +26237,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.91324555873871</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H892" t="n">
         <v>470871</v>
@@ -26266,7 +26266,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G893" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H893" t="n">
         <v>291178</v>
@@ -26295,7 +26295,7 @@
         <v>2.625</v>
       </c>
       <c r="G894" t="n">
-        <v>1.89877879619598</v>
+        <v>1.89877843856812</v>
       </c>
       <c r="H894" t="n">
         <v>237876</v>
@@ -26353,7 +26353,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H896" t="n">
         <v>911289</v>
@@ -26382,7 +26382,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G897" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H897" t="n">
         <v>805951</v>
@@ -26440,7 +26440,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G899" t="n">
-        <v>2.0325973033905</v>
+        <v>2.03259754180908</v>
       </c>
       <c r="H899" t="n">
         <v>626504</v>
@@ -26469,7 +26469,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G900" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H900" t="n">
         <v>386888</v>
@@ -26498,7 +26498,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>1.97472977638245</v>
+        <v>1.97472965717316</v>
       </c>
       <c r="H901" t="n">
         <v>318897</v>
@@ -26527,7 +26527,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>1.9313291311264</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H902" t="n">
         <v>257125</v>
@@ -26585,7 +26585,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G904" t="n">
-        <v>1.83006083965302</v>
+        <v>1.83006107807159</v>
       </c>
       <c r="H904" t="n">
         <v>909668</v>
@@ -26614,7 +26614,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="n">
-        <v>1.88069498538971</v>
+        <v>1.880695104599</v>
       </c>
       <c r="H905" t="n">
         <v>562530</v>
@@ -26643,7 +26643,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G906" t="n">
-        <v>1.90239560604095</v>
+        <v>1.90239536762238</v>
       </c>
       <c r="H906" t="n">
         <v>234433</v>
@@ -26672,7 +26672,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.90601217746735</v>
+        <v>1.90601181983948</v>
       </c>
       <c r="H907" t="n">
         <v>228173</v>
@@ -26701,7 +26701,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91324555873871</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H908" t="n">
         <v>91411</v>
@@ -26730,7 +26730,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.86261117458344</v>
+        <v>1.86261165142059</v>
       </c>
       <c r="H909" t="n">
         <v>371388</v>
@@ -26759,7 +26759,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G910" t="n">
-        <v>1.79389369487762</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H910" t="n">
         <v>493642</v>
@@ -26817,7 +26817,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H912" t="n">
         <v>465653</v>
@@ -26846,7 +26846,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G913" t="n">
-        <v>1.80474364757538</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H913" t="n">
         <v>618635</v>
@@ -26875,7 +26875,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>1.79389369487762</v>
+        <v>1.79389357566833</v>
       </c>
       <c r="H914" t="n">
         <v>465588</v>
@@ -26933,7 +26933,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H916" t="n">
         <v>862579</v>
@@ -27020,7 +27020,7 @@
         <v>2.25</v>
       </c>
       <c r="G919" t="n">
-        <v>1.62752449512482</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H919" t="n">
         <v>393031</v>
@@ -27078,7 +27078,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.57327353954315</v>
+        <v>1.57327365875244</v>
       </c>
       <c r="H921" t="n">
         <v>763177</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.66369163990021</v>
+        <v>1.6636917591095</v>
       </c>
       <c r="H922" t="n">
         <v>294260</v>
@@ -27136,7 +27136,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H923" t="n">
         <v>378459</v>
@@ -27252,7 +27252,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G927" t="n">
-        <v>1.57689046859741</v>
+        <v>1.5768905878067</v>
       </c>
       <c r="H927" t="n">
         <v>526312</v>
@@ -27339,7 +27339,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G930" t="n">
-        <v>1.58412384986877</v>
+        <v>1.58412396907806</v>
       </c>
       <c r="H930" t="n">
         <v>987694</v>
@@ -27368,7 +27368,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G931" t="n">
-        <v>1.66007506847382</v>
+        <v>1.66007518768311</v>
       </c>
       <c r="H931" t="n">
         <v>679589</v>
@@ -27397,7 +27397,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>1.60944068431854</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H932" t="n">
         <v>532189</v>
@@ -27571,7 +27571,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G938" t="n">
-        <v>1.71070909500122</v>
+        <v>1.7107093334198</v>
       </c>
       <c r="H938" t="n">
         <v>298104</v>
@@ -27629,7 +27629,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G940" t="n">
-        <v>1.71070909500122</v>
+        <v>1.7107093334198</v>
       </c>
       <c r="H940" t="n">
         <v>372190</v>
@@ -27658,7 +27658,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G941" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H941" t="n">
         <v>345682</v>
@@ -27716,7 +27716,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G943" t="n">
-        <v>1.71070909500122</v>
+        <v>1.7107093334198</v>
       </c>
       <c r="H943" t="n">
         <v>343096</v>
@@ -27745,7 +27745,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H944" t="n">
         <v>336528</v>
@@ -27774,7 +27774,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G945" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H945" t="n">
         <v>255600</v>
@@ -27803,7 +27803,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G946" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H946" t="n">
         <v>241984</v>
@@ -27832,7 +27832,7 @@
         <v>2.25</v>
       </c>
       <c r="G947" t="n">
-        <v>1.62752449512482</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H947" t="n">
         <v>1680843</v>
@@ -27977,7 +27977,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>1.6456081867218</v>
+        <v>1.64560806751251</v>
       </c>
       <c r="H952" t="n">
         <v>114952</v>
@@ -28064,7 +28064,7 @@
         <v>2.25</v>
       </c>
       <c r="G955" t="n">
-        <v>1.62752449512482</v>
+        <v>1.62752461433411</v>
       </c>
       <c r="H955" t="n">
         <v>414852</v>
@@ -28093,7 +28093,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G956" t="n">
-        <v>1.63114130496979</v>
+        <v>1.63114142417908</v>
       </c>
       <c r="H956" t="n">
         <v>272469</v>
@@ -28180,7 +28180,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G959" t="n">
-        <v>1.63475787639618</v>
+        <v>1.63475811481476</v>
       </c>
       <c r="H959" t="n">
         <v>198189</v>
@@ -28209,7 +28209,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G960" t="n">
-        <v>1.60944068431854</v>
+        <v>1.60944080352783</v>
       </c>
       <c r="H960" t="n">
         <v>254516</v>
@@ -28238,7 +28238,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G961" t="n">
-        <v>1.63837468624115</v>
+        <v>1.63837480545044</v>
       </c>
       <c r="H961" t="n">
         <v>175327</v>
@@ -28267,7 +28267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G962" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H962" t="n">
         <v>546781</v>
@@ -28325,7 +28325,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H964" t="n">
         <v>258696</v>
@@ -28354,7 +28354,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H965" t="n">
         <v>412054</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H966" t="n">
         <v>445642</v>
@@ -28470,7 +28470,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G969" t="n">
-        <v>1.6962423324585</v>
+        <v>1.69624221324921</v>
       </c>
       <c r="H969" t="n">
         <v>150403</v>
@@ -28499,7 +28499,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H970" t="n">
         <v>116106</v>
@@ -28528,7 +28528,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G971" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H971" t="n">
         <v>185489</v>
@@ -28557,7 +28557,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G972" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H972" t="n">
         <v>278746</v>
@@ -28586,7 +28586,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G973" t="n">
-        <v>1.67815852165222</v>
+        <v>1.6781587600708</v>
       </c>
       <c r="H973" t="n">
         <v>190802</v>
@@ -28644,7 +28644,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G975" t="n">
-        <v>1.67092525959015</v>
+        <v>1.67092514038086</v>
       </c>
       <c r="H975" t="n">
         <v>145445</v>
@@ -28673,7 +28673,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G976" t="n">
-        <v>1.66730868816376</v>
+        <v>1.66730856895447</v>
       </c>
       <c r="H976" t="n">
         <v>145725</v>
@@ -28731,7 +28731,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G978" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H978" t="n">
         <v>456317</v>
@@ -28760,7 +28760,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G979" t="n">
-        <v>1.77942681312561</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H979" t="n">
         <v>1130319</v>
@@ -28789,7 +28789,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G980" t="n">
-        <v>1.79751026630402</v>
+        <v>1.79751038551331</v>
       </c>
       <c r="H980" t="n">
         <v>683548</v>
@@ -28818,7 +28818,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>1.75772655010223</v>
+        <v>1.75772666931152</v>
       </c>
       <c r="H981" t="n">
         <v>635657</v>
@@ -28876,7 +28876,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G983" t="n">
-        <v>1.74325966835022</v>
+        <v>1.74325954914093</v>
       </c>
       <c r="H983" t="n">
         <v>346060</v>
@@ -28905,7 +28905,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>1.77219331264496</v>
+        <v>1.77219355106354</v>
       </c>
       <c r="H984" t="n">
         <v>304114</v>
@@ -28934,7 +28934,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>1.76134312152863</v>
+        <v>1.76134324073792</v>
       </c>
       <c r="H985" t="n">
         <v>462415</v>
@@ -29021,7 +29021,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G988" t="n">
-        <v>1.70709228515625</v>
+        <v>1.70709240436554</v>
       </c>
       <c r="H988" t="n">
         <v>321015</v>
@@ -29079,7 +29079,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>1.71070909500122</v>
+        <v>1.7107093334198</v>
       </c>
       <c r="H990" t="n">
         <v>404717</v>
@@ -29137,7 +29137,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>1.77942681312561</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H992" t="n">
         <v>947214</v>
@@ -29166,7 +29166,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G993" t="n">
-        <v>1.78666019439697</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H993" t="n">
         <v>380638</v>
@@ -29195,7 +29195,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G994" t="n">
-        <v>1.78666019439697</v>
+        <v>1.78666043281555</v>
       </c>
       <c r="H994" t="n">
         <v>337289</v>
@@ -29224,7 +29224,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G995" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H995" t="n">
         <v>1295316</v>
@@ -29369,7 +29369,7 @@
         <v>2.75</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1000" t="n">
         <v>951588</v>
@@ -29398,7 +29398,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.98196339607239</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1001" t="n">
         <v>659632</v>
@@ -29427,7 +29427,7 @@
         <v>2.75</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1002" t="n">
         <v>591585</v>
@@ -29456,7 +29456,7 @@
         <v>2.75</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1003" t="n">
         <v>552967</v>
@@ -29485,7 +29485,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.06153130531311</v>
+        <v>2.06153106689453</v>
       </c>
       <c r="H1004" t="n">
         <v>981209</v>
@@ -29543,7 +29543,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.03621435165405</v>
+        <v>2.03621387481689</v>
       </c>
       <c r="H1006" t="n">
         <v>950508</v>
@@ -29601,7 +29601,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.04344773292542</v>
+        <v>2.04344749450684</v>
       </c>
       <c r="H1008" t="n">
         <v>410384</v>
@@ -29688,7 +29688,7 @@
         <v>2.75</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.98919677734375</v>
+        <v>1.98919665813446</v>
       </c>
       <c r="H1011" t="n">
         <v>341025</v>
@@ -29717,7 +29717,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.98196339607239</v>
+        <v>1.9819632768631</v>
       </c>
       <c r="H1012" t="n">
         <v>244318</v>
@@ -29746,7 +29746,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.99281358718872</v>
+        <v>1.9928138256073</v>
       </c>
       <c r="H1013" t="n">
         <v>183722</v>
@@ -29775,7 +29775,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.99643015861511</v>
+        <v>1.99643003940582</v>
       </c>
       <c r="H1014" t="n">
         <v>219712</v>
@@ -29804,7 +29804,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1015" t="n">
         <v>196502</v>
@@ -29862,7 +29862,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1017" t="n">
         <v>308613</v>
@@ -29891,7 +29891,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856263160706</v>
       </c>
       <c r="H1018" t="n">
         <v>371965</v>
@@ -29949,7 +29949,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.9313291311264</v>
+        <v>1.93132925033569</v>
       </c>
       <c r="H1020" t="n">
         <v>417414</v>
@@ -29978,7 +29978,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.95664620399475</v>
+        <v>1.95664584636688</v>
       </c>
       <c r="H1021" t="n">
         <v>243379</v>
@@ -30007,7 +30007,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856263160706</v>
       </c>
       <c r="H1022" t="n">
         <v>218394</v>
@@ -30036,7 +30036,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.91324555873871</v>
+        <v>1.913245677948</v>
       </c>
       <c r="H1023" t="n">
         <v>212691</v>
@@ -30065,7 +30065,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.87346148490906</v>
+        <v>1.87346172332764</v>
       </c>
       <c r="H1024" t="n">
         <v>368919</v>
@@ -30094,7 +30094,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.84814441204071</v>
+        <v>1.84814453125</v>
       </c>
       <c r="H1025" t="n">
         <v>225576</v>
@@ -30123,7 +30123,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H1026" t="n">
         <v>271070</v>
@@ -30152,7 +30152,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.93856251239777</v>
+        <v>1.93856263160706</v>
       </c>
       <c r="H1027" t="n">
         <v>619856</v>
@@ -30239,7 +30239,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96387958526611</v>
+        <v>1.96387946605682</v>
       </c>
       <c r="H1030" t="n">
         <v>334352</v>
@@ -30268,7 +30268,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.97111296653748</v>
+        <v>1.97111320495605</v>
       </c>
       <c r="H1031" t="n">
         <v>346362</v>
@@ -30326,7 +30326,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.86984491348267</v>
+        <v>1.86984503269196</v>
       </c>
       <c r="H1033" t="n">
         <v>665587</v>
@@ -30355,7 +30355,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.88431179523468</v>
+        <v>1.88431191444397</v>
       </c>
       <c r="H1034" t="n">
         <v>562475</v>
@@ -30384,7 +30384,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1035" t="n">
         <v>361531</v>
@@ -30413,7 +30413,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.80474364757538</v>
+        <v>1.80474376678467</v>
       </c>
       <c r="H1036" t="n">
         <v>595397</v>
@@ -30471,7 +30471,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.73964285850525</v>
+        <v>1.73964273929596</v>
       </c>
       <c r="H1038" t="n">
         <v>332631</v>
@@ -30500,7 +30500,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.77219331264496</v>
+        <v>1.77219355106354</v>
       </c>
       <c r="H1039" t="n">
         <v>337490</v>
@@ -30529,7 +30529,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.77580988407135</v>
+        <v>1.77581024169922</v>
       </c>
       <c r="H1040" t="n">
         <v>435901</v>
@@ -30587,7 +30587,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.77942681312561</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1042" t="n">
         <v>282267</v>
@@ -30616,7 +30616,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.7649599313736</v>
+        <v>1.76496005058289</v>
       </c>
       <c r="H1043" t="n">
         <v>116889</v>
@@ -30645,7 +30645,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.77942681312561</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1044" t="n">
         <v>331929</v>
@@ -30674,7 +30674,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1045" t="n">
         <v>215954</v>
@@ -30732,7 +30732,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.87707829475403</v>
+        <v>1.87707841396332</v>
       </c>
       <c r="H1047" t="n">
         <v>448193</v>
@@ -30761,7 +30761,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.81921076774597</v>
+        <v>1.81921088695526</v>
       </c>
       <c r="H1048" t="n">
         <v>428986</v>
@@ -30848,7 +30848,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.815593957901</v>
+        <v>1.81559407711029</v>
       </c>
       <c r="H1051" t="n">
         <v>301333</v>
@@ -30877,7 +30877,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.77942681312561</v>
+        <v>1.7794269323349</v>
       </c>
       <c r="H1052" t="n">
         <v>278255</v>
@@ -30906,7 +30906,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.69262528419495</v>
+        <v>1.69262552261353</v>
       </c>
       <c r="H1053" t="n">
         <v>578759</v>
@@ -31080,7 +31080,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.48285579681396</v>
+        <v>1.48285555839539</v>
       </c>
       <c r="H1059" t="n">
         <v>394349</v>
@@ -31283,7 +31283,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.01412856578827</v>
+        <v>1.01412868499756</v>
       </c>
       <c r="H1066" t="n">
         <v>500114</v>
@@ -31341,7 +31341,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00400173664093</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1068" t="n">
         <v>418504</v>
@@ -31370,7 +31370,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1069" t="n">
         <v>281501</v>
@@ -31515,7 +31515,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.23547196388245</v>
+        <v>1.23547208309174</v>
       </c>
       <c r="H1074" t="n">
         <v>727270</v>
@@ -31573,7 +31573,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.2586190700531</v>
+        <v>1.25861895084381</v>
       </c>
       <c r="H1076" t="n">
         <v>129270</v>
@@ -31631,7 +31631,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.1776043176651</v>
+        <v>1.17760455608368</v>
       </c>
       <c r="H1078" t="n">
         <v>204338</v>
@@ -31718,7 +31718,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.22968518733978</v>
+        <v>1.22968530654907</v>
       </c>
       <c r="H1081" t="n">
         <v>100009</v>
@@ -31747,7 +31747,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1082" t="n">
         <v>144468</v>
@@ -31834,7 +31834,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.2947860956192</v>
+        <v>1.29478621482849</v>
       </c>
       <c r="H1085" t="n">
         <v>332626</v>
@@ -31863,7 +31863,7 @@
         <v>1.75</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.26585233211517</v>
+        <v>1.26585245132446</v>
       </c>
       <c r="H1086" t="n">
         <v>355406</v>
@@ -31892,7 +31892,7 @@
         <v>1.75</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.26585233211517</v>
+        <v>1.26585245132446</v>
       </c>
       <c r="H1087" t="n">
         <v>214011</v>
@@ -32066,7 +32066,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1093" t="n">
         <v>222649</v>
@@ -32095,7 +32095,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.22100508213043</v>
+        <v>1.22100496292114</v>
       </c>
       <c r="H1094" t="n">
         <v>124832</v>
@@ -32153,7 +32153,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.20075142383575</v>
+        <v>1.20075154304504</v>
       </c>
       <c r="H1096" t="n">
         <v>153500</v>
@@ -32182,7 +32182,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1097" t="n">
         <v>97350</v>
@@ -32211,7 +32211,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.20798480510712</v>
+        <v>1.20798492431641</v>
       </c>
       <c r="H1098" t="n">
         <v>241005</v>
@@ -32240,7 +32240,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.19207119941711</v>
+        <v>1.1920713186264</v>
       </c>
       <c r="H1099" t="n">
         <v>188648</v>
@@ -32327,7 +32327,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1102" t="n">
         <v>88940</v>
@@ -32356,7 +32356,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.15590417385101</v>
+        <v>1.15590405464172</v>
       </c>
       <c r="H1103" t="n">
         <v>128118</v>
@@ -32385,7 +32385,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.15590417385101</v>
+        <v>1.15590405464172</v>
       </c>
       <c r="H1104" t="n">
         <v>105864</v>
@@ -32414,7 +32414,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.12407696247101</v>
+        <v>1.12407684326172</v>
       </c>
       <c r="H1105" t="n">
         <v>152349</v>
@@ -32472,7 +32472,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.05318927764893</v>
+        <v>1.05318915843964</v>
       </c>
       <c r="H1107" t="n">
         <v>149211</v>
@@ -32530,7 +32530,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1109" t="n">
         <v>171022</v>
@@ -32588,7 +32588,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978875160217</v>
       </c>
       <c r="H1111" t="n">
         <v>304217</v>
@@ -32617,7 +32617,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.982301473617554</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1112" t="n">
         <v>157009</v>
@@ -32646,7 +32646,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1113" t="n">
         <v>128951</v>
@@ -32675,7 +32675,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.992428243160248</v>
+        <v>0.992428302764893</v>
       </c>
       <c r="H1114" t="n">
         <v>168726</v>
@@ -32762,7 +32762,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186938285828</v>
       </c>
       <c r="H1117" t="n">
         <v>1781957</v>
@@ -32820,7 +32820,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1119" t="n">
         <v>276892</v>
@@ -32849,7 +32849,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1120" t="n">
         <v>352921</v>
@@ -32907,7 +32907,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.15011727809906</v>
+        <v>1.15011751651764</v>
       </c>
       <c r="H1122" t="n">
         <v>444295</v>
@@ -32994,7 +32994,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1125" t="n">
         <v>636837</v>
@@ -33197,7 +33197,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.12118339538574</v>
+        <v>1.12118351459503</v>
       </c>
       <c r="H1132" t="n">
         <v>360030</v>
@@ -33226,7 +33226,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1133" t="n">
         <v>140955</v>
@@ -33284,7 +33284,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.10382354259491</v>
+        <v>1.10382342338562</v>
       </c>
       <c r="H1135" t="n">
         <v>163559</v>
@@ -33313,7 +33313,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.125523686409</v>
+        <v>1.12552356719971</v>
       </c>
       <c r="H1136" t="n">
         <v>207095</v>
@@ -33371,7 +33371,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.10237658023834</v>
+        <v>1.10237669944763</v>
       </c>
       <c r="H1138" t="n">
         <v>192526</v>
@@ -33429,7 +33429,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.076336145401</v>
+        <v>1.07633626461029</v>
       </c>
       <c r="H1140" t="n">
         <v>134302</v>
@@ -33487,7 +33487,7 @@
         <v>1.46399998664856</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.05897605419159</v>
+        <v>1.0589759349823</v>
       </c>
       <c r="H1142" t="n">
         <v>271139</v>
@@ -33516,7 +33516,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1143" t="n">
         <v>651459</v>
@@ -33574,7 +33574,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.11395001411438</v>
+        <v>1.11395013332367</v>
       </c>
       <c r="H1145" t="n">
         <v>289061</v>
@@ -33603,7 +33603,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.08790969848633</v>
+        <v>1.08790957927704</v>
       </c>
       <c r="H1146" t="n">
         <v>227859</v>
@@ -33661,7 +33661,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.06476283073425</v>
+        <v>1.06476271152496</v>
       </c>
       <c r="H1148" t="n">
         <v>229091</v>
@@ -33719,7 +33719,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.0908031463623</v>
+        <v>1.09080302715302</v>
       </c>
       <c r="H1150" t="n">
         <v>125732</v>
@@ -33748,7 +33748,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.07054936885834</v>
+        <v>1.07054960727692</v>
       </c>
       <c r="H1151" t="n">
         <v>175817</v>
@@ -33835,7 +33835,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1154" t="n">
         <v>63350</v>
@@ -33893,7 +33893,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.08356964588165</v>
+        <v>1.08356976509094</v>
       </c>
       <c r="H1156" t="n">
         <v>244507</v>
@@ -33922,7 +33922,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.07488965988159</v>
+        <v>1.0748895406723</v>
       </c>
       <c r="H1157" t="n">
         <v>172984</v>
@@ -33951,7 +33951,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186938285828</v>
       </c>
       <c r="H1158" t="n">
         <v>208272</v>
@@ -34009,7 +34009,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.01846861839294</v>
+        <v>1.01846873760223</v>
       </c>
       <c r="H1160" t="n">
         <v>289771</v>
@@ -34067,7 +34067,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.990981698036194</v>
+        <v>0.990981638431549</v>
       </c>
       <c r="H1162" t="n">
         <v>183349</v>
@@ -34183,7 +34183,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.00400173664093</v>
+        <v>1.00400185585022</v>
       </c>
       <c r="H1166" t="n">
         <v>268517</v>
@@ -34299,7 +34299,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.995321810245514</v>
+        <v>0.99532163143158</v>
       </c>
       <c r="H1170" t="n">
         <v>284109</v>
@@ -34444,7 +34444,7 @@
         <v>1.3639999628067</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.986641585826874</v>
+        <v>0.986641526222229</v>
       </c>
       <c r="H1175" t="n">
         <v>123963</v>
@@ -34473,7 +34473,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.985194802284241</v>
+        <v>0.985194861888885</v>
       </c>
       <c r="H1176" t="n">
         <v>165512</v>
@@ -34531,7 +34531,7 @@
         <v>1.34399998188019</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.972174644470215</v>
+        <v>0.972174763679504</v>
       </c>
       <c r="H1178" t="n">
         <v>90569</v>
@@ -34560,7 +34560,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.966387927532196</v>
+        <v>0.966387867927551</v>
       </c>
       <c r="H1179" t="n">
         <v>235988</v>
@@ -34589,7 +34589,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.966387927532196</v>
+        <v>0.966387867927551</v>
       </c>
       <c r="H1180" t="n">
         <v>341818</v>
@@ -34618,7 +34618,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.966387927532196</v>
+        <v>0.966387867927551</v>
       </c>
       <c r="H1181" t="n">
         <v>515945</v>
@@ -34647,7 +34647,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.967834532260895</v>
+        <v>0.967834651470184</v>
       </c>
       <c r="H1182" t="n">
         <v>267761</v>
@@ -34676,7 +34676,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1183" t="n">
         <v>281167</v>
@@ -34705,7 +34705,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.962047874927521</v>
+        <v>0.962047934532166</v>
       </c>
       <c r="H1184" t="n">
         <v>241006</v>
@@ -34763,7 +34763,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.950474381446838</v>
+        <v>0.950474321842194</v>
       </c>
       <c r="H1186" t="n">
         <v>250204</v>
@@ -34821,7 +34821,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1188" t="n">
         <v>555967</v>
@@ -34850,7 +34850,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468766450882</v>
       </c>
       <c r="H1189" t="n">
         <v>485261</v>
@@ -34879,7 +34879,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.944687604904175</v>
+        <v>0.94468766450882</v>
       </c>
       <c r="H1190" t="n">
         <v>152429</v>
@@ -34908,7 +34908,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454044818878</v>
       </c>
       <c r="H1191" t="n">
         <v>312695</v>
@@ -34937,7 +34937,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.938900828361511</v>
+        <v>0.938900947570801</v>
       </c>
       <c r="H1192" t="n">
         <v>194055</v>
@@ -34966,7 +34966,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.930220663547516</v>
+        <v>0.930220723152161</v>
       </c>
       <c r="H1193" t="n">
         <v>285073</v>
@@ -34995,7 +34995,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.930220663547516</v>
+        <v>0.930220723152161</v>
       </c>
       <c r="H1194" t="n">
         <v>248063</v>
@@ -35024,7 +35024,7 @@
         <v>1.27400004863739</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.92154061794281</v>
+        <v>0.921540677547455</v>
       </c>
       <c r="H1195" t="n">
         <v>289851</v>
@@ -35082,7 +35082,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.896946847438812</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1197" t="n">
         <v>192408</v>
@@ -35111,7 +35111,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1198" t="n">
         <v>368604</v>
@@ -35140,7 +35140,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.886820077896118</v>
+        <v>0.886819958686829</v>
       </c>
       <c r="H1199" t="n">
         <v>2193562</v>
@@ -35198,7 +35198,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093953609467</v>
       </c>
       <c r="H1201" t="n">
         <v>504293</v>
@@ -35227,7 +35227,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.937454164028168</v>
+        <v>0.937454044818878</v>
       </c>
       <c r="H1202" t="n">
         <v>519628</v>
@@ -35285,7 +35285,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1204" t="n">
         <v>232364</v>
@@ -35314,7 +35314,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1205" t="n">
         <v>119791</v>
@@ -35343,7 +35343,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.889713406562805</v>
+        <v>0.88971346616745</v>
       </c>
       <c r="H1206" t="n">
         <v>196518</v>
@@ -35372,7 +35372,7 @@
         <v>1.27199995517731</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.920093774795532</v>
+        <v>0.920093953609467</v>
       </c>
       <c r="H1207" t="n">
         <v>363479</v>
@@ -35401,7 +35401,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413848400116</v>
       </c>
       <c r="H1208" t="n">
         <v>255998</v>
@@ -35430,7 +35430,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.911413669586182</v>
+        <v>0.911413848400116</v>
       </c>
       <c r="H1209" t="n">
         <v>107552</v>
@@ -35459,7 +35459,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.928773999214172</v>
+        <v>0.928774058818817</v>
       </c>
       <c r="H1210" t="n">
         <v>89660</v>
@@ -35488,7 +35488,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.960601150989532</v>
+        <v>0.960601031780243</v>
       </c>
       <c r="H1211" t="n">
         <v>668739</v>
@@ -35546,7 +35546,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.989534854888916</v>
+        <v>0.989534974098206</v>
       </c>
       <c r="H1213" t="n">
         <v>306233</v>
@@ -35575,7 +35575,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1214" t="n">
         <v>432837</v>
@@ -35604,7 +35604,7 @@
         <v>1.31599998474121</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.951921105384827</v>
+        <v>0.951921045780182</v>
       </c>
       <c r="H1215" t="n">
         <v>224463</v>
@@ -35662,7 +35662,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915753901004791</v>
+        <v>0.915753841400146</v>
       </c>
       <c r="H1217" t="n">
         <v>178785</v>
@@ -35691,7 +35691,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246584415436</v>
       </c>
       <c r="H1218" t="n">
         <v>276978</v>
@@ -35720,7 +35720,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1219" t="n">
         <v>154359</v>
@@ -35749,7 +35749,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1220" t="n">
         <v>238072</v>
@@ -35778,7 +35778,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013024330139</v>
       </c>
       <c r="H1221" t="n">
         <v>219329</v>
@@ -35807,7 +35807,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.840525925159454</v>
+        <v>0.840525984764099</v>
       </c>
       <c r="H1222" t="n">
         <v>361515</v>
@@ -35836,7 +35836,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.81737893819809</v>
+        <v>0.817379057407379</v>
       </c>
       <c r="H1223" t="n">
         <v>171062</v>
@@ -35923,7 +35923,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.828952550888062</v>
+        <v>0.828952491283417</v>
       </c>
       <c r="H1226" t="n">
         <v>322984</v>
@@ -35952,7 +35952,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.776871681213379</v>
+        <v>0.776871740818024</v>
       </c>
       <c r="H1227" t="n">
         <v>366061</v>
@@ -35981,7 +35981,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.746491253376007</v>
+        <v>0.746491193771362</v>
       </c>
       <c r="H1228" t="n">
         <v>469607</v>
@@ -36068,7 +36068,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.772531569004059</v>
+        <v>0.772531628608704</v>
       </c>
       <c r="H1231" t="n">
         <v>205732</v>
@@ -36097,7 +36097,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.781211853027344</v>
+        <v>0.781211793422699</v>
       </c>
       <c r="H1232" t="n">
         <v>238451</v>
@@ -36155,7 +36155,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.759511411190033</v>
+        <v>0.759511470794678</v>
       </c>
       <c r="H1234" t="n">
         <v>160813</v>
@@ -36242,7 +36242,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.839079260826111</v>
+        <v>0.8390793800354</v>
       </c>
       <c r="H1237" t="n">
         <v>399300</v>
@@ -36329,7 +36329,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520519733429</v>
       </c>
       <c r="H1240" t="n">
         <v>465758</v>
@@ -36358,7 +36358,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.896946847438812</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1241" t="n">
         <v>475088</v>
@@ -36387,7 +36387,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520519733429</v>
       </c>
       <c r="H1242" t="n">
         <v>529118</v>
@@ -36416,7 +36416,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.895500242710114</v>
+        <v>0.895500183105469</v>
       </c>
       <c r="H1243" t="n">
         <v>309302</v>
@@ -36474,7 +36474,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1245" t="n">
         <v>371270</v>
@@ -36503,7 +36503,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.914307057857513</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1246" t="n">
         <v>599351</v>
@@ -36532,7 +36532,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.914307057857513</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1247" t="n">
         <v>474055</v>
@@ -36561,7 +36561,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.909967064857483</v>
+        <v>0.909967124462128</v>
       </c>
       <c r="H1248" t="n">
         <v>283507</v>
@@ -36590,7 +36590,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.914307057857513</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1249" t="n">
         <v>208821</v>
@@ -36619,7 +36619,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.863673090934753</v>
+        <v>0.863673031330109</v>
       </c>
       <c r="H1250" t="n">
         <v>2118508</v>
@@ -36648,7 +36648,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.886820077896118</v>
+        <v>0.886819958686829</v>
       </c>
       <c r="H1251" t="n">
         <v>315281</v>
@@ -36677,7 +36677,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1252" t="n">
         <v>343874</v>
@@ -36706,7 +36706,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.895500242710114</v>
+        <v>0.895500183105469</v>
       </c>
       <c r="H1253" t="n">
         <v>276903</v>
@@ -36735,7 +36735,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.89405345916748</v>
+        <v>0.894053399562836</v>
       </c>
       <c r="H1254" t="n">
         <v>333750</v>
@@ -36793,7 +36793,7 @@
         <v>1.22599995136261</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.886820077896118</v>
+        <v>0.886819958686829</v>
       </c>
       <c r="H1256" t="n">
         <v>196304</v>
@@ -36822,7 +36822,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.889713406562805</v>
+        <v>0.88971346616745</v>
       </c>
       <c r="H1257" t="n">
         <v>276597</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.876693189144135</v>
+        <v>0.876693248748779</v>
       </c>
       <c r="H1258" t="n">
         <v>265557</v>
@@ -36880,7 +36880,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013024330139</v>
       </c>
       <c r="H1259" t="n">
         <v>258243</v>
@@ -36909,7 +36909,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013024330139</v>
       </c>
       <c r="H1260" t="n">
         <v>250978</v>
@@ -36938,7 +36938,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.865119755268097</v>
+        <v>0.865119695663452</v>
       </c>
       <c r="H1261" t="n">
         <v>73429</v>
@@ -36967,7 +36967,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.875246524810791</v>
+        <v>0.875246584415436</v>
       </c>
       <c r="H1262" t="n">
         <v>261444</v>
@@ -36996,7 +36996,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.882479965686798</v>
+        <v>0.882480025291443</v>
       </c>
       <c r="H1263" t="n">
         <v>171832</v>
@@ -37025,7 +37025,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.88537323474884</v>
+        <v>0.885373294353485</v>
       </c>
       <c r="H1264" t="n">
         <v>229764</v>
@@ -37054,7 +37054,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.86222630739212</v>
+        <v>0.862226366996765</v>
       </c>
       <c r="H1265" t="n">
         <v>389130</v>
@@ -37083,7 +37083,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1266" t="n">
         <v>174813</v>
@@ -37112,7 +37112,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.869459748268127</v>
+        <v>0.869459807872772</v>
       </c>
       <c r="H1267" t="n">
         <v>207362</v>
@@ -37141,7 +37141,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.896946847438812</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1268" t="n">
         <v>362696</v>
@@ -37170,7 +37170,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.908520460128784</v>
+        <v>0.908520519733429</v>
       </c>
       <c r="H1269" t="n">
         <v>264575</v>
@@ -37199,7 +37199,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.914307057857513</v>
+        <v>0.914307117462158</v>
       </c>
       <c r="H1270" t="n">
         <v>297896</v>
@@ -37228,7 +37228,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.896946847438812</v>
+        <v>0.896946787834167</v>
       </c>
       <c r="H1271" t="n">
         <v>357067</v>
@@ -37257,7 +37257,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.899840176105499</v>
+        <v>0.899840235710144</v>
       </c>
       <c r="H1272" t="n">
         <v>196824</v>
@@ -37315,7 +37315,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.902733743190765</v>
+        <v>0.902733623981476</v>
       </c>
       <c r="H1274" t="n">
         <v>125768</v>
@@ -37344,7 +37344,7 @@
         <v>1.23199999332428</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.891160070896149</v>
+        <v>0.891160130500793</v>
       </c>
       <c r="H1275" t="n">
         <v>199794</v>
@@ -37402,7 +37402,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.868013143539429</v>
+        <v>0.868013024330139</v>
       </c>
       <c r="H1277" t="n">
         <v>273169</v>
@@ -37460,7 +37460,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.860779643058777</v>
+        <v>0.860779702663422</v>
       </c>
       <c r="H1279" t="n">
         <v>178958</v>
@@ -37489,7 +37489,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.849206149578094</v>
+        <v>0.849206209182739</v>
       </c>
       <c r="H1280" t="n">
         <v>159959</v>
@@ -37518,7 +37518,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.839079260826111</v>
+        <v>0.8390793800354</v>
       </c>
       <c r="H1281" t="n">
         <v>188343</v>
@@ -37547,7 +37547,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.840525925159454</v>
+        <v>0.840525984764099</v>
       </c>
       <c r="H1282" t="n">
         <v>192827</v>
@@ -37692,7 +37692,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1287" t="n">
         <v>307350</v>
@@ -37721,7 +37721,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.844866156578064</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1288" t="n">
         <v>234994</v>
@@ -37750,7 +37750,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.853546142578125</v>
+        <v>0.85354620218277</v>
       </c>
       <c r="H1289" t="n">
         <v>211199</v>
@@ -37779,7 +37779,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.831845819950104</v>
+        <v>0.831845879554749</v>
       </c>
       <c r="H1290" t="n">
         <v>153639</v>
@@ -37808,7 +37808,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.844866156578064</v>
+        <v>0.844866096973419</v>
       </c>
       <c r="H1291" t="n">
         <v>84133</v>
@@ -37837,7 +37837,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.846312642097473</v>
+        <v>0.846312761306763</v>
       </c>
       <c r="H1292" t="n">
         <v>193484</v>
@@ -37866,7 +37866,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.865119755268097</v>
+        <v>0.865119695663452</v>
       </c>
       <c r="H1293" t="n">
         <v>395877</v>
@@ -38040,7 +38040,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.982301473617554</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1299" t="n">
         <v>514735</v>
@@ -38098,7 +38098,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.00978863239288</v>
+        <v>1.00978875160217</v>
       </c>
       <c r="H1301" t="n">
         <v>487433</v>
@@ -38127,7 +38127,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.982301473617554</v>
+        <v>0.982301592826843</v>
       </c>
       <c r="H1302" t="n">
         <v>468329</v>
@@ -38156,7 +38156,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.979408085346222</v>
+        <v>0.979408144950867</v>
       </c>
       <c r="H1303" t="n">
         <v>386487</v>
@@ -38185,7 +38185,7 @@
         <v>1.31400001049042</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.950474381446838</v>
+        <v>0.950474321842194</v>
       </c>
       <c r="H1304" t="n">
         <v>534039</v>
@@ -38214,7 +38214,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1305" t="n">
         <v>460160</v>
@@ -38243,7 +38243,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.06186926364899</v>
+        <v>1.06186938285828</v>
       </c>
       <c r="H1306" t="n">
         <v>1146881</v>
@@ -38272,7 +38272,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.05752921104431</v>
+        <v>1.0575293302536</v>
       </c>
       <c r="H1307" t="n">
         <v>670651</v>
@@ -38301,7 +38301,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.07778286933899</v>
+        <v>1.07778298854828</v>
       </c>
       <c r="H1308" t="n">
         <v>656005</v>
@@ -38417,7 +38417,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1312" t="n">
         <v>192416</v>
@@ -38446,7 +38446,7 @@
         <v>1.41199994087219</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.02136206626892</v>
+        <v>1.02136194705963</v>
       </c>
       <c r="H1313" t="n">
         <v>246366</v>
@@ -38504,7 +38504,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.983748197555542</v>
+        <v>0.983748137950897</v>
       </c>
       <c r="H1315" t="n">
         <v>436542</v>
@@ -38533,7 +38533,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.989534854888916</v>
+        <v>0.989534974098206</v>
       </c>
       <c r="H1316" t="n">
         <v>242430</v>
@@ -38562,7 +38562,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.0257021188736</v>
+        <v>1.02570199966431</v>
       </c>
       <c r="H1317" t="n">
         <v>330734</v>
@@ -38591,7 +38591,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.04884910583496</v>
+        <v>1.04884922504425</v>
       </c>
       <c r="H1318" t="n">
         <v>602483</v>
@@ -38823,7 +38823,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.19785797595978</v>
+        <v>1.19785809516907</v>
       </c>
       <c r="H1326" t="n">
         <v>1612557</v>
@@ -38852,7 +38852,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1327" t="n">
         <v>582330</v>
@@ -38881,7 +38881,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1328" t="n">
         <v>411680</v>
@@ -39026,7 +39026,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.13999056816101</v>
+        <v>1.1399906873703</v>
       </c>
       <c r="H1333" t="n">
         <v>498148</v>
@@ -39055,7 +39055,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.14433062076569</v>
+        <v>1.1443305015564</v>
       </c>
       <c r="H1334" t="n">
         <v>246192</v>
@@ -39113,7 +39113,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.18049788475037</v>
+        <v>1.18049776554108</v>
       </c>
       <c r="H1336" t="n">
         <v>648102</v>
@@ -39142,7 +39142,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.17037093639374</v>
+        <v>1.17037105560303</v>
       </c>
       <c r="H1337" t="n">
         <v>823456</v>
@@ -39171,7 +39171,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.16892433166504</v>
+        <v>1.16892445087433</v>
       </c>
       <c r="H1338" t="n">
         <v>336802</v>
@@ -39200,7 +39200,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.17905104160309</v>
+        <v>1.17905116081238</v>
       </c>
       <c r="H1339" t="n">
         <v>508534</v>
@@ -39316,7 +39316,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.17905104160309</v>
+        <v>1.17905116081238</v>
       </c>
       <c r="H1343" t="n">
         <v>476067</v>
@@ -39374,7 +39374,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.15156412124634</v>
+        <v>1.15156400203705</v>
       </c>
       <c r="H1345" t="n">
         <v>402831</v>
@@ -39403,7 +39403,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.26440584659576</v>
+        <v>1.26440560817719</v>
       </c>
       <c r="H1346" t="n">
         <v>1836829</v>
@@ -39519,7 +39519,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.2745326757431</v>
+        <v>1.27453243732452</v>
       </c>
       <c r="H1350" t="n">
         <v>314905</v>
@@ -39548,7 +39548,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.30057287216187</v>
+        <v>1.30057299137115</v>
       </c>
       <c r="H1351" t="n">
         <v>318670</v>
@@ -39635,7 +39635,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912638664246</v>
       </c>
       <c r="H1354" t="n">
         <v>744694</v>
@@ -39693,7 +39693,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.29912626743317</v>
+        <v>1.29912638664246</v>
       </c>
       <c r="H1356" t="n">
         <v>193651</v>
@@ -39722,7 +39722,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.30635964870453</v>
+        <v>1.30635976791382</v>
       </c>
       <c r="H1357" t="n">
         <v>181760</v>
@@ -39780,7 +39780,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1359" t="n">
         <v>1365631</v>
@@ -39809,7 +39809,7 @@
         <v>1.9539999961853</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.41341471672058</v>
+        <v>1.41341459751129</v>
       </c>
       <c r="H1360" t="n">
         <v>612054</v>
@@ -39896,7 +39896,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.47562217712402</v>
+        <v>1.47562229633331</v>
       </c>
       <c r="H1363" t="n">
         <v>690935</v>
@@ -39925,7 +39925,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.429328083992</v>
+        <v>1.42932820320129</v>
       </c>
       <c r="H1364" t="n">
         <v>2260128</v>
@@ -39954,7 +39954,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.40762782096863</v>
+        <v>1.40762794017792</v>
       </c>
       <c r="H1365" t="n">
         <v>1106457</v>
@@ -39983,7 +39983,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.39750099182129</v>
+        <v>1.39750111103058</v>
       </c>
       <c r="H1366" t="n">
         <v>375019</v>
@@ -40012,7 +40012,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.39894783496857</v>
+        <v>1.39894795417786</v>
       </c>
       <c r="H1367" t="n">
         <v>239547</v>
@@ -40041,7 +40041,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.38592755794525</v>
+        <v>1.38592767715454</v>
       </c>
       <c r="H1368" t="n">
         <v>221103</v>
@@ -40070,7 +40070,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1369" t="n">
         <v>249082</v>
@@ -40099,7 +40099,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.36524212360382</v>
+        <v>1.36524224281311</v>
       </c>
       <c r="H1370" t="n">
         <v>393822</v>
@@ -40302,7 +40302,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.38592755794525</v>
+        <v>1.38592767715454</v>
       </c>
       <c r="H1377" t="n">
         <v>224156</v>
@@ -40331,7 +40331,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1378" t="n">
         <v>217402</v>
@@ -40389,7 +40389,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.44502902030945</v>
+        <v>1.44502890110016</v>
       </c>
       <c r="H1380" t="n">
         <v>213603</v>
@@ -40418,7 +40418,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1381" t="n">
         <v>159305</v>
@@ -40447,7 +40447,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1382" t="n">
         <v>287514</v>
@@ -40476,7 +40476,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.45537161827087</v>
+        <v>1.45537173748016</v>
       </c>
       <c r="H1383" t="n">
         <v>131183</v>
@@ -40505,7 +40505,7 @@
         <v>1.97200000286102</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.45684933662415</v>
+        <v>1.45684921741486</v>
       </c>
       <c r="H1384" t="n">
         <v>91908</v>
@@ -40534,7 +40534,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.44650638103485</v>
+        <v>1.44650650024414</v>
       </c>
       <c r="H1385" t="n">
         <v>278517</v>
@@ -40592,7 +40592,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.41991102695465</v>
+        <v>1.41991090774536</v>
       </c>
       <c r="H1387" t="n">
         <v>150398</v>
@@ -40621,7 +40621,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.36671960353851</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1388" t="n">
         <v>291702</v>
@@ -40679,7 +40679,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.34160161018372</v>
+        <v>1.34160149097443</v>
       </c>
       <c r="H1390" t="n">
         <v>161663</v>
@@ -40708,7 +40708,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.30761814117432</v>
+        <v>1.30761826038361</v>
       </c>
       <c r="H1391" t="n">
         <v>345672</v>
@@ -40737,7 +40737,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.3327362537384</v>
+        <v>1.33273637294769</v>
       </c>
       <c r="H1392" t="n">
         <v>230681</v>
@@ -40766,7 +40766,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1393" t="n">
         <v>166696</v>
@@ -40795,7 +40795,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.29432034492493</v>
+        <v>1.29432046413422</v>
       </c>
       <c r="H1394" t="n">
         <v>728450</v>
@@ -40824,7 +40824,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.2618145942688</v>
+        <v>1.26181471347809</v>
       </c>
       <c r="H1395" t="n">
         <v>555187</v>
@@ -40940,7 +40940,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.2603372335434</v>
+        <v>1.26033711433411</v>
       </c>
       <c r="H1399" t="n">
         <v>195621</v>
@@ -40969,7 +40969,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.226353764534</v>
+        <v>1.22635388374329</v>
       </c>
       <c r="H1400" t="n">
         <v>215998</v>
@@ -41027,7 +41027,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.18646049499512</v>
+        <v>1.18646025657654</v>
       </c>
       <c r="H1402" t="n">
         <v>319571</v>
@@ -41114,7 +41114,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.21896612644196</v>
+        <v>1.21896600723267</v>
       </c>
       <c r="H1405" t="n">
         <v>286470</v>
@@ -41172,7 +41172,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.19384801387787</v>
+        <v>1.19384825229645</v>
       </c>
       <c r="H1407" t="n">
         <v>147880</v>
@@ -41259,7 +41259,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622426986694</v>
       </c>
       <c r="H1410" t="n">
         <v>139750</v>
@@ -41288,7 +41288,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.16725254058838</v>
+        <v>1.16725242137909</v>
       </c>
       <c r="H1411" t="n">
         <v>286124</v>
@@ -41346,7 +41346,7 @@
         <v>1.57799994945526</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.16577482223511</v>
+        <v>1.1657749414444</v>
       </c>
       <c r="H1413" t="n">
         <v>116151</v>
@@ -41404,7 +41404,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.14065682888031</v>
+        <v>1.1406569480896</v>
       </c>
       <c r="H1415" t="n">
         <v>566131</v>
@@ -41433,7 +41433,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.12588155269623</v>
+        <v>1.12588143348694</v>
       </c>
       <c r="H1416" t="n">
         <v>229887</v>
@@ -41462,7 +41462,7 @@
         <v>1.52400004863739</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.12588155269623</v>
+        <v>1.12588143348694</v>
       </c>
       <c r="H1417" t="n">
         <v>205128</v>
@@ -41491,7 +41491,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.13622415065765</v>
+        <v>1.13622426986694</v>
       </c>
       <c r="H1418" t="n">
         <v>323570</v>
@@ -41520,7 +41520,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.18350529670715</v>
+        <v>1.18350541591644</v>
       </c>
       <c r="H1419" t="n">
         <v>385901</v>
@@ -41549,7 +41549,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H1420" t="n">
         <v>399404</v>
@@ -41636,7 +41636,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.2603372335434</v>
+        <v>1.26033711433411</v>
       </c>
       <c r="H1423" t="n">
         <v>241029</v>
@@ -41665,7 +41665,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.2603372335434</v>
+        <v>1.26033711433411</v>
       </c>
       <c r="H1424" t="n">
         <v>260328</v>
@@ -41781,7 +41781,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.28397762775421</v>
+        <v>1.2839777469635</v>
       </c>
       <c r="H1428" t="n">
         <v>139450</v>
@@ -41810,7 +41810,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.2485169172287</v>
+        <v>1.24851679801941</v>
       </c>
       <c r="H1429" t="n">
         <v>265485</v>
@@ -41868,7 +41868,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.2618145942688</v>
+        <v>1.26181471347809</v>
       </c>
       <c r="H1431" t="n">
         <v>118584</v>
@@ -41984,7 +41984,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.32830357551575</v>
+        <v>1.32830381393433</v>
       </c>
       <c r="H1435" t="n">
         <v>261431</v>
@@ -42013,7 +42013,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.30614078044891</v>
+        <v>1.30614066123962</v>
       </c>
       <c r="H1436" t="n">
         <v>371377</v>
@@ -42100,7 +42100,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.41991102695465</v>
+        <v>1.41991090774536</v>
       </c>
       <c r="H1439" t="n">
         <v>194067</v>
@@ -42129,7 +42129,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.3918377161026</v>
+        <v>1.39183759689331</v>
       </c>
       <c r="H1440" t="n">
         <v>280527</v>
@@ -42216,7 +42216,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.36671960353851</v>
+        <v>1.3667197227478</v>
       </c>
       <c r="H1443" t="n">
         <v>203945</v>
@@ -42245,7 +42245,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.36524212360382</v>
+        <v>1.36524224281311</v>
       </c>
       <c r="H1444" t="n">
         <v>376924</v>
@@ -42274,7 +42274,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682633399963</v>
       </c>
       <c r="H1445" t="n">
         <v>537192</v>
@@ -42332,7 +42332,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.32830357551575</v>
+        <v>1.32830381393433</v>
       </c>
       <c r="H1447" t="n">
         <v>140764</v>
@@ -42535,7 +42535,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.24703919887543</v>
+        <v>1.24703931808472</v>
       </c>
       <c r="H1454" t="n">
         <v>311006</v>
@@ -42564,7 +42564,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.24112915992737</v>
+        <v>1.24112927913666</v>
       </c>
       <c r="H1455" t="n">
         <v>333161</v>
@@ -42651,7 +42651,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.28102266788483</v>
+        <v>1.28102254867554</v>
       </c>
       <c r="H1458" t="n">
         <v>335681</v>
@@ -42738,7 +42738,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.23669672012329</v>
+        <v>1.236696600914</v>
       </c>
       <c r="H1461" t="n">
         <v>302646</v>
@@ -42854,7 +42854,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.28397762775421</v>
+        <v>1.2839777469635</v>
       </c>
       <c r="H1465" t="n">
         <v>181638</v>
@@ -42912,7 +42912,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.2603372335434</v>
+        <v>1.26033711433411</v>
       </c>
       <c r="H1467" t="n">
         <v>124843</v>
@@ -42999,7 +42999,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.34160161018372</v>
+        <v>1.34160149097443</v>
       </c>
       <c r="H1470" t="n">
         <v>398939</v>
@@ -43028,7 +43028,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479291439056</v>
       </c>
       <c r="H1471" t="n">
         <v>1009740</v>
@@ -43057,7 +43057,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.41400074958801</v>
+        <v>1.4140008687973</v>
       </c>
       <c r="H1472" t="n">
         <v>435343</v>
@@ -43086,7 +43086,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1473" t="n">
         <v>224203</v>
@@ -43144,7 +43144,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.40218031406403</v>
+        <v>1.40218043327332</v>
       </c>
       <c r="H1475" t="n">
         <v>161915</v>
@@ -43231,7 +43231,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1478" t="n">
         <v>146750</v>
@@ -43405,7 +43405,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.38297247886658</v>
+        <v>1.38297235965729</v>
       </c>
       <c r="H1484" t="n">
         <v>183001</v>
@@ -43434,7 +43434,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558484077454</v>
       </c>
       <c r="H1485" t="n">
         <v>148734</v>
@@ -43608,7 +43608,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.52186071872711</v>
+        <v>1.52186059951782</v>
       </c>
       <c r="H1491" t="n">
         <v>963778</v>
@@ -43637,7 +43637,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.54771769046783</v>
+        <v>1.54771757125854</v>
       </c>
       <c r="H1492" t="n">
         <v>586422</v>
@@ -43666,7 +43666,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.5587991476059</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1493" t="n">
         <v>728617</v>
@@ -43724,7 +43724,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.5587991476059</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1495" t="n">
         <v>407217</v>
@@ -43753,7 +43753,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.53663599491119</v>
+        <v>1.53663611412048</v>
       </c>
       <c r="H1496" t="n">
         <v>505426</v>
@@ -43782,7 +43782,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.49231004714966</v>
+        <v>1.49230992794037</v>
       </c>
       <c r="H1497" t="n">
         <v>91048</v>
@@ -43811,7 +43811,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.44798398017883</v>
+        <v>1.44798409938812</v>
       </c>
       <c r="H1498" t="n">
         <v>355414</v>
@@ -43869,7 +43869,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1500" t="n">
         <v>271549</v>
@@ -43898,7 +43898,7 @@
         <v>1.9559999704361</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.44502902030945</v>
+        <v>1.44502890110016</v>
       </c>
       <c r="H1501" t="n">
         <v>177494</v>
@@ -44014,7 +44014,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.33716881275177</v>
+        <v>1.33716893196106</v>
       </c>
       <c r="H1505" t="n">
         <v>248601</v>
@@ -44101,7 +44101,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682633399963</v>
       </c>
       <c r="H1508" t="n">
         <v>153178</v>
@@ -44130,7 +44130,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.34160161018372</v>
+        <v>1.34160149097443</v>
       </c>
       <c r="H1509" t="n">
         <v>120342</v>
@@ -44159,7 +44159,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.3445565700531</v>
+        <v>1.34455668926239</v>
       </c>
       <c r="H1510" t="n">
         <v>116822</v>
@@ -44188,7 +44188,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1511" t="n">
         <v>138621</v>
@@ -44246,7 +44246,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.34898924827576</v>
+        <v>1.34898912906647</v>
       </c>
       <c r="H1513" t="n">
         <v>216613</v>
@@ -44275,7 +44275,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.32830357551575</v>
+        <v>1.32830381393433</v>
       </c>
       <c r="H1514" t="n">
         <v>106604</v>
@@ -44304,7 +44304,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682633399963</v>
       </c>
       <c r="H1515" t="n">
         <v>144985</v>
@@ -44333,7 +44333,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.34307897090912</v>
+        <v>1.34307909011841</v>
       </c>
       <c r="H1516" t="n">
         <v>156869</v>
@@ -44362,7 +44362,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.3445565700531</v>
+        <v>1.34455668926239</v>
       </c>
       <c r="H1517" t="n">
         <v>89004</v>
@@ -44507,7 +44507,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.45980417728424</v>
+        <v>1.45980429649353</v>
       </c>
       <c r="H1522" t="n">
         <v>604333</v>
@@ -44536,7 +44536,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1523" t="n">
         <v>205657</v>
@@ -44565,7 +44565,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.50339162349701</v>
+        <v>1.5033917427063</v>
       </c>
       <c r="H1524" t="n">
         <v>245135</v>
@@ -44594,7 +44594,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816689968109</v>
       </c>
       <c r="H1525" t="n">
         <v>301193</v>
@@ -44681,7 +44681,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1528" t="n">
         <v>66350</v>
@@ -44739,7 +44739,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1530" t="n">
         <v>116204</v>
@@ -44768,7 +44768,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.47605717182159</v>
+        <v>1.47605729103088</v>
       </c>
       <c r="H1531" t="n">
         <v>102916</v>
@@ -44826,7 +44826,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.51447308063507</v>
+        <v>1.51447296142578</v>
       </c>
       <c r="H1533" t="n">
         <v>132143</v>
@@ -44855,7 +44855,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.51816701889038</v>
+        <v>1.51816689968109</v>
       </c>
       <c r="H1534" t="n">
         <v>108707</v>
@@ -44913,7 +44913,7 @@
         <v>2.03500008583069</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.50339162349701</v>
+        <v>1.5033917427063</v>
       </c>
       <c r="H1536" t="n">
         <v>152395</v>
@@ -44942,7 +44942,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.54402375221252</v>
+        <v>1.54402363300323</v>
       </c>
       <c r="H1537" t="n">
         <v>294711</v>
@@ -44971,7 +44971,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1538" t="n">
         <v>195545</v>
@@ -45000,7 +45000,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.52186071872711</v>
+        <v>1.52186059951782</v>
       </c>
       <c r="H1539" t="n">
         <v>145076</v>
@@ -45029,7 +45029,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.4996976852417</v>
+        <v>1.49969780445099</v>
       </c>
       <c r="H1540" t="n">
         <v>72325</v>
@@ -45058,7 +45058,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.51447308063507</v>
+        <v>1.51447296142578</v>
       </c>
       <c r="H1541" t="n">
         <v>253545</v>
@@ -45087,7 +45087,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1542" t="n">
         <v>283203</v>
@@ -45116,7 +45116,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.41104567050934</v>
+        <v>1.41104555130005</v>
       </c>
       <c r="H1543" t="n">
         <v>303306</v>
@@ -45261,7 +45261,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.41400074958801</v>
+        <v>1.4140008687973</v>
       </c>
       <c r="H1548" t="n">
         <v>110404</v>
@@ -45319,7 +45319,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.39627027511597</v>
+        <v>1.39627039432526</v>
       </c>
       <c r="H1550" t="n">
         <v>195135</v>
@@ -45348,7 +45348,7 @@
         <v>1.88399994373322</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.3918377161026</v>
+        <v>1.39183759689331</v>
       </c>
       <c r="H1551" t="n">
         <v>99853</v>
@@ -45406,7 +45406,7 @@
         <v>1.88800001144409</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.39479279518127</v>
+        <v>1.39479291439056</v>
       </c>
       <c r="H1553" t="n">
         <v>222677</v>
@@ -45638,7 +45638,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.37558495998383</v>
+        <v>1.37558484077454</v>
       </c>
       <c r="H1561" t="n">
         <v>147702</v>
@@ -45667,7 +45667,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.34898924827576</v>
+        <v>1.34898912906647</v>
       </c>
       <c r="H1562" t="n">
         <v>264942</v>
@@ -45696,7 +45696,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.32978129386902</v>
+        <v>1.32978117465973</v>
       </c>
       <c r="H1563" t="n">
         <v>314147</v>
@@ -45725,7 +45725,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.33716881275177</v>
+        <v>1.33716893196106</v>
       </c>
       <c r="H1564" t="n">
         <v>219956</v>
@@ -45754,7 +45754,7 @@
         <v>1.72800004482269</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.27659010887146</v>
+        <v>1.27658998966217</v>
       </c>
       <c r="H1565" t="n">
         <v>563690</v>
@@ -45812,7 +45812,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.24112915992737</v>
+        <v>1.24112927913666</v>
       </c>
       <c r="H1567" t="n">
         <v>290390</v>
@@ -45870,7 +45870,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.21601116657257</v>
+        <v>1.21601104736328</v>
       </c>
       <c r="H1569" t="n">
         <v>186496</v>
@@ -46044,7 +46044,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.226353764534</v>
+        <v>1.22635388374329</v>
       </c>
       <c r="H1575" t="n">
         <v>95606</v>
@@ -46305,7 +46305,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.32682609558105</v>
+        <v>1.32682633399963</v>
       </c>
       <c r="H1584" t="n">
         <v>111356</v>
@@ -46392,7 +46392,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.51447308063507</v>
+        <v>1.51447296142578</v>
       </c>
       <c r="H1587" t="n">
         <v>2303043</v>
@@ -46421,7 +46421,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.54771769046783</v>
+        <v>1.54771757125854</v>
       </c>
       <c r="H1588" t="n">
         <v>1110225</v>
@@ -46508,7 +46508,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.63636958599091</v>
+        <v>1.6363697052002</v>
       </c>
       <c r="H1591" t="n">
         <v>519821</v>
@@ -46537,7 +46537,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1592" t="n">
         <v>488837</v>
@@ -46566,7 +46566,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.6548388004303</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1593" t="n">
         <v>358597</v>
@@ -46595,7 +46595,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.62159419059753</v>
+        <v>1.62159442901611</v>
       </c>
       <c r="H1594" t="n">
         <v>308615</v>
@@ -46624,7 +46624,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.62159419059753</v>
+        <v>1.62159442901611</v>
       </c>
       <c r="H1595" t="n">
         <v>268063</v>
@@ -46769,7 +46769,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.69916474819183</v>
+        <v>1.69916486740112</v>
       </c>
       <c r="H1600" t="n">
         <v>291517</v>
@@ -46827,7 +46827,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.72132778167725</v>
+        <v>1.72132802009583</v>
       </c>
       <c r="H1602" t="n">
         <v>313832</v>
@@ -46972,7 +46972,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.6954710483551</v>
+        <v>1.69547128677368</v>
       </c>
       <c r="H1607" t="n">
         <v>254784</v>
@@ -47001,7 +47001,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.65114486217499</v>
+        <v>1.65114498138428</v>
       </c>
       <c r="H1608" t="n">
         <v>219912</v>
@@ -47030,7 +47030,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.66592037677765</v>
+        <v>1.66592049598694</v>
       </c>
       <c r="H1609" t="n">
         <v>120344</v>
@@ -47059,7 +47059,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1610" t="n">
         <v>91769</v>
@@ -47088,7 +47088,7 @@
         <v>2.25</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.66222655773163</v>
+        <v>1.66222667694092</v>
       </c>
       <c r="H1611" t="n">
         <v>68045</v>
@@ -47117,7 +47117,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.64375722408295</v>
+        <v>1.64375734329224</v>
       </c>
       <c r="H1612" t="n">
         <v>180712</v>
@@ -47146,7 +47146,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.63636958599091</v>
+        <v>1.6363697052002</v>
       </c>
       <c r="H1613" t="n">
         <v>180456</v>
@@ -47175,7 +47175,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.60681879520416</v>
+        <v>1.60681891441345</v>
       </c>
       <c r="H1614" t="n">
         <v>227809</v>
@@ -47204,7 +47204,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.52924835681915</v>
+        <v>1.52924847602844</v>
       </c>
       <c r="H1615" t="n">
         <v>245261</v>
@@ -47233,7 +47233,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.5587991476059</v>
+        <v>1.55879902839661</v>
       </c>
       <c r="H1616" t="n">
         <v>147876</v>
@@ -47262,7 +47262,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.59573769569397</v>
+        <v>1.59573757648468</v>
       </c>
       <c r="H1617" t="n">
         <v>312009</v>
@@ -47291,7 +47291,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.61420655250549</v>
+        <v>1.61420679092407</v>
       </c>
       <c r="H1618" t="n">
         <v>173191</v>
@@ -47349,7 +47349,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.64006340503693</v>
+        <v>1.64006352424622</v>
       </c>
       <c r="H1620" t="n">
         <v>229999</v>
@@ -47378,7 +47378,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.6548388004303</v>
+        <v>1.65483891963959</v>
       </c>
       <c r="H1621" t="n">
         <v>179258</v>
@@ -47436,7 +47436,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.64745116233826</v>
+        <v>1.64745128154755</v>
       </c>
       <c r="H1623" t="n">
         <v>712219</v>
@@ -47465,7 +47465,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.66592037677765</v>
+        <v>1.66592049598694</v>
       </c>
       <c r="H1624" t="n">
         <v>652663</v>
@@ -47494,7 +47494,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.66592037677765</v>
+        <v>1.66592049598694</v>
       </c>
       <c r="H1625" t="n">
         <v>863616</v>
@@ -47523,7 +47523,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.61774921417236</v>
+        <v>1.61774933338165</v>
       </c>
       <c r="H1626" t="n">
         <v>295022</v>
@@ -47958,7 +47958,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1641" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1641" t="n">
         <v>199201</v>
@@ -48016,7 +48016,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1643" t="n">
         <v>247724</v>
@@ -48161,7 +48161,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.37448465824127</v>
+        <v>1.37448477745056</v>
       </c>
       <c r="H1648" t="n">
         <v>89430</v>
@@ -48190,7 +48190,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1649" t="n">
         <v>141025</v>
@@ -48248,7 +48248,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1651" t="n">
         <v>56456</v>
@@ -48277,7 +48277,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1652" t="n">
-        <v>1.37609028816223</v>
+        <v>1.37609040737152</v>
       </c>
       <c r="H1652" t="n">
         <v>83408</v>
@@ -48306,7 +48306,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.38411891460419</v>
+        <v>1.3841187953949</v>
       </c>
       <c r="H1653" t="n">
         <v>351494</v>
@@ -48364,7 +48364,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1655" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1655" t="n">
         <v>31246</v>
@@ -48451,7 +48451,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1658" t="n">
         <v>87013</v>
@@ -48538,7 +48538,7 @@
         <v>1.59200000762939</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.27814221382141</v>
+        <v>1.2781423330307</v>
       </c>
       <c r="H1661" t="n">
         <v>79903</v>
@@ -48625,7 +48625,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1664" t="n">
-        <v>1.42105007171631</v>
+        <v>1.4210501909256</v>
       </c>
       <c r="H1664" t="n">
         <v>842299</v>
@@ -48683,7 +48683,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.48688399791718</v>
+        <v>1.48688411712646</v>
       </c>
       <c r="H1666" t="n">
         <v>370783</v>
@@ -48741,7 +48741,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.43871295452118</v>
+        <v>1.43871283531189</v>
       </c>
       <c r="H1668" t="n">
         <v>426769</v>
@@ -48799,7 +48799,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.43871295452118</v>
+        <v>1.43871283531189</v>
       </c>
       <c r="H1670" t="n">
         <v>160424</v>
@@ -48886,7 +48886,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1673" t="n">
         <v>316953</v>
@@ -48915,7 +48915,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.49170136451721</v>
+        <v>1.49170124530792</v>
       </c>
       <c r="H1674" t="n">
         <v>418301</v>
@@ -48944,7 +48944,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.47082710266113</v>
+        <v>1.47082698345184</v>
       </c>
       <c r="H1675" t="n">
         <v>352968</v>
@@ -49089,7 +49089,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.40820443630219</v>
+        <v>1.40820455551147</v>
       </c>
       <c r="H1680" t="n">
         <v>95443</v>
@@ -49147,7 +49147,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1682" t="n">
         <v>66535</v>
@@ -49176,7 +49176,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.38893616199493</v>
+        <v>1.38893604278564</v>
       </c>
       <c r="H1683" t="n">
         <v>260032</v>
@@ -49263,7 +49263,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.3664562702179</v>
+        <v>1.36645615100861</v>
       </c>
       <c r="H1686" t="n">
         <v>210620</v>
@@ -49321,7 +49321,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.35200476646423</v>
+        <v>1.35200488567352</v>
       </c>
       <c r="H1688" t="n">
         <v>122057</v>
@@ -49408,7 +49408,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.34558188915253</v>
+        <v>1.34558200836182</v>
       </c>
       <c r="H1691" t="n">
         <v>192296</v>
@@ -49466,7 +49466,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.29419934749603</v>
+        <v>1.29419922828674</v>
       </c>
       <c r="H1693" t="n">
         <v>143170</v>
@@ -49524,7 +49524,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1695" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1695" t="n">
         <v>180799</v>
@@ -49727,7 +49727,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.23639380931854</v>
+        <v>1.23639392852783</v>
       </c>
       <c r="H1702" t="n">
         <v>357526</v>
@@ -49756,7 +49756,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.23639380931854</v>
+        <v>1.23639392852783</v>
       </c>
       <c r="H1703" t="n">
         <v>194246</v>
@@ -49785,7 +49785,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.28295946121216</v>
+        <v>1.28295934200287</v>
       </c>
       <c r="H1704" t="n">
         <v>252692</v>
@@ -49843,7 +49843,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.23960542678833</v>
+        <v>1.23960530757904</v>
       </c>
       <c r="H1706" t="n">
         <v>395480</v>
@@ -49872,7 +49872,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1707" t="n">
         <v>328393</v>
@@ -50046,7 +50046,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.13844585418701</v>
+        <v>1.13844573497772</v>
       </c>
       <c r="H1713" t="n">
         <v>189407</v>
@@ -50162,7 +50162,7 @@
         <v>1.37600004673004</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.1047260761261</v>
+        <v>1.10472595691681</v>
       </c>
       <c r="H1717" t="n">
         <v>265221</v>
@@ -50365,7 +50365,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1724" t="n">
         <v>195897</v>
@@ -50394,7 +50394,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.20267403125763</v>
+        <v>1.20267415046692</v>
       </c>
       <c r="H1725" t="n">
         <v>200716</v>
@@ -50481,7 +50481,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1728" t="n">
         <v>106830</v>
@@ -50539,7 +50539,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.22515392303467</v>
+        <v>1.22515404224396</v>
       </c>
       <c r="H1730" t="n">
         <v>107088</v>
@@ -50568,7 +50568,7 @@
         <v>1.57200002670288</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.26208531856537</v>
+        <v>1.26208519935608</v>
       </c>
       <c r="H1731" t="n">
         <v>225301</v>
@@ -50597,7 +50597,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.29741072654724</v>
+        <v>1.29741084575653</v>
       </c>
       <c r="H1732" t="n">
         <v>220981</v>
@@ -50626,7 +50626,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1733" t="n">
         <v>162741</v>
@@ -50655,7 +50655,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1734" t="n">
         <v>122962</v>
@@ -50684,7 +50684,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.33273613452911</v>
+        <v>1.33273637294769</v>
       </c>
       <c r="H1735" t="n">
         <v>209163</v>
@@ -50771,7 +50771,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1738" t="n">
         <v>72837</v>
@@ -50800,7 +50800,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.31989061832428</v>
+        <v>1.31989073753357</v>
       </c>
       <c r="H1739" t="n">
         <v>139276</v>
@@ -50829,7 +50829,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.30383348464966</v>
+        <v>1.30383360385895</v>
       </c>
       <c r="H1740" t="n">
         <v>63847</v>
@@ -50858,7 +50858,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1741" t="n">
         <v>362136</v>
@@ -50887,7 +50887,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.30222773551941</v>
+        <v>1.3022278547287</v>
       </c>
       <c r="H1742" t="n">
         <v>126434</v>
@@ -51061,7 +51061,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.34879338741302</v>
+        <v>1.34879326820374</v>
       </c>
       <c r="H1748" t="n">
         <v>394461</v>
@@ -51119,7 +51119,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.28938221931458</v>
+        <v>1.28938210010529</v>
       </c>
       <c r="H1750" t="n">
         <v>292273</v>
@@ -51177,7 +51177,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.23478829860687</v>
+        <v>1.23478817939758</v>
       </c>
       <c r="H1752" t="n">
         <v>120642</v>
@@ -51235,7 +51235,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1754" t="n">
         <v>268250</v>
@@ -51293,7 +51293,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1756" t="n">
         <v>58942</v>
@@ -51380,7 +51380,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1759" t="n">
         <v>207138</v>
@@ -51467,7 +51467,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1762" t="n">
         <v>195165</v>
@@ -51496,7 +51496,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.25726819038391</v>
+        <v>1.25726807117462</v>
       </c>
       <c r="H1763" t="n">
         <v>180397</v>
@@ -51583,7 +51583,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1766" t="n">
         <v>177051</v>
@@ -51641,7 +51641,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1768" t="n">
-        <v>1.21391403675079</v>
+        <v>1.2139139175415</v>
       </c>
       <c r="H1768" t="n">
         <v>44622</v>
@@ -51670,7 +51670,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1769" t="n">
         <v>310689</v>
@@ -51728,7 +51728,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1771" t="n">
         <v>224093</v>
@@ -51815,7 +51815,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1774" t="n">
         <v>131817</v>
@@ -51844,7 +51844,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G1775" t="n">
-        <v>1.18180000782013</v>
+        <v>1.18179988861084</v>
       </c>
       <c r="H1775" t="n">
         <v>99387</v>
@@ -51960,7 +51960,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.18661713600159</v>
+        <v>1.1866170167923</v>
       </c>
       <c r="H1779" t="n">
         <v>103412</v>
@@ -51989,7 +51989,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1780" t="n">
-        <v>1.18340563774109</v>
+        <v>1.1834055185318</v>
       </c>
       <c r="H1780" t="n">
         <v>171787</v>
@@ -52018,7 +52018,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.20749115943909</v>
+        <v>1.2074910402298</v>
       </c>
       <c r="H1781" t="n">
         <v>224232</v>
@@ -52105,7 +52105,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.21873104572296</v>
+        <v>1.21873116493225</v>
       </c>
       <c r="H1784" t="n">
         <v>259226</v>
@@ -52134,7 +52134,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.23639380931854</v>
+        <v>1.23639392852783</v>
       </c>
       <c r="H1785" t="n">
         <v>173675</v>
@@ -52163,7 +52163,7 @@
         <v>1.51600003242493</v>
       </c>
       <c r="G1786" t="n">
-        <v>1.21712553501129</v>
+        <v>1.217125415802</v>
       </c>
       <c r="H1786" t="n">
         <v>102156</v>
@@ -52250,7 +52250,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.23639380931854</v>
+        <v>1.23639392852783</v>
       </c>
       <c r="H1789" t="n">
         <v>132643</v>
@@ -52308,7 +52308,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.24281668663025</v>
+        <v>1.24281680583954</v>
       </c>
       <c r="H1791" t="n">
         <v>163525</v>
@@ -52337,7 +52337,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.23639380931854</v>
+        <v>1.23639392852783</v>
       </c>
       <c r="H1792" t="n">
         <v>118527</v>
@@ -52366,7 +52366,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1793" t="n">
-        <v>1.24281668663025</v>
+        <v>1.24281680583954</v>
       </c>
       <c r="H1793" t="n">
         <v>186386</v>
@@ -52424,7 +52424,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.24923944473267</v>
+        <v>1.24923956394196</v>
       </c>
       <c r="H1795" t="n">
         <v>224358</v>
@@ -52453,7 +52453,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.247633934021</v>
+        <v>1.24763381481171</v>
       </c>
       <c r="H1796" t="n">
         <v>158009</v>
@@ -52482,7 +52482,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.23960542678833</v>
+        <v>1.23960530757904</v>
       </c>
       <c r="H1797" t="n">
         <v>155780</v>
@@ -52743,7 +52743,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1806" t="n">
         <v>302074</v>
@@ -52801,7 +52801,7 @@
         <v>1.75</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.40499305725098</v>
+        <v>1.40499293804169</v>
       </c>
       <c r="H1808" t="n">
         <v>628014</v>
@@ -52859,7 +52859,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.42586731910706</v>
+        <v>1.42586719989777</v>
       </c>
       <c r="H1810" t="n">
         <v>259535</v>
@@ -52888,7 +52888,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1811" t="n">
-        <v>1.44995296001434</v>
+        <v>1.44995284080505</v>
       </c>
       <c r="H1811" t="n">
         <v>238771</v>
@@ -53004,7 +53004,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1815" t="n">
-        <v>1.42907857894897</v>
+        <v>1.42907869815826</v>
       </c>
       <c r="H1815" t="n">
         <v>261500</v>
@@ -53120,7 +53120,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.38411891460419</v>
+        <v>1.3841187953949</v>
       </c>
       <c r="H1819" t="n">
         <v>180097</v>
@@ -53149,7 +53149,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.37127327919006</v>
+        <v>1.37127315998077</v>
       </c>
       <c r="H1820" t="n">
         <v>185044</v>
@@ -53207,7 +53207,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1822" t="n">
-        <v>1.34879338741302</v>
+        <v>1.34879326820374</v>
       </c>
       <c r="H1822" t="n">
         <v>112098</v>
@@ -53236,7 +53236,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.40981018543243</v>
+        <v>1.40981030464172</v>
       </c>
       <c r="H1823" t="n">
         <v>229481</v>
@@ -53323,7 +53323,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1826" t="n">
         <v>66052</v>
@@ -53410,7 +53410,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.37930178642273</v>
+        <v>1.37930190563202</v>
       </c>
       <c r="H1829" t="n">
         <v>144448</v>
@@ -53439,7 +53439,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1830" t="n">
         <v>142891</v>
@@ -53468,7 +53468,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.39054179191589</v>
+        <v>1.3905416727066</v>
       </c>
       <c r="H1831" t="n">
         <v>169426</v>
@@ -53497,7 +53497,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.36163902282715</v>
+        <v>1.36163890361786</v>
       </c>
       <c r="H1832" t="n">
         <v>160687</v>
@@ -53526,7 +53526,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.32310211658478</v>
+        <v>1.32310199737549</v>
       </c>
       <c r="H1833" t="n">
         <v>313479</v>
@@ -53555,7 +53555,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.33594787120819</v>
+        <v>1.3359477519989</v>
       </c>
       <c r="H1834" t="n">
         <v>89373</v>
@@ -53584,7 +53584,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1835" t="n">
         <v>126203</v>
@@ -53642,7 +53642,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.29901647567749</v>
+        <v>1.29901659488678</v>
       </c>
       <c r="H1837" t="n">
         <v>137726</v>
@@ -53758,7 +53758,7 @@
         <v>1.78600001335144</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.43389570713043</v>
+        <v>1.43389582633972</v>
       </c>
       <c r="H1841" t="n">
         <v>519268</v>
@@ -53845,7 +53845,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1844" t="n">
-        <v>1.42907857894897</v>
+        <v>1.42907869815826</v>
       </c>
       <c r="H1844" t="n">
         <v>214215</v>
@@ -53903,7 +53903,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.48206686973572</v>
+        <v>1.48206698894501</v>
       </c>
       <c r="H1846" t="n">
         <v>230147</v>
@@ -54135,7 +54135,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1854" t="n">
-        <v>1.53344964981079</v>
+        <v>1.5334495306015</v>
       </c>
       <c r="H1854" t="n">
         <v>220217</v>
@@ -54164,7 +54164,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1855" t="n">
-        <v>1.51418113708496</v>
+        <v>1.51418101787567</v>
       </c>
       <c r="H1855" t="n">
         <v>165782</v>
@@ -54193,7 +54193,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1856" t="n">
         <v>136076</v>
@@ -54222,7 +54222,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1857" t="n">
-        <v>1.52220964431763</v>
+        <v>1.52220976352692</v>
       </c>
       <c r="H1857" t="n">
         <v>84316</v>
@@ -54251,7 +54251,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1858" t="n">
         <v>58868</v>
@@ -54309,7 +54309,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.50294125080109</v>
+        <v>1.5029411315918</v>
       </c>
       <c r="H1860" t="n">
         <v>288447</v>
@@ -54425,7 +54425,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.44995296001434</v>
+        <v>1.44995284080505</v>
       </c>
       <c r="H1864" t="n">
         <v>80968</v>
@@ -54628,7 +54628,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1871" t="n">
         <v>152966</v>
@@ -54657,7 +54657,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.51739251613617</v>
+        <v>1.51739263534546</v>
       </c>
       <c r="H1872" t="n">
         <v>111449</v>
@@ -54860,7 +54860,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.46279847621918</v>
+        <v>1.46279859542847</v>
       </c>
       <c r="H1879" t="n">
         <v>148220</v>
@@ -54918,7 +54918,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.49330699443817</v>
+        <v>1.49330687522888</v>
       </c>
       <c r="H1881" t="n">
         <v>411337</v>
@@ -80209,9 +80209,38 @@
         <v>2.05999994277954</v>
       </c>
       <c r="H2753" t="n">
-        <v>57695</v>
+        <v>58153</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>2.03500008583069</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>113671</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
